--- a/Shahidi_Assemblage_Model.xlsx
+++ b/Shahidi_Assemblage_Model.xlsx
@@ -1888,7 +1888,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="B48" s="12" t="inlineStr">
         <is>
-          <t>the Bayview land); treat Publix as a long-dated, land-value option (not a current seller). The blended in-place income covers the</t>
+          <t>the Bayview land); structure Publix as a SALE-LEASEBACK — acquire the fee and lease it back during entitlement. The blended in-place income covers the</t>
         </is>
       </c>
       <c r="C48" s="13" t="n"/>
@@ -2423,7 +2423,7 @@
         </is>
       </c>
       <c r="C19" s="18">
-        <f>'Assumptions'!C107</f>
+        <f>'Assumptions'!C111</f>
         <v/>
       </c>
       <c r="D19" s="22" t="inlineStr">
@@ -2448,7 +2448,7 @@
         </is>
       </c>
       <c r="C20" s="26">
-        <f>'Assumptions'!C108</f>
+        <f>'Assumptions'!C112</f>
         <v/>
       </c>
       <c r="D20" s="22" t="inlineStr">
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="C21" s="26">
-        <f>'Assumptions'!C109</f>
+        <f>'Assumptions'!C113</f>
         <v/>
       </c>
       <c r="D21" s="22" t="inlineStr">
@@ -2498,7 +2498,7 @@
         </is>
       </c>
       <c r="C22" s="18">
-        <f>'Assumptions'!C110</f>
+        <f>'Assumptions'!C114</f>
         <v/>
       </c>
       <c r="D22" s="22" t="inlineStr">
@@ -2547,7 +2547,7 @@
         </is>
       </c>
       <c r="C24" s="23">
-        <f>'Assumptions'!C106</f>
+        <f>'Assumptions'!C110</f>
         <v/>
       </c>
       <c r="D24" s="22" t="inlineStr">
@@ -2644,7 +2644,7 @@
         </is>
       </c>
       <c r="C28" s="18">
-        <f>'Assumptions'!C111</f>
+        <f>'Assumptions'!C115</f>
         <v/>
       </c>
       <c r="D28" s="22" t="inlineStr">
@@ -2669,7 +2669,7 @@
         </is>
       </c>
       <c r="C29" s="24">
-        <f>'Assumptions'!C112</f>
+        <f>'Assumptions'!C116</f>
         <v/>
       </c>
       <c r="D29" s="22" t="inlineStr">
@@ -3793,7 +3793,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M66"/>
+  <dimension ref="A1:M67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.5" customWidth="1" min="1" max="1"/>
@@ -4148,7 +4148,7 @@
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
-          <t>Summed control cost (each parcel at the greater of income or land value; Publix at its land basis, as it is not a seller) plus a 15/20/25% assemblage premium.</t>
+          <t>Summed control cost (each parcel at the greater of income or land value; Publix via sale-leaseback at its fee price) plus a 15/20/25% assemblage premium.</t>
         </is>
       </c>
       <c r="E20" s="13" t="n"/>
@@ -4161,15 +4161,15 @@
       <c r="L20" s="13" t="n"/>
       <c r="M20" s="14" t="n"/>
     </row>
-    <row r="21" ht="15" customHeight="1">
+    <row r="21" ht="27" customHeight="1">
       <c r="B21" s="52" t="inlineStr">
         <is>
-          <t>Reversion</t>
+          <t>Publix sale-leaseback</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
-          <t>Each asset sells in the hold year at its forward NOI ÷ exit cap, net of cost of sale; the consolidated reversion sums the asset-level reversions.</t>
+          <t>Acquire the Publix fee; Publix leases back and pays NNN rent during entitlement (rent covers the operating carry), then vacates for redevelopment. Leaseback rent, SF, price, and term are on the Assumptions tab.</t>
         </is>
       </c>
       <c r="E21" s="13" t="n"/>
@@ -4185,12 +4185,12 @@
     <row r="22" ht="15" customHeight="1">
       <c r="B22" s="52" t="inlineStr">
         <is>
-          <t>Redevelopment</t>
+          <t>Reversion</t>
         </is>
       </c>
       <c r="D22" s="12" t="inlineStr">
         <is>
-          <t>The Live Local residual runs negative in the AE flood zone at current coastal hard costs; the model does NOT force it positive — the conclusion is HOLD.</t>
+          <t>Each asset sells in the hold year at its forward NOI ÷ exit cap, net of cost of sale; the consolidated reversion sums the asset-level reversions.</t>
         </is>
       </c>
       <c r="E22" s="13" t="n"/>
@@ -4203,54 +4203,54 @@
       <c r="L22" s="13" t="n"/>
       <c r="M22" s="14" t="n"/>
     </row>
-    <row r="23"/>
-    <row r="24">
-      <c r="B24" s="11" t="inlineStr">
+    <row r="23" ht="15" customHeight="1">
+      <c r="B23" s="52" t="inlineStr">
+        <is>
+          <t>Redevelopment</t>
+        </is>
+      </c>
+      <c r="D23" s="12" t="inlineStr">
+        <is>
+          <t>The Live Local residual runs negative in the AE flood zone at current coastal hard costs; the model does NOT force it positive — the conclusion is HOLD.</t>
+        </is>
+      </c>
+      <c r="E23" s="13" t="n"/>
+      <c r="F23" s="13" t="n"/>
+      <c r="G23" s="13" t="n"/>
+      <c r="H23" s="13" t="n"/>
+      <c r="I23" s="13" t="n"/>
+      <c r="J23" s="13" t="n"/>
+      <c r="K23" s="13" t="n"/>
+      <c r="L23" s="13" t="n"/>
+      <c r="M23" s="14" t="n"/>
+    </row>
+    <row r="24"/>
+    <row r="25">
+      <c r="B25" s="11" t="inlineStr">
         <is>
           <t>SENIOR DEBT  —  SIZING CONVENTION</t>
         </is>
       </c>
-      <c r="C24" s="2" t="n"/>
-      <c r="D24" s="2" t="n"/>
-      <c r="E24" s="2" t="n"/>
-      <c r="F24" s="2" t="n"/>
-      <c r="G24" s="2" t="n"/>
-      <c r="H24" s="2" t="n"/>
-      <c r="I24" s="2" t="n"/>
-      <c r="J24" s="2" t="n"/>
-      <c r="K24" s="2" t="n"/>
-      <c r="L24" s="2" t="n"/>
-      <c r="M24" s="3" t="n"/>
-    </row>
-    <row r="25" ht="15" customHeight="1">
-      <c r="B25" s="12" t="inlineStr">
+      <c r="C25" s="2" t="n"/>
+      <c r="D25" s="2" t="n"/>
+      <c r="E25" s="2" t="n"/>
+      <c r="F25" s="2" t="n"/>
+      <c r="G25" s="2" t="n"/>
+      <c r="H25" s="2" t="n"/>
+      <c r="I25" s="2" t="n"/>
+      <c r="J25" s="2" t="n"/>
+      <c r="K25" s="2" t="n"/>
+      <c r="L25" s="2" t="n"/>
+      <c r="M25" s="3" t="n"/>
+    </row>
+    <row r="26" ht="15" customHeight="1">
+      <c r="B26" s="12" t="inlineStr">
         <is>
           <t>Debt is sized to the LESSER OF three lender constraints, sized on as-is in-place NOI:</t>
         </is>
       </c>
-      <c r="C25" s="13" t="n"/>
-      <c r="D25" s="13" t="n"/>
-      <c r="E25" s="13" t="n"/>
-      <c r="F25" s="13" t="n"/>
-      <c r="G25" s="13" t="n"/>
-      <c r="H25" s="13" t="n"/>
-      <c r="I25" s="13" t="n"/>
-      <c r="J25" s="13" t="n"/>
-      <c r="K25" s="13" t="n"/>
-      <c r="L25" s="13" t="n"/>
-      <c r="M25" s="14" t="n"/>
-    </row>
-    <row r="26" ht="15" customHeight="1">
-      <c r="B26" s="52" t="inlineStr">
-        <is>
-          <t>Constraint 1 — LTV</t>
-        </is>
-      </c>
-      <c r="D26" s="12" t="inlineStr">
-        <is>
-          <t>Loan ≤ max LTV × purchase price (default 60%).</t>
-        </is>
-      </c>
+      <c r="C26" s="13" t="n"/>
+      <c r="D26" s="13" t="n"/>
       <c r="E26" s="13" t="n"/>
       <c r="F26" s="13" t="n"/>
       <c r="G26" s="13" t="n"/>
@@ -4264,12 +4264,12 @@
     <row r="27" ht="15" customHeight="1">
       <c r="B27" s="52" t="inlineStr">
         <is>
-          <t>Constraint 2 — DSCR</t>
+          <t>Constraint 1 — LTV</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
-          <t>Loan ≤ NOI ÷ (min DSCR × mortgage constant); default min DSCR 1.30x.</t>
+          <t>Loan ≤ max LTV × purchase price (default 60%).</t>
         </is>
       </c>
       <c r="E27" s="13" t="n"/>
@@ -4285,12 +4285,12 @@
     <row r="28" ht="15" customHeight="1">
       <c r="B28" s="52" t="inlineStr">
         <is>
-          <t>Constraint 3 — Debt yield</t>
+          <t>Constraint 2 — DSCR</t>
         </is>
       </c>
       <c r="D28" s="12" t="inlineStr">
         <is>
-          <t>Loan ≤ NOI ÷ min debt yield (default 8.5%).</t>
+          <t>Loan ≤ NOI ÷ (min DSCR × mortgage constant); default min DSCR 1.30x.</t>
         </is>
       </c>
       <c r="E28" s="13" t="n"/>
@@ -4304,13 +4304,16 @@
       <c r="M28" s="14" t="n"/>
     </row>
     <row r="29" ht="15" customHeight="1">
-      <c r="B29" s="12" t="inlineStr">
-        <is>
-          <t>The sized loan is the minimum of the three; the binding constraint is flagged on the Income Valuation tab.</t>
-        </is>
-      </c>
-      <c r="C29" s="13" t="n"/>
-      <c r="D29" s="13" t="n"/>
+      <c r="B29" s="52" t="inlineStr">
+        <is>
+          <t>Constraint 3 — Debt yield</t>
+        </is>
+      </c>
+      <c r="D29" s="12" t="inlineStr">
+        <is>
+          <t>Loan ≤ NOI ÷ min debt yield (default 8.5%).</t>
+        </is>
+      </c>
       <c r="E29" s="13" t="n"/>
       <c r="F29" s="13" t="n"/>
       <c r="G29" s="13" t="n"/>
@@ -4321,56 +4324,52 @@
       <c r="L29" s="13" t="n"/>
       <c r="M29" s="14" t="n"/>
     </row>
-    <row r="30"/>
-    <row r="31">
-      <c r="B31" s="11" t="inlineStr">
+    <row r="30" ht="15" customHeight="1">
+      <c r="B30" s="12" t="inlineStr">
+        <is>
+          <t>The sized loan is the minimum of the three; the binding constraint is flagged on the Income Valuation tab.</t>
+        </is>
+      </c>
+      <c r="C30" s="13" t="n"/>
+      <c r="D30" s="13" t="n"/>
+      <c r="E30" s="13" t="n"/>
+      <c r="F30" s="13" t="n"/>
+      <c r="G30" s="13" t="n"/>
+      <c r="H30" s="13" t="n"/>
+      <c r="I30" s="13" t="n"/>
+      <c r="J30" s="13" t="n"/>
+      <c r="K30" s="13" t="n"/>
+      <c r="L30" s="13" t="n"/>
+      <c r="M30" s="14" t="n"/>
+    </row>
+    <row r="31"/>
+    <row r="32">
+      <c r="B32" s="11" t="inlineStr">
         <is>
           <t>DATA SOURCES  &amp;  CONFIDENCE FLAGS</t>
         </is>
       </c>
-      <c r="C31" s="2" t="n"/>
-      <c r="D31" s="2" t="n"/>
-      <c r="E31" s="2" t="n"/>
-      <c r="F31" s="2" t="n"/>
-      <c r="G31" s="2" t="n"/>
-      <c r="H31" s="2" t="n"/>
-      <c r="I31" s="2" t="n"/>
-      <c r="J31" s="2" t="n"/>
-      <c r="K31" s="2" t="n"/>
-      <c r="L31" s="2" t="n"/>
-      <c r="M31" s="3" t="n"/>
-    </row>
-    <row r="32" ht="15" customHeight="1">
-      <c r="B32" s="16" t="inlineStr">
+      <c r="C32" s="2" t="n"/>
+      <c r="D32" s="2" t="n"/>
+      <c r="E32" s="2" t="n"/>
+      <c r="F32" s="2" t="n"/>
+      <c r="G32" s="2" t="n"/>
+      <c r="H32" s="2" t="n"/>
+      <c r="I32" s="2" t="n"/>
+      <c r="J32" s="2" t="n"/>
+      <c r="K32" s="2" t="n"/>
+      <c r="L32" s="2" t="n"/>
+      <c r="M32" s="3" t="n"/>
+    </row>
+    <row r="33" ht="15" customHeight="1">
+      <c r="B33" s="16" t="inlineStr">
         <is>
           <t>Flag</t>
         </is>
       </c>
-      <c r="C32" s="15" t="inlineStr">
+      <c r="C33" s="15" t="inlineStr">
         <is>
           <t>Meaning</t>
-        </is>
-      </c>
-      <c r="D32" s="13" t="n"/>
-      <c r="E32" s="13" t="n"/>
-      <c r="F32" s="13" t="n"/>
-      <c r="G32" s="13" t="n"/>
-      <c r="H32" s="13" t="n"/>
-      <c r="I32" s="13" t="n"/>
-      <c r="J32" s="13" t="n"/>
-      <c r="K32" s="13" t="n"/>
-      <c r="L32" s="13" t="n"/>
-      <c r="M32" s="14" t="n"/>
-    </row>
-    <row r="33" ht="15" customHeight="1">
-      <c r="B33" s="30" t="inlineStr">
-        <is>
-          <t>✅ VERIFIED</t>
-        </is>
-      </c>
-      <c r="C33" s="12" t="inlineStr">
-        <is>
-          <t>public record — BCPA property appraiser / FL Sunbiz / recorded deed</t>
         </is>
       </c>
       <c r="D33" s="13" t="n"/>
@@ -4387,12 +4386,12 @@
     <row r="34" ht="15" customHeight="1">
       <c r="B34" s="30" t="inlineStr">
         <is>
-          <t>⚠️ REPORTED</t>
+          <t>✅ VERIFIED</t>
         </is>
       </c>
       <c r="C34" s="12" t="inlineStr">
         <is>
-          <t>counterparty, broker listing (LoopNet/Crexi), or press — unconfirmed at the county</t>
+          <t>public record — BCPA property appraiser / FL Sunbiz / recorded deed</t>
         </is>
       </c>
       <c r="D34" s="13" t="n"/>
@@ -4409,12 +4408,12 @@
     <row r="35" ht="15" customHeight="1">
       <c r="B35" s="30" t="inlineStr">
         <is>
-          <t>🔶 MODELED</t>
+          <t>⚠️ REPORTED</t>
         </is>
       </c>
       <c r="C35" s="12" t="inlineStr">
         <is>
-          <t>assumption from mid-2026 market research; moves with the blue inputs</t>
+          <t>counterparty, broker listing (LoopNet/Crexi), or press — unconfirmed at the county</t>
         </is>
       </c>
       <c r="D35" s="13" t="n"/>
@@ -4428,46 +4427,43 @@
       <c r="L35" s="13" t="n"/>
       <c r="M35" s="14" t="n"/>
     </row>
-    <row r="36"/>
-    <row r="37" ht="15" customHeight="1">
-      <c r="B37" s="15" t="inlineStr">
+    <row r="36" ht="15" customHeight="1">
+      <c r="B36" s="30" t="inlineStr">
+        <is>
+          <t>🔶 MODELED</t>
+        </is>
+      </c>
+      <c r="C36" s="12" t="inlineStr">
+        <is>
+          <t>assumption from mid-2026 market research; moves with the blue inputs</t>
+        </is>
+      </c>
+      <c r="D36" s="13" t="n"/>
+      <c r="E36" s="13" t="n"/>
+      <c r="F36" s="13" t="n"/>
+      <c r="G36" s="13" t="n"/>
+      <c r="H36" s="13" t="n"/>
+      <c r="I36" s="13" t="n"/>
+      <c r="J36" s="13" t="n"/>
+      <c r="K36" s="13" t="n"/>
+      <c r="L36" s="13" t="n"/>
+      <c r="M36" s="14" t="n"/>
+    </row>
+    <row r="37"/>
+    <row r="38" ht="15" customHeight="1">
+      <c r="B38" s="15" t="inlineStr">
         <is>
           <t>Asset</t>
         </is>
       </c>
-      <c r="D37" s="16" t="inlineStr">
+      <c r="D38" s="16" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="E37" s="15" t="inlineStr">
+      <c r="E38" s="15" t="inlineStr">
         <is>
           <t>Sources</t>
-        </is>
-      </c>
-      <c r="F37" s="13" t="n"/>
-      <c r="G37" s="13" t="n"/>
-      <c r="H37" s="13" t="n"/>
-      <c r="I37" s="13" t="n"/>
-      <c r="J37" s="13" t="n"/>
-      <c r="K37" s="13" t="n"/>
-      <c r="L37" s="13" t="n"/>
-      <c r="M37" s="14" t="n"/>
-    </row>
-    <row r="38" ht="15" customHeight="1">
-      <c r="B38" s="12" t="inlineStr">
-        <is>
-          <t>Shahidi Retail (Galleria Plaza)</t>
-        </is>
-      </c>
-      <c r="D38" s="30" t="inlineStr">
-        <is>
-          <t>✅ BCPA/Sunbiz</t>
-        </is>
-      </c>
-      <c r="E38" s="12" t="inlineStr">
-        <is>
-          <t>Folio 49-42-36-12-0070; tenants via LoopNet/Southeast Centers, Yelp, official locators; rents from corridor comps</t>
         </is>
       </c>
       <c r="F38" s="13" t="n"/>
@@ -4482,17 +4478,17 @@
     <row r="39" ht="15" customHeight="1">
       <c r="B39" s="12" t="inlineStr">
         <is>
-          <t>Publix + Starbucks</t>
+          <t>Shahidi Retail (Galleria Plaza)</t>
         </is>
       </c>
       <c r="D39" s="30" t="inlineStr">
         <is>
-          <t>✅ BCPA/deed</t>
+          <t>✅ BCPA/Sunbiz</t>
         </is>
       </c>
       <c r="E39" s="12" t="inlineStr">
         <is>
-          <t>Folio -0060; $25M Trustee's Deed 03/2025 (The Real Deal); rents/caps from net-lease research (Boulder Group, Matthews)</t>
+          <t>Folio 49-42-36-12-0070; tenants via LoopNet/Southeast Centers, Yelp, official locators; rents from corridor comps</t>
         </is>
       </c>
       <c r="F39" s="13" t="n"/>
@@ -4507,17 +4503,17 @@
     <row r="40" ht="15" customHeight="1">
       <c r="B40" s="12" t="inlineStr">
         <is>
-          <t>Sunrise Plaza (Kar Luen)</t>
+          <t>Publix + Starbucks</t>
         </is>
       </c>
       <c r="D40" s="30" t="inlineStr">
         <is>
-          <t>⚠️ reported</t>
+          <t>✅ BCPA/deed</t>
         </is>
       </c>
       <c r="E40" s="12" t="inlineStr">
         <is>
-          <t>Folio -0011; LoopNet/Sunbiz/Cortera; tenants via Yelp; value &amp; sale unconfirmed — VERIFY AT BCPA</t>
+          <t>Folio -0060; $25M Trustee's Deed 03/2025 (The Real Deal); rents/caps from net-lease research (Boulder Group, Matthews)</t>
         </is>
       </c>
       <c r="F40" s="13" t="n"/>
@@ -4532,7 +4528,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="B41" s="12" t="inlineStr">
         <is>
-          <t>Galleria Corporate Centre</t>
+          <t>Sunrise Plaza (Kar Luen)</t>
         </is>
       </c>
       <c r="D41" s="30" t="inlineStr">
@@ -4542,7 +4538,7 @@
       </c>
       <c r="E41" s="12" t="inlineStr">
         <is>
-          <t>2455 E Sunrise; owners via Daily Business Review 10/2019 (Main Street Fund 57.4%); per-unit folios not enumerated</t>
+          <t>Folio -0011; LoopNet/Sunbiz/Cortera; tenants via Yelp; value &amp; sale unconfirmed — VERIFY AT BCPA</t>
         </is>
       </c>
       <c r="F41" s="13" t="n"/>
@@ -4557,7 +4553,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="B42" s="12" t="inlineStr">
         <is>
-          <t>1040 Bayview (land)</t>
+          <t>Galleria Corporate Centre</t>
         </is>
       </c>
       <c r="D42" s="30" t="inlineStr">
@@ -4567,7 +4563,7 @@
       </c>
       <c r="E42" s="12" t="inlineStr">
         <is>
-          <t>Folio -0040; Florida YIMBY/Traded/BBX/Procacci; entitlement 259 units; BCPA market value reported not confirmed</t>
+          <t>2455 E Sunrise; owners via Daily Business Review 10/2019 (Main Street Fund 57.4%); per-unit folios not enumerated</t>
         </is>
       </c>
       <c r="F42" s="13" t="n"/>
@@ -4580,14 +4576,21 @@
       <c r="M42" s="14" t="n"/>
     </row>
     <row r="43" ht="15" customHeight="1">
-      <c r="B43" s="40" t="inlineStr">
-        <is>
-          <t>BCPA (bcpa.net) was blocked from the build environment; ⚠️ items were sourced from web mirrors of the tax roll and must be confirmed at the county before close.</t>
-        </is>
-      </c>
-      <c r="C43" s="13" t="n"/>
-      <c r="D43" s="13" t="n"/>
-      <c r="E43" s="13" t="n"/>
+      <c r="B43" s="12" t="inlineStr">
+        <is>
+          <t>1040 Bayview (land)</t>
+        </is>
+      </c>
+      <c r="D43" s="30" t="inlineStr">
+        <is>
+          <t>⚠️ reported</t>
+        </is>
+      </c>
+      <c r="E43" s="12" t="inlineStr">
+        <is>
+          <t>Folio -0040; Florida YIMBY/Traded/BBX/Procacci; entitlement 259 units; BCPA market value reported not confirmed</t>
+        </is>
+      </c>
       <c r="F43" s="13" t="n"/>
       <c r="G43" s="13" t="n"/>
       <c r="H43" s="13" t="n"/>
@@ -4597,55 +4600,52 @@
       <c r="L43" s="13" t="n"/>
       <c r="M43" s="14" t="n"/>
     </row>
-    <row r="44"/>
-    <row r="45">
-      <c r="B45" s="11" t="inlineStr">
+    <row r="44" ht="15" customHeight="1">
+      <c r="B44" s="40" t="inlineStr">
+        <is>
+          <t>BCPA (bcpa.net) was blocked from the build environment; ⚠️ items were sourced from web mirrors of the tax roll and must be confirmed at the county before close.</t>
+        </is>
+      </c>
+      <c r="C44" s="13" t="n"/>
+      <c r="D44" s="13" t="n"/>
+      <c r="E44" s="13" t="n"/>
+      <c r="F44" s="13" t="n"/>
+      <c r="G44" s="13" t="n"/>
+      <c r="H44" s="13" t="n"/>
+      <c r="I44" s="13" t="n"/>
+      <c r="J44" s="13" t="n"/>
+      <c r="K44" s="13" t="n"/>
+      <c r="L44" s="13" t="n"/>
+      <c r="M44" s="14" t="n"/>
+    </row>
+    <row r="45"/>
+    <row r="46">
+      <c r="B46" s="11" t="inlineStr">
         <is>
           <t>KEY MARKET ASSUMPTIONS  (mid-2026, MODELED)</t>
         </is>
       </c>
-      <c r="C45" s="2" t="n"/>
-      <c r="D45" s="2" t="n"/>
-      <c r="E45" s="2" t="n"/>
-      <c r="F45" s="2" t="n"/>
-      <c r="G45" s="2" t="n"/>
-      <c r="H45" s="2" t="n"/>
-      <c r="I45" s="2" t="n"/>
-      <c r="J45" s="2" t="n"/>
-      <c r="K45" s="2" t="n"/>
-      <c r="L45" s="2" t="n"/>
-      <c r="M45" s="3" t="n"/>
-    </row>
-    <row r="46" ht="15" customHeight="1">
-      <c r="B46" s="52" t="inlineStr">
-        <is>
-          <t>Retail rents</t>
-        </is>
-      </c>
-      <c r="D46" s="12" t="inlineStr">
-        <is>
-          <t>in-line $32–55/SF NNN (Sunrise corridor $45–60); restaurant/end-cap $40–50/SF</t>
-        </is>
-      </c>
-      <c r="E46" s="13" t="n"/>
-      <c r="F46" s="13" t="n"/>
-      <c r="G46" s="13" t="n"/>
-      <c r="H46" s="13" t="n"/>
-      <c r="I46" s="13" t="n"/>
-      <c r="J46" s="13" t="n"/>
-      <c r="K46" s="13" t="n"/>
-      <c r="L46" s="13" t="n"/>
-      <c r="M46" s="14" t="n"/>
+      <c r="C46" s="2" t="n"/>
+      <c r="D46" s="2" t="n"/>
+      <c r="E46" s="2" t="n"/>
+      <c r="F46" s="2" t="n"/>
+      <c r="G46" s="2" t="n"/>
+      <c r="H46" s="2" t="n"/>
+      <c r="I46" s="2" t="n"/>
+      <c r="J46" s="2" t="n"/>
+      <c r="K46" s="2" t="n"/>
+      <c r="L46" s="2" t="n"/>
+      <c r="M46" s="3" t="n"/>
     </row>
     <row r="47" ht="15" customHeight="1">
       <c r="B47" s="52" t="inlineStr">
         <is>
-          <t>Publix / Starbucks</t>
+          <t>Retail rents</t>
         </is>
       </c>
       <c r="D47" s="12" t="inlineStr">
         <is>
-          <t>grocery ~$13/SF NNN, cap 6.0–6.75%; Starbucks pad ~$60/SF, cap 4.75–5.5%</t>
+          <t>in-line $32–55/SF NNN (Sunrise corridor $45–60); restaurant/end-cap $40–50/SF</t>
         </is>
       </c>
       <c r="E47" s="13" t="n"/>
@@ -4661,12 +4661,12 @@
     <row r="48" ht="15" customHeight="1">
       <c r="B48" s="52" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Publix / Starbucks</t>
         </is>
       </c>
       <c r="D48" s="12" t="inlineStr">
         <is>
-          <t>small Class B/C ~$20–30/SF gross (~$15–24 NNN); cap 7.5–9.0%</t>
+          <t>grocery ~$13/SF NNN, cap 6.0–6.75%; Starbucks pad ~$60/SF, cap 4.75–5.5%</t>
         </is>
       </c>
       <c r="E48" s="13" t="n"/>
@@ -4682,12 +4682,12 @@
     <row r="49" ht="15" customHeight="1">
       <c r="B49" s="52" t="inlineStr">
         <is>
-          <t>Retail caps</t>
+          <t>Office</t>
         </is>
       </c>
       <c r="D49" s="12" t="inlineStr">
         <is>
-          <t>stabilized strip 6.25–6.75%; value-add 7.25–8.0%; exit = going-in +25 bps</t>
+          <t>small Class B/C ~$20–30/SF gross (~$15–24 NNN); cap 7.5–9.0%</t>
         </is>
       </c>
       <c r="E49" s="13" t="n"/>
@@ -4703,12 +4703,12 @@
     <row r="50" ht="15" customHeight="1">
       <c r="B50" s="52" t="inlineStr">
         <is>
-          <t>Land</t>
+          <t>Retail caps</t>
         </is>
       </c>
       <c r="D50" s="12" t="inlineStr">
         <is>
-          <t>Fort Lauderdale infill ~$248/SF (subject comps $228–255); Galleria bulk ~$53/SF</t>
+          <t>stabilized strip 6.25–6.75%; value-add 7.25–8.0%; exit = going-in +25 bps</t>
         </is>
       </c>
       <c r="E50" s="13" t="n"/>
@@ -4724,12 +4724,12 @@
     <row r="51" ht="15" customHeight="1">
       <c r="B51" s="52" t="inlineStr">
         <is>
-          <t>Senior debt</t>
+          <t>Land</t>
         </is>
       </c>
       <c r="D51" s="12" t="inlineStr">
         <is>
-          <t>stabilized 5.75–7.0%, 60–75% LTV, DSCR 1.25–1.40x, debt yield 7–10%</t>
+          <t>Fort Lauderdale infill ~$248/SF (subject comps $228–255); Galleria bulk ~$53/SF</t>
         </is>
       </c>
       <c r="E51" s="13" t="n"/>
@@ -4745,12 +4745,12 @@
     <row r="52" ht="15" customHeight="1">
       <c r="B52" s="52" t="inlineStr">
         <is>
-          <t>Covered-land cap</t>
+          <t>Senior debt</t>
         </is>
       </c>
       <c r="D52" s="12" t="inlineStr">
         <is>
-          <t>in-place income cap ~3–5% — income covers carry, not a yield play</t>
+          <t>stabilized 5.75–7.0%, 60–75% LTV, DSCR 1.25–1.40x, debt yield 7–10%</t>
         </is>
       </c>
       <c r="E52" s="13" t="n"/>
@@ -4763,55 +4763,55 @@
       <c r="L52" s="13" t="n"/>
       <c r="M52" s="14" t="n"/>
     </row>
-    <row r="53"/>
-    <row r="54">
-      <c r="B54" s="11" t="inlineStr">
+    <row r="53" ht="15" customHeight="1">
+      <c r="B53" s="52" t="inlineStr">
+        <is>
+          <t>Covered-land cap</t>
+        </is>
+      </c>
+      <c r="D53" s="12" t="inlineStr">
+        <is>
+          <t>in-place income cap ~3–5% — income covers carry, not a yield play</t>
+        </is>
+      </c>
+      <c r="E53" s="13" t="n"/>
+      <c r="F53" s="13" t="n"/>
+      <c r="G53" s="13" t="n"/>
+      <c r="H53" s="13" t="n"/>
+      <c r="I53" s="13" t="n"/>
+      <c r="J53" s="13" t="n"/>
+      <c r="K53" s="13" t="n"/>
+      <c r="L53" s="13" t="n"/>
+      <c r="M53" s="14" t="n"/>
+    </row>
+    <row r="54"/>
+    <row r="55">
+      <c r="B55" s="11" t="inlineStr">
         <is>
           <t>COLOR  &amp;  FONT LEGEND</t>
         </is>
       </c>
-      <c r="C54" s="2" t="n"/>
-      <c r="D54" s="2" t="n"/>
-      <c r="E54" s="2" t="n"/>
-      <c r="F54" s="2" t="n"/>
-      <c r="G54" s="2" t="n"/>
-      <c r="H54" s="2" t="n"/>
-      <c r="I54" s="2" t="n"/>
-      <c r="J54" s="2" t="n"/>
-      <c r="K54" s="2" t="n"/>
-      <c r="L54" s="2" t="n"/>
-      <c r="M54" s="3" t="n"/>
-    </row>
-    <row r="55" ht="15" customHeight="1">
-      <c r="B55" s="52" t="inlineStr">
-        <is>
-          <t>Blue on yellow</t>
-        </is>
-      </c>
-      <c r="D55" s="12" t="inlineStr">
-        <is>
-          <t>hardcoded input — the only cells to change</t>
-        </is>
-      </c>
-      <c r="E55" s="13" t="n"/>
-      <c r="F55" s="13" t="n"/>
-      <c r="G55" s="13" t="n"/>
-      <c r="H55" s="13" t="n"/>
-      <c r="I55" s="13" t="n"/>
-      <c r="J55" s="13" t="n"/>
-      <c r="K55" s="13" t="n"/>
-      <c r="L55" s="13" t="n"/>
-      <c r="M55" s="14" t="n"/>
+      <c r="C55" s="2" t="n"/>
+      <c r="D55" s="2" t="n"/>
+      <c r="E55" s="2" t="n"/>
+      <c r="F55" s="2" t="n"/>
+      <c r="G55" s="2" t="n"/>
+      <c r="H55" s="2" t="n"/>
+      <c r="I55" s="2" t="n"/>
+      <c r="J55" s="2" t="n"/>
+      <c r="K55" s="2" t="n"/>
+      <c r="L55" s="2" t="n"/>
+      <c r="M55" s="3" t="n"/>
     </row>
     <row r="56" ht="15" customHeight="1">
       <c r="B56" s="52" t="inlineStr">
         <is>
-          <t>Black on white</t>
+          <t>Blue on yellow</t>
         </is>
       </c>
       <c r="D56" s="12" t="inlineStr">
         <is>
-          <t>formula / calculation</t>
+          <t>hardcoded input — the only cells to change</t>
         </is>
       </c>
       <c r="E56" s="13" t="n"/>
@@ -4827,12 +4827,12 @@
     <row r="57" ht="15" customHeight="1">
       <c r="B57" s="52" t="inlineStr">
         <is>
-          <t>Green</t>
+          <t>Black on white</t>
         </is>
       </c>
       <c r="D57" s="12" t="inlineStr">
         <is>
-          <t>public-record verified fact or cross-sheet link</t>
+          <t>formula / calculation</t>
         </is>
       </c>
       <c r="E57" s="13" t="n"/>
@@ -4848,12 +4848,12 @@
     <row r="58" ht="15" customHeight="1">
       <c r="B58" s="52" t="inlineStr">
         <is>
-          <t>Gold on navy / dark</t>
+          <t>Green</t>
         </is>
       </c>
       <c r="D58" s="12" t="inlineStr">
         <is>
-          <t>section header, total, KPI box, banner</t>
+          <t>public-record verified fact or cross-sheet link</t>
         </is>
       </c>
       <c r="E58" s="13" t="n"/>
@@ -4869,12 +4869,12 @@
     <row r="59" ht="15" customHeight="1">
       <c r="B59" s="52" t="inlineStr">
         <is>
-          <t>Orange / dark red</t>
+          <t>Gold on navy / dark</t>
         </is>
       </c>
       <c r="D59" s="12" t="inlineStr">
         <is>
-          <t>warning, flag, or excluded-from note</t>
+          <t>section header, total, KPI box, banner</t>
         </is>
       </c>
       <c r="E59" s="13" t="n"/>
@@ -4887,47 +4887,50 @@
       <c r="L59" s="13" t="n"/>
       <c r="M59" s="14" t="n"/>
     </row>
-    <row r="60"/>
-    <row r="61">
-      <c r="B61" s="11" t="inlineStr">
+    <row r="60" ht="15" customHeight="1">
+      <c r="B60" s="52" t="inlineStr">
+        <is>
+          <t>Orange / dark red</t>
+        </is>
+      </c>
+      <c r="D60" s="12" t="inlineStr">
+        <is>
+          <t>warning, flag, or excluded-from note</t>
+        </is>
+      </c>
+      <c r="E60" s="13" t="n"/>
+      <c r="F60" s="13" t="n"/>
+      <c r="G60" s="13" t="n"/>
+      <c r="H60" s="13" t="n"/>
+      <c r="I60" s="13" t="n"/>
+      <c r="J60" s="13" t="n"/>
+      <c r="K60" s="13" t="n"/>
+      <c r="L60" s="13" t="n"/>
+      <c r="M60" s="14" t="n"/>
+    </row>
+    <row r="61"/>
+    <row r="62">
+      <c r="B62" s="11" t="inlineStr">
         <is>
           <t>LIMITATIONS  &amp;  DISCLAIMERS</t>
         </is>
       </c>
-      <c r="C61" s="2" t="n"/>
-      <c r="D61" s="2" t="n"/>
-      <c r="E61" s="2" t="n"/>
-      <c r="F61" s="2" t="n"/>
-      <c r="G61" s="2" t="n"/>
-      <c r="H61" s="2" t="n"/>
-      <c r="I61" s="2" t="n"/>
-      <c r="J61" s="2" t="n"/>
-      <c r="K61" s="2" t="n"/>
-      <c r="L61" s="2" t="n"/>
-      <c r="M61" s="3" t="n"/>
-    </row>
-    <row r="62" ht="15" customHeight="1">
-      <c r="B62" s="12" t="inlineStr">
-        <is>
-          <t>• Space-level rent rolls are estimated; no tenant-by-tenant lease abstracts (expirations, options, recovery type) were available. Replace with real leases in diligence.</t>
-        </is>
-      </c>
-      <c r="C62" s="13" t="n"/>
-      <c r="D62" s="13" t="n"/>
-      <c r="E62" s="13" t="n"/>
-      <c r="F62" s="13" t="n"/>
-      <c r="G62" s="13" t="n"/>
-      <c r="H62" s="13" t="n"/>
-      <c r="I62" s="13" t="n"/>
-      <c r="J62" s="13" t="n"/>
-      <c r="K62" s="13" t="n"/>
-      <c r="L62" s="13" t="n"/>
-      <c r="M62" s="14" t="n"/>
+      <c r="C62" s="2" t="n"/>
+      <c r="D62" s="2" t="n"/>
+      <c r="E62" s="2" t="n"/>
+      <c r="F62" s="2" t="n"/>
+      <c r="G62" s="2" t="n"/>
+      <c r="H62" s="2" t="n"/>
+      <c r="I62" s="2" t="n"/>
+      <c r="J62" s="2" t="n"/>
+      <c r="K62" s="2" t="n"/>
+      <c r="L62" s="2" t="n"/>
+      <c r="M62" s="3" t="n"/>
     </row>
     <row r="63" ht="15" customHeight="1">
       <c r="B63" s="12" t="inlineStr">
         <is>
-          <t>• Publix and the office-condo units are not listed for sale; they are modeled as acquisition cases. Publix is a fee owner, so its 'rent' is a mark-to-market, not contract income.</t>
+          <t>• Space-level rent rolls are estimated; no tenant-by-tenant lease abstracts (expirations, options, recovery type) were available. Replace with real leases in diligence.</t>
         </is>
       </c>
       <c r="C63" s="13" t="n"/>
@@ -4945,7 +4948,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="B64" s="12" t="inlineStr">
         <is>
-          <t>• Property-tax reassessment is modeled to each asset's own price (FL rule); an assemblage purchase would reallocate basis and taxes across parcels.</t>
+          <t>• Publix and the office-condo units are not listed for sale; they are modeled as acquisition cases. Publix is a fee owner, so its 'rent' is a mark-to-market, not contract income.</t>
         </is>
       </c>
       <c r="C64" s="13" t="n"/>
@@ -4963,7 +4966,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="B65" s="12" t="inlineStr">
         <is>
-          <t>• Returns exclude any LP/GP promote/waterfall, transfer taxes, and portfolio-level G&amp;A. This is a screening model, not a closing model.</t>
+          <t>• Property-tax reassessment is modeled to each asset's own price (FL rule); an assemblage purchase would reallocate basis and taxes across parcels.</t>
         </is>
       </c>
       <c r="C65" s="13" t="n"/>
@@ -4981,7 +4984,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="B66" s="12" t="inlineStr">
         <is>
-          <t>• All figures are estimates for internal evaluation only and are not an appraisal, an offer, or investment advice. Confirm all ⚠️ REPORTED data at the county before relying on it.</t>
+          <t>• Returns exclude any LP/GP promote/waterfall, transfer taxes, and portfolio-level G&amp;A. This is a screening model, not a closing model.</t>
         </is>
       </c>
       <c r="C66" s="13" t="n"/>
@@ -4996,63 +4999,82 @@
       <c r="L66" s="13" t="n"/>
       <c r="M66" s="14" t="n"/>
     </row>
+    <row r="67" ht="15" customHeight="1">
+      <c r="B67" s="12" t="inlineStr">
+        <is>
+          <t>• All figures are estimates for internal evaluation only and are not an appraisal, an offer, or investment advice. Confirm all ⚠️ REPORTED data at the county before relying on it.</t>
+        </is>
+      </c>
+      <c r="C67" s="13" t="n"/>
+      <c r="D67" s="13" t="n"/>
+      <c r="E67" s="13" t="n"/>
+      <c r="F67" s="13" t="n"/>
+      <c r="G67" s="13" t="n"/>
+      <c r="H67" s="13" t="n"/>
+      <c r="I67" s="13" t="n"/>
+      <c r="J67" s="13" t="n"/>
+      <c r="K67" s="13" t="n"/>
+      <c r="L67" s="13" t="n"/>
+      <c r="M67" s="14" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="58">
+  <mergeCells count="59">
     <mergeCell ref="B2:M2"/>
     <mergeCell ref="C34:M34"/>
     <mergeCell ref="D18:M18"/>
     <mergeCell ref="D56:M56"/>
     <mergeCell ref="D58:M58"/>
-    <mergeCell ref="B61:M61"/>
+    <mergeCell ref="B67:M67"/>
     <mergeCell ref="C33:M33"/>
     <mergeCell ref="B8:M8"/>
     <mergeCell ref="E40:M40"/>
     <mergeCell ref="D15:M15"/>
     <mergeCell ref="B1:M1"/>
-    <mergeCell ref="D55:M55"/>
+    <mergeCell ref="B44:M44"/>
     <mergeCell ref="D51:M51"/>
-    <mergeCell ref="B29:M29"/>
     <mergeCell ref="D14:M14"/>
+    <mergeCell ref="D29:M29"/>
+    <mergeCell ref="D23:M23"/>
     <mergeCell ref="C35:M35"/>
     <mergeCell ref="B10:M10"/>
     <mergeCell ref="D50:M50"/>
-    <mergeCell ref="D26:M26"/>
     <mergeCell ref="D59:M59"/>
+    <mergeCell ref="D60:M60"/>
     <mergeCell ref="D20:M20"/>
     <mergeCell ref="B9:M9"/>
+    <mergeCell ref="B30:M30"/>
     <mergeCell ref="B65:M65"/>
     <mergeCell ref="D19:M19"/>
+    <mergeCell ref="B55:M55"/>
     <mergeCell ref="B6:M6"/>
-    <mergeCell ref="B24:M24"/>
     <mergeCell ref="B64:M64"/>
     <mergeCell ref="E41:M41"/>
-    <mergeCell ref="D46:M46"/>
     <mergeCell ref="D22:M22"/>
     <mergeCell ref="B5:M5"/>
-    <mergeCell ref="E37:M37"/>
-    <mergeCell ref="B45:M45"/>
     <mergeCell ref="B63:M63"/>
     <mergeCell ref="D52:M52"/>
     <mergeCell ref="D21:M21"/>
+    <mergeCell ref="B32:M32"/>
+    <mergeCell ref="B26:M26"/>
+    <mergeCell ref="C36:M36"/>
     <mergeCell ref="D57:M57"/>
     <mergeCell ref="B4:M4"/>
+    <mergeCell ref="E43:M43"/>
     <mergeCell ref="D13:M13"/>
     <mergeCell ref="D49:M49"/>
     <mergeCell ref="D27:M27"/>
-    <mergeCell ref="B54:M54"/>
     <mergeCell ref="B62:M62"/>
     <mergeCell ref="B7:M7"/>
     <mergeCell ref="B25:M25"/>
     <mergeCell ref="E42:M42"/>
     <mergeCell ref="D48:M48"/>
     <mergeCell ref="D17:M17"/>
-    <mergeCell ref="B31:M31"/>
-    <mergeCell ref="C32:M32"/>
+    <mergeCell ref="B46:M46"/>
     <mergeCell ref="B66:M66"/>
+    <mergeCell ref="D53:M53"/>
     <mergeCell ref="E39:M39"/>
     <mergeCell ref="D16:M16"/>
     <mergeCell ref="D47:M47"/>
-    <mergeCell ref="B43:M43"/>
     <mergeCell ref="B12:M12"/>
     <mergeCell ref="D28:M28"/>
     <mergeCell ref="E38:M38"/>
@@ -5070,7 +5092,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M128"/>
+  <dimension ref="A1:M132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.5" customWidth="1" min="1" max="1"/>
@@ -6358,7 +6380,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="B61" s="15" t="inlineStr">
         <is>
-          <t>Publix + Starbucks — grocery + pad (NNN)  ✅ verified parcel · not a seller</t>
+          <t>Publix + Starbucks — SALE-LEASEBACK (acquire fee, lease back during entitlement)  ✅ verified parcel</t>
         </is>
       </c>
       <c r="C61" s="13" t="n"/>
@@ -6376,11 +6398,11 @@
     <row r="62" ht="15" customHeight="1">
       <c r="B62" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Income-value basis</t>
+          <t xml:space="preserve">   SLB acquisition price (fee)</t>
         </is>
       </c>
       <c r="C62" s="37" t="n">
-        <v>9700000</v>
+        <v>25000000</v>
       </c>
     </row>
     <row r="63" ht="15" customHeight="1">
@@ -6406,634 +6428,558 @@
     <row r="65" ht="15" customHeight="1">
       <c r="B65" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Market rent ($/SF NNN)</t>
+          <t xml:space="preserve">   Publix leaseback rent ($/SF NNN)</t>
         </is>
       </c>
       <c r="C65" s="34" t="n">
-        <v>15.81</v>
+        <v>22</v>
       </c>
     </row>
     <row r="66" ht="15" customHeight="1">
       <c r="B66" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   In-place occupancy</t>
-        </is>
-      </c>
-      <c r="C66" s="31" t="n">
-        <v>1</v>
+          <t xml:space="preserve">   Publix leaseback SF</t>
+        </is>
+      </c>
+      <c r="C66" s="36" t="n">
+        <v>34622</v>
       </c>
     </row>
     <row r="67" ht="15" customHeight="1">
       <c r="B67" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Stabilized occupancy</t>
-        </is>
-      </c>
-      <c r="C67" s="31" t="n">
-        <v>1</v>
+          <t xml:space="preserve">   Starbucks pad rent ($/SF NNN)</t>
+        </is>
+      </c>
+      <c r="C67" s="34" t="n">
+        <v>60</v>
       </c>
     </row>
     <row r="68" ht="15" customHeight="1">
       <c r="B68" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Insurance ($/yr)</t>
-        </is>
-      </c>
-      <c r="C68" s="35" t="n">
-        <v>45000</v>
+          <t xml:space="preserve">   Starbucks pad SF</t>
+        </is>
+      </c>
+      <c r="C68" s="36" t="n">
+        <v>2200</v>
       </c>
     </row>
     <row r="69" ht="15" customHeight="1">
       <c r="B69" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   CAM ($/yr, recoverable)</t>
-        </is>
-      </c>
-      <c r="C69" s="35" t="n">
-        <v>35000</v>
+          <t xml:space="preserve">   Leaseback term / entitlement (yrs)</t>
+        </is>
+      </c>
+      <c r="C69" s="32" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="70" ht="15" customHeight="1">
       <c r="B70" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Repairs &amp; maintenance ($/yr)</t>
-        </is>
-      </c>
-      <c r="C70" s="35" t="n">
-        <v>25000</v>
+          <t xml:space="preserve">   In-place occupancy</t>
+        </is>
+      </c>
+      <c r="C70" s="31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="71" ht="15" customHeight="1">
       <c r="B71" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Management fee (% EGR)</t>
+          <t xml:space="preserve">   Stabilized occupancy</t>
         </is>
       </c>
       <c r="C71" s="31" t="n">
-        <v>0.02</v>
+        <v>1</v>
       </c>
     </row>
     <row r="72" ht="15" customHeight="1">
       <c r="B72" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Going-in cap</t>
-        </is>
-      </c>
-      <c r="C72" s="29" t="n">
-        <v>0.06</v>
+          <t xml:space="preserve">   Insurance ($/yr)</t>
+        </is>
+      </c>
+      <c r="C72" s="35" t="n">
+        <v>45000</v>
       </c>
     </row>
     <row r="73" ht="15" customHeight="1">
       <c r="B73" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Exit cap</t>
-        </is>
-      </c>
-      <c r="C73" s="29" t="n">
-        <v>0.0625</v>
+          <t xml:space="preserve">   CAM ($/yr, recoverable)</t>
+        </is>
+      </c>
+      <c r="C73" s="35" t="n">
+        <v>35000</v>
       </c>
     </row>
     <row r="74" ht="15" customHeight="1">
       <c r="B74" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Senior LTV</t>
-        </is>
-      </c>
-      <c r="C74" s="31" t="n">
-        <v>0.55</v>
+          <t xml:space="preserve">   Repairs &amp; maintenance ($/yr)</t>
+        </is>
+      </c>
+      <c r="C74" s="35" t="n">
+        <v>25000</v>
       </c>
     </row>
     <row r="75" ht="15" customHeight="1">
       <c r="B75" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Senior rate</t>
-        </is>
-      </c>
-      <c r="C75" s="29" t="n">
+          <t xml:space="preserve">   Management fee (% EGR)</t>
+        </is>
+      </c>
+      <c r="C75" s="31" t="n">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="76" ht="15" customHeight="1">
+      <c r="B76" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Going-in cap (reference)</t>
+        </is>
+      </c>
+      <c r="C76" s="29" t="n">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="77" ht="15" customHeight="1">
+      <c r="B77" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Exit cap</t>
+        </is>
+      </c>
+      <c r="C77" s="29" t="n">
         <v>0.0625</v>
       </c>
-    </row>
-    <row r="76"/>
-    <row r="77" ht="15" customHeight="1">
-      <c r="B77" s="15" t="inlineStr">
-        <is>
-          <t>Sunrise Plaza (Kar Luen) — value-add retail  ⚠️ reported parcel</t>
-        </is>
-      </c>
-      <c r="C77" s="13" t="n"/>
-      <c r="D77" s="13" t="n"/>
-      <c r="E77" s="13" t="n"/>
-      <c r="F77" s="13" t="n"/>
-      <c r="G77" s="13" t="n"/>
-      <c r="H77" s="13" t="n"/>
-      <c r="I77" s="13" t="n"/>
-      <c r="J77" s="13" t="n"/>
-      <c r="K77" s="13" t="n"/>
-      <c r="L77" s="13" t="n"/>
-      <c r="M77" s="14" t="n"/>
     </row>
     <row r="78" ht="15" customHeight="1">
       <c r="B78" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Purchase price / basis</t>
-        </is>
-      </c>
-      <c r="C78" s="37" t="n">
-        <v>8500000</v>
+          <t xml:space="preserve">   Senior LTV (covered-land, conservative)</t>
+        </is>
+      </c>
+      <c r="C78" s="31" t="n">
+        <v>0.45</v>
       </c>
     </row>
     <row r="79" ht="15" customHeight="1">
       <c r="B79" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Land (SF)</t>
-        </is>
-      </c>
-      <c r="C79" s="36" t="n">
-        <v>30928</v>
-      </c>
-    </row>
-    <row r="80" ht="15" customHeight="1">
-      <c r="B80" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Land value ($/SF)</t>
-        </is>
-      </c>
-      <c r="C80" s="34" t="n">
-        <v>248</v>
-      </c>
-    </row>
+          <t xml:space="preserve">   Senior rate</t>
+        </is>
+      </c>
+      <c r="C79" s="29" t="n">
+        <v>0.0625</v>
+      </c>
+    </row>
+    <row r="80"/>
     <row r="81" ht="15" customHeight="1">
-      <c r="B81" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Market rent ($/SF NNN)</t>
-        </is>
-      </c>
-      <c r="C81" s="34" t="n">
-        <v>34</v>
-      </c>
+      <c r="B81" s="15" t="inlineStr">
+        <is>
+          <t>Sunrise Plaza (Kar Luen) — value-add retail  ⚠️ reported parcel</t>
+        </is>
+      </c>
+      <c r="C81" s="13" t="n"/>
+      <c r="D81" s="13" t="n"/>
+      <c r="E81" s="13" t="n"/>
+      <c r="F81" s="13" t="n"/>
+      <c r="G81" s="13" t="n"/>
+      <c r="H81" s="13" t="n"/>
+      <c r="I81" s="13" t="n"/>
+      <c r="J81" s="13" t="n"/>
+      <c r="K81" s="13" t="n"/>
+      <c r="L81" s="13" t="n"/>
+      <c r="M81" s="14" t="n"/>
     </row>
     <row r="82" ht="15" customHeight="1">
       <c r="B82" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   In-place occupancy</t>
-        </is>
-      </c>
-      <c r="C82" s="31" t="n">
-        <v>0.801</v>
+          <t xml:space="preserve">   Purchase price / basis</t>
+        </is>
+      </c>
+      <c r="C82" s="37" t="n">
+        <v>8500000</v>
       </c>
     </row>
     <row r="83" ht="15" customHeight="1">
       <c r="B83" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Stabilized occupancy</t>
-        </is>
-      </c>
-      <c r="C83" s="31" t="n">
-        <v>0.95</v>
+          <t xml:space="preserve">   Land (SF)</t>
+        </is>
+      </c>
+      <c r="C83" s="36" t="n">
+        <v>30928</v>
       </c>
     </row>
     <row r="84" ht="15" customHeight="1">
       <c r="B84" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Insurance ($/yr)</t>
-        </is>
-      </c>
-      <c r="C84" s="35" t="n">
-        <v>40000</v>
+          <t xml:space="preserve">   Land value ($/SF)</t>
+        </is>
+      </c>
+      <c r="C84" s="34" t="n">
+        <v>248</v>
       </c>
     </row>
     <row r="85" ht="15" customHeight="1">
       <c r="B85" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   CAM ($/yr, recoverable)</t>
-        </is>
-      </c>
-      <c r="C85" s="35" t="n">
-        <v>40000</v>
+          <t xml:space="preserve">   Market rent ($/SF NNN)</t>
+        </is>
+      </c>
+      <c r="C85" s="34" t="n">
+        <v>34</v>
       </c>
     </row>
     <row r="86" ht="15" customHeight="1">
       <c r="B86" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Repairs &amp; maintenance ($/yr)</t>
-        </is>
-      </c>
-      <c r="C86" s="35" t="n">
-        <v>30000</v>
+          <t xml:space="preserve">   In-place occupancy</t>
+        </is>
+      </c>
+      <c r="C86" s="31" t="n">
+        <v>0.801</v>
       </c>
     </row>
     <row r="87" ht="15" customHeight="1">
       <c r="B87" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Management fee (% EGR)</t>
+          <t xml:space="preserve">   Stabilized occupancy</t>
         </is>
       </c>
       <c r="C87" s="31" t="n">
-        <v>0.04</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="88" ht="15" customHeight="1">
       <c r="B88" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Going-in cap</t>
-        </is>
-      </c>
-      <c r="C88" s="29" t="n">
-        <v>0.075</v>
+          <t xml:space="preserve">   Insurance ($/yr)</t>
+        </is>
+      </c>
+      <c r="C88" s="35" t="n">
+        <v>40000</v>
       </c>
     </row>
     <row r="89" ht="15" customHeight="1">
       <c r="B89" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Exit cap</t>
-        </is>
-      </c>
-      <c r="C89" s="29" t="n">
-        <v>0.0775</v>
+          <t xml:space="preserve">   CAM ($/yr, recoverable)</t>
+        </is>
+      </c>
+      <c r="C89" s="35" t="n">
+        <v>40000</v>
       </c>
     </row>
     <row r="90" ht="15" customHeight="1">
       <c r="B90" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Senior LTV</t>
-        </is>
-      </c>
-      <c r="C90" s="31" t="n">
-        <v>0.6</v>
+          <t xml:space="preserve">   Repairs &amp; maintenance ($/yr)</t>
+        </is>
+      </c>
+      <c r="C90" s="35" t="n">
+        <v>30000</v>
       </c>
     </row>
     <row r="91" ht="15" customHeight="1">
       <c r="B91" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Senior rate</t>
-        </is>
-      </c>
-      <c r="C91" s="29" t="n">
+          <t xml:space="preserve">   Management fee (% EGR)</t>
+        </is>
+      </c>
+      <c r="C91" s="31" t="n">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="92" ht="15" customHeight="1">
+      <c r="B92" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Going-in cap</t>
+        </is>
+      </c>
+      <c r="C92" s="29" t="n">
         <v>0.075</v>
       </c>
     </row>
-    <row r="92"/>
     <row r="93" ht="15" customHeight="1">
-      <c r="B93" s="15" t="inlineStr">
-        <is>
-          <t>Galleria Corporate Centre — office, Modified Gross  ⚠️ reported parcel</t>
-        </is>
-      </c>
-      <c r="C93" s="13" t="n"/>
-      <c r="D93" s="13" t="n"/>
-      <c r="E93" s="13" t="n"/>
-      <c r="F93" s="13" t="n"/>
-      <c r="G93" s="13" t="n"/>
-      <c r="H93" s="13" t="n"/>
-      <c r="I93" s="13" t="n"/>
-      <c r="J93" s="13" t="n"/>
-      <c r="K93" s="13" t="n"/>
-      <c r="L93" s="13" t="n"/>
-      <c r="M93" s="14" t="n"/>
+      <c r="B93" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Exit cap</t>
+        </is>
+      </c>
+      <c r="C93" s="29" t="n">
+        <v>0.0775</v>
+      </c>
     </row>
     <row r="94" ht="15" customHeight="1">
       <c r="B94" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Acquisition basis</t>
-        </is>
-      </c>
-      <c r="C94" s="37" t="n">
-        <v>21700000</v>
+          <t xml:space="preserve">   Senior LTV</t>
+        </is>
+      </c>
+      <c r="C94" s="31" t="n">
+        <v>0.6</v>
       </c>
     </row>
     <row r="95" ht="15" customHeight="1">
       <c r="B95" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Market rent ($/SF MG)</t>
-        </is>
-      </c>
-      <c r="C95" s="34" t="n">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="96" ht="15" customHeight="1">
-      <c r="B96" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   In-place occupancy</t>
-        </is>
-      </c>
-      <c r="C96" s="31" t="n">
-        <v>0.85</v>
-      </c>
-    </row>
+          <t xml:space="preserve">   Senior rate</t>
+        </is>
+      </c>
+      <c r="C95" s="29" t="n">
+        <v>0.075</v>
+      </c>
+    </row>
+    <row r="96"/>
     <row r="97" ht="15" customHeight="1">
-      <c r="B97" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Stabilized occupancy</t>
-        </is>
-      </c>
-      <c r="C97" s="31" t="n">
-        <v>0.88</v>
-      </c>
+      <c r="B97" s="15" t="inlineStr">
+        <is>
+          <t>Galleria Corporate Centre — office, Modified Gross  ⚠️ reported parcel</t>
+        </is>
+      </c>
+      <c r="C97" s="13" t="n"/>
+      <c r="D97" s="13" t="n"/>
+      <c r="E97" s="13" t="n"/>
+      <c r="F97" s="13" t="n"/>
+      <c r="G97" s="13" t="n"/>
+      <c r="H97" s="13" t="n"/>
+      <c r="I97" s="13" t="n"/>
+      <c r="J97" s="13" t="n"/>
+      <c r="K97" s="13" t="n"/>
+      <c r="L97" s="13" t="n"/>
+      <c r="M97" s="14" t="n"/>
     </row>
     <row r="98" ht="15" customHeight="1">
       <c r="B98" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Office opex ex-taxes ($/SF, landlord)</t>
-        </is>
-      </c>
-      <c r="C98" s="34" t="n">
-        <v>8</v>
+          <t xml:space="preserve">   Acquisition basis</t>
+        </is>
+      </c>
+      <c r="C98" s="37" t="n">
+        <v>21700000</v>
       </c>
     </row>
     <row r="99" ht="15" customHeight="1">
       <c r="B99" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Management fee (% EGR)</t>
-        </is>
-      </c>
-      <c r="C99" s="31" t="n">
-        <v>0.03</v>
+          <t xml:space="preserve">   Market rent ($/SF MG)</t>
+        </is>
+      </c>
+      <c r="C99" s="34" t="n">
+        <v>26</v>
       </c>
     </row>
     <row r="100" ht="15" customHeight="1">
       <c r="B100" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Going-in cap</t>
-        </is>
-      </c>
-      <c r="C100" s="29" t="n">
-        <v>0.08</v>
+          <t xml:space="preserve">   In-place occupancy</t>
+        </is>
+      </c>
+      <c r="C100" s="31" t="n">
+        <v>0.85</v>
       </c>
     </row>
     <row r="101" ht="15" customHeight="1">
       <c r="B101" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Exit cap</t>
-        </is>
-      </c>
-      <c r="C101" s="29" t="n">
-        <v>0.0825</v>
+          <t xml:space="preserve">   Stabilized occupancy</t>
+        </is>
+      </c>
+      <c r="C101" s="31" t="n">
+        <v>0.88</v>
       </c>
     </row>
     <row r="102" ht="15" customHeight="1">
       <c r="B102" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Senior LTV</t>
-        </is>
-      </c>
-      <c r="C102" s="31" t="n">
-        <v>0.55</v>
+          <t xml:space="preserve">   Office opex ex-taxes ($/SF, landlord)</t>
+        </is>
+      </c>
+      <c r="C102" s="34" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="103" ht="15" customHeight="1">
       <c r="B103" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Senior rate</t>
-        </is>
-      </c>
-      <c r="C103" s="29" t="n">
-        <v>0.075</v>
-      </c>
-    </row>
-    <row r="104"/>
+          <t xml:space="preserve">   Management fee (% EGR)</t>
+        </is>
+      </c>
+      <c r="C103" s="31" t="n">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="104" ht="15" customHeight="1">
+      <c r="B104" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Going-in cap</t>
+        </is>
+      </c>
+      <c r="C104" s="29" t="n">
+        <v>0.08</v>
+      </c>
+    </row>
     <row r="105" ht="15" customHeight="1">
-      <c r="B105" s="15" t="inlineStr">
-        <is>
-          <t>1040 Bayview — covered land (interim office)  ⚠️ reported parcel</t>
-        </is>
-      </c>
-      <c r="C105" s="13" t="n"/>
-      <c r="D105" s="13" t="n"/>
-      <c r="E105" s="13" t="n"/>
-      <c r="F105" s="13" t="n"/>
-      <c r="G105" s="13" t="n"/>
-      <c r="H105" s="13" t="n"/>
-      <c r="I105" s="13" t="n"/>
-      <c r="J105" s="13" t="n"/>
-      <c r="K105" s="13" t="n"/>
-      <c r="L105" s="13" t="n"/>
-      <c r="M105" s="14" t="n"/>
+      <c r="B105" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Exit cap</t>
+        </is>
+      </c>
+      <c r="C105" s="29" t="n">
+        <v>0.0825</v>
+      </c>
     </row>
     <row r="106" ht="15" customHeight="1">
       <c r="B106" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Acquisition basis (entitled land)</t>
-        </is>
-      </c>
-      <c r="C106" s="37" t="n">
-        <v>13000000</v>
+          <t xml:space="preserve">   Senior LTV</t>
+        </is>
+      </c>
+      <c r="C106" s="31" t="n">
+        <v>0.55</v>
       </c>
     </row>
     <row r="107" ht="15" customHeight="1">
       <c r="B107" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Interim office occupancy</t>
-        </is>
-      </c>
-      <c r="C107" s="31" t="n">
-        <v>0.72</v>
-      </c>
-    </row>
-    <row r="108" ht="15" customHeight="1">
-      <c r="B108" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Interim office rent ($/SF MG)</t>
-        </is>
-      </c>
-      <c r="C108" s="34" t="n">
-        <v>23</v>
-      </c>
-    </row>
+          <t xml:space="preserve">   Senior rate</t>
+        </is>
+      </c>
+      <c r="C107" s="29" t="n">
+        <v>0.075</v>
+      </c>
+    </row>
+    <row r="108"/>
     <row r="109" ht="15" customHeight="1">
-      <c r="B109" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Interim office opex ($/SF)</t>
-        </is>
-      </c>
-      <c r="C109" s="34" t="n">
-        <v>8</v>
-      </c>
+      <c r="B109" s="15" t="inlineStr">
+        <is>
+          <t>1040 Bayview — covered land (interim office)  ⚠️ reported parcel</t>
+        </is>
+      </c>
+      <c r="C109" s="13" t="n"/>
+      <c r="D109" s="13" t="n"/>
+      <c r="E109" s="13" t="n"/>
+      <c r="F109" s="13" t="n"/>
+      <c r="G109" s="13" t="n"/>
+      <c r="H109" s="13" t="n"/>
+      <c r="I109" s="13" t="n"/>
+      <c r="J109" s="13" t="n"/>
+      <c r="K109" s="13" t="n"/>
+      <c r="L109" s="13" t="n"/>
+      <c r="M109" s="14" t="n"/>
     </row>
     <row r="110" ht="15" customHeight="1">
       <c r="B110" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Management fee (% EGR)</t>
-        </is>
-      </c>
-      <c r="C110" s="31" t="n">
-        <v>0.03</v>
+          <t xml:space="preserve">   Acquisition basis (entitled land)</t>
+        </is>
+      </c>
+      <c r="C110" s="37" t="n">
+        <v>13000000</v>
       </c>
     </row>
     <row r="111" ht="15" customHeight="1">
       <c r="B111" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Land loan LTV</t>
+          <t xml:space="preserve">   Interim office occupancy</t>
         </is>
       </c>
       <c r="C111" s="31" t="n">
-        <v>0.4</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="112" ht="15" customHeight="1">
       <c r="B112" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Land loan rate</t>
-        </is>
-      </c>
-      <c r="C112" s="29" t="n">
-        <v>0.08500000000000001</v>
-      </c>
-    </row>
-    <row r="113"/>
-    <row r="114">
-      <c r="B114" s="11" t="inlineStr">
-        <is>
-          <t>DATA-GAP REGISTER  —  reported figures to verify at BCPA (shown live from source)</t>
-        </is>
-      </c>
-      <c r="C114" s="2" t="n"/>
-      <c r="D114" s="2" t="n"/>
-      <c r="E114" s="2" t="n"/>
-      <c r="F114" s="2" t="n"/>
-      <c r="G114" s="2" t="n"/>
-      <c r="H114" s="2" t="n"/>
-      <c r="I114" s="2" t="n"/>
-      <c r="J114" s="2" t="n"/>
-      <c r="K114" s="2" t="n"/>
-      <c r="L114" s="2" t="n"/>
-      <c r="M114" s="3" t="n"/>
+          <t xml:space="preserve">   Interim office rent ($/SF MG)</t>
+        </is>
+      </c>
+      <c r="C112" s="34" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="113" ht="15" customHeight="1">
+      <c r="B113" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Interim office opex ($/SF)</t>
+        </is>
+      </c>
+      <c r="C113" s="34" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="114" ht="15" customHeight="1">
+      <c r="B114" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Management fee (% EGR)</t>
+        </is>
+      </c>
+      <c r="C114" s="31" t="n">
+        <v>0.03</v>
+      </c>
     </row>
     <row r="115" ht="15" customHeight="1">
-      <c r="B115" s="15" t="inlineStr">
-        <is>
-          <t>Figure</t>
-        </is>
-      </c>
-      <c r="C115" s="16" t="inlineStr">
-        <is>
-          <t>Current</t>
-        </is>
-      </c>
-      <c r="D115" s="16" t="inlineStr">
-        <is>
-          <t>Flag</t>
-        </is>
-      </c>
-      <c r="E115" s="15" t="inlineStr">
-        <is>
-          <t>Lives on</t>
-        </is>
-      </c>
-      <c r="F115" s="13" t="n"/>
-      <c r="G115" s="13" t="n"/>
-      <c r="H115" s="13" t="n"/>
-      <c r="I115" s="13" t="n"/>
-      <c r="J115" s="13" t="n"/>
-      <c r="K115" s="13" t="n"/>
-      <c r="L115" s="13" t="n"/>
-      <c r="M115" s="14" t="n"/>
+      <c r="B115" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Land loan LTV</t>
+        </is>
+      </c>
+      <c r="C115" s="31" t="n">
+        <v>0.4</v>
+      </c>
     </row>
     <row r="116" ht="15" customHeight="1">
       <c r="B116" s="12" t="inlineStr">
         <is>
-          <t>Sunrise Plaza — value / basis</t>
-        </is>
-      </c>
-      <c r="C116" s="38">
-        <f>'Assumptions'!C78</f>
-        <v/>
-      </c>
-      <c r="D116" s="30" t="inlineStr">
-        <is>
-          <t>⚠️</t>
-        </is>
-      </c>
-      <c r="E116" s="22" t="inlineStr">
-        <is>
-          <t>Assumptions · Sunrise block</t>
-        </is>
-      </c>
-      <c r="F116" s="13" t="n"/>
-      <c r="G116" s="13" t="n"/>
-      <c r="H116" s="13" t="n"/>
-      <c r="I116" s="13" t="n"/>
-      <c r="J116" s="13" t="n"/>
-      <c r="K116" s="13" t="n"/>
-      <c r="L116" s="13" t="n"/>
-      <c r="M116" s="14" t="n"/>
-    </row>
-    <row r="117" ht="15" customHeight="1">
-      <c r="B117" s="12" t="inlineStr">
-        <is>
-          <t>Sunrise Plaza — building SF</t>
-        </is>
-      </c>
-      <c r="C117" s="39">
-        <f>'Sunrise Plaza'!C27</f>
-        <v/>
-      </c>
-      <c r="D117" s="30" t="inlineStr">
-        <is>
-          <t>⚠️</t>
-        </is>
-      </c>
-      <c r="E117" s="22" t="inlineStr">
-        <is>
-          <t>Sunrise Plaza tab</t>
-        </is>
-      </c>
-      <c r="F117" s="13" t="n"/>
-      <c r="G117" s="13" t="n"/>
-      <c r="H117" s="13" t="n"/>
-      <c r="I117" s="13" t="n"/>
-      <c r="J117" s="13" t="n"/>
-      <c r="K117" s="13" t="n"/>
-      <c r="L117" s="13" t="n"/>
-      <c r="M117" s="14" t="n"/>
-    </row>
-    <row r="118" ht="15" customHeight="1">
-      <c r="B118" s="12" t="inlineStr">
-        <is>
-          <t>Sunrise Plaza — land SF</t>
-        </is>
-      </c>
-      <c r="C118" s="39">
-        <f>'Assumptions'!C79</f>
-        <v/>
-      </c>
-      <c r="D118" s="30" t="inlineStr">
-        <is>
-          <t>⚠️</t>
-        </is>
-      </c>
-      <c r="E118" s="22" t="inlineStr">
-        <is>
-          <t>Assumptions · Sunrise block</t>
-        </is>
-      </c>
-      <c r="F118" s="13" t="n"/>
-      <c r="G118" s="13" t="n"/>
-      <c r="H118" s="13" t="n"/>
-      <c r="I118" s="13" t="n"/>
-      <c r="J118" s="13" t="n"/>
-      <c r="K118" s="13" t="n"/>
-      <c r="L118" s="13" t="n"/>
-      <c r="M118" s="14" t="n"/>
+          <t xml:space="preserve">   Land loan rate</t>
+        </is>
+      </c>
+      <c r="C116" s="29" t="n">
+        <v>0.08500000000000001</v>
+      </c>
+    </row>
+    <row r="117"/>
+    <row r="118">
+      <c r="B118" s="11" t="inlineStr">
+        <is>
+          <t>DATA-GAP REGISTER  —  reported figures to verify at BCPA (shown live from source)</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="n"/>
+      <c r="D118" s="2" t="n"/>
+      <c r="E118" s="2" t="n"/>
+      <c r="F118" s="2" t="n"/>
+      <c r="G118" s="2" t="n"/>
+      <c r="H118" s="2" t="n"/>
+      <c r="I118" s="2" t="n"/>
+      <c r="J118" s="2" t="n"/>
+      <c r="K118" s="2" t="n"/>
+      <c r="L118" s="2" t="n"/>
+      <c r="M118" s="3" t="n"/>
     </row>
     <row r="119" ht="15" customHeight="1">
-      <c r="B119" s="12" t="inlineStr">
-        <is>
-          <t>Office — building SF</t>
-        </is>
-      </c>
-      <c r="C119" s="39">
-        <f>'Office Condo'!C15</f>
-        <v/>
-      </c>
-      <c r="D119" s="30" t="inlineStr">
-        <is>
-          <t>⚠️</t>
-        </is>
-      </c>
-      <c r="E119" s="22" t="inlineStr">
-        <is>
-          <t>Office Condo tab</t>
+      <c r="B119" s="15" t="inlineStr">
+        <is>
+          <t>Figure</t>
+        </is>
+      </c>
+      <c r="C119" s="16" t="inlineStr">
+        <is>
+          <t>Current</t>
+        </is>
+      </c>
+      <c r="D119" s="16" t="inlineStr">
+        <is>
+          <t>Flag</t>
+        </is>
+      </c>
+      <c r="E119" s="15" t="inlineStr">
+        <is>
+          <t>Lives on</t>
         </is>
       </c>
       <c r="F119" s="13" t="n"/>
@@ -7048,11 +6994,11 @@
     <row r="120" ht="15" customHeight="1">
       <c r="B120" s="12" t="inlineStr">
         <is>
-          <t>Office — Main St Fund SF (57.4%)</t>
-        </is>
-      </c>
-      <c r="C120" s="39">
-        <f>'Office Condo'!D87</f>
+          <t>Sunrise Plaza — value / basis</t>
+        </is>
+      </c>
+      <c r="C120" s="38">
+        <f>'Assumptions'!C82</f>
         <v/>
       </c>
       <c r="D120" s="30" t="inlineStr">
@@ -7062,7 +7008,7 @@
       </c>
       <c r="E120" s="22" t="inlineStr">
         <is>
-          <t>Office Condo tab</t>
+          <t>Assumptions · Sunrise block</t>
         </is>
       </c>
       <c r="F120" s="13" t="n"/>
@@ -7077,11 +7023,11 @@
     <row r="121" ht="15" customHeight="1">
       <c r="B121" s="12" t="inlineStr">
         <is>
-          <t>Office — Intl Sunrise SF (42.6%)</t>
+          <t>Sunrise Plaza — building SF</t>
         </is>
       </c>
       <c r="C121" s="39">
-        <f>'Office Condo'!D88</f>
+        <f>'Sunrise Plaza'!C27</f>
         <v/>
       </c>
       <c r="D121" s="30" t="inlineStr">
@@ -7091,7 +7037,7 @@
       </c>
       <c r="E121" s="22" t="inlineStr">
         <is>
-          <t>Office Condo tab</t>
+          <t>Sunrise Plaza tab</t>
         </is>
       </c>
       <c r="F121" s="13" t="n"/>
@@ -7106,21 +7052,21 @@
     <row r="122" ht="15" customHeight="1">
       <c r="B122" s="12" t="inlineStr">
         <is>
-          <t>Office — acquisition basis</t>
-        </is>
-      </c>
-      <c r="C122" s="38">
-        <f>'Assumptions'!C94</f>
+          <t>Sunrise Plaza — land SF</t>
+        </is>
+      </c>
+      <c r="C122" s="39">
+        <f>'Assumptions'!C83</f>
         <v/>
       </c>
       <c r="D122" s="30" t="inlineStr">
         <is>
-          <t>🔶</t>
+          <t>⚠️</t>
         </is>
       </c>
       <c r="E122" s="22" t="inlineStr">
         <is>
-          <t>Assumptions · Office block</t>
+          <t>Assumptions · Sunrise block</t>
         </is>
       </c>
       <c r="F122" s="13" t="n"/>
@@ -7135,11 +7081,11 @@
     <row r="123" ht="15" customHeight="1">
       <c r="B123" s="12" t="inlineStr">
         <is>
-          <t>1040 Bayview — land SF</t>
+          <t>Office — building SF</t>
         </is>
       </c>
       <c r="C123" s="39">
-        <f>'Land'!C15</f>
+        <f>'Office Condo'!C15</f>
         <v/>
       </c>
       <c r="D123" s="30" t="inlineStr">
@@ -7149,7 +7095,7 @@
       </c>
       <c r="E123" s="22" t="inlineStr">
         <is>
-          <t>Land tab</t>
+          <t>Office Condo tab</t>
         </is>
       </c>
       <c r="F123" s="13" t="n"/>
@@ -7164,11 +7110,11 @@
     <row r="124" ht="15" customHeight="1">
       <c r="B124" s="12" t="inlineStr">
         <is>
-          <t>1040 Bayview — office SF</t>
+          <t>Office — Main St Fund SF (57.4%)</t>
         </is>
       </c>
       <c r="C124" s="39">
-        <f>'Land'!C16</f>
+        <f>'Office Condo'!D87</f>
         <v/>
       </c>
       <c r="D124" s="30" t="inlineStr">
@@ -7178,7 +7124,7 @@
       </c>
       <c r="E124" s="22" t="inlineStr">
         <is>
-          <t>Land tab</t>
+          <t>Office Condo tab</t>
         </is>
       </c>
       <c r="F124" s="13" t="n"/>
@@ -7193,11 +7139,11 @@
     <row r="125" ht="15" customHeight="1">
       <c r="B125" s="12" t="inlineStr">
         <is>
-          <t>1040 Bayview — entitled units</t>
+          <t>Office — Intl Sunrise SF (42.6%)</t>
         </is>
       </c>
       <c r="C125" s="39">
-        <f>'Land'!C17</f>
+        <f>'Office Condo'!D88</f>
         <v/>
       </c>
       <c r="D125" s="30" t="inlineStr">
@@ -7207,7 +7153,7 @@
       </c>
       <c r="E125" s="22" t="inlineStr">
         <is>
-          <t>Land tab</t>
+          <t>Office Condo tab</t>
         </is>
       </c>
       <c r="F125" s="13" t="n"/>
@@ -7222,21 +7168,21 @@
     <row r="126" ht="15" customHeight="1">
       <c r="B126" s="12" t="inlineStr">
         <is>
-          <t>1040 Bayview — BCPA value</t>
+          <t>Office — acquisition basis</t>
         </is>
       </c>
       <c r="C126" s="38">
-        <f>'Land'!C18</f>
+        <f>'Assumptions'!C98</f>
         <v/>
       </c>
       <c r="D126" s="30" t="inlineStr">
         <is>
-          <t>⚠️</t>
+          <t>🔶</t>
         </is>
       </c>
       <c r="E126" s="22" t="inlineStr">
         <is>
-          <t>Land tab</t>
+          <t>Assumptions · Office block</t>
         </is>
       </c>
       <c r="F126" s="13" t="n"/>
@@ -7248,19 +7194,55 @@
       <c r="L126" s="13" t="n"/>
       <c r="M126" s="14" t="n"/>
     </row>
-    <row r="127"/>
-    <row r="128" ht="39" customHeight="1">
-      <c r="B128" s="40" t="inlineStr">
-        <is>
-          <t>How to use</t>
-        </is>
-      </c>
-      <c r="D128" s="40" t="inlineStr">
-        <is>
-          <t>Everything you tune is on THIS tab: global drivers up top, then a block per asset (price · rents · occupancy · operating expenses · caps · debt). Standard modeling params (rent/expense growth, TI/LC, reserves, closing detail) remain blue on each asset tab. ⚠️ = reported, verify at bcpa.net. Change any blue cell → the model recalculates.</t>
-        </is>
-      </c>
-      <c r="E128" s="13" t="n"/>
+    <row r="127" ht="15" customHeight="1">
+      <c r="B127" s="12" t="inlineStr">
+        <is>
+          <t>1040 Bayview — land SF</t>
+        </is>
+      </c>
+      <c r="C127" s="39">
+        <f>'Land'!C15</f>
+        <v/>
+      </c>
+      <c r="D127" s="30" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
+      <c r="E127" s="22" t="inlineStr">
+        <is>
+          <t>Land tab</t>
+        </is>
+      </c>
+      <c r="F127" s="13" t="n"/>
+      <c r="G127" s="13" t="n"/>
+      <c r="H127" s="13" t="n"/>
+      <c r="I127" s="13" t="n"/>
+      <c r="J127" s="13" t="n"/>
+      <c r="K127" s="13" t="n"/>
+      <c r="L127" s="13" t="n"/>
+      <c r="M127" s="14" t="n"/>
+    </row>
+    <row r="128" ht="15" customHeight="1">
+      <c r="B128" s="12" t="inlineStr">
+        <is>
+          <t>1040 Bayview — office SF</t>
+        </is>
+      </c>
+      <c r="C128" s="39">
+        <f>'Land'!C16</f>
+        <v/>
+      </c>
+      <c r="D128" s="30" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
+      <c r="E128" s="22" t="inlineStr">
+        <is>
+          <t>Land tab</t>
+        </is>
+      </c>
       <c r="F128" s="13" t="n"/>
       <c r="G128" s="13" t="n"/>
       <c r="H128" s="13" t="n"/>
@@ -7270,65 +7252,145 @@
       <c r="L128" s="13" t="n"/>
       <c r="M128" s="14" t="n"/>
     </row>
+    <row r="129" ht="15" customHeight="1">
+      <c r="B129" s="12" t="inlineStr">
+        <is>
+          <t>1040 Bayview — entitled units</t>
+        </is>
+      </c>
+      <c r="C129" s="39">
+        <f>'Land'!C17</f>
+        <v/>
+      </c>
+      <c r="D129" s="30" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
+      <c r="E129" s="22" t="inlineStr">
+        <is>
+          <t>Land tab</t>
+        </is>
+      </c>
+      <c r="F129" s="13" t="n"/>
+      <c r="G129" s="13" t="n"/>
+      <c r="H129" s="13" t="n"/>
+      <c r="I129" s="13" t="n"/>
+      <c r="J129" s="13" t="n"/>
+      <c r="K129" s="13" t="n"/>
+      <c r="L129" s="13" t="n"/>
+      <c r="M129" s="14" t="n"/>
+    </row>
+    <row r="130" ht="15" customHeight="1">
+      <c r="B130" s="12" t="inlineStr">
+        <is>
+          <t>1040 Bayview — BCPA value</t>
+        </is>
+      </c>
+      <c r="C130" s="38">
+        <f>'Land'!C18</f>
+        <v/>
+      </c>
+      <c r="D130" s="30" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
+      <c r="E130" s="22" t="inlineStr">
+        <is>
+          <t>Land tab</t>
+        </is>
+      </c>
+      <c r="F130" s="13" t="n"/>
+      <c r="G130" s="13" t="n"/>
+      <c r="H130" s="13" t="n"/>
+      <c r="I130" s="13" t="n"/>
+      <c r="J130" s="13" t="n"/>
+      <c r="K130" s="13" t="n"/>
+      <c r="L130" s="13" t="n"/>
+      <c r="M130" s="14" t="n"/>
+    </row>
+    <row r="131"/>
+    <row r="132" ht="39" customHeight="1">
+      <c r="B132" s="40" t="inlineStr">
+        <is>
+          <t>How to use</t>
+        </is>
+      </c>
+      <c r="D132" s="40" t="inlineStr">
+        <is>
+          <t>Everything you tune is on THIS tab: global drivers up top, then a block per asset (price · rents · occupancy · operating expenses · caps · debt). Standard modeling params (rent/expense growth, TI/LC, reserves, closing detail) remain blue on each asset tab. ⚠️ = reported, verify at bcpa.net. Change any blue cell → the model recalculates.</t>
+        </is>
+      </c>
+      <c r="E132" s="13" t="n"/>
+      <c r="F132" s="13" t="n"/>
+      <c r="G132" s="13" t="n"/>
+      <c r="H132" s="13" t="n"/>
+      <c r="I132" s="13" t="n"/>
+      <c r="J132" s="13" t="n"/>
+      <c r="K132" s="13" t="n"/>
+      <c r="L132" s="13" t="n"/>
+      <c r="M132" s="14" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="61">
     <mergeCell ref="B2:M2"/>
     <mergeCell ref="E29:M29"/>
+    <mergeCell ref="E128:M128"/>
     <mergeCell ref="E10:M10"/>
     <mergeCell ref="E28:M28"/>
     <mergeCell ref="E13:M13"/>
     <mergeCell ref="B61:M61"/>
     <mergeCell ref="E40:M40"/>
     <mergeCell ref="E9:M9"/>
-    <mergeCell ref="E118:M118"/>
     <mergeCell ref="E31:M31"/>
     <mergeCell ref="B1:M1"/>
     <mergeCell ref="E34:M34"/>
     <mergeCell ref="B44:M44"/>
     <mergeCell ref="E6:M6"/>
     <mergeCell ref="E15:M15"/>
+    <mergeCell ref="D132:M132"/>
     <mergeCell ref="E11:M11"/>
     <mergeCell ref="B19:M19"/>
     <mergeCell ref="E27:M27"/>
     <mergeCell ref="E36:M36"/>
     <mergeCell ref="E119:M119"/>
     <mergeCell ref="E26:M26"/>
-    <mergeCell ref="E116:M116"/>
+    <mergeCell ref="B118:M118"/>
     <mergeCell ref="E124:M124"/>
     <mergeCell ref="B30:M30"/>
     <mergeCell ref="E120:M120"/>
-    <mergeCell ref="D128:M128"/>
     <mergeCell ref="E16:M16"/>
     <mergeCell ref="E32:M32"/>
     <mergeCell ref="E7:M7"/>
-    <mergeCell ref="B77:M77"/>
     <mergeCell ref="E125:M125"/>
     <mergeCell ref="E41:M41"/>
-    <mergeCell ref="B114:M114"/>
     <mergeCell ref="E37:M37"/>
     <mergeCell ref="B45:M45"/>
     <mergeCell ref="E22:M22"/>
-    <mergeCell ref="E115:M115"/>
     <mergeCell ref="E18:M18"/>
+    <mergeCell ref="B97:M97"/>
     <mergeCell ref="E21:M21"/>
     <mergeCell ref="B4:M4"/>
     <mergeCell ref="E121:M121"/>
+    <mergeCell ref="B109:M109"/>
+    <mergeCell ref="E130:M130"/>
     <mergeCell ref="E24:M24"/>
+    <mergeCell ref="B81:M81"/>
     <mergeCell ref="B25:M25"/>
     <mergeCell ref="E33:M33"/>
-    <mergeCell ref="E117:M117"/>
     <mergeCell ref="E122:M122"/>
+    <mergeCell ref="E129:M129"/>
     <mergeCell ref="E5:M5"/>
     <mergeCell ref="E23:M23"/>
     <mergeCell ref="E42:M42"/>
     <mergeCell ref="E14:M14"/>
+    <mergeCell ref="E127:M127"/>
     <mergeCell ref="E123:M123"/>
-    <mergeCell ref="B93:M93"/>
     <mergeCell ref="E17:M17"/>
     <mergeCell ref="E39:M39"/>
     <mergeCell ref="E8:M8"/>
     <mergeCell ref="E126:M126"/>
-    <mergeCell ref="B105:M105"/>
     <mergeCell ref="E35:M35"/>
     <mergeCell ref="B12:M12"/>
     <mergeCell ref="E20:M20"/>
@@ -11396,7 +11458,7 @@
         </is>
       </c>
       <c r="C13" s="17">
-        <f>'Publix &amp; Starbucks'!C67</f>
+        <f>'Publix &amp; Starbucks'!C44</f>
         <v/>
       </c>
       <c r="D13" s="17">
@@ -11425,7 +11487,7 @@
       </c>
       <c r="J13" s="12" t="inlineStr">
         <is>
-          <t>NOT a seller · priced at land value</t>
+          <t>sale-leaseback · acquire fee, lease back</t>
         </is>
       </c>
       <c r="K13" s="13" t="n"/>
@@ -15935,7 +15997,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>PUBLIX + STARBUCKS  ·  SHADOW-ANCHOR PAD</t>
+          <t>PUBLIX + STARBUCKS  ·  SALE-LEASEBACK  (acquire fee, lease back during entitlement)</t>
         </is>
       </c>
       <c r="C1" s="2" t="n"/>
@@ -15950,10 +16012,10 @@
       <c r="L1" s="2" t="n"/>
       <c r="M1" s="3" t="n"/>
     </row>
-    <row r="2" ht="18" customHeight="1">
+    <row r="2" ht="31" customHeight="1">
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>2501–2519 E Sunrise Blvd   |   Folio 49-42-36-12-0060   |   REAL SUB LLC (Publix) — fee owner, NOT a seller · 36,822 SF · built 2011 · valued off the rent it produces</t>
+          <t>2501–2519 E Sunrise Blvd   |   Folio 49-42-36-12-0060   |   REAL SUB LLC (Publix) · 36,822 SF · built 2011 · acquire the fee → Publix leases back → rent covers carry while you entitle the land</t>
         </is>
       </c>
       <c r="C2" s="2" t="n"/>
@@ -15972,7 +16034,7 @@
     <row r="4">
       <c r="B4" s="11" t="inlineStr">
         <is>
-          <t>PROPERTY FACTS  —  ✅ BCPA / ⚠️ REPORTED (Publix is not a seller — modeled as a mark-to-market case)</t>
+          <t>PROPERTY FACTS  —  ✅ BCPA / 🔶 SALE-LEASEBACK STRUCTURE (leaseback terms on the Assumptions tab)</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -15990,12 +16052,12 @@
     <row r="5" ht="15" customHeight="1">
       <c r="B5" s="70" t="inlineStr">
         <is>
-          <t>Record owner</t>
+          <t>Record owner (today)</t>
         </is>
       </c>
       <c r="D5" s="70" t="inlineStr">
         <is>
-          <t>REAL SUB LLC (Publix Super Markets real-estate entity, Lakeland FL)</t>
+          <t>REAL SUB LLC (Publix Super Markets real-estate entity, Lakeland FL) — fee owner</t>
         </is>
       </c>
       <c r="E5" s="13" t="n"/>
@@ -16011,12 +16073,12 @@
     <row r="6" ht="15" customHeight="1">
       <c r="B6" s="12" t="inlineStr">
         <is>
-          <t>Status</t>
+          <t>Deal structure</t>
         </is>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
-          <t>Publix bought the FEE under its own store 03/2025 — NOT a seller; modeled as assumption case</t>
+          <t>Sale-leaseback: DAWN RE acquires the fee; Publix leases back and pays rent during the entitlement period, then vacates for redevelopment</t>
         </is>
       </c>
       <c r="E6" s="13" t="n"/>
@@ -16037,7 +16099,7 @@
       </c>
       <c r="D7" s="70" t="inlineStr">
         <is>
-          <t>36,822 SF (Publix ~34,622 SF + Starbucks drive-thru pad ~2,200 SF)</t>
+          <t>36,822 SF (Publix ~34,622 SF leaseback + Starbucks drive-thru pad ~2,200 SF)</t>
         </is>
       </c>
       <c r="E7" s="13" t="n"/>
@@ -16121,7 +16183,7 @@
       </c>
       <c r="D11" s="70" t="inlineStr">
         <is>
-          <t>$208,467   (2024: $217,404)</t>
+          <t>$208,467   (2024: $217,404) — NNN, reimbursed by Publix during leaseback</t>
         </is>
       </c>
       <c r="E11" s="13" t="n"/>
@@ -16137,12 +16199,12 @@
     <row r="12" ht="15" customHeight="1">
       <c r="B12" s="12" t="inlineStr">
         <is>
-          <t>Rent economics (market)</t>
+          <t>Leaseback economics</t>
         </is>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
-          <t>Publix ~$13/SF NNN (newer FL store); Starbucks pad ~$60/SF NNN</t>
+          <t>Publix leaseback ~$22/SF NNN (bridge rate) + Starbucks pad ~$60/SF NNN; ~4-yr term (adjustable on Assumptions tab)</t>
         </is>
       </c>
       <c r="E12" s="13" t="n"/>
@@ -16158,12 +16220,12 @@
     <row r="13" ht="15" customHeight="1">
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>Cap rates (market)</t>
+          <t>Covered-land logic</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>Grocery-anchored 6.0–6.75%; Starbucks pad 4.75–5.5%</t>
+          <t>The leaseback rent covers the operating carry (Publix pays taxes/ins NNN) while the land is entitled; the play is the dirt, not the current yield</t>
         </is>
       </c>
       <c r="E13" s="13" t="n"/>
@@ -16176,15 +16238,15 @@
       <c r="L13" s="13" t="n"/>
       <c r="M13" s="14" t="n"/>
     </row>
-    <row r="14" ht="15" customHeight="1">
+    <row r="14" ht="27" customHeight="1">
       <c r="B14" s="12" t="inlineStr">
         <is>
-          <t>Covered-land insight</t>
+          <t>Standalone return (below)</t>
         </is>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
-          <t>Publix paid $25M (land value) vs. ~$9–10M rent-supported income value — the land premium IS the covered-land thesis</t>
+          <t>NEGATIVE on a pure income basis by design — you pay land value ($25M) for income supporting only ~$13M. The return is the LAND, realized via the assemblage / redevelopment; the leaseback (DSCR ≈ 1.0x) simply covers the entitlement carry</t>
         </is>
       </c>
       <c r="E14" s="13" t="n"/>
@@ -16201,7 +16263,7 @@
     <row r="16">
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>RENT DETAIL  —  🔶 market mark-to-market (Publix is fee-owned; no contract rent flows today)</t>
+          <t>RENT ROLL  —  🔶 sale-leaseback terms (set on the Assumptions tab · Publix block)</t>
         </is>
       </c>
       <c r="C16" s="2" t="n"/>
@@ -16254,17 +16316,17 @@
       </c>
       <c r="M17" s="14" t="n"/>
     </row>
-    <row r="18" ht="15" customHeight="1">
+    <row r="18" ht="27" customHeight="1">
       <c r="B18" s="12" t="inlineStr">
         <is>
-          <t>Publix Super Market</t>
+          <t>Publix (sale-leaseback)</t>
         </is>
       </c>
       <c r="C18" s="13" t="n"/>
       <c r="D18" s="14" t="n"/>
       <c r="E18" s="12" t="inlineStr">
         <is>
-          <t>Grocery anchor (credit)</t>
+          <t>Grocery anchor (credit) — leases back during entitlement</t>
         </is>
       </c>
       <c r="F18" s="14" t="n"/>
@@ -16272,7 +16334,7 @@
         <v>34622</v>
       </c>
       <c r="H18" s="71" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="I18" s="47">
         <f>G18*H18</f>
@@ -16282,7 +16344,7 @@
       <c r="K18" s="14" t="n"/>
       <c r="L18" s="12" t="inlineStr">
         <is>
-          <t>~$13/SF NNN newer store</t>
+          <t>leaseback NNN; terms on Assumptions tab</t>
         </is>
       </c>
       <c r="M18" s="14" t="n"/>
@@ -16315,12 +16377,12 @@
       <c r="K19" s="14" t="n"/>
       <c r="L19" s="12" t="inlineStr">
         <is>
-          <t>~$60/SF NNN pad</t>
+          <t>pad NNN; terms on Assumptions tab</t>
         </is>
       </c>
       <c r="M19" s="14" t="n"/>
     </row>
-    <row r="20" ht="15" customHeight="1">
+    <row r="20" ht="27" customHeight="1">
       <c r="B20" s="19" t="inlineStr">
         <is>
           <t>TOTAL / WTD AVG</t>
@@ -16346,7 +16408,7 @@
       <c r="K20" s="14" t="n"/>
       <c r="L20" s="19" t="inlineStr">
         <is>
-          <t>100% occ · credit tenants</t>
+          <t>100% occ · credit tenants · sale-leaseback</t>
         </is>
       </c>
       <c r="M20" s="14" t="n"/>
@@ -16444,7 +16506,7 @@
         </is>
       </c>
       <c r="C26" s="18">
-        <f>'Assumptions'!C66</f>
+        <f>'Assumptions'!C70</f>
         <v/>
       </c>
       <c r="D26" s="22" t="inlineStr">
@@ -16469,7 +16531,7 @@
         </is>
       </c>
       <c r="C27" s="18">
-        <f>'Assumptions'!C67</f>
+        <f>'Assumptions'!C71</f>
         <v/>
       </c>
       <c r="D27" s="22" t="inlineStr">
@@ -16490,16 +16552,16 @@
     <row r="28" ht="15" customHeight="1">
       <c r="B28" s="12" t="inlineStr">
         <is>
-          <t>Market rent ($/SF NNN)</t>
+          <t>Blended NNN rent ($/SF) — leaseback + pad</t>
         </is>
       </c>
       <c r="C28" s="26">
-        <f>'Assumptions'!C65</f>
+        <f>('Assumptions'!C66*'Assumptions'!C65+'Assumptions'!C68*'Assumptions'!C67)/C24</f>
         <v/>
       </c>
       <c r="D28" s="22" t="inlineStr">
         <is>
-          <t>🟢 Assumptions</t>
+          <t>🟢 computed from Publix leaseback + Starbucks pad (Assumptions)</t>
         </is>
       </c>
       <c r="E28" s="13" t="n"/>
@@ -16609,7 +16671,7 @@
         </is>
       </c>
       <c r="C33" s="23">
-        <f>'Assumptions'!C68</f>
+        <f>'Assumptions'!C72</f>
         <v/>
       </c>
       <c r="D33" s="22" t="inlineStr">
@@ -16634,7 +16696,7 @@
         </is>
       </c>
       <c r="C34" s="23">
-        <f>'Assumptions'!C69</f>
+        <f>'Assumptions'!C73</f>
         <v/>
       </c>
       <c r="D34" s="22" t="inlineStr">
@@ -16659,7 +16721,7 @@
         </is>
       </c>
       <c r="C35" s="23">
-        <f>'Assumptions'!C70</f>
+        <f>'Assumptions'!C74</f>
         <v/>
       </c>
       <c r="D35" s="22" t="inlineStr">
@@ -16684,7 +16746,7 @@
         </is>
       </c>
       <c r="C36" s="18">
-        <f>'Assumptions'!C71</f>
+        <f>'Assumptions'!C75</f>
         <v/>
       </c>
       <c r="D36" s="22" t="inlineStr">
@@ -16914,7 +16976,7 @@
         </is>
       </c>
       <c r="C46" s="18">
-        <f>'Assumptions'!C74</f>
+        <f>'Assumptions'!C78</f>
         <v/>
       </c>
       <c r="D46" s="22" t="inlineStr">
@@ -16939,7 +17001,7 @@
         </is>
       </c>
       <c r="C47" s="24">
-        <f>'Assumptions'!C75</f>
+        <f>'Assumptions'!C79</f>
         <v/>
       </c>
       <c r="D47" s="22" t="inlineStr">
@@ -17006,7 +17068,7 @@
         </is>
       </c>
       <c r="C50" s="24">
-        <f>'Assumptions'!C72</f>
+        <f>'Assumptions'!C76</f>
         <v/>
       </c>
       <c r="D50" s="22" t="inlineStr">
@@ -17031,7 +17093,7 @@
         </is>
       </c>
       <c r="C51" s="24">
-        <f>'Assumptions'!C73</f>
+        <f>'Assumptions'!C77</f>
         <v/>
       </c>
       <c r="D51" s="22" t="inlineStr">
@@ -18726,7 +18788,7 @@
         </is>
       </c>
       <c r="C104" s="53">
-        <f>IRR(C96:M96)</f>
+        <f>IFERROR(IRR(C96:M96),"n/m")</f>
         <v/>
       </c>
     </row>
@@ -18759,7 +18821,7 @@
         </is>
       </c>
       <c r="C107" s="53">
-        <f>IRR(C101:M101)</f>
+        <f>IFERROR(IRR(C101:M101),"n/m")</f>
         <v/>
       </c>
     </row>
@@ -20026,7 +20088,7 @@
         </is>
       </c>
       <c r="C28" s="25">
-        <f>'Assumptions'!C79</f>
+        <f>'Assumptions'!C83</f>
         <v/>
       </c>
       <c r="D28" s="22" t="inlineStr">
@@ -20051,7 +20113,7 @@
         </is>
       </c>
       <c r="C29" s="18">
-        <f>'Assumptions'!C82</f>
+        <f>'Assumptions'!C86</f>
         <v/>
       </c>
       <c r="D29" s="22" t="inlineStr">
@@ -20076,7 +20138,7 @@
         </is>
       </c>
       <c r="C30" s="18">
-        <f>'Assumptions'!C83</f>
+        <f>'Assumptions'!C87</f>
         <v/>
       </c>
       <c r="D30" s="22" t="inlineStr">
@@ -20101,7 +20163,7 @@
         </is>
       </c>
       <c r="C31" s="26">
-        <f>'Assumptions'!C81</f>
+        <f>'Assumptions'!C85</f>
         <v/>
       </c>
       <c r="D31" s="22" t="inlineStr">
@@ -20216,7 +20278,7 @@
         </is>
       </c>
       <c r="C36" s="23">
-        <f>'Assumptions'!C84</f>
+        <f>'Assumptions'!C88</f>
         <v/>
       </c>
       <c r="D36" s="22" t="inlineStr">
@@ -20241,7 +20303,7 @@
         </is>
       </c>
       <c r="C37" s="23">
-        <f>'Assumptions'!C85</f>
+        <f>'Assumptions'!C89</f>
         <v/>
       </c>
       <c r="D37" s="22" t="inlineStr">
@@ -20266,7 +20328,7 @@
         </is>
       </c>
       <c r="C38" s="23">
-        <f>'Assumptions'!C86</f>
+        <f>'Assumptions'!C90</f>
         <v/>
       </c>
       <c r="D38" s="22" t="inlineStr">
@@ -20291,7 +20353,7 @@
         </is>
       </c>
       <c r="C39" s="18">
-        <f>'Assumptions'!C87</f>
+        <f>'Assumptions'!C91</f>
         <v/>
       </c>
       <c r="D39" s="22" t="inlineStr">
@@ -20472,7 +20534,7 @@
         </is>
       </c>
       <c r="C47" s="23">
-        <f>'Assumptions'!C78</f>
+        <f>'Assumptions'!C82</f>
         <v/>
       </c>
       <c r="D47" s="22" t="inlineStr">
@@ -20521,7 +20583,7 @@
         </is>
       </c>
       <c r="C49" s="18">
-        <f>'Assumptions'!C90</f>
+        <f>'Assumptions'!C94</f>
         <v/>
       </c>
       <c r="D49" s="22" t="inlineStr">
@@ -20546,7 +20608,7 @@
         </is>
       </c>
       <c r="C50" s="24">
-        <f>'Assumptions'!C91</f>
+        <f>'Assumptions'!C95</f>
         <v/>
       </c>
       <c r="D50" s="22" t="inlineStr">
@@ -20613,7 +20675,7 @@
         </is>
       </c>
       <c r="C53" s="24">
-        <f>'Assumptions'!C88</f>
+        <f>'Assumptions'!C92</f>
         <v/>
       </c>
       <c r="D53" s="22" t="inlineStr">
@@ -20638,7 +20700,7 @@
         </is>
       </c>
       <c r="C54" s="24">
-        <f>'Assumptions'!C89</f>
+        <f>'Assumptions'!C93</f>
         <v/>
       </c>
       <c r="D54" s="22" t="inlineStr">
@@ -20735,7 +20797,7 @@
         </is>
       </c>
       <c r="C58" s="26">
-        <f>'Assumptions'!C80</f>
+        <f>'Assumptions'!C84</f>
         <v/>
       </c>
       <c r="D58" s="22" t="inlineStr">
@@ -22333,7 +22395,7 @@
         </is>
       </c>
       <c r="C107" s="53">
-        <f>IRR(C99:M99)</f>
+        <f>IFERROR(IRR(C99:M99),"n/m")</f>
         <v/>
       </c>
     </row>
@@ -22366,7 +22428,7 @@
         </is>
       </c>
       <c r="C110" s="53">
-        <f>IRR(C104:M104)</f>
+        <f>IFERROR(IRR(C104:M104),"n/m")</f>
         <v/>
       </c>
     </row>
@@ -23320,7 +23382,7 @@
         </is>
       </c>
       <c r="C16" s="18">
-        <f>'Assumptions'!C96</f>
+        <f>'Assumptions'!C100</f>
         <v/>
       </c>
       <c r="D16" s="22" t="inlineStr">
@@ -23345,7 +23407,7 @@
         </is>
       </c>
       <c r="C17" s="18">
-        <f>'Assumptions'!C97</f>
+        <f>'Assumptions'!C101</f>
         <v/>
       </c>
       <c r="D17" s="22" t="inlineStr">
@@ -23370,7 +23432,7 @@
         </is>
       </c>
       <c r="C18" s="26">
-        <f>'Assumptions'!C95</f>
+        <f>'Assumptions'!C99</f>
         <v/>
       </c>
       <c r="D18" s="22" t="inlineStr">
@@ -23467,7 +23529,7 @@
         </is>
       </c>
       <c r="C22" s="26">
-        <f>'Assumptions'!C98</f>
+        <f>'Assumptions'!C102</f>
         <v/>
       </c>
       <c r="D22" s="22" t="inlineStr">
@@ -23492,7 +23554,7 @@
         </is>
       </c>
       <c r="C23" s="18">
-        <f>'Assumptions'!C99</f>
+        <f>'Assumptions'!C103</f>
         <v/>
       </c>
       <c r="D23" s="22" t="inlineStr">
@@ -23565,7 +23627,7 @@
         </is>
       </c>
       <c r="C26" s="23">
-        <f>'Assumptions'!C94</f>
+        <f>'Assumptions'!C98</f>
         <v/>
       </c>
       <c r="D26" s="22" t="inlineStr">
@@ -23614,7 +23676,7 @@
         </is>
       </c>
       <c r="C28" s="18">
-        <f>'Assumptions'!C102</f>
+        <f>'Assumptions'!C106</f>
         <v/>
       </c>
       <c r="D28" s="22" t="inlineStr">
@@ -23639,7 +23701,7 @@
         </is>
       </c>
       <c r="C29" s="24">
-        <f>'Assumptions'!C103</f>
+        <f>'Assumptions'!C107</f>
         <v/>
       </c>
       <c r="D29" s="22" t="inlineStr">
@@ -23688,7 +23750,7 @@
         </is>
       </c>
       <c r="C31" s="24">
-        <f>'Assumptions'!C100</f>
+        <f>'Assumptions'!C104</f>
         <v/>
       </c>
       <c r="D31" s="22" t="inlineStr">
@@ -23713,7 +23775,7 @@
         </is>
       </c>
       <c r="C32" s="24">
-        <f>'Assumptions'!C101</f>
+        <f>'Assumptions'!C105</f>
         <v/>
       </c>
       <c r="D32" s="22" t="inlineStr">

--- a/Shahidi_Assemblage_Model.xlsx
+++ b/Shahidi_Assemblage_Model.xlsx
@@ -305,7 +305,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="86">
+  <cellXfs count="87">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -543,6 +543,9 @@
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="4" fontId="12" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -2937,7 +2940,7 @@
           <t>Concluded acquisition basis</t>
         </is>
       </c>
-      <c r="E40" s="85">
+      <c r="E40" s="86">
         <f>C24</f>
         <v/>
       </c>
@@ -4161,7 +4164,7 @@
       <c r="L20" s="13" t="n"/>
       <c r="M20" s="14" t="n"/>
     </row>
-    <row r="21" ht="27" customHeight="1">
+    <row r="21" ht="39" customHeight="1">
       <c r="B21" s="52" t="inlineStr">
         <is>
           <t>Publix sale-leaseback</t>
@@ -4169,7 +4172,7 @@
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
-          <t>Acquire the Publix fee; Publix leases back and pays NNN rent during entitlement (rent covers the operating carry), then vacates for redevelopment. Leaseback rent, SF, price, and term are on the Assumptions tab.</t>
+          <t>Acquire the Publix fee; Publix leases back and pays NNN rent for the entitlement term (rent covers carry), then vacates. The leaseback income CLIFFS at term-end and the parcel EXITS AT LAND VALUE (covered-land), not an income cap. A solver on the Publix tab back-solves the leaseback rent for a target DSCR or cap. Rent, SF, price, term, and leverage are on the Assumptions tab.</t>
         </is>
       </c>
       <c r="E21" s="13" t="n"/>
@@ -15976,7 +15979,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M134"/>
+  <dimension ref="A1:M142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.5" customWidth="1" min="1" max="1"/>
@@ -17617,47 +17620,47 @@
     <row r="75" ht="15" customHeight="1">
       <c r="B75" s="12" t="inlineStr">
         <is>
-          <t>Base rental income</t>
+          <t>Base rental income (leaseback cliffs at term)</t>
         </is>
       </c>
       <c r="D75" s="51">
-        <f>D73*C28*(1+C29)^(1-1)</f>
+        <f>IF(1&lt;='Assumptions'!C69,D73*C28*(1+C29)^(1-1),0)</f>
         <v/>
       </c>
       <c r="E75" s="47">
-        <f>E73*C28*(1+C29)^(2-1)</f>
+        <f>IF(2&lt;='Assumptions'!C69,E73*C28*(1+C29)^(2-1),0)</f>
         <v/>
       </c>
       <c r="F75" s="47">
-        <f>F73*C28*(1+C29)^(3-1)</f>
+        <f>IF(3&lt;='Assumptions'!C69,F73*C28*(1+C29)^(3-1),0)</f>
         <v/>
       </c>
       <c r="G75" s="47">
-        <f>G73*C28*(1+C29)^(4-1)</f>
+        <f>IF(4&lt;='Assumptions'!C69,G73*C28*(1+C29)^(4-1),0)</f>
         <v/>
       </c>
       <c r="H75" s="47">
-        <f>H73*C28*(1+C29)^(5-1)</f>
+        <f>IF(5&lt;='Assumptions'!C69,H73*C28*(1+C29)^(5-1),0)</f>
         <v/>
       </c>
       <c r="I75" s="47">
-        <f>I73*C28*(1+C29)^(6-1)</f>
+        <f>IF(6&lt;='Assumptions'!C69,I73*C28*(1+C29)^(6-1),0)</f>
         <v/>
       </c>
       <c r="J75" s="47">
-        <f>J73*C28*(1+C29)^(7-1)</f>
+        <f>IF(7&lt;='Assumptions'!C69,J73*C28*(1+C29)^(7-1),0)</f>
         <v/>
       </c>
       <c r="K75" s="47">
-        <f>K73*C28*(1+C29)^(8-1)</f>
+        <f>IF(8&lt;='Assumptions'!C69,K73*C28*(1+C29)^(8-1),0)</f>
         <v/>
       </c>
       <c r="L75" s="47">
-        <f>L73*C28*(1+C29)^(9-1)</f>
+        <f>IF(9&lt;='Assumptions'!C69,L73*C28*(1+C29)^(9-1),0)</f>
         <v/>
       </c>
       <c r="M75" s="47">
-        <f>M73*C28*(1+C29)^(10-1)</f>
+        <f>IF(10&lt;='Assumptions'!C69,M73*C28*(1+C29)^(10-1),0)</f>
         <v/>
       </c>
     </row>
@@ -18428,47 +18431,47 @@
     <row r="95" ht="15" customHeight="1">
       <c r="B95" s="12" t="inlineStr">
         <is>
-          <t>Net sale proceeds (exit year)</t>
+          <t>Net sale — land value (covered-land exit)</t>
         </is>
       </c>
       <c r="D95" s="47">
-        <f>IF(1=C53,(D87*(1+C29)/C51)*(1-C52),0)</f>
+        <f>IF(1=C53,C67*(1-C52),0)</f>
         <v/>
       </c>
       <c r="E95" s="47">
-        <f>IF(2=C53,(E87*(1+C29)/C51)*(1-C52),0)</f>
+        <f>IF(2=C53,C67*(1-C52),0)</f>
         <v/>
       </c>
       <c r="F95" s="47">
-        <f>IF(3=C53,(F87*(1+C29)/C51)*(1-C52),0)</f>
+        <f>IF(3=C53,C67*(1-C52),0)</f>
         <v/>
       </c>
       <c r="G95" s="47">
-        <f>IF(4=C53,(G87*(1+C29)/C51)*(1-C52),0)</f>
+        <f>IF(4=C53,C67*(1-C52),0)</f>
         <v/>
       </c>
       <c r="H95" s="47">
-        <f>IF(5=C53,(H87*(1+C29)/C51)*(1-C52),0)</f>
+        <f>IF(5=C53,C67*(1-C52),0)</f>
         <v/>
       </c>
       <c r="I95" s="47">
-        <f>IF(6=C53,(I87*(1+C29)/C51)*(1-C52),0)</f>
+        <f>IF(6=C53,C67*(1-C52),0)</f>
         <v/>
       </c>
       <c r="J95" s="47">
-        <f>IF(7=C53,(J87*(1+C29)/C51)*(1-C52),0)</f>
+        <f>IF(7=C53,C67*(1-C52),0)</f>
         <v/>
       </c>
       <c r="K95" s="47">
-        <f>IF(8=C53,(K87*(1+C29)/C51)*(1-C52),0)</f>
+        <f>IF(8=C53,C67*(1-C52),0)</f>
         <v/>
       </c>
       <c r="L95" s="47">
-        <f>IF(9=C53,(L87*(1+C29)/C51)*(1-C52),0)</f>
+        <f>IF(9=C53,C67*(1-C52),0)</f>
         <v/>
       </c>
       <c r="M95" s="47">
-        <f>IF(10=C53,(M87*(1+C29)/C51)*(1-C52),0)</f>
+        <f>IF(10=C53,C67*(1-C52),0)</f>
         <v/>
       </c>
     </row>
@@ -18928,7 +18931,7 @@
     <row r="118">
       <c r="B118" s="11" t="inlineStr">
         <is>
-          <t>PROFIT &amp; LOSS STATEMENT  —  Year 1 vs. Stabilized (Yr 2)</t>
+          <t>SALE-LEASEBACK SOLVER  —  required Publix leaseback rent to hit a target</t>
         </is>
       </c>
       <c r="C118" s="2" t="n"/>
@@ -18944,52 +18947,49 @@
       <c r="M118" s="3" t="n"/>
     </row>
     <row r="119" ht="15" customHeight="1">
-      <c r="B119" s="15" t="inlineStr">
-        <is>
-          <t>$ / year</t>
-        </is>
-      </c>
-      <c r="F119" s="81" t="inlineStr">
-        <is>
-          <t>Year 1</t>
-        </is>
-      </c>
-      <c r="G119" s="14" t="n"/>
-      <c r="H119" s="81" t="inlineStr">
-        <is>
-          <t>Stabilized</t>
-        </is>
-      </c>
-      <c r="I119" s="14" t="n"/>
-      <c r="J119" s="81" t="inlineStr">
-        <is>
-          <t>Per SF (stab.)</t>
-        </is>
-      </c>
+      <c r="B119" s="12" t="inlineStr">
+        <is>
+          <t>Target Year-1 DSCR</t>
+        </is>
+      </c>
+      <c r="C119" s="83" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="D119" s="22" t="inlineStr">
+        <is>
+          <t>🔵 your coverage target</t>
+        </is>
+      </c>
+      <c r="E119" s="13" t="n"/>
+      <c r="F119" s="13" t="n"/>
+      <c r="G119" s="13" t="n"/>
+      <c r="H119" s="13" t="n"/>
+      <c r="I119" s="13" t="n"/>
+      <c r="J119" s="13" t="n"/>
       <c r="K119" s="13" t="n"/>
       <c r="L119" s="13" t="n"/>
       <c r="M119" s="14" t="n"/>
     </row>
     <row r="120" ht="15" customHeight="1">
-      <c r="B120" s="52" t="inlineStr">
-        <is>
-          <t>Base rental income</t>
-        </is>
-      </c>
-      <c r="F120" s="45">
-        <f>D75</f>
-        <v/>
-      </c>
-      <c r="G120" s="14" t="n"/>
-      <c r="H120" s="44">
-        <f>E75</f>
-        <v/>
-      </c>
-      <c r="I120" s="14" t="n"/>
-      <c r="J120" s="82">
-        <f>H120/C24</f>
-        <v/>
-      </c>
+      <c r="B120" s="12" t="inlineStr">
+        <is>
+          <t>Target going-in cap</t>
+        </is>
+      </c>
+      <c r="C120" s="77" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D120" s="22" t="inlineStr">
+        <is>
+          <t>🔵 your yield target</t>
+        </is>
+      </c>
+      <c r="E120" s="13" t="n"/>
+      <c r="F120" s="13" t="n"/>
+      <c r="G120" s="13" t="n"/>
+      <c r="H120" s="13" t="n"/>
+      <c r="I120" s="13" t="n"/>
+      <c r="J120" s="13" t="n"/>
       <c r="K120" s="13" t="n"/>
       <c r="L120" s="13" t="n"/>
       <c r="M120" s="14" t="n"/>
@@ -18997,188 +18997,138 @@
     <row r="121" ht="15" customHeight="1">
       <c r="B121" s="12" t="inlineStr">
         <is>
-          <t>Expense reimbursements</t>
-        </is>
-      </c>
-      <c r="F121" s="47">
-        <f>D77</f>
-        <v/>
-      </c>
-      <c r="G121" s="14" t="n"/>
-      <c r="H121" s="47">
-        <f>E77</f>
-        <v/>
-      </c>
-      <c r="I121" s="14" t="n"/>
-      <c r="J121" s="68">
-        <f>H121/C24</f>
-        <v/>
-      </c>
-      <c r="K121" s="13" t="n"/>
-      <c r="L121" s="13" t="n"/>
-      <c r="M121" s="14" t="n"/>
+          <t>K = (1−credit)(1−mgmt)</t>
+        </is>
+      </c>
+      <c r="C121" s="68">
+        <f>(1-C30)*(1-C36)</f>
+        <v/>
+      </c>
     </row>
     <row r="122" ht="15" customHeight="1">
       <c r="B122" s="12" t="inlineStr">
         <is>
-          <t>Less: credit loss</t>
-        </is>
-      </c>
-      <c r="F122" s="47">
-        <f>D78</f>
-        <v/>
-      </c>
-      <c r="G122" s="14" t="n"/>
-      <c r="H122" s="47">
-        <f>E78</f>
-        <v/>
-      </c>
-      <c r="I122" s="14" t="n"/>
-      <c r="J122" s="68">
-        <f>H122/C24</f>
-        <v/>
-      </c>
-      <c r="K122" s="13" t="n"/>
-      <c r="L122" s="13" t="n"/>
-      <c r="M122" s="14" t="n"/>
+          <t>Recoverable opex (taxes+ins+CAM)</t>
+        </is>
+      </c>
+      <c r="C122" s="47">
+        <f>C44*C31+C33+C34</f>
+        <v/>
+      </c>
     </row>
     <row r="123" ht="15" customHeight="1">
       <c r="B123" s="43" t="inlineStr">
         <is>
-          <t>Effective Gross Income</t>
-        </is>
-      </c>
-      <c r="F123" s="45">
-        <f>D79</f>
-        <v/>
-      </c>
-      <c r="G123" s="14" t="n"/>
-      <c r="H123" s="44">
-        <f>E79</f>
-        <v/>
-      </c>
-      <c r="I123" s="14" t="n"/>
-      <c r="J123" s="82">
-        <f>H123/C24</f>
-        <v/>
-      </c>
+          <t>→ Required leaseback rent for target DSCR</t>
+        </is>
+      </c>
+      <c r="C123" s="82">
+        <f>(((C119*C60+C122*C36+C35)/C121)-'Assumptions'!C68*'Assumptions'!C67)/'Assumptions'!C66</f>
+        <v/>
+      </c>
+      <c r="D123" s="22" t="inlineStr">
+        <is>
+          <t>$/SF NNN — set Publix leaseback rent (Assumptions) to this</t>
+        </is>
+      </c>
+      <c r="E123" s="13" t="n"/>
+      <c r="F123" s="13" t="n"/>
+      <c r="G123" s="13" t="n"/>
+      <c r="H123" s="13" t="n"/>
+      <c r="I123" s="13" t="n"/>
+      <c r="J123" s="13" t="n"/>
       <c r="K123" s="13" t="n"/>
       <c r="L123" s="13" t="n"/>
       <c r="M123" s="14" t="n"/>
     </row>
     <row r="124" ht="15" customHeight="1">
-      <c r="B124" s="12" t="inlineStr">
-        <is>
-          <t>Real-estate taxes</t>
-        </is>
-      </c>
-      <c r="F124" s="47">
-        <f>-D81</f>
-        <v/>
-      </c>
-      <c r="G124" s="14" t="n"/>
-      <c r="H124" s="47">
-        <f>-E81</f>
-        <v/>
-      </c>
-      <c r="I124" s="14" t="n"/>
-      <c r="J124" s="68">
-        <f>H124/C24</f>
-        <v/>
-      </c>
+      <c r="B124" s="43" t="inlineStr">
+        <is>
+          <t>→ Required leaseback rent for target cap</t>
+        </is>
+      </c>
+      <c r="C124" s="82">
+        <f>(((C120*C44+C122*C36+C35)/C121)-'Assumptions'!C68*'Assumptions'!C67)/'Assumptions'!C66</f>
+        <v/>
+      </c>
+      <c r="D124" s="22" t="inlineStr">
+        <is>
+          <t>$/SF NNN — set Publix leaseback rent (Assumptions) to this</t>
+        </is>
+      </c>
+      <c r="E124" s="13" t="n"/>
+      <c r="F124" s="13" t="n"/>
+      <c r="G124" s="13" t="n"/>
+      <c r="H124" s="13" t="n"/>
+      <c r="I124" s="13" t="n"/>
+      <c r="J124" s="13" t="n"/>
       <c r="K124" s="13" t="n"/>
       <c r="L124" s="13" t="n"/>
       <c r="M124" s="14" t="n"/>
     </row>
-    <row r="125" ht="15" customHeight="1">
-      <c r="B125" s="12" t="inlineStr">
-        <is>
-          <t>Insurance</t>
-        </is>
-      </c>
-      <c r="F125" s="47">
-        <f>-D82</f>
-        <v/>
-      </c>
-      <c r="G125" s="14" t="n"/>
-      <c r="H125" s="47">
-        <f>-E82</f>
-        <v/>
-      </c>
-      <c r="I125" s="14" t="n"/>
-      <c r="J125" s="68">
-        <f>H125/C24</f>
-        <v/>
-      </c>
-      <c r="K125" s="13" t="n"/>
-      <c r="L125" s="13" t="n"/>
-      <c r="M125" s="14" t="n"/>
-    </row>
-    <row r="126" ht="15" customHeight="1">
-      <c r="B126" s="12" t="inlineStr">
-        <is>
-          <t>CAM</t>
-        </is>
-      </c>
-      <c r="F126" s="47">
-        <f>-D83</f>
-        <v/>
-      </c>
-      <c r="G126" s="14" t="n"/>
-      <c r="H126" s="47">
-        <f>-E83</f>
-        <v/>
-      </c>
-      <c r="I126" s="14" t="n"/>
-      <c r="J126" s="68">
-        <f>H126/C24</f>
-        <v/>
-      </c>
-      <c r="K126" s="13" t="n"/>
-      <c r="L126" s="13" t="n"/>
-      <c r="M126" s="14" t="n"/>
+    <row r="125"/>
+    <row r="126">
+      <c r="B126" s="11" t="inlineStr">
+        <is>
+          <t>PROFIT &amp; LOSS STATEMENT  —  Year 1 vs. Stabilized (Yr 2)</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="n"/>
+      <c r="D126" s="2" t="n"/>
+      <c r="E126" s="2" t="n"/>
+      <c r="F126" s="2" t="n"/>
+      <c r="G126" s="2" t="n"/>
+      <c r="H126" s="2" t="n"/>
+      <c r="I126" s="2" t="n"/>
+      <c r="J126" s="2" t="n"/>
+      <c r="K126" s="2" t="n"/>
+      <c r="L126" s="2" t="n"/>
+      <c r="M126" s="3" t="n"/>
     </row>
     <row r="127" ht="15" customHeight="1">
-      <c r="B127" s="12" t="inlineStr">
-        <is>
-          <t>Repairs &amp; maintenance</t>
-        </is>
-      </c>
-      <c r="F127" s="47">
-        <f>-D84</f>
-        <v/>
+      <c r="B127" s="15" t="inlineStr">
+        <is>
+          <t>$ / year</t>
+        </is>
+      </c>
+      <c r="F127" s="81" t="inlineStr">
+        <is>
+          <t>Year 1</t>
+        </is>
       </c>
       <c r="G127" s="14" t="n"/>
-      <c r="H127" s="47">
-        <f>-E84</f>
-        <v/>
+      <c r="H127" s="81" t="inlineStr">
+        <is>
+          <t>Stabilized</t>
+        </is>
       </c>
       <c r="I127" s="14" t="n"/>
-      <c r="J127" s="68">
-        <f>H127/C24</f>
-        <v/>
+      <c r="J127" s="81" t="inlineStr">
+        <is>
+          <t>Per SF (stab.)</t>
+        </is>
       </c>
       <c r="K127" s="13" t="n"/>
       <c r="L127" s="13" t="n"/>
       <c r="M127" s="14" t="n"/>
     </row>
     <row r="128" ht="15" customHeight="1">
-      <c r="B128" s="12" t="inlineStr">
-        <is>
-          <t>Management fee</t>
-        </is>
-      </c>
-      <c r="F128" s="47">
-        <f>-D85</f>
+      <c r="B128" s="52" t="inlineStr">
+        <is>
+          <t>Base rental income</t>
+        </is>
+      </c>
+      <c r="F128" s="45">
+        <f>D75</f>
         <v/>
       </c>
       <c r="G128" s="14" t="n"/>
-      <c r="H128" s="47">
-        <f>-E85</f>
+      <c r="H128" s="44">
+        <f>E75</f>
         <v/>
       </c>
       <c r="I128" s="14" t="n"/>
-      <c r="J128" s="68">
+      <c r="J128" s="82">
         <f>H128/C24</f>
         <v/>
       </c>
@@ -19187,22 +19137,22 @@
       <c r="M128" s="14" t="n"/>
     </row>
     <row r="129" ht="15" customHeight="1">
-      <c r="B129" s="43" t="inlineStr">
-        <is>
-          <t>Net Operating Income</t>
-        </is>
-      </c>
-      <c r="F129" s="45">
-        <f>D87</f>
+      <c r="B129" s="12" t="inlineStr">
+        <is>
+          <t>Expense reimbursements</t>
+        </is>
+      </c>
+      <c r="F129" s="47">
+        <f>D77</f>
         <v/>
       </c>
       <c r="G129" s="14" t="n"/>
-      <c r="H129" s="44">
-        <f>E87</f>
+      <c r="H129" s="47">
+        <f>E77</f>
         <v/>
       </c>
       <c r="I129" s="14" t="n"/>
-      <c r="J129" s="82">
+      <c r="J129" s="68">
         <f>H129/C24</f>
         <v/>
       </c>
@@ -19213,16 +19163,16 @@
     <row r="130" ht="15" customHeight="1">
       <c r="B130" s="12" t="inlineStr">
         <is>
-          <t>Replacement reserves</t>
+          <t>Less: credit loss</t>
         </is>
       </c>
       <c r="F130" s="47">
-        <f>-D89</f>
+        <f>D78</f>
         <v/>
       </c>
       <c r="G130" s="14" t="n"/>
       <c r="H130" s="47">
-        <f>-E89</f>
+        <f>E78</f>
         <v/>
       </c>
       <c r="I130" s="14" t="n"/>
@@ -19235,22 +19185,22 @@
       <c r="M130" s="14" t="n"/>
     </row>
     <row r="131" ht="15" customHeight="1">
-      <c r="B131" s="12" t="inlineStr">
-        <is>
-          <t>Leasing costs</t>
-        </is>
-      </c>
-      <c r="F131" s="47">
-        <f>-D90</f>
+      <c r="B131" s="43" t="inlineStr">
+        <is>
+          <t>Effective Gross Income</t>
+        </is>
+      </c>
+      <c r="F131" s="45">
+        <f>D79</f>
         <v/>
       </c>
       <c r="G131" s="14" t="n"/>
-      <c r="H131" s="47">
-        <f>-E90</f>
+      <c r="H131" s="44">
+        <f>E79</f>
         <v/>
       </c>
       <c r="I131" s="14" t="n"/>
-      <c r="J131" s="68">
+      <c r="J131" s="82">
         <f>H131/C24</f>
         <v/>
       </c>
@@ -19259,22 +19209,22 @@
       <c r="M131" s="14" t="n"/>
     </row>
     <row r="132" ht="15" customHeight="1">
-      <c r="B132" s="43" t="inlineStr">
-        <is>
-          <t>Cash Flow Before Debt</t>
-        </is>
-      </c>
-      <c r="F132" s="45">
-        <f>D92</f>
+      <c r="B132" s="12" t="inlineStr">
+        <is>
+          <t>Real-estate taxes</t>
+        </is>
+      </c>
+      <c r="F132" s="47">
+        <f>-D81</f>
         <v/>
       </c>
       <c r="G132" s="14" t="n"/>
-      <c r="H132" s="44">
-        <f>E92</f>
+      <c r="H132" s="47">
+        <f>-E81</f>
         <v/>
       </c>
       <c r="I132" s="14" t="n"/>
-      <c r="J132" s="82">
+      <c r="J132" s="68">
         <f>H132/C24</f>
         <v/>
       </c>
@@ -19285,16 +19235,16 @@
     <row r="133" ht="15" customHeight="1">
       <c r="B133" s="12" t="inlineStr">
         <is>
-          <t>Debt service</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="F133" s="47">
-        <f>-C60</f>
+        <f>-D82</f>
         <v/>
       </c>
       <c r="G133" s="14" t="n"/>
       <c r="H133" s="47">
-        <f>-C60</f>
+        <f>-E82</f>
         <v/>
       </c>
       <c r="I133" s="14" t="n"/>
@@ -19307,22 +19257,22 @@
       <c r="M133" s="14" t="n"/>
     </row>
     <row r="134" ht="15" customHeight="1">
-      <c r="B134" s="43" t="inlineStr">
-        <is>
-          <t>Cash Flow After Debt (levered)</t>
-        </is>
-      </c>
-      <c r="F134" s="44">
-        <f>F132-C60</f>
+      <c r="B134" s="12" t="inlineStr">
+        <is>
+          <t>CAM</t>
+        </is>
+      </c>
+      <c r="F134" s="47">
+        <f>-D83</f>
         <v/>
       </c>
       <c r="G134" s="14" t="n"/>
-      <c r="H134" s="44">
-        <f>H132-C60</f>
+      <c r="H134" s="47">
+        <f>-E83</f>
         <v/>
       </c>
       <c r="I134" s="14" t="n"/>
-      <c r="J134" s="82">
+      <c r="J134" s="68">
         <f>H134/C24</f>
         <v/>
       </c>
@@ -19330,8 +19280,200 @@
       <c r="L134" s="13" t="n"/>
       <c r="M134" s="14" t="n"/>
     </row>
+    <row r="135" ht="15" customHeight="1">
+      <c r="B135" s="12" t="inlineStr">
+        <is>
+          <t>Repairs &amp; maintenance</t>
+        </is>
+      </c>
+      <c r="F135" s="47">
+        <f>-D84</f>
+        <v/>
+      </c>
+      <c r="G135" s="14" t="n"/>
+      <c r="H135" s="47">
+        <f>-E84</f>
+        <v/>
+      </c>
+      <c r="I135" s="14" t="n"/>
+      <c r="J135" s="68">
+        <f>H135/C24</f>
+        <v/>
+      </c>
+      <c r="K135" s="13" t="n"/>
+      <c r="L135" s="13" t="n"/>
+      <c r="M135" s="14" t="n"/>
+    </row>
+    <row r="136" ht="15" customHeight="1">
+      <c r="B136" s="12" t="inlineStr">
+        <is>
+          <t>Management fee</t>
+        </is>
+      </c>
+      <c r="F136" s="47">
+        <f>-D85</f>
+        <v/>
+      </c>
+      <c r="G136" s="14" t="n"/>
+      <c r="H136" s="47">
+        <f>-E85</f>
+        <v/>
+      </c>
+      <c r="I136" s="14" t="n"/>
+      <c r="J136" s="68">
+        <f>H136/C24</f>
+        <v/>
+      </c>
+      <c r="K136" s="13" t="n"/>
+      <c r="L136" s="13" t="n"/>
+      <c r="M136" s="14" t="n"/>
+    </row>
+    <row r="137" ht="15" customHeight="1">
+      <c r="B137" s="43" t="inlineStr">
+        <is>
+          <t>Net Operating Income</t>
+        </is>
+      </c>
+      <c r="F137" s="45">
+        <f>D87</f>
+        <v/>
+      </c>
+      <c r="G137" s="14" t="n"/>
+      <c r="H137" s="44">
+        <f>E87</f>
+        <v/>
+      </c>
+      <c r="I137" s="14" t="n"/>
+      <c r="J137" s="82">
+        <f>H137/C24</f>
+        <v/>
+      </c>
+      <c r="K137" s="13" t="n"/>
+      <c r="L137" s="13" t="n"/>
+      <c r="M137" s="14" t="n"/>
+    </row>
+    <row r="138" ht="15" customHeight="1">
+      <c r="B138" s="12" t="inlineStr">
+        <is>
+          <t>Replacement reserves</t>
+        </is>
+      </c>
+      <c r="F138" s="47">
+        <f>-D89</f>
+        <v/>
+      </c>
+      <c r="G138" s="14" t="n"/>
+      <c r="H138" s="47">
+        <f>-E89</f>
+        <v/>
+      </c>
+      <c r="I138" s="14" t="n"/>
+      <c r="J138" s="68">
+        <f>H138/C24</f>
+        <v/>
+      </c>
+      <c r="K138" s="13" t="n"/>
+      <c r="L138" s="13" t="n"/>
+      <c r="M138" s="14" t="n"/>
+    </row>
+    <row r="139" ht="15" customHeight="1">
+      <c r="B139" s="12" t="inlineStr">
+        <is>
+          <t>Leasing costs</t>
+        </is>
+      </c>
+      <c r="F139" s="47">
+        <f>-D90</f>
+        <v/>
+      </c>
+      <c r="G139" s="14" t="n"/>
+      <c r="H139" s="47">
+        <f>-E90</f>
+        <v/>
+      </c>
+      <c r="I139" s="14" t="n"/>
+      <c r="J139" s="68">
+        <f>H139/C24</f>
+        <v/>
+      </c>
+      <c r="K139" s="13" t="n"/>
+      <c r="L139" s="13" t="n"/>
+      <c r="M139" s="14" t="n"/>
+    </row>
+    <row r="140" ht="15" customHeight="1">
+      <c r="B140" s="43" t="inlineStr">
+        <is>
+          <t>Cash Flow Before Debt</t>
+        </is>
+      </c>
+      <c r="F140" s="45">
+        <f>D92</f>
+        <v/>
+      </c>
+      <c r="G140" s="14" t="n"/>
+      <c r="H140" s="44">
+        <f>E92</f>
+        <v/>
+      </c>
+      <c r="I140" s="14" t="n"/>
+      <c r="J140" s="82">
+        <f>H140/C24</f>
+        <v/>
+      </c>
+      <c r="K140" s="13" t="n"/>
+      <c r="L140" s="13" t="n"/>
+      <c r="M140" s="14" t="n"/>
+    </row>
+    <row r="141" ht="15" customHeight="1">
+      <c r="B141" s="12" t="inlineStr">
+        <is>
+          <t>Debt service</t>
+        </is>
+      </c>
+      <c r="F141" s="47">
+        <f>-C60</f>
+        <v/>
+      </c>
+      <c r="G141" s="14" t="n"/>
+      <c r="H141" s="47">
+        <f>-C60</f>
+        <v/>
+      </c>
+      <c r="I141" s="14" t="n"/>
+      <c r="J141" s="68">
+        <f>H141/C24</f>
+        <v/>
+      </c>
+      <c r="K141" s="13" t="n"/>
+      <c r="L141" s="13" t="n"/>
+      <c r="M141" s="14" t="n"/>
+    </row>
+    <row r="142" ht="15" customHeight="1">
+      <c r="B142" s="43" t="inlineStr">
+        <is>
+          <t>Cash Flow After Debt (levered)</t>
+        </is>
+      </c>
+      <c r="F142" s="44">
+        <f>F140-C60</f>
+        <v/>
+      </c>
+      <c r="G142" s="14" t="n"/>
+      <c r="H142" s="44">
+        <f>H140-C60</f>
+        <v/>
+      </c>
+      <c r="I142" s="14" t="n"/>
+      <c r="J142" s="82">
+        <f>H142/C24</f>
+        <v/>
+      </c>
+      <c r="K142" s="13" t="n"/>
+      <c r="L142" s="13" t="n"/>
+      <c r="M142" s="14" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="123">
+  <mergeCells count="128">
     <mergeCell ref="L17:M17"/>
     <mergeCell ref="B2:M2"/>
     <mergeCell ref="D37:M37"/>
@@ -19340,32 +19482,34 @@
     <mergeCell ref="D30:M30"/>
     <mergeCell ref="D39:M39"/>
     <mergeCell ref="L19:M19"/>
+    <mergeCell ref="J138:M138"/>
     <mergeCell ref="D14:M14"/>
     <mergeCell ref="D29:M29"/>
     <mergeCell ref="F133:G133"/>
     <mergeCell ref="H133:I133"/>
-    <mergeCell ref="J126:M126"/>
+    <mergeCell ref="F142:G142"/>
+    <mergeCell ref="H142:I142"/>
     <mergeCell ref="I17:K17"/>
     <mergeCell ref="H129:I129"/>
     <mergeCell ref="B118:M118"/>
+    <mergeCell ref="D119:M119"/>
+    <mergeCell ref="F135:G135"/>
     <mergeCell ref="B20:D20"/>
-    <mergeCell ref="F122:G122"/>
-    <mergeCell ref="F125:G125"/>
     <mergeCell ref="B80:M80"/>
     <mergeCell ref="B94:M94"/>
     <mergeCell ref="F134:G134"/>
     <mergeCell ref="H128:I128"/>
-    <mergeCell ref="F121:G121"/>
     <mergeCell ref="D27:M27"/>
+    <mergeCell ref="D120:M120"/>
     <mergeCell ref="D41:M41"/>
-    <mergeCell ref="F120:G120"/>
-    <mergeCell ref="H120:I120"/>
+    <mergeCell ref="H139:I139"/>
     <mergeCell ref="B43:M43"/>
     <mergeCell ref="J128:M128"/>
-    <mergeCell ref="J124:M124"/>
+    <mergeCell ref="J137:M137"/>
     <mergeCell ref="J134:M134"/>
     <mergeCell ref="B17:D17"/>
     <mergeCell ref="D25:M25"/>
+    <mergeCell ref="J139:M139"/>
     <mergeCell ref="B57:M57"/>
     <mergeCell ref="D55:M55"/>
     <mergeCell ref="B88:M88"/>
@@ -19375,49 +19519,51 @@
     <mergeCell ref="D5:M5"/>
     <mergeCell ref="B19:D19"/>
     <mergeCell ref="D54:M54"/>
-    <mergeCell ref="J120:M120"/>
+    <mergeCell ref="F138:G138"/>
     <mergeCell ref="H132:I132"/>
     <mergeCell ref="B74:M74"/>
-    <mergeCell ref="H119:I119"/>
-    <mergeCell ref="F126:G126"/>
+    <mergeCell ref="J141:M141"/>
     <mergeCell ref="D31:M31"/>
     <mergeCell ref="D46:M46"/>
     <mergeCell ref="L20:M20"/>
     <mergeCell ref="D40:M40"/>
     <mergeCell ref="B4:M4"/>
-    <mergeCell ref="J119:M119"/>
+    <mergeCell ref="B126:M126"/>
+    <mergeCell ref="F136:G136"/>
+    <mergeCell ref="H136:I136"/>
     <mergeCell ref="D7:M7"/>
     <mergeCell ref="E18:F18"/>
     <mergeCell ref="D58:M58"/>
     <mergeCell ref="B23:M23"/>
     <mergeCell ref="F128:G128"/>
-    <mergeCell ref="H122:I122"/>
-    <mergeCell ref="J125:M125"/>
     <mergeCell ref="D8:M8"/>
-    <mergeCell ref="F124:G124"/>
+    <mergeCell ref="F137:G137"/>
+    <mergeCell ref="H137:I137"/>
     <mergeCell ref="D42:M42"/>
     <mergeCell ref="D51:M51"/>
-    <mergeCell ref="H121:I121"/>
     <mergeCell ref="E20:F20"/>
+    <mergeCell ref="D123:M123"/>
+    <mergeCell ref="F139:G139"/>
     <mergeCell ref="D35:M35"/>
     <mergeCell ref="D50:M50"/>
     <mergeCell ref="D44:M44"/>
     <mergeCell ref="L18:M18"/>
-    <mergeCell ref="H123:I123"/>
     <mergeCell ref="D34:M34"/>
     <mergeCell ref="I20:K20"/>
     <mergeCell ref="J131:M131"/>
+    <mergeCell ref="J140:M140"/>
     <mergeCell ref="D36:M36"/>
     <mergeCell ref="D45:M45"/>
+    <mergeCell ref="F141:G141"/>
+    <mergeCell ref="D124:M124"/>
     <mergeCell ref="D6:M6"/>
     <mergeCell ref="D13:M13"/>
     <mergeCell ref="J132:M132"/>
     <mergeCell ref="D48:M48"/>
     <mergeCell ref="B22:M22"/>
-    <mergeCell ref="F119:G119"/>
-    <mergeCell ref="H125:I125"/>
+    <mergeCell ref="H141:I141"/>
+    <mergeCell ref="H135:I135"/>
     <mergeCell ref="H134:I134"/>
-    <mergeCell ref="J121:M121"/>
     <mergeCell ref="J133:M133"/>
     <mergeCell ref="I18:K18"/>
     <mergeCell ref="B1:M1"/>
@@ -19427,33 +19573,34 @@
     <mergeCell ref="H127:I127"/>
     <mergeCell ref="J130:M130"/>
     <mergeCell ref="D33:M33"/>
+    <mergeCell ref="J142:M142"/>
     <mergeCell ref="B69:M69"/>
     <mergeCell ref="B38:M38"/>
     <mergeCell ref="B103:M103"/>
+    <mergeCell ref="J135:M135"/>
     <mergeCell ref="E19:F19"/>
     <mergeCell ref="D26:M26"/>
-    <mergeCell ref="J122:M122"/>
     <mergeCell ref="D10:M10"/>
     <mergeCell ref="B49:M49"/>
     <mergeCell ref="I19:K19"/>
     <mergeCell ref="F129:G129"/>
     <mergeCell ref="J127:M127"/>
+    <mergeCell ref="J136:M136"/>
+    <mergeCell ref="H138:I138"/>
     <mergeCell ref="D52:M52"/>
     <mergeCell ref="B32:M32"/>
-    <mergeCell ref="J123:M123"/>
     <mergeCell ref="F131:G131"/>
     <mergeCell ref="H131:I131"/>
+    <mergeCell ref="F140:G140"/>
+    <mergeCell ref="H140:I140"/>
     <mergeCell ref="D11:M11"/>
     <mergeCell ref="B16:M16"/>
     <mergeCell ref="F130:G130"/>
-    <mergeCell ref="H124:I124"/>
     <mergeCell ref="D66:M66"/>
     <mergeCell ref="B18:D18"/>
     <mergeCell ref="D53:M53"/>
     <mergeCell ref="D47:M47"/>
-    <mergeCell ref="F123:G123"/>
     <mergeCell ref="F132:G132"/>
-    <mergeCell ref="H126:I126"/>
     <mergeCell ref="D28:M28"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
@@ -25231,7 +25378,7 @@
         <f>D88/C15</f>
         <v/>
       </c>
-      <c r="F88" s="83" t="inlineStr">
+      <c r="F88" s="84" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -25269,7 +25416,7 @@
         <f>SUM(E87:E88)</f>
         <v/>
       </c>
-      <c r="F89" s="84" t="inlineStr">
+      <c r="F89" s="85" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/Shahidi_Assemblage_Model.xlsx
+++ b/Shahidi_Assemblage_Model.xlsx
@@ -306,7 +306,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="89">
+  <cellXfs count="92">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -507,6 +507,18 @@
     <xf numFmtId="0" fontId="9" fillId="6" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="8" fillId="5" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="3" fontId="12" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
@@ -518,9 +530,6 @@
     </xf>
     <xf numFmtId="3" fontId="6" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="4" fontId="6" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
@@ -1621,7 +1630,7 @@
         </is>
       </c>
       <c r="C32" s="23">
-        <f>'Highest &amp; Best Use'!C30</f>
+        <f>'Highest &amp; Best Use'!C39</f>
         <v/>
       </c>
       <c r="D32" s="22" t="inlineStr">
@@ -2414,7 +2423,7 @@
           <t>Rentable SF (both owners)</t>
         </is>
       </c>
-      <c r="C15" s="73" t="n">
+      <c r="C15" s="77" t="n">
         <v>168807</v>
       </c>
       <c r="D15" s="22" t="inlineStr">
@@ -2439,7 +2448,7 @@
         </is>
       </c>
       <c r="C16" s="18">
-        <f>'Assumptions'!C100</f>
+        <f>'Assumptions'!C101</f>
         <v/>
       </c>
       <c r="D16" s="22" t="inlineStr">
@@ -2464,7 +2473,7 @@
         </is>
       </c>
       <c r="C17" s="18">
-        <f>'Assumptions'!C101</f>
+        <f>'Assumptions'!C102</f>
         <v/>
       </c>
       <c r="D17" s="22" t="inlineStr">
@@ -2489,7 +2498,7 @@
         </is>
       </c>
       <c r="C18" s="26">
-        <f>'Assumptions'!C99</f>
+        <f>'Assumptions'!C100</f>
         <v/>
       </c>
       <c r="D18" s="22" t="inlineStr">
@@ -2513,7 +2522,7 @@
           <t>Rent growth</t>
         </is>
       </c>
-      <c r="C19" s="81" t="n">
+      <c r="C19" s="84" t="n">
         <v>0.03</v>
       </c>
       <c r="D19" s="22" t="inlineStr">
@@ -2537,7 +2546,7 @@
           <t>Credit &amp; vacancy loss</t>
         </is>
       </c>
-      <c r="C20" s="81" t="n">
+      <c r="C20" s="84" t="n">
         <v>0.03</v>
       </c>
       <c r="D20" s="22" t="inlineStr">
@@ -2561,7 +2570,7 @@
           <t>Effective millage</t>
         </is>
       </c>
-      <c r="C21" s="80" t="n">
+      <c r="C21" s="83" t="n">
         <v>0.0191</v>
       </c>
       <c r="D21" s="22" t="inlineStr">
@@ -2586,7 +2595,7 @@
         </is>
       </c>
       <c r="C22" s="26">
-        <f>'Assumptions'!C102</f>
+        <f>'Assumptions'!C103</f>
         <v/>
       </c>
       <c r="D22" s="22" t="inlineStr">
@@ -2611,7 +2620,7 @@
         </is>
       </c>
       <c r="C23" s="18">
-        <f>'Assumptions'!C103</f>
+        <f>'Assumptions'!C104</f>
         <v/>
       </c>
       <c r="D23" s="22" t="inlineStr">
@@ -2635,7 +2644,7 @@
           <t>Expense growth</t>
         </is>
       </c>
-      <c r="C24" s="81" t="n">
+      <c r="C24" s="84" t="n">
         <v>0.03</v>
       </c>
       <c r="D24" s="22" t="inlineStr">
@@ -2659,7 +2668,7 @@
           <t>Replacement reserves ($/SF/yr)</t>
         </is>
       </c>
-      <c r="C25" s="75" t="n">
+      <c r="C25" s="78" t="n">
         <v>0.2</v>
       </c>
       <c r="D25" s="22" t="inlineStr">
@@ -2684,7 +2693,7 @@
         </is>
       </c>
       <c r="C26" s="23">
-        <f>'Assumptions'!C98</f>
+        <f>'Assumptions'!C99</f>
         <v/>
       </c>
       <c r="D26" s="22" t="inlineStr">
@@ -2708,7 +2717,7 @@
           <t>Closing &amp; acq costs (% price)</t>
         </is>
       </c>
-      <c r="C27" s="81" t="n">
+      <c r="C27" s="84" t="n">
         <v>0.02</v>
       </c>
       <c r="D27" s="22" t="inlineStr">
@@ -2733,7 +2742,7 @@
         </is>
       </c>
       <c r="C28" s="18">
-        <f>'Assumptions'!C106</f>
+        <f>'Assumptions'!C107</f>
         <v/>
       </c>
       <c r="D28" s="22" t="inlineStr">
@@ -2758,7 +2767,7 @@
         </is>
       </c>
       <c r="C29" s="24">
-        <f>'Assumptions'!C107</f>
+        <f>'Assumptions'!C108</f>
         <v/>
       </c>
       <c r="D29" s="22" t="inlineStr">
@@ -2782,7 +2791,7 @@
           <t>Amortization (yrs)</t>
         </is>
       </c>
-      <c r="C30" s="83" t="n">
+      <c r="C30" s="86" t="n">
         <v>30</v>
       </c>
       <c r="D30" s="22" t="inlineStr">
@@ -2807,7 +2816,7 @@
         </is>
       </c>
       <c r="C31" s="24">
-        <f>'Assumptions'!C104</f>
+        <f>'Assumptions'!C105</f>
         <v/>
       </c>
       <c r="D31" s="22" t="inlineStr">
@@ -2832,7 +2841,7 @@
         </is>
       </c>
       <c r="C32" s="24">
-        <f>'Assumptions'!C105</f>
+        <f>'Assumptions'!C106</f>
         <v/>
       </c>
       <c r="D32" s="22" t="inlineStr">
@@ -2856,7 +2865,7 @@
           <t>Cost of sale</t>
         </is>
       </c>
-      <c r="C33" s="81" t="n">
+      <c r="C33" s="84" t="n">
         <v>0.02</v>
       </c>
       <c r="D33" s="22" t="inlineStr">
@@ -2880,7 +2889,7 @@
           <t>Hold period (yrs)</t>
         </is>
       </c>
-      <c r="C34" s="83" t="n">
+      <c r="C34" s="86" t="n">
         <v>5</v>
       </c>
       <c r="D34" s="22" t="inlineStr">
@@ -2904,7 +2913,7 @@
           <t>Discount rate (NPV)</t>
         </is>
       </c>
-      <c r="C35" s="81" t="n">
+      <c r="C35" s="84" t="n">
         <v>0.1</v>
       </c>
       <c r="D35" s="22" t="inlineStr">
@@ -2928,7 +2937,7 @@
           <t>Sale comp ($/SF)</t>
         </is>
       </c>
-      <c r="C36" s="75" t="n">
+      <c r="C36" s="78" t="n">
         <v>300</v>
       </c>
       <c r="D36" s="22" t="inlineStr">
@@ -4246,7 +4255,7 @@
         </is>
       </c>
       <c r="C87" s="14" t="n"/>
-      <c r="D87" s="73" t="n">
+      <c r="D87" s="77" t="n">
         <v>96930</v>
       </c>
       <c r="E87" s="53">
@@ -4281,14 +4290,14 @@
         </is>
       </c>
       <c r="C88" s="14" t="n"/>
-      <c r="D88" s="73" t="n">
+      <c r="D88" s="77" t="n">
         <v>71877</v>
       </c>
       <c r="E88" s="53">
         <f>D88/C15</f>
         <v/>
       </c>
-      <c r="F88" s="87" t="inlineStr">
+      <c r="F88" s="90" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4326,7 +4335,7 @@
         <f>SUM(E87:E88)</f>
         <v/>
       </c>
-      <c r="F89" s="88" t="inlineStr">
+      <c r="F89" s="91" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4374,7 +4383,7 @@
           <t>Condo buyout premium (fractured ownership / holdout)</t>
         </is>
       </c>
-      <c r="C92" s="81" t="n">
+      <c r="C92" s="84" t="n">
         <v>0.12</v>
       </c>
       <c r="D92" s="22" t="inlineStr">
@@ -4488,19 +4497,19 @@
           <t>$ / year</t>
         </is>
       </c>
-      <c r="F99" s="84" t="inlineStr">
+      <c r="F99" s="87" t="inlineStr">
         <is>
           <t>Year 1</t>
         </is>
       </c>
       <c r="G99" s="14" t="n"/>
-      <c r="H99" s="84" t="inlineStr">
+      <c r="H99" s="87" t="inlineStr">
         <is>
           <t>Stabilized</t>
         </is>
       </c>
       <c r="I99" s="14" t="n"/>
-      <c r="J99" s="84" t="inlineStr">
+      <c r="J99" s="87" t="inlineStr">
         <is>
           <t>Per SF (stab.)</t>
         </is>
@@ -4525,7 +4534,7 @@
         <v/>
       </c>
       <c r="I100" s="14" t="n"/>
-      <c r="J100" s="85">
+      <c r="J100" s="88">
         <f>H100/C15</f>
         <v/>
       </c>
@@ -4573,7 +4582,7 @@
         <v/>
       </c>
       <c r="I102" s="14" t="n"/>
-      <c r="J102" s="85">
+      <c r="J102" s="88">
         <f>H102/C15</f>
         <v/>
       </c>
@@ -4669,7 +4678,7 @@
         <v/>
       </c>
       <c r="I106" s="14" t="n"/>
-      <c r="J106" s="85">
+      <c r="J106" s="88">
         <f>H106/C15</f>
         <v/>
       </c>
@@ -4717,7 +4726,7 @@
         <v/>
       </c>
       <c r="I108" s="14" t="n"/>
-      <c r="J108" s="85">
+      <c r="J108" s="88">
         <f>H108/C15</f>
         <v/>
       </c>
@@ -4765,7 +4774,7 @@
         <v/>
       </c>
       <c r="I110" s="14" t="n"/>
-      <c r="J110" s="85">
+      <c r="J110" s="88">
         <f>H110/C15</f>
         <v/>
       </c>
@@ -5145,7 +5154,7 @@
           <t>Land (SF)</t>
         </is>
       </c>
-      <c r="C15" s="73" t="n">
+      <c r="C15" s="77" t="n">
         <v>104108</v>
       </c>
       <c r="D15" s="22" t="inlineStr">
@@ -5169,7 +5178,7 @@
           <t>Existing office SF</t>
         </is>
       </c>
-      <c r="C16" s="73" t="n">
+      <c r="C16" s="77" t="n">
         <v>84495</v>
       </c>
       <c r="D16" s="22" t="inlineStr">
@@ -5193,7 +5202,7 @@
           <t>Entitled units</t>
         </is>
       </c>
-      <c r="C17" s="73" t="n">
+      <c r="C17" s="77" t="n">
         <v>259</v>
       </c>
       <c r="D17" s="22" t="inlineStr">
@@ -5217,7 +5226,7 @@
           <t>BCPA market value</t>
         </is>
       </c>
-      <c r="C18" s="82" t="n">
+      <c r="C18" s="85" t="n">
         <v>6685580</v>
       </c>
       <c r="D18" s="22" t="inlineStr">
@@ -5242,7 +5251,7 @@
         </is>
       </c>
       <c r="C19" s="18">
-        <f>'Assumptions'!C111</f>
+        <f>'Assumptions'!C112</f>
         <v/>
       </c>
       <c r="D19" s="22" t="inlineStr">
@@ -5267,7 +5276,7 @@
         </is>
       </c>
       <c r="C20" s="26">
-        <f>'Assumptions'!C112</f>
+        <f>'Assumptions'!C113</f>
         <v/>
       </c>
       <c r="D20" s="22" t="inlineStr">
@@ -5292,7 +5301,7 @@
         </is>
       </c>
       <c r="C21" s="26">
-        <f>'Assumptions'!C113</f>
+        <f>'Assumptions'!C114</f>
         <v/>
       </c>
       <c r="D21" s="22" t="inlineStr">
@@ -5317,7 +5326,7 @@
         </is>
       </c>
       <c r="C22" s="18">
-        <f>'Assumptions'!C114</f>
+        <f>'Assumptions'!C115</f>
         <v/>
       </c>
       <c r="D22" s="22" t="inlineStr">
@@ -5341,7 +5350,7 @@
           <t>Effective millage</t>
         </is>
       </c>
-      <c r="C23" s="80" t="n">
+      <c r="C23" s="83" t="n">
         <v>0.0191</v>
       </c>
       <c r="D23" s="22" t="inlineStr">
@@ -5366,7 +5375,7 @@
         </is>
       </c>
       <c r="C24" s="23">
-        <f>'Assumptions'!C110</f>
+        <f>'Assumptions'!C111</f>
         <v/>
       </c>
       <c r="D24" s="22" t="inlineStr">
@@ -5390,7 +5399,7 @@
           <t>Closing &amp; acq costs (% price)</t>
         </is>
       </c>
-      <c r="C25" s="81" t="n">
+      <c r="C25" s="84" t="n">
         <v>0.02</v>
       </c>
       <c r="D25" s="22" t="inlineStr">
@@ -5414,7 +5423,7 @@
           <t>Land value growth</t>
         </is>
       </c>
-      <c r="C26" s="81" t="n">
+      <c r="C26" s="84" t="n">
         <v>0.04</v>
       </c>
       <c r="D26" s="22" t="inlineStr">
@@ -5438,7 +5447,7 @@
           <t>Hold period (yrs)</t>
         </is>
       </c>
-      <c r="C27" s="83" t="n">
+      <c r="C27" s="86" t="n">
         <v>5</v>
       </c>
       <c r="D27" s="22" t="inlineStr">
@@ -5463,7 +5472,7 @@
         </is>
       </c>
       <c r="C28" s="18">
-        <f>'Assumptions'!C115</f>
+        <f>'Assumptions'!C116</f>
         <v/>
       </c>
       <c r="D28" s="22" t="inlineStr">
@@ -5488,7 +5497,7 @@
         </is>
       </c>
       <c r="C29" s="24">
-        <f>'Assumptions'!C116</f>
+        <f>'Assumptions'!C117</f>
         <v/>
       </c>
       <c r="D29" s="22" t="inlineStr">
@@ -5512,7 +5521,7 @@
           <t>Cost of sale at exit</t>
         </is>
       </c>
-      <c r="C30" s="81" t="n">
+      <c r="C30" s="84" t="n">
         <v>0.02</v>
       </c>
       <c r="D30" s="22" t="inlineStr">
@@ -5536,7 +5545,7 @@
           <t>Discount rate (NPV)</t>
         </is>
       </c>
-      <c r="C31" s="81" t="n">
+      <c r="C31" s="84" t="n">
         <v>0.1</v>
       </c>
       <c r="D31" s="22" t="inlineStr">
@@ -5560,7 +5569,7 @@
           <t>Expense growth</t>
         </is>
       </c>
-      <c r="C32" s="81" t="n">
+      <c r="C32" s="84" t="n">
         <v>0.03</v>
       </c>
       <c r="D32" s="22" t="inlineStr">
@@ -5603,17 +5612,17 @@
           <t>Approach</t>
         </is>
       </c>
-      <c r="D35" s="84" t="inlineStr">
+      <c r="D35" s="87" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E35" s="84" t="inlineStr">
+      <c r="E35" s="87" t="inlineStr">
         <is>
           <t>Base</t>
         </is>
       </c>
-      <c r="F35" s="84" t="inlineStr">
+      <c r="F35" s="87" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -5637,15 +5646,15 @@
         </is>
       </c>
       <c r="D36" s="47">
-        <f>C15*'Assumptions'!C32</f>
+        <f>C15*'Assumptions'!C33</f>
         <v/>
       </c>
       <c r="E36" s="51">
-        <f>C15*'Assumptions'!C33</f>
+        <f>C15*'Assumptions'!C34</f>
         <v/>
       </c>
       <c r="F36" s="47">
-        <f>C15*'Assumptions'!C34</f>
+        <f>C15*'Assumptions'!C35</f>
         <v/>
       </c>
       <c r="G36" s="22" t="inlineStr">
@@ -5667,15 +5676,15 @@
         </is>
       </c>
       <c r="D37" s="47">
-        <f>C17*'Assumptions'!C35</f>
+        <f>C17*'Assumptions'!C36</f>
         <v/>
       </c>
       <c r="E37" s="51">
-        <f>C17*'Assumptions'!C36</f>
+        <f>C17*'Assumptions'!C37</f>
         <v/>
       </c>
       <c r="F37" s="47">
-        <f>C17*'Assumptions'!C37</f>
+        <f>C17*'Assumptions'!C38</f>
         <v/>
       </c>
       <c r="G37" s="22" t="inlineStr">
@@ -5756,7 +5765,7 @@
           <t>Concluded acquisition basis</t>
         </is>
       </c>
-      <c r="E40" s="72">
+      <c r="E40" s="76">
         <f>C24</f>
         <v/>
       </c>
@@ -6392,7 +6401,7 @@
         </is>
       </c>
       <c r="C73" s="51">
-        <f>C17*'Assumptions'!C38</f>
+        <f>C17*'Assumptions'!C39</f>
         <v/>
       </c>
       <c r="D73" s="22" t="inlineStr">
@@ -6417,7 +6426,7 @@
         </is>
       </c>
       <c r="C74" s="64">
-        <f>C17*'Assumptions'!C40</f>
+        <f>C17*'Assumptions'!C41</f>
         <v/>
       </c>
       <c r="D74" s="22" t="inlineStr">
@@ -6442,7 +6451,7 @@
         </is>
       </c>
       <c r="C75" s="47">
-        <f>-C74*'Assumptions'!C39</f>
+        <f>-C74*'Assumptions'!C40</f>
         <v/>
       </c>
       <c r="D75" s="22" t="inlineStr">
@@ -6467,7 +6476,7 @@
         </is>
       </c>
       <c r="C76" s="47">
-        <f>-C74*'Assumptions'!C39*'Assumptions'!C41</f>
+        <f>-C74*'Assumptions'!C40*'Assumptions'!C42</f>
         <v/>
       </c>
       <c r="D76" s="22" t="inlineStr">
@@ -6492,7 +6501,7 @@
         </is>
       </c>
       <c r="C77" s="47">
-        <f>-C73*'Assumptions'!C42</f>
+        <f>-C73*'Assumptions'!C43</f>
         <v/>
       </c>
       <c r="D77" s="22" t="inlineStr">
@@ -7930,7 +7939,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M132"/>
+  <dimension ref="A1:M133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.5" customWidth="1" min="1" max="1"/>
@@ -8732,11 +8741,11 @@
     <row r="32" ht="15" customHeight="1">
       <c r="B32" s="12" t="inlineStr">
         <is>
-          <t>Land value — low ($/SF)</t>
-        </is>
-      </c>
-      <c r="C32" s="34" t="n">
-        <v>64</v>
+          <t>Entitlement lift (% uplift post-Live Local approval)</t>
+        </is>
+      </c>
+      <c r="C32" s="31" t="n">
+        <v>0.3</v>
       </c>
       <c r="D32" s="30" t="inlineStr">
         <is>
@@ -8745,7 +8754,7 @@
       </c>
       <c r="E32" s="22" t="inlineStr">
         <is>
-          <t>BCPA-implied floor</t>
+          <t>assembled land value bump once entitled</t>
         </is>
       </c>
       <c r="F32" s="13" t="n"/>
@@ -8760,11 +8769,11 @@
     <row r="33" ht="15" customHeight="1">
       <c r="B33" s="12" t="inlineStr">
         <is>
-          <t>Land value — base ($/SF)</t>
+          <t>Land value — low ($/SF)</t>
         </is>
       </c>
       <c r="C33" s="34" t="n">
-        <v>125</v>
+        <v>64</v>
       </c>
       <c r="D33" s="30" t="inlineStr">
         <is>
@@ -8773,7 +8782,7 @@
       </c>
       <c r="E33" s="22" t="inlineStr">
         <is>
-          <t>mid-block corridor</t>
+          <t>BCPA-implied floor</t>
         </is>
       </c>
       <c r="F33" s="13" t="n"/>
@@ -8788,11 +8797,11 @@
     <row r="34" ht="15" customHeight="1">
       <c r="B34" s="12" t="inlineStr">
         <is>
-          <t>Land value — high ($/SF)</t>
+          <t>Land value — base ($/SF)</t>
         </is>
       </c>
       <c r="C34" s="34" t="n">
-        <v>200</v>
+        <v>125</v>
       </c>
       <c r="D34" s="30" t="inlineStr">
         <is>
@@ -8801,7 +8810,7 @@
       </c>
       <c r="E34" s="22" t="inlineStr">
         <is>
-          <t>toward hard-corner comps</t>
+          <t>mid-block corridor</t>
         </is>
       </c>
       <c r="F34" s="13" t="n"/>
@@ -8816,11 +8825,11 @@
     <row r="35" ht="15" customHeight="1">
       <c r="B35" s="12" t="inlineStr">
         <is>
-          <t>Per entitled unit — low ($)</t>
-        </is>
-      </c>
-      <c r="C35" s="35" t="n">
-        <v>40000</v>
+          <t>Land value — high ($/SF)</t>
+        </is>
+      </c>
+      <c r="C35" s="34" t="n">
+        <v>200</v>
       </c>
       <c r="D35" s="30" t="inlineStr">
         <is>
@@ -8829,7 +8838,7 @@
       </c>
       <c r="E35" s="22" t="inlineStr">
         <is>
-          <t>259 units</t>
+          <t>toward hard-corner comps</t>
         </is>
       </c>
       <c r="F35" s="13" t="n"/>
@@ -8844,11 +8853,11 @@
     <row r="36" ht="15" customHeight="1">
       <c r="B36" s="12" t="inlineStr">
         <is>
-          <t>Per entitled unit — base ($)</t>
+          <t>Per entitled unit — low ($)</t>
         </is>
       </c>
       <c r="C36" s="35" t="n">
-        <v>55000</v>
+        <v>40000</v>
       </c>
       <c r="D36" s="30" t="inlineStr">
         <is>
@@ -8857,7 +8866,7 @@
       </c>
       <c r="E36" s="22" t="inlineStr">
         <is>
-          <t>entitled-land value</t>
+          <t>259 units</t>
         </is>
       </c>
       <c r="F36" s="13" t="n"/>
@@ -8872,11 +8881,11 @@
     <row r="37" ht="15" customHeight="1">
       <c r="B37" s="12" t="inlineStr">
         <is>
-          <t>Per entitled unit — high ($)</t>
+          <t>Per entitled unit — base ($)</t>
         </is>
       </c>
       <c r="C37" s="35" t="n">
-        <v>70000</v>
+        <v>55000</v>
       </c>
       <c r="D37" s="30" t="inlineStr">
         <is>
@@ -8885,7 +8894,7 @@
       </c>
       <c r="E37" s="22" t="inlineStr">
         <is>
-          <t>strong entitlement</t>
+          <t>entitled-land value</t>
         </is>
       </c>
       <c r="F37" s="13" t="n"/>
@@ -8900,11 +8909,11 @@
     <row r="38" ht="15" customHeight="1">
       <c r="B38" s="12" t="inlineStr">
         <is>
-          <t>Achievable value per unit ($)</t>
+          <t>Per entitled unit — high ($)</t>
         </is>
       </c>
       <c r="C38" s="35" t="n">
-        <v>600000</v>
+        <v>70000</v>
       </c>
       <c r="D38" s="30" t="inlineStr">
         <is>
@@ -8913,7 +8922,7 @@
       </c>
       <c r="E38" s="22" t="inlineStr">
         <is>
-          <t>sellout / cap'd rental</t>
+          <t>strong entitlement</t>
         </is>
       </c>
       <c r="F38" s="13" t="n"/>
@@ -8928,11 +8937,11 @@
     <row r="39" ht="15" customHeight="1">
       <c r="B39" s="12" t="inlineStr">
         <is>
-          <t>Hard cost ($/GBA SF)</t>
-        </is>
-      </c>
-      <c r="C39" s="34" t="n">
-        <v>500</v>
+          <t>Achievable value per unit ($)</t>
+        </is>
+      </c>
+      <c r="C39" s="35" t="n">
+        <v>600000</v>
       </c>
       <c r="D39" s="30" t="inlineStr">
         <is>
@@ -8941,7 +8950,7 @@
       </c>
       <c r="E39" s="22" t="inlineStr">
         <is>
-          <t>AE-zone coastal</t>
+          <t>sellout / cap'd rental</t>
         </is>
       </c>
       <c r="F39" s="13" t="n"/>
@@ -8956,11 +8965,11 @@
     <row r="40" ht="15" customHeight="1">
       <c r="B40" s="12" t="inlineStr">
         <is>
-          <t>GBA per unit (SF)</t>
-        </is>
-      </c>
-      <c r="C40" s="36" t="n">
-        <v>950</v>
+          <t>Hard cost ($/GBA SF)</t>
+        </is>
+      </c>
+      <c r="C40" s="34" t="n">
+        <v>500</v>
       </c>
       <c r="D40" s="30" t="inlineStr">
         <is>
@@ -8969,7 +8978,7 @@
       </c>
       <c r="E40" s="22" t="inlineStr">
         <is>
-          <t>gross buildable/unit</t>
+          <t>AE-zone coastal</t>
         </is>
       </c>
       <c r="F40" s="13" t="n"/>
@@ -8984,11 +8993,11 @@
     <row r="41" ht="15" customHeight="1">
       <c r="B41" s="12" t="inlineStr">
         <is>
-          <t>Soft cost (% hard)</t>
-        </is>
-      </c>
-      <c r="C41" s="31" t="n">
-        <v>0.2</v>
+          <t>GBA per unit (SF)</t>
+        </is>
+      </c>
+      <c r="C41" s="36" t="n">
+        <v>950</v>
       </c>
       <c r="D41" s="30" t="inlineStr">
         <is>
@@ -8997,7 +9006,7 @@
       </c>
       <c r="E41" s="22" t="inlineStr">
         <is>
-          <t>A&amp;E, financing, fees</t>
+          <t>gross buildable/unit</t>
         </is>
       </c>
       <c r="F41" s="13" t="n"/>
@@ -9012,11 +9021,11 @@
     <row r="42" ht="15" customHeight="1">
       <c r="B42" s="12" t="inlineStr">
         <is>
-          <t>Developer profit (% GDV)</t>
+          <t>Soft cost (% hard)</t>
         </is>
       </c>
       <c r="C42" s="31" t="n">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="D42" s="30" t="inlineStr">
         <is>
@@ -9025,7 +9034,7 @@
       </c>
       <c r="E42" s="22" t="inlineStr">
         <is>
-          <t>required margin</t>
+          <t>A&amp;E, financing, fees</t>
         </is>
       </c>
       <c r="F42" s="13" t="n"/>
@@ -9037,157 +9046,175 @@
       <c r="L42" s="13" t="n"/>
       <c r="M42" s="14" t="n"/>
     </row>
-    <row r="43"/>
-    <row r="44">
-      <c r="B44" s="11" t="inlineStr">
+    <row r="43" ht="15" customHeight="1">
+      <c r="B43" s="12" t="inlineStr">
+        <is>
+          <t>Developer profit (% GDV)</t>
+        </is>
+      </c>
+      <c r="C43" s="31" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D43" s="30" t="inlineStr">
+        <is>
+          <t>🔶</t>
+        </is>
+      </c>
+      <c r="E43" s="22" t="inlineStr">
+        <is>
+          <t>required margin</t>
+        </is>
+      </c>
+      <c r="F43" s="13" t="n"/>
+      <c r="G43" s="13" t="n"/>
+      <c r="H43" s="13" t="n"/>
+      <c r="I43" s="13" t="n"/>
+      <c r="J43" s="13" t="n"/>
+      <c r="K43" s="13" t="n"/>
+      <c r="L43" s="13" t="n"/>
+      <c r="M43" s="14" t="n"/>
+    </row>
+    <row r="44"/>
+    <row r="45">
+      <c r="B45" s="11" t="inlineStr">
         <is>
           <t>PER-ASSET INPUTS  —  value drivers &amp; OPERATING EXPENSES  (each asset tab reads these)</t>
         </is>
       </c>
-      <c r="C44" s="2" t="n"/>
-      <c r="D44" s="2" t="n"/>
-      <c r="E44" s="2" t="n"/>
-      <c r="F44" s="2" t="n"/>
-      <c r="G44" s="2" t="n"/>
-      <c r="H44" s="2" t="n"/>
-      <c r="I44" s="2" t="n"/>
-      <c r="J44" s="2" t="n"/>
-      <c r="K44" s="2" t="n"/>
-      <c r="L44" s="2" t="n"/>
-      <c r="M44" s="3" t="n"/>
-    </row>
-    <row r="45" ht="15" customHeight="1">
-      <c r="B45" s="15" t="inlineStr">
+      <c r="C45" s="2" t="n"/>
+      <c r="D45" s="2" t="n"/>
+      <c r="E45" s="2" t="n"/>
+      <c r="F45" s="2" t="n"/>
+      <c r="G45" s="2" t="n"/>
+      <c r="H45" s="2" t="n"/>
+      <c r="I45" s="2" t="n"/>
+      <c r="J45" s="2" t="n"/>
+      <c r="K45" s="2" t="n"/>
+      <c r="L45" s="2" t="n"/>
+      <c r="M45" s="3" t="n"/>
+    </row>
+    <row r="46" ht="15" customHeight="1">
+      <c r="B46" s="15" t="inlineStr">
         <is>
           <t>Shahidi Retail (Galleria Plaza) — NNN retail  ✅ verified parcel</t>
         </is>
       </c>
-      <c r="C45" s="13" t="n"/>
-      <c r="D45" s="13" t="n"/>
-      <c r="E45" s="13" t="n"/>
-      <c r="F45" s="13" t="n"/>
-      <c r="G45" s="13" t="n"/>
-      <c r="H45" s="13" t="n"/>
-      <c r="I45" s="13" t="n"/>
-      <c r="J45" s="13" t="n"/>
-      <c r="K45" s="13" t="n"/>
-      <c r="L45" s="13" t="n"/>
-      <c r="M45" s="14" t="n"/>
-    </row>
-    <row r="46" ht="15" customHeight="1">
-      <c r="B46" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Purchase price / basis</t>
-        </is>
-      </c>
-      <c r="C46" s="37" t="n">
-        <v>17100000</v>
-      </c>
+      <c r="C46" s="13" t="n"/>
+      <c r="D46" s="13" t="n"/>
+      <c r="E46" s="13" t="n"/>
+      <c r="F46" s="13" t="n"/>
+      <c r="G46" s="13" t="n"/>
+      <c r="H46" s="13" t="n"/>
+      <c r="I46" s="13" t="n"/>
+      <c r="J46" s="13" t="n"/>
+      <c r="K46" s="13" t="n"/>
+      <c r="L46" s="13" t="n"/>
+      <c r="M46" s="14" t="n"/>
     </row>
     <row r="47" ht="15" customHeight="1">
       <c r="B47" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Land (SF)</t>
-        </is>
-      </c>
-      <c r="C47" s="36" t="n">
-        <v>67080</v>
+          <t xml:space="preserve">   Purchase price / basis</t>
+        </is>
+      </c>
+      <c r="C47" s="37" t="n">
+        <v>17100000</v>
       </c>
     </row>
     <row r="48" ht="15" customHeight="1">
       <c r="B48" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Land value ($/SF)</t>
-        </is>
-      </c>
-      <c r="C48" s="34" t="n">
-        <v>254.92</v>
+          <t xml:space="preserve">   Land (SF)</t>
+        </is>
+      </c>
+      <c r="C48" s="36" t="n">
+        <v>67080</v>
       </c>
     </row>
     <row r="49" ht="15" customHeight="1">
       <c r="B49" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Market rent ($/SF NNN)</t>
+          <t xml:space="preserve">   Land value ($/SF)</t>
         </is>
       </c>
       <c r="C49" s="34" t="n">
-        <v>55</v>
+        <v>254.92</v>
       </c>
     </row>
     <row r="50" ht="15" customHeight="1">
       <c r="B50" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   In-place occupancy</t>
-        </is>
-      </c>
-      <c r="C50" s="31" t="n">
-        <v>0.8317</v>
+          <t xml:space="preserve">   Market rent ($/SF NNN)</t>
+        </is>
+      </c>
+      <c r="C50" s="34" t="n">
+        <v>55</v>
       </c>
     </row>
     <row r="51" ht="15" customHeight="1">
       <c r="B51" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Stabilized occupancy</t>
+          <t xml:space="preserve">   In-place occupancy</t>
         </is>
       </c>
       <c r="C51" s="31" t="n">
-        <v>0.95</v>
+        <v>0.8317</v>
       </c>
     </row>
     <row r="52" ht="15" customHeight="1">
       <c r="B52" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Insurance ($/yr)</t>
-        </is>
-      </c>
-      <c r="C52" s="35" t="n">
-        <v>65000</v>
+          <t xml:space="preserve">   Stabilized occupancy</t>
+        </is>
+      </c>
+      <c r="C52" s="31" t="n">
+        <v>0.95</v>
       </c>
     </row>
     <row r="53" ht="15" customHeight="1">
       <c r="B53" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   CAM ($/yr, recoverable)</t>
+          <t xml:space="preserve">   Insurance ($/yr)</t>
         </is>
       </c>
       <c r="C53" s="35" t="n">
-        <v>55000</v>
+        <v>65000</v>
       </c>
     </row>
     <row r="54" ht="15" customHeight="1">
       <c r="B54" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Repairs &amp; maintenance ($/yr)</t>
+          <t xml:space="preserve">   CAM ($/yr, recoverable)</t>
         </is>
       </c>
       <c r="C54" s="35" t="n">
-        <v>40000</v>
+        <v>55000</v>
       </c>
     </row>
     <row r="55" ht="15" customHeight="1">
       <c r="B55" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Management fee (% EGR)</t>
-        </is>
-      </c>
-      <c r="C55" s="31" t="n">
-        <v>0.04</v>
+          <t xml:space="preserve">   Repairs &amp; maintenance ($/yr)</t>
+        </is>
+      </c>
+      <c r="C55" s="35" t="n">
+        <v>40000</v>
       </c>
     </row>
     <row r="56" ht="15" customHeight="1">
       <c r="B56" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Going-in cap</t>
-        </is>
-      </c>
-      <c r="C56" s="29" t="n">
-        <v>0.06</v>
+          <t xml:space="preserve">   Management fee (% EGR)</t>
+        </is>
+      </c>
+      <c r="C56" s="31" t="n">
+        <v>0.04</v>
       </c>
     </row>
     <row r="57" ht="15" customHeight="1">
       <c r="B57" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Exit cap</t>
+          <t xml:space="preserve">   Going-in cap</t>
         </is>
       </c>
       <c r="C57" s="29" t="n">
@@ -9197,136 +9224,136 @@
     <row r="58" ht="15" customHeight="1">
       <c r="B58" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Senior LTV</t>
-        </is>
-      </c>
-      <c r="C58" s="31" t="n">
-        <v>0.65</v>
+          <t xml:space="preserve">   Exit cap</t>
+        </is>
+      </c>
+      <c r="C58" s="29" t="n">
+        <v>0.06</v>
       </c>
     </row>
     <row r="59" ht="15" customHeight="1">
       <c r="B59" s="12" t="inlineStr">
         <is>
+          <t xml:space="preserve">   Senior LTV</t>
+        </is>
+      </c>
+      <c r="C59" s="31" t="n">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="60" ht="15" customHeight="1">
+      <c r="B60" s="12" t="inlineStr">
+        <is>
           <t xml:space="preserve">   Senior rate</t>
         </is>
       </c>
-      <c r="C59" s="29" t="n">
+      <c r="C60" s="29" t="n">
         <v>0.0675</v>
       </c>
     </row>
-    <row r="60"/>
-    <row r="61" ht="15" customHeight="1">
-      <c r="B61" s="15" t="inlineStr">
+    <row r="61"/>
+    <row r="62" ht="15" customHeight="1">
+      <c r="B62" s="15" t="inlineStr">
         <is>
           <t>Publix + Starbucks — SALE-LEASEBACK (acquire fee, lease back during entitlement)  ✅ verified parcel</t>
         </is>
       </c>
-      <c r="C61" s="13" t="n"/>
-      <c r="D61" s="13" t="n"/>
-      <c r="E61" s="13" t="n"/>
-      <c r="F61" s="13" t="n"/>
-      <c r="G61" s="13" t="n"/>
-      <c r="H61" s="13" t="n"/>
-      <c r="I61" s="13" t="n"/>
-      <c r="J61" s="13" t="n"/>
-      <c r="K61" s="13" t="n"/>
-      <c r="L61" s="13" t="n"/>
-      <c r="M61" s="14" t="n"/>
-    </row>
-    <row r="62" ht="15" customHeight="1">
-      <c r="B62" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   SLB acquisition price (fee)</t>
-        </is>
-      </c>
-      <c r="C62" s="37" t="n">
-        <v>25000000</v>
-      </c>
+      <c r="C62" s="13" t="n"/>
+      <c r="D62" s="13" t="n"/>
+      <c r="E62" s="13" t="n"/>
+      <c r="F62" s="13" t="n"/>
+      <c r="G62" s="13" t="n"/>
+      <c r="H62" s="13" t="n"/>
+      <c r="I62" s="13" t="n"/>
+      <c r="J62" s="13" t="n"/>
+      <c r="K62" s="13" t="n"/>
+      <c r="L62" s="13" t="n"/>
+      <c r="M62" s="14" t="n"/>
     </row>
     <row r="63" ht="15" customHeight="1">
       <c r="B63" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Land (SF)</t>
-        </is>
-      </c>
-      <c r="C63" s="36" t="n">
-        <v>109791</v>
+          <t xml:space="preserve">   SLB acquisition price (fee)</t>
+        </is>
+      </c>
+      <c r="C63" s="37" t="n">
+        <v>25000000</v>
       </c>
     </row>
     <row r="64" ht="15" customHeight="1">
       <c r="B64" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Land value ($/SF)</t>
-        </is>
-      </c>
-      <c r="C64" s="34" t="n">
-        <v>227.75</v>
+          <t xml:space="preserve">   Land (SF)</t>
+        </is>
+      </c>
+      <c r="C64" s="36" t="n">
+        <v>109791</v>
       </c>
     </row>
     <row r="65" ht="15" customHeight="1">
       <c r="B65" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Publix leaseback rent ($/SF NNN)</t>
+          <t xml:space="preserve">   Land value ($/SF)</t>
         </is>
       </c>
       <c r="C65" s="34" t="n">
-        <v>22</v>
+        <v>227.75</v>
       </c>
     </row>
     <row r="66" ht="15" customHeight="1">
       <c r="B66" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Publix leaseback SF</t>
-        </is>
-      </c>
-      <c r="C66" s="36" t="n">
-        <v>34622</v>
+          <t xml:space="preserve">   Publix leaseback rent ($/SF NNN)</t>
+        </is>
+      </c>
+      <c r="C66" s="34" t="n">
+        <v>22</v>
       </c>
     </row>
     <row r="67" ht="15" customHeight="1">
       <c r="B67" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Starbucks pad rent ($/SF NNN)</t>
-        </is>
-      </c>
-      <c r="C67" s="34" t="n">
-        <v>60</v>
+          <t xml:space="preserve">   Publix leaseback SF</t>
+        </is>
+      </c>
+      <c r="C67" s="36" t="n">
+        <v>34622</v>
       </c>
     </row>
     <row r="68" ht="15" customHeight="1">
       <c r="B68" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Starbucks pad SF</t>
-        </is>
-      </c>
-      <c r="C68" s="36" t="n">
-        <v>2200</v>
+          <t xml:space="preserve">   Starbucks pad rent ($/SF NNN)</t>
+        </is>
+      </c>
+      <c r="C68" s="34" t="n">
+        <v>60</v>
       </c>
     </row>
     <row r="69" ht="15" customHeight="1">
       <c r="B69" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Leaseback term / entitlement (yrs)</t>
-        </is>
-      </c>
-      <c r="C69" s="32" t="n">
-        <v>4</v>
+          <t xml:space="preserve">   Starbucks pad SF</t>
+        </is>
+      </c>
+      <c r="C69" s="36" t="n">
+        <v>2200</v>
       </c>
     </row>
     <row r="70" ht="15" customHeight="1">
       <c r="B70" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   In-place occupancy</t>
-        </is>
-      </c>
-      <c r="C70" s="31" t="n">
-        <v>1</v>
+          <t xml:space="preserve">   Leaseback term / entitlement (yrs)</t>
+        </is>
+      </c>
+      <c r="C70" s="32" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="71" ht="15" customHeight="1">
       <c r="B71" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Stabilized occupancy</t>
+          <t xml:space="preserve">   In-place occupancy</t>
         </is>
       </c>
       <c r="C71" s="31" t="n">
@@ -9336,176 +9363,176 @@
     <row r="72" ht="15" customHeight="1">
       <c r="B72" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Insurance ($/yr)</t>
-        </is>
-      </c>
-      <c r="C72" s="35" t="n">
-        <v>45000</v>
+          <t xml:space="preserve">   Stabilized occupancy</t>
+        </is>
+      </c>
+      <c r="C72" s="31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="73" ht="15" customHeight="1">
       <c r="B73" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   CAM ($/yr, recoverable)</t>
+          <t xml:space="preserve">   Insurance ($/yr)</t>
         </is>
       </c>
       <c r="C73" s="35" t="n">
-        <v>35000</v>
+        <v>45000</v>
       </c>
     </row>
     <row r="74" ht="15" customHeight="1">
       <c r="B74" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Repairs &amp; maintenance ($/yr)</t>
+          <t xml:space="preserve">   CAM ($/yr, recoverable)</t>
         </is>
       </c>
       <c r="C74" s="35" t="n">
-        <v>25000</v>
+        <v>35000</v>
       </c>
     </row>
     <row r="75" ht="15" customHeight="1">
       <c r="B75" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Management fee (% EGR)</t>
-        </is>
-      </c>
-      <c r="C75" s="31" t="n">
-        <v>0.02</v>
+          <t xml:space="preserve">   Repairs &amp; maintenance ($/yr)</t>
+        </is>
+      </c>
+      <c r="C75" s="35" t="n">
+        <v>25000</v>
       </c>
     </row>
     <row r="76" ht="15" customHeight="1">
       <c r="B76" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Going-in cap (reference)</t>
-        </is>
-      </c>
-      <c r="C76" s="29" t="n">
-        <v>0.06</v>
+          <t xml:space="preserve">   Management fee (% EGR)</t>
+        </is>
+      </c>
+      <c r="C76" s="31" t="n">
+        <v>0.02</v>
       </c>
     </row>
     <row r="77" ht="15" customHeight="1">
       <c r="B77" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Exit cap</t>
+          <t xml:space="preserve">   Going-in cap (reference)</t>
         </is>
       </c>
       <c r="C77" s="29" t="n">
-        <v>0.0625</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="78" ht="15" customHeight="1">
       <c r="B78" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Senior LTV (covered-land, conservative)</t>
-        </is>
-      </c>
-      <c r="C78" s="31" t="n">
-        <v>0.45</v>
+          <t xml:space="preserve">   Exit cap</t>
+        </is>
+      </c>
+      <c r="C78" s="29" t="n">
+        <v>0.0625</v>
       </c>
     </row>
     <row r="79" ht="15" customHeight="1">
       <c r="B79" s="12" t="inlineStr">
         <is>
+          <t xml:space="preserve">   Senior LTV (covered-land, conservative)</t>
+        </is>
+      </c>
+      <c r="C79" s="31" t="n">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="80" ht="15" customHeight="1">
+      <c r="B80" s="12" t="inlineStr">
+        <is>
           <t xml:space="preserve">   Senior rate</t>
         </is>
       </c>
-      <c r="C79" s="29" t="n">
+      <c r="C80" s="29" t="n">
         <v>0.0625</v>
       </c>
     </row>
-    <row r="80"/>
-    <row r="81" ht="15" customHeight="1">
-      <c r="B81" s="15" t="inlineStr">
+    <row r="81"/>
+    <row r="82" ht="15" customHeight="1">
+      <c r="B82" s="15" t="inlineStr">
         <is>
           <t>Sunrise Plaza (Kar Luen) — value-add retail  ⚠️ reported parcel</t>
         </is>
       </c>
-      <c r="C81" s="13" t="n"/>
-      <c r="D81" s="13" t="n"/>
-      <c r="E81" s="13" t="n"/>
-      <c r="F81" s="13" t="n"/>
-      <c r="G81" s="13" t="n"/>
-      <c r="H81" s="13" t="n"/>
-      <c r="I81" s="13" t="n"/>
-      <c r="J81" s="13" t="n"/>
-      <c r="K81" s="13" t="n"/>
-      <c r="L81" s="13" t="n"/>
-      <c r="M81" s="14" t="n"/>
-    </row>
-    <row r="82" ht="15" customHeight="1">
-      <c r="B82" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Purchase price / basis</t>
-        </is>
-      </c>
-      <c r="C82" s="37" t="n">
-        <v>8500000</v>
-      </c>
+      <c r="C82" s="13" t="n"/>
+      <c r="D82" s="13" t="n"/>
+      <c r="E82" s="13" t="n"/>
+      <c r="F82" s="13" t="n"/>
+      <c r="G82" s="13" t="n"/>
+      <c r="H82" s="13" t="n"/>
+      <c r="I82" s="13" t="n"/>
+      <c r="J82" s="13" t="n"/>
+      <c r="K82" s="13" t="n"/>
+      <c r="L82" s="13" t="n"/>
+      <c r="M82" s="14" t="n"/>
     </row>
     <row r="83" ht="15" customHeight="1">
       <c r="B83" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Land (SF)</t>
-        </is>
-      </c>
-      <c r="C83" s="36" t="n">
-        <v>30928</v>
+          <t xml:space="preserve">   Purchase price / basis</t>
+        </is>
+      </c>
+      <c r="C83" s="37" t="n">
+        <v>8500000</v>
       </c>
     </row>
     <row r="84" ht="15" customHeight="1">
       <c r="B84" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Land value ($/SF)</t>
-        </is>
-      </c>
-      <c r="C84" s="34" t="n">
-        <v>248</v>
+          <t xml:space="preserve">   Land (SF)</t>
+        </is>
+      </c>
+      <c r="C84" s="36" t="n">
+        <v>30928</v>
       </c>
     </row>
     <row r="85" ht="15" customHeight="1">
       <c r="B85" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Market rent ($/SF NNN)</t>
+          <t xml:space="preserve">   Land value ($/SF)</t>
         </is>
       </c>
       <c r="C85" s="34" t="n">
-        <v>34</v>
+        <v>248</v>
       </c>
     </row>
     <row r="86" ht="15" customHeight="1">
       <c r="B86" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   In-place occupancy</t>
-        </is>
-      </c>
-      <c r="C86" s="31" t="n">
-        <v>0.801</v>
+          <t xml:space="preserve">   Market rent ($/SF NNN)</t>
+        </is>
+      </c>
+      <c r="C86" s="34" t="n">
+        <v>34</v>
       </c>
     </row>
     <row r="87" ht="15" customHeight="1">
       <c r="B87" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Stabilized occupancy</t>
+          <t xml:space="preserve">   In-place occupancy</t>
         </is>
       </c>
       <c r="C87" s="31" t="n">
-        <v>0.95</v>
+        <v>0.801</v>
       </c>
     </row>
     <row r="88" ht="15" customHeight="1">
       <c r="B88" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Insurance ($/yr)</t>
-        </is>
-      </c>
-      <c r="C88" s="35" t="n">
-        <v>40000</v>
+          <t xml:space="preserve">   Stabilized occupancy</t>
+        </is>
+      </c>
+      <c r="C88" s="31" t="n">
+        <v>0.95</v>
       </c>
     </row>
     <row r="89" ht="15" customHeight="1">
       <c r="B89" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   CAM ($/yr, recoverable)</t>
+          <t xml:space="preserve">   Insurance ($/yr)</t>
         </is>
       </c>
       <c r="C89" s="35" t="n">
@@ -9515,338 +9542,319 @@
     <row r="90" ht="15" customHeight="1">
       <c r="B90" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Repairs &amp; maintenance ($/yr)</t>
+          <t xml:space="preserve">   CAM ($/yr, recoverable)</t>
         </is>
       </c>
       <c r="C90" s="35" t="n">
-        <v>30000</v>
+        <v>40000</v>
       </c>
     </row>
     <row r="91" ht="15" customHeight="1">
       <c r="B91" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Management fee (% EGR)</t>
-        </is>
-      </c>
-      <c r="C91" s="31" t="n">
-        <v>0.04</v>
+          <t xml:space="preserve">   Repairs &amp; maintenance ($/yr)</t>
+        </is>
+      </c>
+      <c r="C91" s="35" t="n">
+        <v>30000</v>
       </c>
     </row>
     <row r="92" ht="15" customHeight="1">
       <c r="B92" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Going-in cap</t>
-        </is>
-      </c>
-      <c r="C92" s="29" t="n">
-        <v>0.075</v>
+          <t xml:space="preserve">   Management fee (% EGR)</t>
+        </is>
+      </c>
+      <c r="C92" s="31" t="n">
+        <v>0.04</v>
       </c>
     </row>
     <row r="93" ht="15" customHeight="1">
       <c r="B93" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Exit cap</t>
+          <t xml:space="preserve">   Going-in cap</t>
         </is>
       </c>
       <c r="C93" s="29" t="n">
-        <v>0.0775</v>
+        <v>0.075</v>
       </c>
     </row>
     <row r="94" ht="15" customHeight="1">
       <c r="B94" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Senior LTV</t>
-        </is>
-      </c>
-      <c r="C94" s="31" t="n">
-        <v>0.6</v>
+          <t xml:space="preserve">   Exit cap</t>
+        </is>
+      </c>
+      <c r="C94" s="29" t="n">
+        <v>0.0775</v>
       </c>
     </row>
     <row r="95" ht="15" customHeight="1">
       <c r="B95" s="12" t="inlineStr">
         <is>
+          <t xml:space="preserve">   Senior LTV</t>
+        </is>
+      </c>
+      <c r="C95" s="31" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="96" ht="15" customHeight="1">
+      <c r="B96" s="12" t="inlineStr">
+        <is>
           <t xml:space="preserve">   Senior rate</t>
         </is>
       </c>
-      <c r="C95" s="29" t="n">
+      <c r="C96" s="29" t="n">
         <v>0.075</v>
       </c>
     </row>
-    <row r="96"/>
-    <row r="97" ht="15" customHeight="1">
-      <c r="B97" s="15" t="inlineStr">
+    <row r="97"/>
+    <row r="98" ht="15" customHeight="1">
+      <c r="B98" s="15" t="inlineStr">
         <is>
           <t>Galleria Corporate Centre — office, Modified Gross  ⚠️ reported parcel</t>
         </is>
       </c>
-      <c r="C97" s="13" t="n"/>
-      <c r="D97" s="13" t="n"/>
-      <c r="E97" s="13" t="n"/>
-      <c r="F97" s="13" t="n"/>
-      <c r="G97" s="13" t="n"/>
-      <c r="H97" s="13" t="n"/>
-      <c r="I97" s="13" t="n"/>
-      <c r="J97" s="13" t="n"/>
-      <c r="K97" s="13" t="n"/>
-      <c r="L97" s="13" t="n"/>
-      <c r="M97" s="14" t="n"/>
-    </row>
-    <row r="98" ht="15" customHeight="1">
-      <c r="B98" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Acquisition basis</t>
-        </is>
-      </c>
-      <c r="C98" s="37" t="n">
-        <v>21700000</v>
-      </c>
+      <c r="C98" s="13" t="n"/>
+      <c r="D98" s="13" t="n"/>
+      <c r="E98" s="13" t="n"/>
+      <c r="F98" s="13" t="n"/>
+      <c r="G98" s="13" t="n"/>
+      <c r="H98" s="13" t="n"/>
+      <c r="I98" s="13" t="n"/>
+      <c r="J98" s="13" t="n"/>
+      <c r="K98" s="13" t="n"/>
+      <c r="L98" s="13" t="n"/>
+      <c r="M98" s="14" t="n"/>
     </row>
     <row r="99" ht="15" customHeight="1">
       <c r="B99" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Market rent ($/SF MG)</t>
-        </is>
-      </c>
-      <c r="C99" s="34" t="n">
-        <v>26</v>
+          <t xml:space="preserve">   Acquisition basis</t>
+        </is>
+      </c>
+      <c r="C99" s="37" t="n">
+        <v>21700000</v>
       </c>
     </row>
     <row r="100" ht="15" customHeight="1">
       <c r="B100" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   In-place occupancy</t>
-        </is>
-      </c>
-      <c r="C100" s="31" t="n">
-        <v>0.85</v>
+          <t xml:space="preserve">   Market rent ($/SF MG)</t>
+        </is>
+      </c>
+      <c r="C100" s="34" t="n">
+        <v>26</v>
       </c>
     </row>
     <row r="101" ht="15" customHeight="1">
       <c r="B101" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Stabilized occupancy</t>
+          <t xml:space="preserve">   In-place occupancy</t>
         </is>
       </c>
       <c r="C101" s="31" t="n">
-        <v>0.88</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="102" ht="15" customHeight="1">
       <c r="B102" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Office opex ex-taxes ($/SF, landlord)</t>
-        </is>
-      </c>
-      <c r="C102" s="34" t="n">
-        <v>8</v>
+          <t xml:space="preserve">   Stabilized occupancy</t>
+        </is>
+      </c>
+      <c r="C102" s="31" t="n">
+        <v>0.88</v>
       </c>
     </row>
     <row r="103" ht="15" customHeight="1">
       <c r="B103" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Management fee (% EGR)</t>
-        </is>
-      </c>
-      <c r="C103" s="31" t="n">
-        <v>0.03</v>
+          <t xml:space="preserve">   Office opex ex-taxes ($/SF, landlord)</t>
+        </is>
+      </c>
+      <c r="C103" s="34" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="104" ht="15" customHeight="1">
       <c r="B104" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Going-in cap</t>
-        </is>
-      </c>
-      <c r="C104" s="29" t="n">
-        <v>0.08</v>
+          <t xml:space="preserve">   Management fee (% EGR)</t>
+        </is>
+      </c>
+      <c r="C104" s="31" t="n">
+        <v>0.03</v>
       </c>
     </row>
     <row r="105" ht="15" customHeight="1">
       <c r="B105" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Exit cap</t>
+          <t xml:space="preserve">   Going-in cap</t>
         </is>
       </c>
       <c r="C105" s="29" t="n">
-        <v>0.0825</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="106" ht="15" customHeight="1">
       <c r="B106" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Senior LTV</t>
-        </is>
-      </c>
-      <c r="C106" s="31" t="n">
-        <v>0.55</v>
+          <t xml:space="preserve">   Exit cap</t>
+        </is>
+      </c>
+      <c r="C106" s="29" t="n">
+        <v>0.0825</v>
       </c>
     </row>
     <row r="107" ht="15" customHeight="1">
       <c r="B107" s="12" t="inlineStr">
         <is>
+          <t xml:space="preserve">   Senior LTV</t>
+        </is>
+      </c>
+      <c r="C107" s="31" t="n">
+        <v>0.55</v>
+      </c>
+    </row>
+    <row r="108" ht="15" customHeight="1">
+      <c r="B108" s="12" t="inlineStr">
+        <is>
           <t xml:space="preserve">   Senior rate</t>
         </is>
       </c>
-      <c r="C107" s="29" t="n">
+      <c r="C108" s="29" t="n">
         <v>0.075</v>
       </c>
     </row>
-    <row r="108"/>
-    <row r="109" ht="15" customHeight="1">
-      <c r="B109" s="15" t="inlineStr">
+    <row r="109"/>
+    <row r="110" ht="15" customHeight="1">
+      <c r="B110" s="15" t="inlineStr">
         <is>
           <t>1040 Bayview — covered land (interim office)  ⚠️ reported parcel</t>
         </is>
       </c>
-      <c r="C109" s="13" t="n"/>
-      <c r="D109" s="13" t="n"/>
-      <c r="E109" s="13" t="n"/>
-      <c r="F109" s="13" t="n"/>
-      <c r="G109" s="13" t="n"/>
-      <c r="H109" s="13" t="n"/>
-      <c r="I109" s="13" t="n"/>
-      <c r="J109" s="13" t="n"/>
-      <c r="K109" s="13" t="n"/>
-      <c r="L109" s="13" t="n"/>
-      <c r="M109" s="14" t="n"/>
-    </row>
-    <row r="110" ht="15" customHeight="1">
-      <c r="B110" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Acquisition basis (entitled land)</t>
-        </is>
-      </c>
-      <c r="C110" s="37" t="n">
-        <v>13000000</v>
-      </c>
+      <c r="C110" s="13" t="n"/>
+      <c r="D110" s="13" t="n"/>
+      <c r="E110" s="13" t="n"/>
+      <c r="F110" s="13" t="n"/>
+      <c r="G110" s="13" t="n"/>
+      <c r="H110" s="13" t="n"/>
+      <c r="I110" s="13" t="n"/>
+      <c r="J110" s="13" t="n"/>
+      <c r="K110" s="13" t="n"/>
+      <c r="L110" s="13" t="n"/>
+      <c r="M110" s="14" t="n"/>
     </row>
     <row r="111" ht="15" customHeight="1">
       <c r="B111" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Interim office occupancy</t>
-        </is>
-      </c>
-      <c r="C111" s="31" t="n">
-        <v>0.72</v>
+          <t xml:space="preserve">   Acquisition basis (entitled land)</t>
+        </is>
+      </c>
+      <c r="C111" s="37" t="n">
+        <v>13000000</v>
       </c>
     </row>
     <row r="112" ht="15" customHeight="1">
       <c r="B112" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Interim office rent ($/SF MG)</t>
-        </is>
-      </c>
-      <c r="C112" s="34" t="n">
-        <v>23</v>
+          <t xml:space="preserve">   Interim office occupancy</t>
+        </is>
+      </c>
+      <c r="C112" s="31" t="n">
+        <v>0.72</v>
       </c>
     </row>
     <row r="113" ht="15" customHeight="1">
       <c r="B113" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Interim office opex ($/SF)</t>
+          <t xml:space="preserve">   Interim office rent ($/SF MG)</t>
         </is>
       </c>
       <c r="C113" s="34" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
     </row>
     <row r="114" ht="15" customHeight="1">
       <c r="B114" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Management fee (% EGR)</t>
-        </is>
-      </c>
-      <c r="C114" s="31" t="n">
-        <v>0.03</v>
+          <t xml:space="preserve">   Interim office opex ($/SF)</t>
+        </is>
+      </c>
+      <c r="C114" s="34" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="115" ht="15" customHeight="1">
       <c r="B115" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Land loan LTV</t>
+          <t xml:space="preserve">   Management fee (% EGR)</t>
         </is>
       </c>
       <c r="C115" s="31" t="n">
-        <v>0.4</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="116" ht="15" customHeight="1">
       <c r="B116" s="12" t="inlineStr">
         <is>
+          <t xml:space="preserve">   Land loan LTV</t>
+        </is>
+      </c>
+      <c r="C116" s="31" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="117" ht="15" customHeight="1">
+      <c r="B117" s="12" t="inlineStr">
+        <is>
           <t xml:space="preserve">   Land loan rate</t>
         </is>
       </c>
-      <c r="C116" s="29" t="n">
+      <c r="C117" s="29" t="n">
         <v>0.08500000000000001</v>
       </c>
     </row>
-    <row r="117"/>
-    <row r="118">
-      <c r="B118" s="11" t="inlineStr">
+    <row r="118"/>
+    <row r="119">
+      <c r="B119" s="11" t="inlineStr">
         <is>
           <t>DATA-GAP REGISTER  —  reported figures to verify at BCPA (shown live from source)</t>
         </is>
       </c>
-      <c r="C118" s="2" t="n"/>
-      <c r="D118" s="2" t="n"/>
-      <c r="E118" s="2" t="n"/>
-      <c r="F118" s="2" t="n"/>
-      <c r="G118" s="2" t="n"/>
-      <c r="H118" s="2" t="n"/>
-      <c r="I118" s="2" t="n"/>
-      <c r="J118" s="2" t="n"/>
-      <c r="K118" s="2" t="n"/>
-      <c r="L118" s="2" t="n"/>
-      <c r="M118" s="3" t="n"/>
-    </row>
-    <row r="119" ht="15" customHeight="1">
-      <c r="B119" s="15" t="inlineStr">
+      <c r="C119" s="2" t="n"/>
+      <c r="D119" s="2" t="n"/>
+      <c r="E119" s="2" t="n"/>
+      <c r="F119" s="2" t="n"/>
+      <c r="G119" s="2" t="n"/>
+      <c r="H119" s="2" t="n"/>
+      <c r="I119" s="2" t="n"/>
+      <c r="J119" s="2" t="n"/>
+      <c r="K119" s="2" t="n"/>
+      <c r="L119" s="2" t="n"/>
+      <c r="M119" s="3" t="n"/>
+    </row>
+    <row r="120" ht="15" customHeight="1">
+      <c r="B120" s="15" t="inlineStr">
         <is>
           <t>Figure</t>
         </is>
       </c>
-      <c r="C119" s="16" t="inlineStr">
+      <c r="C120" s="16" t="inlineStr">
         <is>
           <t>Current</t>
         </is>
       </c>
-      <c r="D119" s="16" t="inlineStr">
+      <c r="D120" s="16" t="inlineStr">
         <is>
           <t>Flag</t>
         </is>
       </c>
-      <c r="E119" s="15" t="inlineStr">
+      <c r="E120" s="15" t="inlineStr">
         <is>
           <t>Lives on</t>
-        </is>
-      </c>
-      <c r="F119" s="13" t="n"/>
-      <c r="G119" s="13" t="n"/>
-      <c r="H119" s="13" t="n"/>
-      <c r="I119" s="13" t="n"/>
-      <c r="J119" s="13" t="n"/>
-      <c r="K119" s="13" t="n"/>
-      <c r="L119" s="13" t="n"/>
-      <c r="M119" s="14" t="n"/>
-    </row>
-    <row r="120" ht="15" customHeight="1">
-      <c r="B120" s="12" t="inlineStr">
-        <is>
-          <t>Sunrise Plaza — value / basis</t>
-        </is>
-      </c>
-      <c r="C120" s="38">
-        <f>'Assumptions'!C82</f>
-        <v/>
-      </c>
-      <c r="D120" s="30" t="inlineStr">
-        <is>
-          <t>⚠️</t>
-        </is>
-      </c>
-      <c r="E120" s="22" t="inlineStr">
-        <is>
-          <t>Assumptions · Sunrise block</t>
         </is>
       </c>
       <c r="F120" s="13" t="n"/>
@@ -9861,11 +9869,11 @@
     <row r="121" ht="15" customHeight="1">
       <c r="B121" s="12" t="inlineStr">
         <is>
-          <t>Sunrise Plaza — building SF</t>
-        </is>
-      </c>
-      <c r="C121" s="39">
-        <f>'Sunrise Plaza'!C27</f>
+          <t>Sunrise Plaza — value / basis</t>
+        </is>
+      </c>
+      <c r="C121" s="38">
+        <f>'Assumptions'!C83</f>
         <v/>
       </c>
       <c r="D121" s="30" t="inlineStr">
@@ -9875,7 +9883,7 @@
       </c>
       <c r="E121" s="22" t="inlineStr">
         <is>
-          <t>Sunrise Plaza tab</t>
+          <t>Assumptions · Sunrise block</t>
         </is>
       </c>
       <c r="F121" s="13" t="n"/>
@@ -9890,11 +9898,11 @@
     <row r="122" ht="15" customHeight="1">
       <c r="B122" s="12" t="inlineStr">
         <is>
-          <t>Sunrise Plaza — land SF</t>
+          <t>Sunrise Plaza — building SF</t>
         </is>
       </c>
       <c r="C122" s="39">
-        <f>'Assumptions'!C83</f>
+        <f>'Sunrise Plaza'!C27</f>
         <v/>
       </c>
       <c r="D122" s="30" t="inlineStr">
@@ -9904,7 +9912,7 @@
       </c>
       <c r="E122" s="22" t="inlineStr">
         <is>
-          <t>Assumptions · Sunrise block</t>
+          <t>Sunrise Plaza tab</t>
         </is>
       </c>
       <c r="F122" s="13" t="n"/>
@@ -9919,11 +9927,11 @@
     <row r="123" ht="15" customHeight="1">
       <c r="B123" s="12" t="inlineStr">
         <is>
-          <t>Office — building SF</t>
+          <t>Sunrise Plaza — land SF</t>
         </is>
       </c>
       <c r="C123" s="39">
-        <f>'Office Condo'!C15</f>
+        <f>'Assumptions'!C84</f>
         <v/>
       </c>
       <c r="D123" s="30" t="inlineStr">
@@ -9933,7 +9941,7 @@
       </c>
       <c r="E123" s="22" t="inlineStr">
         <is>
-          <t>Office Condo tab</t>
+          <t>Assumptions · Sunrise block</t>
         </is>
       </c>
       <c r="F123" s="13" t="n"/>
@@ -9948,11 +9956,11 @@
     <row r="124" ht="15" customHeight="1">
       <c r="B124" s="12" t="inlineStr">
         <is>
-          <t>Office — Main St Fund SF (57.4%)</t>
+          <t>Office — building SF</t>
         </is>
       </c>
       <c r="C124" s="39">
-        <f>'Office Condo'!D87</f>
+        <f>'Office Condo'!C15</f>
         <v/>
       </c>
       <c r="D124" s="30" t="inlineStr">
@@ -9977,11 +9985,11 @@
     <row r="125" ht="15" customHeight="1">
       <c r="B125" s="12" t="inlineStr">
         <is>
-          <t>Office — Intl Sunrise SF (42.6%)</t>
+          <t>Office — Main St Fund SF (57.4%)</t>
         </is>
       </c>
       <c r="C125" s="39">
-        <f>'Office Condo'!D88</f>
+        <f>'Office Condo'!D87</f>
         <v/>
       </c>
       <c r="D125" s="30" t="inlineStr">
@@ -10006,21 +10014,21 @@
     <row r="126" ht="15" customHeight="1">
       <c r="B126" s="12" t="inlineStr">
         <is>
-          <t>Office — acquisition basis</t>
-        </is>
-      </c>
-      <c r="C126" s="38">
-        <f>'Assumptions'!C98</f>
+          <t>Office — Intl Sunrise SF (42.6%)</t>
+        </is>
+      </c>
+      <c r="C126" s="39">
+        <f>'Office Condo'!D88</f>
         <v/>
       </c>
       <c r="D126" s="30" t="inlineStr">
         <is>
-          <t>🔶</t>
+          <t>⚠️</t>
         </is>
       </c>
       <c r="E126" s="22" t="inlineStr">
         <is>
-          <t>Assumptions · Office block</t>
+          <t>Office Condo tab</t>
         </is>
       </c>
       <c r="F126" s="13" t="n"/>
@@ -10035,21 +10043,21 @@
     <row r="127" ht="15" customHeight="1">
       <c r="B127" s="12" t="inlineStr">
         <is>
-          <t>1040 Bayview — land SF</t>
-        </is>
-      </c>
-      <c r="C127" s="39">
-        <f>'Land'!C15</f>
+          <t>Office — acquisition basis</t>
+        </is>
+      </c>
+      <c r="C127" s="38">
+        <f>'Assumptions'!C99</f>
         <v/>
       </c>
       <c r="D127" s="30" t="inlineStr">
         <is>
-          <t>⚠️</t>
+          <t>🔶</t>
         </is>
       </c>
       <c r="E127" s="22" t="inlineStr">
         <is>
-          <t>Land tab</t>
+          <t>Assumptions · Office block</t>
         </is>
       </c>
       <c r="F127" s="13" t="n"/>
@@ -10064,11 +10072,11 @@
     <row r="128" ht="15" customHeight="1">
       <c r="B128" s="12" t="inlineStr">
         <is>
-          <t>1040 Bayview — office SF</t>
+          <t>1040 Bayview — land SF</t>
         </is>
       </c>
       <c r="C128" s="39">
-        <f>'Land'!C16</f>
+        <f>'Land'!C15</f>
         <v/>
       </c>
       <c r="D128" s="30" t="inlineStr">
@@ -10093,11 +10101,11 @@
     <row r="129" ht="15" customHeight="1">
       <c r="B129" s="12" t="inlineStr">
         <is>
-          <t>1040 Bayview — entitled units</t>
+          <t>1040 Bayview — office SF</t>
         </is>
       </c>
       <c r="C129" s="39">
-        <f>'Land'!C17</f>
+        <f>'Land'!C16</f>
         <v/>
       </c>
       <c r="D129" s="30" t="inlineStr">
@@ -10122,11 +10130,11 @@
     <row r="130" ht="15" customHeight="1">
       <c r="B130" s="12" t="inlineStr">
         <is>
-          <t>1040 Bayview — BCPA value</t>
-        </is>
-      </c>
-      <c r="C130" s="38">
-        <f>'Land'!C18</f>
+          <t>1040 Bayview — entitled units</t>
+        </is>
+      </c>
+      <c r="C130" s="39">
+        <f>'Land'!C17</f>
         <v/>
       </c>
       <c r="D130" s="30" t="inlineStr">
@@ -10148,54 +10156,83 @@
       <c r="L130" s="13" t="n"/>
       <c r="M130" s="14" t="n"/>
     </row>
-    <row r="131"/>
-    <row r="132" ht="39" customHeight="1">
-      <c r="B132" s="40" t="inlineStr">
+    <row r="131" ht="15" customHeight="1">
+      <c r="B131" s="12" t="inlineStr">
+        <is>
+          <t>1040 Bayview — BCPA value</t>
+        </is>
+      </c>
+      <c r="C131" s="38">
+        <f>'Land'!C18</f>
+        <v/>
+      </c>
+      <c r="D131" s="30" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
+      <c r="E131" s="22" t="inlineStr">
+        <is>
+          <t>Land tab</t>
+        </is>
+      </c>
+      <c r="F131" s="13" t="n"/>
+      <c r="G131" s="13" t="n"/>
+      <c r="H131" s="13" t="n"/>
+      <c r="I131" s="13" t="n"/>
+      <c r="J131" s="13" t="n"/>
+      <c r="K131" s="13" t="n"/>
+      <c r="L131" s="13" t="n"/>
+      <c r="M131" s="14" t="n"/>
+    </row>
+    <row r="132"/>
+    <row r="133" ht="39" customHeight="1">
+      <c r="B133" s="40" t="inlineStr">
         <is>
           <t>How to use</t>
         </is>
       </c>
-      <c r="D132" s="40" t="inlineStr">
+      <c r="D133" s="40" t="inlineStr">
         <is>
           <t>Everything you tune is on THIS tab: global drivers up top, then a block per asset (price · rents · occupancy · operating expenses · caps · debt). Standard modeling params (rent/expense growth, TI/LC, reserves, closing detail) remain blue on each asset tab. ⚠️ = reported, verify at bcpa.net. Change any blue cell → the model recalculates.</t>
         </is>
       </c>
-      <c r="E132" s="13" t="n"/>
-      <c r="F132" s="13" t="n"/>
-      <c r="G132" s="13" t="n"/>
-      <c r="H132" s="13" t="n"/>
-      <c r="I132" s="13" t="n"/>
-      <c r="J132" s="13" t="n"/>
-      <c r="K132" s="13" t="n"/>
-      <c r="L132" s="13" t="n"/>
-      <c r="M132" s="14" t="n"/>
+      <c r="E133" s="13" t="n"/>
+      <c r="F133" s="13" t="n"/>
+      <c r="G133" s="13" t="n"/>
+      <c r="H133" s="13" t="n"/>
+      <c r="I133" s="13" t="n"/>
+      <c r="J133" s="13" t="n"/>
+      <c r="K133" s="13" t="n"/>
+      <c r="L133" s="13" t="n"/>
+      <c r="M133" s="14" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="61">
+  <mergeCells count="62">
     <mergeCell ref="B2:M2"/>
     <mergeCell ref="E29:M29"/>
     <mergeCell ref="E128:M128"/>
     <mergeCell ref="E10:M10"/>
     <mergeCell ref="E28:M28"/>
+    <mergeCell ref="B98:M98"/>
     <mergeCell ref="E13:M13"/>
-    <mergeCell ref="B61:M61"/>
     <mergeCell ref="E40:M40"/>
     <mergeCell ref="E9:M9"/>
     <mergeCell ref="E31:M31"/>
     <mergeCell ref="B1:M1"/>
+    <mergeCell ref="B119:M119"/>
     <mergeCell ref="E34:M34"/>
-    <mergeCell ref="B44:M44"/>
+    <mergeCell ref="B82:M82"/>
+    <mergeCell ref="D133:M133"/>
     <mergeCell ref="E6:M6"/>
     <mergeCell ref="E15:M15"/>
-    <mergeCell ref="D132:M132"/>
     <mergeCell ref="E11:M11"/>
     <mergeCell ref="B19:M19"/>
     <mergeCell ref="E27:M27"/>
     <mergeCell ref="E36:M36"/>
-    <mergeCell ref="E119:M119"/>
     <mergeCell ref="E26:M26"/>
-    <mergeCell ref="B118:M118"/>
     <mergeCell ref="E124:M124"/>
+    <mergeCell ref="E131:M131"/>
     <mergeCell ref="B30:M30"/>
     <mergeCell ref="E120:M120"/>
     <mergeCell ref="E16:M16"/>
@@ -10207,14 +10244,14 @@
     <mergeCell ref="B45:M45"/>
     <mergeCell ref="E22:M22"/>
     <mergeCell ref="E18:M18"/>
-    <mergeCell ref="B97:M97"/>
+    <mergeCell ref="B110:M110"/>
     <mergeCell ref="E21:M21"/>
     <mergeCell ref="B4:M4"/>
+    <mergeCell ref="E43:M43"/>
     <mergeCell ref="E121:M121"/>
-    <mergeCell ref="B109:M109"/>
     <mergeCell ref="E130:M130"/>
+    <mergeCell ref="B62:M62"/>
     <mergeCell ref="E24:M24"/>
-    <mergeCell ref="B81:M81"/>
     <mergeCell ref="B25:M25"/>
     <mergeCell ref="E33:M33"/>
     <mergeCell ref="E122:M122"/>
@@ -10222,6 +10259,7 @@
     <mergeCell ref="E5:M5"/>
     <mergeCell ref="E23:M23"/>
     <mergeCell ref="E42:M42"/>
+    <mergeCell ref="B46:M46"/>
     <mergeCell ref="E14:M14"/>
     <mergeCell ref="E127:M127"/>
     <mergeCell ref="E123:M123"/>
@@ -14873,7 +14911,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M52"/>
+  <dimension ref="A1:M63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.5" customWidth="1" min="1" max="1"/>
@@ -15171,7 +15209,7 @@
     <row r="15">
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>②  LAND VALUE  —  as REGULAR (fragmented) parcels</t>
+          <t>ACQUISITION HISTORY  —  what each owner paid, and when  (seller basis = negotiation leverage)</t>
         </is>
       </c>
       <c r="C15" s="2" t="n"/>
@@ -15189,22 +15227,22 @@
     <row r="16" ht="15" customHeight="1">
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>Parcel</t>
+          <t>Component / owner</t>
         </is>
       </c>
       <c r="C16" s="16" t="inlineStr">
         <is>
-          <t>Land SF</t>
+          <t>Bought</t>
         </is>
       </c>
       <c r="D16" s="16" t="inlineStr">
         <is>
-          <t>$/SF</t>
+          <t>For</t>
         </is>
       </c>
       <c r="E16" s="16" t="inlineStr">
         <is>
-          <t>Land value</t>
+          <t>Our modeled price</t>
         </is>
       </c>
       <c r="F16" s="15" t="inlineStr">
@@ -15221,26 +15259,26 @@
       <c r="M16" s="14" t="n"/>
     </row>
     <row r="17" ht="15" customHeight="1">
-      <c r="B17" s="12" t="inlineStr">
-        <is>
-          <t>Shahidi Retail</t>
-        </is>
-      </c>
-      <c r="C17" s="25">
-        <f>'Shahidi Retail'!C36</f>
-        <v/>
-      </c>
-      <c r="D17" s="26">
-        <f>'Shahidi Retail'!C79</f>
-        <v/>
+      <c r="B17" s="70" t="inlineStr">
+        <is>
+          <t>Shahidi Retail — Shawnick Galleria LLC (Shahidi)</t>
+        </is>
+      </c>
+      <c r="C17" s="71" t="inlineStr">
+        <is>
+          <t>11/09/2021</t>
+        </is>
+      </c>
+      <c r="D17" s="72" t="n">
+        <v>17100000</v>
       </c>
       <c r="E17" s="17">
-        <f>'Shahidi Retail'!C80</f>
+        <f>'Shahidi Retail'!C57</f>
         <v/>
       </c>
       <c r="F17" s="22" t="inlineStr">
         <is>
-          <t>standalone parcel</t>
+          <t>Special Warranty Deed (flagged disqualified sale)</t>
         </is>
       </c>
       <c r="G17" s="13" t="n"/>
@@ -15252,26 +15290,26 @@
       <c r="M17" s="14" t="n"/>
     </row>
     <row r="18" ht="15" customHeight="1">
-      <c r="B18" s="12" t="inlineStr">
-        <is>
-          <t>Publix + Starbucks</t>
-        </is>
-      </c>
-      <c r="C18" s="25">
-        <f>'Publix &amp; Starbucks'!C25</f>
-        <v/>
-      </c>
-      <c r="D18" s="26">
-        <f>'Publix &amp; Starbucks'!C55</f>
-        <v/>
+      <c r="B18" s="70" t="inlineStr">
+        <is>
+          <t>Publix + Starbucks — REAL SUB LLC (Publix)</t>
+        </is>
+      </c>
+      <c r="C18" s="71" t="inlineStr">
+        <is>
+          <t>03/14/2025</t>
+        </is>
+      </c>
+      <c r="D18" s="72" t="n">
+        <v>25000000</v>
       </c>
       <c r="E18" s="17">
-        <f>'Publix &amp; Starbucks'!C67</f>
+        <f>'Publix &amp; Starbucks'!C44</f>
         <v/>
       </c>
       <c r="F18" s="22" t="inlineStr">
         <is>
-          <t>standalone parcel</t>
+          <t>Trustee's Deed · $679/SF bldg</t>
         </is>
       </c>
       <c r="G18" s="13" t="n"/>
@@ -15285,24 +15323,24 @@
     <row r="19" ht="15" customHeight="1">
       <c r="B19" s="12" t="inlineStr">
         <is>
-          <t>Sunrise Plaza (Kar Luen)</t>
-        </is>
-      </c>
-      <c r="C19" s="25">
-        <f>'Sunrise Plaza'!C28</f>
-        <v/>
-      </c>
-      <c r="D19" s="26">
-        <f>'Sunrise Plaza'!C58</f>
-        <v/>
+          <t>Sunrise Plaza — Kar Luen Inc</t>
+        </is>
+      </c>
+      <c r="C19" s="30" t="inlineStr">
+        <is>
+          <t>Oct 2000</t>
+        </is>
+      </c>
+      <c r="D19" s="47" t="n">
+        <v>128000</v>
       </c>
       <c r="E19" s="17">
-        <f>'Sunrise Plaza'!C70</f>
+        <f>'Sunrise Plaza'!C47</f>
         <v/>
       </c>
       <c r="F19" s="22" t="inlineStr">
         <is>
-          <t>standalone parcel</t>
+          <t>stale/nominal — held since; no recent arm's-length</t>
         </is>
       </c>
       <c r="G19" s="13" t="n"/>
@@ -15316,24 +15354,24 @@
     <row r="20" ht="15" customHeight="1">
       <c r="B20" s="12" t="inlineStr">
         <is>
-          <t>1040 Bayview</t>
-        </is>
-      </c>
-      <c r="C20" s="25">
-        <f>'Land'!C15</f>
-        <v/>
-      </c>
-      <c r="D20" s="68">
-        <f>'Land'!E40/'Land'!C15</f>
-        <v/>
+          <t>Office — Main St Fund LLC (57.4%)</t>
+        </is>
+      </c>
+      <c r="C20" s="30" t="inlineStr">
+        <is>
+          <t>09/23/2019</t>
+        </is>
+      </c>
+      <c r="D20" s="47" t="n">
+        <v>10000000</v>
       </c>
       <c r="E20" s="17">
-        <f>'Land'!E40</f>
+        <f>'Office Condo'!C93</f>
         <v/>
       </c>
       <c r="F20" s="22" t="inlineStr">
         <is>
-          <t>standalone parcel</t>
+          <t>96,930 SF + 2 parking lots (Daily Business Review)</t>
         </is>
       </c>
       <c r="G20" s="13" t="n"/>
@@ -15345,26 +15383,28 @@
       <c r="M20" s="14" t="n"/>
     </row>
     <row r="21" ht="15" customHeight="1">
-      <c r="B21" s="43" t="inlineStr">
-        <is>
-          <t>SUM OF THE PARTS  (fragmented land)</t>
-        </is>
-      </c>
-      <c r="C21" s="70">
-        <f>SUM(C17:C20)</f>
-        <v/>
-      </c>
-      <c r="D21" s="71">
-        <f>SUM(E17:E20)/SUM(C17:C20)</f>
-        <v/>
-      </c>
-      <c r="E21" s="72">
-        <f>SUM(E17:E20)</f>
+      <c r="B21" s="12" t="inlineStr">
+        <is>
+          <t>Office — Intl Sunrise Partners (42.6%)</t>
+        </is>
+      </c>
+      <c r="C21" s="30" t="inlineStr">
+        <is>
+          <t>2011</t>
+        </is>
+      </c>
+      <c r="D21" s="73" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E21" s="17">
+        <f>'Office Condo'!C94</f>
         <v/>
       </c>
       <c r="F21" s="22" t="inlineStr">
         <is>
-          <t>office excluded — building, not land (buy-out below)</t>
+          <t>condo-conversion sponsor (Bush Development)</t>
         </is>
       </c>
       <c r="G21" s="13" t="n"/>
@@ -15375,75 +15415,84 @@
       <c r="L21" s="13" t="n"/>
       <c r="M21" s="14" t="n"/>
     </row>
-    <row r="22">
-      <c r="B22" s="11" t="inlineStr">
-        <is>
-          <t>②  LAND VALUE  —  as an ASSEMBLED SUPERBLOCK  (plottage: worth more, hard to assemble)</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="n"/>
-      <c r="D22" s="2" t="n"/>
-      <c r="E22" s="2" t="n"/>
-      <c r="F22" s="2" t="n"/>
-      <c r="G22" s="2" t="n"/>
-      <c r="H22" s="2" t="n"/>
-      <c r="I22" s="2" t="n"/>
-      <c r="J22" s="2" t="n"/>
-      <c r="K22" s="2" t="n"/>
-      <c r="L22" s="2" t="n"/>
-      <c r="M22" s="3" t="n"/>
-    </row>
-    <row r="23" ht="15" customHeight="1">
-      <c r="B23" s="12" t="inlineStr">
-        <is>
-          <t>Assembled land (SF)</t>
-        </is>
-      </c>
-      <c r="C23" s="64">
-        <f>C21</f>
-        <v/>
-      </c>
-      <c r="E23" s="22" t="inlineStr">
-        <is>
-          <t>4 contiguous land parcels, one plat block</t>
-        </is>
-      </c>
-      <c r="F23" s="13" t="n"/>
-      <c r="G23" s="13" t="n"/>
-      <c r="H23" s="13" t="n"/>
-      <c r="I23" s="13" t="n"/>
-      <c r="J23" s="13" t="n"/>
-      <c r="K23" s="13" t="n"/>
-      <c r="L23" s="13" t="n"/>
-      <c r="M23" s="14" t="n"/>
-    </row>
-    <row r="24" ht="15" customHeight="1">
-      <c r="B24" s="12" t="inlineStr">
-        <is>
-          <t>Assembled land (acres)</t>
-        </is>
-      </c>
-      <c r="C24" s="68">
-        <f>C21/43560</f>
-        <v/>
-      </c>
+    <row r="22" ht="15" customHeight="1">
+      <c r="B22" s="12" t="inlineStr">
+        <is>
+          <t>1040 Bayview — Sunrise &amp; Bayview Partners</t>
+        </is>
+      </c>
+      <c r="C22" s="30" t="inlineStr">
+        <is>
+          <t>2014 (JV)</t>
+        </is>
+      </c>
+      <c r="D22" s="73" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E22" s="17">
+        <f>'Land'!E40</f>
+        <v/>
+      </c>
+      <c r="F22" s="22" t="inlineStr">
+        <is>
+          <t>Procacci; BBX exited 2022; stale 1961 deed $801,933</t>
+        </is>
+      </c>
+      <c r="G22" s="13" t="n"/>
+      <c r="H22" s="13" t="n"/>
+      <c r="I22" s="13" t="n"/>
+      <c r="J22" s="13" t="n"/>
+      <c r="K22" s="13" t="n"/>
+      <c r="L22" s="13" t="n"/>
+      <c r="M22" s="14" t="n"/>
+    </row>
+    <row r="23"/>
+    <row r="24">
+      <c r="B24" s="11" t="inlineStr">
+        <is>
+          <t>②  LAND VALUE  —  as REGULAR (fragmented) parcels</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="n"/>
+      <c r="D24" s="2" t="n"/>
+      <c r="E24" s="2" t="n"/>
+      <c r="F24" s="2" t="n"/>
+      <c r="G24" s="2" t="n"/>
+      <c r="H24" s="2" t="n"/>
+      <c r="I24" s="2" t="n"/>
+      <c r="J24" s="2" t="n"/>
+      <c r="K24" s="2" t="n"/>
+      <c r="L24" s="2" t="n"/>
+      <c r="M24" s="3" t="n"/>
     </row>
     <row r="25" ht="15" customHeight="1">
-      <c r="B25" s="12" t="inlineStr">
-        <is>
-          <t>Plottage / assemblage premium (base)</t>
-        </is>
-      </c>
-      <c r="C25" s="53">
-        <f>'Assumptions'!C28</f>
-        <v/>
-      </c>
-      <c r="E25" s="22" t="inlineStr">
-        <is>
-          <t>uplift for a large contiguous development site</t>
-        </is>
-      </c>
-      <c r="F25" s="13" t="n"/>
+      <c r="B25" s="15" t="inlineStr">
+        <is>
+          <t>Parcel</t>
+        </is>
+      </c>
+      <c r="C25" s="16" t="inlineStr">
+        <is>
+          <t>Land SF</t>
+        </is>
+      </c>
+      <c r="D25" s="16" t="inlineStr">
+        <is>
+          <t>$/SF</t>
+        </is>
+      </c>
+      <c r="E25" s="16" t="inlineStr">
+        <is>
+          <t>Land value</t>
+        </is>
+      </c>
+      <c r="F25" s="15" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
       <c r="G25" s="13" t="n"/>
       <c r="H25" s="13" t="n"/>
       <c r="I25" s="13" t="n"/>
@@ -15455,52 +15504,119 @@
     <row r="26" ht="15" customHeight="1">
       <c r="B26" s="12" t="inlineStr">
         <is>
-          <t>Assembled land value — low</t>
-        </is>
-      </c>
-      <c r="C26" s="47">
-        <f>E21*(1+'Assumptions'!C27)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27" ht="16" customHeight="1">
-      <c r="B27" s="55" t="inlineStr">
-        <is>
-          <t>Assembled land value — BASE</t>
-        </is>
-      </c>
-      <c r="C27" s="56">
-        <f>E21*(1+'Assumptions'!C28)</f>
-        <v/>
-      </c>
+          <t>Shahidi Retail</t>
+        </is>
+      </c>
+      <c r="C26" s="25">
+        <f>'Shahidi Retail'!C36</f>
+        <v/>
+      </c>
+      <c r="D26" s="26">
+        <f>'Shahidi Retail'!C79</f>
+        <v/>
+      </c>
+      <c r="E26" s="17">
+        <f>'Shahidi Retail'!C80</f>
+        <v/>
+      </c>
+      <c r="F26" s="22" t="inlineStr">
+        <is>
+          <t>standalone parcel</t>
+        </is>
+      </c>
+      <c r="G26" s="13" t="n"/>
+      <c r="H26" s="13" t="n"/>
+      <c r="I26" s="13" t="n"/>
+      <c r="J26" s="13" t="n"/>
+      <c r="K26" s="13" t="n"/>
+      <c r="L26" s="13" t="n"/>
+      <c r="M26" s="14" t="n"/>
+    </row>
+    <row r="27" ht="15" customHeight="1">
+      <c r="B27" s="12" t="inlineStr">
+        <is>
+          <t>Publix + Starbucks</t>
+        </is>
+      </c>
+      <c r="C27" s="25">
+        <f>'Publix &amp; Starbucks'!C25</f>
+        <v/>
+      </c>
+      <c r="D27" s="26">
+        <f>'Publix &amp; Starbucks'!C55</f>
+        <v/>
+      </c>
+      <c r="E27" s="17">
+        <f>'Publix &amp; Starbucks'!C67</f>
+        <v/>
+      </c>
+      <c r="F27" s="22" t="inlineStr">
+        <is>
+          <t>standalone parcel</t>
+        </is>
+      </c>
+      <c r="G27" s="13" t="n"/>
+      <c r="H27" s="13" t="n"/>
+      <c r="I27" s="13" t="n"/>
+      <c r="J27" s="13" t="n"/>
+      <c r="K27" s="13" t="n"/>
+      <c r="L27" s="13" t="n"/>
+      <c r="M27" s="14" t="n"/>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="B28" s="12" t="inlineStr">
         <is>
-          <t>Assembled land value — high</t>
-        </is>
-      </c>
-      <c r="C28" s="47">
-        <f>E21*(1+'Assumptions'!C29)</f>
-        <v/>
-      </c>
+          <t>Sunrise Plaza (Kar Luen)</t>
+        </is>
+      </c>
+      <c r="C28" s="25">
+        <f>'Sunrise Plaza'!C28</f>
+        <v/>
+      </c>
+      <c r="D28" s="26">
+        <f>'Sunrise Plaza'!C58</f>
+        <v/>
+      </c>
+      <c r="E28" s="17">
+        <f>'Sunrise Plaza'!C70</f>
+        <v/>
+      </c>
+      <c r="F28" s="22" t="inlineStr">
+        <is>
+          <t>standalone parcel</t>
+        </is>
+      </c>
+      <c r="G28" s="13" t="n"/>
+      <c r="H28" s="13" t="n"/>
+      <c r="I28" s="13" t="n"/>
+      <c r="J28" s="13" t="n"/>
+      <c r="K28" s="13" t="n"/>
+      <c r="L28" s="13" t="n"/>
+      <c r="M28" s="14" t="n"/>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="B29" s="12" t="inlineStr">
         <is>
-          <t>Implied assembled $/SF (base)</t>
-        </is>
-      </c>
-      <c r="C29" s="68">
-        <f>C27/C21</f>
-        <v/>
-      </c>
-      <c r="E29" s="22" t="inlineStr">
-        <is>
-          <t>vs. fragmented blend above</t>
-        </is>
-      </c>
-      <c r="F29" s="13" t="n"/>
+          <t>1040 Bayview</t>
+        </is>
+      </c>
+      <c r="C29" s="25">
+        <f>'Land'!C15</f>
+        <v/>
+      </c>
+      <c r="D29" s="68">
+        <f>'Land'!E40/'Land'!C15</f>
+        <v/>
+      </c>
+      <c r="E29" s="17">
+        <f>'Land'!E40</f>
+        <v/>
+      </c>
+      <c r="F29" s="22" t="inlineStr">
+        <is>
+          <t>standalone parcel</t>
+        </is>
+      </c>
       <c r="G29" s="13" t="n"/>
       <c r="H29" s="13" t="n"/>
       <c r="I29" s="13" t="n"/>
@@ -15510,21 +15626,28 @@
       <c r="M29" s="14" t="n"/>
     </row>
     <row r="30" ht="15" customHeight="1">
-      <c r="B30" s="12" t="inlineStr">
-        <is>
-          <t>PLOTTAGE PREMIUM (assembled − fragmented)</t>
-        </is>
-      </c>
-      <c r="C30" s="51">
-        <f>C27-E21</f>
-        <v/>
-      </c>
-      <c r="E30" s="22" t="inlineStr">
-        <is>
-          <t>the value created / cost incurred by assembling the hard-to-put-together block</t>
-        </is>
-      </c>
-      <c r="F30" s="13" t="n"/>
+      <c r="B30" s="43" t="inlineStr">
+        <is>
+          <t>SUM OF THE PARTS  (fragmented land)</t>
+        </is>
+      </c>
+      <c r="C30" s="74">
+        <f>SUM(C26:C29)</f>
+        <v/>
+      </c>
+      <c r="D30" s="75">
+        <f>SUM(E26:E29)/SUM(C26:C29)</f>
+        <v/>
+      </c>
+      <c r="E30" s="76">
+        <f>SUM(E26:E29)</f>
+        <v/>
+      </c>
+      <c r="F30" s="22" t="inlineStr">
+        <is>
+          <t>office excluded — building, not land (buy-out below)</t>
+        </is>
+      </c>
       <c r="G30" s="13" t="n"/>
       <c r="H30" s="13" t="n"/>
       <c r="I30" s="13" t="n"/>
@@ -15533,62 +15656,72 @@
       <c r="L30" s="13" t="n"/>
       <c r="M30" s="14" t="n"/>
     </row>
-    <row r="31"/>
-    <row r="32">
-      <c r="B32" s="11" t="inlineStr">
-        <is>
-          <t>③  OFFICE CONDO  —  FULL BUY-OUT  (the building on the corner, two dominant owners)</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="n"/>
-      <c r="D32" s="2" t="n"/>
-      <c r="E32" s="2" t="n"/>
-      <c r="F32" s="2" t="n"/>
-      <c r="G32" s="2" t="n"/>
-      <c r="H32" s="2" t="n"/>
-      <c r="I32" s="2" t="n"/>
-      <c r="J32" s="2" t="n"/>
-      <c r="K32" s="2" t="n"/>
-      <c r="L32" s="2" t="n"/>
-      <c r="M32" s="3" t="n"/>
+    <row r="31">
+      <c r="B31" s="11" t="inlineStr">
+        <is>
+          <t>②  LAND VALUE  —  as an ASSEMBLED SUPERBLOCK  (plottage: worth more, hard to assemble)</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="n"/>
+      <c r="D31" s="2" t="n"/>
+      <c r="E31" s="2" t="n"/>
+      <c r="F31" s="2" t="n"/>
+      <c r="G31" s="2" t="n"/>
+      <c r="H31" s="2" t="n"/>
+      <c r="I31" s="2" t="n"/>
+      <c r="J31" s="2" t="n"/>
+      <c r="K31" s="2" t="n"/>
+      <c r="L31" s="2" t="n"/>
+      <c r="M31" s="3" t="n"/>
+    </row>
+    <row r="32" ht="15" customHeight="1">
+      <c r="B32" s="12" t="inlineStr">
+        <is>
+          <t>Assembled land (SF)</t>
+        </is>
+      </c>
+      <c r="C32" s="64">
+        <f>C30</f>
+        <v/>
+      </c>
+      <c r="E32" s="22" t="inlineStr">
+        <is>
+          <t>4 contiguous land parcels, one plat block</t>
+        </is>
+      </c>
+      <c r="F32" s="13" t="n"/>
+      <c r="G32" s="13" t="n"/>
+      <c r="H32" s="13" t="n"/>
+      <c r="I32" s="13" t="n"/>
+      <c r="J32" s="13" t="n"/>
+      <c r="K32" s="13" t="n"/>
+      <c r="L32" s="13" t="n"/>
+      <c r="M32" s="14" t="n"/>
     </row>
     <row r="33" ht="15" customHeight="1">
       <c r="B33" s="12" t="inlineStr">
         <is>
-          <t>Main Street Fund LLC (Grove Gate, 57.4%)</t>
-        </is>
-      </c>
-      <c r="C33" s="17">
-        <f>'Office Condo'!C93</f>
-        <v/>
-      </c>
-      <c r="E33" s="22" t="inlineStr">
-        <is>
-          <t>bought 96,930 SF + 2 parking lots for $10M (2019)</t>
-        </is>
-      </c>
-      <c r="F33" s="13" t="n"/>
-      <c r="G33" s="13" t="n"/>
-      <c r="H33" s="13" t="n"/>
-      <c r="I33" s="13" t="n"/>
-      <c r="J33" s="13" t="n"/>
-      <c r="K33" s="13" t="n"/>
-      <c r="L33" s="13" t="n"/>
-      <c r="M33" s="14" t="n"/>
+          <t>Assembled land (acres)</t>
+        </is>
+      </c>
+      <c r="C33" s="68">
+        <f>C30/43560</f>
+        <v/>
+      </c>
     </row>
     <row r="34" ht="15" customHeight="1">
       <c r="B34" s="12" t="inlineStr">
         <is>
-          <t>International Sunrise Partners LLC (42.6%)</t>
-        </is>
-      </c>
-      <c r="C34" s="17">
-        <f>'Office Condo'!C94</f>
+          <t>Plottage / assemblage premium (base)</t>
+        </is>
+      </c>
+      <c r="C34" s="53">
+        <f>'Assumptions'!C28</f>
         <v/>
       </c>
       <c r="E34" s="22" t="inlineStr">
         <is>
-          <t>prior bulk owner (2011 condo-conversion sponsor)</t>
+          <t>uplift for a large contiguous development site</t>
         </is>
       </c>
       <c r="F34" s="13" t="n"/>
@@ -15600,64 +15733,54 @@
       <c r="L34" s="13" t="n"/>
       <c r="M34" s="14" t="n"/>
     </row>
-    <row r="35" ht="16" customHeight="1">
-      <c r="B35" s="55" t="inlineStr">
-        <is>
-          <t>FULL BUY-OUT VALUE (both owners)</t>
-        </is>
-      </c>
-      <c r="C35" s="56">
-        <f>'Office Condo'!C95</f>
-        <v/>
-      </c>
-      <c r="E35" s="22" t="inlineStr">
-        <is>
-          <t>income value + buy-out premium; adjust the premium on the Office Condo tab</t>
-        </is>
-      </c>
-      <c r="F35" s="13" t="n"/>
-      <c r="G35" s="13" t="n"/>
-      <c r="H35" s="13" t="n"/>
-      <c r="I35" s="13" t="n"/>
-      <c r="J35" s="13" t="n"/>
-      <c r="K35" s="13" t="n"/>
-      <c r="L35" s="13" t="n"/>
-      <c r="M35" s="14" t="n"/>
-    </row>
-    <row r="36"/>
-    <row r="37">
-      <c r="B37" s="11" t="inlineStr">
-        <is>
-          <t>④  REDEVELOPMENT — LIVE LOCAL RESIDUAL  (assemblage scale · ⚠️ negative → HOLD)</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="n"/>
-      <c r="D37" s="2" t="n"/>
-      <c r="E37" s="2" t="n"/>
-      <c r="F37" s="2" t="n"/>
-      <c r="G37" s="2" t="n"/>
-      <c r="H37" s="2" t="n"/>
-      <c r="I37" s="2" t="n"/>
-      <c r="J37" s="2" t="n"/>
-      <c r="K37" s="2" t="n"/>
-      <c r="L37" s="2" t="n"/>
-      <c r="M37" s="3" t="n"/>
+    <row r="35" ht="15" customHeight="1">
+      <c r="B35" s="12" t="inlineStr">
+        <is>
+          <t>Assembled land value — low</t>
+        </is>
+      </c>
+      <c r="C35" s="47">
+        <f>E30*(1+'Assumptions'!C27)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36" ht="16" customHeight="1">
+      <c r="B36" s="55" t="inlineStr">
+        <is>
+          <t>Assembled land value — BASE</t>
+        </is>
+      </c>
+      <c r="C36" s="56">
+        <f>E30*(1+'Assumptions'!C28)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37" ht="15" customHeight="1">
+      <c r="B37" s="12" t="inlineStr">
+        <is>
+          <t>Assembled land value — high</t>
+        </is>
+      </c>
+      <c r="C37" s="47">
+        <f>E30*(1+'Assumptions'!C29)</f>
+        <v/>
+      </c>
     </row>
     <row r="38" ht="15" customHeight="1">
       <c r="B38" s="12" t="inlineStr">
         <is>
-          <t>Buildable density (units/acre)</t>
-        </is>
-      </c>
-      <c r="C38" s="73" t="n">
-        <v>100</v>
-      </c>
-      <c r="D38" s="22" t="inlineStr">
-        <is>
-          <t>🔵 Live Local target</t>
-        </is>
-      </c>
-      <c r="E38" s="13" t="n"/>
+          <t>Implied assembled $/SF (base)</t>
+        </is>
+      </c>
+      <c r="C38" s="68">
+        <f>C36/C30</f>
+        <v/>
+      </c>
+      <c r="E38" s="22" t="inlineStr">
+        <is>
+          <t>vs. fragmented blend above</t>
+        </is>
+      </c>
       <c r="F38" s="13" t="n"/>
       <c r="G38" s="13" t="n"/>
       <c r="H38" s="13" t="n"/>
@@ -15670,16 +15793,16 @@
     <row r="39" ht="15" customHeight="1">
       <c r="B39" s="12" t="inlineStr">
         <is>
-          <t>Assemblage buildable units</t>
-        </is>
-      </c>
-      <c r="C39" s="64">
-        <f>C21/43560*C38</f>
+          <t>PLOTTAGE PREMIUM (assembled − fragmented)</t>
+        </is>
+      </c>
+      <c r="C39" s="51">
+        <f>C36-E30</f>
         <v/>
       </c>
       <c r="E39" s="22" t="inlineStr">
         <is>
-          <t>acres × density</t>
+          <t>the value created / cost incurred by assembling the hard-to-put-together block</t>
         </is>
       </c>
       <c r="F39" s="13" t="n"/>
@@ -15694,16 +15817,16 @@
     <row r="40" ht="15" customHeight="1">
       <c r="B40" s="12" t="inlineStr">
         <is>
-          <t>Gross development value (GDV)</t>
-        </is>
-      </c>
-      <c r="C40" s="51">
-        <f>C39*'Assumptions'!C38</f>
+          <t>Entitlement lift (post-Live Local approval)</t>
+        </is>
+      </c>
+      <c r="C40" s="53">
+        <f>'Assumptions'!C32</f>
         <v/>
       </c>
       <c r="E40" s="22" t="inlineStr">
         <is>
-          <t>units × achievable value/unit (Assumptions)</t>
+          <t>value bump once entitled for Live Local density</t>
         </is>
       </c>
       <c r="F40" s="13" t="n"/>
@@ -15715,78 +15838,112 @@
       <c r="L40" s="13" t="n"/>
       <c r="M40" s="14" t="n"/>
     </row>
-    <row r="41" ht="15" customHeight="1">
-      <c r="B41" s="12" t="inlineStr">
-        <is>
-          <t>Buildable GBA (SF)</t>
-        </is>
-      </c>
-      <c r="C41" s="64">
-        <f>C39*'Assumptions'!C40</f>
-        <v/>
-      </c>
-    </row>
-    <row r="42" ht="15" customHeight="1">
-      <c r="B42" s="12" t="inlineStr">
-        <is>
-          <t>− Hard cost</t>
-        </is>
-      </c>
-      <c r="C42" s="47">
-        <f>-C41*'Assumptions'!C39</f>
-        <v/>
-      </c>
-    </row>
-    <row r="43" ht="15" customHeight="1">
-      <c r="B43" s="12" t="inlineStr">
-        <is>
-          <t>− Soft cost</t>
-        </is>
-      </c>
-      <c r="C43" s="47">
-        <f>-C41*'Assumptions'!C39*'Assumptions'!C41</f>
-        <v/>
-      </c>
+    <row r="41" ht="16" customHeight="1">
+      <c r="B41" s="55" t="inlineStr">
+        <is>
+          <t>POST-APPROVAL assembled land value</t>
+        </is>
+      </c>
+      <c r="C41" s="56">
+        <f>C36*(1+'Assumptions'!C32)</f>
+        <v/>
+      </c>
+      <c r="E41" s="22" t="inlineStr">
+        <is>
+          <t>what the ENTITLED dirt is worth — the redevelopment upside the premium buys you the option on</t>
+        </is>
+      </c>
+      <c r="F41" s="13" t="n"/>
+      <c r="G41" s="13" t="n"/>
+      <c r="H41" s="13" t="n"/>
+      <c r="I41" s="13" t="n"/>
+      <c r="J41" s="13" t="n"/>
+      <c r="K41" s="13" t="n"/>
+      <c r="L41" s="13" t="n"/>
+      <c r="M41" s="14" t="n"/>
+    </row>
+    <row r="42"/>
+    <row r="43">
+      <c r="B43" s="11" t="inlineStr">
+        <is>
+          <t>③  OFFICE CONDO  —  FULL BUY-OUT  (the building on the corner, two dominant owners)</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="n"/>
+      <c r="D43" s="2" t="n"/>
+      <c r="E43" s="2" t="n"/>
+      <c r="F43" s="2" t="n"/>
+      <c r="G43" s="2" t="n"/>
+      <c r="H43" s="2" t="n"/>
+      <c r="I43" s="2" t="n"/>
+      <c r="J43" s="2" t="n"/>
+      <c r="K43" s="2" t="n"/>
+      <c r="L43" s="2" t="n"/>
+      <c r="M43" s="3" t="n"/>
     </row>
     <row r="44" ht="15" customHeight="1">
       <c r="B44" s="12" t="inlineStr">
         <is>
-          <t>− Developer profit</t>
-        </is>
-      </c>
-      <c r="C44" s="47">
-        <f>-C40*'Assumptions'!C42</f>
-        <v/>
-      </c>
-    </row>
-    <row r="45" ht="16" customHeight="1">
-      <c r="B45" s="55" t="inlineStr">
-        <is>
-          <t>RESIDUAL LAND VALUE (supports acquisition?)</t>
-        </is>
-      </c>
-      <c r="C45" s="56">
-        <f>C40+C42-C41*'Assumptions'!C39*'Assumptions'!C41-C40*'Assumptions'!C42</f>
-        <v/>
-      </c>
-    </row>
-    <row r="46" ht="27" customHeight="1">
-      <c r="B46" s="40" t="inlineStr">
-        <is>
-          <t>HBU verdict</t>
-        </is>
-      </c>
-      <c r="C46" s="69" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="D46" s="40" t="inlineStr">
-        <is>
-          <t>Residual runs NEGATIVE at coastal AE-zone hard costs — redevelopment does not pencil today. Highest &amp; best use = acquire and HOLD the income-covered assemblage; redevelop when achievable rents / hard costs support Live Local density.</t>
-        </is>
-      </c>
-      <c r="E46" s="13" t="n"/>
+          <t>Main Street Fund LLC (Grove Gate, 57.4%)</t>
+        </is>
+      </c>
+      <c r="C44" s="17">
+        <f>'Office Condo'!C93</f>
+        <v/>
+      </c>
+      <c r="E44" s="22" t="inlineStr">
+        <is>
+          <t>bought 96,930 SF + 2 parking lots for $10M (2019)</t>
+        </is>
+      </c>
+      <c r="F44" s="13" t="n"/>
+      <c r="G44" s="13" t="n"/>
+      <c r="H44" s="13" t="n"/>
+      <c r="I44" s="13" t="n"/>
+      <c r="J44" s="13" t="n"/>
+      <c r="K44" s="13" t="n"/>
+      <c r="L44" s="13" t="n"/>
+      <c r="M44" s="14" t="n"/>
+    </row>
+    <row r="45" ht="15" customHeight="1">
+      <c r="B45" s="12" t="inlineStr">
+        <is>
+          <t>International Sunrise Partners LLC (42.6%)</t>
+        </is>
+      </c>
+      <c r="C45" s="17">
+        <f>'Office Condo'!C94</f>
+        <v/>
+      </c>
+      <c r="E45" s="22" t="inlineStr">
+        <is>
+          <t>prior bulk owner (2011 condo-conversion sponsor)</t>
+        </is>
+      </c>
+      <c r="F45" s="13" t="n"/>
+      <c r="G45" s="13" t="n"/>
+      <c r="H45" s="13" t="n"/>
+      <c r="I45" s="13" t="n"/>
+      <c r="J45" s="13" t="n"/>
+      <c r="K45" s="13" t="n"/>
+      <c r="L45" s="13" t="n"/>
+      <c r="M45" s="14" t="n"/>
+    </row>
+    <row r="46" ht="16" customHeight="1">
+      <c r="B46" s="55" t="inlineStr">
+        <is>
+          <t>FULL BUY-OUT VALUE (both owners)</t>
+        </is>
+      </c>
+      <c r="C46" s="56">
+        <f>'Office Condo'!C95</f>
+        <v/>
+      </c>
+      <c r="E46" s="22" t="inlineStr">
+        <is>
+          <t>income value + buy-out premium; adjust the premium on the Office Condo tab</t>
+        </is>
+      </c>
       <c r="F46" s="13" t="n"/>
       <c r="G46" s="13" t="n"/>
       <c r="H46" s="13" t="n"/>
@@ -15800,7 +15957,7 @@
     <row r="48">
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t>⑤  CONCLUSION</t>
+          <t>④  REDEVELOPMENT — LIVE LOCAL RESIDUAL  (assemblage scale · ⚠️ negative → HOLD)</t>
         </is>
       </c>
       <c r="C48" s="2" t="n"/>
@@ -15818,11 +15975,17 @@
     <row r="49" ht="15" customHeight="1">
       <c r="B49" s="12" t="inlineStr">
         <is>
-          <t>• Priced independently, the components sum to ~$86M; as an assemblage (base premium) ~$103M — the premium is the cost of controlling</t>
-        </is>
-      </c>
-      <c r="C49" s="13" t="n"/>
-      <c r="D49" s="13" t="n"/>
+          <t>Buildable density (units/acre)</t>
+        </is>
+      </c>
+      <c r="C49" s="77" t="n">
+        <v>100</v>
+      </c>
+      <c r="D49" s="22" t="inlineStr">
+        <is>
+          <t>🔵 Live Local target</t>
+        </is>
+      </c>
       <c r="E49" s="13" t="n"/>
       <c r="F49" s="13" t="n"/>
       <c r="G49" s="13" t="n"/>
@@ -15836,12 +15999,18 @@
     <row r="50" ht="15" customHeight="1">
       <c r="B50" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  a contiguous block held by five owners (a sale-leaseback, a fractured condo, and holdout risk).</t>
-        </is>
-      </c>
-      <c r="C50" s="13" t="n"/>
-      <c r="D50" s="13" t="n"/>
-      <c r="E50" s="13" t="n"/>
+          <t>Assemblage buildable units</t>
+        </is>
+      </c>
+      <c r="C50" s="64">
+        <f>C30/43560*C49</f>
+        <v/>
+      </c>
+      <c r="E50" s="22" t="inlineStr">
+        <is>
+          <t>acres × density</t>
+        </is>
+      </c>
       <c r="F50" s="13" t="n"/>
       <c r="G50" s="13" t="n"/>
       <c r="H50" s="13" t="n"/>
@@ -15854,12 +16023,18 @@
     <row r="51" ht="15" customHeight="1">
       <c r="B51" s="12" t="inlineStr">
         <is>
-          <t>• The land alone is worth more assembled (plottage) than as fragmented parcels — but redevelopment does not yet pencil, so the</t>
-        </is>
-      </c>
-      <c r="C51" s="13" t="n"/>
-      <c r="D51" s="13" t="n"/>
-      <c r="E51" s="13" t="n"/>
+          <t>Gross development value (GDV)</t>
+        </is>
+      </c>
+      <c r="C51" s="51">
+        <f>C50*'Assumptions'!C39</f>
+        <v/>
+      </c>
+      <c r="E51" s="22" t="inlineStr">
+        <is>
+          <t>units × achievable value/unit (Assumptions)</t>
+        </is>
+      </c>
       <c r="F51" s="13" t="n"/>
       <c r="G51" s="13" t="n"/>
       <c r="H51" s="13" t="n"/>
@@ -15872,61 +16047,225 @@
     <row r="52" ht="15" customHeight="1">
       <c r="B52" s="12" t="inlineStr">
         <is>
+          <t>Buildable GBA (SF)</t>
+        </is>
+      </c>
+      <c r="C52" s="64">
+        <f>C50*'Assumptions'!C41</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53" ht="15" customHeight="1">
+      <c r="B53" s="12" t="inlineStr">
+        <is>
+          <t>− Hard cost</t>
+        </is>
+      </c>
+      <c r="C53" s="47">
+        <f>-C52*'Assumptions'!C40</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54" ht="15" customHeight="1">
+      <c r="B54" s="12" t="inlineStr">
+        <is>
+          <t>− Soft cost</t>
+        </is>
+      </c>
+      <c r="C54" s="47">
+        <f>-C52*'Assumptions'!C40*'Assumptions'!C42</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55" ht="15" customHeight="1">
+      <c r="B55" s="12" t="inlineStr">
+        <is>
+          <t>− Developer profit</t>
+        </is>
+      </c>
+      <c r="C55" s="47">
+        <f>-C51*'Assumptions'!C43</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56" ht="16" customHeight="1">
+      <c r="B56" s="55" t="inlineStr">
+        <is>
+          <t>RESIDUAL LAND VALUE (supports acquisition?)</t>
+        </is>
+      </c>
+      <c r="C56" s="56">
+        <f>C51+C53-C52*'Assumptions'!C40*'Assumptions'!C42-C51*'Assumptions'!C43</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57" ht="27" customHeight="1">
+      <c r="B57" s="40" t="inlineStr">
+        <is>
+          <t>HBU verdict</t>
+        </is>
+      </c>
+      <c r="C57" s="69" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="D57" s="40" t="inlineStr">
+        <is>
+          <t>Residual runs NEGATIVE at coastal AE-zone hard costs — redevelopment does not pencil today. Highest &amp; best use = acquire and HOLD the income-covered assemblage; redevelop when achievable rents / hard costs support Live Local density.</t>
+        </is>
+      </c>
+      <c r="E57" s="13" t="n"/>
+      <c r="F57" s="13" t="n"/>
+      <c r="G57" s="13" t="n"/>
+      <c r="H57" s="13" t="n"/>
+      <c r="I57" s="13" t="n"/>
+      <c r="J57" s="13" t="n"/>
+      <c r="K57" s="13" t="n"/>
+      <c r="L57" s="13" t="n"/>
+      <c r="M57" s="14" t="n"/>
+    </row>
+    <row r="58"/>
+    <row r="59">
+      <c r="B59" s="11" t="inlineStr">
+        <is>
+          <t>⑤  CONCLUSION</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="n"/>
+      <c r="D59" s="2" t="n"/>
+      <c r="E59" s="2" t="n"/>
+      <c r="F59" s="2" t="n"/>
+      <c r="G59" s="2" t="n"/>
+      <c r="H59" s="2" t="n"/>
+      <c r="I59" s="2" t="n"/>
+      <c r="J59" s="2" t="n"/>
+      <c r="K59" s="2" t="n"/>
+      <c r="L59" s="2" t="n"/>
+      <c r="M59" s="3" t="n"/>
+    </row>
+    <row r="60" ht="15" customHeight="1">
+      <c r="B60" s="12" t="inlineStr">
+        <is>
+          <t>• Priced independently, the components sum to ~$86M; as an assemblage (base premium) ~$103M — the premium is the cost of controlling</t>
+        </is>
+      </c>
+      <c r="C60" s="13" t="n"/>
+      <c r="D60" s="13" t="n"/>
+      <c r="E60" s="13" t="n"/>
+      <c r="F60" s="13" t="n"/>
+      <c r="G60" s="13" t="n"/>
+      <c r="H60" s="13" t="n"/>
+      <c r="I60" s="13" t="n"/>
+      <c r="J60" s="13" t="n"/>
+      <c r="K60" s="13" t="n"/>
+      <c r="L60" s="13" t="n"/>
+      <c r="M60" s="14" t="n"/>
+    </row>
+    <row r="61" ht="15" customHeight="1">
+      <c r="B61" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  a contiguous block held by five owners (a sale-leaseback, a fractured condo, and holdout risk).</t>
+        </is>
+      </c>
+      <c r="C61" s="13" t="n"/>
+      <c r="D61" s="13" t="n"/>
+      <c r="E61" s="13" t="n"/>
+      <c r="F61" s="13" t="n"/>
+      <c r="G61" s="13" t="n"/>
+      <c r="H61" s="13" t="n"/>
+      <c r="I61" s="13" t="n"/>
+      <c r="J61" s="13" t="n"/>
+      <c r="K61" s="13" t="n"/>
+      <c r="L61" s="13" t="n"/>
+      <c r="M61" s="14" t="n"/>
+    </row>
+    <row r="62" ht="15" customHeight="1">
+      <c r="B62" s="12" t="inlineStr">
+        <is>
+          <t>• The land alone is worth more assembled (plottage) than as fragmented parcels — but redevelopment does not yet pencil, so the</t>
+        </is>
+      </c>
+      <c r="C62" s="13" t="n"/>
+      <c r="D62" s="13" t="n"/>
+      <c r="E62" s="13" t="n"/>
+      <c r="F62" s="13" t="n"/>
+      <c r="G62" s="13" t="n"/>
+      <c r="H62" s="13" t="n"/>
+      <c r="I62" s="13" t="n"/>
+      <c r="J62" s="13" t="n"/>
+      <c r="K62" s="13" t="n"/>
+      <c r="L62" s="13" t="n"/>
+      <c r="M62" s="14" t="n"/>
+    </row>
+    <row r="63" ht="15" customHeight="1">
+      <c r="B63" s="12" t="inlineStr">
+        <is>
           <t xml:space="preserve">  return today is income-covered land banking, with the Live Local density as the option you are paying the premium to hold.</t>
         </is>
       </c>
-      <c r="C52" s="13" t="n"/>
-      <c r="D52" s="13" t="n"/>
-      <c r="E52" s="13" t="n"/>
-      <c r="F52" s="13" t="n"/>
-      <c r="G52" s="13" t="n"/>
-      <c r="H52" s="13" t="n"/>
-      <c r="I52" s="13" t="n"/>
-      <c r="J52" s="13" t="n"/>
-      <c r="K52" s="13" t="n"/>
-      <c r="L52" s="13" t="n"/>
-      <c r="M52" s="14" t="n"/>
+      <c r="C63" s="13" t="n"/>
+      <c r="D63" s="13" t="n"/>
+      <c r="E63" s="13" t="n"/>
+      <c r="F63" s="13" t="n"/>
+      <c r="G63" s="13" t="n"/>
+      <c r="H63" s="13" t="n"/>
+      <c r="I63" s="13" t="n"/>
+      <c r="J63" s="13" t="n"/>
+      <c r="K63" s="13" t="n"/>
+      <c r="L63" s="13" t="n"/>
+      <c r="M63" s="14" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="38">
+  <mergeCells count="48">
     <mergeCell ref="B2:M2"/>
-    <mergeCell ref="E29:M29"/>
     <mergeCell ref="B48:M48"/>
+    <mergeCell ref="F29:M29"/>
     <mergeCell ref="E10:M10"/>
+    <mergeCell ref="B60:M60"/>
     <mergeCell ref="E13:M13"/>
     <mergeCell ref="F19:M19"/>
+    <mergeCell ref="F25:M25"/>
     <mergeCell ref="F16:M16"/>
+    <mergeCell ref="B61:M61"/>
     <mergeCell ref="E40:M40"/>
     <mergeCell ref="E9:M9"/>
     <mergeCell ref="B1:M1"/>
     <mergeCell ref="E34:M34"/>
-    <mergeCell ref="D38:M38"/>
     <mergeCell ref="E6:M6"/>
-    <mergeCell ref="E30:M30"/>
+    <mergeCell ref="E46:M46"/>
+    <mergeCell ref="F30:M30"/>
+    <mergeCell ref="E44:M44"/>
     <mergeCell ref="E11:M11"/>
     <mergeCell ref="F21:M21"/>
-    <mergeCell ref="B37:M37"/>
+    <mergeCell ref="E45:M45"/>
     <mergeCell ref="F20:M20"/>
     <mergeCell ref="F18:M18"/>
-    <mergeCell ref="B49:M49"/>
+    <mergeCell ref="B24:M24"/>
+    <mergeCell ref="F26:M26"/>
     <mergeCell ref="E7:M7"/>
     <mergeCell ref="B15:M15"/>
     <mergeCell ref="F17:M17"/>
-    <mergeCell ref="E25:M25"/>
-    <mergeCell ref="D46:M46"/>
-    <mergeCell ref="B51:M51"/>
-    <mergeCell ref="B32:M32"/>
-    <mergeCell ref="B50:M50"/>
+    <mergeCell ref="E32:M32"/>
+    <mergeCell ref="E41:M41"/>
+    <mergeCell ref="B63:M63"/>
+    <mergeCell ref="F22:M22"/>
+    <mergeCell ref="F28:M28"/>
+    <mergeCell ref="D57:M57"/>
     <mergeCell ref="B4:M4"/>
     <mergeCell ref="E12:M12"/>
-    <mergeCell ref="E33:M33"/>
+    <mergeCell ref="F27:M27"/>
+    <mergeCell ref="E50:M50"/>
+    <mergeCell ref="D49:M49"/>
+    <mergeCell ref="B62:M62"/>
+    <mergeCell ref="B59:M59"/>
     <mergeCell ref="E5:M5"/>
-    <mergeCell ref="E23:M23"/>
-    <mergeCell ref="B22:M22"/>
+    <mergeCell ref="B31:M31"/>
     <mergeCell ref="E39:M39"/>
     <mergeCell ref="E8:M8"/>
-    <mergeCell ref="B52:M52"/>
-    <mergeCell ref="E35:M35"/>
+    <mergeCell ref="B43:M43"/>
+    <mergeCell ref="E51:M51"/>
+    <mergeCell ref="E38:M38"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
@@ -16015,12 +16354,12 @@
       <c r="M4" s="3" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="B5" s="74" t="inlineStr">
+      <c r="B5" s="70" t="inlineStr">
         <is>
           <t>Record owner</t>
         </is>
       </c>
-      <c r="D5" s="74" t="inlineStr">
+      <c r="D5" s="70" t="inlineStr">
         <is>
           <t>SHAWNICK GALLERIA LLC</t>
         </is>
@@ -16036,12 +16375,12 @@
       <c r="M5" s="14" t="n"/>
     </row>
     <row r="6" ht="15" customHeight="1">
-      <c r="B6" s="74" t="inlineStr">
+      <c r="B6" s="70" t="inlineStr">
         <is>
           <t>Principal / manager</t>
         </is>
       </c>
-      <c r="D6" s="74" t="inlineStr">
+      <c r="D6" s="70" t="inlineStr">
         <is>
           <t>Esmail Shahidi (mgr) — Sunbiz L21000389291</t>
         </is>
@@ -16057,12 +16396,12 @@
       <c r="M6" s="14" t="n"/>
     </row>
     <row r="7" ht="15" customHeight="1">
-      <c r="B7" s="74" t="inlineStr">
+      <c r="B7" s="70" t="inlineStr">
         <is>
           <t>Gross leasable area (GLA)</t>
         </is>
       </c>
-      <c r="D7" s="74" t="inlineStr">
+      <c r="D7" s="70" t="inlineStr">
         <is>
           <t>26,272 SF</t>
         </is>
@@ -16078,12 +16417,12 @@
       <c r="M7" s="14" t="n"/>
     </row>
     <row r="8" ht="15" customHeight="1">
-      <c r="B8" s="74" t="inlineStr">
+      <c r="B8" s="70" t="inlineStr">
         <is>
           <t>Land</t>
         </is>
       </c>
-      <c r="D8" s="74" t="inlineStr">
+      <c r="D8" s="70" t="inlineStr">
         <is>
           <t>67,080 SF  (1.54 ac)</t>
         </is>
@@ -16099,12 +16438,12 @@
       <c r="M8" s="14" t="n"/>
     </row>
     <row r="9" ht="15" customHeight="1">
-      <c r="B9" s="74" t="inlineStr">
+      <c r="B9" s="70" t="inlineStr">
         <is>
           <t>Year built</t>
         </is>
       </c>
-      <c r="D9" s="74" t="inlineStr">
+      <c r="D9" s="70" t="inlineStr">
         <is>
           <t>1960 (eff. 1980)</t>
         </is>
@@ -16120,12 +16459,12 @@
       <c r="M9" s="14" t="n"/>
     </row>
     <row r="10" ht="15" customHeight="1">
-      <c r="B10" s="74" t="inlineStr">
+      <c r="B10" s="70" t="inlineStr">
         <is>
           <t>Zoning / flood</t>
         </is>
       </c>
-      <c r="D10" s="74" t="inlineStr">
+      <c r="D10" s="70" t="inlineStr">
         <is>
           <t>B-1 (Boulevard Business) / FEMA AE</t>
         </is>
@@ -16141,12 +16480,12 @@
       <c r="M10" s="14" t="n"/>
     </row>
     <row r="11" ht="15" customHeight="1">
-      <c r="B11" s="74" t="inlineStr">
+      <c r="B11" s="70" t="inlineStr">
         <is>
           <t>Last sale</t>
         </is>
       </c>
-      <c r="D11" s="74" t="inlineStr">
+      <c r="D11" s="70" t="inlineStr">
         <is>
           <t>11/09/2021  —  $17,100,000  (Special Warranty Deed)</t>
         </is>
@@ -16162,12 +16501,12 @@
       <c r="M11" s="14" t="n"/>
     </row>
     <row r="12" ht="15" customHeight="1">
-      <c r="B12" s="74" t="inlineStr">
+      <c r="B12" s="70" t="inlineStr">
         <is>
           <t>2025 real-estate taxes</t>
         </is>
       </c>
-      <c r="D12" s="74" t="inlineStr">
+      <c r="D12" s="70" t="inlineStr">
         <is>
           <t>$162,366   (2024: $152,766)</t>
         </is>
@@ -16183,12 +16522,12 @@
       <c r="M12" s="14" t="n"/>
     </row>
     <row r="13" ht="15" customHeight="1">
-      <c r="B13" s="74" t="inlineStr">
+      <c r="B13" s="70" t="inlineStr">
         <is>
           <t>2026 just / market value (BCPA)</t>
         </is>
       </c>
-      <c r="D13" s="74" t="inlineStr">
+      <c r="D13" s="70" t="inlineStr">
         <is>
           <t>$8,911,690</t>
         </is>
@@ -16204,12 +16543,12 @@
       <c r="M13" s="14" t="n"/>
     </row>
     <row r="14" ht="15" customHeight="1">
-      <c r="B14" s="74" t="inlineStr">
+      <c r="B14" s="70" t="inlineStr">
         <is>
           <t>Effective millage</t>
         </is>
       </c>
-      <c r="D14" s="74" t="inlineStr">
+      <c r="D14" s="70" t="inlineStr">
         <is>
           <t>1.91%   (2025 tax ÷ just value)</t>
         </is>
@@ -16225,12 +16564,12 @@
       <c r="M14" s="14" t="n"/>
     </row>
     <row r="15" ht="15" customHeight="1">
-      <c r="B15" s="74" t="inlineStr">
+      <c r="B15" s="70" t="inlineStr">
         <is>
           <t>Derived basis on $17.1M</t>
         </is>
       </c>
-      <c r="D15" s="74" t="inlineStr">
+      <c r="D15" s="70" t="inlineStr">
         <is>
           <t>$254.92/SF land · $650.88/SF building</t>
         </is>
@@ -16246,12 +16585,12 @@
       <c r="M15" s="14" t="n"/>
     </row>
     <row r="16" ht="15" customHeight="1">
-      <c r="B16" s="74" t="inlineStr">
+      <c r="B16" s="70" t="inlineStr">
         <is>
           <t>In-place occupancy</t>
         </is>
       </c>
-      <c r="D16" s="74" t="inlineStr">
+      <c r="D16" s="70" t="inlineStr">
         <is>
           <t>83.17%   →  ~4,422 SF vacant to lease</t>
         </is>
@@ -16347,7 +16686,7 @@
       <c r="F20" s="64" t="n">
         <v>4000</v>
       </c>
-      <c r="G20" s="75" t="n">
+      <c r="G20" s="78" t="n">
         <v>48</v>
       </c>
       <c r="H20" s="47">
@@ -16384,7 +16723,7 @@
       <c r="F21" s="64" t="n">
         <v>3500</v>
       </c>
-      <c r="G21" s="75" t="n">
+      <c r="G21" s="78" t="n">
         <v>62</v>
       </c>
       <c r="H21" s="47">
@@ -16393,7 +16732,7 @@
       </c>
       <c r="I21" s="13" t="n"/>
       <c r="J21" s="14" t="n"/>
-      <c r="K21" s="74" t="inlineStr">
+      <c r="K21" s="70" t="inlineStr">
         <is>
           <t>NATIONAL credit</t>
         </is>
@@ -16421,7 +16760,7 @@
       <c r="F22" s="64" t="n">
         <v>3700</v>
       </c>
-      <c r="G22" s="75" t="n">
+      <c r="G22" s="78" t="n">
         <v>52</v>
       </c>
       <c r="H22" s="47">
@@ -16458,7 +16797,7 @@
       <c r="F23" s="64" t="n">
         <v>2200</v>
       </c>
-      <c r="G23" s="75" t="n">
+      <c r="G23" s="78" t="n">
         <v>58</v>
       </c>
       <c r="H23" s="47">
@@ -16467,7 +16806,7 @@
       </c>
       <c r="I23" s="13" t="n"/>
       <c r="J23" s="14" t="n"/>
-      <c r="K23" s="74" t="inlineStr">
+      <c r="K23" s="70" t="inlineStr">
         <is>
           <t>NATIONAL credit</t>
         </is>
@@ -16495,7 +16834,7 @@
       <c r="F24" s="64" t="n">
         <v>2200</v>
       </c>
-      <c r="G24" s="75" t="n">
+      <c r="G24" s="78" t="n">
         <v>54</v>
       </c>
       <c r="H24" s="47">
@@ -16532,7 +16871,7 @@
       <c r="F25" s="64" t="n">
         <v>2000</v>
       </c>
-      <c r="G25" s="75" t="n">
+      <c r="G25" s="78" t="n">
         <v>50</v>
       </c>
       <c r="H25" s="47">
@@ -16569,7 +16908,7 @@
       <c r="F26" s="64" t="n">
         <v>1800</v>
       </c>
-      <c r="G26" s="75" t="n">
+      <c r="G26" s="78" t="n">
         <v>56</v>
       </c>
       <c r="H26" s="47">
@@ -16606,7 +16945,7 @@
       <c r="F27" s="64" t="n">
         <v>1250</v>
       </c>
-      <c r="G27" s="75" t="n">
+      <c r="G27" s="78" t="n">
         <v>58</v>
       </c>
       <c r="H27" s="47">
@@ -16643,7 +16982,7 @@
       <c r="F28" s="64" t="n">
         <v>1200</v>
       </c>
-      <c r="G28" s="75" t="n">
+      <c r="G28" s="78" t="n">
         <v>56</v>
       </c>
       <c r="H28" s="47">
@@ -16677,15 +17016,15 @@
         </is>
       </c>
       <c r="E29" s="14" t="n"/>
-      <c r="F29" s="76" t="n">
+      <c r="F29" s="79" t="n">
         <v>4422</v>
       </c>
-      <c r="G29" s="77" t="inlineStr">
+      <c r="G29" s="80" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H29" s="77" t="inlineStr">
+      <c r="H29" s="80" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -16711,13 +17050,13 @@
           <t>9 tenants + vacancy</t>
         </is>
       </c>
-      <c r="D30" s="78" t="inlineStr"/>
+      <c r="D30" s="81" t="inlineStr"/>
       <c r="E30" s="14" t="n"/>
       <c r="F30" s="66">
         <f>SUM(F20:F29)</f>
         <v/>
       </c>
-      <c r="G30" s="79">
+      <c r="G30" s="82">
         <f>IFERROR(SUM(H20:H28)/SUM(F20:F28),0)</f>
         <v/>
       </c>
@@ -16778,7 +17117,7 @@
           <t>GLA (SF)</t>
         </is>
       </c>
-      <c r="C34" s="73" t="n">
+      <c r="C34" s="77" t="n">
         <v>26272</v>
       </c>
       <c r="D34" s="22" t="inlineStr">
@@ -16803,7 +17142,7 @@
         </is>
       </c>
       <c r="C35" s="24">
-        <f>'Assumptions'!C50</f>
+        <f>'Assumptions'!C51</f>
         <v/>
       </c>
       <c r="D35" s="22" t="inlineStr">
@@ -16828,7 +17167,7 @@
         </is>
       </c>
       <c r="C36" s="25">
-        <f>'Assumptions'!C47</f>
+        <f>'Assumptions'!C48</f>
         <v/>
       </c>
       <c r="D36" s="22" t="inlineStr">
@@ -16852,7 +17191,7 @@
           <t>Effective millage</t>
         </is>
       </c>
-      <c r="C37" s="80" t="n">
+      <c r="C37" s="83" t="n">
         <v>0.0191</v>
       </c>
       <c r="D37" s="22" t="inlineStr">
@@ -16894,7 +17233,7 @@
           <t>In-place base rent ($/SF NNN)</t>
         </is>
       </c>
-      <c r="C39" s="75" t="n">
+      <c r="C39" s="78" t="n">
         <v>55</v>
       </c>
       <c r="D39" s="22" t="inlineStr">
@@ -16919,7 +17258,7 @@
         </is>
       </c>
       <c r="C40" s="26">
-        <f>'Assumptions'!C49</f>
+        <f>'Assumptions'!C50</f>
         <v/>
       </c>
       <c r="D40" s="22" t="inlineStr">
@@ -16943,7 +17282,7 @@
           <t>Market rent growth</t>
         </is>
       </c>
-      <c r="C41" s="81" t="n">
+      <c r="C41" s="84" t="n">
         <v>0.03</v>
       </c>
       <c r="D41" s="22" t="inlineStr">
@@ -16968,7 +17307,7 @@
         </is>
       </c>
       <c r="C42" s="18">
-        <f>'Assumptions'!C51</f>
+        <f>'Assumptions'!C52</f>
         <v/>
       </c>
       <c r="D42" s="22" t="inlineStr">
@@ -16992,7 +17331,7 @@
           <t>Credit &amp; collection loss</t>
         </is>
       </c>
-      <c r="C43" s="81" t="n">
+      <c r="C43" s="84" t="n">
         <v>0.02</v>
       </c>
       <c r="D43" s="22" t="inlineStr">
@@ -17034,7 +17373,7 @@
           <t>Reassessed value (= price, FL rule)</t>
         </is>
       </c>
-      <c r="C45" s="82" t="n">
+      <c r="C45" s="85" t="n">
         <v>17100000</v>
       </c>
       <c r="D45" s="22" t="inlineStr">
@@ -17059,7 +17398,7 @@
         </is>
       </c>
       <c r="C46" s="23">
-        <f>'Assumptions'!C52</f>
+        <f>'Assumptions'!C53</f>
         <v/>
       </c>
       <c r="D46" s="22" t="inlineStr">
@@ -17084,7 +17423,7 @@
         </is>
       </c>
       <c r="C47" s="23">
-        <f>'Assumptions'!C53</f>
+        <f>'Assumptions'!C54</f>
         <v/>
       </c>
       <c r="D47" s="22" t="inlineStr">
@@ -17109,7 +17448,7 @@
         </is>
       </c>
       <c r="C48" s="23">
-        <f>'Assumptions'!C54</f>
+        <f>'Assumptions'!C55</f>
         <v/>
       </c>
       <c r="D48" s="22" t="inlineStr">
@@ -17134,7 +17473,7 @@
         </is>
       </c>
       <c r="C49" s="18">
-        <f>'Assumptions'!C55</f>
+        <f>'Assumptions'!C56</f>
         <v/>
       </c>
       <c r="D49" s="22" t="inlineStr">
@@ -17158,7 +17497,7 @@
           <t>Expense growth</t>
         </is>
       </c>
-      <c r="C50" s="81" t="n">
+      <c r="C50" s="84" t="n">
         <v>0.03</v>
       </c>
       <c r="D50" s="22" t="inlineStr">
@@ -17200,7 +17539,7 @@
           <t>Tenant improvements ($/SF)</t>
         </is>
       </c>
-      <c r="C52" s="75" t="n">
+      <c r="C52" s="78" t="n">
         <v>30</v>
       </c>
       <c r="D52" s="22" t="inlineStr">
@@ -17224,7 +17563,7 @@
           <t>Leasing commissions ($/SF)</t>
         </is>
       </c>
-      <c r="C53" s="75" t="n">
+      <c r="C53" s="78" t="n">
         <v>20</v>
       </c>
       <c r="D53" s="22" t="inlineStr">
@@ -17248,7 +17587,7 @@
           <t>Replacement reserves ($/SF/yr)</t>
         </is>
       </c>
-      <c r="C54" s="75" t="n">
+      <c r="C54" s="78" t="n">
         <v>0.15</v>
       </c>
       <c r="D54" s="22" t="inlineStr">
@@ -17272,7 +17611,7 @@
           <t>Rollover leasing reserve ($/SF/yr)</t>
         </is>
       </c>
-      <c r="C55" s="75" t="n">
+      <c r="C55" s="78" t="n">
         <v>0.75</v>
       </c>
       <c r="D55" s="22" t="inlineStr">
@@ -17315,7 +17654,7 @@
         </is>
       </c>
       <c r="C57" s="23">
-        <f>'Assumptions'!C46</f>
+        <f>'Assumptions'!C47</f>
         <v/>
       </c>
       <c r="D57" s="22" t="inlineStr">
@@ -17339,7 +17678,7 @@
           <t>Closing &amp; acq costs (% price)</t>
         </is>
       </c>
-      <c r="C58" s="81" t="n">
+      <c r="C58" s="84" t="n">
         <v>0.025</v>
       </c>
       <c r="D58" s="22" t="inlineStr">
@@ -17364,7 +17703,7 @@
         </is>
       </c>
       <c r="C59" s="18">
-        <f>'Assumptions'!C58</f>
+        <f>'Assumptions'!C59</f>
         <v/>
       </c>
       <c r="D59" s="22" t="inlineStr">
@@ -17389,7 +17728,7 @@
         </is>
       </c>
       <c r="C60" s="24">
-        <f>'Assumptions'!C59</f>
+        <f>'Assumptions'!C60</f>
         <v/>
       </c>
       <c r="D60" s="22" t="inlineStr">
@@ -17413,7 +17752,7 @@
           <t>Senior loan amortization (yrs)</t>
         </is>
       </c>
-      <c r="C61" s="83" t="n">
+      <c r="C61" s="86" t="n">
         <v>30</v>
       </c>
       <c r="D61" s="22" t="inlineStr">
@@ -17456,7 +17795,7 @@
         </is>
       </c>
       <c r="C63" s="18">
-        <f>'Assumptions'!C56</f>
+        <f>'Assumptions'!C57</f>
         <v/>
       </c>
       <c r="D63" s="22" t="inlineStr">
@@ -17481,7 +17820,7 @@
         </is>
       </c>
       <c r="C64" s="18">
-        <f>'Assumptions'!C57</f>
+        <f>'Assumptions'!C58</f>
         <v/>
       </c>
       <c r="D64" s="22" t="inlineStr">
@@ -17505,7 +17844,7 @@
           <t>Cost of sale at exit</t>
         </is>
       </c>
-      <c r="C65" s="81" t="n">
+      <c r="C65" s="84" t="n">
         <v>0.02</v>
       </c>
       <c r="D65" s="22" t="inlineStr">
@@ -17529,7 +17868,7 @@
           <t>Hold period (yrs)</t>
         </is>
       </c>
-      <c r="C66" s="83" t="n">
+      <c r="C66" s="86" t="n">
         <v>5</v>
       </c>
       <c r="D66" s="22" t="inlineStr">
@@ -17553,7 +17892,7 @@
           <t>Discount rate (unlevered, for NPV)</t>
         </is>
       </c>
-      <c r="C67" s="81" t="n">
+      <c r="C67" s="84" t="n">
         <v>0.09</v>
       </c>
       <c r="D67" s="22" t="inlineStr">
@@ -17724,7 +18063,7 @@
         </is>
       </c>
       <c r="C79" s="26">
-        <f>'Assumptions'!C48</f>
+        <f>'Assumptions'!C49</f>
         <v/>
       </c>
       <c r="D79" s="22" t="inlineStr">
@@ -19337,19 +19676,19 @@
           <t>$ / year</t>
         </is>
       </c>
-      <c r="F132" s="84" t="inlineStr">
+      <c r="F132" s="87" t="inlineStr">
         <is>
           <t>In-place (Yr 1)</t>
         </is>
       </c>
       <c r="G132" s="14" t="n"/>
-      <c r="H132" s="84" t="inlineStr">
+      <c r="H132" s="87" t="inlineStr">
         <is>
           <t>Stabilized (Yr 2)</t>
         </is>
       </c>
       <c r="I132" s="14" t="n"/>
-      <c r="J132" s="84" t="inlineStr">
+      <c r="J132" s="87" t="inlineStr">
         <is>
           <t>Per SF (stab.)</t>
         </is>
@@ -19374,7 +19713,7 @@
         <v/>
       </c>
       <c r="I133" s="14" t="n"/>
-      <c r="J133" s="85">
+      <c r="J133" s="88">
         <f>H133/C34</f>
         <v/>
       </c>
@@ -19446,7 +19785,7 @@
         <v/>
       </c>
       <c r="I136" s="14" t="n"/>
-      <c r="J136" s="85">
+      <c r="J136" s="88">
         <f>H136/C34</f>
         <v/>
       </c>
@@ -19590,7 +19929,7 @@
         <v/>
       </c>
       <c r="I142" s="14" t="n"/>
-      <c r="J142" s="85">
+      <c r="J142" s="88">
         <f>H142/C34</f>
         <v/>
       </c>
@@ -19662,7 +20001,7 @@
         <v/>
       </c>
       <c r="I145" s="14" t="n"/>
-      <c r="J145" s="85">
+      <c r="J145" s="88">
         <f>H145/C34</f>
         <v/>
       </c>
@@ -19710,7 +20049,7 @@
         <v/>
       </c>
       <c r="I147" s="14" t="n"/>
-      <c r="J147" s="85">
+      <c r="J147" s="88">
         <f>H147/C34</f>
         <v/>
       </c>
@@ -19956,12 +20295,12 @@
       <c r="M4" s="3" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="B5" s="74" t="inlineStr">
+      <c r="B5" s="70" t="inlineStr">
         <is>
           <t>Record owner (today)</t>
         </is>
       </c>
-      <c r="D5" s="74" t="inlineStr">
+      <c r="D5" s="70" t="inlineStr">
         <is>
           <t>REAL SUB LLC (Publix Super Markets real-estate entity, Lakeland FL) — fee owner</t>
         </is>
@@ -19998,12 +20337,12 @@
       <c r="M6" s="14" t="n"/>
     </row>
     <row r="7" ht="15" customHeight="1">
-      <c r="B7" s="74" t="inlineStr">
+      <c r="B7" s="70" t="inlineStr">
         <is>
           <t>Building</t>
         </is>
       </c>
-      <c r="D7" s="74" t="inlineStr">
+      <c r="D7" s="70" t="inlineStr">
         <is>
           <t>36,822 SF (Publix ~34,622 SF leaseback + Starbucks drive-thru pad ~2,200 SF)</t>
         </is>
@@ -20019,12 +20358,12 @@
       <c r="M7" s="14" t="n"/>
     </row>
     <row r="8" ht="15" customHeight="1">
-      <c r="B8" s="74" t="inlineStr">
+      <c r="B8" s="70" t="inlineStr">
         <is>
           <t>Land</t>
         </is>
       </c>
-      <c r="D8" s="74" t="inlineStr">
+      <c r="D8" s="70" t="inlineStr">
         <is>
           <t>109,791 SF  (2.520 ac)</t>
         </is>
@@ -20040,12 +20379,12 @@
       <c r="M8" s="14" t="n"/>
     </row>
     <row r="9" ht="15" customHeight="1">
-      <c r="B9" s="74" t="inlineStr">
+      <c r="B9" s="70" t="inlineStr">
         <is>
           <t>Year built</t>
         </is>
       </c>
-      <c r="D9" s="74" t="inlineStr">
+      <c r="D9" s="70" t="inlineStr">
         <is>
           <t>2011 (eff. 2012)</t>
         </is>
@@ -20061,12 +20400,12 @@
       <c r="M9" s="14" t="n"/>
     </row>
     <row r="10" ht="15" customHeight="1">
-      <c r="B10" s="74" t="inlineStr">
+      <c r="B10" s="70" t="inlineStr">
         <is>
           <t>Last sale</t>
         </is>
       </c>
-      <c r="D10" s="74" t="inlineStr">
+      <c r="D10" s="70" t="inlineStr">
         <is>
           <t>03/14/2025  —  $25,000,000  (Trustee's Deed)  =  $679/SF bldg · $228/SF land</t>
         </is>
@@ -20082,12 +20421,12 @@
       <c r="M10" s="14" t="n"/>
     </row>
     <row r="11" ht="15" customHeight="1">
-      <c r="B11" s="74" t="inlineStr">
+      <c r="B11" s="70" t="inlineStr">
         <is>
           <t>2025 real-estate taxes</t>
         </is>
       </c>
-      <c r="D11" s="74" t="inlineStr">
+      <c r="D11" s="70" t="inlineStr">
         <is>
           <t>$208,467   (2024: $217,404) — NNN, reimbursed by Publix during leaseback</t>
         </is>
@@ -20239,7 +20578,7 @@
       <c r="G18" s="64" t="n">
         <v>34622</v>
       </c>
-      <c r="H18" s="75" t="n">
+      <c r="H18" s="78" t="n">
         <v>22</v>
       </c>
       <c r="I18" s="47">
@@ -20272,7 +20611,7 @@
       <c r="G19" s="64" t="n">
         <v>2200</v>
       </c>
-      <c r="H19" s="75" t="n">
+      <c r="H19" s="78" t="n">
         <v>60</v>
       </c>
       <c r="I19" s="47">
@@ -20296,13 +20635,13 @@
       </c>
       <c r="C20" s="13" t="n"/>
       <c r="D20" s="14" t="n"/>
-      <c r="E20" s="78" t="inlineStr"/>
+      <c r="E20" s="81" t="inlineStr"/>
       <c r="F20" s="14" t="n"/>
       <c r="G20" s="66">
         <f>SUM(G18:G19)</f>
         <v/>
       </c>
-      <c r="H20" s="79">
+      <c r="H20" s="82">
         <f>IFERROR(SUM(I18:I19)/SUM(G18:G19),0)</f>
         <v/>
       </c>
@@ -20362,7 +20701,7 @@
           <t>Rentable SF</t>
         </is>
       </c>
-      <c r="C24" s="73" t="n">
+      <c r="C24" s="77" t="n">
         <v>36822</v>
       </c>
       <c r="D24" s="22" t="inlineStr">
@@ -20387,7 +20726,7 @@
         </is>
       </c>
       <c r="C25" s="25">
-        <f>'Assumptions'!C63</f>
+        <f>'Assumptions'!C64</f>
         <v/>
       </c>
       <c r="D25" s="22" t="inlineStr">
@@ -20412,7 +20751,7 @@
         </is>
       </c>
       <c r="C26" s="18">
-        <f>'Assumptions'!C70</f>
+        <f>'Assumptions'!C71</f>
         <v/>
       </c>
       <c r="D26" s="22" t="inlineStr">
@@ -20437,7 +20776,7 @@
         </is>
       </c>
       <c r="C27" s="18">
-        <f>'Assumptions'!C71</f>
+        <f>'Assumptions'!C72</f>
         <v/>
       </c>
       <c r="D27" s="22" t="inlineStr">
@@ -20462,7 +20801,7 @@
         </is>
       </c>
       <c r="C28" s="26">
-        <f>('Assumptions'!C66*'Assumptions'!C65+'Assumptions'!C68*'Assumptions'!C67)/C24</f>
+        <f>('Assumptions'!C67*'Assumptions'!C66+'Assumptions'!C69*'Assumptions'!C68)/C24</f>
         <v/>
       </c>
       <c r="D28" s="22" t="inlineStr">
@@ -20486,7 +20825,7 @@
           <t>Rent growth</t>
         </is>
       </c>
-      <c r="C29" s="81" t="n">
+      <c r="C29" s="84" t="n">
         <v>0.02</v>
       </c>
       <c r="D29" s="22" t="inlineStr">
@@ -20510,7 +20849,7 @@
           <t>Credit &amp; collection loss</t>
         </is>
       </c>
-      <c r="C30" s="81" t="n">
+      <c r="C30" s="84" t="n">
         <v>0.01</v>
       </c>
       <c r="D30" s="22" t="inlineStr">
@@ -20534,7 +20873,7 @@
           <t>Effective millage</t>
         </is>
       </c>
-      <c r="C31" s="80" t="n">
+      <c r="C31" s="83" t="n">
         <v>0.0191</v>
       </c>
       <c r="D31" s="22" t="inlineStr">
@@ -20577,7 +20916,7 @@
         </is>
       </c>
       <c r="C33" s="23">
-        <f>'Assumptions'!C72</f>
+        <f>'Assumptions'!C73</f>
         <v/>
       </c>
       <c r="D33" s="22" t="inlineStr">
@@ -20602,7 +20941,7 @@
         </is>
       </c>
       <c r="C34" s="23">
-        <f>'Assumptions'!C73</f>
+        <f>'Assumptions'!C74</f>
         <v/>
       </c>
       <c r="D34" s="22" t="inlineStr">
@@ -20627,7 +20966,7 @@
         </is>
       </c>
       <c r="C35" s="23">
-        <f>'Assumptions'!C74</f>
+        <f>'Assumptions'!C75</f>
         <v/>
       </c>
       <c r="D35" s="22" t="inlineStr">
@@ -20652,7 +20991,7 @@
         </is>
       </c>
       <c r="C36" s="18">
-        <f>'Assumptions'!C75</f>
+        <f>'Assumptions'!C76</f>
         <v/>
       </c>
       <c r="D36" s="22" t="inlineStr">
@@ -20676,7 +21015,7 @@
           <t>Expense growth</t>
         </is>
       </c>
-      <c r="C37" s="81" t="n">
+      <c r="C37" s="84" t="n">
         <v>0.03</v>
       </c>
       <c r="D37" s="22" t="inlineStr">
@@ -20718,7 +21057,7 @@
           <t>Tenant improvements ($/SF)</t>
         </is>
       </c>
-      <c r="C39" s="75" t="n">
+      <c r="C39" s="78" t="n">
         <v>0</v>
       </c>
       <c r="D39" s="22" t="inlineStr">
@@ -20742,7 +21081,7 @@
           <t>Leasing commissions ($/SF)</t>
         </is>
       </c>
-      <c r="C40" s="75" t="n">
+      <c r="C40" s="78" t="n">
         <v>0</v>
       </c>
       <c r="D40" s="22" t="inlineStr">
@@ -20766,7 +21105,7 @@
           <t>Replacement reserves ($/SF/yr)</t>
         </is>
       </c>
-      <c r="C41" s="75" t="n">
+      <c r="C41" s="78" t="n">
         <v>0.15</v>
       </c>
       <c r="D41" s="22" t="inlineStr">
@@ -20790,7 +21129,7 @@
           <t>Rollover leasing reserve ($/SF/yr)</t>
         </is>
       </c>
-      <c r="C42" s="75" t="n">
+      <c r="C42" s="78" t="n">
         <v>0.15</v>
       </c>
       <c r="D42" s="22" t="inlineStr">
@@ -20833,7 +21172,7 @@
         </is>
       </c>
       <c r="C44" s="23">
-        <f>'Assumptions'!C62</f>
+        <f>'Assumptions'!C63</f>
         <v/>
       </c>
       <c r="D44" s="22" t="inlineStr">
@@ -20857,7 +21196,7 @@
           <t>Closing &amp; acq costs (% price)</t>
         </is>
       </c>
-      <c r="C45" s="81" t="n">
+      <c r="C45" s="84" t="n">
         <v>0.02</v>
       </c>
       <c r="D45" s="22" t="inlineStr">
@@ -20882,7 +21221,7 @@
         </is>
       </c>
       <c r="C46" s="18">
-        <f>'Assumptions'!C78</f>
+        <f>'Assumptions'!C79</f>
         <v/>
       </c>
       <c r="D46" s="22" t="inlineStr">
@@ -20907,7 +21246,7 @@
         </is>
       </c>
       <c r="C47" s="24">
-        <f>'Assumptions'!C79</f>
+        <f>'Assumptions'!C80</f>
         <v/>
       </c>
       <c r="D47" s="22" t="inlineStr">
@@ -20931,7 +21270,7 @@
           <t>Senior loan amortization (yrs)</t>
         </is>
       </c>
-      <c r="C48" s="83" t="n">
+      <c r="C48" s="86" t="n">
         <v>30</v>
       </c>
       <c r="D48" s="22" t="inlineStr">
@@ -20974,7 +21313,7 @@
         </is>
       </c>
       <c r="C50" s="24">
-        <f>'Assumptions'!C76</f>
+        <f>'Assumptions'!C77</f>
         <v/>
       </c>
       <c r="D50" s="22" t="inlineStr">
@@ -20999,7 +21338,7 @@
         </is>
       </c>
       <c r="C51" s="24">
-        <f>'Assumptions'!C77</f>
+        <f>'Assumptions'!C78</f>
         <v/>
       </c>
       <c r="D51" s="22" t="inlineStr">
@@ -21023,7 +21362,7 @@
           <t>Cost of sale at exit</t>
         </is>
       </c>
-      <c r="C52" s="81" t="n">
+      <c r="C52" s="84" t="n">
         <v>0.02</v>
       </c>
       <c r="D52" s="22" t="inlineStr">
@@ -21047,7 +21386,7 @@
           <t>Hold period (yrs)</t>
         </is>
       </c>
-      <c r="C53" s="83" t="n">
+      <c r="C53" s="86" t="n">
         <v>5</v>
       </c>
       <c r="D53" s="22" t="inlineStr">
@@ -21071,7 +21410,7 @@
           <t>Discount rate (NPV)</t>
         </is>
       </c>
-      <c r="C54" s="81" t="n">
+      <c r="C54" s="84" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="D54" s="22" t="inlineStr">
@@ -21096,7 +21435,7 @@
         </is>
       </c>
       <c r="C55" s="26">
-        <f>'Assumptions'!C64</f>
+        <f>'Assumptions'!C65</f>
         <v/>
       </c>
       <c r="D55" s="22" t="inlineStr">
@@ -21527,43 +21866,43 @@
         </is>
       </c>
       <c r="D75" s="51">
-        <f>IF(1&lt;='Assumptions'!C69,D73*C28*(1+C29)^(1-1),0)</f>
+        <f>IF(1&lt;='Assumptions'!C70,D73*C28*(1+C29)^(1-1),0)</f>
         <v/>
       </c>
       <c r="E75" s="47">
-        <f>IF(2&lt;='Assumptions'!C69,E73*C28*(1+C29)^(2-1),0)</f>
+        <f>IF(2&lt;='Assumptions'!C70,E73*C28*(1+C29)^(2-1),0)</f>
         <v/>
       </c>
       <c r="F75" s="47">
-        <f>IF(3&lt;='Assumptions'!C69,F73*C28*(1+C29)^(3-1),0)</f>
+        <f>IF(3&lt;='Assumptions'!C70,F73*C28*(1+C29)^(3-1),0)</f>
         <v/>
       </c>
       <c r="G75" s="47">
-        <f>IF(4&lt;='Assumptions'!C69,G73*C28*(1+C29)^(4-1),0)</f>
+        <f>IF(4&lt;='Assumptions'!C70,G73*C28*(1+C29)^(4-1),0)</f>
         <v/>
       </c>
       <c r="H75" s="47">
-        <f>IF(5&lt;='Assumptions'!C69,H73*C28*(1+C29)^(5-1),0)</f>
+        <f>IF(5&lt;='Assumptions'!C70,H73*C28*(1+C29)^(5-1),0)</f>
         <v/>
       </c>
       <c r="I75" s="47">
-        <f>IF(6&lt;='Assumptions'!C69,I73*C28*(1+C29)^(6-1),0)</f>
+        <f>IF(6&lt;='Assumptions'!C70,I73*C28*(1+C29)^(6-1),0)</f>
         <v/>
       </c>
       <c r="J75" s="47">
-        <f>IF(7&lt;='Assumptions'!C69,J73*C28*(1+C29)^(7-1),0)</f>
+        <f>IF(7&lt;='Assumptions'!C70,J73*C28*(1+C29)^(7-1),0)</f>
         <v/>
       </c>
       <c r="K75" s="47">
-        <f>IF(8&lt;='Assumptions'!C69,K73*C28*(1+C29)^(8-1),0)</f>
+        <f>IF(8&lt;='Assumptions'!C70,K73*C28*(1+C29)^(8-1),0)</f>
         <v/>
       </c>
       <c r="L75" s="47">
-        <f>IF(9&lt;='Assumptions'!C69,L73*C28*(1+C29)^(9-1),0)</f>
+        <f>IF(9&lt;='Assumptions'!C70,L73*C28*(1+C29)^(9-1),0)</f>
         <v/>
       </c>
       <c r="M75" s="47">
-        <f>IF(10&lt;='Assumptions'!C69,M73*C28*(1+C29)^(10-1),0)</f>
+        <f>IF(10&lt;='Assumptions'!C70,M73*C28*(1+C29)^(10-1),0)</f>
         <v/>
       </c>
     </row>
@@ -22855,7 +23194,7 @@
           <t>Target Year-1 DSCR</t>
         </is>
       </c>
-      <c r="C119" s="86" t="n">
+      <c r="C119" s="89" t="n">
         <v>1.2</v>
       </c>
       <c r="D119" s="22" t="inlineStr">
@@ -22879,7 +23218,7 @@
           <t>Target going-in cap</t>
         </is>
       </c>
-      <c r="C120" s="80" t="n">
+      <c r="C120" s="83" t="n">
         <v>0.05</v>
       </c>
       <c r="D120" s="22" t="inlineStr">
@@ -22925,8 +23264,8 @@
           <t>→ Required leaseback rent for target DSCR</t>
         </is>
       </c>
-      <c r="C123" s="85">
-        <f>(((C119*C60+C122*C36+C35)/C121)-'Assumptions'!C68*'Assumptions'!C67)/'Assumptions'!C66</f>
+      <c r="C123" s="88">
+        <f>(((C119*C60+C122*C36+C35)/C121)-'Assumptions'!C69*'Assumptions'!C68)/'Assumptions'!C67</f>
         <v/>
       </c>
       <c r="D123" s="22" t="inlineStr">
@@ -22950,8 +23289,8 @@
           <t>→ Required leaseback rent for target cap</t>
         </is>
       </c>
-      <c r="C124" s="85">
-        <f>(((C120*C44+C122*C36+C35)/C121)-'Assumptions'!C68*'Assumptions'!C67)/'Assumptions'!C66</f>
+      <c r="C124" s="88">
+        <f>(((C120*C44+C122*C36+C35)/C121)-'Assumptions'!C69*'Assumptions'!C68)/'Assumptions'!C67</f>
         <v/>
       </c>
       <c r="D124" s="22" t="inlineStr">
@@ -22994,19 +23333,19 @@
           <t>$ / year</t>
         </is>
       </c>
-      <c r="F127" s="84" t="inlineStr">
+      <c r="F127" s="87" t="inlineStr">
         <is>
           <t>Year 1</t>
         </is>
       </c>
       <c r="G127" s="14" t="n"/>
-      <c r="H127" s="84" t="inlineStr">
+      <c r="H127" s="87" t="inlineStr">
         <is>
           <t>Stabilized</t>
         </is>
       </c>
       <c r="I127" s="14" t="n"/>
-      <c r="J127" s="84" t="inlineStr">
+      <c r="J127" s="87" t="inlineStr">
         <is>
           <t>Per SF (stab.)</t>
         </is>
@@ -23031,7 +23370,7 @@
         <v/>
       </c>
       <c r="I128" s="14" t="n"/>
-      <c r="J128" s="85">
+      <c r="J128" s="88">
         <f>H128/C24</f>
         <v/>
       </c>
@@ -23103,7 +23442,7 @@
         <v/>
       </c>
       <c r="I131" s="14" t="n"/>
-      <c r="J131" s="85">
+      <c r="J131" s="88">
         <f>H131/C24</f>
         <v/>
       </c>
@@ -23247,7 +23586,7 @@
         <v/>
       </c>
       <c r="I137" s="14" t="n"/>
-      <c r="J137" s="85">
+      <c r="J137" s="88">
         <f>H137/C24</f>
         <v/>
       </c>
@@ -23319,7 +23658,7 @@
         <v/>
       </c>
       <c r="I140" s="14" t="n"/>
-      <c r="J140" s="85">
+      <c r="J140" s="88">
         <f>H140/C24</f>
         <v/>
       </c>
@@ -23367,7 +23706,7 @@
         <v/>
       </c>
       <c r="I142" s="14" t="n"/>
-      <c r="J142" s="85">
+      <c r="J142" s="88">
         <f>H142/C24</f>
         <v/>
       </c>
@@ -23855,7 +24194,7 @@
       <c r="G17" s="64" t="n">
         <v>6000</v>
       </c>
-      <c r="H17" s="75" t="n">
+      <c r="H17" s="78" t="n">
         <v>34</v>
       </c>
       <c r="I17" s="47">
@@ -23888,7 +24227,7 @@
       <c r="G18" s="64" t="n">
         <v>4000</v>
       </c>
-      <c r="H18" s="75" t="n">
+      <c r="H18" s="78" t="n">
         <v>36</v>
       </c>
       <c r="I18" s="47">
@@ -23921,7 +24260,7 @@
       <c r="G19" s="64" t="n">
         <v>3000</v>
       </c>
-      <c r="H19" s="75" t="n">
+      <c r="H19" s="78" t="n">
         <v>40</v>
       </c>
       <c r="I19" s="47">
@@ -23954,7 +24293,7 @@
       <c r="G20" s="64" t="n">
         <v>6005</v>
       </c>
-      <c r="H20" s="75" t="n">
+      <c r="H20" s="78" t="n">
         <v>30</v>
       </c>
       <c r="I20" s="47">
@@ -23987,7 +24326,7 @@
       <c r="G21" s="64" t="n">
         <v>1100</v>
       </c>
-      <c r="H21" s="75" t="n">
+      <c r="H21" s="78" t="n">
         <v>32</v>
       </c>
       <c r="I21" s="47">
@@ -24017,15 +24356,15 @@
         </is>
       </c>
       <c r="F22" s="14" t="n"/>
-      <c r="G22" s="76" t="n">
+      <c r="G22" s="79" t="n">
         <v>5000</v>
       </c>
-      <c r="H22" s="77" t="inlineStr">
+      <c r="H22" s="80" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I22" s="77" t="inlineStr">
+      <c r="I22" s="80" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -24047,13 +24386,13 @@
       </c>
       <c r="C23" s="13" t="n"/>
       <c r="D23" s="14" t="n"/>
-      <c r="E23" s="78" t="inlineStr"/>
+      <c r="E23" s="81" t="inlineStr"/>
       <c r="F23" s="14" t="n"/>
       <c r="G23" s="66">
         <f>SUM(G17:G22)</f>
         <v/>
       </c>
-      <c r="H23" s="79">
+      <c r="H23" s="82">
         <f>IFERROR(SUM(I17:I21)/SUM(G17:G21),0)</f>
         <v/>
       </c>
@@ -24113,7 +24452,7 @@
           <t>Rentable SF</t>
         </is>
       </c>
-      <c r="C27" s="73" t="n">
+      <c r="C27" s="77" t="n">
         <v>25105</v>
       </c>
       <c r="D27" s="22" t="inlineStr">
@@ -24138,7 +24477,7 @@
         </is>
       </c>
       <c r="C28" s="25">
-        <f>'Assumptions'!C83</f>
+        <f>'Assumptions'!C84</f>
         <v/>
       </c>
       <c r="D28" s="22" t="inlineStr">
@@ -24163,7 +24502,7 @@
         </is>
       </c>
       <c r="C29" s="18">
-        <f>'Assumptions'!C86</f>
+        <f>'Assumptions'!C87</f>
         <v/>
       </c>
       <c r="D29" s="22" t="inlineStr">
@@ -24188,7 +24527,7 @@
         </is>
       </c>
       <c r="C30" s="18">
-        <f>'Assumptions'!C87</f>
+        <f>'Assumptions'!C88</f>
         <v/>
       </c>
       <c r="D30" s="22" t="inlineStr">
@@ -24213,7 +24552,7 @@
         </is>
       </c>
       <c r="C31" s="26">
-        <f>'Assumptions'!C85</f>
+        <f>'Assumptions'!C86</f>
         <v/>
       </c>
       <c r="D31" s="22" t="inlineStr">
@@ -24237,7 +24576,7 @@
           <t>Rent growth</t>
         </is>
       </c>
-      <c r="C32" s="81" t="n">
+      <c r="C32" s="84" t="n">
         <v>0.03</v>
       </c>
       <c r="D32" s="22" t="inlineStr">
@@ -24261,7 +24600,7 @@
           <t>Credit &amp; collection loss</t>
         </is>
       </c>
-      <c r="C33" s="81" t="n">
+      <c r="C33" s="84" t="n">
         <v>0.03</v>
       </c>
       <c r="D33" s="22" t="inlineStr">
@@ -24285,7 +24624,7 @@
           <t>Effective millage</t>
         </is>
       </c>
-      <c r="C34" s="80" t="n">
+      <c r="C34" s="83" t="n">
         <v>0.0191</v>
       </c>
       <c r="D34" s="22" t="inlineStr">
@@ -24328,7 +24667,7 @@
         </is>
       </c>
       <c r="C36" s="23">
-        <f>'Assumptions'!C88</f>
+        <f>'Assumptions'!C89</f>
         <v/>
       </c>
       <c r="D36" s="22" t="inlineStr">
@@ -24353,7 +24692,7 @@
         </is>
       </c>
       <c r="C37" s="23">
-        <f>'Assumptions'!C89</f>
+        <f>'Assumptions'!C90</f>
         <v/>
       </c>
       <c r="D37" s="22" t="inlineStr">
@@ -24378,7 +24717,7 @@
         </is>
       </c>
       <c r="C38" s="23">
-        <f>'Assumptions'!C90</f>
+        <f>'Assumptions'!C91</f>
         <v/>
       </c>
       <c r="D38" s="22" t="inlineStr">
@@ -24403,7 +24742,7 @@
         </is>
       </c>
       <c r="C39" s="18">
-        <f>'Assumptions'!C91</f>
+        <f>'Assumptions'!C92</f>
         <v/>
       </c>
       <c r="D39" s="22" t="inlineStr">
@@ -24427,7 +24766,7 @@
           <t>Expense growth</t>
         </is>
       </c>
-      <c r="C40" s="81" t="n">
+      <c r="C40" s="84" t="n">
         <v>0.03</v>
       </c>
       <c r="D40" s="22" t="inlineStr">
@@ -24469,7 +24808,7 @@
           <t>Tenant improvements ($/SF)</t>
         </is>
       </c>
-      <c r="C42" s="75" t="n">
+      <c r="C42" s="78" t="n">
         <v>30</v>
       </c>
       <c r="D42" s="22" t="inlineStr">
@@ -24493,7 +24832,7 @@
           <t>Leasing commissions ($/SF)</t>
         </is>
       </c>
-      <c r="C43" s="75" t="n">
+      <c r="C43" s="78" t="n">
         <v>20</v>
       </c>
       <c r="D43" s="22" t="inlineStr">
@@ -24517,7 +24856,7 @@
           <t>Replacement reserves ($/SF/yr)</t>
         </is>
       </c>
-      <c r="C44" s="75" t="n">
+      <c r="C44" s="78" t="n">
         <v>0.15</v>
       </c>
       <c r="D44" s="22" t="inlineStr">
@@ -24541,7 +24880,7 @@
           <t>Rollover leasing reserve ($/SF/yr)</t>
         </is>
       </c>
-      <c r="C45" s="75" t="n">
+      <c r="C45" s="78" t="n">
         <v>0.75</v>
       </c>
       <c r="D45" s="22" t="inlineStr">
@@ -24584,7 +24923,7 @@
         </is>
       </c>
       <c r="C47" s="23">
-        <f>'Assumptions'!C82</f>
+        <f>'Assumptions'!C83</f>
         <v/>
       </c>
       <c r="D47" s="22" t="inlineStr">
@@ -24608,7 +24947,7 @@
           <t>Closing &amp; acq costs (% price)</t>
         </is>
       </c>
-      <c r="C48" s="81" t="n">
+      <c r="C48" s="84" t="n">
         <v>0.025</v>
       </c>
       <c r="D48" s="22" t="inlineStr">
@@ -24633,7 +24972,7 @@
         </is>
       </c>
       <c r="C49" s="18">
-        <f>'Assumptions'!C94</f>
+        <f>'Assumptions'!C95</f>
         <v/>
       </c>
       <c r="D49" s="22" t="inlineStr">
@@ -24658,7 +24997,7 @@
         </is>
       </c>
       <c r="C50" s="24">
-        <f>'Assumptions'!C95</f>
+        <f>'Assumptions'!C96</f>
         <v/>
       </c>
       <c r="D50" s="22" t="inlineStr">
@@ -24682,7 +25021,7 @@
           <t>Senior loan amortization (yrs)</t>
         </is>
       </c>
-      <c r="C51" s="83" t="n">
+      <c r="C51" s="86" t="n">
         <v>30</v>
       </c>
       <c r="D51" s="22" t="inlineStr">
@@ -24725,7 +25064,7 @@
         </is>
       </c>
       <c r="C53" s="24">
-        <f>'Assumptions'!C92</f>
+        <f>'Assumptions'!C93</f>
         <v/>
       </c>
       <c r="D53" s="22" t="inlineStr">
@@ -24750,7 +25089,7 @@
         </is>
       </c>
       <c r="C54" s="24">
-        <f>'Assumptions'!C93</f>
+        <f>'Assumptions'!C94</f>
         <v/>
       </c>
       <c r="D54" s="22" t="inlineStr">
@@ -24774,7 +25113,7 @@
           <t>Cost of sale at exit</t>
         </is>
       </c>
-      <c r="C55" s="81" t="n">
+      <c r="C55" s="84" t="n">
         <v>0.02</v>
       </c>
       <c r="D55" s="22" t="inlineStr">
@@ -24798,7 +25137,7 @@
           <t>Hold period (yrs)</t>
         </is>
       </c>
-      <c r="C56" s="83" t="n">
+      <c r="C56" s="86" t="n">
         <v>5</v>
       </c>
       <c r="D56" s="22" t="inlineStr">
@@ -24822,7 +25161,7 @@
           <t>Discount rate (NPV)</t>
         </is>
       </c>
-      <c r="C57" s="81" t="n">
+      <c r="C57" s="84" t="n">
         <v>0.09</v>
       </c>
       <c r="D57" s="22" t="inlineStr">
@@ -24847,7 +25186,7 @@
         </is>
       </c>
       <c r="C58" s="26">
-        <f>'Assumptions'!C84</f>
+        <f>'Assumptions'!C85</f>
         <v/>
       </c>
       <c r="D58" s="22" t="inlineStr">
@@ -26606,19 +26945,19 @@
           <t>$ / year</t>
         </is>
       </c>
-      <c r="F122" s="84" t="inlineStr">
+      <c r="F122" s="87" t="inlineStr">
         <is>
           <t>Year 1</t>
         </is>
       </c>
       <c r="G122" s="14" t="n"/>
-      <c r="H122" s="84" t="inlineStr">
+      <c r="H122" s="87" t="inlineStr">
         <is>
           <t>Stabilized</t>
         </is>
       </c>
       <c r="I122" s="14" t="n"/>
-      <c r="J122" s="84" t="inlineStr">
+      <c r="J122" s="87" t="inlineStr">
         <is>
           <t>Per SF (stab.)</t>
         </is>
@@ -26643,7 +26982,7 @@
         <v/>
       </c>
       <c r="I123" s="14" t="n"/>
-      <c r="J123" s="85">
+      <c r="J123" s="88">
         <f>H123/C27</f>
         <v/>
       </c>
@@ -26715,7 +27054,7 @@
         <v/>
       </c>
       <c r="I126" s="14" t="n"/>
-      <c r="J126" s="85">
+      <c r="J126" s="88">
         <f>H126/C27</f>
         <v/>
       </c>
@@ -26859,7 +27198,7 @@
         <v/>
       </c>
       <c r="I132" s="14" t="n"/>
-      <c r="J132" s="85">
+      <c r="J132" s="88">
         <f>H132/C27</f>
         <v/>
       </c>
@@ -26931,7 +27270,7 @@
         <v/>
       </c>
       <c r="I135" s="14" t="n"/>
-      <c r="J135" s="85">
+      <c r="J135" s="88">
         <f>H135/C27</f>
         <v/>
       </c>
@@ -26979,7 +27318,7 @@
         <v/>
       </c>
       <c r="I137" s="14" t="n"/>
-      <c r="J137" s="85">
+      <c r="J137" s="88">
         <f>H137/C27</f>
         <v/>
       </c>

--- a/Shahidi_Assemblage_Model.xlsx
+++ b/Shahidi_Assemblage_Model.xlsx
@@ -306,7 +306,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="92">
+  <cellXfs count="95">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -570,7 +570,16 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="3" fillId="7" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="7" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1376,20 +1385,20 @@
       <c r="E21" s="13" t="n"/>
       <c r="F21" s="14" t="n"/>
       <c r="G21" s="17">
-        <f>'Office Condo'!C95</f>
+        <f>'Office Condo'!I97</f>
         <v/>
       </c>
       <c r="H21" s="17">
-        <f>'Office Condo'!C76</f>
+        <f>'Office Condo'!C78</f>
         <v/>
       </c>
       <c r="I21" s="14" t="n"/>
       <c r="J21" s="18">
-        <f>'Office Condo'!C71</f>
+        <f>'Office Condo'!C73</f>
         <v/>
       </c>
       <c r="K21" s="18">
-        <f>'Office Condo'!C74</f>
+        <f>'Office Condo'!C76</f>
         <v/>
       </c>
       <c r="L21" s="13" t="n"/>
@@ -1605,7 +1614,7 @@
         </is>
       </c>
       <c r="C31" s="23">
-        <f>'Office Condo'!C95</f>
+        <f>'Office Condo'!I97</f>
         <v/>
       </c>
       <c r="D31" s="22" t="inlineStr">
@@ -2157,7 +2166,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M110"/>
+  <dimension ref="A1:M112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.5" customWidth="1" min="1" max="1"/>
@@ -2193,10 +2202,10 @@
       <c r="L1" s="2" t="n"/>
       <c r="M1" s="3" t="n"/>
     </row>
-    <row r="2" ht="18" customHeight="1">
+    <row r="2" ht="20" customHeight="1">
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>2455 E Sunrise Blvd   |   13-story Class B office condo · ~168,807 SF · built 1973 (renov. 2007) · two dominant owners — lease-position valuation</t>
+          <t>2455 E Sunrise Blvd   |   13-story Class B office condo · ~168,807 SF · built 1973 (renov. 2007) · fractured ownership — every owner modeled individually + full buy-out</t>
         </is>
       </c>
       <c r="C2" s="2" t="n"/>
@@ -2377,15 +2386,15 @@
       <c r="L11" s="13" t="n"/>
       <c r="M11" s="14" t="n"/>
     </row>
-    <row r="12" ht="15" customHeight="1">
+    <row r="12" ht="27" customHeight="1">
       <c r="B12" s="12" t="inlineStr">
         <is>
-          <t>Deal note</t>
+          <t>Ownership</t>
         </is>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
-          <t>Assembling the building = buying out BOTH dominant owners' condo positions</t>
+          <t>Fractured condo: Main St Fund (Grove Gate) held 57.4% and is NOW RESELLING units individually; the balance is International Sunrise + a growing number of small owners (Jorgensen, Hublot, Merrimac, individual suites)</t>
         </is>
       </c>
       <c r="E12" s="13" t="n"/>
@@ -2398,87 +2407,79 @@
       <c r="L12" s="13" t="n"/>
       <c r="M12" s="14" t="n"/>
     </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="B14" s="11" t="inlineStr">
+    <row r="13" ht="15" customHeight="1">
+      <c r="B13" s="12" t="inlineStr">
+        <is>
+          <t>Buy-out note</t>
+        </is>
+      </c>
+      <c r="D13" s="12" t="inlineStr">
+        <is>
+          <t>Assembling the building = buying out EVERY unit owner (modeled individually below; the un-itemizable balance is grouped)</t>
+        </is>
+      </c>
+      <c r="E13" s="13" t="n"/>
+      <c r="F13" s="13" t="n"/>
+      <c r="G13" s="13" t="n"/>
+      <c r="H13" s="13" t="n"/>
+      <c r="I13" s="13" t="n"/>
+      <c r="J13" s="13" t="n"/>
+      <c r="K13" s="13" t="n"/>
+      <c r="L13" s="13" t="n"/>
+      <c r="M13" s="14" t="n"/>
+    </row>
+    <row r="14" ht="27" customHeight="1">
+      <c r="B14" s="12" t="inlineStr">
+        <is>
+          <t>⚠️ BCPA limitation</t>
+        </is>
+      </c>
+      <c r="D14" s="12" t="inlineStr">
+        <is>
+          <t>bcpa.net and the Broward Clerk are egress-blocked in this build; the complete per-unit folio roster (every unit, owner, price, date) needs a direct BCPA pull to finish</t>
+        </is>
+      </c>
+      <c r="E14" s="13" t="n"/>
+      <c r="F14" s="13" t="n"/>
+      <c r="G14" s="13" t="n"/>
+      <c r="H14" s="13" t="n"/>
+      <c r="I14" s="13" t="n"/>
+      <c r="J14" s="13" t="n"/>
+      <c r="K14" s="13" t="n"/>
+      <c r="L14" s="13" t="n"/>
+      <c r="M14" s="14" t="n"/>
+    </row>
+    <row r="15"/>
+    <row r="16">
+      <c r="B16" s="11" t="inlineStr">
         <is>
           <t>ASSUMPTIONS  —  🔵 blue = hardcoded inputs (Modified-Gross office)</t>
         </is>
       </c>
-      <c r="C14" s="2" t="n"/>
-      <c r="D14" s="2" t="n"/>
-      <c r="E14" s="2" t="n"/>
-      <c r="F14" s="2" t="n"/>
-      <c r="G14" s="2" t="n"/>
-      <c r="H14" s="2" t="n"/>
-      <c r="I14" s="2" t="n"/>
-      <c r="J14" s="2" t="n"/>
-      <c r="K14" s="2" t="n"/>
-      <c r="L14" s="2" t="n"/>
-      <c r="M14" s="3" t="n"/>
-    </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="B15" s="12" t="inlineStr">
-        <is>
-          <t>Rentable SF (both owners)</t>
-        </is>
-      </c>
-      <c r="C15" s="77" t="n">
-        <v>168807</v>
-      </c>
-      <c r="D15" s="22" t="inlineStr">
-        <is>
-          <t>⚠️ ~168,807 SF</t>
-        </is>
-      </c>
-      <c r="E15" s="13" t="n"/>
-      <c r="F15" s="13" t="n"/>
-      <c r="G15" s="13" t="n"/>
-      <c r="H15" s="13" t="n"/>
-      <c r="I15" s="13" t="n"/>
-      <c r="J15" s="13" t="n"/>
-      <c r="K15" s="13" t="n"/>
-      <c r="L15" s="13" t="n"/>
-      <c r="M15" s="14" t="n"/>
-    </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="B16" s="12" t="inlineStr">
-        <is>
-          <t>In-place occupancy</t>
-        </is>
-      </c>
-      <c r="C16" s="18">
-        <f>'Assumptions'!C101</f>
-        <v/>
-      </c>
-      <c r="D16" s="22" t="inlineStr">
-        <is>
-          <t>🟢 Assumptions</t>
-        </is>
-      </c>
-      <c r="E16" s="13" t="n"/>
-      <c r="F16" s="13" t="n"/>
-      <c r="G16" s="13" t="n"/>
-      <c r="H16" s="13" t="n"/>
-      <c r="I16" s="13" t="n"/>
-      <c r="J16" s="13" t="n"/>
-      <c r="K16" s="13" t="n"/>
-      <c r="L16" s="13" t="n"/>
-      <c r="M16" s="14" t="n"/>
+      <c r="C16" s="2" t="n"/>
+      <c r="D16" s="2" t="n"/>
+      <c r="E16" s="2" t="n"/>
+      <c r="F16" s="2" t="n"/>
+      <c r="G16" s="2" t="n"/>
+      <c r="H16" s="2" t="n"/>
+      <c r="I16" s="2" t="n"/>
+      <c r="J16" s="2" t="n"/>
+      <c r="K16" s="2" t="n"/>
+      <c r="L16" s="2" t="n"/>
+      <c r="M16" s="3" t="n"/>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="B17" s="12" t="inlineStr">
         <is>
-          <t>Stabilized occupancy</t>
-        </is>
-      </c>
-      <c r="C17" s="18">
-        <f>'Assumptions'!C102</f>
-        <v/>
+          <t>Rentable SF (both owners)</t>
+        </is>
+      </c>
+      <c r="C17" s="77" t="n">
+        <v>168807</v>
       </c>
       <c r="D17" s="22" t="inlineStr">
         <is>
-          <t>🟢 Assumptions</t>
+          <t>⚠️ ~168,807 SF</t>
         </is>
       </c>
       <c r="E17" s="13" t="n"/>
@@ -2494,11 +2495,11 @@
     <row r="18" ht="15" customHeight="1">
       <c r="B18" s="12" t="inlineStr">
         <is>
-          <t>Market rent ($/SF Modified Gross)</t>
-        </is>
-      </c>
-      <c r="C18" s="26">
-        <f>'Assumptions'!C100</f>
+          <t>In-place occupancy</t>
+        </is>
+      </c>
+      <c r="C18" s="18">
+        <f>'Assumptions'!C101</f>
         <v/>
       </c>
       <c r="D18" s="22" t="inlineStr">
@@ -2519,15 +2520,16 @@
     <row r="19" ht="15" customHeight="1">
       <c r="B19" s="12" t="inlineStr">
         <is>
-          <t>Rent growth</t>
-        </is>
-      </c>
-      <c r="C19" s="84" t="n">
-        <v>0.03</v>
+          <t>Stabilized occupancy</t>
+        </is>
+      </c>
+      <c r="C19" s="18">
+        <f>'Assumptions'!C102</f>
+        <v/>
       </c>
       <c r="D19" s="22" t="inlineStr">
         <is>
-          <t>🔶</t>
+          <t>🟢 Assumptions</t>
         </is>
       </c>
       <c r="E19" s="13" t="n"/>
@@ -2543,15 +2545,16 @@
     <row r="20" ht="15" customHeight="1">
       <c r="B20" s="12" t="inlineStr">
         <is>
-          <t>Credit &amp; vacancy loss</t>
-        </is>
-      </c>
-      <c r="C20" s="84" t="n">
-        <v>0.03</v>
+          <t>Market rent ($/SF Modified Gross)</t>
+        </is>
+      </c>
+      <c r="C20" s="26">
+        <f>'Assumptions'!C100</f>
+        <v/>
       </c>
       <c r="D20" s="22" t="inlineStr">
         <is>
-          <t>🔶</t>
+          <t>🟢 Assumptions</t>
         </is>
       </c>
       <c r="E20" s="13" t="n"/>
@@ -2567,15 +2570,15 @@
     <row r="21" ht="15" customHeight="1">
       <c r="B21" s="12" t="inlineStr">
         <is>
-          <t>Effective millage</t>
-        </is>
-      </c>
-      <c r="C21" s="83" t="n">
-        <v>0.0191</v>
+          <t>Rent growth</t>
+        </is>
+      </c>
+      <c r="C21" s="84" t="n">
+        <v>0.03</v>
       </c>
       <c r="D21" s="22" t="inlineStr">
         <is>
-          <t>✅ area millage</t>
+          <t>🔶</t>
         </is>
       </c>
       <c r="E21" s="13" t="n"/>
@@ -2591,16 +2594,15 @@
     <row r="22" ht="15" customHeight="1">
       <c r="B22" s="12" t="inlineStr">
         <is>
-          <t>Office opex ex-taxes ($/SF, landlord)</t>
-        </is>
-      </c>
-      <c r="C22" s="26">
-        <f>'Assumptions'!C103</f>
-        <v/>
+          <t>Credit &amp; vacancy loss</t>
+        </is>
+      </c>
+      <c r="C22" s="84" t="n">
+        <v>0.03</v>
       </c>
       <c r="D22" s="22" t="inlineStr">
         <is>
-          <t>🟢 Assumptions</t>
+          <t>🔶</t>
         </is>
       </c>
       <c r="E22" s="13" t="n"/>
@@ -2616,16 +2618,15 @@
     <row r="23" ht="15" customHeight="1">
       <c r="B23" s="12" t="inlineStr">
         <is>
-          <t>Management fee (% EGR)</t>
-        </is>
-      </c>
-      <c r="C23" s="18">
-        <f>'Assumptions'!C104</f>
-        <v/>
+          <t>Effective millage</t>
+        </is>
+      </c>
+      <c r="C23" s="83" t="n">
+        <v>0.0191</v>
       </c>
       <c r="D23" s="22" t="inlineStr">
         <is>
-          <t>🟢 Assumptions</t>
+          <t>✅ area millage</t>
         </is>
       </c>
       <c r="E23" s="13" t="n"/>
@@ -2641,15 +2642,16 @@
     <row r="24" ht="15" customHeight="1">
       <c r="B24" s="12" t="inlineStr">
         <is>
-          <t>Expense growth</t>
-        </is>
-      </c>
-      <c r="C24" s="84" t="n">
-        <v>0.03</v>
+          <t>Office opex ex-taxes ($/SF, landlord)</t>
+        </is>
+      </c>
+      <c r="C24" s="26">
+        <f>'Assumptions'!C103</f>
+        <v/>
       </c>
       <c r="D24" s="22" t="inlineStr">
         <is>
-          <t>🔶</t>
+          <t>🟢 Assumptions</t>
         </is>
       </c>
       <c r="E24" s="13" t="n"/>
@@ -2665,15 +2667,16 @@
     <row r="25" ht="15" customHeight="1">
       <c r="B25" s="12" t="inlineStr">
         <is>
-          <t>Replacement reserves ($/SF/yr)</t>
-        </is>
-      </c>
-      <c r="C25" s="78" t="n">
-        <v>0.2</v>
+          <t>Management fee (% EGR)</t>
+        </is>
+      </c>
+      <c r="C25" s="18">
+        <f>'Assumptions'!C104</f>
+        <v/>
       </c>
       <c r="D25" s="22" t="inlineStr">
         <is>
-          <t>🔶</t>
+          <t>🟢 Assumptions</t>
         </is>
       </c>
       <c r="E25" s="13" t="n"/>
@@ -2689,16 +2692,15 @@
     <row r="26" ht="15" customHeight="1">
       <c r="B26" s="12" t="inlineStr">
         <is>
-          <t>Acquisition basis (income value)</t>
-        </is>
-      </c>
-      <c r="C26" s="23">
-        <f>'Assumptions'!C99</f>
-        <v/>
+          <t>Expense growth</t>
+        </is>
+      </c>
+      <c r="C26" s="84" t="n">
+        <v>0.03</v>
       </c>
       <c r="D26" s="22" t="inlineStr">
         <is>
-          <t>🟢 Assumptions</t>
+          <t>🔶</t>
         </is>
       </c>
       <c r="E26" s="13" t="n"/>
@@ -2714,11 +2716,11 @@
     <row r="27" ht="15" customHeight="1">
       <c r="B27" s="12" t="inlineStr">
         <is>
-          <t>Closing &amp; acq costs (% price)</t>
-        </is>
-      </c>
-      <c r="C27" s="84" t="n">
-        <v>0.02</v>
+          <t>Replacement reserves ($/SF/yr)</t>
+        </is>
+      </c>
+      <c r="C27" s="78" t="n">
+        <v>0.2</v>
       </c>
       <c r="D27" s="22" t="inlineStr">
         <is>
@@ -2738,11 +2740,11 @@
     <row r="28" ht="15" customHeight="1">
       <c r="B28" s="12" t="inlineStr">
         <is>
-          <t>Senior loan LTV</t>
-        </is>
-      </c>
-      <c r="C28" s="18">
-        <f>'Assumptions'!C107</f>
+          <t>Acquisition basis (income value)</t>
+        </is>
+      </c>
+      <c r="C28" s="23">
+        <f>'Assumptions'!C99</f>
         <v/>
       </c>
       <c r="D28" s="22" t="inlineStr">
@@ -2763,16 +2765,15 @@
     <row r="29" ht="15" customHeight="1">
       <c r="B29" s="12" t="inlineStr">
         <is>
-          <t>Senior loan rate</t>
-        </is>
-      </c>
-      <c r="C29" s="24">
-        <f>'Assumptions'!C108</f>
-        <v/>
+          <t>Closing &amp; acq costs (% price)</t>
+        </is>
+      </c>
+      <c r="C29" s="84" t="n">
+        <v>0.02</v>
       </c>
       <c r="D29" s="22" t="inlineStr">
         <is>
-          <t>🟢 Assumptions</t>
+          <t>🔶</t>
         </is>
       </c>
       <c r="E29" s="13" t="n"/>
@@ -2788,15 +2789,16 @@
     <row r="30" ht="15" customHeight="1">
       <c r="B30" s="12" t="inlineStr">
         <is>
-          <t>Amortization (yrs)</t>
-        </is>
-      </c>
-      <c r="C30" s="86" t="n">
-        <v>30</v>
+          <t>Senior loan LTV</t>
+        </is>
+      </c>
+      <c r="C30" s="18">
+        <f>'Assumptions'!C107</f>
+        <v/>
       </c>
       <c r="D30" s="22" t="inlineStr">
         <is>
-          <t>🔶</t>
+          <t>🟢 Assumptions</t>
         </is>
       </c>
       <c r="E30" s="13" t="n"/>
@@ -2812,11 +2814,11 @@
     <row r="31" ht="15" customHeight="1">
       <c r="B31" s="12" t="inlineStr">
         <is>
-          <t>Going-in cap</t>
+          <t>Senior loan rate</t>
         </is>
       </c>
       <c r="C31" s="24">
-        <f>'Assumptions'!C105</f>
+        <f>'Assumptions'!C108</f>
         <v/>
       </c>
       <c r="D31" s="22" t="inlineStr">
@@ -2837,16 +2839,15 @@
     <row r="32" ht="15" customHeight="1">
       <c r="B32" s="12" t="inlineStr">
         <is>
-          <t>Exit cap</t>
-        </is>
-      </c>
-      <c r="C32" s="24">
-        <f>'Assumptions'!C106</f>
-        <v/>
+          <t>Amortization (yrs)</t>
+        </is>
+      </c>
+      <c r="C32" s="86" t="n">
+        <v>30</v>
       </c>
       <c r="D32" s="22" t="inlineStr">
         <is>
-          <t>🟢 Assumptions</t>
+          <t>🔶</t>
         </is>
       </c>
       <c r="E32" s="13" t="n"/>
@@ -2862,15 +2863,16 @@
     <row r="33" ht="15" customHeight="1">
       <c r="B33" s="12" t="inlineStr">
         <is>
-          <t>Cost of sale</t>
-        </is>
-      </c>
-      <c r="C33" s="84" t="n">
-        <v>0.02</v>
+          <t>Going-in cap</t>
+        </is>
+      </c>
+      <c r="C33" s="24">
+        <f>'Assumptions'!C105</f>
+        <v/>
       </c>
       <c r="D33" s="22" t="inlineStr">
         <is>
-          <t>🔶</t>
+          <t>🟢 Assumptions</t>
         </is>
       </c>
       <c r="E33" s="13" t="n"/>
@@ -2886,15 +2888,16 @@
     <row r="34" ht="15" customHeight="1">
       <c r="B34" s="12" t="inlineStr">
         <is>
-          <t>Hold period (yrs)</t>
-        </is>
-      </c>
-      <c r="C34" s="86" t="n">
-        <v>5</v>
+          <t>Exit cap</t>
+        </is>
+      </c>
+      <c r="C34" s="24">
+        <f>'Assumptions'!C106</f>
+        <v/>
       </c>
       <c r="D34" s="22" t="inlineStr">
         <is>
-          <t>🔶</t>
+          <t>🟢 Assumptions</t>
         </is>
       </c>
       <c r="E34" s="13" t="n"/>
@@ -2910,11 +2913,11 @@
     <row r="35" ht="15" customHeight="1">
       <c r="B35" s="12" t="inlineStr">
         <is>
-          <t>Discount rate (NPV)</t>
+          <t>Cost of sale</t>
         </is>
       </c>
       <c r="C35" s="84" t="n">
-        <v>0.1</v>
+        <v>0.02</v>
       </c>
       <c r="D35" s="22" t="inlineStr">
         <is>
@@ -2934,15 +2937,15 @@
     <row r="36" ht="15" customHeight="1">
       <c r="B36" s="12" t="inlineStr">
         <is>
-          <t>Sale comp ($/SF)</t>
-        </is>
-      </c>
-      <c r="C36" s="78" t="n">
-        <v>300</v>
+          <t>Hold period (yrs)</t>
+        </is>
+      </c>
+      <c r="C36" s="86" t="n">
+        <v>5</v>
       </c>
       <c r="D36" s="22" t="inlineStr">
         <is>
-          <t>⚠️ historical ~$300/SF</t>
+          <t>🔶</t>
         </is>
       </c>
       <c r="E36" s="13" t="n"/>
@@ -2955,1448 +2958,1490 @@
       <c r="L36" s="13" t="n"/>
       <c r="M36" s="14" t="n"/>
     </row>
-    <row r="37"/>
-    <row r="38">
-      <c r="B38" s="11" t="inlineStr">
+    <row r="37" ht="15" customHeight="1">
+      <c r="B37" s="12" t="inlineStr">
+        <is>
+          <t>Discount rate (NPV)</t>
+        </is>
+      </c>
+      <c r="C37" s="84" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D37" s="22" t="inlineStr">
+        <is>
+          <t>🔶</t>
+        </is>
+      </c>
+      <c r="E37" s="13" t="n"/>
+      <c r="F37" s="13" t="n"/>
+      <c r="G37" s="13" t="n"/>
+      <c r="H37" s="13" t="n"/>
+      <c r="I37" s="13" t="n"/>
+      <c r="J37" s="13" t="n"/>
+      <c r="K37" s="13" t="n"/>
+      <c r="L37" s="13" t="n"/>
+      <c r="M37" s="14" t="n"/>
+    </row>
+    <row r="38" ht="15" customHeight="1">
+      <c r="B38" s="12" t="inlineStr">
+        <is>
+          <t>Sale comp ($/SF)</t>
+        </is>
+      </c>
+      <c r="C38" s="78" t="n">
+        <v>300</v>
+      </c>
+      <c r="D38" s="22" t="inlineStr">
+        <is>
+          <t>⚠️ historical ~$300/SF</t>
+        </is>
+      </c>
+      <c r="E38" s="13" t="n"/>
+      <c r="F38" s="13" t="n"/>
+      <c r="G38" s="13" t="n"/>
+      <c r="H38" s="13" t="n"/>
+      <c r="I38" s="13" t="n"/>
+      <c r="J38" s="13" t="n"/>
+      <c r="K38" s="13" t="n"/>
+      <c r="L38" s="13" t="n"/>
+      <c r="M38" s="14" t="n"/>
+    </row>
+    <row r="39"/>
+    <row r="40">
+      <c r="B40" s="11" t="inlineStr">
         <is>
           <t>DERIVED VALUES  &amp;  DEBT SIZING</t>
         </is>
       </c>
-      <c r="C38" s="2" t="n"/>
-      <c r="D38" s="2" t="n"/>
-      <c r="E38" s="2" t="n"/>
-      <c r="F38" s="2" t="n"/>
-      <c r="G38" s="2" t="n"/>
-      <c r="H38" s="2" t="n"/>
-      <c r="I38" s="2" t="n"/>
-      <c r="J38" s="2" t="n"/>
-      <c r="K38" s="2" t="n"/>
-      <c r="L38" s="2" t="n"/>
-      <c r="M38" s="3" t="n"/>
-    </row>
-    <row r="39" ht="15" customHeight="1">
-      <c r="B39" s="12" t="inlineStr">
-        <is>
-          <t>Senior loan amount</t>
-        </is>
-      </c>
-      <c r="C39" s="51">
-        <f>C26*C28</f>
-        <v/>
-      </c>
-      <c r="D39" s="22" t="inlineStr">
-        <is>
-          <t>price × LTV</t>
-        </is>
-      </c>
-      <c r="E39" s="13" t="n"/>
-      <c r="F39" s="13" t="n"/>
-      <c r="G39" s="13" t="n"/>
-      <c r="H39" s="13" t="n"/>
-      <c r="I39" s="13" t="n"/>
-      <c r="J39" s="13" t="n"/>
-      <c r="K39" s="13" t="n"/>
-      <c r="L39" s="13" t="n"/>
-      <c r="M39" s="14" t="n"/>
-    </row>
-    <row r="40" ht="15" customHeight="1">
-      <c r="B40" s="12" t="inlineStr">
-        <is>
-          <t>Monthly rate</t>
-        </is>
-      </c>
-      <c r="C40" s="50">
-        <f>C29/12</f>
-        <v/>
-      </c>
+      <c r="C40" s="2" t="n"/>
+      <c r="D40" s="2" t="n"/>
+      <c r="E40" s="2" t="n"/>
+      <c r="F40" s="2" t="n"/>
+      <c r="G40" s="2" t="n"/>
+      <c r="H40" s="2" t="n"/>
+      <c r="I40" s="2" t="n"/>
+      <c r="J40" s="2" t="n"/>
+      <c r="K40" s="2" t="n"/>
+      <c r="L40" s="2" t="n"/>
+      <c r="M40" s="3" t="n"/>
     </row>
     <row r="41" ht="15" customHeight="1">
       <c r="B41" s="12" t="inlineStr">
         <is>
-          <t>Annual debt service</t>
+          <t>Senior loan amount</t>
         </is>
       </c>
       <c r="C41" s="51">
-        <f>C39*(C40/(1-(1+C40)^(-C30*12)))*12</f>
-        <v/>
-      </c>
+        <f>C28*C30</f>
+        <v/>
+      </c>
+      <c r="D41" s="22" t="inlineStr">
+        <is>
+          <t>price × LTV</t>
+        </is>
+      </c>
+      <c r="E41" s="13" t="n"/>
+      <c r="F41" s="13" t="n"/>
+      <c r="G41" s="13" t="n"/>
+      <c r="H41" s="13" t="n"/>
+      <c r="I41" s="13" t="n"/>
+      <c r="J41" s="13" t="n"/>
+      <c r="K41" s="13" t="n"/>
+      <c r="L41" s="13" t="n"/>
+      <c r="M41" s="14" t="n"/>
     </row>
     <row r="42" ht="15" customHeight="1">
       <c r="B42" s="12" t="inlineStr">
         <is>
-          <t>Equity at acquisition</t>
-        </is>
-      </c>
-      <c r="C42" s="51">
-        <f>C26*(1+C27)-C39</f>
+          <t>Monthly rate</t>
+        </is>
+      </c>
+      <c r="C42" s="50">
+        <f>C31/12</f>
         <v/>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1">
       <c r="B43" s="12" t="inlineStr">
         <is>
-          <t>Total cost basis</t>
+          <t>Annual debt service</t>
         </is>
       </c>
       <c r="C43" s="51">
-        <f>C26*(1+C27)</f>
+        <f>C41*(C42/(1-(1+C42)^(-C32*12)))*12</f>
         <v/>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1">
       <c r="B44" s="12" t="inlineStr">
         <is>
+          <t>Equity at acquisition</t>
+        </is>
+      </c>
+      <c r="C44" s="51">
+        <f>C28*(1+C29)-C41</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45" ht="15" customHeight="1">
+      <c r="B45" s="12" t="inlineStr">
+        <is>
+          <t>Total cost basis</t>
+        </is>
+      </c>
+      <c r="C45" s="51">
+        <f>C28*(1+C29)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46" ht="15" customHeight="1">
+      <c r="B46" s="12" t="inlineStr">
+        <is>
           <t>Total equity required</t>
         </is>
       </c>
-      <c r="C44" s="51">
-        <f>C43-C39</f>
-        <v/>
-      </c>
-    </row>
-    <row r="45"/>
-    <row r="46">
-      <c r="B46" s="11" t="inlineStr">
+      <c r="C46" s="51">
+        <f>C45-C41</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47"/>
+    <row r="48">
+      <c r="B48" s="11" t="inlineStr">
         <is>
           <t>OPERATING CASH FLOW  —  10-year annual (Modified Gross)</t>
         </is>
       </c>
-      <c r="C46" s="2" t="n"/>
-      <c r="D46" s="2" t="n"/>
-      <c r="E46" s="2" t="n"/>
-      <c r="F46" s="2" t="n"/>
-      <c r="G46" s="2" t="n"/>
-      <c r="H46" s="2" t="n"/>
-      <c r="I46" s="2" t="n"/>
-      <c r="J46" s="2" t="n"/>
-      <c r="K46" s="2" t="n"/>
-      <c r="L46" s="2" t="n"/>
-      <c r="M46" s="3" t="n"/>
-    </row>
-    <row r="47" ht="15" customHeight="1">
-      <c r="B47" s="15" t="inlineStr">
+      <c r="C48" s="2" t="n"/>
+      <c r="D48" s="2" t="n"/>
+      <c r="E48" s="2" t="n"/>
+      <c r="F48" s="2" t="n"/>
+      <c r="G48" s="2" t="n"/>
+      <c r="H48" s="2" t="n"/>
+      <c r="I48" s="2" t="n"/>
+      <c r="J48" s="2" t="n"/>
+      <c r="K48" s="2" t="n"/>
+      <c r="L48" s="2" t="n"/>
+      <c r="M48" s="3" t="n"/>
+    </row>
+    <row r="49" ht="15" customHeight="1">
+      <c r="B49" s="15" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="C47" s="16" t="inlineStr">
+      <c r="C49" s="16" t="inlineStr">
         <is>
           <t>0 / Acq</t>
         </is>
       </c>
-      <c r="D47" s="41" t="n">
+      <c r="D49" s="41" t="n">
         <v>1</v>
       </c>
-      <c r="E47" s="41" t="n">
+      <c r="E49" s="41" t="n">
         <v>2</v>
       </c>
-      <c r="F47" s="41" t="n">
+      <c r="F49" s="41" t="n">
         <v>3</v>
       </c>
-      <c r="G47" s="41" t="n">
+      <c r="G49" s="41" t="n">
         <v>4</v>
       </c>
-      <c r="H47" s="41" t="n">
+      <c r="H49" s="41" t="n">
         <v>5</v>
       </c>
-      <c r="I47" s="41" t="n">
+      <c r="I49" s="41" t="n">
         <v>6</v>
       </c>
-      <c r="J47" s="41" t="n">
+      <c r="J49" s="41" t="n">
         <v>7</v>
       </c>
-      <c r="K47" s="41" t="n">
+      <c r="K49" s="41" t="n">
         <v>8</v>
       </c>
-      <c r="L47" s="41" t="n">
+      <c r="L49" s="41" t="n">
         <v>9</v>
       </c>
-      <c r="M47" s="41" t="n">
+      <c r="M49" s="41" t="n">
         <v>10</v>
       </c>
     </row>
-    <row r="48" ht="15" customHeight="1">
-      <c r="B48" s="22" t="inlineStr">
+    <row r="50" ht="15" customHeight="1">
+      <c r="B50" s="22" t="inlineStr">
         <is>
           <t>Year ending</t>
         </is>
       </c>
-      <c r="C48" s="42" t="inlineStr">
+      <c r="C50" s="42" t="inlineStr">
         <is>
           <t>At close</t>
         </is>
       </c>
-      <c r="D48" s="42" t="inlineStr">
+      <c r="D50" s="42" t="inlineStr">
         <is>
           <t>Dec-2027</t>
         </is>
       </c>
-      <c r="E48" s="42" t="inlineStr">
+      <c r="E50" s="42" t="inlineStr">
         <is>
           <t>Dec-2028</t>
         </is>
       </c>
-      <c r="F48" s="42" t="inlineStr">
+      <c r="F50" s="42" t="inlineStr">
         <is>
           <t>Dec-2029</t>
         </is>
       </c>
-      <c r="G48" s="42" t="inlineStr">
+      <c r="G50" s="42" t="inlineStr">
         <is>
           <t>Dec-2030</t>
         </is>
       </c>
-      <c r="H48" s="42" t="inlineStr">
+      <c r="H50" s="42" t="inlineStr">
         <is>
           <t>Dec-2031</t>
         </is>
       </c>
-      <c r="I48" s="42" t="inlineStr">
+      <c r="I50" s="42" t="inlineStr">
         <is>
           <t>Dec-2032</t>
         </is>
       </c>
-      <c r="J48" s="42" t="inlineStr">
+      <c r="J50" s="42" t="inlineStr">
         <is>
           <t>Dec-2033</t>
         </is>
       </c>
-      <c r="K48" s="42" t="inlineStr">
+      <c r="K50" s="42" t="inlineStr">
         <is>
           <t>Dec-2034</t>
         </is>
       </c>
-      <c r="L48" s="42" t="inlineStr">
+      <c r="L50" s="42" t="inlineStr">
         <is>
           <t>Dec-2035</t>
         </is>
       </c>
-      <c r="M48" s="42" t="inlineStr">
+      <c r="M50" s="42" t="inlineStr">
         <is>
           <t>Dec-2036</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="15" customHeight="1">
-      <c r="B49" s="12" t="inlineStr">
+    <row r="51" ht="15" customHeight="1">
+      <c r="B51" s="12" t="inlineStr">
         <is>
           <t>Occupancy</t>
         </is>
       </c>
-      <c r="D49" s="53">
-        <f>(C16+C17)/2</f>
-        <v/>
-      </c>
-      <c r="E49" s="53">
-        <f>C17</f>
-        <v/>
-      </c>
-      <c r="F49" s="53">
-        <f>C17</f>
-        <v/>
-      </c>
-      <c r="G49" s="53">
-        <f>C17</f>
-        <v/>
-      </c>
-      <c r="H49" s="53">
-        <f>C17</f>
-        <v/>
-      </c>
-      <c r="I49" s="53">
-        <f>C17</f>
-        <v/>
-      </c>
-      <c r="J49" s="53">
-        <f>C17</f>
-        <v/>
-      </c>
-      <c r="K49" s="53">
-        <f>C17</f>
-        <v/>
-      </c>
-      <c r="L49" s="53">
-        <f>C17</f>
-        <v/>
-      </c>
-      <c r="M49" s="53">
-        <f>C17</f>
-        <v/>
-      </c>
-    </row>
-    <row r="50" ht="15" customHeight="1">
-      <c r="B50" s="12" t="inlineStr">
-        <is>
-          <t>Leased SF</t>
-        </is>
-      </c>
-      <c r="D50" s="64">
-        <f>C15*D49</f>
-        <v/>
-      </c>
-      <c r="E50" s="64">
-        <f>C15*E49</f>
-        <v/>
-      </c>
-      <c r="F50" s="64">
-        <f>C15*F49</f>
-        <v/>
-      </c>
-      <c r="G50" s="64">
-        <f>C15*G49</f>
-        <v/>
-      </c>
-      <c r="H50" s="64">
-        <f>C15*H49</f>
-        <v/>
-      </c>
-      <c r="I50" s="64">
-        <f>C15*I49</f>
-        <v/>
-      </c>
-      <c r="J50" s="64">
-        <f>C15*J49</f>
-        <v/>
-      </c>
-      <c r="K50" s="64">
-        <f>C15*K49</f>
-        <v/>
-      </c>
-      <c r="L50" s="64">
-        <f>C15*L49</f>
-        <v/>
-      </c>
-      <c r="M50" s="64">
-        <f>C15*M49</f>
-        <v/>
-      </c>
-    </row>
-    <row r="51" ht="15" customHeight="1">
-      <c r="B51" s="52" t="inlineStr">
-        <is>
-          <t>Gross rental income (MG)</t>
-        </is>
-      </c>
-      <c r="D51" s="51">
-        <f>D50*C18*(1+C19)^(1-1)</f>
-        <v/>
-      </c>
-      <c r="E51" s="47">
-        <f>E50*C18*(1+C19)^(2-1)</f>
-        <v/>
-      </c>
-      <c r="F51" s="47">
-        <f>F50*C18*(1+C19)^(3-1)</f>
-        <v/>
-      </c>
-      <c r="G51" s="47">
-        <f>G50*C18*(1+C19)^(4-1)</f>
-        <v/>
-      </c>
-      <c r="H51" s="47">
-        <f>H50*C18*(1+C19)^(5-1)</f>
-        <v/>
-      </c>
-      <c r="I51" s="47">
-        <f>I50*C18*(1+C19)^(6-1)</f>
-        <v/>
-      </c>
-      <c r="J51" s="47">
-        <f>J50*C18*(1+C19)^(7-1)</f>
-        <v/>
-      </c>
-      <c r="K51" s="47">
-        <f>K50*C18*(1+C19)^(8-1)</f>
-        <v/>
-      </c>
-      <c r="L51" s="47">
-        <f>L50*C18*(1+C19)^(9-1)</f>
-        <v/>
-      </c>
-      <c r="M51" s="47">
-        <f>M50*C18*(1+C19)^(10-1)</f>
+      <c r="D51" s="53">
+        <f>(C18+C19)/2</f>
+        <v/>
+      </c>
+      <c r="E51" s="53">
+        <f>C19</f>
+        <v/>
+      </c>
+      <c r="F51" s="53">
+        <f>C19</f>
+        <v/>
+      </c>
+      <c r="G51" s="53">
+        <f>C19</f>
+        <v/>
+      </c>
+      <c r="H51" s="53">
+        <f>C19</f>
+        <v/>
+      </c>
+      <c r="I51" s="53">
+        <f>C19</f>
+        <v/>
+      </c>
+      <c r="J51" s="53">
+        <f>C19</f>
+        <v/>
+      </c>
+      <c r="K51" s="53">
+        <f>C19</f>
+        <v/>
+      </c>
+      <c r="L51" s="53">
+        <f>C19</f>
+        <v/>
+      </c>
+      <c r="M51" s="53">
+        <f>C19</f>
         <v/>
       </c>
     </row>
     <row r="52" ht="15" customHeight="1">
       <c r="B52" s="12" t="inlineStr">
         <is>
+          <t>Leased SF</t>
+        </is>
+      </c>
+      <c r="D52" s="64">
+        <f>C17*D51</f>
+        <v/>
+      </c>
+      <c r="E52" s="64">
+        <f>C17*E51</f>
+        <v/>
+      </c>
+      <c r="F52" s="64">
+        <f>C17*F51</f>
+        <v/>
+      </c>
+      <c r="G52" s="64">
+        <f>C17*G51</f>
+        <v/>
+      </c>
+      <c r="H52" s="64">
+        <f>C17*H51</f>
+        <v/>
+      </c>
+      <c r="I52" s="64">
+        <f>C17*I51</f>
+        <v/>
+      </c>
+      <c r="J52" s="64">
+        <f>C17*J51</f>
+        <v/>
+      </c>
+      <c r="K52" s="64">
+        <f>C17*K51</f>
+        <v/>
+      </c>
+      <c r="L52" s="64">
+        <f>C17*L51</f>
+        <v/>
+      </c>
+      <c r="M52" s="64">
+        <f>C17*M51</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53" ht="15" customHeight="1">
+      <c r="B53" s="52" t="inlineStr">
+        <is>
+          <t>Gross rental income (MG)</t>
+        </is>
+      </c>
+      <c r="D53" s="51">
+        <f>D52*C20*(1+C21)^(1-1)</f>
+        <v/>
+      </c>
+      <c r="E53" s="47">
+        <f>E52*C20*(1+C21)^(2-1)</f>
+        <v/>
+      </c>
+      <c r="F53" s="47">
+        <f>F52*C20*(1+C21)^(3-1)</f>
+        <v/>
+      </c>
+      <c r="G53" s="47">
+        <f>G52*C20*(1+C21)^(4-1)</f>
+        <v/>
+      </c>
+      <c r="H53" s="47">
+        <f>H52*C20*(1+C21)^(5-1)</f>
+        <v/>
+      </c>
+      <c r="I53" s="47">
+        <f>I52*C20*(1+C21)^(6-1)</f>
+        <v/>
+      </c>
+      <c r="J53" s="47">
+        <f>J52*C20*(1+C21)^(7-1)</f>
+        <v/>
+      </c>
+      <c r="K53" s="47">
+        <f>K52*C20*(1+C21)^(8-1)</f>
+        <v/>
+      </c>
+      <c r="L53" s="47">
+        <f>L52*C20*(1+C21)^(9-1)</f>
+        <v/>
+      </c>
+      <c r="M53" s="47">
+        <f>M52*C20*(1+C21)^(10-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54" ht="15" customHeight="1">
+      <c r="B54" s="12" t="inlineStr">
+        <is>
           <t>Less: credit &amp; vacancy loss</t>
         </is>
       </c>
-      <c r="D52" s="47">
-        <f>-D51*C20</f>
-        <v/>
-      </c>
-      <c r="E52" s="47">
-        <f>-E51*C20</f>
-        <v/>
-      </c>
-      <c r="F52" s="47">
-        <f>-F51*C20</f>
-        <v/>
-      </c>
-      <c r="G52" s="47">
-        <f>-G51*C20</f>
-        <v/>
-      </c>
-      <c r="H52" s="47">
-        <f>-H51*C20</f>
-        <v/>
-      </c>
-      <c r="I52" s="47">
-        <f>-I51*C20</f>
-        <v/>
-      </c>
-      <c r="J52" s="47">
-        <f>-J51*C20</f>
-        <v/>
-      </c>
-      <c r="K52" s="47">
-        <f>-K51*C20</f>
-        <v/>
-      </c>
-      <c r="L52" s="47">
-        <f>-L51*C20</f>
-        <v/>
-      </c>
-      <c r="M52" s="47">
-        <f>-M51*C20</f>
-        <v/>
-      </c>
-    </row>
-    <row r="53" ht="15" customHeight="1">
-      <c r="B53" s="43" t="inlineStr">
+      <c r="D54" s="47">
+        <f>-D53*C22</f>
+        <v/>
+      </c>
+      <c r="E54" s="47">
+        <f>-E53*C22</f>
+        <v/>
+      </c>
+      <c r="F54" s="47">
+        <f>-F53*C22</f>
+        <v/>
+      </c>
+      <c r="G54" s="47">
+        <f>-G53*C22</f>
+        <v/>
+      </c>
+      <c r="H54" s="47">
+        <f>-H53*C22</f>
+        <v/>
+      </c>
+      <c r="I54" s="47">
+        <f>-I53*C22</f>
+        <v/>
+      </c>
+      <c r="J54" s="47">
+        <f>-J53*C22</f>
+        <v/>
+      </c>
+      <c r="K54" s="47">
+        <f>-K53*C22</f>
+        <v/>
+      </c>
+      <c r="L54" s="47">
+        <f>-L53*C22</f>
+        <v/>
+      </c>
+      <c r="M54" s="47">
+        <f>-M53*C22</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55" ht="15" customHeight="1">
+      <c r="B55" s="43" t="inlineStr">
         <is>
           <t>Effective Gross Revenue</t>
         </is>
       </c>
-      <c r="D53" s="51">
-        <f>D51+D52</f>
-        <v/>
-      </c>
-      <c r="E53" s="47">
-        <f>E51+E52</f>
-        <v/>
-      </c>
-      <c r="F53" s="47">
-        <f>F51+F52</f>
-        <v/>
-      </c>
-      <c r="G53" s="47">
-        <f>G51+G52</f>
-        <v/>
-      </c>
-      <c r="H53" s="47">
-        <f>H51+H52</f>
-        <v/>
-      </c>
-      <c r="I53" s="47">
-        <f>I51+I52</f>
-        <v/>
-      </c>
-      <c r="J53" s="47">
-        <f>J51+J52</f>
-        <v/>
-      </c>
-      <c r="K53" s="47">
-        <f>K51+K52</f>
-        <v/>
-      </c>
-      <c r="L53" s="47">
-        <f>L51+L52</f>
-        <v/>
-      </c>
-      <c r="M53" s="47">
-        <f>M51+M52</f>
-        <v/>
-      </c>
-    </row>
-    <row r="54" ht="15" customHeight="1">
-      <c r="B54" s="15" t="inlineStr">
+      <c r="D55" s="51">
+        <f>D53+D54</f>
+        <v/>
+      </c>
+      <c r="E55" s="47">
+        <f>E53+E54</f>
+        <v/>
+      </c>
+      <c r="F55" s="47">
+        <f>F53+F54</f>
+        <v/>
+      </c>
+      <c r="G55" s="47">
+        <f>G53+G54</f>
+        <v/>
+      </c>
+      <c r="H55" s="47">
+        <f>H53+H54</f>
+        <v/>
+      </c>
+      <c r="I55" s="47">
+        <f>I53+I54</f>
+        <v/>
+      </c>
+      <c r="J55" s="47">
+        <f>J53+J54</f>
+        <v/>
+      </c>
+      <c r="K55" s="47">
+        <f>K53+K54</f>
+        <v/>
+      </c>
+      <c r="L55" s="47">
+        <f>L53+L54</f>
+        <v/>
+      </c>
+      <c r="M55" s="47">
+        <f>M53+M54</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56" ht="15" customHeight="1">
+      <c r="B56" s="15" t="inlineStr">
         <is>
           <t>OPERATING EXPENSES (landlord — Modified Gross)</t>
         </is>
       </c>
-      <c r="C54" s="13" t="n"/>
-      <c r="D54" s="13" t="n"/>
-      <c r="E54" s="13" t="n"/>
-      <c r="F54" s="13" t="n"/>
-      <c r="G54" s="13" t="n"/>
-      <c r="H54" s="13" t="n"/>
-      <c r="I54" s="13" t="n"/>
-      <c r="J54" s="13" t="n"/>
-      <c r="K54" s="13" t="n"/>
-      <c r="L54" s="13" t="n"/>
-      <c r="M54" s="14" t="n"/>
-    </row>
-    <row r="55" ht="15" customHeight="1">
-      <c r="B55" s="12" t="inlineStr">
-        <is>
-          <t>Real-estate taxes</t>
-        </is>
-      </c>
-      <c r="D55" s="47">
-        <f>C26*C21*(1+C24)^(1-1)</f>
-        <v/>
-      </c>
-      <c r="E55" s="47">
-        <f>C26*C21*(1+C24)^(2-1)</f>
-        <v/>
-      </c>
-      <c r="F55" s="47">
-        <f>C26*C21*(1+C24)^(3-1)</f>
-        <v/>
-      </c>
-      <c r="G55" s="47">
-        <f>C26*C21*(1+C24)^(4-1)</f>
-        <v/>
-      </c>
-      <c r="H55" s="47">
-        <f>C26*C21*(1+C24)^(5-1)</f>
-        <v/>
-      </c>
-      <c r="I55" s="47">
-        <f>C26*C21*(1+C24)^(6-1)</f>
-        <v/>
-      </c>
-      <c r="J55" s="47">
-        <f>C26*C21*(1+C24)^(7-1)</f>
-        <v/>
-      </c>
-      <c r="K55" s="47">
-        <f>C26*C21*(1+C24)^(8-1)</f>
-        <v/>
-      </c>
-      <c r="L55" s="47">
-        <f>C26*C21*(1+C24)^(9-1)</f>
-        <v/>
-      </c>
-      <c r="M55" s="47">
-        <f>C26*C21*(1+C24)^(10-1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="56" ht="15" customHeight="1">
-      <c r="B56" s="12" t="inlineStr">
-        <is>
-          <t>Office opex (utilities, R&amp;M, ins, CAM)</t>
-        </is>
-      </c>
-      <c r="D56" s="47">
-        <f>C15*C22*(1+C24)^(1-1)</f>
-        <v/>
-      </c>
-      <c r="E56" s="47">
-        <f>C15*C22*(1+C24)^(2-1)</f>
-        <v/>
-      </c>
-      <c r="F56" s="47">
-        <f>C15*C22*(1+C24)^(3-1)</f>
-        <v/>
-      </c>
-      <c r="G56" s="47">
-        <f>C15*C22*(1+C24)^(4-1)</f>
-        <v/>
-      </c>
-      <c r="H56" s="47">
-        <f>C15*C22*(1+C24)^(5-1)</f>
-        <v/>
-      </c>
-      <c r="I56" s="47">
-        <f>C15*C22*(1+C24)^(6-1)</f>
-        <v/>
-      </c>
-      <c r="J56" s="47">
-        <f>C15*C22*(1+C24)^(7-1)</f>
-        <v/>
-      </c>
-      <c r="K56" s="47">
-        <f>C15*C22*(1+C24)^(8-1)</f>
-        <v/>
-      </c>
-      <c r="L56" s="47">
-        <f>C15*C22*(1+C24)^(9-1)</f>
-        <v/>
-      </c>
-      <c r="M56" s="47">
-        <f>C15*C22*(1+C24)^(10-1)</f>
-        <v/>
-      </c>
+      <c r="C56" s="13" t="n"/>
+      <c r="D56" s="13" t="n"/>
+      <c r="E56" s="13" t="n"/>
+      <c r="F56" s="13" t="n"/>
+      <c r="G56" s="13" t="n"/>
+      <c r="H56" s="13" t="n"/>
+      <c r="I56" s="13" t="n"/>
+      <c r="J56" s="13" t="n"/>
+      <c r="K56" s="13" t="n"/>
+      <c r="L56" s="13" t="n"/>
+      <c r="M56" s="14" t="n"/>
     </row>
     <row r="57" ht="15" customHeight="1">
       <c r="B57" s="12" t="inlineStr">
         <is>
+          <t>Real-estate taxes</t>
+        </is>
+      </c>
+      <c r="D57" s="47">
+        <f>C28*C23*(1+C26)^(1-1)</f>
+        <v/>
+      </c>
+      <c r="E57" s="47">
+        <f>C28*C23*(1+C26)^(2-1)</f>
+        <v/>
+      </c>
+      <c r="F57" s="47">
+        <f>C28*C23*(1+C26)^(3-1)</f>
+        <v/>
+      </c>
+      <c r="G57" s="47">
+        <f>C28*C23*(1+C26)^(4-1)</f>
+        <v/>
+      </c>
+      <c r="H57" s="47">
+        <f>C28*C23*(1+C26)^(5-1)</f>
+        <v/>
+      </c>
+      <c r="I57" s="47">
+        <f>C28*C23*(1+C26)^(6-1)</f>
+        <v/>
+      </c>
+      <c r="J57" s="47">
+        <f>C28*C23*(1+C26)^(7-1)</f>
+        <v/>
+      </c>
+      <c r="K57" s="47">
+        <f>C28*C23*(1+C26)^(8-1)</f>
+        <v/>
+      </c>
+      <c r="L57" s="47">
+        <f>C28*C23*(1+C26)^(9-1)</f>
+        <v/>
+      </c>
+      <c r="M57" s="47">
+        <f>C28*C23*(1+C26)^(10-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58" ht="15" customHeight="1">
+      <c r="B58" s="12" t="inlineStr">
+        <is>
+          <t>Office opex (utilities, R&amp;M, ins, CAM)</t>
+        </is>
+      </c>
+      <c r="D58" s="47">
+        <f>C17*C24*(1+C26)^(1-1)</f>
+        <v/>
+      </c>
+      <c r="E58" s="47">
+        <f>C17*C24*(1+C26)^(2-1)</f>
+        <v/>
+      </c>
+      <c r="F58" s="47">
+        <f>C17*C24*(1+C26)^(3-1)</f>
+        <v/>
+      </c>
+      <c r="G58" s="47">
+        <f>C17*C24*(1+C26)^(4-1)</f>
+        <v/>
+      </c>
+      <c r="H58" s="47">
+        <f>C17*C24*(1+C26)^(5-1)</f>
+        <v/>
+      </c>
+      <c r="I58" s="47">
+        <f>C17*C24*(1+C26)^(6-1)</f>
+        <v/>
+      </c>
+      <c r="J58" s="47">
+        <f>C17*C24*(1+C26)^(7-1)</f>
+        <v/>
+      </c>
+      <c r="K58" s="47">
+        <f>C17*C24*(1+C26)^(8-1)</f>
+        <v/>
+      </c>
+      <c r="L58" s="47">
+        <f>C17*C24*(1+C26)^(9-1)</f>
+        <v/>
+      </c>
+      <c r="M58" s="47">
+        <f>C17*C24*(1+C26)^(10-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59" ht="15" customHeight="1">
+      <c r="B59" s="12" t="inlineStr">
+        <is>
           <t>Management fee</t>
         </is>
       </c>
-      <c r="D57" s="47">
-        <f>D53*C23</f>
-        <v/>
-      </c>
-      <c r="E57" s="47">
-        <f>E53*C23</f>
-        <v/>
-      </c>
-      <c r="F57" s="47">
-        <f>F53*C23</f>
-        <v/>
-      </c>
-      <c r="G57" s="47">
-        <f>G53*C23</f>
-        <v/>
-      </c>
-      <c r="H57" s="47">
-        <f>H53*C23</f>
-        <v/>
-      </c>
-      <c r="I57" s="47">
-        <f>I53*C23</f>
-        <v/>
-      </c>
-      <c r="J57" s="47">
-        <f>J53*C23</f>
-        <v/>
-      </c>
-      <c r="K57" s="47">
-        <f>K53*C23</f>
-        <v/>
-      </c>
-      <c r="L57" s="47">
-        <f>L53*C23</f>
-        <v/>
-      </c>
-      <c r="M57" s="47">
-        <f>M53*C23</f>
-        <v/>
-      </c>
-    </row>
-    <row r="58" ht="15" customHeight="1">
-      <c r="B58" s="43" t="inlineStr">
+      <c r="D59" s="47">
+        <f>D55*C25</f>
+        <v/>
+      </c>
+      <c r="E59" s="47">
+        <f>E55*C25</f>
+        <v/>
+      </c>
+      <c r="F59" s="47">
+        <f>F55*C25</f>
+        <v/>
+      </c>
+      <c r="G59" s="47">
+        <f>G55*C25</f>
+        <v/>
+      </c>
+      <c r="H59" s="47">
+        <f>H55*C25</f>
+        <v/>
+      </c>
+      <c r="I59" s="47">
+        <f>I55*C25</f>
+        <v/>
+      </c>
+      <c r="J59" s="47">
+        <f>J55*C25</f>
+        <v/>
+      </c>
+      <c r="K59" s="47">
+        <f>K55*C25</f>
+        <v/>
+      </c>
+      <c r="L59" s="47">
+        <f>L55*C25</f>
+        <v/>
+      </c>
+      <c r="M59" s="47">
+        <f>M55*C25</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60" ht="15" customHeight="1">
+      <c r="B60" s="43" t="inlineStr">
         <is>
           <t>Total operating expenses</t>
         </is>
       </c>
-      <c r="D58" s="51">
-        <f>SUM(D55:D57)</f>
-        <v/>
-      </c>
-      <c r="E58" s="47">
-        <f>SUM(E55:E57)</f>
-        <v/>
-      </c>
-      <c r="F58" s="47">
-        <f>SUM(F55:F57)</f>
-        <v/>
-      </c>
-      <c r="G58" s="47">
-        <f>SUM(G55:G57)</f>
-        <v/>
-      </c>
-      <c r="H58" s="47">
-        <f>SUM(H55:H57)</f>
-        <v/>
-      </c>
-      <c r="I58" s="47">
-        <f>SUM(I55:I57)</f>
-        <v/>
-      </c>
-      <c r="J58" s="47">
-        <f>SUM(J55:J57)</f>
-        <v/>
-      </c>
-      <c r="K58" s="47">
-        <f>SUM(K55:K57)</f>
-        <v/>
-      </c>
-      <c r="L58" s="47">
-        <f>SUM(L55:L57)</f>
-        <v/>
-      </c>
-      <c r="M58" s="47">
-        <f>SUM(M55:M57)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="59" ht="15" customHeight="1">
-      <c r="B59" s="43" t="inlineStr">
-        <is>
-          <t>NET OPERATING INCOME</t>
-        </is>
-      </c>
-      <c r="D59" s="44">
-        <f>D53-D58</f>
-        <v/>
-      </c>
-      <c r="E59" s="45">
-        <f>E53-E58</f>
-        <v/>
-      </c>
-      <c r="F59" s="45">
-        <f>F53-F58</f>
-        <v/>
-      </c>
-      <c r="G59" s="45">
-        <f>G53-G58</f>
-        <v/>
-      </c>
-      <c r="H59" s="45">
-        <f>H53-H58</f>
-        <v/>
-      </c>
-      <c r="I59" s="45">
-        <f>I53-I58</f>
-        <v/>
-      </c>
-      <c r="J59" s="45">
-        <f>J53-J58</f>
-        <v/>
-      </c>
-      <c r="K59" s="45">
-        <f>K53-K58</f>
-        <v/>
-      </c>
-      <c r="L59" s="45">
-        <f>L53-L58</f>
-        <v/>
-      </c>
-      <c r="M59" s="45">
-        <f>M53-M58</f>
-        <v/>
-      </c>
-    </row>
-    <row r="60" ht="15" customHeight="1">
-      <c r="B60" s="12" t="inlineStr">
-        <is>
-          <t>Replacement reserves</t>
-        </is>
-      </c>
-      <c r="D60" s="47">
-        <f>C15*C25*(1+C24)^(1-1)</f>
+      <c r="D60" s="51">
+        <f>SUM(D57:D59)</f>
         <v/>
       </c>
       <c r="E60" s="47">
-        <f>C15*C25*(1+C24)^(2-1)</f>
+        <f>SUM(E57:E59)</f>
         <v/>
       </c>
       <c r="F60" s="47">
-        <f>C15*C25*(1+C24)^(3-1)</f>
+        <f>SUM(F57:F59)</f>
         <v/>
       </c>
       <c r="G60" s="47">
-        <f>C15*C25*(1+C24)^(4-1)</f>
+        <f>SUM(G57:G59)</f>
         <v/>
       </c>
       <c r="H60" s="47">
-        <f>C15*C25*(1+C24)^(5-1)</f>
+        <f>SUM(H57:H59)</f>
         <v/>
       </c>
       <c r="I60" s="47">
-        <f>C15*C25*(1+C24)^(6-1)</f>
+        <f>SUM(I57:I59)</f>
         <v/>
       </c>
       <c r="J60" s="47">
-        <f>C15*C25*(1+C24)^(7-1)</f>
+        <f>SUM(J57:J59)</f>
         <v/>
       </c>
       <c r="K60" s="47">
-        <f>C15*C25*(1+C24)^(8-1)</f>
+        <f>SUM(K57:K59)</f>
         <v/>
       </c>
       <c r="L60" s="47">
-        <f>C15*C25*(1+C24)^(9-1)</f>
+        <f>SUM(L57:L59)</f>
         <v/>
       </c>
       <c r="M60" s="47">
-        <f>C15*C25*(1+C24)^(10-1)</f>
+        <f>SUM(M57:M59)</f>
         <v/>
       </c>
     </row>
     <row r="61" ht="15" customHeight="1">
       <c r="B61" s="43" t="inlineStr">
         <is>
+          <t>NET OPERATING INCOME</t>
+        </is>
+      </c>
+      <c r="D61" s="44">
+        <f>D55-D60</f>
+        <v/>
+      </c>
+      <c r="E61" s="45">
+        <f>E55-E60</f>
+        <v/>
+      </c>
+      <c r="F61" s="45">
+        <f>F55-F60</f>
+        <v/>
+      </c>
+      <c r="G61" s="45">
+        <f>G55-G60</f>
+        <v/>
+      </c>
+      <c r="H61" s="45">
+        <f>H55-H60</f>
+        <v/>
+      </c>
+      <c r="I61" s="45">
+        <f>I55-I60</f>
+        <v/>
+      </c>
+      <c r="J61" s="45">
+        <f>J55-J60</f>
+        <v/>
+      </c>
+      <c r="K61" s="45">
+        <f>K55-K60</f>
+        <v/>
+      </c>
+      <c r="L61" s="45">
+        <f>L55-L60</f>
+        <v/>
+      </c>
+      <c r="M61" s="45">
+        <f>M55-M60</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62" ht="15" customHeight="1">
+      <c r="B62" s="12" t="inlineStr">
+        <is>
+          <t>Replacement reserves</t>
+        </is>
+      </c>
+      <c r="D62" s="47">
+        <f>C17*C27*(1+C26)^(1-1)</f>
+        <v/>
+      </c>
+      <c r="E62" s="47">
+        <f>C17*C27*(1+C26)^(2-1)</f>
+        <v/>
+      </c>
+      <c r="F62" s="47">
+        <f>C17*C27*(1+C26)^(3-1)</f>
+        <v/>
+      </c>
+      <c r="G62" s="47">
+        <f>C17*C27*(1+C26)^(4-1)</f>
+        <v/>
+      </c>
+      <c r="H62" s="47">
+        <f>C17*C27*(1+C26)^(5-1)</f>
+        <v/>
+      </c>
+      <c r="I62" s="47">
+        <f>C17*C27*(1+C26)^(6-1)</f>
+        <v/>
+      </c>
+      <c r="J62" s="47">
+        <f>C17*C27*(1+C26)^(7-1)</f>
+        <v/>
+      </c>
+      <c r="K62" s="47">
+        <f>C17*C27*(1+C26)^(8-1)</f>
+        <v/>
+      </c>
+      <c r="L62" s="47">
+        <f>C17*C27*(1+C26)^(9-1)</f>
+        <v/>
+      </c>
+      <c r="M62" s="47">
+        <f>C17*C27*(1+C26)^(10-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63" ht="15" customHeight="1">
+      <c r="B63" s="43" t="inlineStr">
+        <is>
           <t>Unlevered cash flow (before reversion)</t>
         </is>
       </c>
-      <c r="C61" s="44">
-        <f>-C26*(1+C27)</f>
-        <v/>
-      </c>
-      <c r="D61" s="44">
-        <f>D59-D60</f>
-        <v/>
-      </c>
-      <c r="E61" s="45">
-        <f>E59-E60</f>
-        <v/>
-      </c>
-      <c r="F61" s="45">
-        <f>F59-F60</f>
-        <v/>
-      </c>
-      <c r="G61" s="45">
-        <f>G59-G60</f>
-        <v/>
-      </c>
-      <c r="H61" s="45">
-        <f>H59-H60</f>
-        <v/>
-      </c>
-      <c r="I61" s="45">
-        <f>I59-I60</f>
-        <v/>
-      </c>
-      <c r="J61" s="45">
-        <f>J59-J60</f>
-        <v/>
-      </c>
-      <c r="K61" s="45">
-        <f>K59-K60</f>
-        <v/>
-      </c>
-      <c r="L61" s="45">
-        <f>L59-L60</f>
-        <v/>
-      </c>
-      <c r="M61" s="45">
-        <f>M59-M60</f>
-        <v/>
-      </c>
-    </row>
-    <row r="62"/>
-    <row r="63">
-      <c r="B63" s="11" t="inlineStr">
+      <c r="C63" s="44">
+        <f>-C28*(1+C29)</f>
+        <v/>
+      </c>
+      <c r="D63" s="44">
+        <f>D61-D62</f>
+        <v/>
+      </c>
+      <c r="E63" s="45">
+        <f>E61-E62</f>
+        <v/>
+      </c>
+      <c r="F63" s="45">
+        <f>F61-F62</f>
+        <v/>
+      </c>
+      <c r="G63" s="45">
+        <f>G61-G62</f>
+        <v/>
+      </c>
+      <c r="H63" s="45">
+        <f>H61-H62</f>
+        <v/>
+      </c>
+      <c r="I63" s="45">
+        <f>I61-I62</f>
+        <v/>
+      </c>
+      <c r="J63" s="45">
+        <f>J61-J62</f>
+        <v/>
+      </c>
+      <c r="K63" s="45">
+        <f>K61-K62</f>
+        <v/>
+      </c>
+      <c r="L63" s="45">
+        <f>L61-L62</f>
+        <v/>
+      </c>
+      <c r="M63" s="45">
+        <f>M61-M62</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64"/>
+    <row r="65">
+      <c r="B65" s="11" t="inlineStr">
         <is>
           <t>REVERSION, DEBT SERVICE  &amp;  LEVERED CASH FLOW</t>
         </is>
       </c>
-      <c r="C63" s="2" t="n"/>
-      <c r="D63" s="2" t="n"/>
-      <c r="E63" s="2" t="n"/>
-      <c r="F63" s="2" t="n"/>
-      <c r="G63" s="2" t="n"/>
-      <c r="H63" s="2" t="n"/>
-      <c r="I63" s="2" t="n"/>
-      <c r="J63" s="2" t="n"/>
-      <c r="K63" s="2" t="n"/>
-      <c r="L63" s="2" t="n"/>
-      <c r="M63" s="3" t="n"/>
-    </row>
-    <row r="64" ht="15" customHeight="1">
-      <c r="B64" s="12" t="inlineStr">
-        <is>
-          <t>Net sale proceeds (exit year)</t>
-        </is>
-      </c>
-      <c r="D64" s="47">
-        <f>IF(1=C34,(D59*(1+C19)/C32)*(1-C33),0)</f>
-        <v/>
-      </c>
-      <c r="E64" s="47">
-        <f>IF(2=C34,(E59*(1+C19)/C32)*(1-C33),0)</f>
-        <v/>
-      </c>
-      <c r="F64" s="47">
-        <f>IF(3=C34,(F59*(1+C19)/C32)*(1-C33),0)</f>
-        <v/>
-      </c>
-      <c r="G64" s="47">
-        <f>IF(4=C34,(G59*(1+C19)/C32)*(1-C33),0)</f>
-        <v/>
-      </c>
-      <c r="H64" s="47">
-        <f>IF(5=C34,(H59*(1+C19)/C32)*(1-C33),0)</f>
-        <v/>
-      </c>
-      <c r="I64" s="47">
-        <f>IF(6=C34,(I59*(1+C19)/C32)*(1-C33),0)</f>
-        <v/>
-      </c>
-      <c r="J64" s="47">
-        <f>IF(7=C34,(J59*(1+C19)/C32)*(1-C33),0)</f>
-        <v/>
-      </c>
-      <c r="K64" s="47">
-        <f>IF(8=C34,(K59*(1+C19)/C32)*(1-C33),0)</f>
-        <v/>
-      </c>
-      <c r="L64" s="47">
-        <f>IF(9=C34,(L59*(1+C19)/C32)*(1-C33),0)</f>
-        <v/>
-      </c>
-      <c r="M64" s="47">
-        <f>IF(10=C34,(M59*(1+C19)/C32)*(1-C33),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="65" ht="15" customHeight="1">
-      <c r="B65" s="43" t="inlineStr">
-        <is>
-          <t>UNLEVERED PROJECT CASH FLOW</t>
-        </is>
-      </c>
-      <c r="C65" s="44">
-        <f>C61</f>
-        <v/>
-      </c>
-      <c r="D65" s="44">
-        <f>IF(1&lt;=C34,D61,0)+D64</f>
-        <v/>
-      </c>
-      <c r="E65" s="45">
-        <f>IF(2&lt;=C34,E61,0)+E64</f>
-        <v/>
-      </c>
-      <c r="F65" s="45">
-        <f>IF(3&lt;=C34,F61,0)+F64</f>
-        <v/>
-      </c>
-      <c r="G65" s="45">
-        <f>IF(4&lt;=C34,G61,0)+G64</f>
-        <v/>
-      </c>
-      <c r="H65" s="45">
-        <f>IF(5&lt;=C34,H61,0)+H64</f>
-        <v/>
-      </c>
-      <c r="I65" s="45">
-        <f>IF(6&lt;=C34,I61,0)+I64</f>
-        <v/>
-      </c>
-      <c r="J65" s="45">
-        <f>IF(7&lt;=C34,J61,0)+J64</f>
-        <v/>
-      </c>
-      <c r="K65" s="45">
-        <f>IF(8&lt;=C34,K61,0)+K64</f>
-        <v/>
-      </c>
-      <c r="L65" s="45">
-        <f>IF(9&lt;=C34,L61,0)+L64</f>
-        <v/>
-      </c>
-      <c r="M65" s="45">
-        <f>IF(10&lt;=C34,M61,0)+M64</f>
-        <v/>
-      </c>
+      <c r="C65" s="2" t="n"/>
+      <c r="D65" s="2" t="n"/>
+      <c r="E65" s="2" t="n"/>
+      <c r="F65" s="2" t="n"/>
+      <c r="G65" s="2" t="n"/>
+      <c r="H65" s="2" t="n"/>
+      <c r="I65" s="2" t="n"/>
+      <c r="J65" s="2" t="n"/>
+      <c r="K65" s="2" t="n"/>
+      <c r="L65" s="2" t="n"/>
+      <c r="M65" s="3" t="n"/>
     </row>
     <row r="66" ht="15" customHeight="1">
       <c r="B66" s="12" t="inlineStr">
         <is>
+          <t>Net sale proceeds (exit year)</t>
+        </is>
+      </c>
+      <c r="D66" s="47">
+        <f>IF(1=C36,(D61*(1+C21)/C34)*(1-C35),0)</f>
+        <v/>
+      </c>
+      <c r="E66" s="47">
+        <f>IF(2=C36,(E61*(1+C21)/C34)*(1-C35),0)</f>
+        <v/>
+      </c>
+      <c r="F66" s="47">
+        <f>IF(3=C36,(F61*(1+C21)/C34)*(1-C35),0)</f>
+        <v/>
+      </c>
+      <c r="G66" s="47">
+        <f>IF(4=C36,(G61*(1+C21)/C34)*(1-C35),0)</f>
+        <v/>
+      </c>
+      <c r="H66" s="47">
+        <f>IF(5=C36,(H61*(1+C21)/C34)*(1-C35),0)</f>
+        <v/>
+      </c>
+      <c r="I66" s="47">
+        <f>IF(6=C36,(I61*(1+C21)/C34)*(1-C35),0)</f>
+        <v/>
+      </c>
+      <c r="J66" s="47">
+        <f>IF(7=C36,(J61*(1+C21)/C34)*(1-C35),0)</f>
+        <v/>
+      </c>
+      <c r="K66" s="47">
+        <f>IF(8=C36,(K61*(1+C21)/C34)*(1-C35),0)</f>
+        <v/>
+      </c>
+      <c r="L66" s="47">
+        <f>IF(9=C36,(L61*(1+C21)/C34)*(1-C35),0)</f>
+        <v/>
+      </c>
+      <c r="M66" s="47">
+        <f>IF(10=C36,(M61*(1+C21)/C34)*(1-C35),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67" ht="15" customHeight="1">
+      <c r="B67" s="43" t="inlineStr">
+        <is>
+          <t>UNLEVERED PROJECT CASH FLOW</t>
+        </is>
+      </c>
+      <c r="C67" s="44">
+        <f>C63</f>
+        <v/>
+      </c>
+      <c r="D67" s="44">
+        <f>IF(1&lt;=C36,D63,0)+D66</f>
+        <v/>
+      </c>
+      <c r="E67" s="45">
+        <f>IF(2&lt;=C36,E63,0)+E66</f>
+        <v/>
+      </c>
+      <c r="F67" s="45">
+        <f>IF(3&lt;=C36,F63,0)+F66</f>
+        <v/>
+      </c>
+      <c r="G67" s="45">
+        <f>IF(4&lt;=C36,G63,0)+G66</f>
+        <v/>
+      </c>
+      <c r="H67" s="45">
+        <f>IF(5&lt;=C36,H63,0)+H66</f>
+        <v/>
+      </c>
+      <c r="I67" s="45">
+        <f>IF(6&lt;=C36,I63,0)+I66</f>
+        <v/>
+      </c>
+      <c r="J67" s="45">
+        <f>IF(7&lt;=C36,J63,0)+J66</f>
+        <v/>
+      </c>
+      <c r="K67" s="45">
+        <f>IF(8&lt;=C36,K63,0)+K66</f>
+        <v/>
+      </c>
+      <c r="L67" s="45">
+        <f>IF(9&lt;=C36,L63,0)+L66</f>
+        <v/>
+      </c>
+      <c r="M67" s="45">
+        <f>IF(10&lt;=C36,M63,0)+M66</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68" ht="15" customHeight="1">
+      <c r="B68" s="12" t="inlineStr">
+        <is>
           <t>Loan balance (year-end)</t>
         </is>
       </c>
-      <c r="D66" s="47">
-        <f>C39*(1+C40)^(12*1)-(C41/12)*((1+C40)^(12*1)-1)/C40</f>
-        <v/>
-      </c>
-      <c r="E66" s="47">
-        <f>C39*(1+C40)^(12*2)-(C41/12)*((1+C40)^(12*2)-1)/C40</f>
-        <v/>
-      </c>
-      <c r="F66" s="47">
-        <f>C39*(1+C40)^(12*3)-(C41/12)*((1+C40)^(12*3)-1)/C40</f>
-        <v/>
-      </c>
-      <c r="G66" s="47">
-        <f>C39*(1+C40)^(12*4)-(C41/12)*((1+C40)^(12*4)-1)/C40</f>
-        <v/>
-      </c>
-      <c r="H66" s="47">
-        <f>C39*(1+C40)^(12*5)-(C41/12)*((1+C40)^(12*5)-1)/C40</f>
-        <v/>
-      </c>
-      <c r="I66" s="47">
-        <f>C39*(1+C40)^(12*6)-(C41/12)*((1+C40)^(12*6)-1)/C40</f>
-        <v/>
-      </c>
-      <c r="J66" s="47">
-        <f>C39*(1+C40)^(12*7)-(C41/12)*((1+C40)^(12*7)-1)/C40</f>
-        <v/>
-      </c>
-      <c r="K66" s="47">
-        <f>C39*(1+C40)^(12*8)-(C41/12)*((1+C40)^(12*8)-1)/C40</f>
-        <v/>
-      </c>
-      <c r="L66" s="47">
-        <f>C39*(1+C40)^(12*9)-(C41/12)*((1+C40)^(12*9)-1)/C40</f>
-        <v/>
-      </c>
-      <c r="M66" s="47">
-        <f>C39*(1+C40)^(12*10)-(C41/12)*((1+C40)^(12*10)-1)/C40</f>
-        <v/>
-      </c>
-    </row>
-    <row r="67" ht="15" customHeight="1">
-      <c r="B67" s="12" t="inlineStr">
+      <c r="D68" s="47">
+        <f>C41*(1+C42)^(12*1)-(C43/12)*((1+C42)^(12*1)-1)/C42</f>
+        <v/>
+      </c>
+      <c r="E68" s="47">
+        <f>C41*(1+C42)^(12*2)-(C43/12)*((1+C42)^(12*2)-1)/C42</f>
+        <v/>
+      </c>
+      <c r="F68" s="47">
+        <f>C41*(1+C42)^(12*3)-(C43/12)*((1+C42)^(12*3)-1)/C42</f>
+        <v/>
+      </c>
+      <c r="G68" s="47">
+        <f>C41*(1+C42)^(12*4)-(C43/12)*((1+C42)^(12*4)-1)/C42</f>
+        <v/>
+      </c>
+      <c r="H68" s="47">
+        <f>C41*(1+C42)^(12*5)-(C43/12)*((1+C42)^(12*5)-1)/C42</f>
+        <v/>
+      </c>
+      <c r="I68" s="47">
+        <f>C41*(1+C42)^(12*6)-(C43/12)*((1+C42)^(12*6)-1)/C42</f>
+        <v/>
+      </c>
+      <c r="J68" s="47">
+        <f>C41*(1+C42)^(12*7)-(C43/12)*((1+C42)^(12*7)-1)/C42</f>
+        <v/>
+      </c>
+      <c r="K68" s="47">
+        <f>C41*(1+C42)^(12*8)-(C43/12)*((1+C42)^(12*8)-1)/C42</f>
+        <v/>
+      </c>
+      <c r="L68" s="47">
+        <f>C41*(1+C42)^(12*9)-(C43/12)*((1+C42)^(12*9)-1)/C42</f>
+        <v/>
+      </c>
+      <c r="M68" s="47">
+        <f>C41*(1+C42)^(12*10)-(C43/12)*((1+C42)^(12*10)-1)/C42</f>
+        <v/>
+      </c>
+    </row>
+    <row r="69" ht="15" customHeight="1">
+      <c r="B69" s="12" t="inlineStr">
         <is>
           <t>DSCR (NOI ÷ DS)</t>
         </is>
       </c>
-      <c r="D67" s="54">
-        <f>D59/C41</f>
-        <v/>
-      </c>
-      <c r="E67" s="54">
-        <f>E59/C41</f>
-        <v/>
-      </c>
-      <c r="F67" s="54">
-        <f>F59/C41</f>
-        <v/>
-      </c>
-      <c r="G67" s="54">
-        <f>G59/C41</f>
-        <v/>
-      </c>
-      <c r="H67" s="54">
-        <f>H59/C41</f>
-        <v/>
-      </c>
-      <c r="I67" s="54">
-        <f>I59/C41</f>
-        <v/>
-      </c>
-      <c r="J67" s="54">
-        <f>J59/C41</f>
-        <v/>
-      </c>
-      <c r="K67" s="54">
-        <f>K59/C41</f>
-        <v/>
-      </c>
-      <c r="L67" s="54">
-        <f>L59/C41</f>
-        <v/>
-      </c>
-      <c r="M67" s="54">
-        <f>M59/C41</f>
-        <v/>
-      </c>
-    </row>
-    <row r="68" ht="15" customHeight="1">
-      <c r="B68" s="43" t="inlineStr">
+      <c r="D69" s="54">
+        <f>D61/C43</f>
+        <v/>
+      </c>
+      <c r="E69" s="54">
+        <f>E61/C43</f>
+        <v/>
+      </c>
+      <c r="F69" s="54">
+        <f>F61/C43</f>
+        <v/>
+      </c>
+      <c r="G69" s="54">
+        <f>G61/C43</f>
+        <v/>
+      </c>
+      <c r="H69" s="54">
+        <f>H61/C43</f>
+        <v/>
+      </c>
+      <c r="I69" s="54">
+        <f>I61/C43</f>
+        <v/>
+      </c>
+      <c r="J69" s="54">
+        <f>J61/C43</f>
+        <v/>
+      </c>
+      <c r="K69" s="54">
+        <f>K61/C43</f>
+        <v/>
+      </c>
+      <c r="L69" s="54">
+        <f>L61/C43</f>
+        <v/>
+      </c>
+      <c r="M69" s="54">
+        <f>M61/C43</f>
+        <v/>
+      </c>
+    </row>
+    <row r="70" ht="15" customHeight="1">
+      <c r="B70" s="43" t="inlineStr">
         <is>
           <t>LEVERED CASH FLOW (equity)</t>
         </is>
       </c>
-      <c r="C68" s="44">
-        <f>-C42</f>
-        <v/>
-      </c>
-      <c r="D68" s="44">
-        <f>IF(1&lt;=C34,D61-C41,0)+IF(1=C34,D64-D66,0)</f>
-        <v/>
-      </c>
-      <c r="E68" s="45">
-        <f>IF(2&lt;=C34,E61-C41,0)+IF(2=C34,E64-E66,0)</f>
-        <v/>
-      </c>
-      <c r="F68" s="45">
-        <f>IF(3&lt;=C34,F61-C41,0)+IF(3=C34,F64-F66,0)</f>
-        <v/>
-      </c>
-      <c r="G68" s="45">
-        <f>IF(4&lt;=C34,G61-C41,0)+IF(4=C34,G64-G66,0)</f>
-        <v/>
-      </c>
-      <c r="H68" s="45">
-        <f>IF(5&lt;=C34,H61-C41,0)+IF(5=C34,H64-H66,0)</f>
-        <v/>
-      </c>
-      <c r="I68" s="45">
-        <f>IF(6&lt;=C34,I61-C41,0)+IF(6=C34,I64-I66,0)</f>
-        <v/>
-      </c>
-      <c r="J68" s="45">
-        <f>IF(7&lt;=C34,J61-C41,0)+IF(7=C34,J64-J66,0)</f>
-        <v/>
-      </c>
-      <c r="K68" s="45">
-        <f>IF(8&lt;=C34,K61-C41,0)+IF(8=C34,K64-K66,0)</f>
-        <v/>
-      </c>
-      <c r="L68" s="45">
-        <f>IF(9&lt;=C34,L61-C41,0)+IF(9=C34,L64-L66,0)</f>
-        <v/>
-      </c>
-      <c r="M68" s="45">
-        <f>IF(10&lt;=C34,M61-C41,0)+IF(10=C34,M64-M66,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="69"/>
-    <row r="70">
-      <c r="B70" s="11" t="inlineStr">
+      <c r="C70" s="44">
+        <f>-C44</f>
+        <v/>
+      </c>
+      <c r="D70" s="44">
+        <f>IF(1&lt;=C36,D63-C43,0)+IF(1=C36,D66-D68,0)</f>
+        <v/>
+      </c>
+      <c r="E70" s="45">
+        <f>IF(2&lt;=C36,E63-C43,0)+IF(2=C36,E66-E68,0)</f>
+        <v/>
+      </c>
+      <c r="F70" s="45">
+        <f>IF(3&lt;=C36,F63-C43,0)+IF(3=C36,F66-F68,0)</f>
+        <v/>
+      </c>
+      <c r="G70" s="45">
+        <f>IF(4&lt;=C36,G63-C43,0)+IF(4=C36,G66-G68,0)</f>
+        <v/>
+      </c>
+      <c r="H70" s="45">
+        <f>IF(5&lt;=C36,H63-C43,0)+IF(5=C36,H66-H68,0)</f>
+        <v/>
+      </c>
+      <c r="I70" s="45">
+        <f>IF(6&lt;=C36,I63-C43,0)+IF(6=C36,I66-I68,0)</f>
+        <v/>
+      </c>
+      <c r="J70" s="45">
+        <f>IF(7&lt;=C36,J63-C43,0)+IF(7=C36,J66-J68,0)</f>
+        <v/>
+      </c>
+      <c r="K70" s="45">
+        <f>IF(8&lt;=C36,K63-C43,0)+IF(8=C36,K66-K68,0)</f>
+        <v/>
+      </c>
+      <c r="L70" s="45">
+        <f>IF(9&lt;=C36,L63-C43,0)+IF(9=C36,L66-L68,0)</f>
+        <v/>
+      </c>
+      <c r="M70" s="45">
+        <f>IF(10&lt;=C36,M63-C43,0)+IF(10=C36,M66-M68,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="71"/>
+    <row r="72">
+      <c r="B72" s="11" t="inlineStr">
         <is>
           <t>RETURNS  —  unlevered &amp; levered</t>
         </is>
       </c>
-      <c r="C70" s="2" t="n"/>
-      <c r="D70" s="2" t="n"/>
-      <c r="E70" s="2" t="n"/>
-      <c r="F70" s="2" t="n"/>
-      <c r="G70" s="2" t="n"/>
-      <c r="H70" s="2" t="n"/>
-      <c r="I70" s="2" t="n"/>
-      <c r="J70" s="2" t="n"/>
-      <c r="K70" s="2" t="n"/>
-      <c r="L70" s="2" t="n"/>
-      <c r="M70" s="3" t="n"/>
-    </row>
-    <row r="71" ht="15" customHeight="1">
-      <c r="B71" s="12" t="inlineStr">
-        <is>
-          <t>Unlevered IRR</t>
-        </is>
-      </c>
-      <c r="C71" s="53">
-        <f>IRR(C65:M65)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="72" ht="15" customHeight="1">
-      <c r="B72" s="12" t="inlineStr">
-        <is>
-          <t>Unlevered equity multiple</t>
-        </is>
-      </c>
-      <c r="C72" s="54">
-        <f>SUM(D65:M65)/-C65</f>
-        <v/>
-      </c>
+      <c r="C72" s="2" t="n"/>
+      <c r="D72" s="2" t="n"/>
+      <c r="E72" s="2" t="n"/>
+      <c r="F72" s="2" t="n"/>
+      <c r="G72" s="2" t="n"/>
+      <c r="H72" s="2" t="n"/>
+      <c r="I72" s="2" t="n"/>
+      <c r="J72" s="2" t="n"/>
+      <c r="K72" s="2" t="n"/>
+      <c r="L72" s="2" t="n"/>
+      <c r="M72" s="3" t="n"/>
     </row>
     <row r="73" ht="15" customHeight="1">
       <c r="B73" s="12" t="inlineStr">
         <is>
-          <t>Unlevered NPV @ discount rate</t>
-        </is>
-      </c>
-      <c r="C73" s="51">
-        <f>C65+NPV(C35,D65:M65)</f>
+          <t>Unlevered IRR</t>
+        </is>
+      </c>
+      <c r="C73" s="53">
+        <f>IRR(C67:M67)</f>
         <v/>
       </c>
     </row>
     <row r="74" ht="15" customHeight="1">
       <c r="B74" s="12" t="inlineStr">
         <is>
-          <t>Levered IRR</t>
-        </is>
-      </c>
-      <c r="C74" s="53">
-        <f>IRR(C68:M68)</f>
+          <t>Unlevered equity multiple</t>
+        </is>
+      </c>
+      <c r="C74" s="54">
+        <f>SUM(D67:M67)/-C67</f>
         <v/>
       </c>
     </row>
     <row r="75" ht="15" customHeight="1">
       <c r="B75" s="12" t="inlineStr">
         <is>
-          <t>Levered equity multiple</t>
-        </is>
-      </c>
-      <c r="C75" s="54">
-        <f>SUM(D68:M68)/C42</f>
+          <t>Unlevered NPV @ discount rate</t>
+        </is>
+      </c>
+      <c r="C75" s="51">
+        <f>C67+NPV(C37,D67:M67)</f>
         <v/>
       </c>
     </row>
     <row r="76" ht="15" customHeight="1">
       <c r="B76" s="12" t="inlineStr">
         <is>
-          <t>Year-1 NOI (pro-forma)</t>
-        </is>
-      </c>
-      <c r="C76" s="51">
-        <f>D59</f>
+          <t>Levered IRR</t>
+        </is>
+      </c>
+      <c r="C76" s="53">
+        <f>IRR(C70:M70)</f>
         <v/>
       </c>
     </row>
     <row r="77" ht="15" customHeight="1">
       <c r="B77" s="12" t="inlineStr">
         <is>
-          <t>As-is in-place NOI (at occ0, no lease-up)</t>
-        </is>
-      </c>
-      <c r="C77" s="51">
-        <f>(C15*C16*C18)-(C15*C16*C18)*C20-(C26*C21+C15*C22)-((C15*C16*C18)-(C15*C16*C18)*C20)*C23</f>
+          <t>Levered equity multiple</t>
+        </is>
+      </c>
+      <c r="C77" s="54">
+        <f>SUM(D70:M70)/C44</f>
         <v/>
       </c>
     </row>
     <row r="78" ht="15" customHeight="1">
       <c r="B78" s="12" t="inlineStr">
         <is>
-          <t>Going-in cap (as-is NOI ÷ price)</t>
-        </is>
-      </c>
-      <c r="C78" s="50">
-        <f>C77/C26</f>
+          <t>Year-1 NOI (pro-forma)</t>
+        </is>
+      </c>
+      <c r="C78" s="51">
+        <f>D61</f>
         <v/>
       </c>
     </row>
     <row r="79" ht="15" customHeight="1">
       <c r="B79" s="12" t="inlineStr">
         <is>
-          <t>Stabilized NOI (Yr 2)</t>
+          <t>As-is in-place NOI (at occ0, no lease-up)</t>
         </is>
       </c>
       <c r="C79" s="51">
-        <f>E59</f>
+        <f>(C17*C18*C20)-(C17*C18*C20)*C22-(C28*C23+C17*C24)-((C17*C18*C20)-(C17*C18*C20)*C22)*C25</f>
         <v/>
       </c>
     </row>
     <row r="80" ht="15" customHeight="1">
       <c r="B80" s="12" t="inlineStr">
         <is>
-          <t>Stabilized value (÷ exit cap)</t>
-        </is>
-      </c>
-      <c r="C80" s="51">
-        <f>C79/C32</f>
+          <t>Going-in cap (as-is NOI ÷ price)</t>
+        </is>
+      </c>
+      <c r="C80" s="50">
+        <f>C79/C28</f>
         <v/>
       </c>
     </row>
     <row r="81" ht="15" customHeight="1">
       <c r="B81" s="12" t="inlineStr">
         <is>
-          <t>In-place NOI per SF</t>
-        </is>
-      </c>
-      <c r="C81" s="68">
-        <f>D59/C15</f>
+          <t>Stabilized NOI (Yr 2)</t>
+        </is>
+      </c>
+      <c r="C81" s="51">
+        <f>E61</f>
         <v/>
       </c>
     </row>
     <row r="82" ht="15" customHeight="1">
       <c r="B82" s="12" t="inlineStr">
         <is>
-          <t>Income value (Yr-1 NOI ÷ going-in cap)</t>
+          <t>Stabilized value (÷ exit cap)</t>
         </is>
       </c>
       <c r="C82" s="51">
-        <f>D59/C31</f>
+        <f>C81/C34</f>
         <v/>
       </c>
     </row>
     <row r="83" ht="15" customHeight="1">
       <c r="B83" s="12" t="inlineStr">
         <is>
+          <t>In-place NOI per SF</t>
+        </is>
+      </c>
+      <c r="C83" s="68">
+        <f>D61/C17</f>
+        <v/>
+      </c>
+    </row>
+    <row r="84" ht="15" customHeight="1">
+      <c r="B84" s="12" t="inlineStr">
+        <is>
+          <t>Income value (Yr-1 NOI ÷ going-in cap)</t>
+        </is>
+      </c>
+      <c r="C84" s="51">
+        <f>D61/C33</f>
+        <v/>
+      </c>
+    </row>
+    <row r="85" ht="15" customHeight="1">
+      <c r="B85" s="12" t="inlineStr">
+        <is>
           <t>Sale-comp value (SF × $/SF)</t>
         </is>
       </c>
-      <c r="C83" s="51">
-        <f>C15*C36</f>
-        <v/>
-      </c>
-    </row>
-    <row r="84"/>
-    <row r="85">
-      <c r="B85" s="11" t="inlineStr">
-        <is>
-          <t>LEASE-POSITION VALUATION BY OWNER  —  the two dominant condo owners</t>
-        </is>
-      </c>
-      <c r="C85" s="2" t="n"/>
-      <c r="D85" s="2" t="n"/>
-      <c r="E85" s="2" t="n"/>
-      <c r="F85" s="2" t="n"/>
-      <c r="G85" s="2" t="n"/>
-      <c r="H85" s="2" t="n"/>
-      <c r="I85" s="2" t="n"/>
-      <c r="J85" s="2" t="n"/>
-      <c r="K85" s="2" t="n"/>
-      <c r="L85" s="2" t="n"/>
-      <c r="M85" s="3" t="n"/>
-    </row>
-    <row r="86" ht="15" customHeight="1">
-      <c r="B86" s="15" t="inlineStr">
-        <is>
-          <t>Owner</t>
-        </is>
-      </c>
-      <c r="C86" s="14" t="n"/>
-      <c r="D86" s="16" t="inlineStr">
-        <is>
-          <t>SF owned</t>
-        </is>
-      </c>
-      <c r="E86" s="16" t="inlineStr">
-        <is>
-          <t>% bldg</t>
-        </is>
-      </c>
-      <c r="F86" s="16" t="inlineStr">
-        <is>
-          <t>2019 basis</t>
-        </is>
-      </c>
-      <c r="G86" s="16" t="inlineStr">
-        <is>
-          <t>Income value</t>
-        </is>
-      </c>
-      <c r="H86" s="16" t="inlineStr">
-        <is>
-          <t>$300/SF comp</t>
-        </is>
-      </c>
-      <c r="I86" s="15" t="inlineStr">
-        <is>
-          <t>Note</t>
-        </is>
-      </c>
-      <c r="J86" s="13" t="n"/>
-      <c r="K86" s="13" t="n"/>
-      <c r="L86" s="13" t="n"/>
-      <c r="M86" s="14" t="n"/>
-    </row>
-    <row r="87" ht="15" customHeight="1">
-      <c r="B87" s="12" t="inlineStr">
-        <is>
-          <t>Main Street Fund LLC</t>
-        </is>
-      </c>
-      <c r="C87" s="14" t="n"/>
-      <c r="D87" s="77" t="n">
-        <v>96930</v>
-      </c>
-      <c r="E87" s="53">
-        <f>D87/C15</f>
-        <v/>
-      </c>
-      <c r="F87" s="47" t="n">
-        <v>10000000</v>
-      </c>
-      <c r="G87" s="47">
-        <f>C81*D87/C31</f>
-        <v/>
-      </c>
-      <c r="H87" s="47">
-        <f>D87*C36</f>
-        <v/>
-      </c>
-      <c r="I87" s="12" t="inlineStr">
-        <is>
-          <t>Bought 57.4% + 2 parking lots for $10.0M (Sept 2019) — dominant owner / lessor</t>
-        </is>
-      </c>
-      <c r="J87" s="13" t="n"/>
-      <c r="K87" s="13" t="n"/>
-      <c r="L87" s="13" t="n"/>
-      <c r="M87" s="14" t="n"/>
-    </row>
-    <row r="88" ht="15" customHeight="1">
+      <c r="C85" s="51">
+        <f>C17*C38</f>
+        <v/>
+      </c>
+    </row>
+    <row r="86"/>
+    <row r="87">
+      <c r="B87" s="11" t="inlineStr">
+        <is>
+          <t>OWNERS &amp; FULL BUY-OUT  —  every identifiable owner modeled individually  (⚠️ BCPA/Clerk egress-blocked; balance grouped)</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="n"/>
+      <c r="D87" s="2" t="n"/>
+      <c r="E87" s="2" t="n"/>
+      <c r="F87" s="2" t="n"/>
+      <c r="G87" s="2" t="n"/>
+      <c r="H87" s="2" t="n"/>
+      <c r="I87" s="2" t="n"/>
+      <c r="J87" s="2" t="n"/>
+      <c r="K87" s="2" t="n"/>
+      <c r="L87" s="2" t="n"/>
+      <c r="M87" s="3" t="n"/>
+    </row>
+    <row r="88" ht="27" customHeight="1">
       <c r="B88" s="12" t="inlineStr">
         <is>
-          <t>International Sunrise Partners LLC</t>
-        </is>
-      </c>
-      <c r="C88" s="14" t="n"/>
-      <c r="D88" s="77" t="n">
-        <v>71877</v>
-      </c>
-      <c r="E88" s="53">
-        <f>D88/C15</f>
-        <v/>
-      </c>
-      <c r="F88" s="90" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G88" s="47">
-        <f>C81*D88/C31</f>
-        <v/>
-      </c>
-      <c r="H88" s="47">
-        <f>D88*C36</f>
-        <v/>
-      </c>
-      <c r="I88" s="12" t="inlineStr">
-        <is>
-          <t>Prior bulk owner (2011 condo-conversion sponsor); retains the balance of units</t>
-        </is>
-      </c>
+          <t>Condo buyout premium (fractured ownership / holdout)</t>
+        </is>
+      </c>
+      <c r="C88" s="84" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="D88" s="22" t="inlineStr">
+        <is>
+          <t>🔵 uplift over income value to get owners to sell</t>
+        </is>
+      </c>
+      <c r="E88" s="13" t="n"/>
+      <c r="F88" s="13" t="n"/>
+      <c r="G88" s="13" t="n"/>
+      <c r="H88" s="13" t="n"/>
+      <c r="I88" s="13" t="n"/>
       <c r="J88" s="13" t="n"/>
       <c r="K88" s="13" t="n"/>
       <c r="L88" s="13" t="n"/>
       <c r="M88" s="14" t="n"/>
     </row>
     <row r="89" ht="15" customHeight="1">
-      <c r="B89" s="19" t="inlineStr">
-        <is>
-          <t>TOTAL BUILDING</t>
+      <c r="B89" s="15" t="inlineStr">
+        <is>
+          <t>Owner / unit</t>
         </is>
       </c>
       <c r="C89" s="14" t="n"/>
-      <c r="D89" s="66">
-        <f>SUM(D87:D88)</f>
-        <v/>
-      </c>
-      <c r="E89" s="21">
-        <f>SUM(E87:E88)</f>
-        <v/>
-      </c>
-      <c r="F89" s="91" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G89" s="20">
-        <f>SUM(G87:G88)</f>
-        <v/>
-      </c>
-      <c r="H89" s="20">
-        <f>SUM(H87:H88)</f>
-        <v/>
-      </c>
-      <c r="I89" s="19" t="inlineStr">
-        <is>
-          <t>buy out both to assemble</t>
-        </is>
-      </c>
-      <c r="J89" s="13" t="n"/>
+      <c r="D89" s="16" t="inlineStr">
+        <is>
+          <t>SF</t>
+        </is>
+      </c>
+      <c r="E89" s="16" t="inlineStr">
+        <is>
+          <t>% bldg</t>
+        </is>
+      </c>
+      <c r="F89" s="16" t="inlineStr">
+        <is>
+          <t>Orig basis</t>
+        </is>
+      </c>
+      <c r="G89" s="16" t="inlineStr">
+        <is>
+          <t>Bought</t>
+        </is>
+      </c>
+      <c r="H89" s="16" t="inlineStr">
+        <is>
+          <t>Income value</t>
+        </is>
+      </c>
+      <c r="I89" s="16" t="inlineStr">
+        <is>
+          <t>Buy-out value</t>
+        </is>
+      </c>
+      <c r="J89" s="15" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
       <c r="K89" s="13" t="n"/>
       <c r="L89" s="13" t="n"/>
       <c r="M89" s="14" t="n"/>
     </row>
-    <row r="90"/>
-    <row r="91">
-      <c r="B91" s="11" t="inlineStr">
-        <is>
-          <t>FULL BUY-OUT VALUE  —  cost to acquire BOTH condo owners' positions</t>
-        </is>
-      </c>
-      <c r="C91" s="2" t="n"/>
-      <c r="D91" s="2" t="n"/>
-      <c r="E91" s="2" t="n"/>
-      <c r="F91" s="2" t="n"/>
-      <c r="G91" s="2" t="n"/>
-      <c r="H91" s="2" t="n"/>
-      <c r="I91" s="2" t="n"/>
-      <c r="J91" s="2" t="n"/>
-      <c r="K91" s="2" t="n"/>
-      <c r="L91" s="2" t="n"/>
-      <c r="M91" s="3" t="n"/>
-    </row>
-    <row r="92" ht="27" customHeight="1">
+    <row r="90" ht="27" customHeight="1">
+      <c r="B90" s="12" t="inlineStr">
+        <is>
+          <t>Main Street Fund LLC (Grove Gate)</t>
+        </is>
+      </c>
+      <c r="C90" s="14" t="n"/>
+      <c r="D90" s="77" t="n">
+        <v>96930</v>
+      </c>
+      <c r="E90" s="53">
+        <f>D90/C17</f>
+        <v/>
+      </c>
+      <c r="F90" s="72" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="G90" s="71" t="inlineStr">
+        <is>
+          <t>09/2019</t>
+        </is>
+      </c>
+      <c r="H90" s="47">
+        <f>C83*D90/C33</f>
+        <v/>
+      </c>
+      <c r="I90" s="47">
+        <f>H90*(1+C88)</f>
+        <v/>
+      </c>
+      <c r="J90" s="12" t="inlineStr">
+        <is>
+          <t>57.4% + 2 parking lots · ✅ press · NOW RESELLING units individually</t>
+        </is>
+      </c>
+      <c r="K90" s="13" t="n"/>
+      <c r="L90" s="13" t="n"/>
+      <c r="M90" s="14" t="n"/>
+    </row>
+    <row r="91" ht="27" customHeight="1">
+      <c r="B91" s="12" t="inlineStr">
+        <is>
+          <t>International Sunrise Partners LLC</t>
+        </is>
+      </c>
+      <c r="C91" s="14" t="n"/>
+      <c r="D91" s="77" t="n">
+        <v>40000</v>
+      </c>
+      <c r="E91" s="53">
+        <f>D91/C17</f>
+        <v/>
+      </c>
+      <c r="F91" s="90" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G91" s="42" t="inlineStr">
+        <is>
+          <t>2011</t>
+        </is>
+      </c>
+      <c r="H91" s="47">
+        <f>C83*D91/C33</f>
+        <v/>
+      </c>
+      <c r="I91" s="47">
+        <f>H91*(1+C88)</f>
+        <v/>
+      </c>
+      <c r="J91" s="12" t="inlineStr">
+        <is>
+          <t>Bush Development condo-conversion sponsor · retained balance · SF est.</t>
+        </is>
+      </c>
+      <c r="K91" s="13" t="n"/>
+      <c r="L91" s="13" t="n"/>
+      <c r="M91" s="14" t="n"/>
+    </row>
+    <row r="92" ht="15" customHeight="1">
       <c r="B92" s="12" t="inlineStr">
         <is>
-          <t>Condo buyout premium (fractured ownership / holdout)</t>
-        </is>
-      </c>
-      <c r="C92" s="84" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="D92" s="22" t="inlineStr">
-        <is>
-          <t>🔵 uplift over income value to get both owners to sell</t>
-        </is>
-      </c>
-      <c r="E92" s="13" t="n"/>
-      <c r="F92" s="13" t="n"/>
-      <c r="G92" s="13" t="n"/>
-      <c r="H92" s="13" t="n"/>
-      <c r="I92" s="13" t="n"/>
-      <c r="J92" s="13" t="n"/>
+          <t>P. Jorgensen Management LLC — Ste 805</t>
+        </is>
+      </c>
+      <c r="C92" s="14" t="n"/>
+      <c r="D92" s="77" t="n">
+        <v>1722</v>
+      </c>
+      <c r="E92" s="53">
+        <f>D92/C17</f>
+        <v/>
+      </c>
+      <c r="F92" s="72" t="n">
+        <v>410000</v>
+      </c>
+      <c r="G92" s="71" t="inlineStr">
+        <is>
+          <t>11/2019</t>
+        </is>
+      </c>
+      <c r="H92" s="47">
+        <f>C83*D92/C33</f>
+        <v/>
+      </c>
+      <c r="I92" s="47">
+        <f>H92*(1+C88)</f>
+        <v/>
+      </c>
+      <c r="J92" s="12" t="inlineStr">
+        <is>
+          <t>Denmark-based US HQ · ✅ press (Berger Commercial)</t>
+        </is>
+      </c>
       <c r="K92" s="13" t="n"/>
       <c r="L92" s="13" t="n"/>
       <c r="M92" s="14" t="n"/>
@@ -4404,172 +4449,273 @@
     <row r="93" ht="15" customHeight="1">
       <c r="B93" s="12" t="inlineStr">
         <is>
-          <t>Main Street Fund LLC (57.4%) — buyout</t>
-        </is>
-      </c>
-      <c r="C93" s="47">
-        <f>G87*(1+C92)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="94" ht="27" customHeight="1">
+          <t>Hublot of America, Inc. — Ste 402</t>
+        </is>
+      </c>
+      <c r="C93" s="14" t="n"/>
+      <c r="D93" s="77" t="n">
+        <v>2000</v>
+      </c>
+      <c r="E93" s="53">
+        <f>D93/C17</f>
+        <v/>
+      </c>
+      <c r="F93" s="90" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G93" s="42" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H93" s="47">
+        <f>C83*D93/C33</f>
+        <v/>
+      </c>
+      <c r="I93" s="47">
+        <f>H93*(1+C88)</f>
+        <v/>
+      </c>
+      <c r="J93" s="12" t="inlineStr">
+        <is>
+          <t>Swiss watchmaker boutique · SF est. · ⚠️ reported</t>
+        </is>
+      </c>
+      <c r="K93" s="13" t="n"/>
+      <c r="L93" s="13" t="n"/>
+      <c r="M93" s="14" t="n"/>
+    </row>
+    <row r="94" ht="15" customHeight="1">
       <c r="B94" s="12" t="inlineStr">
         <is>
-          <t>International Sunrise Partners LLC (42.6%) — buyout</t>
-        </is>
-      </c>
-      <c r="C94" s="47">
-        <f>G88*(1+C92)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="95" ht="16" customHeight="1">
-      <c r="B95" s="55" t="inlineStr">
-        <is>
-          <t>FULL BUY-OUT VALUE (both owners)</t>
-        </is>
-      </c>
-      <c r="C95" s="56">
-        <f>C93+C94</f>
-        <v/>
-      </c>
-      <c r="D95" s="22" t="inlineStr">
-        <is>
-          <t>cost to control the whole building (income value + buyout premium)</t>
-        </is>
-      </c>
-      <c r="E95" s="13" t="n"/>
-      <c r="F95" s="13" t="n"/>
-      <c r="G95" s="13" t="n"/>
-      <c r="H95" s="13" t="n"/>
-      <c r="I95" s="13" t="n"/>
-      <c r="J95" s="13" t="n"/>
+          <t>Merrimac Ventures (Motwani) — unit(s)</t>
+        </is>
+      </c>
+      <c r="C94" s="14" t="n"/>
+      <c r="D94" s="77" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E94" s="53">
+        <f>D94/C17</f>
+        <v/>
+      </c>
+      <c r="F94" s="90" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G94" s="42" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H94" s="47">
+        <f>C83*D94/C33</f>
+        <v/>
+      </c>
+      <c r="I94" s="47">
+        <f>H94*(1+C88)</f>
+        <v/>
+      </c>
+      <c r="J94" s="12" t="inlineStr">
+        <is>
+          <t>reported owner · SF est. · ⚠️ reported</t>
+        </is>
+      </c>
+      <c r="K94" s="13" t="n"/>
+      <c r="L94" s="13" t="n"/>
+      <c r="M94" s="14" t="n"/>
+    </row>
+    <row r="95" ht="15" customHeight="1">
+      <c r="B95" s="12" t="inlineStr">
+        <is>
+          <t>Unit 401 owner — Ste 401</t>
+        </is>
+      </c>
+      <c r="C95" s="14" t="n"/>
+      <c r="D95" s="77" t="n">
+        <v>682</v>
+      </c>
+      <c r="E95" s="53">
+        <f>D95/C17</f>
+        <v/>
+      </c>
+      <c r="F95" s="72" t="n">
+        <v>260000</v>
+      </c>
+      <c r="G95" s="71" t="inlineStr">
+        <is>
+          <t>06/2024</t>
+        </is>
+      </c>
+      <c r="H95" s="47">
+        <f>C83*D95/C33</f>
+        <v/>
+      </c>
+      <c r="I95" s="47">
+        <f>H95*(1+C88)</f>
+        <v/>
+      </c>
+      <c r="J95" s="12" t="inlineStr">
+        <is>
+          <t>sold via MLS 6/2024 · ⚠️ reported</t>
+        </is>
+      </c>
       <c r="K95" s="13" t="n"/>
       <c r="L95" s="13" t="n"/>
       <c r="M95" s="14" t="n"/>
     </row>
     <row r="96" ht="15" customHeight="1">
-      <c r="B96" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  cross-check — income value (no premium)</t>
-        </is>
-      </c>
-      <c r="C96" s="47">
-        <f>G89</f>
-        <v/>
-      </c>
-      <c r="E96" s="22" t="inlineStr">
-        <is>
-          <t>vs. $300/SF sale comp (stale/high) shown in Returns above</t>
-        </is>
-      </c>
-      <c r="F96" s="13" t="n"/>
-      <c r="G96" s="13" t="n"/>
-      <c r="H96" s="13" t="n"/>
-      <c r="I96" s="13" t="n"/>
-      <c r="J96" s="13" t="n"/>
+      <c r="B96" s="12" t="inlineStr">
+        <is>
+          <t>Other unit owners (dozens of small units)</t>
+        </is>
+      </c>
+      <c r="C96" s="14" t="n"/>
+      <c r="D96" s="77" t="n">
+        <v>24473</v>
+      </c>
+      <c r="E96" s="53">
+        <f>D96/C17</f>
+        <v/>
+      </c>
+      <c r="F96" s="90" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G96" s="42" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H96" s="47">
+        <f>C83*D96/C33</f>
+        <v/>
+      </c>
+      <c r="I96" s="47">
+        <f>H96*(1+C88)</f>
+        <v/>
+      </c>
+      <c r="J96" s="12" t="inlineStr">
+        <is>
+          <t>⚠️ balance — needs a BCPA folio pull to itemize each</t>
+        </is>
+      </c>
       <c r="K96" s="13" t="n"/>
       <c r="L96" s="13" t="n"/>
       <c r="M96" s="14" t="n"/>
     </row>
-    <row r="97"/>
-    <row r="98">
-      <c r="B98" s="11" t="inlineStr">
+    <row r="97" ht="16" customHeight="1">
+      <c r="B97" s="55" t="inlineStr">
+        <is>
+          <t>TOTAL BUILDING — FULL BUY-OUT</t>
+        </is>
+      </c>
+      <c r="C97" s="14" t="n"/>
+      <c r="D97" s="91">
+        <f>SUM(D90:D96)</f>
+        <v/>
+      </c>
+      <c r="E97" s="92">
+        <f>SUM(E90:E96)</f>
+        <v/>
+      </c>
+      <c r="F97" s="93" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G97" s="93" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H97" s="56">
+        <f>SUM(H90:H96)</f>
+        <v/>
+      </c>
+      <c r="I97" s="56">
+        <f>SUM(I90:I96)</f>
+        <v/>
+      </c>
+      <c r="J97" s="55" t="inlineStr">
+        <is>
+          <t>cost to control the whole building</t>
+        </is>
+      </c>
+      <c r="K97" s="13" t="n"/>
+      <c r="L97" s="13" t="n"/>
+      <c r="M97" s="14" t="n"/>
+    </row>
+    <row r="98" ht="15" customHeight="1">
+      <c r="B98" s="22" t="inlineStr">
+        <is>
+          <t>cross-check — income value (no premium) vs. $300/SF comp</t>
+        </is>
+      </c>
+      <c r="C98" s="14" t="n"/>
+      <c r="H98" s="94">
+        <f>H97</f>
+        <v/>
+      </c>
+      <c r="I98" s="94">
+        <f>C85</f>
+        <v/>
+      </c>
+    </row>
+    <row r="99"/>
+    <row r="100">
+      <c r="B100" s="11" t="inlineStr">
         <is>
           <t>PROFIT &amp; LOSS STATEMENT  —  Year 1 vs. Stabilized (Yr 2)</t>
         </is>
       </c>
-      <c r="C98" s="2" t="n"/>
-      <c r="D98" s="2" t="n"/>
-      <c r="E98" s="2" t="n"/>
-      <c r="F98" s="2" t="n"/>
-      <c r="G98" s="2" t="n"/>
-      <c r="H98" s="2" t="n"/>
-      <c r="I98" s="2" t="n"/>
-      <c r="J98" s="2" t="n"/>
-      <c r="K98" s="2" t="n"/>
-      <c r="L98" s="2" t="n"/>
-      <c r="M98" s="3" t="n"/>
-    </row>
-    <row r="99" ht="15" customHeight="1">
-      <c r="B99" s="15" t="inlineStr">
+      <c r="C100" s="2" t="n"/>
+      <c r="D100" s="2" t="n"/>
+      <c r="E100" s="2" t="n"/>
+      <c r="F100" s="2" t="n"/>
+      <c r="G100" s="2" t="n"/>
+      <c r="H100" s="2" t="n"/>
+      <c r="I100" s="2" t="n"/>
+      <c r="J100" s="2" t="n"/>
+      <c r="K100" s="2" t="n"/>
+      <c r="L100" s="2" t="n"/>
+      <c r="M100" s="3" t="n"/>
+    </row>
+    <row r="101" ht="15" customHeight="1">
+      <c r="B101" s="15" t="inlineStr">
         <is>
           <t>$ / year</t>
         </is>
       </c>
-      <c r="F99" s="87" t="inlineStr">
+      <c r="F101" s="87" t="inlineStr">
         <is>
           <t>Year 1</t>
         </is>
       </c>
-      <c r="G99" s="14" t="n"/>
-      <c r="H99" s="87" t="inlineStr">
+      <c r="G101" s="14" t="n"/>
+      <c r="H101" s="87" t="inlineStr">
         <is>
           <t>Stabilized</t>
         </is>
       </c>
-      <c r="I99" s="14" t="n"/>
-      <c r="J99" s="87" t="inlineStr">
+      <c r="I101" s="14" t="n"/>
+      <c r="J101" s="87" t="inlineStr">
         <is>
           <t>Per SF (stab.)</t>
         </is>
-      </c>
-      <c r="K99" s="13" t="n"/>
-      <c r="L99" s="13" t="n"/>
-      <c r="M99" s="14" t="n"/>
-    </row>
-    <row r="100" ht="15" customHeight="1">
-      <c r="B100" s="52" t="inlineStr">
-        <is>
-          <t>Gross rental income (MG)</t>
-        </is>
-      </c>
-      <c r="F100" s="45">
-        <f>D51</f>
-        <v/>
-      </c>
-      <c r="G100" s="14" t="n"/>
-      <c r="H100" s="44">
-        <f>E51</f>
-        <v/>
-      </c>
-      <c r="I100" s="14" t="n"/>
-      <c r="J100" s="88">
-        <f>H100/C15</f>
-        <v/>
-      </c>
-      <c r="K100" s="13" t="n"/>
-      <c r="L100" s="13" t="n"/>
-      <c r="M100" s="14" t="n"/>
-    </row>
-    <row r="101" ht="15" customHeight="1">
-      <c r="B101" s="12" t="inlineStr">
-        <is>
-          <t>Less: credit &amp; vacancy loss</t>
-        </is>
-      </c>
-      <c r="F101" s="47">
-        <f>D52</f>
-        <v/>
-      </c>
-      <c r="G101" s="14" t="n"/>
-      <c r="H101" s="47">
-        <f>E52</f>
-        <v/>
-      </c>
-      <c r="I101" s="14" t="n"/>
-      <c r="J101" s="68">
-        <f>H101/C15</f>
-        <v/>
       </c>
       <c r="K101" s="13" t="n"/>
       <c r="L101" s="13" t="n"/>
       <c r="M101" s="14" t="n"/>
     </row>
     <row r="102" ht="15" customHeight="1">
-      <c r="B102" s="43" t="inlineStr">
-        <is>
-          <t>Effective Gross Income</t>
+      <c r="B102" s="52" t="inlineStr">
+        <is>
+          <t>Gross rental income (MG)</t>
         </is>
       </c>
       <c r="F102" s="45">
@@ -4583,7 +4729,7 @@
       </c>
       <c r="I102" s="14" t="n"/>
       <c r="J102" s="88">
-        <f>H102/C15</f>
+        <f>H102/C17</f>
         <v/>
       </c>
       <c r="K102" s="13" t="n"/>
@@ -4593,21 +4739,21 @@
     <row r="103" ht="15" customHeight="1">
       <c r="B103" s="12" t="inlineStr">
         <is>
-          <t>Real-estate taxes</t>
+          <t>Less: credit &amp; vacancy loss</t>
         </is>
       </c>
       <c r="F103" s="47">
-        <f>-D55</f>
+        <f>D54</f>
         <v/>
       </c>
       <c r="G103" s="14" t="n"/>
       <c r="H103" s="47">
-        <f>-E55</f>
+        <f>E54</f>
         <v/>
       </c>
       <c r="I103" s="14" t="n"/>
       <c r="J103" s="68">
-        <f>H103/C15</f>
+        <f>H103/C17</f>
         <v/>
       </c>
       <c r="K103" s="13" t="n"/>
@@ -4615,23 +4761,23 @@
       <c r="M103" s="14" t="n"/>
     </row>
     <row r="104" ht="15" customHeight="1">
-      <c r="B104" s="12" t="inlineStr">
-        <is>
-          <t>Office opex (landlord)</t>
-        </is>
-      </c>
-      <c r="F104" s="47">
-        <f>-D56</f>
+      <c r="B104" s="43" t="inlineStr">
+        <is>
+          <t>Effective Gross Income</t>
+        </is>
+      </c>
+      <c r="F104" s="45">
+        <f>D55</f>
         <v/>
       </c>
       <c r="G104" s="14" t="n"/>
-      <c r="H104" s="47">
-        <f>-E56</f>
+      <c r="H104" s="44">
+        <f>E55</f>
         <v/>
       </c>
       <c r="I104" s="14" t="n"/>
-      <c r="J104" s="68">
-        <f>H104/C15</f>
+      <c r="J104" s="88">
+        <f>H104/C17</f>
         <v/>
       </c>
       <c r="K104" s="13" t="n"/>
@@ -4641,7 +4787,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="B105" s="12" t="inlineStr">
         <is>
-          <t>Management fee</t>
+          <t>Real-estate taxes</t>
         </is>
       </c>
       <c r="F105" s="47">
@@ -4655,7 +4801,7 @@
       </c>
       <c r="I105" s="14" t="n"/>
       <c r="J105" s="68">
-        <f>H105/C15</f>
+        <f>H105/C17</f>
         <v/>
       </c>
       <c r="K105" s="13" t="n"/>
@@ -4663,23 +4809,23 @@
       <c r="M105" s="14" t="n"/>
     </row>
     <row r="106" ht="15" customHeight="1">
-      <c r="B106" s="43" t="inlineStr">
-        <is>
-          <t>Net Operating Income</t>
-        </is>
-      </c>
-      <c r="F106" s="45">
-        <f>D59</f>
+      <c r="B106" s="12" t="inlineStr">
+        <is>
+          <t>Office opex (landlord)</t>
+        </is>
+      </c>
+      <c r="F106" s="47">
+        <f>-D58</f>
         <v/>
       </c>
       <c r="G106" s="14" t="n"/>
-      <c r="H106" s="44">
-        <f>E59</f>
+      <c r="H106" s="47">
+        <f>-E58</f>
         <v/>
       </c>
       <c r="I106" s="14" t="n"/>
-      <c r="J106" s="88">
-        <f>H106/C15</f>
+      <c r="J106" s="68">
+        <f>H106/C17</f>
         <v/>
       </c>
       <c r="K106" s="13" t="n"/>
@@ -4689,21 +4835,21 @@
     <row r="107" ht="15" customHeight="1">
       <c r="B107" s="12" t="inlineStr">
         <is>
-          <t>Replacement reserves</t>
+          <t>Management fee</t>
         </is>
       </c>
       <c r="F107" s="47">
-        <f>-D60</f>
+        <f>-D59</f>
         <v/>
       </c>
       <c r="G107" s="14" t="n"/>
       <c r="H107" s="47">
-        <f>-E60</f>
+        <f>-E59</f>
         <v/>
       </c>
       <c r="I107" s="14" t="n"/>
       <c r="J107" s="68">
-        <f>H107/C15</f>
+        <f>H107/C17</f>
         <v/>
       </c>
       <c r="K107" s="13" t="n"/>
@@ -4713,7 +4859,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="B108" s="43" t="inlineStr">
         <is>
-          <t>Cash Flow Before Debt</t>
+          <t>Net Operating Income</t>
         </is>
       </c>
       <c r="F108" s="45">
@@ -4727,7 +4873,7 @@
       </c>
       <c r="I108" s="14" t="n"/>
       <c r="J108" s="88">
-        <f>H108/C15</f>
+        <f>H108/C17</f>
         <v/>
       </c>
       <c r="K108" s="13" t="n"/>
@@ -4737,21 +4883,21 @@
     <row r="109" ht="15" customHeight="1">
       <c r="B109" s="12" t="inlineStr">
         <is>
-          <t>Debt service</t>
+          <t>Replacement reserves</t>
         </is>
       </c>
       <c r="F109" s="47">
-        <f>-C41</f>
+        <f>-D62</f>
         <v/>
       </c>
       <c r="G109" s="14" t="n"/>
       <c r="H109" s="47">
-        <f>-C41</f>
+        <f>-E62</f>
         <v/>
       </c>
       <c r="I109" s="14" t="n"/>
       <c r="J109" s="68">
-        <f>H109/C15</f>
+        <f>H109/C17</f>
         <v/>
       </c>
       <c r="K109" s="13" t="n"/>
@@ -4761,116 +4907,174 @@
     <row r="110" ht="15" customHeight="1">
       <c r="B110" s="43" t="inlineStr">
         <is>
-          <t>Cash Flow After Debt (levered)</t>
-        </is>
-      </c>
-      <c r="F110" s="44">
-        <f>F108-C41</f>
+          <t>Cash Flow Before Debt</t>
+        </is>
+      </c>
+      <c r="F110" s="45">
+        <f>D63</f>
         <v/>
       </c>
       <c r="G110" s="14" t="n"/>
       <c r="H110" s="44">
-        <f>H108-C41</f>
+        <f>E63</f>
         <v/>
       </c>
       <c r="I110" s="14" t="n"/>
       <c r="J110" s="88">
-        <f>H110/C15</f>
+        <f>H110/C17</f>
         <v/>
       </c>
       <c r="K110" s="13" t="n"/>
       <c r="L110" s="13" t="n"/>
       <c r="M110" s="14" t="n"/>
     </row>
+    <row r="111" ht="15" customHeight="1">
+      <c r="B111" s="12" t="inlineStr">
+        <is>
+          <t>Debt service</t>
+        </is>
+      </c>
+      <c r="F111" s="47">
+        <f>-C43</f>
+        <v/>
+      </c>
+      <c r="G111" s="14" t="n"/>
+      <c r="H111" s="47">
+        <f>-C43</f>
+        <v/>
+      </c>
+      <c r="I111" s="14" t="n"/>
+      <c r="J111" s="68">
+        <f>H111/C17</f>
+        <v/>
+      </c>
+      <c r="K111" s="13" t="n"/>
+      <c r="L111" s="13" t="n"/>
+      <c r="M111" s="14" t="n"/>
+    </row>
+    <row r="112" ht="15" customHeight="1">
+      <c r="B112" s="43" t="inlineStr">
+        <is>
+          <t>Cash Flow After Debt (levered)</t>
+        </is>
+      </c>
+      <c r="F112" s="44">
+        <f>F110-C43</f>
+        <v/>
+      </c>
+      <c r="G112" s="14" t="n"/>
+      <c r="H112" s="44">
+        <f>H110-C43</f>
+        <v/>
+      </c>
+      <c r="I112" s="14" t="n"/>
+      <c r="J112" s="88">
+        <f>H112/C17</f>
+        <v/>
+      </c>
+      <c r="K112" s="13" t="n"/>
+      <c r="L112" s="13" t="n"/>
+      <c r="M112" s="14" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="90">
+  <mergeCells count="100">
+    <mergeCell ref="B91:C91"/>
     <mergeCell ref="B2:M2"/>
+    <mergeCell ref="D37:M37"/>
     <mergeCell ref="D12:M12"/>
+    <mergeCell ref="J96:M96"/>
     <mergeCell ref="D9:M9"/>
     <mergeCell ref="F103:G103"/>
     <mergeCell ref="J105:M105"/>
-    <mergeCell ref="I86:M86"/>
-    <mergeCell ref="D92:M92"/>
+    <mergeCell ref="F108:G108"/>
     <mergeCell ref="D30:M30"/>
-    <mergeCell ref="D39:M39"/>
-    <mergeCell ref="F108:G108"/>
+    <mergeCell ref="B93:C93"/>
     <mergeCell ref="J106:M106"/>
+    <mergeCell ref="D14:M14"/>
     <mergeCell ref="D29:M29"/>
     <mergeCell ref="D23:M23"/>
-    <mergeCell ref="B86:C86"/>
     <mergeCell ref="H108:I108"/>
-    <mergeCell ref="I87:M87"/>
     <mergeCell ref="F105:G105"/>
     <mergeCell ref="D27:M27"/>
-    <mergeCell ref="I88:M88"/>
-    <mergeCell ref="B54:M54"/>
     <mergeCell ref="H105:I105"/>
+    <mergeCell ref="D41:M41"/>
+    <mergeCell ref="B72:M72"/>
     <mergeCell ref="J108:M108"/>
     <mergeCell ref="D17:M17"/>
+    <mergeCell ref="J95:M95"/>
     <mergeCell ref="F107:G107"/>
     <mergeCell ref="H107:I107"/>
-    <mergeCell ref="B98:M98"/>
+    <mergeCell ref="B56:M56"/>
+    <mergeCell ref="B90:C90"/>
     <mergeCell ref="J109:M109"/>
     <mergeCell ref="D25:M25"/>
-    <mergeCell ref="F99:G99"/>
+    <mergeCell ref="J90:M90"/>
     <mergeCell ref="H102:I102"/>
     <mergeCell ref="D5:M5"/>
     <mergeCell ref="J110:M110"/>
+    <mergeCell ref="J93:M93"/>
     <mergeCell ref="F109:G109"/>
     <mergeCell ref="D31:M31"/>
     <mergeCell ref="H109:I109"/>
     <mergeCell ref="J102:M102"/>
-    <mergeCell ref="B85:M85"/>
     <mergeCell ref="D21:M21"/>
-    <mergeCell ref="J99:M99"/>
-    <mergeCell ref="D95:M95"/>
+    <mergeCell ref="F111:G111"/>
     <mergeCell ref="B4:M4"/>
+    <mergeCell ref="H111:I111"/>
     <mergeCell ref="D32:M32"/>
     <mergeCell ref="J101:M101"/>
     <mergeCell ref="H104:I104"/>
-    <mergeCell ref="B46:M46"/>
+    <mergeCell ref="B95:C95"/>
     <mergeCell ref="B89:C89"/>
     <mergeCell ref="D7:M7"/>
-    <mergeCell ref="D16:M16"/>
-    <mergeCell ref="J100:M100"/>
+    <mergeCell ref="J94:M94"/>
     <mergeCell ref="H106:I106"/>
-    <mergeCell ref="B70:M70"/>
+    <mergeCell ref="B97:C97"/>
+    <mergeCell ref="B48:M48"/>
     <mergeCell ref="D18:M18"/>
     <mergeCell ref="D8:M8"/>
+    <mergeCell ref="B96:C96"/>
+    <mergeCell ref="B87:M87"/>
+    <mergeCell ref="J97:M97"/>
     <mergeCell ref="D35:M35"/>
+    <mergeCell ref="B98:C98"/>
+    <mergeCell ref="J111:M111"/>
     <mergeCell ref="D20:M20"/>
     <mergeCell ref="D34:M34"/>
-    <mergeCell ref="B88:C88"/>
     <mergeCell ref="F101:G101"/>
+    <mergeCell ref="B65:M65"/>
     <mergeCell ref="F110:G110"/>
     <mergeCell ref="H110:I110"/>
-    <mergeCell ref="F100:G100"/>
     <mergeCell ref="D22:M22"/>
-    <mergeCell ref="H100:I100"/>
     <mergeCell ref="D36:M36"/>
-    <mergeCell ref="B63:M63"/>
     <mergeCell ref="D6:M6"/>
-    <mergeCell ref="E96:M96"/>
     <mergeCell ref="F102:G102"/>
-    <mergeCell ref="B91:M91"/>
+    <mergeCell ref="D13:M13"/>
+    <mergeCell ref="B92:C92"/>
+    <mergeCell ref="B100:M100"/>
+    <mergeCell ref="B94:C94"/>
     <mergeCell ref="J103:M103"/>
+    <mergeCell ref="J91:M91"/>
     <mergeCell ref="H103:I103"/>
-    <mergeCell ref="I89:M89"/>
-    <mergeCell ref="B14:M14"/>
-    <mergeCell ref="D15:M15"/>
+    <mergeCell ref="F112:G112"/>
+    <mergeCell ref="H112:I112"/>
     <mergeCell ref="B1:M1"/>
     <mergeCell ref="D24:M24"/>
+    <mergeCell ref="D38:M38"/>
     <mergeCell ref="D33:M33"/>
-    <mergeCell ref="B38:M38"/>
+    <mergeCell ref="J92:M92"/>
+    <mergeCell ref="D88:M88"/>
     <mergeCell ref="F104:G104"/>
     <mergeCell ref="D26:M26"/>
+    <mergeCell ref="B40:M40"/>
     <mergeCell ref="D10:M10"/>
+    <mergeCell ref="J112:M112"/>
     <mergeCell ref="D19:M19"/>
     <mergeCell ref="F106:G106"/>
-    <mergeCell ref="B87:C87"/>
-    <mergeCell ref="H99:I99"/>
     <mergeCell ref="D11:M11"/>
     <mergeCell ref="J107:M107"/>
+    <mergeCell ref="J89:M89"/>
+    <mergeCell ref="B16:M16"/>
     <mergeCell ref="H101:I101"/>
     <mergeCell ref="J104:M104"/>
     <mergeCell ref="D28:M28"/>
@@ -9960,7 +10164,7 @@
         </is>
       </c>
       <c r="C124" s="39">
-        <f>'Office Condo'!C15</f>
+        <f>'Office Condo'!C17</f>
         <v/>
       </c>
       <c r="D124" s="30" t="inlineStr">
@@ -9989,7 +10193,7 @@
         </is>
       </c>
       <c r="C125" s="39">
-        <f>'Office Condo'!D87</f>
+        <f>'Office Condo'!D90</f>
         <v/>
       </c>
       <c r="D125" s="30" t="inlineStr">
@@ -10018,7 +10222,7 @@
         </is>
       </c>
       <c r="C126" s="39">
-        <f>'Office Condo'!D88</f>
+        <f>'Office Condo'!D91</f>
         <v/>
       </c>
       <c r="D126" s="30" t="inlineStr">
@@ -10709,43 +10913,43 @@
         </is>
       </c>
       <c r="D17" s="23">
-        <f>'Office Condo'!D59</f>
+        <f>'Office Condo'!D61</f>
         <v/>
       </c>
       <c r="E17" s="17">
-        <f>'Office Condo'!E59</f>
+        <f>'Office Condo'!E61</f>
         <v/>
       </c>
       <c r="F17" s="17">
-        <f>'Office Condo'!F59</f>
+        <f>'Office Condo'!F61</f>
         <v/>
       </c>
       <c r="G17" s="17">
-        <f>'Office Condo'!G59</f>
+        <f>'Office Condo'!G61</f>
         <v/>
       </c>
       <c r="H17" s="17">
-        <f>'Office Condo'!H59</f>
+        <f>'Office Condo'!H61</f>
         <v/>
       </c>
       <c r="I17" s="17">
-        <f>'Office Condo'!I59</f>
+        <f>'Office Condo'!I61</f>
         <v/>
       </c>
       <c r="J17" s="17">
-        <f>'Office Condo'!J59</f>
+        <f>'Office Condo'!J61</f>
         <v/>
       </c>
       <c r="K17" s="17">
-        <f>'Office Condo'!K59</f>
+        <f>'Office Condo'!K61</f>
         <v/>
       </c>
       <c r="L17" s="17">
-        <f>'Office Condo'!L59</f>
+        <f>'Office Condo'!L61</f>
         <v/>
       </c>
       <c r="M17" s="17">
-        <f>'Office Condo'!M59</f>
+        <f>'Office Condo'!M61</f>
         <v/>
       </c>
     </row>
@@ -10850,43 +11054,43 @@
         </is>
       </c>
       <c r="D20" s="17">
-        <f>-('Shahidi Retail'!D104+'Publix &amp; Starbucks'!D91+'Sunrise Plaza'!D94+'Office Condo'!D60)</f>
+        <f>-('Shahidi Retail'!D104+'Publix &amp; Starbucks'!D91+'Sunrise Plaza'!D94+'Office Condo'!D62)</f>
         <v/>
       </c>
       <c r="E20" s="17">
-        <f>-('Shahidi Retail'!E104+'Publix &amp; Starbucks'!E91+'Sunrise Plaza'!E94+'Office Condo'!E60)</f>
+        <f>-('Shahidi Retail'!E104+'Publix &amp; Starbucks'!E91+'Sunrise Plaza'!E94+'Office Condo'!E62)</f>
         <v/>
       </c>
       <c r="F20" s="17">
-        <f>-('Shahidi Retail'!F104+'Publix &amp; Starbucks'!F91+'Sunrise Plaza'!F94+'Office Condo'!F60)</f>
+        <f>-('Shahidi Retail'!F104+'Publix &amp; Starbucks'!F91+'Sunrise Plaza'!F94+'Office Condo'!F62)</f>
         <v/>
       </c>
       <c r="G20" s="17">
-        <f>-('Shahidi Retail'!G104+'Publix &amp; Starbucks'!G91+'Sunrise Plaza'!G94+'Office Condo'!G60)</f>
+        <f>-('Shahidi Retail'!G104+'Publix &amp; Starbucks'!G91+'Sunrise Plaza'!G94+'Office Condo'!G62)</f>
         <v/>
       </c>
       <c r="H20" s="17">
-        <f>-('Shahidi Retail'!H104+'Publix &amp; Starbucks'!H91+'Sunrise Plaza'!H94+'Office Condo'!H60)</f>
+        <f>-('Shahidi Retail'!H104+'Publix &amp; Starbucks'!H91+'Sunrise Plaza'!H94+'Office Condo'!H62)</f>
         <v/>
       </c>
       <c r="I20" s="17">
-        <f>-('Shahidi Retail'!I104+'Publix &amp; Starbucks'!I91+'Sunrise Plaza'!I94+'Office Condo'!I60)</f>
+        <f>-('Shahidi Retail'!I104+'Publix &amp; Starbucks'!I91+'Sunrise Plaza'!I94+'Office Condo'!I62)</f>
         <v/>
       </c>
       <c r="J20" s="17">
-        <f>-('Shahidi Retail'!J104+'Publix &amp; Starbucks'!J91+'Sunrise Plaza'!J94+'Office Condo'!J60)</f>
+        <f>-('Shahidi Retail'!J104+'Publix &amp; Starbucks'!J91+'Sunrise Plaza'!J94+'Office Condo'!J62)</f>
         <v/>
       </c>
       <c r="K20" s="17">
-        <f>-('Shahidi Retail'!K104+'Publix &amp; Starbucks'!K91+'Sunrise Plaza'!K94+'Office Condo'!K60)</f>
+        <f>-('Shahidi Retail'!K104+'Publix &amp; Starbucks'!K91+'Sunrise Plaza'!K94+'Office Condo'!K62)</f>
         <v/>
       </c>
       <c r="L20" s="17">
-        <f>-('Shahidi Retail'!L104+'Publix &amp; Starbucks'!L91+'Sunrise Plaza'!L94+'Office Condo'!L60)</f>
+        <f>-('Shahidi Retail'!L104+'Publix &amp; Starbucks'!L91+'Sunrise Plaza'!L94+'Office Condo'!L62)</f>
         <v/>
       </c>
       <c r="M20" s="17">
-        <f>-('Shahidi Retail'!M104+'Publix &amp; Starbucks'!M91+'Sunrise Plaza'!M94+'Office Condo'!M60)</f>
+        <f>-('Shahidi Retail'!M104+'Publix &amp; Starbucks'!M91+'Sunrise Plaza'!M94+'Office Condo'!M62)</f>
         <v/>
       </c>
     </row>
@@ -10944,43 +11148,43 @@
         </is>
       </c>
       <c r="D22" s="17">
-        <f>'Shahidi Retail'!D108+'Publix &amp; Starbucks'!D95+'Sunrise Plaza'!D98+'Office Condo'!D64+'Land'!D59</f>
+        <f>'Shahidi Retail'!D108+'Publix &amp; Starbucks'!D95+'Sunrise Plaza'!D98+'Office Condo'!D66+'Land'!D59</f>
         <v/>
       </c>
       <c r="E22" s="17">
-        <f>'Shahidi Retail'!E108+'Publix &amp; Starbucks'!E95+'Sunrise Plaza'!E98+'Office Condo'!E64+'Land'!E59</f>
+        <f>'Shahidi Retail'!E108+'Publix &amp; Starbucks'!E95+'Sunrise Plaza'!E98+'Office Condo'!E66+'Land'!E59</f>
         <v/>
       </c>
       <c r="F22" s="17">
-        <f>'Shahidi Retail'!F108+'Publix &amp; Starbucks'!F95+'Sunrise Plaza'!F98+'Office Condo'!F64+'Land'!F59</f>
+        <f>'Shahidi Retail'!F108+'Publix &amp; Starbucks'!F95+'Sunrise Plaza'!F98+'Office Condo'!F66+'Land'!F59</f>
         <v/>
       </c>
       <c r="G22" s="17">
-        <f>'Shahidi Retail'!G108+'Publix &amp; Starbucks'!G95+'Sunrise Plaza'!G98+'Office Condo'!G64+'Land'!G59</f>
+        <f>'Shahidi Retail'!G108+'Publix &amp; Starbucks'!G95+'Sunrise Plaza'!G98+'Office Condo'!G66+'Land'!G59</f>
         <v/>
       </c>
       <c r="H22" s="17">
-        <f>'Shahidi Retail'!H108+'Publix &amp; Starbucks'!H95+'Sunrise Plaza'!H98+'Office Condo'!H64+'Land'!H59</f>
+        <f>'Shahidi Retail'!H108+'Publix &amp; Starbucks'!H95+'Sunrise Plaza'!H98+'Office Condo'!H66+'Land'!H59</f>
         <v/>
       </c>
       <c r="I22" s="17">
-        <f>'Shahidi Retail'!I108+'Publix &amp; Starbucks'!I95+'Sunrise Plaza'!I98+'Office Condo'!I64+'Land'!I59</f>
+        <f>'Shahidi Retail'!I108+'Publix &amp; Starbucks'!I95+'Sunrise Plaza'!I98+'Office Condo'!I66+'Land'!I59</f>
         <v/>
       </c>
       <c r="J22" s="17">
-        <f>'Shahidi Retail'!J108+'Publix &amp; Starbucks'!J95+'Sunrise Plaza'!J98+'Office Condo'!J64+'Land'!J59</f>
+        <f>'Shahidi Retail'!J108+'Publix &amp; Starbucks'!J95+'Sunrise Plaza'!J98+'Office Condo'!J66+'Land'!J59</f>
         <v/>
       </c>
       <c r="K22" s="17">
-        <f>'Shahidi Retail'!K108+'Publix &amp; Starbucks'!K95+'Sunrise Plaza'!K98+'Office Condo'!K64+'Land'!K59</f>
+        <f>'Shahidi Retail'!K108+'Publix &amp; Starbucks'!K95+'Sunrise Plaza'!K98+'Office Condo'!K66+'Land'!K59</f>
         <v/>
       </c>
       <c r="L22" s="17">
-        <f>'Shahidi Retail'!L108+'Publix &amp; Starbucks'!L95+'Sunrise Plaza'!L98+'Office Condo'!L64+'Land'!L59</f>
+        <f>'Shahidi Retail'!L108+'Publix &amp; Starbucks'!L95+'Sunrise Plaza'!L98+'Office Condo'!L66+'Land'!L59</f>
         <v/>
       </c>
       <c r="M22" s="17">
-        <f>'Shahidi Retail'!M108+'Publix &amp; Starbucks'!M95+'Sunrise Plaza'!M98+'Office Condo'!M64+'Land'!M59</f>
+        <f>'Shahidi Retail'!M108+'Publix &amp; Starbucks'!M95+'Sunrise Plaza'!M98+'Office Condo'!M66+'Land'!M59</f>
         <v/>
       </c>
     </row>
@@ -11010,7 +11214,7 @@
         </is>
       </c>
       <c r="C25" s="46">
-        <f>'Shahidi Retail'!C122+'Publix &amp; Starbucks'!C110+'Sunrise Plaza'!C113+'Office Condo'!C77+'Land'!C47</f>
+        <f>'Shahidi Retail'!C122+'Publix &amp; Starbucks'!C110+'Sunrise Plaza'!C113+'Office Condo'!C79+'Land'!C47</f>
         <v/>
       </c>
       <c r="D25" s="22" t="inlineStr">
@@ -11035,7 +11239,7 @@
         </is>
       </c>
       <c r="C26" s="46">
-        <f>'Shahidi Retail'!C124+'Publix &amp; Starbucks'!C112+'Sunrise Plaza'!C115+'Office Condo'!C79+'Land'!C47</f>
+        <f>'Shahidi Retail'!C124+'Publix &amp; Starbucks'!C112+'Sunrise Plaza'!C115+'Office Condo'!C81+'Land'!C47</f>
         <v/>
       </c>
       <c r="D26" s="22" t="inlineStr">
@@ -14420,11 +14624,11 @@
         </is>
       </c>
       <c r="C15" s="17">
-        <f>'Office Condo'!C95</f>
+        <f>'Office Condo'!I97</f>
         <v/>
       </c>
       <c r="D15" s="17">
-        <f>'Office Condo'!C76</f>
+        <f>'Office Condo'!C78</f>
         <v/>
       </c>
       <c r="E15" s="50">
@@ -14439,11 +14643,11 @@
         <v/>
       </c>
       <c r="H15" s="18">
-        <f>'Office Condo'!C71</f>
+        <f>'Office Condo'!C73</f>
         <v/>
       </c>
       <c r="I15" s="18">
-        <f>'Office Condo'!C74</f>
+        <f>'Office Condo'!C76</f>
         <v/>
       </c>
       <c r="J15" s="12" t="inlineStr">
@@ -14833,7 +15037,7 @@
         </is>
       </c>
       <c r="C36" s="51">
-        <f>'Shahidi Retail'!C78+'Publix &amp; Starbucks'!C65+'Sunrise Plaza'!C68+'Office Condo'!C44+'Land'!C52</f>
+        <f>'Shahidi Retail'!C78+'Publix &amp; Starbucks'!C65+'Sunrise Plaza'!C68+'Office Condo'!C46+'Land'!C52</f>
         <v/>
       </c>
     </row>
@@ -15088,7 +15292,7 @@
         </is>
       </c>
       <c r="C9" s="17">
-        <f>'Office Condo'!C95</f>
+        <f>'Office Condo'!I97</f>
         <v/>
       </c>
       <c r="E9" s="22" t="inlineStr">
@@ -15366,7 +15570,7 @@
         <v>10000000</v>
       </c>
       <c r="E20" s="17">
-        <f>'Office Condo'!C93</f>
+        <f>'Office Condo'!I90</f>
         <v/>
       </c>
       <c r="F20" s="22" t="inlineStr">
@@ -15399,7 +15603,7 @@
         </is>
       </c>
       <c r="E21" s="17">
-        <f>'Office Condo'!C94</f>
+        <f>'Office Condo'!I91</f>
         <v/>
       </c>
       <c r="F21" s="22" t="inlineStr">
@@ -15888,7 +16092,7 @@
         </is>
       </c>
       <c r="C44" s="17">
-        <f>'Office Condo'!C93</f>
+        <f>'Office Condo'!I90</f>
         <v/>
       </c>
       <c r="E44" s="22" t="inlineStr">
@@ -15912,7 +16116,7 @@
         </is>
       </c>
       <c r="C45" s="17">
-        <f>'Office Condo'!C94</f>
+        <f>'Office Condo'!I91</f>
         <v/>
       </c>
       <c r="E45" s="22" t="inlineStr">
@@ -15936,7 +16140,7 @@
         </is>
       </c>
       <c r="C46" s="56">
-        <f>'Office Condo'!C95</f>
+        <f>'Office Condo'!I97</f>
         <v/>
       </c>
       <c r="E46" s="22" t="inlineStr">

--- a/Shahidi_Assemblage_Model.xlsx
+++ b/Shahidi_Assemblage_Model.xlsx
@@ -306,7 +306,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="95">
+  <cellXfs count="94">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -519,6 +519,9 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="3" fontId="12" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
@@ -567,9 +570,6 @@
     <xf numFmtId="165" fontId="6" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="3" fontId="3" fillId="7" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
@@ -578,9 +578,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1385,20 +1382,20 @@
       <c r="E21" s="13" t="n"/>
       <c r="F21" s="14" t="n"/>
       <c r="G21" s="17">
-        <f>'Office Condo'!I97</f>
+        <f>'Office Condo'!I99</f>
         <v/>
       </c>
       <c r="H21" s="17">
-        <f>'Office Condo'!C78</f>
+        <f>'Office Condo'!C79</f>
         <v/>
       </c>
       <c r="I21" s="14" t="n"/>
       <c r="J21" s="18">
-        <f>'Office Condo'!C73</f>
+        <f>'Office Condo'!C74</f>
         <v/>
       </c>
       <c r="K21" s="18">
-        <f>'Office Condo'!C76</f>
+        <f>'Office Condo'!C77</f>
         <v/>
       </c>
       <c r="L21" s="13" t="n"/>
@@ -1614,7 +1611,7 @@
         </is>
       </c>
       <c r="C31" s="23">
-        <f>'Office Condo'!I97</f>
+        <f>'Office Condo'!I99</f>
         <v/>
       </c>
       <c r="D31" s="22" t="inlineStr">
@@ -2166,7 +2163,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M112"/>
+  <dimension ref="A1:M115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.5" customWidth="1" min="1" max="1"/>
@@ -2394,7 +2391,7 @@
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
-          <t>Fractured condo: Main St Fund (Grove Gate) held 57.4% and is NOW RESELLING units individually; the balance is International Sunrise + a growing number of small owners (Jorgensen, Hublot, Merrimac, individual suites)</t>
+          <t>Fractured condo: Main St Fund (Grove Gate) holds ~57.4% and is NOW RESELLING units at $270–381/SF; the 42.6% balance is ~40 individual owners (Merrimac/Motwani, Cosmo/Blaison, Jorgensen, Hublot, single suites). International Sunrise Partners = the 2011 converter/seller, DISSOLVED 2020 — not a current owner</t>
         </is>
       </c>
       <c r="E12" s="13" t="n"/>
@@ -2407,15 +2404,15 @@
       <c r="L12" s="13" t="n"/>
       <c r="M12" s="14" t="n"/>
     </row>
-    <row r="13" ht="15" customHeight="1">
+    <row r="13" ht="27" customHeight="1">
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>Buy-out note</t>
+          <t>Control / who to approach</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>Assembling the building = buying out EVERY unit owner (modeled individually below; the un-itemizable balance is grouped)</t>
+          <t>Bradley Weiss (Grove Gate) controls the majority AND the condo board (3 of ~5 seats); gatekeeper is attorney Neale Poller (Ste 200, in the building). Merrimac → Dev &amp; Nitin Motwani; Cosmo → Marc Blaison (board president)</t>
         </is>
       </c>
       <c r="E13" s="13" t="n"/>
@@ -2428,15 +2425,15 @@
       <c r="L13" s="13" t="n"/>
       <c r="M13" s="14" t="n"/>
     </row>
-    <row r="14" ht="27" customHeight="1">
+    <row r="14" ht="15" customHeight="1">
       <c r="B14" s="12" t="inlineStr">
         <is>
-          <t>⚠️ BCPA limitation</t>
+          <t>Buy-out note</t>
         </is>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
-          <t>bcpa.net and the Broward Clerk are egress-blocked in this build; the complete per-unit folio roster (every unit, owner, price, date) needs a direct BCPA pull to finish</t>
+          <t>Assembling the building = buying out EVERY unit owner at unit-market $/SF (modeled individually below; un-itemizable balance grouped)</t>
         </is>
       </c>
       <c r="E14" s="13" t="n"/>
@@ -2449,62 +2446,58 @@
       <c r="L14" s="13" t="n"/>
       <c r="M14" s="14" t="n"/>
     </row>
-    <row r="15"/>
-    <row r="16">
-      <c r="B16" s="11" t="inlineStr">
+    <row r="15" ht="27" customHeight="1">
+      <c r="B15" s="12" t="inlineStr">
+        <is>
+          <t>⚠️ BCPA limitation</t>
+        </is>
+      </c>
+      <c r="D15" s="12" t="inlineStr">
+        <is>
+          <t>bcpa.net and the Broward Clerk are egress-blocked here; the complete per-unit folio roster needs a direct BCPA pull. Entity/owner data above is from Sunbiz/press via web search</t>
+        </is>
+      </c>
+      <c r="E15" s="13" t="n"/>
+      <c r="F15" s="13" t="n"/>
+      <c r="G15" s="13" t="n"/>
+      <c r="H15" s="13" t="n"/>
+      <c r="I15" s="13" t="n"/>
+      <c r="J15" s="13" t="n"/>
+      <c r="K15" s="13" t="n"/>
+      <c r="L15" s="13" t="n"/>
+      <c r="M15" s="14" t="n"/>
+    </row>
+    <row r="16"/>
+    <row r="17">
+      <c r="B17" s="11" t="inlineStr">
         <is>
           <t>ASSUMPTIONS  —  🔵 blue = hardcoded inputs (Modified-Gross office)</t>
         </is>
       </c>
-      <c r="C16" s="2" t="n"/>
-      <c r="D16" s="2" t="n"/>
-      <c r="E16" s="2" t="n"/>
-      <c r="F16" s="2" t="n"/>
-      <c r="G16" s="2" t="n"/>
-      <c r="H16" s="2" t="n"/>
-      <c r="I16" s="2" t="n"/>
-      <c r="J16" s="2" t="n"/>
-      <c r="K16" s="2" t="n"/>
-      <c r="L16" s="2" t="n"/>
-      <c r="M16" s="3" t="n"/>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="B17" s="12" t="inlineStr">
-        <is>
-          <t>Rentable SF (both owners)</t>
-        </is>
-      </c>
-      <c r="C17" s="77" t="n">
-        <v>168807</v>
-      </c>
-      <c r="D17" s="22" t="inlineStr">
-        <is>
-          <t>⚠️ ~168,807 SF</t>
-        </is>
-      </c>
-      <c r="E17" s="13" t="n"/>
-      <c r="F17" s="13" t="n"/>
-      <c r="G17" s="13" t="n"/>
-      <c r="H17" s="13" t="n"/>
-      <c r="I17" s="13" t="n"/>
-      <c r="J17" s="13" t="n"/>
-      <c r="K17" s="13" t="n"/>
-      <c r="L17" s="13" t="n"/>
-      <c r="M17" s="14" t="n"/>
+      <c r="C17" s="2" t="n"/>
+      <c r="D17" s="2" t="n"/>
+      <c r="E17" s="2" t="n"/>
+      <c r="F17" s="2" t="n"/>
+      <c r="G17" s="2" t="n"/>
+      <c r="H17" s="2" t="n"/>
+      <c r="I17" s="2" t="n"/>
+      <c r="J17" s="2" t="n"/>
+      <c r="K17" s="2" t="n"/>
+      <c r="L17" s="2" t="n"/>
+      <c r="M17" s="3" t="n"/>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="B18" s="12" t="inlineStr">
         <is>
-          <t>In-place occupancy</t>
-        </is>
-      </c>
-      <c r="C18" s="18">
-        <f>'Assumptions'!C101</f>
-        <v/>
+          <t>Rentable SF (both owners)</t>
+        </is>
+      </c>
+      <c r="C18" s="78" t="n">
+        <v>168807</v>
       </c>
       <c r="D18" s="22" t="inlineStr">
         <is>
-          <t>🟢 Assumptions</t>
+          <t>⚠️ ~168,807 SF</t>
         </is>
       </c>
       <c r="E18" s="13" t="n"/>
@@ -2520,11 +2513,11 @@
     <row r="19" ht="15" customHeight="1">
       <c r="B19" s="12" t="inlineStr">
         <is>
-          <t>Stabilized occupancy</t>
+          <t>In-place occupancy</t>
         </is>
       </c>
       <c r="C19" s="18">
-        <f>'Assumptions'!C102</f>
+        <f>'Assumptions'!C101</f>
         <v/>
       </c>
       <c r="D19" s="22" t="inlineStr">
@@ -2545,11 +2538,11 @@
     <row r="20" ht="15" customHeight="1">
       <c r="B20" s="12" t="inlineStr">
         <is>
-          <t>Market rent ($/SF Modified Gross)</t>
-        </is>
-      </c>
-      <c r="C20" s="26">
-        <f>'Assumptions'!C100</f>
+          <t>Stabilized occupancy</t>
+        </is>
+      </c>
+      <c r="C20" s="18">
+        <f>'Assumptions'!C102</f>
         <v/>
       </c>
       <c r="D20" s="22" t="inlineStr">
@@ -2570,15 +2563,16 @@
     <row r="21" ht="15" customHeight="1">
       <c r="B21" s="12" t="inlineStr">
         <is>
-          <t>Rent growth</t>
-        </is>
-      </c>
-      <c r="C21" s="84" t="n">
-        <v>0.03</v>
+          <t>Market rent ($/SF Modified Gross)</t>
+        </is>
+      </c>
+      <c r="C21" s="26">
+        <f>'Assumptions'!C100</f>
+        <v/>
       </c>
       <c r="D21" s="22" t="inlineStr">
         <is>
-          <t>🔶</t>
+          <t>🟢 Assumptions</t>
         </is>
       </c>
       <c r="E21" s="13" t="n"/>
@@ -2594,10 +2588,10 @@
     <row r="22" ht="15" customHeight="1">
       <c r="B22" s="12" t="inlineStr">
         <is>
-          <t>Credit &amp; vacancy loss</t>
-        </is>
-      </c>
-      <c r="C22" s="84" t="n">
+          <t>Rent growth</t>
+        </is>
+      </c>
+      <c r="C22" s="85" t="n">
         <v>0.03</v>
       </c>
       <c r="D22" s="22" t="inlineStr">
@@ -2618,15 +2612,15 @@
     <row r="23" ht="15" customHeight="1">
       <c r="B23" s="12" t="inlineStr">
         <is>
-          <t>Effective millage</t>
-        </is>
-      </c>
-      <c r="C23" s="83" t="n">
-        <v>0.0191</v>
+          <t>Credit &amp; vacancy loss</t>
+        </is>
+      </c>
+      <c r="C23" s="85" t="n">
+        <v>0.03</v>
       </c>
       <c r="D23" s="22" t="inlineStr">
         <is>
-          <t>✅ area millage</t>
+          <t>🔶</t>
         </is>
       </c>
       <c r="E23" s="13" t="n"/>
@@ -2642,16 +2636,15 @@
     <row r="24" ht="15" customHeight="1">
       <c r="B24" s="12" t="inlineStr">
         <is>
-          <t>Office opex ex-taxes ($/SF, landlord)</t>
-        </is>
-      </c>
-      <c r="C24" s="26">
-        <f>'Assumptions'!C103</f>
-        <v/>
+          <t>Effective millage</t>
+        </is>
+      </c>
+      <c r="C24" s="84" t="n">
+        <v>0.0191</v>
       </c>
       <c r="D24" s="22" t="inlineStr">
         <is>
-          <t>🟢 Assumptions</t>
+          <t>✅ area millage</t>
         </is>
       </c>
       <c r="E24" s="13" t="n"/>
@@ -2667,11 +2660,11 @@
     <row r="25" ht="15" customHeight="1">
       <c r="B25" s="12" t="inlineStr">
         <is>
-          <t>Management fee (% EGR)</t>
-        </is>
-      </c>
-      <c r="C25" s="18">
-        <f>'Assumptions'!C104</f>
+          <t>Office opex ex-taxes ($/SF, landlord)</t>
+        </is>
+      </c>
+      <c r="C25" s="26">
+        <f>'Assumptions'!C103</f>
         <v/>
       </c>
       <c r="D25" s="22" t="inlineStr">
@@ -2692,15 +2685,16 @@
     <row r="26" ht="15" customHeight="1">
       <c r="B26" s="12" t="inlineStr">
         <is>
-          <t>Expense growth</t>
-        </is>
-      </c>
-      <c r="C26" s="84" t="n">
-        <v>0.03</v>
+          <t>Management fee (% EGR)</t>
+        </is>
+      </c>
+      <c r="C26" s="18">
+        <f>'Assumptions'!C104</f>
+        <v/>
       </c>
       <c r="D26" s="22" t="inlineStr">
         <is>
-          <t>🔶</t>
+          <t>🟢 Assumptions</t>
         </is>
       </c>
       <c r="E26" s="13" t="n"/>
@@ -2716,11 +2710,11 @@
     <row r="27" ht="15" customHeight="1">
       <c r="B27" s="12" t="inlineStr">
         <is>
-          <t>Replacement reserves ($/SF/yr)</t>
-        </is>
-      </c>
-      <c r="C27" s="78" t="n">
-        <v>0.2</v>
+          <t>Expense growth</t>
+        </is>
+      </c>
+      <c r="C27" s="85" t="n">
+        <v>0.03</v>
       </c>
       <c r="D27" s="22" t="inlineStr">
         <is>
@@ -2740,16 +2734,15 @@
     <row r="28" ht="15" customHeight="1">
       <c r="B28" s="12" t="inlineStr">
         <is>
-          <t>Acquisition basis (income value)</t>
-        </is>
-      </c>
-      <c r="C28" s="23">
-        <f>'Assumptions'!C99</f>
-        <v/>
+          <t>Replacement reserves ($/SF/yr)</t>
+        </is>
+      </c>
+      <c r="C28" s="79" t="n">
+        <v>0.2</v>
       </c>
       <c r="D28" s="22" t="inlineStr">
         <is>
-          <t>🟢 Assumptions</t>
+          <t>🔶</t>
         </is>
       </c>
       <c r="E28" s="13" t="n"/>
@@ -2765,15 +2758,16 @@
     <row r="29" ht="15" customHeight="1">
       <c r="B29" s="12" t="inlineStr">
         <is>
-          <t>Closing &amp; acq costs (% price)</t>
-        </is>
-      </c>
-      <c r="C29" s="84" t="n">
-        <v>0.02</v>
+          <t>Acquisition basis (income value)</t>
+        </is>
+      </c>
+      <c r="C29" s="23">
+        <f>'Assumptions'!C99</f>
+        <v/>
       </c>
       <c r="D29" s="22" t="inlineStr">
         <is>
-          <t>🔶</t>
+          <t>🟢 Assumptions</t>
         </is>
       </c>
       <c r="E29" s="13" t="n"/>
@@ -2789,16 +2783,15 @@
     <row r="30" ht="15" customHeight="1">
       <c r="B30" s="12" t="inlineStr">
         <is>
-          <t>Senior loan LTV</t>
-        </is>
-      </c>
-      <c r="C30" s="18">
-        <f>'Assumptions'!C107</f>
-        <v/>
+          <t>Closing &amp; acq costs (% price)</t>
+        </is>
+      </c>
+      <c r="C30" s="85" t="n">
+        <v>0.02</v>
       </c>
       <c r="D30" s="22" t="inlineStr">
         <is>
-          <t>🟢 Assumptions</t>
+          <t>🔶</t>
         </is>
       </c>
       <c r="E30" s="13" t="n"/>
@@ -2814,11 +2807,11 @@
     <row r="31" ht="15" customHeight="1">
       <c r="B31" s="12" t="inlineStr">
         <is>
-          <t>Senior loan rate</t>
-        </is>
-      </c>
-      <c r="C31" s="24">
-        <f>'Assumptions'!C108</f>
+          <t>Senior loan LTV</t>
+        </is>
+      </c>
+      <c r="C31" s="18">
+        <f>'Assumptions'!C107</f>
         <v/>
       </c>
       <c r="D31" s="22" t="inlineStr">
@@ -2839,15 +2832,16 @@
     <row r="32" ht="15" customHeight="1">
       <c r="B32" s="12" t="inlineStr">
         <is>
-          <t>Amortization (yrs)</t>
-        </is>
-      </c>
-      <c r="C32" s="86" t="n">
-        <v>30</v>
+          <t>Senior loan rate</t>
+        </is>
+      </c>
+      <c r="C32" s="24">
+        <f>'Assumptions'!C108</f>
+        <v/>
       </c>
       <c r="D32" s="22" t="inlineStr">
         <is>
-          <t>🔶</t>
+          <t>🟢 Assumptions</t>
         </is>
       </c>
       <c r="E32" s="13" t="n"/>
@@ -2863,16 +2857,15 @@
     <row r="33" ht="15" customHeight="1">
       <c r="B33" s="12" t="inlineStr">
         <is>
-          <t>Going-in cap</t>
-        </is>
-      </c>
-      <c r="C33" s="24">
-        <f>'Assumptions'!C105</f>
-        <v/>
+          <t>Amortization (yrs)</t>
+        </is>
+      </c>
+      <c r="C33" s="87" t="n">
+        <v>30</v>
       </c>
       <c r="D33" s="22" t="inlineStr">
         <is>
-          <t>🟢 Assumptions</t>
+          <t>🔶</t>
         </is>
       </c>
       <c r="E33" s="13" t="n"/>
@@ -2888,11 +2881,11 @@
     <row r="34" ht="15" customHeight="1">
       <c r="B34" s="12" t="inlineStr">
         <is>
-          <t>Exit cap</t>
+          <t>Going-in cap</t>
         </is>
       </c>
       <c r="C34" s="24">
-        <f>'Assumptions'!C106</f>
+        <f>'Assumptions'!C105</f>
         <v/>
       </c>
       <c r="D34" s="22" t="inlineStr">
@@ -2913,15 +2906,16 @@
     <row r="35" ht="15" customHeight="1">
       <c r="B35" s="12" t="inlineStr">
         <is>
-          <t>Cost of sale</t>
-        </is>
-      </c>
-      <c r="C35" s="84" t="n">
-        <v>0.02</v>
+          <t>Exit cap</t>
+        </is>
+      </c>
+      <c r="C35" s="24">
+        <f>'Assumptions'!C106</f>
+        <v/>
       </c>
       <c r="D35" s="22" t="inlineStr">
         <is>
-          <t>🔶</t>
+          <t>🟢 Assumptions</t>
         </is>
       </c>
       <c r="E35" s="13" t="n"/>
@@ -2937,11 +2931,11 @@
     <row r="36" ht="15" customHeight="1">
       <c r="B36" s="12" t="inlineStr">
         <is>
-          <t>Hold period (yrs)</t>
-        </is>
-      </c>
-      <c r="C36" s="86" t="n">
-        <v>5</v>
+          <t>Cost of sale</t>
+        </is>
+      </c>
+      <c r="C36" s="85" t="n">
+        <v>0.02</v>
       </c>
       <c r="D36" s="22" t="inlineStr">
         <is>
@@ -2961,11 +2955,11 @@
     <row r="37" ht="15" customHeight="1">
       <c r="B37" s="12" t="inlineStr">
         <is>
-          <t>Discount rate (NPV)</t>
-        </is>
-      </c>
-      <c r="C37" s="84" t="n">
-        <v>0.1</v>
+          <t>Hold period (yrs)</t>
+        </is>
+      </c>
+      <c r="C37" s="87" t="n">
+        <v>5</v>
       </c>
       <c r="D37" s="22" t="inlineStr">
         <is>
@@ -2985,15 +2979,15 @@
     <row r="38" ht="15" customHeight="1">
       <c r="B38" s="12" t="inlineStr">
         <is>
-          <t>Sale comp ($/SF)</t>
-        </is>
-      </c>
-      <c r="C38" s="78" t="n">
-        <v>300</v>
+          <t>Discount rate (NPV)</t>
+        </is>
+      </c>
+      <c r="C38" s="85" t="n">
+        <v>0.1</v>
       </c>
       <c r="D38" s="22" t="inlineStr">
         <is>
-          <t>⚠️ historical ~$300/SF</t>
+          <t>🔶</t>
         </is>
       </c>
       <c r="E38" s="13" t="n"/>
@@ -3006,1360 +3000,1345 @@
       <c r="L38" s="13" t="n"/>
       <c r="M38" s="14" t="n"/>
     </row>
-    <row r="39"/>
-    <row r="40">
-      <c r="B40" s="11" t="inlineStr">
+    <row r="39" ht="15" customHeight="1">
+      <c r="B39" s="12" t="inlineStr">
+        <is>
+          <t>Sale comp ($/SF)</t>
+        </is>
+      </c>
+      <c r="C39" s="79" t="n">
+        <v>300</v>
+      </c>
+      <c r="D39" s="22" t="inlineStr">
+        <is>
+          <t>⚠️ historical ~$300/SF</t>
+        </is>
+      </c>
+      <c r="E39" s="13" t="n"/>
+      <c r="F39" s="13" t="n"/>
+      <c r="G39" s="13" t="n"/>
+      <c r="H39" s="13" t="n"/>
+      <c r="I39" s="13" t="n"/>
+      <c r="J39" s="13" t="n"/>
+      <c r="K39" s="13" t="n"/>
+      <c r="L39" s="13" t="n"/>
+      <c r="M39" s="14" t="n"/>
+    </row>
+    <row r="40"/>
+    <row r="41">
+      <c r="B41" s="11" t="inlineStr">
         <is>
           <t>DERIVED VALUES  &amp;  DEBT SIZING</t>
         </is>
       </c>
-      <c r="C40" s="2" t="n"/>
-      <c r="D40" s="2" t="n"/>
-      <c r="E40" s="2" t="n"/>
-      <c r="F40" s="2" t="n"/>
-      <c r="G40" s="2" t="n"/>
-      <c r="H40" s="2" t="n"/>
-      <c r="I40" s="2" t="n"/>
-      <c r="J40" s="2" t="n"/>
-      <c r="K40" s="2" t="n"/>
-      <c r="L40" s="2" t="n"/>
-      <c r="M40" s="3" t="n"/>
-    </row>
-    <row r="41" ht="15" customHeight="1">
-      <c r="B41" s="12" t="inlineStr">
-        <is>
-          <t>Senior loan amount</t>
-        </is>
-      </c>
-      <c r="C41" s="51">
-        <f>C28*C30</f>
-        <v/>
-      </c>
-      <c r="D41" s="22" t="inlineStr">
-        <is>
-          <t>price × LTV</t>
-        </is>
-      </c>
-      <c r="E41" s="13" t="n"/>
-      <c r="F41" s="13" t="n"/>
-      <c r="G41" s="13" t="n"/>
-      <c r="H41" s="13" t="n"/>
-      <c r="I41" s="13" t="n"/>
-      <c r="J41" s="13" t="n"/>
-      <c r="K41" s="13" t="n"/>
-      <c r="L41" s="13" t="n"/>
-      <c r="M41" s="14" t="n"/>
+      <c r="C41" s="2" t="n"/>
+      <c r="D41" s="2" t="n"/>
+      <c r="E41" s="2" t="n"/>
+      <c r="F41" s="2" t="n"/>
+      <c r="G41" s="2" t="n"/>
+      <c r="H41" s="2" t="n"/>
+      <c r="I41" s="2" t="n"/>
+      <c r="J41" s="2" t="n"/>
+      <c r="K41" s="2" t="n"/>
+      <c r="L41" s="2" t="n"/>
+      <c r="M41" s="3" t="n"/>
     </row>
     <row r="42" ht="15" customHeight="1">
       <c r="B42" s="12" t="inlineStr">
         <is>
-          <t>Monthly rate</t>
-        </is>
-      </c>
-      <c r="C42" s="50">
-        <f>C31/12</f>
-        <v/>
-      </c>
+          <t>Senior loan amount</t>
+        </is>
+      </c>
+      <c r="C42" s="51">
+        <f>C29*C31</f>
+        <v/>
+      </c>
+      <c r="D42" s="22" t="inlineStr">
+        <is>
+          <t>price × LTV</t>
+        </is>
+      </c>
+      <c r="E42" s="13" t="n"/>
+      <c r="F42" s="13" t="n"/>
+      <c r="G42" s="13" t="n"/>
+      <c r="H42" s="13" t="n"/>
+      <c r="I42" s="13" t="n"/>
+      <c r="J42" s="13" t="n"/>
+      <c r="K42" s="13" t="n"/>
+      <c r="L42" s="13" t="n"/>
+      <c r="M42" s="14" t="n"/>
     </row>
     <row r="43" ht="15" customHeight="1">
       <c r="B43" s="12" t="inlineStr">
         <is>
-          <t>Annual debt service</t>
-        </is>
-      </c>
-      <c r="C43" s="51">
-        <f>C41*(C42/(1-(1+C42)^(-C32*12)))*12</f>
+          <t>Monthly rate</t>
+        </is>
+      </c>
+      <c r="C43" s="50">
+        <f>C32/12</f>
         <v/>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1">
       <c r="B44" s="12" t="inlineStr">
         <is>
-          <t>Equity at acquisition</t>
+          <t>Annual debt service</t>
         </is>
       </c>
       <c r="C44" s="51">
-        <f>C28*(1+C29)-C41</f>
+        <f>C42*(C43/(1-(1+C43)^(-C33*12)))*12</f>
         <v/>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1">
       <c r="B45" s="12" t="inlineStr">
         <is>
-          <t>Total cost basis</t>
+          <t>Equity at acquisition</t>
         </is>
       </c>
       <c r="C45" s="51">
-        <f>C28*(1+C29)</f>
+        <f>C29*(1+C30)-C42</f>
         <v/>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1">
       <c r="B46" s="12" t="inlineStr">
         <is>
+          <t>Total cost basis</t>
+        </is>
+      </c>
+      <c r="C46" s="51">
+        <f>C29*(1+C30)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47" ht="15" customHeight="1">
+      <c r="B47" s="12" t="inlineStr">
+        <is>
           <t>Total equity required</t>
         </is>
       </c>
-      <c r="C46" s="51">
-        <f>C45-C41</f>
-        <v/>
-      </c>
-    </row>
-    <row r="47"/>
-    <row r="48">
-      <c r="B48" s="11" t="inlineStr">
+      <c r="C47" s="51">
+        <f>C46-C42</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48"/>
+    <row r="49">
+      <c r="B49" s="11" t="inlineStr">
         <is>
           <t>OPERATING CASH FLOW  —  10-year annual (Modified Gross)</t>
         </is>
       </c>
-      <c r="C48" s="2" t="n"/>
-      <c r="D48" s="2" t="n"/>
-      <c r="E48" s="2" t="n"/>
-      <c r="F48" s="2" t="n"/>
-      <c r="G48" s="2" t="n"/>
-      <c r="H48" s="2" t="n"/>
-      <c r="I48" s="2" t="n"/>
-      <c r="J48" s="2" t="n"/>
-      <c r="K48" s="2" t="n"/>
-      <c r="L48" s="2" t="n"/>
-      <c r="M48" s="3" t="n"/>
-    </row>
-    <row r="49" ht="15" customHeight="1">
-      <c r="B49" s="15" t="inlineStr">
+      <c r="C49" s="2" t="n"/>
+      <c r="D49" s="2" t="n"/>
+      <c r="E49" s="2" t="n"/>
+      <c r="F49" s="2" t="n"/>
+      <c r="G49" s="2" t="n"/>
+      <c r="H49" s="2" t="n"/>
+      <c r="I49" s="2" t="n"/>
+      <c r="J49" s="2" t="n"/>
+      <c r="K49" s="2" t="n"/>
+      <c r="L49" s="2" t="n"/>
+      <c r="M49" s="3" t="n"/>
+    </row>
+    <row r="50" ht="15" customHeight="1">
+      <c r="B50" s="15" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="C49" s="16" t="inlineStr">
+      <c r="C50" s="16" t="inlineStr">
         <is>
           <t>0 / Acq</t>
         </is>
       </c>
-      <c r="D49" s="41" t="n">
+      <c r="D50" s="41" t="n">
         <v>1</v>
       </c>
-      <c r="E49" s="41" t="n">
+      <c r="E50" s="41" t="n">
         <v>2</v>
       </c>
-      <c r="F49" s="41" t="n">
+      <c r="F50" s="41" t="n">
         <v>3</v>
       </c>
-      <c r="G49" s="41" t="n">
+      <c r="G50" s="41" t="n">
         <v>4</v>
       </c>
-      <c r="H49" s="41" t="n">
+      <c r="H50" s="41" t="n">
         <v>5</v>
       </c>
-      <c r="I49" s="41" t="n">
+      <c r="I50" s="41" t="n">
         <v>6</v>
       </c>
-      <c r="J49" s="41" t="n">
+      <c r="J50" s="41" t="n">
         <v>7</v>
       </c>
-      <c r="K49" s="41" t="n">
+      <c r="K50" s="41" t="n">
         <v>8</v>
       </c>
-      <c r="L49" s="41" t="n">
+      <c r="L50" s="41" t="n">
         <v>9</v>
       </c>
-      <c r="M49" s="41" t="n">
+      <c r="M50" s="41" t="n">
         <v>10</v>
       </c>
     </row>
-    <row r="50" ht="15" customHeight="1">
-      <c r="B50" s="22" t="inlineStr">
+    <row r="51" ht="15" customHeight="1">
+      <c r="B51" s="22" t="inlineStr">
         <is>
           <t>Year ending</t>
         </is>
       </c>
-      <c r="C50" s="42" t="inlineStr">
+      <c r="C51" s="42" t="inlineStr">
         <is>
           <t>At close</t>
         </is>
       </c>
-      <c r="D50" s="42" t="inlineStr">
+      <c r="D51" s="42" t="inlineStr">
         <is>
           <t>Dec-2027</t>
         </is>
       </c>
-      <c r="E50" s="42" t="inlineStr">
+      <c r="E51" s="42" t="inlineStr">
         <is>
           <t>Dec-2028</t>
         </is>
       </c>
-      <c r="F50" s="42" t="inlineStr">
+      <c r="F51" s="42" t="inlineStr">
         <is>
           <t>Dec-2029</t>
         </is>
       </c>
-      <c r="G50" s="42" t="inlineStr">
+      <c r="G51" s="42" t="inlineStr">
         <is>
           <t>Dec-2030</t>
         </is>
       </c>
-      <c r="H50" s="42" t="inlineStr">
+      <c r="H51" s="42" t="inlineStr">
         <is>
           <t>Dec-2031</t>
         </is>
       </c>
-      <c r="I50" s="42" t="inlineStr">
+      <c r="I51" s="42" t="inlineStr">
         <is>
           <t>Dec-2032</t>
         </is>
       </c>
-      <c r="J50" s="42" t="inlineStr">
+      <c r="J51" s="42" t="inlineStr">
         <is>
           <t>Dec-2033</t>
         </is>
       </c>
-      <c r="K50" s="42" t="inlineStr">
+      <c r="K51" s="42" t="inlineStr">
         <is>
           <t>Dec-2034</t>
         </is>
       </c>
-      <c r="L50" s="42" t="inlineStr">
+      <c r="L51" s="42" t="inlineStr">
         <is>
           <t>Dec-2035</t>
         </is>
       </c>
-      <c r="M50" s="42" t="inlineStr">
+      <c r="M51" s="42" t="inlineStr">
         <is>
           <t>Dec-2036</t>
         </is>
-      </c>
-    </row>
-    <row r="51" ht="15" customHeight="1">
-      <c r="B51" s="12" t="inlineStr">
-        <is>
-          <t>Occupancy</t>
-        </is>
-      </c>
-      <c r="D51" s="53">
-        <f>(C18+C19)/2</f>
-        <v/>
-      </c>
-      <c r="E51" s="53">
-        <f>C19</f>
-        <v/>
-      </c>
-      <c r="F51" s="53">
-        <f>C19</f>
-        <v/>
-      </c>
-      <c r="G51" s="53">
-        <f>C19</f>
-        <v/>
-      </c>
-      <c r="H51" s="53">
-        <f>C19</f>
-        <v/>
-      </c>
-      <c r="I51" s="53">
-        <f>C19</f>
-        <v/>
-      </c>
-      <c r="J51" s="53">
-        <f>C19</f>
-        <v/>
-      </c>
-      <c r="K51" s="53">
-        <f>C19</f>
-        <v/>
-      </c>
-      <c r="L51" s="53">
-        <f>C19</f>
-        <v/>
-      </c>
-      <c r="M51" s="53">
-        <f>C19</f>
-        <v/>
       </c>
     </row>
     <row r="52" ht="15" customHeight="1">
       <c r="B52" s="12" t="inlineStr">
         <is>
+          <t>Occupancy</t>
+        </is>
+      </c>
+      <c r="D52" s="53">
+        <f>(C19+C20)/2</f>
+        <v/>
+      </c>
+      <c r="E52" s="53">
+        <f>C20</f>
+        <v/>
+      </c>
+      <c r="F52" s="53">
+        <f>C20</f>
+        <v/>
+      </c>
+      <c r="G52" s="53">
+        <f>C20</f>
+        <v/>
+      </c>
+      <c r="H52" s="53">
+        <f>C20</f>
+        <v/>
+      </c>
+      <c r="I52" s="53">
+        <f>C20</f>
+        <v/>
+      </c>
+      <c r="J52" s="53">
+        <f>C20</f>
+        <v/>
+      </c>
+      <c r="K52" s="53">
+        <f>C20</f>
+        <v/>
+      </c>
+      <c r="L52" s="53">
+        <f>C20</f>
+        <v/>
+      </c>
+      <c r="M52" s="53">
+        <f>C20</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53" ht="15" customHeight="1">
+      <c r="B53" s="12" t="inlineStr">
+        <is>
           <t>Leased SF</t>
         </is>
       </c>
-      <c r="D52" s="64">
-        <f>C17*D51</f>
-        <v/>
-      </c>
-      <c r="E52" s="64">
-        <f>C17*E51</f>
-        <v/>
-      </c>
-      <c r="F52" s="64">
-        <f>C17*F51</f>
-        <v/>
-      </c>
-      <c r="G52" s="64">
-        <f>C17*G51</f>
-        <v/>
-      </c>
-      <c r="H52" s="64">
-        <f>C17*H51</f>
-        <v/>
-      </c>
-      <c r="I52" s="64">
-        <f>C17*I51</f>
-        <v/>
-      </c>
-      <c r="J52" s="64">
-        <f>C17*J51</f>
-        <v/>
-      </c>
-      <c r="K52" s="64">
-        <f>C17*K51</f>
-        <v/>
-      </c>
-      <c r="L52" s="64">
-        <f>C17*L51</f>
-        <v/>
-      </c>
-      <c r="M52" s="64">
-        <f>C17*M51</f>
-        <v/>
-      </c>
-    </row>
-    <row r="53" ht="15" customHeight="1">
-      <c r="B53" s="52" t="inlineStr">
+      <c r="D53" s="64">
+        <f>C18*D52</f>
+        <v/>
+      </c>
+      <c r="E53" s="64">
+        <f>C18*E52</f>
+        <v/>
+      </c>
+      <c r="F53" s="64">
+        <f>C18*F52</f>
+        <v/>
+      </c>
+      <c r="G53" s="64">
+        <f>C18*G52</f>
+        <v/>
+      </c>
+      <c r="H53" s="64">
+        <f>C18*H52</f>
+        <v/>
+      </c>
+      <c r="I53" s="64">
+        <f>C18*I52</f>
+        <v/>
+      </c>
+      <c r="J53" s="64">
+        <f>C18*J52</f>
+        <v/>
+      </c>
+      <c r="K53" s="64">
+        <f>C18*K52</f>
+        <v/>
+      </c>
+      <c r="L53" s="64">
+        <f>C18*L52</f>
+        <v/>
+      </c>
+      <c r="M53" s="64">
+        <f>C18*M52</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54" ht="15" customHeight="1">
+      <c r="B54" s="52" t="inlineStr">
         <is>
           <t>Gross rental income (MG)</t>
         </is>
       </c>
-      <c r="D53" s="51">
-        <f>D52*C20*(1+C21)^(1-1)</f>
-        <v/>
-      </c>
-      <c r="E53" s="47">
-        <f>E52*C20*(1+C21)^(2-1)</f>
-        <v/>
-      </c>
-      <c r="F53" s="47">
-        <f>F52*C20*(1+C21)^(3-1)</f>
-        <v/>
-      </c>
-      <c r="G53" s="47">
-        <f>G52*C20*(1+C21)^(4-1)</f>
-        <v/>
-      </c>
-      <c r="H53" s="47">
-        <f>H52*C20*(1+C21)^(5-1)</f>
-        <v/>
-      </c>
-      <c r="I53" s="47">
-        <f>I52*C20*(1+C21)^(6-1)</f>
-        <v/>
-      </c>
-      <c r="J53" s="47">
-        <f>J52*C20*(1+C21)^(7-1)</f>
-        <v/>
-      </c>
-      <c r="K53" s="47">
-        <f>K52*C20*(1+C21)^(8-1)</f>
-        <v/>
-      </c>
-      <c r="L53" s="47">
-        <f>L52*C20*(1+C21)^(9-1)</f>
-        <v/>
-      </c>
-      <c r="M53" s="47">
-        <f>M52*C20*(1+C21)^(10-1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="54" ht="15" customHeight="1">
-      <c r="B54" s="12" t="inlineStr">
+      <c r="D54" s="51">
+        <f>D53*C21*(1+C22)^(1-1)</f>
+        <v/>
+      </c>
+      <c r="E54" s="47">
+        <f>E53*C21*(1+C22)^(2-1)</f>
+        <v/>
+      </c>
+      <c r="F54" s="47">
+        <f>F53*C21*(1+C22)^(3-1)</f>
+        <v/>
+      </c>
+      <c r="G54" s="47">
+        <f>G53*C21*(1+C22)^(4-1)</f>
+        <v/>
+      </c>
+      <c r="H54" s="47">
+        <f>H53*C21*(1+C22)^(5-1)</f>
+        <v/>
+      </c>
+      <c r="I54" s="47">
+        <f>I53*C21*(1+C22)^(6-1)</f>
+        <v/>
+      </c>
+      <c r="J54" s="47">
+        <f>J53*C21*(1+C22)^(7-1)</f>
+        <v/>
+      </c>
+      <c r="K54" s="47">
+        <f>K53*C21*(1+C22)^(8-1)</f>
+        <v/>
+      </c>
+      <c r="L54" s="47">
+        <f>L53*C21*(1+C22)^(9-1)</f>
+        <v/>
+      </c>
+      <c r="M54" s="47">
+        <f>M53*C21*(1+C22)^(10-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55" ht="15" customHeight="1">
+      <c r="B55" s="12" t="inlineStr">
         <is>
           <t>Less: credit &amp; vacancy loss</t>
         </is>
       </c>
-      <c r="D54" s="47">
-        <f>-D53*C22</f>
-        <v/>
-      </c>
-      <c r="E54" s="47">
-        <f>-E53*C22</f>
-        <v/>
-      </c>
-      <c r="F54" s="47">
-        <f>-F53*C22</f>
-        <v/>
-      </c>
-      <c r="G54" s="47">
-        <f>-G53*C22</f>
-        <v/>
-      </c>
-      <c r="H54" s="47">
-        <f>-H53*C22</f>
-        <v/>
-      </c>
-      <c r="I54" s="47">
-        <f>-I53*C22</f>
-        <v/>
-      </c>
-      <c r="J54" s="47">
-        <f>-J53*C22</f>
-        <v/>
-      </c>
-      <c r="K54" s="47">
-        <f>-K53*C22</f>
-        <v/>
-      </c>
-      <c r="L54" s="47">
-        <f>-L53*C22</f>
-        <v/>
-      </c>
-      <c r="M54" s="47">
-        <f>-M53*C22</f>
-        <v/>
-      </c>
-    </row>
-    <row r="55" ht="15" customHeight="1">
-      <c r="B55" s="43" t="inlineStr">
+      <c r="D55" s="47">
+        <f>-D54*C23</f>
+        <v/>
+      </c>
+      <c r="E55" s="47">
+        <f>-E54*C23</f>
+        <v/>
+      </c>
+      <c r="F55" s="47">
+        <f>-F54*C23</f>
+        <v/>
+      </c>
+      <c r="G55" s="47">
+        <f>-G54*C23</f>
+        <v/>
+      </c>
+      <c r="H55" s="47">
+        <f>-H54*C23</f>
+        <v/>
+      </c>
+      <c r="I55" s="47">
+        <f>-I54*C23</f>
+        <v/>
+      </c>
+      <c r="J55" s="47">
+        <f>-J54*C23</f>
+        <v/>
+      </c>
+      <c r="K55" s="47">
+        <f>-K54*C23</f>
+        <v/>
+      </c>
+      <c r="L55" s="47">
+        <f>-L54*C23</f>
+        <v/>
+      </c>
+      <c r="M55" s="47">
+        <f>-M54*C23</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56" ht="15" customHeight="1">
+      <c r="B56" s="43" t="inlineStr">
         <is>
           <t>Effective Gross Revenue</t>
         </is>
       </c>
-      <c r="D55" s="51">
-        <f>D53+D54</f>
-        <v/>
-      </c>
-      <c r="E55" s="47">
-        <f>E53+E54</f>
-        <v/>
-      </c>
-      <c r="F55" s="47">
-        <f>F53+F54</f>
-        <v/>
-      </c>
-      <c r="G55" s="47">
-        <f>G53+G54</f>
-        <v/>
-      </c>
-      <c r="H55" s="47">
-        <f>H53+H54</f>
-        <v/>
-      </c>
-      <c r="I55" s="47">
-        <f>I53+I54</f>
-        <v/>
-      </c>
-      <c r="J55" s="47">
-        <f>J53+J54</f>
-        <v/>
-      </c>
-      <c r="K55" s="47">
-        <f>K53+K54</f>
-        <v/>
-      </c>
-      <c r="L55" s="47">
-        <f>L53+L54</f>
-        <v/>
-      </c>
-      <c r="M55" s="47">
-        <f>M53+M54</f>
-        <v/>
-      </c>
-    </row>
-    <row r="56" ht="15" customHeight="1">
-      <c r="B56" s="15" t="inlineStr">
+      <c r="D56" s="51">
+        <f>D54+D55</f>
+        <v/>
+      </c>
+      <c r="E56" s="47">
+        <f>E54+E55</f>
+        <v/>
+      </c>
+      <c r="F56" s="47">
+        <f>F54+F55</f>
+        <v/>
+      </c>
+      <c r="G56" s="47">
+        <f>G54+G55</f>
+        <v/>
+      </c>
+      <c r="H56" s="47">
+        <f>H54+H55</f>
+        <v/>
+      </c>
+      <c r="I56" s="47">
+        <f>I54+I55</f>
+        <v/>
+      </c>
+      <c r="J56" s="47">
+        <f>J54+J55</f>
+        <v/>
+      </c>
+      <c r="K56" s="47">
+        <f>K54+K55</f>
+        <v/>
+      </c>
+      <c r="L56" s="47">
+        <f>L54+L55</f>
+        <v/>
+      </c>
+      <c r="M56" s="47">
+        <f>M54+M55</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57" ht="15" customHeight="1">
+      <c r="B57" s="15" t="inlineStr">
         <is>
           <t>OPERATING EXPENSES (landlord — Modified Gross)</t>
         </is>
       </c>
-      <c r="C56" s="13" t="n"/>
-      <c r="D56" s="13" t="n"/>
-      <c r="E56" s="13" t="n"/>
-      <c r="F56" s="13" t="n"/>
-      <c r="G56" s="13" t="n"/>
-      <c r="H56" s="13" t="n"/>
-      <c r="I56" s="13" t="n"/>
-      <c r="J56" s="13" t="n"/>
-      <c r="K56" s="13" t="n"/>
-      <c r="L56" s="13" t="n"/>
-      <c r="M56" s="14" t="n"/>
-    </row>
-    <row r="57" ht="15" customHeight="1">
-      <c r="B57" s="12" t="inlineStr">
-        <is>
-          <t>Real-estate taxes</t>
-        </is>
-      </c>
-      <c r="D57" s="47">
-        <f>C28*C23*(1+C26)^(1-1)</f>
-        <v/>
-      </c>
-      <c r="E57" s="47">
-        <f>C28*C23*(1+C26)^(2-1)</f>
-        <v/>
-      </c>
-      <c r="F57" s="47">
-        <f>C28*C23*(1+C26)^(3-1)</f>
-        <v/>
-      </c>
-      <c r="G57" s="47">
-        <f>C28*C23*(1+C26)^(4-1)</f>
-        <v/>
-      </c>
-      <c r="H57" s="47">
-        <f>C28*C23*(1+C26)^(5-1)</f>
-        <v/>
-      </c>
-      <c r="I57" s="47">
-        <f>C28*C23*(1+C26)^(6-1)</f>
-        <v/>
-      </c>
-      <c r="J57" s="47">
-        <f>C28*C23*(1+C26)^(7-1)</f>
-        <v/>
-      </c>
-      <c r="K57" s="47">
-        <f>C28*C23*(1+C26)^(8-1)</f>
-        <v/>
-      </c>
-      <c r="L57" s="47">
-        <f>C28*C23*(1+C26)^(9-1)</f>
-        <v/>
-      </c>
-      <c r="M57" s="47">
-        <f>C28*C23*(1+C26)^(10-1)</f>
-        <v/>
-      </c>
+      <c r="C57" s="13" t="n"/>
+      <c r="D57" s="13" t="n"/>
+      <c r="E57" s="13" t="n"/>
+      <c r="F57" s="13" t="n"/>
+      <c r="G57" s="13" t="n"/>
+      <c r="H57" s="13" t="n"/>
+      <c r="I57" s="13" t="n"/>
+      <c r="J57" s="13" t="n"/>
+      <c r="K57" s="13" t="n"/>
+      <c r="L57" s="13" t="n"/>
+      <c r="M57" s="14" t="n"/>
     </row>
     <row r="58" ht="15" customHeight="1">
       <c r="B58" s="12" t="inlineStr">
         <is>
-          <t>Office opex (utilities, R&amp;M, ins, CAM)</t>
+          <t>Real-estate taxes</t>
         </is>
       </c>
       <c r="D58" s="47">
-        <f>C17*C24*(1+C26)^(1-1)</f>
+        <f>C29*C24*(1+C27)^(1-1)</f>
         <v/>
       </c>
       <c r="E58" s="47">
-        <f>C17*C24*(1+C26)^(2-1)</f>
+        <f>C29*C24*(1+C27)^(2-1)</f>
         <v/>
       </c>
       <c r="F58" s="47">
-        <f>C17*C24*(1+C26)^(3-1)</f>
+        <f>C29*C24*(1+C27)^(3-1)</f>
         <v/>
       </c>
       <c r="G58" s="47">
-        <f>C17*C24*(1+C26)^(4-1)</f>
+        <f>C29*C24*(1+C27)^(4-1)</f>
         <v/>
       </c>
       <c r="H58" s="47">
-        <f>C17*C24*(1+C26)^(5-1)</f>
+        <f>C29*C24*(1+C27)^(5-1)</f>
         <v/>
       </c>
       <c r="I58" s="47">
-        <f>C17*C24*(1+C26)^(6-1)</f>
+        <f>C29*C24*(1+C27)^(6-1)</f>
         <v/>
       </c>
       <c r="J58" s="47">
-        <f>C17*C24*(1+C26)^(7-1)</f>
+        <f>C29*C24*(1+C27)^(7-1)</f>
         <v/>
       </c>
       <c r="K58" s="47">
-        <f>C17*C24*(1+C26)^(8-1)</f>
+        <f>C29*C24*(1+C27)^(8-1)</f>
         <v/>
       </c>
       <c r="L58" s="47">
-        <f>C17*C24*(1+C26)^(9-1)</f>
+        <f>C29*C24*(1+C27)^(9-1)</f>
         <v/>
       </c>
       <c r="M58" s="47">
-        <f>C17*C24*(1+C26)^(10-1)</f>
+        <f>C29*C24*(1+C27)^(10-1)</f>
         <v/>
       </c>
     </row>
     <row r="59" ht="15" customHeight="1">
       <c r="B59" s="12" t="inlineStr">
         <is>
+          <t>Office opex (utilities, R&amp;M, ins, CAM)</t>
+        </is>
+      </c>
+      <c r="D59" s="47">
+        <f>C18*C25*(1+C27)^(1-1)</f>
+        <v/>
+      </c>
+      <c r="E59" s="47">
+        <f>C18*C25*(1+C27)^(2-1)</f>
+        <v/>
+      </c>
+      <c r="F59" s="47">
+        <f>C18*C25*(1+C27)^(3-1)</f>
+        <v/>
+      </c>
+      <c r="G59" s="47">
+        <f>C18*C25*(1+C27)^(4-1)</f>
+        <v/>
+      </c>
+      <c r="H59" s="47">
+        <f>C18*C25*(1+C27)^(5-1)</f>
+        <v/>
+      </c>
+      <c r="I59" s="47">
+        <f>C18*C25*(1+C27)^(6-1)</f>
+        <v/>
+      </c>
+      <c r="J59" s="47">
+        <f>C18*C25*(1+C27)^(7-1)</f>
+        <v/>
+      </c>
+      <c r="K59" s="47">
+        <f>C18*C25*(1+C27)^(8-1)</f>
+        <v/>
+      </c>
+      <c r="L59" s="47">
+        <f>C18*C25*(1+C27)^(9-1)</f>
+        <v/>
+      </c>
+      <c r="M59" s="47">
+        <f>C18*C25*(1+C27)^(10-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60" ht="15" customHeight="1">
+      <c r="B60" s="12" t="inlineStr">
+        <is>
           <t>Management fee</t>
         </is>
       </c>
-      <c r="D59" s="47">
-        <f>D55*C25</f>
-        <v/>
-      </c>
-      <c r="E59" s="47">
-        <f>E55*C25</f>
-        <v/>
-      </c>
-      <c r="F59" s="47">
-        <f>F55*C25</f>
-        <v/>
-      </c>
-      <c r="G59" s="47">
-        <f>G55*C25</f>
-        <v/>
-      </c>
-      <c r="H59" s="47">
-        <f>H55*C25</f>
-        <v/>
-      </c>
-      <c r="I59" s="47">
-        <f>I55*C25</f>
-        <v/>
-      </c>
-      <c r="J59" s="47">
-        <f>J55*C25</f>
-        <v/>
-      </c>
-      <c r="K59" s="47">
-        <f>K55*C25</f>
-        <v/>
-      </c>
-      <c r="L59" s="47">
-        <f>L55*C25</f>
-        <v/>
-      </c>
-      <c r="M59" s="47">
-        <f>M55*C25</f>
-        <v/>
-      </c>
-    </row>
-    <row r="60" ht="15" customHeight="1">
-      <c r="B60" s="43" t="inlineStr">
-        <is>
-          <t>Total operating expenses</t>
-        </is>
-      </c>
-      <c r="D60" s="51">
-        <f>SUM(D57:D59)</f>
+      <c r="D60" s="47">
+        <f>D56*C26</f>
         <v/>
       </c>
       <c r="E60" s="47">
-        <f>SUM(E57:E59)</f>
+        <f>E56*C26</f>
         <v/>
       </c>
       <c r="F60" s="47">
-        <f>SUM(F57:F59)</f>
+        <f>F56*C26</f>
         <v/>
       </c>
       <c r="G60" s="47">
-        <f>SUM(G57:G59)</f>
+        <f>G56*C26</f>
         <v/>
       </c>
       <c r="H60" s="47">
-        <f>SUM(H57:H59)</f>
+        <f>H56*C26</f>
         <v/>
       </c>
       <c r="I60" s="47">
-        <f>SUM(I57:I59)</f>
+        <f>I56*C26</f>
         <v/>
       </c>
       <c r="J60" s="47">
-        <f>SUM(J57:J59)</f>
+        <f>J56*C26</f>
         <v/>
       </c>
       <c r="K60" s="47">
-        <f>SUM(K57:K59)</f>
+        <f>K56*C26</f>
         <v/>
       </c>
       <c r="L60" s="47">
-        <f>SUM(L57:L59)</f>
+        <f>L56*C26</f>
         <v/>
       </c>
       <c r="M60" s="47">
-        <f>SUM(M57:M59)</f>
+        <f>M56*C26</f>
         <v/>
       </c>
     </row>
     <row r="61" ht="15" customHeight="1">
       <c r="B61" s="43" t="inlineStr">
         <is>
+          <t>Total operating expenses</t>
+        </is>
+      </c>
+      <c r="D61" s="51">
+        <f>SUM(D58:D60)</f>
+        <v/>
+      </c>
+      <c r="E61" s="47">
+        <f>SUM(E58:E60)</f>
+        <v/>
+      </c>
+      <c r="F61" s="47">
+        <f>SUM(F58:F60)</f>
+        <v/>
+      </c>
+      <c r="G61" s="47">
+        <f>SUM(G58:G60)</f>
+        <v/>
+      </c>
+      <c r="H61" s="47">
+        <f>SUM(H58:H60)</f>
+        <v/>
+      </c>
+      <c r="I61" s="47">
+        <f>SUM(I58:I60)</f>
+        <v/>
+      </c>
+      <c r="J61" s="47">
+        <f>SUM(J58:J60)</f>
+        <v/>
+      </c>
+      <c r="K61" s="47">
+        <f>SUM(K58:K60)</f>
+        <v/>
+      </c>
+      <c r="L61" s="47">
+        <f>SUM(L58:L60)</f>
+        <v/>
+      </c>
+      <c r="M61" s="47">
+        <f>SUM(M58:M60)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62" ht="15" customHeight="1">
+      <c r="B62" s="43" t="inlineStr">
+        <is>
           <t>NET OPERATING INCOME</t>
         </is>
       </c>
-      <c r="D61" s="44">
-        <f>D55-D60</f>
-        <v/>
-      </c>
-      <c r="E61" s="45">
-        <f>E55-E60</f>
-        <v/>
-      </c>
-      <c r="F61" s="45">
-        <f>F55-F60</f>
-        <v/>
-      </c>
-      <c r="G61" s="45">
-        <f>G55-G60</f>
-        <v/>
-      </c>
-      <c r="H61" s="45">
-        <f>H55-H60</f>
-        <v/>
-      </c>
-      <c r="I61" s="45">
-        <f>I55-I60</f>
-        <v/>
-      </c>
-      <c r="J61" s="45">
-        <f>J55-J60</f>
-        <v/>
-      </c>
-      <c r="K61" s="45">
-        <f>K55-K60</f>
-        <v/>
-      </c>
-      <c r="L61" s="45">
-        <f>L55-L60</f>
-        <v/>
-      </c>
-      <c r="M61" s="45">
-        <f>M55-M60</f>
-        <v/>
-      </c>
-    </row>
-    <row r="62" ht="15" customHeight="1">
-      <c r="B62" s="12" t="inlineStr">
+      <c r="D62" s="44">
+        <f>D56-D61</f>
+        <v/>
+      </c>
+      <c r="E62" s="45">
+        <f>E56-E61</f>
+        <v/>
+      </c>
+      <c r="F62" s="45">
+        <f>F56-F61</f>
+        <v/>
+      </c>
+      <c r="G62" s="45">
+        <f>G56-G61</f>
+        <v/>
+      </c>
+      <c r="H62" s="45">
+        <f>H56-H61</f>
+        <v/>
+      </c>
+      <c r="I62" s="45">
+        <f>I56-I61</f>
+        <v/>
+      </c>
+      <c r="J62" s="45">
+        <f>J56-J61</f>
+        <v/>
+      </c>
+      <c r="K62" s="45">
+        <f>K56-K61</f>
+        <v/>
+      </c>
+      <c r="L62" s="45">
+        <f>L56-L61</f>
+        <v/>
+      </c>
+      <c r="M62" s="45">
+        <f>M56-M61</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63" ht="15" customHeight="1">
+      <c r="B63" s="12" t="inlineStr">
         <is>
           <t>Replacement reserves</t>
         </is>
       </c>
-      <c r="D62" s="47">
-        <f>C17*C27*(1+C26)^(1-1)</f>
-        <v/>
-      </c>
-      <c r="E62" s="47">
-        <f>C17*C27*(1+C26)^(2-1)</f>
-        <v/>
-      </c>
-      <c r="F62" s="47">
-        <f>C17*C27*(1+C26)^(3-1)</f>
-        <v/>
-      </c>
-      <c r="G62" s="47">
-        <f>C17*C27*(1+C26)^(4-1)</f>
-        <v/>
-      </c>
-      <c r="H62" s="47">
-        <f>C17*C27*(1+C26)^(5-1)</f>
-        <v/>
-      </c>
-      <c r="I62" s="47">
-        <f>C17*C27*(1+C26)^(6-1)</f>
-        <v/>
-      </c>
-      <c r="J62" s="47">
-        <f>C17*C27*(1+C26)^(7-1)</f>
-        <v/>
-      </c>
-      <c r="K62" s="47">
-        <f>C17*C27*(1+C26)^(8-1)</f>
-        <v/>
-      </c>
-      <c r="L62" s="47">
-        <f>C17*C27*(1+C26)^(9-1)</f>
-        <v/>
-      </c>
-      <c r="M62" s="47">
-        <f>C17*C27*(1+C26)^(10-1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="63" ht="15" customHeight="1">
-      <c r="B63" s="43" t="inlineStr">
+      <c r="D63" s="47">
+        <f>C18*C28*(1+C27)^(1-1)</f>
+        <v/>
+      </c>
+      <c r="E63" s="47">
+        <f>C18*C28*(1+C27)^(2-1)</f>
+        <v/>
+      </c>
+      <c r="F63" s="47">
+        <f>C18*C28*(1+C27)^(3-1)</f>
+        <v/>
+      </c>
+      <c r="G63" s="47">
+        <f>C18*C28*(1+C27)^(4-1)</f>
+        <v/>
+      </c>
+      <c r="H63" s="47">
+        <f>C18*C28*(1+C27)^(5-1)</f>
+        <v/>
+      </c>
+      <c r="I63" s="47">
+        <f>C18*C28*(1+C27)^(6-1)</f>
+        <v/>
+      </c>
+      <c r="J63" s="47">
+        <f>C18*C28*(1+C27)^(7-1)</f>
+        <v/>
+      </c>
+      <c r="K63" s="47">
+        <f>C18*C28*(1+C27)^(8-1)</f>
+        <v/>
+      </c>
+      <c r="L63" s="47">
+        <f>C18*C28*(1+C27)^(9-1)</f>
+        <v/>
+      </c>
+      <c r="M63" s="47">
+        <f>C18*C28*(1+C27)^(10-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64" ht="15" customHeight="1">
+      <c r="B64" s="43" t="inlineStr">
         <is>
           <t>Unlevered cash flow (before reversion)</t>
         </is>
       </c>
-      <c r="C63" s="44">
-        <f>-C28*(1+C29)</f>
-        <v/>
-      </c>
-      <c r="D63" s="44">
-        <f>D61-D62</f>
-        <v/>
-      </c>
-      <c r="E63" s="45">
-        <f>E61-E62</f>
-        <v/>
-      </c>
-      <c r="F63" s="45">
-        <f>F61-F62</f>
-        <v/>
-      </c>
-      <c r="G63" s="45">
-        <f>G61-G62</f>
-        <v/>
-      </c>
-      <c r="H63" s="45">
-        <f>H61-H62</f>
-        <v/>
-      </c>
-      <c r="I63" s="45">
-        <f>I61-I62</f>
-        <v/>
-      </c>
-      <c r="J63" s="45">
-        <f>J61-J62</f>
-        <v/>
-      </c>
-      <c r="K63" s="45">
-        <f>K61-K62</f>
-        <v/>
-      </c>
-      <c r="L63" s="45">
-        <f>L61-L62</f>
-        <v/>
-      </c>
-      <c r="M63" s="45">
-        <f>M61-M62</f>
-        <v/>
-      </c>
-    </row>
-    <row r="64"/>
-    <row r="65">
-      <c r="B65" s="11" t="inlineStr">
+      <c r="C64" s="44">
+        <f>-C29*(1+C30)</f>
+        <v/>
+      </c>
+      <c r="D64" s="44">
+        <f>D62-D63</f>
+        <v/>
+      </c>
+      <c r="E64" s="45">
+        <f>E62-E63</f>
+        <v/>
+      </c>
+      <c r="F64" s="45">
+        <f>F62-F63</f>
+        <v/>
+      </c>
+      <c r="G64" s="45">
+        <f>G62-G63</f>
+        <v/>
+      </c>
+      <c r="H64" s="45">
+        <f>H62-H63</f>
+        <v/>
+      </c>
+      <c r="I64" s="45">
+        <f>I62-I63</f>
+        <v/>
+      </c>
+      <c r="J64" s="45">
+        <f>J62-J63</f>
+        <v/>
+      </c>
+      <c r="K64" s="45">
+        <f>K62-K63</f>
+        <v/>
+      </c>
+      <c r="L64" s="45">
+        <f>L62-L63</f>
+        <v/>
+      </c>
+      <c r="M64" s="45">
+        <f>M62-M63</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65"/>
+    <row r="66">
+      <c r="B66" s="11" t="inlineStr">
         <is>
           <t>REVERSION, DEBT SERVICE  &amp;  LEVERED CASH FLOW</t>
         </is>
       </c>
-      <c r="C65" s="2" t="n"/>
-      <c r="D65" s="2" t="n"/>
-      <c r="E65" s="2" t="n"/>
-      <c r="F65" s="2" t="n"/>
-      <c r="G65" s="2" t="n"/>
-      <c r="H65" s="2" t="n"/>
-      <c r="I65" s="2" t="n"/>
-      <c r="J65" s="2" t="n"/>
-      <c r="K65" s="2" t="n"/>
-      <c r="L65" s="2" t="n"/>
-      <c r="M65" s="3" t="n"/>
-    </row>
-    <row r="66" ht="15" customHeight="1">
-      <c r="B66" s="12" t="inlineStr">
+      <c r="C66" s="2" t="n"/>
+      <c r="D66" s="2" t="n"/>
+      <c r="E66" s="2" t="n"/>
+      <c r="F66" s="2" t="n"/>
+      <c r="G66" s="2" t="n"/>
+      <c r="H66" s="2" t="n"/>
+      <c r="I66" s="2" t="n"/>
+      <c r="J66" s="2" t="n"/>
+      <c r="K66" s="2" t="n"/>
+      <c r="L66" s="2" t="n"/>
+      <c r="M66" s="3" t="n"/>
+    </row>
+    <row r="67" ht="15" customHeight="1">
+      <c r="B67" s="12" t="inlineStr">
         <is>
           <t>Net sale proceeds (exit year)</t>
         </is>
       </c>
-      <c r="D66" s="47">
-        <f>IF(1=C36,(D61*(1+C21)/C34)*(1-C35),0)</f>
-        <v/>
-      </c>
-      <c r="E66" s="47">
-        <f>IF(2=C36,(E61*(1+C21)/C34)*(1-C35),0)</f>
-        <v/>
-      </c>
-      <c r="F66" s="47">
-        <f>IF(3=C36,(F61*(1+C21)/C34)*(1-C35),0)</f>
-        <v/>
-      </c>
-      <c r="G66" s="47">
-        <f>IF(4=C36,(G61*(1+C21)/C34)*(1-C35),0)</f>
-        <v/>
-      </c>
-      <c r="H66" s="47">
-        <f>IF(5=C36,(H61*(1+C21)/C34)*(1-C35),0)</f>
-        <v/>
-      </c>
-      <c r="I66" s="47">
-        <f>IF(6=C36,(I61*(1+C21)/C34)*(1-C35),0)</f>
-        <v/>
-      </c>
-      <c r="J66" s="47">
-        <f>IF(7=C36,(J61*(1+C21)/C34)*(1-C35),0)</f>
-        <v/>
-      </c>
-      <c r="K66" s="47">
-        <f>IF(8=C36,(K61*(1+C21)/C34)*(1-C35),0)</f>
-        <v/>
-      </c>
-      <c r="L66" s="47">
-        <f>IF(9=C36,(L61*(1+C21)/C34)*(1-C35),0)</f>
-        <v/>
-      </c>
-      <c r="M66" s="47">
-        <f>IF(10=C36,(M61*(1+C21)/C34)*(1-C35),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="67" ht="15" customHeight="1">
-      <c r="B67" s="43" t="inlineStr">
+      <c r="D67" s="47">
+        <f>IF(1=C37,(D62*(1+C22)/C35)*(1-C36),0)</f>
+        <v/>
+      </c>
+      <c r="E67" s="47">
+        <f>IF(2=C37,(E62*(1+C22)/C35)*(1-C36),0)</f>
+        <v/>
+      </c>
+      <c r="F67" s="47">
+        <f>IF(3=C37,(F62*(1+C22)/C35)*(1-C36),0)</f>
+        <v/>
+      </c>
+      <c r="G67" s="47">
+        <f>IF(4=C37,(G62*(1+C22)/C35)*(1-C36),0)</f>
+        <v/>
+      </c>
+      <c r="H67" s="47">
+        <f>IF(5=C37,(H62*(1+C22)/C35)*(1-C36),0)</f>
+        <v/>
+      </c>
+      <c r="I67" s="47">
+        <f>IF(6=C37,(I62*(1+C22)/C35)*(1-C36),0)</f>
+        <v/>
+      </c>
+      <c r="J67" s="47">
+        <f>IF(7=C37,(J62*(1+C22)/C35)*(1-C36),0)</f>
+        <v/>
+      </c>
+      <c r="K67" s="47">
+        <f>IF(8=C37,(K62*(1+C22)/C35)*(1-C36),0)</f>
+        <v/>
+      </c>
+      <c r="L67" s="47">
+        <f>IF(9=C37,(L62*(1+C22)/C35)*(1-C36),0)</f>
+        <v/>
+      </c>
+      <c r="M67" s="47">
+        <f>IF(10=C37,(M62*(1+C22)/C35)*(1-C36),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68" ht="15" customHeight="1">
+      <c r="B68" s="43" t="inlineStr">
         <is>
           <t>UNLEVERED PROJECT CASH FLOW</t>
         </is>
       </c>
-      <c r="C67" s="44">
-        <f>C63</f>
-        <v/>
-      </c>
-      <c r="D67" s="44">
-        <f>IF(1&lt;=C36,D63,0)+D66</f>
-        <v/>
-      </c>
-      <c r="E67" s="45">
-        <f>IF(2&lt;=C36,E63,0)+E66</f>
-        <v/>
-      </c>
-      <c r="F67" s="45">
-        <f>IF(3&lt;=C36,F63,0)+F66</f>
-        <v/>
-      </c>
-      <c r="G67" s="45">
-        <f>IF(4&lt;=C36,G63,0)+G66</f>
-        <v/>
-      </c>
-      <c r="H67" s="45">
-        <f>IF(5&lt;=C36,H63,0)+H66</f>
-        <v/>
-      </c>
-      <c r="I67" s="45">
-        <f>IF(6&lt;=C36,I63,0)+I66</f>
-        <v/>
-      </c>
-      <c r="J67" s="45">
-        <f>IF(7&lt;=C36,J63,0)+J66</f>
-        <v/>
-      </c>
-      <c r="K67" s="45">
-        <f>IF(8&lt;=C36,K63,0)+K66</f>
-        <v/>
-      </c>
-      <c r="L67" s="45">
-        <f>IF(9&lt;=C36,L63,0)+L66</f>
-        <v/>
-      </c>
-      <c r="M67" s="45">
-        <f>IF(10&lt;=C36,M63,0)+M66</f>
-        <v/>
-      </c>
-    </row>
-    <row r="68" ht="15" customHeight="1">
-      <c r="B68" s="12" t="inlineStr">
-        <is>
-          <t>Loan balance (year-end)</t>
-        </is>
-      </c>
-      <c r="D68" s="47">
-        <f>C41*(1+C42)^(12*1)-(C43/12)*((1+C42)^(12*1)-1)/C42</f>
-        <v/>
-      </c>
-      <c r="E68" s="47">
-        <f>C41*(1+C42)^(12*2)-(C43/12)*((1+C42)^(12*2)-1)/C42</f>
-        <v/>
-      </c>
-      <c r="F68" s="47">
-        <f>C41*(1+C42)^(12*3)-(C43/12)*((1+C42)^(12*3)-1)/C42</f>
-        <v/>
-      </c>
-      <c r="G68" s="47">
-        <f>C41*(1+C42)^(12*4)-(C43/12)*((1+C42)^(12*4)-1)/C42</f>
-        <v/>
-      </c>
-      <c r="H68" s="47">
-        <f>C41*(1+C42)^(12*5)-(C43/12)*((1+C42)^(12*5)-1)/C42</f>
-        <v/>
-      </c>
-      <c r="I68" s="47">
-        <f>C41*(1+C42)^(12*6)-(C43/12)*((1+C42)^(12*6)-1)/C42</f>
-        <v/>
-      </c>
-      <c r="J68" s="47">
-        <f>C41*(1+C42)^(12*7)-(C43/12)*((1+C42)^(12*7)-1)/C42</f>
-        <v/>
-      </c>
-      <c r="K68" s="47">
-        <f>C41*(1+C42)^(12*8)-(C43/12)*((1+C42)^(12*8)-1)/C42</f>
-        <v/>
-      </c>
-      <c r="L68" s="47">
-        <f>C41*(1+C42)^(12*9)-(C43/12)*((1+C42)^(12*9)-1)/C42</f>
-        <v/>
-      </c>
-      <c r="M68" s="47">
-        <f>C41*(1+C42)^(12*10)-(C43/12)*((1+C42)^(12*10)-1)/C42</f>
+      <c r="C68" s="44">
+        <f>C64</f>
+        <v/>
+      </c>
+      <c r="D68" s="44">
+        <f>IF(1&lt;=C37,D64,0)+D67</f>
+        <v/>
+      </c>
+      <c r="E68" s="45">
+        <f>IF(2&lt;=C37,E64,0)+E67</f>
+        <v/>
+      </c>
+      <c r="F68" s="45">
+        <f>IF(3&lt;=C37,F64,0)+F67</f>
+        <v/>
+      </c>
+      <c r="G68" s="45">
+        <f>IF(4&lt;=C37,G64,0)+G67</f>
+        <v/>
+      </c>
+      <c r="H68" s="45">
+        <f>IF(5&lt;=C37,H64,0)+H67</f>
+        <v/>
+      </c>
+      <c r="I68" s="45">
+        <f>IF(6&lt;=C37,I64,0)+I67</f>
+        <v/>
+      </c>
+      <c r="J68" s="45">
+        <f>IF(7&lt;=C37,J64,0)+J67</f>
+        <v/>
+      </c>
+      <c r="K68" s="45">
+        <f>IF(8&lt;=C37,K64,0)+K67</f>
+        <v/>
+      </c>
+      <c r="L68" s="45">
+        <f>IF(9&lt;=C37,L64,0)+L67</f>
+        <v/>
+      </c>
+      <c r="M68" s="45">
+        <f>IF(10&lt;=C37,M64,0)+M67</f>
         <v/>
       </c>
     </row>
     <row r="69" ht="15" customHeight="1">
       <c r="B69" s="12" t="inlineStr">
         <is>
+          <t>Loan balance (year-end)</t>
+        </is>
+      </c>
+      <c r="D69" s="47">
+        <f>C42*(1+C43)^(12*1)-(C44/12)*((1+C43)^(12*1)-1)/C43</f>
+        <v/>
+      </c>
+      <c r="E69" s="47">
+        <f>C42*(1+C43)^(12*2)-(C44/12)*((1+C43)^(12*2)-1)/C43</f>
+        <v/>
+      </c>
+      <c r="F69" s="47">
+        <f>C42*(1+C43)^(12*3)-(C44/12)*((1+C43)^(12*3)-1)/C43</f>
+        <v/>
+      </c>
+      <c r="G69" s="47">
+        <f>C42*(1+C43)^(12*4)-(C44/12)*((1+C43)^(12*4)-1)/C43</f>
+        <v/>
+      </c>
+      <c r="H69" s="47">
+        <f>C42*(1+C43)^(12*5)-(C44/12)*((1+C43)^(12*5)-1)/C43</f>
+        <v/>
+      </c>
+      <c r="I69" s="47">
+        <f>C42*(1+C43)^(12*6)-(C44/12)*((1+C43)^(12*6)-1)/C43</f>
+        <v/>
+      </c>
+      <c r="J69" s="47">
+        <f>C42*(1+C43)^(12*7)-(C44/12)*((1+C43)^(12*7)-1)/C43</f>
+        <v/>
+      </c>
+      <c r="K69" s="47">
+        <f>C42*(1+C43)^(12*8)-(C44/12)*((1+C43)^(12*8)-1)/C43</f>
+        <v/>
+      </c>
+      <c r="L69" s="47">
+        <f>C42*(1+C43)^(12*9)-(C44/12)*((1+C43)^(12*9)-1)/C43</f>
+        <v/>
+      </c>
+      <c r="M69" s="47">
+        <f>C42*(1+C43)^(12*10)-(C44/12)*((1+C43)^(12*10)-1)/C43</f>
+        <v/>
+      </c>
+    </row>
+    <row r="70" ht="15" customHeight="1">
+      <c r="B70" s="12" t="inlineStr">
+        <is>
           <t>DSCR (NOI ÷ DS)</t>
         </is>
       </c>
-      <c r="D69" s="54">
-        <f>D61/C43</f>
-        <v/>
-      </c>
-      <c r="E69" s="54">
-        <f>E61/C43</f>
-        <v/>
-      </c>
-      <c r="F69" s="54">
-        <f>F61/C43</f>
-        <v/>
-      </c>
-      <c r="G69" s="54">
-        <f>G61/C43</f>
-        <v/>
-      </c>
-      <c r="H69" s="54">
-        <f>H61/C43</f>
-        <v/>
-      </c>
-      <c r="I69" s="54">
-        <f>I61/C43</f>
-        <v/>
-      </c>
-      <c r="J69" s="54">
-        <f>J61/C43</f>
-        <v/>
-      </c>
-      <c r="K69" s="54">
-        <f>K61/C43</f>
-        <v/>
-      </c>
-      <c r="L69" s="54">
-        <f>L61/C43</f>
-        <v/>
-      </c>
-      <c r="M69" s="54">
-        <f>M61/C43</f>
-        <v/>
-      </c>
-    </row>
-    <row r="70" ht="15" customHeight="1">
-      <c r="B70" s="43" t="inlineStr">
+      <c r="D70" s="54">
+        <f>D62/C44</f>
+        <v/>
+      </c>
+      <c r="E70" s="54">
+        <f>E62/C44</f>
+        <v/>
+      </c>
+      <c r="F70" s="54">
+        <f>F62/C44</f>
+        <v/>
+      </c>
+      <c r="G70" s="54">
+        <f>G62/C44</f>
+        <v/>
+      </c>
+      <c r="H70" s="54">
+        <f>H62/C44</f>
+        <v/>
+      </c>
+      <c r="I70" s="54">
+        <f>I62/C44</f>
+        <v/>
+      </c>
+      <c r="J70" s="54">
+        <f>J62/C44</f>
+        <v/>
+      </c>
+      <c r="K70" s="54">
+        <f>K62/C44</f>
+        <v/>
+      </c>
+      <c r="L70" s="54">
+        <f>L62/C44</f>
+        <v/>
+      </c>
+      <c r="M70" s="54">
+        <f>M62/C44</f>
+        <v/>
+      </c>
+    </row>
+    <row r="71" ht="15" customHeight="1">
+      <c r="B71" s="43" t="inlineStr">
         <is>
           <t>LEVERED CASH FLOW (equity)</t>
         </is>
       </c>
-      <c r="C70" s="44">
-        <f>-C44</f>
-        <v/>
-      </c>
-      <c r="D70" s="44">
-        <f>IF(1&lt;=C36,D63-C43,0)+IF(1=C36,D66-D68,0)</f>
-        <v/>
-      </c>
-      <c r="E70" s="45">
-        <f>IF(2&lt;=C36,E63-C43,0)+IF(2=C36,E66-E68,0)</f>
-        <v/>
-      </c>
-      <c r="F70" s="45">
-        <f>IF(3&lt;=C36,F63-C43,0)+IF(3=C36,F66-F68,0)</f>
-        <v/>
-      </c>
-      <c r="G70" s="45">
-        <f>IF(4&lt;=C36,G63-C43,0)+IF(4=C36,G66-G68,0)</f>
-        <v/>
-      </c>
-      <c r="H70" s="45">
-        <f>IF(5&lt;=C36,H63-C43,0)+IF(5=C36,H66-H68,0)</f>
-        <v/>
-      </c>
-      <c r="I70" s="45">
-        <f>IF(6&lt;=C36,I63-C43,0)+IF(6=C36,I66-I68,0)</f>
-        <v/>
-      </c>
-      <c r="J70" s="45">
-        <f>IF(7&lt;=C36,J63-C43,0)+IF(7=C36,J66-J68,0)</f>
-        <v/>
-      </c>
-      <c r="K70" s="45">
-        <f>IF(8&lt;=C36,K63-C43,0)+IF(8=C36,K66-K68,0)</f>
-        <v/>
-      </c>
-      <c r="L70" s="45">
-        <f>IF(9&lt;=C36,L63-C43,0)+IF(9=C36,L66-L68,0)</f>
-        <v/>
-      </c>
-      <c r="M70" s="45">
-        <f>IF(10&lt;=C36,M63-C43,0)+IF(10=C36,M66-M68,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="71"/>
-    <row r="72">
-      <c r="B72" s="11" t="inlineStr">
+      <c r="C71" s="44">
+        <f>-C45</f>
+        <v/>
+      </c>
+      <c r="D71" s="44">
+        <f>IF(1&lt;=C37,D64-C44,0)+IF(1=C37,D67-D69,0)</f>
+        <v/>
+      </c>
+      <c r="E71" s="45">
+        <f>IF(2&lt;=C37,E64-C44,0)+IF(2=C37,E67-E69,0)</f>
+        <v/>
+      </c>
+      <c r="F71" s="45">
+        <f>IF(3&lt;=C37,F64-C44,0)+IF(3=C37,F67-F69,0)</f>
+        <v/>
+      </c>
+      <c r="G71" s="45">
+        <f>IF(4&lt;=C37,G64-C44,0)+IF(4=C37,G67-G69,0)</f>
+        <v/>
+      </c>
+      <c r="H71" s="45">
+        <f>IF(5&lt;=C37,H64-C44,0)+IF(5=C37,H67-H69,0)</f>
+        <v/>
+      </c>
+      <c r="I71" s="45">
+        <f>IF(6&lt;=C37,I64-C44,0)+IF(6=C37,I67-I69,0)</f>
+        <v/>
+      </c>
+      <c r="J71" s="45">
+        <f>IF(7&lt;=C37,J64-C44,0)+IF(7=C37,J67-J69,0)</f>
+        <v/>
+      </c>
+      <c r="K71" s="45">
+        <f>IF(8&lt;=C37,K64-C44,0)+IF(8=C37,K67-K69,0)</f>
+        <v/>
+      </c>
+      <c r="L71" s="45">
+        <f>IF(9&lt;=C37,L64-C44,0)+IF(9=C37,L67-L69,0)</f>
+        <v/>
+      </c>
+      <c r="M71" s="45">
+        <f>IF(10&lt;=C37,M64-C44,0)+IF(10=C37,M67-M69,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="72"/>
+    <row r="73">
+      <c r="B73" s="11" t="inlineStr">
         <is>
           <t>RETURNS  —  unlevered &amp; levered</t>
         </is>
       </c>
-      <c r="C72" s="2" t="n"/>
-      <c r="D72" s="2" t="n"/>
-      <c r="E72" s="2" t="n"/>
-      <c r="F72" s="2" t="n"/>
-      <c r="G72" s="2" t="n"/>
-      <c r="H72" s="2" t="n"/>
-      <c r="I72" s="2" t="n"/>
-      <c r="J72" s="2" t="n"/>
-      <c r="K72" s="2" t="n"/>
-      <c r="L72" s="2" t="n"/>
-      <c r="M72" s="3" t="n"/>
-    </row>
-    <row r="73" ht="15" customHeight="1">
-      <c r="B73" s="12" t="inlineStr">
-        <is>
-          <t>Unlevered IRR</t>
-        </is>
-      </c>
-      <c r="C73" s="53">
-        <f>IRR(C67:M67)</f>
-        <v/>
-      </c>
+      <c r="C73" s="2" t="n"/>
+      <c r="D73" s="2" t="n"/>
+      <c r="E73" s="2" t="n"/>
+      <c r="F73" s="2" t="n"/>
+      <c r="G73" s="2" t="n"/>
+      <c r="H73" s="2" t="n"/>
+      <c r="I73" s="2" t="n"/>
+      <c r="J73" s="2" t="n"/>
+      <c r="K73" s="2" t="n"/>
+      <c r="L73" s="2" t="n"/>
+      <c r="M73" s="3" t="n"/>
     </row>
     <row r="74" ht="15" customHeight="1">
       <c r="B74" s="12" t="inlineStr">
         <is>
-          <t>Unlevered equity multiple</t>
-        </is>
-      </c>
-      <c r="C74" s="54">
-        <f>SUM(D67:M67)/-C67</f>
+          <t>Unlevered IRR</t>
+        </is>
+      </c>
+      <c r="C74" s="53">
+        <f>IRR(C68:M68)</f>
         <v/>
       </c>
     </row>
     <row r="75" ht="15" customHeight="1">
       <c r="B75" s="12" t="inlineStr">
         <is>
-          <t>Unlevered NPV @ discount rate</t>
-        </is>
-      </c>
-      <c r="C75" s="51">
-        <f>C67+NPV(C37,D67:M67)</f>
+          <t>Unlevered equity multiple</t>
+        </is>
+      </c>
+      <c r="C75" s="54">
+        <f>SUM(D68:M68)/-C68</f>
         <v/>
       </c>
     </row>
     <row r="76" ht="15" customHeight="1">
       <c r="B76" s="12" t="inlineStr">
         <is>
-          <t>Levered IRR</t>
-        </is>
-      </c>
-      <c r="C76" s="53">
-        <f>IRR(C70:M70)</f>
+          <t>Unlevered NPV @ discount rate</t>
+        </is>
+      </c>
+      <c r="C76" s="51">
+        <f>C68+NPV(C38,D68:M68)</f>
         <v/>
       </c>
     </row>
     <row r="77" ht="15" customHeight="1">
       <c r="B77" s="12" t="inlineStr">
         <is>
-          <t>Levered equity multiple</t>
-        </is>
-      </c>
-      <c r="C77" s="54">
-        <f>SUM(D70:M70)/C44</f>
+          <t>Levered IRR</t>
+        </is>
+      </c>
+      <c r="C77" s="53">
+        <f>IRR(C71:M71)</f>
         <v/>
       </c>
     </row>
     <row r="78" ht="15" customHeight="1">
       <c r="B78" s="12" t="inlineStr">
         <is>
-          <t>Year-1 NOI (pro-forma)</t>
-        </is>
-      </c>
-      <c r="C78" s="51">
-        <f>D61</f>
+          <t>Levered equity multiple</t>
+        </is>
+      </c>
+      <c r="C78" s="54">
+        <f>SUM(D71:M71)/C45</f>
         <v/>
       </c>
     </row>
     <row r="79" ht="15" customHeight="1">
       <c r="B79" s="12" t="inlineStr">
         <is>
-          <t>As-is in-place NOI (at occ0, no lease-up)</t>
+          <t>Year-1 NOI (pro-forma)</t>
         </is>
       </c>
       <c r="C79" s="51">
-        <f>(C17*C18*C20)-(C17*C18*C20)*C22-(C28*C23+C17*C24)-((C17*C18*C20)-(C17*C18*C20)*C22)*C25</f>
+        <f>D62</f>
         <v/>
       </c>
     </row>
     <row r="80" ht="15" customHeight="1">
       <c r="B80" s="12" t="inlineStr">
         <is>
-          <t>Going-in cap (as-is NOI ÷ price)</t>
-        </is>
-      </c>
-      <c r="C80" s="50">
-        <f>C79/C28</f>
+          <t>As-is in-place NOI (at occ0, no lease-up)</t>
+        </is>
+      </c>
+      <c r="C80" s="51">
+        <f>(C18*C19*C21)-(C18*C19*C21)*C23-(C29*C24+C18*C25)-((C18*C19*C21)-(C18*C19*C21)*C23)*C26</f>
         <v/>
       </c>
     </row>
     <row r="81" ht="15" customHeight="1">
       <c r="B81" s="12" t="inlineStr">
         <is>
-          <t>Stabilized NOI (Yr 2)</t>
-        </is>
-      </c>
-      <c r="C81" s="51">
-        <f>E61</f>
+          <t>Going-in cap (as-is NOI ÷ price)</t>
+        </is>
+      </c>
+      <c r="C81" s="50">
+        <f>C80/C29</f>
         <v/>
       </c>
     </row>
     <row r="82" ht="15" customHeight="1">
       <c r="B82" s="12" t="inlineStr">
         <is>
-          <t>Stabilized value (÷ exit cap)</t>
+          <t>Stabilized NOI (Yr 2)</t>
         </is>
       </c>
       <c r="C82" s="51">
-        <f>C81/C34</f>
+        <f>E62</f>
         <v/>
       </c>
     </row>
     <row r="83" ht="15" customHeight="1">
       <c r="B83" s="12" t="inlineStr">
         <is>
-          <t>In-place NOI per SF</t>
-        </is>
-      </c>
-      <c r="C83" s="68">
-        <f>D61/C17</f>
+          <t>Stabilized value (÷ exit cap)</t>
+        </is>
+      </c>
+      <c r="C83" s="51">
+        <f>C82/C35</f>
         <v/>
       </c>
     </row>
     <row r="84" ht="15" customHeight="1">
       <c r="B84" s="12" t="inlineStr">
         <is>
-          <t>Income value (Yr-1 NOI ÷ going-in cap)</t>
-        </is>
-      </c>
-      <c r="C84" s="51">
-        <f>D61/C33</f>
+          <t>In-place NOI per SF</t>
+        </is>
+      </c>
+      <c r="C84" s="68">
+        <f>D62/C18</f>
         <v/>
       </c>
     </row>
     <row r="85" ht="15" customHeight="1">
       <c r="B85" s="12" t="inlineStr">
         <is>
+          <t>Income value (Yr-1 NOI ÷ going-in cap)</t>
+        </is>
+      </c>
+      <c r="C85" s="51">
+        <f>D62/C34</f>
+        <v/>
+      </c>
+    </row>
+    <row r="86" ht="15" customHeight="1">
+      <c r="B86" s="12" t="inlineStr">
+        <is>
           <t>Sale-comp value (SF × $/SF)</t>
         </is>
       </c>
-      <c r="C85" s="51">
-        <f>C17*C38</f>
-        <v/>
-      </c>
-    </row>
-    <row r="86"/>
-    <row r="87">
-      <c r="B87" s="11" t="inlineStr">
-        <is>
-          <t>OWNERS &amp; FULL BUY-OUT  —  every identifiable owner modeled individually  (⚠️ BCPA/Clerk egress-blocked; balance grouped)</t>
-        </is>
-      </c>
-      <c r="C87" s="2" t="n"/>
-      <c r="D87" s="2" t="n"/>
-      <c r="E87" s="2" t="n"/>
-      <c r="F87" s="2" t="n"/>
-      <c r="G87" s="2" t="n"/>
-      <c r="H87" s="2" t="n"/>
-      <c r="I87" s="2" t="n"/>
-      <c r="J87" s="2" t="n"/>
-      <c r="K87" s="2" t="n"/>
-      <c r="L87" s="2" t="n"/>
-      <c r="M87" s="3" t="n"/>
-    </row>
-    <row r="88" ht="27" customHeight="1">
-      <c r="B88" s="12" t="inlineStr">
-        <is>
-          <t>Condo buyout premium (fractured ownership / holdout)</t>
-        </is>
-      </c>
-      <c r="C88" s="84" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="D88" s="22" t="inlineStr">
-        <is>
-          <t>🔵 uplift over income value to get owners to sell</t>
-        </is>
-      </c>
-      <c r="E88" s="13" t="n"/>
-      <c r="F88" s="13" t="n"/>
-      <c r="G88" s="13" t="n"/>
-      <c r="H88" s="13" t="n"/>
-      <c r="I88" s="13" t="n"/>
-      <c r="J88" s="13" t="n"/>
-      <c r="K88" s="13" t="n"/>
-      <c r="L88" s="13" t="n"/>
-      <c r="M88" s="14" t="n"/>
+      <c r="C86" s="51">
+        <f>C18*C39</f>
+        <v/>
+      </c>
+    </row>
+    <row r="87"/>
+    <row r="88">
+      <c r="B88" s="11" t="inlineStr">
+        <is>
+          <t>OWNERS &amp; FULL BUY-OUT  —  every identifiable owner; buy-out at UNIT-MARKET $/SF  (⚠️ BCPA blocked; balance grouped)</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="n"/>
+      <c r="D88" s="2" t="n"/>
+      <c r="E88" s="2" t="n"/>
+      <c r="F88" s="2" t="n"/>
+      <c r="G88" s="2" t="n"/>
+      <c r="H88" s="2" t="n"/>
+      <c r="I88" s="2" t="n"/>
+      <c r="J88" s="2" t="n"/>
+      <c r="K88" s="2" t="n"/>
+      <c r="L88" s="2" t="n"/>
+      <c r="M88" s="3" t="n"/>
     </row>
     <row r="89" ht="15" customHeight="1">
-      <c r="B89" s="15" t="inlineStr">
-        <is>
-          <t>Owner / unit</t>
-        </is>
-      </c>
-      <c r="C89" s="14" t="n"/>
-      <c r="D89" s="16" t="inlineStr">
-        <is>
-          <t>SF</t>
-        </is>
-      </c>
-      <c r="E89" s="16" t="inlineStr">
-        <is>
-          <t>% bldg</t>
-        </is>
-      </c>
-      <c r="F89" s="16" t="inlineStr">
-        <is>
-          <t>Orig basis</t>
-        </is>
-      </c>
-      <c r="G89" s="16" t="inlineStr">
-        <is>
-          <t>Bought</t>
-        </is>
-      </c>
-      <c r="H89" s="16" t="inlineStr">
-        <is>
-          <t>Income value</t>
-        </is>
-      </c>
-      <c r="I89" s="16" t="inlineStr">
-        <is>
-          <t>Buy-out value</t>
-        </is>
-      </c>
-      <c r="J89" s="15" t="inlineStr">
-        <is>
-          <t>Note</t>
-        </is>
-      </c>
+      <c r="B89" s="12" t="inlineStr">
+        <is>
+          <t>Buy-out $/SF (unit market)</t>
+        </is>
+      </c>
+      <c r="C89" s="79" t="n">
+        <v>225</v>
+      </c>
+      <c r="D89" s="22" t="inlineStr">
+        <is>
+          <t>🔵 closed comps: 805 $238 · CU-11A $276 · 401 $381; Grove Gate resale ask ~$270–285 (bulk-discounted here)</t>
+        </is>
+      </c>
+      <c r="E89" s="13" t="n"/>
+      <c r="F89" s="13" t="n"/>
+      <c r="G89" s="13" t="n"/>
+      <c r="H89" s="13" t="n"/>
+      <c r="I89" s="13" t="n"/>
+      <c r="J89" s="13" t="n"/>
       <c r="K89" s="13" t="n"/>
       <c r="L89" s="13" t="n"/>
       <c r="M89" s="14" t="n"/>
     </row>
-    <row r="90" ht="27" customHeight="1">
-      <c r="B90" s="12" t="inlineStr">
-        <is>
-          <t>Main Street Fund LLC (Grove Gate)</t>
+    <row r="90" ht="15" customHeight="1">
+      <c r="B90" s="15" t="inlineStr">
+        <is>
+          <t>Owner / unit</t>
         </is>
       </c>
       <c r="C90" s="14" t="n"/>
-      <c r="D90" s="77" t="n">
-        <v>96930</v>
-      </c>
-      <c r="E90" s="53">
-        <f>D90/C17</f>
-        <v/>
-      </c>
-      <c r="F90" s="72" t="n">
-        <v>10000000</v>
-      </c>
-      <c r="G90" s="71" t="inlineStr">
-        <is>
-          <t>09/2019</t>
-        </is>
-      </c>
-      <c r="H90" s="47">
-        <f>C83*D90/C33</f>
-        <v/>
-      </c>
-      <c r="I90" s="47">
-        <f>H90*(1+C88)</f>
-        <v/>
-      </c>
-      <c r="J90" s="12" t="inlineStr">
-        <is>
-          <t>57.4% + 2 parking lots · ✅ press · NOW RESELLING units individually</t>
+      <c r="D90" s="16" t="inlineStr">
+        <is>
+          <t>SF</t>
+        </is>
+      </c>
+      <c r="E90" s="16" t="inlineStr">
+        <is>
+          <t>% bldg</t>
+        </is>
+      </c>
+      <c r="F90" s="16" t="inlineStr">
+        <is>
+          <t>Orig basis</t>
+        </is>
+      </c>
+      <c r="G90" s="16" t="inlineStr">
+        <is>
+          <t>Bought</t>
+        </is>
+      </c>
+      <c r="H90" s="16" t="inlineStr">
+        <is>
+          <t>Income value</t>
+        </is>
+      </c>
+      <c r="I90" s="16" t="inlineStr">
+        <is>
+          <t>Buy-out ($/SF)</t>
+        </is>
+      </c>
+      <c r="J90" s="15" t="inlineStr">
+        <is>
+          <t>Note</t>
         </is>
       </c>
       <c r="K90" s="13" t="n"/>
@@ -4369,38 +4348,36 @@
     <row r="91" ht="27" customHeight="1">
       <c r="B91" s="12" t="inlineStr">
         <is>
-          <t>International Sunrise Partners LLC</t>
+          <t>Main Street Fund LLC — Grove Gate (Brad Weiss)</t>
         </is>
       </c>
       <c r="C91" s="14" t="n"/>
-      <c r="D91" s="77" t="n">
-        <v>40000</v>
+      <c r="D91" s="78" t="n">
+        <v>94381</v>
       </c>
       <c r="E91" s="53">
-        <f>D91/C17</f>
-        <v/>
-      </c>
-      <c r="F91" s="90" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G91" s="42" t="inlineStr">
-        <is>
-          <t>2011</t>
+        <f>D91/C18</f>
+        <v/>
+      </c>
+      <c r="F91" s="72" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="G91" s="71" t="inlineStr">
+        <is>
+          <t>09/2019</t>
         </is>
       </c>
       <c r="H91" s="47">
-        <f>C83*D91/C33</f>
+        <f>C84*D91/C34</f>
         <v/>
       </c>
       <c r="I91" s="47">
-        <f>H91*(1+C88)</f>
+        <f>D91*C89</f>
         <v/>
       </c>
       <c r="J91" s="12" t="inlineStr">
         <is>
-          <t>Bush Development condo-conversion sponsor · retained balance · SF est.</t>
+          <t>57.4% bulk @ $103/SF; RESELLING units $270–381/SF · controls the condo board</t>
         </is>
       </c>
       <c r="K91" s="13" t="n"/>
@@ -4410,15 +4387,15 @@
     <row r="92" ht="15" customHeight="1">
       <c r="B92" s="12" t="inlineStr">
         <is>
-          <t>P. Jorgensen Management LLC — Ste 805</t>
+          <t>P. Jorgensen Mgmt — Ste 805</t>
         </is>
       </c>
       <c r="C92" s="14" t="n"/>
-      <c r="D92" s="77" t="n">
+      <c r="D92" s="78" t="n">
         <v>1722</v>
       </c>
       <c r="E92" s="53">
-        <f>D92/C17</f>
+        <f>D92/C18</f>
         <v/>
       </c>
       <c r="F92" s="72" t="n">
@@ -4430,16 +4407,16 @@
         </is>
       </c>
       <c r="H92" s="47">
-        <f>C83*D92/C33</f>
+        <f>C84*D92/C34</f>
         <v/>
       </c>
       <c r="I92" s="47">
-        <f>H92*(1+C88)</f>
+        <f>D92*C89</f>
         <v/>
       </c>
       <c r="J92" s="12" t="inlineStr">
         <is>
-          <t>Denmark-based US HQ · ✅ press (Berger Commercial)</t>
+          <t>$238/SF · ✅ Berger Commercial (prior owner Pelican Invest)</t>
         </is>
       </c>
       <c r="K92" s="13" t="n"/>
@@ -4449,38 +4426,36 @@
     <row r="93" ht="15" customHeight="1">
       <c r="B93" s="12" t="inlineStr">
         <is>
-          <t>Hublot of America, Inc. — Ste 402</t>
+          <t>CU-11A owner</t>
         </is>
       </c>
       <c r="C93" s="14" t="n"/>
-      <c r="D93" s="77" t="n">
-        <v>2000</v>
+      <c r="D93" s="78" t="n">
+        <v>1867</v>
       </c>
       <c r="E93" s="53">
-        <f>D93/C17</f>
-        <v/>
-      </c>
-      <c r="F93" s="90" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G93" s="42" t="inlineStr">
-        <is>
-          <t>—</t>
+        <f>D93/C18</f>
+        <v/>
+      </c>
+      <c r="F93" s="72" t="n">
+        <v>515000</v>
+      </c>
+      <c r="G93" s="71" t="inlineStr">
+        <is>
+          <t>02/2025</t>
         </is>
       </c>
       <c r="H93" s="47">
-        <f>C83*D93/C33</f>
+        <f>C84*D93/C34</f>
         <v/>
       </c>
       <c r="I93" s="47">
-        <f>H93*(1+C88)</f>
+        <f>D93*C89</f>
         <v/>
       </c>
       <c r="J93" s="12" t="inlineStr">
         <is>
-          <t>Swiss watchmaker boutique · SF est. · ⚠️ reported</t>
+          <t>$276/SF closed · ✅ Elliman MLS A11538174</t>
         </is>
       </c>
       <c r="K93" s="13" t="n"/>
@@ -4490,38 +4465,36 @@
     <row r="94" ht="15" customHeight="1">
       <c r="B94" s="12" t="inlineStr">
         <is>
-          <t>Merrimac Ventures (Motwani) — unit(s)</t>
+          <t>Unit 401 owner — Ste 401</t>
         </is>
       </c>
       <c r="C94" s="14" t="n"/>
-      <c r="D94" s="77" t="n">
-        <v>3000</v>
+      <c r="D94" s="78" t="n">
+        <v>682</v>
       </c>
       <c r="E94" s="53">
-        <f>D94/C17</f>
-        <v/>
-      </c>
-      <c r="F94" s="90" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G94" s="42" t="inlineStr">
-        <is>
-          <t>—</t>
+        <f>D94/C18</f>
+        <v/>
+      </c>
+      <c r="F94" s="72" t="n">
+        <v>260000</v>
+      </c>
+      <c r="G94" s="71" t="inlineStr">
+        <is>
+          <t>06/2024</t>
         </is>
       </c>
       <c r="H94" s="47">
-        <f>C83*D94/C33</f>
+        <f>C84*D94/C34</f>
         <v/>
       </c>
       <c r="I94" s="47">
-        <f>H94*(1+C88)</f>
+        <f>D94*C89</f>
         <v/>
       </c>
       <c r="J94" s="12" t="inlineStr">
         <is>
-          <t>reported owner · SF est. · ⚠️ reported</t>
+          <t>$381/SF closed · ✅ MLS A11438689</t>
         </is>
       </c>
       <c r="K94" s="13" t="n"/>
@@ -4531,36 +4504,38 @@
     <row r="95" ht="15" customHeight="1">
       <c r="B95" s="12" t="inlineStr">
         <is>
-          <t>Unit 401 owner — Ste 401</t>
+          <t>Merrimac Ventures — Motwani family</t>
         </is>
       </c>
       <c r="C95" s="14" t="n"/>
-      <c r="D95" s="77" t="n">
-        <v>682</v>
+      <c r="D95" s="78" t="n">
+        <v>3000</v>
       </c>
       <c r="E95" s="53">
-        <f>D95/C17</f>
-        <v/>
-      </c>
-      <c r="F95" s="72" t="n">
-        <v>260000</v>
-      </c>
-      <c r="G95" s="71" t="inlineStr">
-        <is>
-          <t>06/2024</t>
+        <f>D95/C18</f>
+        <v/>
+      </c>
+      <c r="F95" s="74" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G95" s="42" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="H95" s="47">
-        <f>C83*D95/C33</f>
+        <f>C84*D95/C34</f>
         <v/>
       </c>
       <c r="I95" s="47">
-        <f>H95*(1+C88)</f>
+        <f>D95*C89</f>
         <v/>
       </c>
       <c r="J95" s="12" t="inlineStr">
         <is>
-          <t>sold via MLS 6/2024 · ⚠️ reported</t>
+          <t>Dev &amp; Nitin Motwani (co-mgrs) · ✅ owner · SF est.</t>
         </is>
       </c>
       <c r="K95" s="13" t="n"/>
@@ -4570,18 +4545,18 @@
     <row r="96" ht="15" customHeight="1">
       <c r="B96" s="12" t="inlineStr">
         <is>
-          <t>Other unit owners (dozens of small units)</t>
+          <t>Cosmo Int'l Fragrances — Marc Blaison</t>
         </is>
       </c>
       <c r="C96" s="14" t="n"/>
-      <c r="D96" s="77" t="n">
-        <v>24473</v>
+      <c r="D96" s="78" t="n">
+        <v>2000</v>
       </c>
       <c r="E96" s="53">
-        <f>D96/C17</f>
-        <v/>
-      </c>
-      <c r="F96" s="90" t="inlineStr">
+        <f>D96/C18</f>
+        <v/>
+      </c>
+      <c r="F96" s="74" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4592,58 +4567,57 @@
         </is>
       </c>
       <c r="H96" s="47">
-        <f>C83*D96/C33</f>
+        <f>C84*D96/C34</f>
         <v/>
       </c>
       <c r="I96" s="47">
-        <f>H96*(1+C88)</f>
+        <f>D96*C89</f>
         <v/>
       </c>
       <c r="J96" s="12" t="inlineStr">
         <is>
-          <t>⚠️ balance — needs a BCPA folio pull to itemize each</t>
+          <t>owner-occupant · condo board president · SF est.</t>
         </is>
       </c>
       <c r="K96" s="13" t="n"/>
       <c r="L96" s="13" t="n"/>
       <c r="M96" s="14" t="n"/>
     </row>
-    <row r="97" ht="16" customHeight="1">
-      <c r="B97" s="55" t="inlineStr">
-        <is>
-          <t>TOTAL BUILDING — FULL BUY-OUT</t>
+    <row r="97" ht="15" customHeight="1">
+      <c r="B97" s="12" t="inlineStr">
+        <is>
+          <t>Hublot of America — Ste 402</t>
         </is>
       </c>
       <c r="C97" s="14" t="n"/>
-      <c r="D97" s="91">
-        <f>SUM(D90:D96)</f>
-        <v/>
-      </c>
-      <c r="E97" s="92">
-        <f>SUM(E90:E96)</f>
-        <v/>
-      </c>
-      <c r="F97" s="93" t="inlineStr">
+      <c r="D97" s="78" t="n">
+        <v>2000</v>
+      </c>
+      <c r="E97" s="53">
+        <f>D97/C18</f>
+        <v/>
+      </c>
+      <c r="F97" s="74" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G97" s="93" t="inlineStr">
+      <c r="G97" s="42" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H97" s="56">
-        <f>SUM(H90:H96)</f>
-        <v/>
-      </c>
-      <c r="I97" s="56">
-        <f>SUM(I90:I96)</f>
-        <v/>
-      </c>
-      <c r="J97" s="55" t="inlineStr">
-        <is>
-          <t>cost to control the whole building</t>
+      <c r="H97" s="47">
+        <f>C84*D97/C34</f>
+        <v/>
+      </c>
+      <c r="I97" s="47">
+        <f>D97*C89</f>
+        <v/>
+      </c>
+      <c r="J97" s="12" t="inlineStr">
+        <is>
+          <t>Swiss watchmaker boutique · owner-occ · SF est.</t>
         </is>
       </c>
       <c r="K97" s="13" t="n"/>
@@ -4651,157 +4625,188 @@
       <c r="M97" s="14" t="n"/>
     </row>
     <row r="98" ht="15" customHeight="1">
-      <c r="B98" s="22" t="inlineStr">
-        <is>
-          <t>cross-check — income value (no premium) vs. $300/SF comp</t>
+      <c r="B98" s="12" t="inlineStr">
+        <is>
+          <t>Other unit owners (~40 small units)</t>
         </is>
       </c>
       <c r="C98" s="14" t="n"/>
-      <c r="H98" s="94">
-        <f>H97</f>
-        <v/>
-      </c>
-      <c r="I98" s="94">
-        <f>C85</f>
-        <v/>
-      </c>
-    </row>
-    <row r="99"/>
-    <row r="100">
-      <c r="B100" s="11" t="inlineStr">
-        <is>
-          <t>PROFIT &amp; LOSS STATEMENT  —  Year 1 vs. Stabilized (Yr 2)</t>
-        </is>
-      </c>
-      <c r="C100" s="2" t="n"/>
-      <c r="D100" s="2" t="n"/>
-      <c r="E100" s="2" t="n"/>
-      <c r="F100" s="2" t="n"/>
-      <c r="G100" s="2" t="n"/>
-      <c r="H100" s="2" t="n"/>
-      <c r="I100" s="2" t="n"/>
-      <c r="J100" s="2" t="n"/>
-      <c r="K100" s="2" t="n"/>
-      <c r="L100" s="2" t="n"/>
-      <c r="M100" s="3" t="n"/>
-    </row>
-    <row r="101" ht="15" customHeight="1">
-      <c r="B101" s="15" t="inlineStr">
-        <is>
-          <t>$ / year</t>
-        </is>
-      </c>
-      <c r="F101" s="87" t="inlineStr">
-        <is>
-          <t>Year 1</t>
-        </is>
-      </c>
-      <c r="G101" s="14" t="n"/>
-      <c r="H101" s="87" t="inlineStr">
-        <is>
-          <t>Stabilized</t>
-        </is>
-      </c>
-      <c r="I101" s="14" t="n"/>
-      <c r="J101" s="87" t="inlineStr">
-        <is>
-          <t>Per SF (stab.)</t>
-        </is>
-      </c>
+      <c r="D98" s="78" t="n">
+        <v>63155</v>
+      </c>
+      <c r="E98" s="53">
+        <f>D98/C18</f>
+        <v/>
+      </c>
+      <c r="F98" s="74" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G98" s="42" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H98" s="47">
+        <f>C84*D98/C34</f>
+        <v/>
+      </c>
+      <c r="I98" s="47">
+        <f>D98*C89</f>
+        <v/>
+      </c>
+      <c r="J98" s="12" t="inlineStr">
+        <is>
+          <t>⚠️ balance of the 42.6% — needs a BCPA folio pull to itemize</t>
+        </is>
+      </c>
+      <c r="K98" s="13" t="n"/>
+      <c r="L98" s="13" t="n"/>
+      <c r="M98" s="14" t="n"/>
+    </row>
+    <row r="99" ht="16" customHeight="1">
+      <c r="B99" s="55" t="inlineStr">
+        <is>
+          <t>TOTAL BUILDING — FULL BUY-OUT</t>
+        </is>
+      </c>
+      <c r="C99" s="14" t="n"/>
+      <c r="D99" s="91">
+        <f>SUM(D91:D98)</f>
+        <v/>
+      </c>
+      <c r="E99" s="92">
+        <f>SUM(E91:E98)</f>
+        <v/>
+      </c>
+      <c r="F99" s="93" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G99" s="93" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H99" s="56">
+        <f>SUM(H91:H98)</f>
+        <v/>
+      </c>
+      <c r="I99" s="56">
+        <f>SUM(I91:I98)</f>
+        <v/>
+      </c>
+      <c r="J99" s="55" t="inlineStr">
+        <is>
+          <t>cost to control the whole building</t>
+        </is>
+      </c>
+      <c r="K99" s="13" t="n"/>
+      <c r="L99" s="13" t="n"/>
+      <c r="M99" s="14" t="n"/>
+    </row>
+    <row r="100" ht="27" customHeight="1">
+      <c r="B100" s="12" t="inlineStr">
+        <is>
+          <t>Income value (cross-check — what rent supports)</t>
+        </is>
+      </c>
+      <c r="C100" s="47">
+        <f>H99</f>
+        <v/>
+      </c>
+    </row>
+    <row r="101" ht="29" customHeight="1">
+      <c r="B101" s="55" t="inlineStr">
+        <is>
+          <t>FRAGMENTATION PREMIUM (buy-out − income value)</t>
+        </is>
+      </c>
+      <c r="C101" s="56">
+        <f>I99-H99</f>
+        <v/>
+      </c>
+      <c r="D101" s="40" t="inlineStr">
+        <is>
+          <t>the office trades higher as fragmented condos than as one income asset — you overpay ~2× income value to re-assemble it</t>
+        </is>
+      </c>
+      <c r="E101" s="13" t="n"/>
+      <c r="F101" s="13" t="n"/>
+      <c r="G101" s="13" t="n"/>
+      <c r="H101" s="13" t="n"/>
+      <c r="I101" s="13" t="n"/>
+      <c r="J101" s="13" t="n"/>
       <c r="K101" s="13" t="n"/>
       <c r="L101" s="13" t="n"/>
       <c r="M101" s="14" t="n"/>
     </row>
-    <row r="102" ht="15" customHeight="1">
-      <c r="B102" s="52" t="inlineStr">
-        <is>
-          <t>Gross rental income (MG)</t>
-        </is>
-      </c>
-      <c r="F102" s="45">
-        <f>D53</f>
-        <v/>
-      </c>
-      <c r="G102" s="14" t="n"/>
-      <c r="H102" s="44">
-        <f>E53</f>
-        <v/>
-      </c>
-      <c r="I102" s="14" t="n"/>
-      <c r="J102" s="88">
-        <f>H102/C17</f>
-        <v/>
-      </c>
-      <c r="K102" s="13" t="n"/>
-      <c r="L102" s="13" t="n"/>
-      <c r="M102" s="14" t="n"/>
-    </row>
-    <row r="103" ht="15" customHeight="1">
-      <c r="B103" s="12" t="inlineStr">
-        <is>
-          <t>Less: credit &amp; vacancy loss</t>
-        </is>
-      </c>
-      <c r="F103" s="47">
-        <f>D54</f>
-        <v/>
-      </c>
-      <c r="G103" s="14" t="n"/>
-      <c r="H103" s="47">
-        <f>E54</f>
-        <v/>
-      </c>
-      <c r="I103" s="14" t="n"/>
-      <c r="J103" s="68">
-        <f>H103/C17</f>
-        <v/>
-      </c>
-      <c r="K103" s="13" t="n"/>
-      <c r="L103" s="13" t="n"/>
-      <c r="M103" s="14" t="n"/>
+    <row r="102"/>
+    <row r="103">
+      <c r="B103" s="11" t="inlineStr">
+        <is>
+          <t>PROFIT &amp; LOSS STATEMENT  —  Year 1 vs. Stabilized (Yr 2)</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="n"/>
+      <c r="D103" s="2" t="n"/>
+      <c r="E103" s="2" t="n"/>
+      <c r="F103" s="2" t="n"/>
+      <c r="G103" s="2" t="n"/>
+      <c r="H103" s="2" t="n"/>
+      <c r="I103" s="2" t="n"/>
+      <c r="J103" s="2" t="n"/>
+      <c r="K103" s="2" t="n"/>
+      <c r="L103" s="2" t="n"/>
+      <c r="M103" s="3" t="n"/>
     </row>
     <row r="104" ht="15" customHeight="1">
-      <c r="B104" s="43" t="inlineStr">
-        <is>
-          <t>Effective Gross Income</t>
-        </is>
-      </c>
-      <c r="F104" s="45">
-        <f>D55</f>
-        <v/>
+      <c r="B104" s="15" t="inlineStr">
+        <is>
+          <t>$ / year</t>
+        </is>
+      </c>
+      <c r="F104" s="88" t="inlineStr">
+        <is>
+          <t>Year 1</t>
+        </is>
       </c>
       <c r="G104" s="14" t="n"/>
-      <c r="H104" s="44">
-        <f>E55</f>
-        <v/>
+      <c r="H104" s="88" t="inlineStr">
+        <is>
+          <t>Stabilized</t>
+        </is>
       </c>
       <c r="I104" s="14" t="n"/>
-      <c r="J104" s="88">
-        <f>H104/C17</f>
-        <v/>
+      <c r="J104" s="88" t="inlineStr">
+        <is>
+          <t>Per SF (stab.)</t>
+        </is>
       </c>
       <c r="K104" s="13" t="n"/>
       <c r="L104" s="13" t="n"/>
       <c r="M104" s="14" t="n"/>
     </row>
     <row r="105" ht="15" customHeight="1">
-      <c r="B105" s="12" t="inlineStr">
-        <is>
-          <t>Real-estate taxes</t>
-        </is>
-      </c>
-      <c r="F105" s="47">
-        <f>-D57</f>
+      <c r="B105" s="52" t="inlineStr">
+        <is>
+          <t>Gross rental income (MG)</t>
+        </is>
+      </c>
+      <c r="F105" s="45">
+        <f>D54</f>
         <v/>
       </c>
       <c r="G105" s="14" t="n"/>
-      <c r="H105" s="47">
-        <f>-E57</f>
+      <c r="H105" s="44">
+        <f>E54</f>
         <v/>
       </c>
       <c r="I105" s="14" t="n"/>
-      <c r="J105" s="68">
-        <f>H105/C17</f>
+      <c r="J105" s="89">
+        <f>H105/C18</f>
         <v/>
       </c>
       <c r="K105" s="13" t="n"/>
@@ -4811,21 +4816,21 @@
     <row r="106" ht="15" customHeight="1">
       <c r="B106" s="12" t="inlineStr">
         <is>
-          <t>Office opex (landlord)</t>
+          <t>Less: credit &amp; vacancy loss</t>
         </is>
       </c>
       <c r="F106" s="47">
-        <f>-D58</f>
+        <f>D55</f>
         <v/>
       </c>
       <c r="G106" s="14" t="n"/>
       <c r="H106" s="47">
-        <f>-E58</f>
+        <f>E55</f>
         <v/>
       </c>
       <c r="I106" s="14" t="n"/>
       <c r="J106" s="68">
-        <f>H106/C17</f>
+        <f>H106/C18</f>
         <v/>
       </c>
       <c r="K106" s="13" t="n"/>
@@ -4833,23 +4838,23 @@
       <c r="M106" s="14" t="n"/>
     </row>
     <row r="107" ht="15" customHeight="1">
-      <c r="B107" s="12" t="inlineStr">
-        <is>
-          <t>Management fee</t>
-        </is>
-      </c>
-      <c r="F107" s="47">
-        <f>-D59</f>
+      <c r="B107" s="43" t="inlineStr">
+        <is>
+          <t>Effective Gross Income</t>
+        </is>
+      </c>
+      <c r="F107" s="45">
+        <f>D56</f>
         <v/>
       </c>
       <c r="G107" s="14" t="n"/>
-      <c r="H107" s="47">
-        <f>-E59</f>
+      <c r="H107" s="44">
+        <f>E56</f>
         <v/>
       </c>
       <c r="I107" s="14" t="n"/>
-      <c r="J107" s="68">
-        <f>H107/C17</f>
+      <c r="J107" s="89">
+        <f>H107/C18</f>
         <v/>
       </c>
       <c r="K107" s="13" t="n"/>
@@ -4857,23 +4862,23 @@
       <c r="M107" s="14" t="n"/>
     </row>
     <row r="108" ht="15" customHeight="1">
-      <c r="B108" s="43" t="inlineStr">
-        <is>
-          <t>Net Operating Income</t>
-        </is>
-      </c>
-      <c r="F108" s="45">
-        <f>D61</f>
+      <c r="B108" s="12" t="inlineStr">
+        <is>
+          <t>Real-estate taxes</t>
+        </is>
+      </c>
+      <c r="F108" s="47">
+        <f>-D58</f>
         <v/>
       </c>
       <c r="G108" s="14" t="n"/>
-      <c r="H108" s="44">
-        <f>E61</f>
+      <c r="H108" s="47">
+        <f>-E58</f>
         <v/>
       </c>
       <c r="I108" s="14" t="n"/>
-      <c r="J108" s="88">
-        <f>H108/C17</f>
+      <c r="J108" s="68">
+        <f>H108/C18</f>
         <v/>
       </c>
       <c r="K108" s="13" t="n"/>
@@ -4883,21 +4888,21 @@
     <row r="109" ht="15" customHeight="1">
       <c r="B109" s="12" t="inlineStr">
         <is>
-          <t>Replacement reserves</t>
+          <t>Office opex (landlord)</t>
         </is>
       </c>
       <c r="F109" s="47">
-        <f>-D62</f>
+        <f>-D59</f>
         <v/>
       </c>
       <c r="G109" s="14" t="n"/>
       <c r="H109" s="47">
-        <f>-E62</f>
+        <f>-E59</f>
         <v/>
       </c>
       <c r="I109" s="14" t="n"/>
       <c r="J109" s="68">
-        <f>H109/C17</f>
+        <f>H109/C18</f>
         <v/>
       </c>
       <c r="K109" s="13" t="n"/>
@@ -4905,23 +4910,23 @@
       <c r="M109" s="14" t="n"/>
     </row>
     <row r="110" ht="15" customHeight="1">
-      <c r="B110" s="43" t="inlineStr">
-        <is>
-          <t>Cash Flow Before Debt</t>
-        </is>
-      </c>
-      <c r="F110" s="45">
-        <f>D63</f>
+      <c r="B110" s="12" t="inlineStr">
+        <is>
+          <t>Management fee</t>
+        </is>
+      </c>
+      <c r="F110" s="47">
+        <f>-D60</f>
         <v/>
       </c>
       <c r="G110" s="14" t="n"/>
-      <c r="H110" s="44">
-        <f>E63</f>
+      <c r="H110" s="47">
+        <f>-E60</f>
         <v/>
       </c>
       <c r="I110" s="14" t="n"/>
-      <c r="J110" s="88">
-        <f>H110/C17</f>
+      <c r="J110" s="68">
+        <f>H110/C18</f>
         <v/>
       </c>
       <c r="K110" s="13" t="n"/>
@@ -4929,23 +4934,23 @@
       <c r="M110" s="14" t="n"/>
     </row>
     <row r="111" ht="15" customHeight="1">
-      <c r="B111" s="12" t="inlineStr">
-        <is>
-          <t>Debt service</t>
-        </is>
-      </c>
-      <c r="F111" s="47">
-        <f>-C43</f>
+      <c r="B111" s="43" t="inlineStr">
+        <is>
+          <t>Net Operating Income</t>
+        </is>
+      </c>
+      <c r="F111" s="45">
+        <f>D62</f>
         <v/>
       </c>
       <c r="G111" s="14" t="n"/>
-      <c r="H111" s="47">
-        <f>-C43</f>
+      <c r="H111" s="44">
+        <f>E62</f>
         <v/>
       </c>
       <c r="I111" s="14" t="n"/>
-      <c r="J111" s="68">
-        <f>H111/C17</f>
+      <c r="J111" s="89">
+        <f>H111/C18</f>
         <v/>
       </c>
       <c r="K111" s="13" t="n"/>
@@ -4953,42 +4958,115 @@
       <c r="M111" s="14" t="n"/>
     </row>
     <row r="112" ht="15" customHeight="1">
-      <c r="B112" s="43" t="inlineStr">
-        <is>
-          <t>Cash Flow After Debt (levered)</t>
-        </is>
-      </c>
-      <c r="F112" s="44">
-        <f>F110-C43</f>
+      <c r="B112" s="12" t="inlineStr">
+        <is>
+          <t>Replacement reserves</t>
+        </is>
+      </c>
+      <c r="F112" s="47">
+        <f>-D63</f>
         <v/>
       </c>
       <c r="G112" s="14" t="n"/>
-      <c r="H112" s="44">
-        <f>H110-C43</f>
+      <c r="H112" s="47">
+        <f>-E63</f>
         <v/>
       </c>
       <c r="I112" s="14" t="n"/>
-      <c r="J112" s="88">
-        <f>H112/C17</f>
+      <c r="J112" s="68">
+        <f>H112/C18</f>
         <v/>
       </c>
       <c r="K112" s="13" t="n"/>
       <c r="L112" s="13" t="n"/>
       <c r="M112" s="14" t="n"/>
     </row>
+    <row r="113" ht="15" customHeight="1">
+      <c r="B113" s="43" t="inlineStr">
+        <is>
+          <t>Cash Flow Before Debt</t>
+        </is>
+      </c>
+      <c r="F113" s="45">
+        <f>D64</f>
+        <v/>
+      </c>
+      <c r="G113" s="14" t="n"/>
+      <c r="H113" s="44">
+        <f>E64</f>
+        <v/>
+      </c>
+      <c r="I113" s="14" t="n"/>
+      <c r="J113" s="89">
+        <f>H113/C18</f>
+        <v/>
+      </c>
+      <c r="K113" s="13" t="n"/>
+      <c r="L113" s="13" t="n"/>
+      <c r="M113" s="14" t="n"/>
+    </row>
+    <row r="114" ht="15" customHeight="1">
+      <c r="B114" s="12" t="inlineStr">
+        <is>
+          <t>Debt service</t>
+        </is>
+      </c>
+      <c r="F114" s="47">
+        <f>-C44</f>
+        <v/>
+      </c>
+      <c r="G114" s="14" t="n"/>
+      <c r="H114" s="47">
+        <f>-C44</f>
+        <v/>
+      </c>
+      <c r="I114" s="14" t="n"/>
+      <c r="J114" s="68">
+        <f>H114/C18</f>
+        <v/>
+      </c>
+      <c r="K114" s="13" t="n"/>
+      <c r="L114" s="13" t="n"/>
+      <c r="M114" s="14" t="n"/>
+    </row>
+    <row r="115" ht="15" customHeight="1">
+      <c r="B115" s="43" t="inlineStr">
+        <is>
+          <t>Cash Flow After Debt (levered)</t>
+        </is>
+      </c>
+      <c r="F115" s="44">
+        <f>F113-C44</f>
+        <v/>
+      </c>
+      <c r="G115" s="14" t="n"/>
+      <c r="H115" s="44">
+        <f>H113-C44</f>
+        <v/>
+      </c>
+      <c r="I115" s="14" t="n"/>
+      <c r="J115" s="89">
+        <f>H115/C18</f>
+        <v/>
+      </c>
+      <c r="K115" s="13" t="n"/>
+      <c r="L115" s="13" t="n"/>
+      <c r="M115" s="14" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="100">
+  <mergeCells count="103">
     <mergeCell ref="B91:C91"/>
     <mergeCell ref="B2:M2"/>
     <mergeCell ref="D37:M37"/>
     <mergeCell ref="D12:M12"/>
     <mergeCell ref="J96:M96"/>
     <mergeCell ref="D9:M9"/>
-    <mergeCell ref="F103:G103"/>
     <mergeCell ref="J105:M105"/>
     <mergeCell ref="F108:G108"/>
     <mergeCell ref="D30:M30"/>
+    <mergeCell ref="D39:M39"/>
     <mergeCell ref="B93:C93"/>
+    <mergeCell ref="H113:I113"/>
     <mergeCell ref="J106:M106"/>
     <mergeCell ref="D14:M14"/>
     <mergeCell ref="D29:M29"/>
@@ -4997,86 +5075,88 @@
     <mergeCell ref="F105:G105"/>
     <mergeCell ref="D27:M27"/>
     <mergeCell ref="H105:I105"/>
-    <mergeCell ref="D41:M41"/>
-    <mergeCell ref="B72:M72"/>
     <mergeCell ref="J108:M108"/>
-    <mergeCell ref="D17:M17"/>
     <mergeCell ref="J95:M95"/>
     <mergeCell ref="F107:G107"/>
     <mergeCell ref="H107:I107"/>
-    <mergeCell ref="B56:M56"/>
     <mergeCell ref="B90:C90"/>
     <mergeCell ref="J109:M109"/>
     <mergeCell ref="D25:M25"/>
     <mergeCell ref="J90:M90"/>
-    <mergeCell ref="H102:I102"/>
+    <mergeCell ref="B17:M17"/>
+    <mergeCell ref="B57:M57"/>
+    <mergeCell ref="B88:M88"/>
     <mergeCell ref="D5:M5"/>
     <mergeCell ref="J110:M110"/>
     <mergeCell ref="J93:M93"/>
     <mergeCell ref="F109:G109"/>
     <mergeCell ref="D31:M31"/>
     <mergeCell ref="H109:I109"/>
-    <mergeCell ref="J102:M102"/>
     <mergeCell ref="D21:M21"/>
+    <mergeCell ref="J99:M99"/>
     <mergeCell ref="F111:G111"/>
     <mergeCell ref="B4:M4"/>
     <mergeCell ref="H111:I111"/>
     <mergeCell ref="D32:M32"/>
-    <mergeCell ref="J101:M101"/>
     <mergeCell ref="H104:I104"/>
     <mergeCell ref="B95:C95"/>
-    <mergeCell ref="B89:C89"/>
     <mergeCell ref="D7:M7"/>
     <mergeCell ref="J94:M94"/>
     <mergeCell ref="H106:I106"/>
     <mergeCell ref="B97:C97"/>
-    <mergeCell ref="B48:M48"/>
     <mergeCell ref="D18:M18"/>
+    <mergeCell ref="J114:M114"/>
     <mergeCell ref="D8:M8"/>
     <mergeCell ref="B96:C96"/>
-    <mergeCell ref="B87:M87"/>
+    <mergeCell ref="D42:M42"/>
+    <mergeCell ref="B73:M73"/>
     <mergeCell ref="J97:M97"/>
     <mergeCell ref="D35:M35"/>
     <mergeCell ref="B98:C98"/>
+    <mergeCell ref="F114:G114"/>
     <mergeCell ref="J111:M111"/>
     <mergeCell ref="D20:M20"/>
     <mergeCell ref="D34:M34"/>
-    <mergeCell ref="F101:G101"/>
-    <mergeCell ref="B65:M65"/>
     <mergeCell ref="F110:G110"/>
     <mergeCell ref="H110:I110"/>
     <mergeCell ref="D22:M22"/>
     <mergeCell ref="D36:M36"/>
+    <mergeCell ref="D101:M101"/>
+    <mergeCell ref="B99:C99"/>
     <mergeCell ref="D6:M6"/>
-    <mergeCell ref="F102:G102"/>
+    <mergeCell ref="F115:G115"/>
     <mergeCell ref="D13:M13"/>
     <mergeCell ref="B92:C92"/>
-    <mergeCell ref="B100:M100"/>
     <mergeCell ref="B94:C94"/>
-    <mergeCell ref="J103:M103"/>
+    <mergeCell ref="J113:M113"/>
     <mergeCell ref="J91:M91"/>
-    <mergeCell ref="H103:I103"/>
     <mergeCell ref="F112:G112"/>
     <mergeCell ref="H112:I112"/>
+    <mergeCell ref="D15:M15"/>
+    <mergeCell ref="J115:M115"/>
     <mergeCell ref="B1:M1"/>
     <mergeCell ref="D24:M24"/>
     <mergeCell ref="D38:M38"/>
     <mergeCell ref="D33:M33"/>
+    <mergeCell ref="D89:M89"/>
+    <mergeCell ref="H114:I114"/>
+    <mergeCell ref="B103:M103"/>
     <mergeCell ref="J92:M92"/>
-    <mergeCell ref="D88:M88"/>
     <mergeCell ref="F104:G104"/>
     <mergeCell ref="D26:M26"/>
-    <mergeCell ref="B40:M40"/>
+    <mergeCell ref="F113:G113"/>
     <mergeCell ref="D10:M10"/>
+    <mergeCell ref="B49:M49"/>
     <mergeCell ref="J112:M112"/>
     <mergeCell ref="D19:M19"/>
     <mergeCell ref="F106:G106"/>
+    <mergeCell ref="H115:I115"/>
+    <mergeCell ref="B41:M41"/>
+    <mergeCell ref="J98:M98"/>
     <mergeCell ref="D11:M11"/>
     <mergeCell ref="J107:M107"/>
-    <mergeCell ref="J89:M89"/>
-    <mergeCell ref="B16:M16"/>
-    <mergeCell ref="H101:I101"/>
     <mergeCell ref="J104:M104"/>
+    <mergeCell ref="B66:M66"/>
     <mergeCell ref="D28:M28"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
@@ -5358,7 +5438,7 @@
           <t>Land (SF)</t>
         </is>
       </c>
-      <c r="C15" s="77" t="n">
+      <c r="C15" s="78" t="n">
         <v>104108</v>
       </c>
       <c r="D15" s="22" t="inlineStr">
@@ -5382,7 +5462,7 @@
           <t>Existing office SF</t>
         </is>
       </c>
-      <c r="C16" s="77" t="n">
+      <c r="C16" s="78" t="n">
         <v>84495</v>
       </c>
       <c r="D16" s="22" t="inlineStr">
@@ -5406,7 +5486,7 @@
           <t>Entitled units</t>
         </is>
       </c>
-      <c r="C17" s="77" t="n">
+      <c r="C17" s="78" t="n">
         <v>259</v>
       </c>
       <c r="D17" s="22" t="inlineStr">
@@ -5430,7 +5510,7 @@
           <t>BCPA market value</t>
         </is>
       </c>
-      <c r="C18" s="85" t="n">
+      <c r="C18" s="86" t="n">
         <v>6685580</v>
       </c>
       <c r="D18" s="22" t="inlineStr">
@@ -5554,7 +5634,7 @@
           <t>Effective millage</t>
         </is>
       </c>
-      <c r="C23" s="83" t="n">
+      <c r="C23" s="84" t="n">
         <v>0.0191</v>
       </c>
       <c r="D23" s="22" t="inlineStr">
@@ -5603,7 +5683,7 @@
           <t>Closing &amp; acq costs (% price)</t>
         </is>
       </c>
-      <c r="C25" s="84" t="n">
+      <c r="C25" s="85" t="n">
         <v>0.02</v>
       </c>
       <c r="D25" s="22" t="inlineStr">
@@ -5627,7 +5707,7 @@
           <t>Land value growth</t>
         </is>
       </c>
-      <c r="C26" s="84" t="n">
+      <c r="C26" s="85" t="n">
         <v>0.04</v>
       </c>
       <c r="D26" s="22" t="inlineStr">
@@ -5651,7 +5731,7 @@
           <t>Hold period (yrs)</t>
         </is>
       </c>
-      <c r="C27" s="86" t="n">
+      <c r="C27" s="87" t="n">
         <v>5</v>
       </c>
       <c r="D27" s="22" t="inlineStr">
@@ -5725,7 +5805,7 @@
           <t>Cost of sale at exit</t>
         </is>
       </c>
-      <c r="C30" s="84" t="n">
+      <c r="C30" s="85" t="n">
         <v>0.02</v>
       </c>
       <c r="D30" s="22" t="inlineStr">
@@ -5749,7 +5829,7 @@
           <t>Discount rate (NPV)</t>
         </is>
       </c>
-      <c r="C31" s="84" t="n">
+      <c r="C31" s="85" t="n">
         <v>0.1</v>
       </c>
       <c r="D31" s="22" t="inlineStr">
@@ -5773,7 +5853,7 @@
           <t>Expense growth</t>
         </is>
       </c>
-      <c r="C32" s="84" t="n">
+      <c r="C32" s="85" t="n">
         <v>0.03</v>
       </c>
       <c r="D32" s="22" t="inlineStr">
@@ -5816,17 +5896,17 @@
           <t>Approach</t>
         </is>
       </c>
-      <c r="D35" s="87" t="inlineStr">
+      <c r="D35" s="88" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E35" s="87" t="inlineStr">
+      <c r="E35" s="88" t="inlineStr">
         <is>
           <t>Base</t>
         </is>
       </c>
-      <c r="F35" s="87" t="inlineStr">
+      <c r="F35" s="88" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -5969,7 +6049,7 @@
           <t>Concluded acquisition basis</t>
         </is>
       </c>
-      <c r="E40" s="76">
+      <c r="E40" s="77">
         <f>C24</f>
         <v/>
       </c>
@@ -10164,7 +10244,7 @@
         </is>
       </c>
       <c r="C124" s="39">
-        <f>'Office Condo'!C17</f>
+        <f>'Office Condo'!C18</f>
         <v/>
       </c>
       <c r="D124" s="30" t="inlineStr">
@@ -10193,7 +10273,7 @@
         </is>
       </c>
       <c r="C125" s="39">
-        <f>'Office Condo'!D90</f>
+        <f>'Office Condo'!D91</f>
         <v/>
       </c>
       <c r="D125" s="30" t="inlineStr">
@@ -10222,7 +10302,7 @@
         </is>
       </c>
       <c r="C126" s="39">
-        <f>'Office Condo'!D91</f>
+        <f>'Office Condo'!D92</f>
         <v/>
       </c>
       <c r="D126" s="30" t="inlineStr">
@@ -10913,43 +10993,43 @@
         </is>
       </c>
       <c r="D17" s="23">
-        <f>'Office Condo'!D61</f>
+        <f>'Office Condo'!D62</f>
         <v/>
       </c>
       <c r="E17" s="17">
-        <f>'Office Condo'!E61</f>
+        <f>'Office Condo'!E62</f>
         <v/>
       </c>
       <c r="F17" s="17">
-        <f>'Office Condo'!F61</f>
+        <f>'Office Condo'!F62</f>
         <v/>
       </c>
       <c r="G17" s="17">
-        <f>'Office Condo'!G61</f>
+        <f>'Office Condo'!G62</f>
         <v/>
       </c>
       <c r="H17" s="17">
-        <f>'Office Condo'!H61</f>
+        <f>'Office Condo'!H62</f>
         <v/>
       </c>
       <c r="I17" s="17">
-        <f>'Office Condo'!I61</f>
+        <f>'Office Condo'!I62</f>
         <v/>
       </c>
       <c r="J17" s="17">
-        <f>'Office Condo'!J61</f>
+        <f>'Office Condo'!J62</f>
         <v/>
       </c>
       <c r="K17" s="17">
-        <f>'Office Condo'!K61</f>
+        <f>'Office Condo'!K62</f>
         <v/>
       </c>
       <c r="L17" s="17">
-        <f>'Office Condo'!L61</f>
+        <f>'Office Condo'!L62</f>
         <v/>
       </c>
       <c r="M17" s="17">
-        <f>'Office Condo'!M61</f>
+        <f>'Office Condo'!M62</f>
         <v/>
       </c>
     </row>
@@ -11054,43 +11134,43 @@
         </is>
       </c>
       <c r="D20" s="17">
-        <f>-('Shahidi Retail'!D104+'Publix &amp; Starbucks'!D91+'Sunrise Plaza'!D94+'Office Condo'!D62)</f>
+        <f>-('Shahidi Retail'!D104+'Publix &amp; Starbucks'!D91+'Sunrise Plaza'!D94+'Office Condo'!D63)</f>
         <v/>
       </c>
       <c r="E20" s="17">
-        <f>-('Shahidi Retail'!E104+'Publix &amp; Starbucks'!E91+'Sunrise Plaza'!E94+'Office Condo'!E62)</f>
+        <f>-('Shahidi Retail'!E104+'Publix &amp; Starbucks'!E91+'Sunrise Plaza'!E94+'Office Condo'!E63)</f>
         <v/>
       </c>
       <c r="F20" s="17">
-        <f>-('Shahidi Retail'!F104+'Publix &amp; Starbucks'!F91+'Sunrise Plaza'!F94+'Office Condo'!F62)</f>
+        <f>-('Shahidi Retail'!F104+'Publix &amp; Starbucks'!F91+'Sunrise Plaza'!F94+'Office Condo'!F63)</f>
         <v/>
       </c>
       <c r="G20" s="17">
-        <f>-('Shahidi Retail'!G104+'Publix &amp; Starbucks'!G91+'Sunrise Plaza'!G94+'Office Condo'!G62)</f>
+        <f>-('Shahidi Retail'!G104+'Publix &amp; Starbucks'!G91+'Sunrise Plaza'!G94+'Office Condo'!G63)</f>
         <v/>
       </c>
       <c r="H20" s="17">
-        <f>-('Shahidi Retail'!H104+'Publix &amp; Starbucks'!H91+'Sunrise Plaza'!H94+'Office Condo'!H62)</f>
+        <f>-('Shahidi Retail'!H104+'Publix &amp; Starbucks'!H91+'Sunrise Plaza'!H94+'Office Condo'!H63)</f>
         <v/>
       </c>
       <c r="I20" s="17">
-        <f>-('Shahidi Retail'!I104+'Publix &amp; Starbucks'!I91+'Sunrise Plaza'!I94+'Office Condo'!I62)</f>
+        <f>-('Shahidi Retail'!I104+'Publix &amp; Starbucks'!I91+'Sunrise Plaza'!I94+'Office Condo'!I63)</f>
         <v/>
       </c>
       <c r="J20" s="17">
-        <f>-('Shahidi Retail'!J104+'Publix &amp; Starbucks'!J91+'Sunrise Plaza'!J94+'Office Condo'!J62)</f>
+        <f>-('Shahidi Retail'!J104+'Publix &amp; Starbucks'!J91+'Sunrise Plaza'!J94+'Office Condo'!J63)</f>
         <v/>
       </c>
       <c r="K20" s="17">
-        <f>-('Shahidi Retail'!K104+'Publix &amp; Starbucks'!K91+'Sunrise Plaza'!K94+'Office Condo'!K62)</f>
+        <f>-('Shahidi Retail'!K104+'Publix &amp; Starbucks'!K91+'Sunrise Plaza'!K94+'Office Condo'!K63)</f>
         <v/>
       </c>
       <c r="L20" s="17">
-        <f>-('Shahidi Retail'!L104+'Publix &amp; Starbucks'!L91+'Sunrise Plaza'!L94+'Office Condo'!L62)</f>
+        <f>-('Shahidi Retail'!L104+'Publix &amp; Starbucks'!L91+'Sunrise Plaza'!L94+'Office Condo'!L63)</f>
         <v/>
       </c>
       <c r="M20" s="17">
-        <f>-('Shahidi Retail'!M104+'Publix &amp; Starbucks'!M91+'Sunrise Plaza'!M94+'Office Condo'!M62)</f>
+        <f>-('Shahidi Retail'!M104+'Publix &amp; Starbucks'!M91+'Sunrise Plaza'!M94+'Office Condo'!M63)</f>
         <v/>
       </c>
     </row>
@@ -11148,43 +11228,43 @@
         </is>
       </c>
       <c r="D22" s="17">
-        <f>'Shahidi Retail'!D108+'Publix &amp; Starbucks'!D95+'Sunrise Plaza'!D98+'Office Condo'!D66+'Land'!D59</f>
+        <f>'Shahidi Retail'!D108+'Publix &amp; Starbucks'!D95+'Sunrise Plaza'!D98+'Office Condo'!D67+'Land'!D59</f>
         <v/>
       </c>
       <c r="E22" s="17">
-        <f>'Shahidi Retail'!E108+'Publix &amp; Starbucks'!E95+'Sunrise Plaza'!E98+'Office Condo'!E66+'Land'!E59</f>
+        <f>'Shahidi Retail'!E108+'Publix &amp; Starbucks'!E95+'Sunrise Plaza'!E98+'Office Condo'!E67+'Land'!E59</f>
         <v/>
       </c>
       <c r="F22" s="17">
-        <f>'Shahidi Retail'!F108+'Publix &amp; Starbucks'!F95+'Sunrise Plaza'!F98+'Office Condo'!F66+'Land'!F59</f>
+        <f>'Shahidi Retail'!F108+'Publix &amp; Starbucks'!F95+'Sunrise Plaza'!F98+'Office Condo'!F67+'Land'!F59</f>
         <v/>
       </c>
       <c r="G22" s="17">
-        <f>'Shahidi Retail'!G108+'Publix &amp; Starbucks'!G95+'Sunrise Plaza'!G98+'Office Condo'!G66+'Land'!G59</f>
+        <f>'Shahidi Retail'!G108+'Publix &amp; Starbucks'!G95+'Sunrise Plaza'!G98+'Office Condo'!G67+'Land'!G59</f>
         <v/>
       </c>
       <c r="H22" s="17">
-        <f>'Shahidi Retail'!H108+'Publix &amp; Starbucks'!H95+'Sunrise Plaza'!H98+'Office Condo'!H66+'Land'!H59</f>
+        <f>'Shahidi Retail'!H108+'Publix &amp; Starbucks'!H95+'Sunrise Plaza'!H98+'Office Condo'!H67+'Land'!H59</f>
         <v/>
       </c>
       <c r="I22" s="17">
-        <f>'Shahidi Retail'!I108+'Publix &amp; Starbucks'!I95+'Sunrise Plaza'!I98+'Office Condo'!I66+'Land'!I59</f>
+        <f>'Shahidi Retail'!I108+'Publix &amp; Starbucks'!I95+'Sunrise Plaza'!I98+'Office Condo'!I67+'Land'!I59</f>
         <v/>
       </c>
       <c r="J22" s="17">
-        <f>'Shahidi Retail'!J108+'Publix &amp; Starbucks'!J95+'Sunrise Plaza'!J98+'Office Condo'!J66+'Land'!J59</f>
+        <f>'Shahidi Retail'!J108+'Publix &amp; Starbucks'!J95+'Sunrise Plaza'!J98+'Office Condo'!J67+'Land'!J59</f>
         <v/>
       </c>
       <c r="K22" s="17">
-        <f>'Shahidi Retail'!K108+'Publix &amp; Starbucks'!K95+'Sunrise Plaza'!K98+'Office Condo'!K66+'Land'!K59</f>
+        <f>'Shahidi Retail'!K108+'Publix &amp; Starbucks'!K95+'Sunrise Plaza'!K98+'Office Condo'!K67+'Land'!K59</f>
         <v/>
       </c>
       <c r="L22" s="17">
-        <f>'Shahidi Retail'!L108+'Publix &amp; Starbucks'!L95+'Sunrise Plaza'!L98+'Office Condo'!L66+'Land'!L59</f>
+        <f>'Shahidi Retail'!L108+'Publix &amp; Starbucks'!L95+'Sunrise Plaza'!L98+'Office Condo'!L67+'Land'!L59</f>
         <v/>
       </c>
       <c r="M22" s="17">
-        <f>'Shahidi Retail'!M108+'Publix &amp; Starbucks'!M95+'Sunrise Plaza'!M98+'Office Condo'!M66+'Land'!M59</f>
+        <f>'Shahidi Retail'!M108+'Publix &amp; Starbucks'!M95+'Sunrise Plaza'!M98+'Office Condo'!M67+'Land'!M59</f>
         <v/>
       </c>
     </row>
@@ -11214,7 +11294,7 @@
         </is>
       </c>
       <c r="C25" s="46">
-        <f>'Shahidi Retail'!C122+'Publix &amp; Starbucks'!C110+'Sunrise Plaza'!C113+'Office Condo'!C79+'Land'!C47</f>
+        <f>'Shahidi Retail'!C122+'Publix &amp; Starbucks'!C110+'Sunrise Plaza'!C113+'Office Condo'!C80+'Land'!C47</f>
         <v/>
       </c>
       <c r="D25" s="22" t="inlineStr">
@@ -11239,7 +11319,7 @@
         </is>
       </c>
       <c r="C26" s="46">
-        <f>'Shahidi Retail'!C124+'Publix &amp; Starbucks'!C112+'Sunrise Plaza'!C115+'Office Condo'!C81+'Land'!C47</f>
+        <f>'Shahidi Retail'!C124+'Publix &amp; Starbucks'!C112+'Sunrise Plaza'!C115+'Office Condo'!C82+'Land'!C47</f>
         <v/>
       </c>
       <c r="D26" s="22" t="inlineStr">
@@ -14624,11 +14704,11 @@
         </is>
       </c>
       <c r="C15" s="17">
-        <f>'Office Condo'!I97</f>
+        <f>'Office Condo'!I99</f>
         <v/>
       </c>
       <c r="D15" s="17">
-        <f>'Office Condo'!C78</f>
+        <f>'Office Condo'!C79</f>
         <v/>
       </c>
       <c r="E15" s="50">
@@ -14643,11 +14723,11 @@
         <v/>
       </c>
       <c r="H15" s="18">
-        <f>'Office Condo'!C73</f>
+        <f>'Office Condo'!C74</f>
         <v/>
       </c>
       <c r="I15" s="18">
-        <f>'Office Condo'!C76</f>
+        <f>'Office Condo'!C77</f>
         <v/>
       </c>
       <c r="J15" s="12" t="inlineStr">
@@ -15037,7 +15117,7 @@
         </is>
       </c>
       <c r="C36" s="51">
-        <f>'Shahidi Retail'!C78+'Publix &amp; Starbucks'!C65+'Sunrise Plaza'!C68+'Office Condo'!C46+'Land'!C52</f>
+        <f>'Shahidi Retail'!C78+'Publix &amp; Starbucks'!C65+'Sunrise Plaza'!C68+'Office Condo'!C47+'Land'!C52</f>
         <v/>
       </c>
     </row>
@@ -15292,7 +15372,7 @@
         </is>
       </c>
       <c r="C9" s="17">
-        <f>'Office Condo'!I97</f>
+        <f>'Office Condo'!I99</f>
         <v/>
       </c>
       <c r="E9" s="22" t="inlineStr">
@@ -15558,7 +15638,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="B20" s="12" t="inlineStr">
         <is>
-          <t>Office — Main St Fund LLC (57.4%)</t>
+          <t>Office — Grove Gate bulk (57.4%)</t>
         </is>
       </c>
       <c r="C20" s="30" t="inlineStr">
@@ -15570,12 +15650,12 @@
         <v>10000000</v>
       </c>
       <c r="E20" s="17">
-        <f>'Office Condo'!I90</f>
+        <f>'Office Condo'!I91</f>
         <v/>
       </c>
       <c r="F20" s="22" t="inlineStr">
         <is>
-          <t>96,930 SF + 2 parking lots (Daily Business Review)</t>
+          <t>$103/SF from Intl Sunrise (dissolved 2020); now reselling units $270–381/SF</t>
         </is>
       </c>
       <c r="G20" s="13" t="n"/>
@@ -15589,12 +15669,12 @@
     <row r="21" ht="15" customHeight="1">
       <c r="B21" s="12" t="inlineStr">
         <is>
-          <t>Office — Intl Sunrise Partners (42.6%)</t>
+          <t>Office — 42.6% individual owners</t>
         </is>
       </c>
       <c r="C21" s="30" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>2011→2026</t>
         </is>
       </c>
       <c r="D21" s="73" t="inlineStr">
@@ -15602,13 +15682,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="E21" s="17">
-        <f>'Office Condo'!I91</f>
-        <v/>
+      <c r="E21" s="74" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="F21" s="22" t="inlineStr">
         <is>
-          <t>condo-conversion sponsor (Bush Development)</t>
+          <t>~40 small owners (Merrimac, Cosmo, Jorgensen, Hublot); un-itemizable without BCPA</t>
         </is>
       </c>
       <c r="G21" s="13" t="n"/>
@@ -15835,15 +15916,15 @@
           <t>SUM OF THE PARTS  (fragmented land)</t>
         </is>
       </c>
-      <c r="C30" s="74">
+      <c r="C30" s="75">
         <f>SUM(C26:C29)</f>
         <v/>
       </c>
-      <c r="D30" s="75">
+      <c r="D30" s="76">
         <f>SUM(E26:E29)/SUM(C26:C29)</f>
         <v/>
       </c>
-      <c r="E30" s="76">
+      <c r="E30" s="77">
         <f>SUM(E26:E29)</f>
         <v/>
       </c>
@@ -16092,7 +16173,7 @@
         </is>
       </c>
       <c r="C44" s="17">
-        <f>'Office Condo'!I90</f>
+        <f>'Office Condo'!I91</f>
         <v/>
       </c>
       <c r="E44" s="22" t="inlineStr">
@@ -16116,7 +16197,7 @@
         </is>
       </c>
       <c r="C45" s="17">
-        <f>'Office Condo'!I91</f>
+        <f>'Office Condo'!I92</f>
         <v/>
       </c>
       <c r="E45" s="22" t="inlineStr">
@@ -16140,7 +16221,7 @@
         </is>
       </c>
       <c r="C46" s="56">
-        <f>'Office Condo'!I97</f>
+        <f>'Office Condo'!I99</f>
         <v/>
       </c>
       <c r="E46" s="22" t="inlineStr">
@@ -16182,7 +16263,7 @@
           <t>Buildable density (units/acre)</t>
         </is>
       </c>
-      <c r="C49" s="77" t="n">
+      <c r="C49" s="78" t="n">
         <v>100</v>
       </c>
       <c r="D49" s="22" t="inlineStr">
@@ -16890,7 +16971,7 @@
       <c r="F20" s="64" t="n">
         <v>4000</v>
       </c>
-      <c r="G20" s="78" t="n">
+      <c r="G20" s="79" t="n">
         <v>48</v>
       </c>
       <c r="H20" s="47">
@@ -16927,7 +17008,7 @@
       <c r="F21" s="64" t="n">
         <v>3500</v>
       </c>
-      <c r="G21" s="78" t="n">
+      <c r="G21" s="79" t="n">
         <v>62</v>
       </c>
       <c r="H21" s="47">
@@ -16964,7 +17045,7 @@
       <c r="F22" s="64" t="n">
         <v>3700</v>
       </c>
-      <c r="G22" s="78" t="n">
+      <c r="G22" s="79" t="n">
         <v>52</v>
       </c>
       <c r="H22" s="47">
@@ -17001,7 +17082,7 @@
       <c r="F23" s="64" t="n">
         <v>2200</v>
       </c>
-      <c r="G23" s="78" t="n">
+      <c r="G23" s="79" t="n">
         <v>58</v>
       </c>
       <c r="H23" s="47">
@@ -17038,7 +17119,7 @@
       <c r="F24" s="64" t="n">
         <v>2200</v>
       </c>
-      <c r="G24" s="78" t="n">
+      <c r="G24" s="79" t="n">
         <v>54</v>
       </c>
       <c r="H24" s="47">
@@ -17075,7 +17156,7 @@
       <c r="F25" s="64" t="n">
         <v>2000</v>
       </c>
-      <c r="G25" s="78" t="n">
+      <c r="G25" s="79" t="n">
         <v>50</v>
       </c>
       <c r="H25" s="47">
@@ -17112,7 +17193,7 @@
       <c r="F26" s="64" t="n">
         <v>1800</v>
       </c>
-      <c r="G26" s="78" t="n">
+      <c r="G26" s="79" t="n">
         <v>56</v>
       </c>
       <c r="H26" s="47">
@@ -17149,7 +17230,7 @@
       <c r="F27" s="64" t="n">
         <v>1250</v>
       </c>
-      <c r="G27" s="78" t="n">
+      <c r="G27" s="79" t="n">
         <v>58</v>
       </c>
       <c r="H27" s="47">
@@ -17186,7 +17267,7 @@
       <c r="F28" s="64" t="n">
         <v>1200</v>
       </c>
-      <c r="G28" s="78" t="n">
+      <c r="G28" s="79" t="n">
         <v>56</v>
       </c>
       <c r="H28" s="47">
@@ -17220,15 +17301,15 @@
         </is>
       </c>
       <c r="E29" s="14" t="n"/>
-      <c r="F29" s="79" t="n">
+      <c r="F29" s="80" t="n">
         <v>4422</v>
       </c>
-      <c r="G29" s="80" t="inlineStr">
+      <c r="G29" s="81" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H29" s="80" t="inlineStr">
+      <c r="H29" s="81" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -17254,13 +17335,13 @@
           <t>9 tenants + vacancy</t>
         </is>
       </c>
-      <c r="D30" s="81" t="inlineStr"/>
+      <c r="D30" s="82" t="inlineStr"/>
       <c r="E30" s="14" t="n"/>
       <c r="F30" s="66">
         <f>SUM(F20:F29)</f>
         <v/>
       </c>
-      <c r="G30" s="82">
+      <c r="G30" s="83">
         <f>IFERROR(SUM(H20:H28)/SUM(F20:F28),0)</f>
         <v/>
       </c>
@@ -17321,7 +17402,7 @@
           <t>GLA (SF)</t>
         </is>
       </c>
-      <c r="C34" s="77" t="n">
+      <c r="C34" s="78" t="n">
         <v>26272</v>
       </c>
       <c r="D34" s="22" t="inlineStr">
@@ -17395,7 +17476,7 @@
           <t>Effective millage</t>
         </is>
       </c>
-      <c r="C37" s="83" t="n">
+      <c r="C37" s="84" t="n">
         <v>0.0191</v>
       </c>
       <c r="D37" s="22" t="inlineStr">
@@ -17437,7 +17518,7 @@
           <t>In-place base rent ($/SF NNN)</t>
         </is>
       </c>
-      <c r="C39" s="78" t="n">
+      <c r="C39" s="79" t="n">
         <v>55</v>
       </c>
       <c r="D39" s="22" t="inlineStr">
@@ -17486,7 +17567,7 @@
           <t>Market rent growth</t>
         </is>
       </c>
-      <c r="C41" s="84" t="n">
+      <c r="C41" s="85" t="n">
         <v>0.03</v>
       </c>
       <c r="D41" s="22" t="inlineStr">
@@ -17535,7 +17616,7 @@
           <t>Credit &amp; collection loss</t>
         </is>
       </c>
-      <c r="C43" s="84" t="n">
+      <c r="C43" s="85" t="n">
         <v>0.02</v>
       </c>
       <c r="D43" s="22" t="inlineStr">
@@ -17577,7 +17658,7 @@
           <t>Reassessed value (= price, FL rule)</t>
         </is>
       </c>
-      <c r="C45" s="85" t="n">
+      <c r="C45" s="86" t="n">
         <v>17100000</v>
       </c>
       <c r="D45" s="22" t="inlineStr">
@@ -17701,7 +17782,7 @@
           <t>Expense growth</t>
         </is>
       </c>
-      <c r="C50" s="84" t="n">
+      <c r="C50" s="85" t="n">
         <v>0.03</v>
       </c>
       <c r="D50" s="22" t="inlineStr">
@@ -17743,7 +17824,7 @@
           <t>Tenant improvements ($/SF)</t>
         </is>
       </c>
-      <c r="C52" s="78" t="n">
+      <c r="C52" s="79" t="n">
         <v>30</v>
       </c>
       <c r="D52" s="22" t="inlineStr">
@@ -17767,7 +17848,7 @@
           <t>Leasing commissions ($/SF)</t>
         </is>
       </c>
-      <c r="C53" s="78" t="n">
+      <c r="C53" s="79" t="n">
         <v>20</v>
       </c>
       <c r="D53" s="22" t="inlineStr">
@@ -17791,7 +17872,7 @@
           <t>Replacement reserves ($/SF/yr)</t>
         </is>
       </c>
-      <c r="C54" s="78" t="n">
+      <c r="C54" s="79" t="n">
         <v>0.15</v>
       </c>
       <c r="D54" s="22" t="inlineStr">
@@ -17815,7 +17896,7 @@
           <t>Rollover leasing reserve ($/SF/yr)</t>
         </is>
       </c>
-      <c r="C55" s="78" t="n">
+      <c r="C55" s="79" t="n">
         <v>0.75</v>
       </c>
       <c r="D55" s="22" t="inlineStr">
@@ -17882,7 +17963,7 @@
           <t>Closing &amp; acq costs (% price)</t>
         </is>
       </c>
-      <c r="C58" s="84" t="n">
+      <c r="C58" s="85" t="n">
         <v>0.025</v>
       </c>
       <c r="D58" s="22" t="inlineStr">
@@ -17956,7 +18037,7 @@
           <t>Senior loan amortization (yrs)</t>
         </is>
       </c>
-      <c r="C61" s="86" t="n">
+      <c r="C61" s="87" t="n">
         <v>30</v>
       </c>
       <c r="D61" s="22" t="inlineStr">
@@ -18048,7 +18129,7 @@
           <t>Cost of sale at exit</t>
         </is>
       </c>
-      <c r="C65" s="84" t="n">
+      <c r="C65" s="85" t="n">
         <v>0.02</v>
       </c>
       <c r="D65" s="22" t="inlineStr">
@@ -18072,7 +18153,7 @@
           <t>Hold period (yrs)</t>
         </is>
       </c>
-      <c r="C66" s="86" t="n">
+      <c r="C66" s="87" t="n">
         <v>5</v>
       </c>
       <c r="D66" s="22" t="inlineStr">
@@ -18096,7 +18177,7 @@
           <t>Discount rate (unlevered, for NPV)</t>
         </is>
       </c>
-      <c r="C67" s="84" t="n">
+      <c r="C67" s="85" t="n">
         <v>0.09</v>
       </c>
       <c r="D67" s="22" t="inlineStr">
@@ -19880,19 +19961,19 @@
           <t>$ / year</t>
         </is>
       </c>
-      <c r="F132" s="87" t="inlineStr">
+      <c r="F132" s="88" t="inlineStr">
         <is>
           <t>In-place (Yr 1)</t>
         </is>
       </c>
       <c r="G132" s="14" t="n"/>
-      <c r="H132" s="87" t="inlineStr">
+      <c r="H132" s="88" t="inlineStr">
         <is>
           <t>Stabilized (Yr 2)</t>
         </is>
       </c>
       <c r="I132" s="14" t="n"/>
-      <c r="J132" s="87" t="inlineStr">
+      <c r="J132" s="88" t="inlineStr">
         <is>
           <t>Per SF (stab.)</t>
         </is>
@@ -19917,7 +19998,7 @@
         <v/>
       </c>
       <c r="I133" s="14" t="n"/>
-      <c r="J133" s="88">
+      <c r="J133" s="89">
         <f>H133/C34</f>
         <v/>
       </c>
@@ -19989,7 +20070,7 @@
         <v/>
       </c>
       <c r="I136" s="14" t="n"/>
-      <c r="J136" s="88">
+      <c r="J136" s="89">
         <f>H136/C34</f>
         <v/>
       </c>
@@ -20133,7 +20214,7 @@
         <v/>
       </c>
       <c r="I142" s="14" t="n"/>
-      <c r="J142" s="88">
+      <c r="J142" s="89">
         <f>H142/C34</f>
         <v/>
       </c>
@@ -20205,7 +20286,7 @@
         <v/>
       </c>
       <c r="I145" s="14" t="n"/>
-      <c r="J145" s="88">
+      <c r="J145" s="89">
         <f>H145/C34</f>
         <v/>
       </c>
@@ -20253,7 +20334,7 @@
         <v/>
       </c>
       <c r="I147" s="14" t="n"/>
-      <c r="J147" s="88">
+      <c r="J147" s="89">
         <f>H147/C34</f>
         <v/>
       </c>
@@ -20782,7 +20863,7 @@
       <c r="G18" s="64" t="n">
         <v>34622</v>
       </c>
-      <c r="H18" s="78" t="n">
+      <c r="H18" s="79" t="n">
         <v>22</v>
       </c>
       <c r="I18" s="47">
@@ -20815,7 +20896,7 @@
       <c r="G19" s="64" t="n">
         <v>2200</v>
       </c>
-      <c r="H19" s="78" t="n">
+      <c r="H19" s="79" t="n">
         <v>60</v>
       </c>
       <c r="I19" s="47">
@@ -20839,13 +20920,13 @@
       </c>
       <c r="C20" s="13" t="n"/>
       <c r="D20" s="14" t="n"/>
-      <c r="E20" s="81" t="inlineStr"/>
+      <c r="E20" s="82" t="inlineStr"/>
       <c r="F20" s="14" t="n"/>
       <c r="G20" s="66">
         <f>SUM(G18:G19)</f>
         <v/>
       </c>
-      <c r="H20" s="82">
+      <c r="H20" s="83">
         <f>IFERROR(SUM(I18:I19)/SUM(G18:G19),0)</f>
         <v/>
       </c>
@@ -20905,7 +20986,7 @@
           <t>Rentable SF</t>
         </is>
       </c>
-      <c r="C24" s="77" t="n">
+      <c r="C24" s="78" t="n">
         <v>36822</v>
       </c>
       <c r="D24" s="22" t="inlineStr">
@@ -21029,7 +21110,7 @@
           <t>Rent growth</t>
         </is>
       </c>
-      <c r="C29" s="84" t="n">
+      <c r="C29" s="85" t="n">
         <v>0.02</v>
       </c>
       <c r="D29" s="22" t="inlineStr">
@@ -21053,7 +21134,7 @@
           <t>Credit &amp; collection loss</t>
         </is>
       </c>
-      <c r="C30" s="84" t="n">
+      <c r="C30" s="85" t="n">
         <v>0.01</v>
       </c>
       <c r="D30" s="22" t="inlineStr">
@@ -21077,7 +21158,7 @@
           <t>Effective millage</t>
         </is>
       </c>
-      <c r="C31" s="83" t="n">
+      <c r="C31" s="84" t="n">
         <v>0.0191</v>
       </c>
       <c r="D31" s="22" t="inlineStr">
@@ -21219,7 +21300,7 @@
           <t>Expense growth</t>
         </is>
       </c>
-      <c r="C37" s="84" t="n">
+      <c r="C37" s="85" t="n">
         <v>0.03</v>
       </c>
       <c r="D37" s="22" t="inlineStr">
@@ -21261,7 +21342,7 @@
           <t>Tenant improvements ($/SF)</t>
         </is>
       </c>
-      <c r="C39" s="78" t="n">
+      <c r="C39" s="79" t="n">
         <v>0</v>
       </c>
       <c r="D39" s="22" t="inlineStr">
@@ -21285,7 +21366,7 @@
           <t>Leasing commissions ($/SF)</t>
         </is>
       </c>
-      <c r="C40" s="78" t="n">
+      <c r="C40" s="79" t="n">
         <v>0</v>
       </c>
       <c r="D40" s="22" t="inlineStr">
@@ -21309,7 +21390,7 @@
           <t>Replacement reserves ($/SF/yr)</t>
         </is>
       </c>
-      <c r="C41" s="78" t="n">
+      <c r="C41" s="79" t="n">
         <v>0.15</v>
       </c>
       <c r="D41" s="22" t="inlineStr">
@@ -21333,7 +21414,7 @@
           <t>Rollover leasing reserve ($/SF/yr)</t>
         </is>
       </c>
-      <c r="C42" s="78" t="n">
+      <c r="C42" s="79" t="n">
         <v>0.15</v>
       </c>
       <c r="D42" s="22" t="inlineStr">
@@ -21400,7 +21481,7 @@
           <t>Closing &amp; acq costs (% price)</t>
         </is>
       </c>
-      <c r="C45" s="84" t="n">
+      <c r="C45" s="85" t="n">
         <v>0.02</v>
       </c>
       <c r="D45" s="22" t="inlineStr">
@@ -21474,7 +21555,7 @@
           <t>Senior loan amortization (yrs)</t>
         </is>
       </c>
-      <c r="C48" s="86" t="n">
+      <c r="C48" s="87" t="n">
         <v>30</v>
       </c>
       <c r="D48" s="22" t="inlineStr">
@@ -21566,7 +21647,7 @@
           <t>Cost of sale at exit</t>
         </is>
       </c>
-      <c r="C52" s="84" t="n">
+      <c r="C52" s="85" t="n">
         <v>0.02</v>
       </c>
       <c r="D52" s="22" t="inlineStr">
@@ -21590,7 +21671,7 @@
           <t>Hold period (yrs)</t>
         </is>
       </c>
-      <c r="C53" s="86" t="n">
+      <c r="C53" s="87" t="n">
         <v>5</v>
       </c>
       <c r="D53" s="22" t="inlineStr">
@@ -21614,7 +21695,7 @@
           <t>Discount rate (NPV)</t>
         </is>
       </c>
-      <c r="C54" s="84" t="n">
+      <c r="C54" s="85" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="D54" s="22" t="inlineStr">
@@ -23398,7 +23479,7 @@
           <t>Target Year-1 DSCR</t>
         </is>
       </c>
-      <c r="C119" s="89" t="n">
+      <c r="C119" s="90" t="n">
         <v>1.2</v>
       </c>
       <c r="D119" s="22" t="inlineStr">
@@ -23422,7 +23503,7 @@
           <t>Target going-in cap</t>
         </is>
       </c>
-      <c r="C120" s="83" t="n">
+      <c r="C120" s="84" t="n">
         <v>0.05</v>
       </c>
       <c r="D120" s="22" t="inlineStr">
@@ -23468,7 +23549,7 @@
           <t>→ Required leaseback rent for target DSCR</t>
         </is>
       </c>
-      <c r="C123" s="88">
+      <c r="C123" s="89">
         <f>(((C119*C60+C122*C36+C35)/C121)-'Assumptions'!C69*'Assumptions'!C68)/'Assumptions'!C67</f>
         <v/>
       </c>
@@ -23493,7 +23574,7 @@
           <t>→ Required leaseback rent for target cap</t>
         </is>
       </c>
-      <c r="C124" s="88">
+      <c r="C124" s="89">
         <f>(((C120*C44+C122*C36+C35)/C121)-'Assumptions'!C69*'Assumptions'!C68)/'Assumptions'!C67</f>
         <v/>
       </c>
@@ -23537,19 +23618,19 @@
           <t>$ / year</t>
         </is>
       </c>
-      <c r="F127" s="87" t="inlineStr">
+      <c r="F127" s="88" t="inlineStr">
         <is>
           <t>Year 1</t>
         </is>
       </c>
       <c r="G127" s="14" t="n"/>
-      <c r="H127" s="87" t="inlineStr">
+      <c r="H127" s="88" t="inlineStr">
         <is>
           <t>Stabilized</t>
         </is>
       </c>
       <c r="I127" s="14" t="n"/>
-      <c r="J127" s="87" t="inlineStr">
+      <c r="J127" s="88" t="inlineStr">
         <is>
           <t>Per SF (stab.)</t>
         </is>
@@ -23574,7 +23655,7 @@
         <v/>
       </c>
       <c r="I128" s="14" t="n"/>
-      <c r="J128" s="88">
+      <c r="J128" s="89">
         <f>H128/C24</f>
         <v/>
       </c>
@@ -23646,7 +23727,7 @@
         <v/>
       </c>
       <c r="I131" s="14" t="n"/>
-      <c r="J131" s="88">
+      <c r="J131" s="89">
         <f>H131/C24</f>
         <v/>
       </c>
@@ -23790,7 +23871,7 @@
         <v/>
       </c>
       <c r="I137" s="14" t="n"/>
-      <c r="J137" s="88">
+      <c r="J137" s="89">
         <f>H137/C24</f>
         <v/>
       </c>
@@ -23862,7 +23943,7 @@
         <v/>
       </c>
       <c r="I140" s="14" t="n"/>
-      <c r="J140" s="88">
+      <c r="J140" s="89">
         <f>H140/C24</f>
         <v/>
       </c>
@@ -23910,7 +23991,7 @@
         <v/>
       </c>
       <c r="I142" s="14" t="n"/>
-      <c r="J142" s="88">
+      <c r="J142" s="89">
         <f>H142/C24</f>
         <v/>
       </c>
@@ -24398,7 +24479,7 @@
       <c r="G17" s="64" t="n">
         <v>6000</v>
       </c>
-      <c r="H17" s="78" t="n">
+      <c r="H17" s="79" t="n">
         <v>34</v>
       </c>
       <c r="I17" s="47">
@@ -24431,7 +24512,7 @@
       <c r="G18" s="64" t="n">
         <v>4000</v>
       </c>
-      <c r="H18" s="78" t="n">
+      <c r="H18" s="79" t="n">
         <v>36</v>
       </c>
       <c r="I18" s="47">
@@ -24464,7 +24545,7 @@
       <c r="G19" s="64" t="n">
         <v>3000</v>
       </c>
-      <c r="H19" s="78" t="n">
+      <c r="H19" s="79" t="n">
         <v>40</v>
       </c>
       <c r="I19" s="47">
@@ -24497,7 +24578,7 @@
       <c r="G20" s="64" t="n">
         <v>6005</v>
       </c>
-      <c r="H20" s="78" t="n">
+      <c r="H20" s="79" t="n">
         <v>30</v>
       </c>
       <c r="I20" s="47">
@@ -24530,7 +24611,7 @@
       <c r="G21" s="64" t="n">
         <v>1100</v>
       </c>
-      <c r="H21" s="78" t="n">
+      <c r="H21" s="79" t="n">
         <v>32</v>
       </c>
       <c r="I21" s="47">
@@ -24560,15 +24641,15 @@
         </is>
       </c>
       <c r="F22" s="14" t="n"/>
-      <c r="G22" s="79" t="n">
+      <c r="G22" s="80" t="n">
         <v>5000</v>
       </c>
-      <c r="H22" s="80" t="inlineStr">
+      <c r="H22" s="81" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I22" s="80" t="inlineStr">
+      <c r="I22" s="81" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -24590,13 +24671,13 @@
       </c>
       <c r="C23" s="13" t="n"/>
       <c r="D23" s="14" t="n"/>
-      <c r="E23" s="81" t="inlineStr"/>
+      <c r="E23" s="82" t="inlineStr"/>
       <c r="F23" s="14" t="n"/>
       <c r="G23" s="66">
         <f>SUM(G17:G22)</f>
         <v/>
       </c>
-      <c r="H23" s="82">
+      <c r="H23" s="83">
         <f>IFERROR(SUM(I17:I21)/SUM(G17:G21),0)</f>
         <v/>
       </c>
@@ -24656,7 +24737,7 @@
           <t>Rentable SF</t>
         </is>
       </c>
-      <c r="C27" s="77" t="n">
+      <c r="C27" s="78" t="n">
         <v>25105</v>
       </c>
       <c r="D27" s="22" t="inlineStr">
@@ -24780,7 +24861,7 @@
           <t>Rent growth</t>
         </is>
       </c>
-      <c r="C32" s="84" t="n">
+      <c r="C32" s="85" t="n">
         <v>0.03</v>
       </c>
       <c r="D32" s="22" t="inlineStr">
@@ -24804,7 +24885,7 @@
           <t>Credit &amp; collection loss</t>
         </is>
       </c>
-      <c r="C33" s="84" t="n">
+      <c r="C33" s="85" t="n">
         <v>0.03</v>
       </c>
       <c r="D33" s="22" t="inlineStr">
@@ -24828,7 +24909,7 @@
           <t>Effective millage</t>
         </is>
       </c>
-      <c r="C34" s="83" t="n">
+      <c r="C34" s="84" t="n">
         <v>0.0191</v>
       </c>
       <c r="D34" s="22" t="inlineStr">
@@ -24970,7 +25051,7 @@
           <t>Expense growth</t>
         </is>
       </c>
-      <c r="C40" s="84" t="n">
+      <c r="C40" s="85" t="n">
         <v>0.03</v>
       </c>
       <c r="D40" s="22" t="inlineStr">
@@ -25012,7 +25093,7 @@
           <t>Tenant improvements ($/SF)</t>
         </is>
       </c>
-      <c r="C42" s="78" t="n">
+      <c r="C42" s="79" t="n">
         <v>30</v>
       </c>
       <c r="D42" s="22" t="inlineStr">
@@ -25036,7 +25117,7 @@
           <t>Leasing commissions ($/SF)</t>
         </is>
       </c>
-      <c r="C43" s="78" t="n">
+      <c r="C43" s="79" t="n">
         <v>20</v>
       </c>
       <c r="D43" s="22" t="inlineStr">
@@ -25060,7 +25141,7 @@
           <t>Replacement reserves ($/SF/yr)</t>
         </is>
       </c>
-      <c r="C44" s="78" t="n">
+      <c r="C44" s="79" t="n">
         <v>0.15</v>
       </c>
       <c r="D44" s="22" t="inlineStr">
@@ -25084,7 +25165,7 @@
           <t>Rollover leasing reserve ($/SF/yr)</t>
         </is>
       </c>
-      <c r="C45" s="78" t="n">
+      <c r="C45" s="79" t="n">
         <v>0.75</v>
       </c>
       <c r="D45" s="22" t="inlineStr">
@@ -25151,7 +25232,7 @@
           <t>Closing &amp; acq costs (% price)</t>
         </is>
       </c>
-      <c r="C48" s="84" t="n">
+      <c r="C48" s="85" t="n">
         <v>0.025</v>
       </c>
       <c r="D48" s="22" t="inlineStr">
@@ -25225,7 +25306,7 @@
           <t>Senior loan amortization (yrs)</t>
         </is>
       </c>
-      <c r="C51" s="86" t="n">
+      <c r="C51" s="87" t="n">
         <v>30</v>
       </c>
       <c r="D51" s="22" t="inlineStr">
@@ -25317,7 +25398,7 @@
           <t>Cost of sale at exit</t>
         </is>
       </c>
-      <c r="C55" s="84" t="n">
+      <c r="C55" s="85" t="n">
         <v>0.02</v>
       </c>
       <c r="D55" s="22" t="inlineStr">
@@ -25341,7 +25422,7 @@
           <t>Hold period (yrs)</t>
         </is>
       </c>
-      <c r="C56" s="86" t="n">
+      <c r="C56" s="87" t="n">
         <v>5</v>
       </c>
       <c r="D56" s="22" t="inlineStr">
@@ -25365,7 +25446,7 @@
           <t>Discount rate (NPV)</t>
         </is>
       </c>
-      <c r="C57" s="84" t="n">
+      <c r="C57" s="85" t="n">
         <v>0.09</v>
       </c>
       <c r="D57" s="22" t="inlineStr">
@@ -27149,19 +27230,19 @@
           <t>$ / year</t>
         </is>
       </c>
-      <c r="F122" s="87" t="inlineStr">
+      <c r="F122" s="88" t="inlineStr">
         <is>
           <t>Year 1</t>
         </is>
       </c>
       <c r="G122" s="14" t="n"/>
-      <c r="H122" s="87" t="inlineStr">
+      <c r="H122" s="88" t="inlineStr">
         <is>
           <t>Stabilized</t>
         </is>
       </c>
       <c r="I122" s="14" t="n"/>
-      <c r="J122" s="87" t="inlineStr">
+      <c r="J122" s="88" t="inlineStr">
         <is>
           <t>Per SF (stab.)</t>
         </is>
@@ -27186,7 +27267,7 @@
         <v/>
       </c>
       <c r="I123" s="14" t="n"/>
-      <c r="J123" s="88">
+      <c r="J123" s="89">
         <f>H123/C27</f>
         <v/>
       </c>
@@ -27258,7 +27339,7 @@
         <v/>
       </c>
       <c r="I126" s="14" t="n"/>
-      <c r="J126" s="88">
+      <c r="J126" s="89">
         <f>H126/C27</f>
         <v/>
       </c>
@@ -27402,7 +27483,7 @@
         <v/>
       </c>
       <c r="I132" s="14" t="n"/>
-      <c r="J132" s="88">
+      <c r="J132" s="89">
         <f>H132/C27</f>
         <v/>
       </c>
@@ -27474,7 +27555,7 @@
         <v/>
       </c>
       <c r="I135" s="14" t="n"/>
-      <c r="J135" s="88">
+      <c r="J135" s="89">
         <f>H135/C27</f>
         <v/>
       </c>
@@ -27522,7 +27603,7 @@
         <v/>
       </c>
       <c r="I137" s="14" t="n"/>
-      <c r="J137" s="88">
+      <c r="J137" s="89">
         <f>H137/C27</f>
         <v/>
       </c>

--- a/Shahidi_Assemblage_Model.xlsx
+++ b/Shahidi_Assemblage_Model.xlsx
@@ -392,6 +392,9 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -457,9 +460,6 @@
     </xf>
     <xf numFmtId="10" fontId="11" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -1036,7 +1036,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M49"/>
+  <dimension ref="A1:M57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -1759,7 +1759,7 @@
     <row r="38">
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>HOW TO CHANGE A NUMBER</t>
+          <t>PLAY WITH IT  —  it's a live model: change a BLUE cell and everything recalculates</t>
         </is>
       </c>
       <c r="C38" s="2" t="n"/>
@@ -1775,16 +1775,12 @@
       <c r="M38" s="3" t="n"/>
     </row>
     <row r="39" ht="15" customHeight="1">
-      <c r="B39" s="6" t="inlineStr">
-        <is>
-          <t>Change an assumption</t>
-        </is>
-      </c>
-      <c r="C39" s="7" t="inlineStr">
-        <is>
-          <t>Go to the Assumptions tab and edit a BLUE cell — that's the only kind of cell you change. The whole model updates on its own.</t>
-        </is>
-      </c>
+      <c r="B39" s="15" t="inlineStr">
+        <is>
+          <t>Open it in Excel or Google Sheets (a preview is read-only). Blue cells are the only ones you touch — the rest updates on its own.</t>
+        </is>
+      </c>
+      <c r="C39" s="8" t="n"/>
       <c r="D39" s="8" t="n"/>
       <c r="E39" s="8" t="n"/>
       <c r="F39" s="8" t="n"/>
@@ -1797,23 +1793,27 @@
       <c r="M39" s="9" t="n"/>
     </row>
     <row r="40" ht="15" customHeight="1">
-      <c r="B40" s="6" t="inlineStr">
-        <is>
-          <t>Fill in real data</t>
-        </is>
-      </c>
-      <c r="C40" s="7" t="inlineStr">
-        <is>
-          <t>As you confirm real facts (a sale price, a rent, a lender rate), put them in the overrides.json file and rebuild — it flows into every tab. That file lists every gap and where to get it.</t>
-        </is>
-      </c>
-      <c r="D40" s="8" t="n"/>
-      <c r="E40" s="8" t="n"/>
+      <c r="B40" s="14" t="inlineStr">
+        <is>
+          <t>To change…</t>
+        </is>
+      </c>
+      <c r="C40" s="8" t="n"/>
+      <c r="D40" s="9" t="n"/>
+      <c r="E40" s="14" t="inlineStr">
+        <is>
+          <t>Go here and edit the blue cell</t>
+        </is>
+      </c>
       <c r="F40" s="8" t="n"/>
       <c r="G40" s="8" t="n"/>
       <c r="H40" s="8" t="n"/>
-      <c r="I40" s="8" t="n"/>
-      <c r="J40" s="8" t="n"/>
+      <c r="I40" s="9" t="n"/>
+      <c r="J40" s="14" t="inlineStr">
+        <is>
+          <t>…and watch this update</t>
+        </is>
+      </c>
       <c r="K40" s="8" t="n"/>
       <c r="L40" s="8" t="n"/>
       <c r="M40" s="9" t="n"/>
@@ -1821,62 +1821,103 @@
     <row r="41" ht="15" customHeight="1">
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>Explore without committing</t>
-        </is>
-      </c>
-      <c r="C41" s="7" t="inlineStr">
-        <is>
-          <t>The Review Board and Capital Stack tabs have their own blue 'sandbox' cells — play there freely; they don't disturb the model.</t>
-        </is>
-      </c>
-      <c r="D41" s="8" t="n"/>
-      <c r="E41" s="8" t="n"/>
+          <t>What you pay for an asset</t>
+        </is>
+      </c>
+      <c r="C41" s="8" t="n"/>
+      <c r="D41" s="9" t="n"/>
+      <c r="E41" s="7" t="inlineStr">
+        <is>
+          <t>Assumptions → that asset's block → 'Purchase price / basis'</t>
+        </is>
+      </c>
       <c r="F41" s="8" t="n"/>
       <c r="G41" s="8" t="n"/>
       <c r="H41" s="8" t="n"/>
-      <c r="I41" s="8" t="n"/>
-      <c r="J41" s="8" t="n"/>
+      <c r="I41" s="9" t="n"/>
+      <c r="J41" s="16" t="inlineStr">
+        <is>
+          <t>income price, returns, Comps &amp; Pricing</t>
+        </is>
+      </c>
       <c r="K41" s="8" t="n"/>
       <c r="L41" s="8" t="n"/>
       <c r="M41" s="9" t="n"/>
     </row>
-    <row r="42"/>
-    <row r="43">
-      <c r="B43" s="5" t="inlineStr">
-        <is>
-          <t>THE COLOR CODE</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="n"/>
-      <c r="D43" s="2" t="n"/>
-      <c r="E43" s="2" t="n"/>
-      <c r="F43" s="2" t="n"/>
-      <c r="G43" s="2" t="n"/>
-      <c r="H43" s="2" t="n"/>
-      <c r="I43" s="2" t="n"/>
-      <c r="J43" s="2" t="n"/>
-      <c r="K43" s="2" t="n"/>
-      <c r="L43" s="2" t="n"/>
-      <c r="M43" s="3" t="n"/>
+    <row r="42" ht="15" customHeight="1">
+      <c r="B42" s="6" t="inlineStr">
+        <is>
+          <t>A cap rate</t>
+        </is>
+      </c>
+      <c r="C42" s="8" t="n"/>
+      <c r="D42" s="9" t="n"/>
+      <c r="E42" s="7" t="inlineStr">
+        <is>
+          <t>Assumptions → 'Blended going-in cap' (or an asset's going-in / exit cap)</t>
+        </is>
+      </c>
+      <c r="F42" s="8" t="n"/>
+      <c r="G42" s="8" t="n"/>
+      <c r="H42" s="8" t="n"/>
+      <c r="I42" s="9" t="n"/>
+      <c r="J42" s="16" t="inlineStr">
+        <is>
+          <t>the value and the price</t>
+        </is>
+      </c>
+      <c r="K42" s="8" t="n"/>
+      <c r="L42" s="8" t="n"/>
+      <c r="M42" s="9" t="n"/>
+    </row>
+    <row r="43" ht="15" customHeight="1">
+      <c r="B43" s="6" t="inlineStr">
+        <is>
+          <t>Rents</t>
+        </is>
+      </c>
+      <c r="C43" s="8" t="n"/>
+      <c r="D43" s="9" t="n"/>
+      <c r="E43" s="7" t="inlineStr">
+        <is>
+          <t>Assumptions → an asset's 'Market rent' (or the Publix leaseback rent)</t>
+        </is>
+      </c>
+      <c r="F43" s="8" t="n"/>
+      <c r="G43" s="8" t="n"/>
+      <c r="H43" s="8" t="n"/>
+      <c r="I43" s="9" t="n"/>
+      <c r="J43" s="16" t="inlineStr">
+        <is>
+          <t>NOI → value → returns</t>
+        </is>
+      </c>
+      <c r="K43" s="8" t="n"/>
+      <c r="L43" s="8" t="n"/>
+      <c r="M43" s="9" t="n"/>
     </row>
     <row r="44" ht="15" customHeight="1">
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>Blue on yellow</t>
-        </is>
-      </c>
-      <c r="C44" s="9" t="n"/>
-      <c r="D44" s="7" t="inlineStr">
-        <is>
-          <t>an input — the only cells you change</t>
-        </is>
-      </c>
-      <c r="E44" s="8" t="n"/>
+          <t>How much you borrow</t>
+        </is>
+      </c>
+      <c r="C44" s="8" t="n"/>
+      <c r="D44" s="9" t="n"/>
+      <c r="E44" s="7" t="inlineStr">
+        <is>
+          <t>Assumptions → 'Max senior LTV' and 'Senior rate'</t>
+        </is>
+      </c>
       <c r="F44" s="8" t="n"/>
       <c r="G44" s="8" t="n"/>
       <c r="H44" s="8" t="n"/>
-      <c r="I44" s="8" t="n"/>
-      <c r="J44" s="8" t="n"/>
+      <c r="I44" s="9" t="n"/>
+      <c r="J44" s="16" t="inlineStr">
+        <is>
+          <t>debt, equity, DSCR, returns</t>
+        </is>
+      </c>
       <c r="K44" s="8" t="n"/>
       <c r="L44" s="8" t="n"/>
       <c r="M44" s="9" t="n"/>
@@ -1884,21 +1925,25 @@
     <row r="45" ht="15" customHeight="1">
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>Black</t>
-        </is>
-      </c>
-      <c r="C45" s="9" t="n"/>
-      <c r="D45" s="7" t="inlineStr">
-        <is>
-          <t>a formula / calculation (leave it)</t>
-        </is>
-      </c>
-      <c r="E45" s="8" t="n"/>
+          <t>The assemblage premium</t>
+        </is>
+      </c>
+      <c r="C45" s="8" t="n"/>
+      <c r="D45" s="9" t="n"/>
+      <c r="E45" s="7" t="inlineStr">
+        <is>
+          <t>Assumptions → 'Assemblage premium — base'</t>
+        </is>
+      </c>
       <c r="F45" s="8" t="n"/>
       <c r="G45" s="8" t="n"/>
       <c r="H45" s="8" t="n"/>
-      <c r="I45" s="8" t="n"/>
-      <c r="J45" s="8" t="n"/>
+      <c r="I45" s="9" t="n"/>
+      <c r="J45" s="16" t="inlineStr">
+        <is>
+          <t>the covered-land price</t>
+        </is>
+      </c>
       <c r="K45" s="8" t="n"/>
       <c r="L45" s="8" t="n"/>
       <c r="M45" s="9" t="n"/>
@@ -1906,21 +1951,25 @@
     <row r="46" ht="15" customHeight="1">
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>Green</t>
-        </is>
-      </c>
-      <c r="C46" s="9" t="n"/>
-      <c r="D46" s="7" t="inlineStr">
-        <is>
-          <t>a verified fact, or a live link pulling from another tab</t>
-        </is>
-      </c>
-      <c r="E46" s="8" t="n"/>
+          <t>The office buy-out price</t>
+        </is>
+      </c>
+      <c r="C46" s="8" t="n"/>
+      <c r="D46" s="9" t="n"/>
+      <c r="E46" s="7" t="inlineStr">
+        <is>
+          <t>Office Condo tab → 'Buy-out $/SF (unit market)'</t>
+        </is>
+      </c>
       <c r="F46" s="8" t="n"/>
       <c r="G46" s="8" t="n"/>
       <c r="H46" s="8" t="n"/>
-      <c r="I46" s="8" t="n"/>
-      <c r="J46" s="8" t="n"/>
+      <c r="I46" s="9" t="n"/>
+      <c r="J46" s="16" t="inlineStr">
+        <is>
+          <t>office price → covered-land</t>
+        </is>
+      </c>
       <c r="K46" s="8" t="n"/>
       <c r="L46" s="8" t="n"/>
       <c r="M46" s="9" t="n"/>
@@ -1928,21 +1977,25 @@
     <row r="47" ht="15" customHeight="1">
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>Gold on navy</t>
-        </is>
-      </c>
-      <c r="C47" s="9" t="n"/>
-      <c r="D47" s="7" t="inlineStr">
-        <is>
-          <t>a header, total, or key number</t>
-        </is>
-      </c>
-      <c r="E47" s="8" t="n"/>
+          <t>A sensitivity (without touching the model)</t>
+        </is>
+      </c>
+      <c r="C47" s="8" t="n"/>
+      <c r="D47" s="9" t="n"/>
+      <c r="E47" s="7" t="inlineStr">
+        <is>
+          <t>Review Board → the blue axis cells on any grid</t>
+        </is>
+      </c>
       <c r="F47" s="8" t="n"/>
       <c r="G47" s="8" t="n"/>
       <c r="H47" s="8" t="n"/>
-      <c r="I47" s="8" t="n"/>
-      <c r="J47" s="8" t="n"/>
+      <c r="I47" s="9" t="n"/>
+      <c r="J47" s="16" t="inlineStr">
+        <is>
+          <t>the grid + driver tornado, live</t>
+        </is>
+      </c>
       <c r="K47" s="8" t="n"/>
       <c r="L47" s="8" t="n"/>
       <c r="M47" s="9" t="n"/>
@@ -1950,123 +2003,305 @@
     <row r="48" ht="15" customHeight="1">
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>Orange</t>
-        </is>
-      </c>
-      <c r="C48" s="9" t="n"/>
-      <c r="D48" s="7" t="inlineStr">
-        <is>
-          <t>a warning, a flag, or something to confirm</t>
-        </is>
-      </c>
-      <c r="E48" s="8" t="n"/>
+          <t>What you can afford</t>
+        </is>
+      </c>
+      <c r="C48" s="8" t="n"/>
+      <c r="D48" s="9" t="n"/>
+      <c r="E48" s="7" t="inlineStr">
+        <is>
+          <t>Capital Stack → 'Equity available'</t>
+        </is>
+      </c>
       <c r="F48" s="8" t="n"/>
       <c r="G48" s="8" t="n"/>
       <c r="H48" s="8" t="n"/>
-      <c r="I48" s="8" t="n"/>
-      <c r="J48" s="8" t="n"/>
+      <c r="I48" s="9" t="n"/>
+      <c r="J48" s="16" t="inlineStr">
+        <is>
+          <t>max price + assemblage capacity</t>
+        </is>
+      </c>
       <c r="K48" s="8" t="n"/>
       <c r="L48" s="8" t="n"/>
       <c r="M48" s="9" t="n"/>
     </row>
-    <row r="49" ht="15" customHeight="1">
-      <c r="B49" s="6" t="inlineStr">
+    <row r="49"/>
+    <row r="50" ht="27" customHeight="1">
+      <c r="B50" s="6" t="inlineStr">
+        <is>
+          <t>Confirming real data</t>
+        </is>
+      </c>
+      <c r="C50" s="8" t="n"/>
+      <c r="D50" s="9" t="n"/>
+      <c r="E50" s="7" t="inlineStr">
+        <is>
+          <t>As you get real facts (a sale price, a rent, a lender quote), put them in the overrides.json file and rebuild — it lists every gap and where to source it. Or just edit the blue cell directly and keep the file.</t>
+        </is>
+      </c>
+      <c r="F50" s="8" t="n"/>
+      <c r="G50" s="8" t="n"/>
+      <c r="H50" s="8" t="n"/>
+      <c r="I50" s="8" t="n"/>
+      <c r="J50" s="8" t="n"/>
+      <c r="K50" s="8" t="n"/>
+      <c r="L50" s="8" t="n"/>
+      <c r="M50" s="9" t="n"/>
+    </row>
+    <row r="51">
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>THE COLOR CODE</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="n"/>
+      <c r="D51" s="2" t="n"/>
+      <c r="E51" s="2" t="n"/>
+      <c r="F51" s="2" t="n"/>
+      <c r="G51" s="2" t="n"/>
+      <c r="H51" s="2" t="n"/>
+      <c r="I51" s="2" t="n"/>
+      <c r="J51" s="2" t="n"/>
+      <c r="K51" s="2" t="n"/>
+      <c r="L51" s="2" t="n"/>
+      <c r="M51" s="3" t="n"/>
+    </row>
+    <row r="52" ht="15" customHeight="1">
+      <c r="B52" s="6" t="inlineStr">
+        <is>
+          <t>Blue on yellow</t>
+        </is>
+      </c>
+      <c r="C52" s="9" t="n"/>
+      <c r="D52" s="7" t="inlineStr">
+        <is>
+          <t>an input — the only cells you change</t>
+        </is>
+      </c>
+      <c r="E52" s="8" t="n"/>
+      <c r="F52" s="8" t="n"/>
+      <c r="G52" s="8" t="n"/>
+      <c r="H52" s="8" t="n"/>
+      <c r="I52" s="8" t="n"/>
+      <c r="J52" s="8" t="n"/>
+      <c r="K52" s="8" t="n"/>
+      <c r="L52" s="8" t="n"/>
+      <c r="M52" s="9" t="n"/>
+    </row>
+    <row r="53" ht="15" customHeight="1">
+      <c r="B53" s="6" t="inlineStr">
+        <is>
+          <t>Black</t>
+        </is>
+      </c>
+      <c r="C53" s="9" t="n"/>
+      <c r="D53" s="7" t="inlineStr">
+        <is>
+          <t>a formula / calculation (leave it)</t>
+        </is>
+      </c>
+      <c r="E53" s="8" t="n"/>
+      <c r="F53" s="8" t="n"/>
+      <c r="G53" s="8" t="n"/>
+      <c r="H53" s="8" t="n"/>
+      <c r="I53" s="8" t="n"/>
+      <c r="J53" s="8" t="n"/>
+      <c r="K53" s="8" t="n"/>
+      <c r="L53" s="8" t="n"/>
+      <c r="M53" s="9" t="n"/>
+    </row>
+    <row r="54" ht="15" customHeight="1">
+      <c r="B54" s="6" t="inlineStr">
+        <is>
+          <t>Green</t>
+        </is>
+      </c>
+      <c r="C54" s="9" t="n"/>
+      <c r="D54" s="7" t="inlineStr">
+        <is>
+          <t>a verified fact, or a live link pulling from another tab</t>
+        </is>
+      </c>
+      <c r="E54" s="8" t="n"/>
+      <c r="F54" s="8" t="n"/>
+      <c r="G54" s="8" t="n"/>
+      <c r="H54" s="8" t="n"/>
+      <c r="I54" s="8" t="n"/>
+      <c r="J54" s="8" t="n"/>
+      <c r="K54" s="8" t="n"/>
+      <c r="L54" s="8" t="n"/>
+      <c r="M54" s="9" t="n"/>
+    </row>
+    <row r="55" ht="15" customHeight="1">
+      <c r="B55" s="6" t="inlineStr">
+        <is>
+          <t>Gold on navy</t>
+        </is>
+      </c>
+      <c r="C55" s="9" t="n"/>
+      <c r="D55" s="7" t="inlineStr">
+        <is>
+          <t>a header, total, or key number</t>
+        </is>
+      </c>
+      <c r="E55" s="8" t="n"/>
+      <c r="F55" s="8" t="n"/>
+      <c r="G55" s="8" t="n"/>
+      <c r="H55" s="8" t="n"/>
+      <c r="I55" s="8" t="n"/>
+      <c r="J55" s="8" t="n"/>
+      <c r="K55" s="8" t="n"/>
+      <c r="L55" s="8" t="n"/>
+      <c r="M55" s="9" t="n"/>
+    </row>
+    <row r="56" ht="15" customHeight="1">
+      <c r="B56" s="6" t="inlineStr">
+        <is>
+          <t>Orange</t>
+        </is>
+      </c>
+      <c r="C56" s="9" t="n"/>
+      <c r="D56" s="7" t="inlineStr">
+        <is>
+          <t>a warning, a flag, or something to confirm</t>
+        </is>
+      </c>
+      <c r="E56" s="8" t="n"/>
+      <c r="F56" s="8" t="n"/>
+      <c r="G56" s="8" t="n"/>
+      <c r="H56" s="8" t="n"/>
+      <c r="I56" s="8" t="n"/>
+      <c r="J56" s="8" t="n"/>
+      <c r="K56" s="8" t="n"/>
+      <c r="L56" s="8" t="n"/>
+      <c r="M56" s="9" t="n"/>
+    </row>
+    <row r="57" ht="15" customHeight="1">
+      <c r="B57" s="6" t="inlineStr">
         <is>
           <t>Confidence</t>
         </is>
       </c>
-      <c r="C49" s="9" t="n"/>
-      <c r="D49" s="15" t="inlineStr">
+      <c r="C57" s="9" t="n"/>
+      <c r="D57" s="16" t="inlineStr">
         <is>
           <t>✅ verified (public record)   ·   ⚠️ reported (confirm at the county)   ·   🔶 modeled (a market assumption)</t>
         </is>
       </c>
-      <c r="E49" s="8" t="n"/>
-      <c r="F49" s="8" t="n"/>
-      <c r="G49" s="8" t="n"/>
-      <c r="H49" s="8" t="n"/>
-      <c r="I49" s="8" t="n"/>
-      <c r="J49" s="8" t="n"/>
-      <c r="K49" s="8" t="n"/>
-      <c r="L49" s="8" t="n"/>
-      <c r="M49" s="9" t="n"/>
+      <c r="E57" s="8" t="n"/>
+      <c r="F57" s="8" t="n"/>
+      <c r="G57" s="8" t="n"/>
+      <c r="H57" s="8" t="n"/>
+      <c r="I57" s="8" t="n"/>
+      <c r="J57" s="8" t="n"/>
+      <c r="K57" s="8" t="n"/>
+      <c r="L57" s="8" t="n"/>
+      <c r="M57" s="9" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="74">
+  <mergeCells count="101">
     <mergeCell ref="B11:D11"/>
     <mergeCell ref="B2:M2"/>
+    <mergeCell ref="B42:D42"/>
+    <mergeCell ref="C6:M6"/>
+    <mergeCell ref="J43:M43"/>
+    <mergeCell ref="B44:D44"/>
+    <mergeCell ref="E34:M34"/>
+    <mergeCell ref="H11:J11"/>
+    <mergeCell ref="E48:I48"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="J42:M42"/>
+    <mergeCell ref="B28:M28"/>
+    <mergeCell ref="E27:M27"/>
+    <mergeCell ref="E36:M36"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="J44:M44"/>
+    <mergeCell ref="E40:I40"/>
+    <mergeCell ref="K10:M10"/>
+    <mergeCell ref="E22:M22"/>
+    <mergeCell ref="D57:M57"/>
+    <mergeCell ref="J45:M45"/>
+    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="B43:D43"/>
+    <mergeCell ref="K11:M11"/>
+    <mergeCell ref="J47:M47"/>
+    <mergeCell ref="E42:I42"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="C5:M5"/>
+    <mergeCell ref="K12:M12"/>
+    <mergeCell ref="D55:M55"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="E44:I44"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="D54:M54"/>
+    <mergeCell ref="B9:M9"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="E25:M25"/>
+    <mergeCell ref="B36:D36"/>
+    <mergeCell ref="B45:D45"/>
+    <mergeCell ref="B20:M20"/>
+    <mergeCell ref="E46:I46"/>
+    <mergeCell ref="E18:M18"/>
+    <mergeCell ref="B4:M4"/>
+    <mergeCell ref="E50:M50"/>
+    <mergeCell ref="B47:D47"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="B46:D46"/>
+    <mergeCell ref="E41:I41"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="E47:I47"/>
+    <mergeCell ref="B48:D48"/>
+    <mergeCell ref="B39:M39"/>
     <mergeCell ref="E10:G10"/>
     <mergeCell ref="E29:M29"/>
-    <mergeCell ref="B47:C47"/>
+    <mergeCell ref="E43:I43"/>
+    <mergeCell ref="B54:C54"/>
+    <mergeCell ref="B23:M23"/>
+    <mergeCell ref="J46:M46"/>
+    <mergeCell ref="E31:M31"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="E15:M15"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="E11:G11"/>
+    <mergeCell ref="J48:M48"/>
+    <mergeCell ref="B57:C57"/>
+    <mergeCell ref="E32:M32"/>
+    <mergeCell ref="J40:M40"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B50:D50"/>
+    <mergeCell ref="E12:G12"/>
+    <mergeCell ref="E45:I45"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="E24:M24"/>
+    <mergeCell ref="H10:J10"/>
+    <mergeCell ref="C7:M7"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="E17:M17"/>
+    <mergeCell ref="B12:D12"/>
     <mergeCell ref="E19:M19"/>
-    <mergeCell ref="C6:M6"/>
-    <mergeCell ref="B23:M23"/>
-    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="D56:M56"/>
     <mergeCell ref="B14:M14"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="C5:M5"/>
-    <mergeCell ref="E31:M31"/>
     <mergeCell ref="B1:M1"/>
-    <mergeCell ref="K12:M12"/>
     <mergeCell ref="B29:D29"/>
-    <mergeCell ref="E34:M34"/>
-    <mergeCell ref="H11:J11"/>
-    <mergeCell ref="B34:D34"/>
     <mergeCell ref="E30:M30"/>
-    <mergeCell ref="B10:D10"/>
     <mergeCell ref="B38:M38"/>
-    <mergeCell ref="E15:M15"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="B48:C48"/>
-    <mergeCell ref="B28:M28"/>
-    <mergeCell ref="E11:G11"/>
-    <mergeCell ref="E27:M27"/>
-    <mergeCell ref="E36:M36"/>
-    <mergeCell ref="D44:M44"/>
-    <mergeCell ref="C41:M41"/>
+    <mergeCell ref="B40:D40"/>
     <mergeCell ref="H12:J12"/>
-    <mergeCell ref="B9:M9"/>
-    <mergeCell ref="B30:D30"/>
     <mergeCell ref="B15:D15"/>
-    <mergeCell ref="C40:M40"/>
     <mergeCell ref="B24:D24"/>
-    <mergeCell ref="E32:M32"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="E25:M25"/>
     <mergeCell ref="B33:M33"/>
-    <mergeCell ref="B36:D36"/>
-    <mergeCell ref="K10:M10"/>
-    <mergeCell ref="D46:M46"/>
-    <mergeCell ref="B20:M20"/>
+    <mergeCell ref="B51:M51"/>
     <mergeCell ref="B32:D32"/>
-    <mergeCell ref="E22:M22"/>
-    <mergeCell ref="D45:M45"/>
-    <mergeCell ref="E12:G12"/>
-    <mergeCell ref="E18:M18"/>
+    <mergeCell ref="D52:M52"/>
     <mergeCell ref="B26:M26"/>
     <mergeCell ref="E21:M21"/>
     <mergeCell ref="B35:M35"/>
-    <mergeCell ref="B4:M4"/>
-    <mergeCell ref="B25:D25"/>
-    <mergeCell ref="B49:C49"/>
-    <mergeCell ref="D49:M49"/>
-    <mergeCell ref="C39:M39"/>
     <mergeCell ref="B16:M16"/>
-    <mergeCell ref="E24:M24"/>
-    <mergeCell ref="H10:J10"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="C7:M7"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="D48:M48"/>
-    <mergeCell ref="B45:C45"/>
     <mergeCell ref="B18:D18"/>
     <mergeCell ref="B27:D27"/>
-    <mergeCell ref="E17:M17"/>
-    <mergeCell ref="B21:D21"/>
-    <mergeCell ref="D47:M47"/>
-    <mergeCell ref="B12:D12"/>
-    <mergeCell ref="B43:M43"/>
-    <mergeCell ref="K11:M11"/>
+    <mergeCell ref="D53:M53"/>
+    <mergeCell ref="J41:M41"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
@@ -2160,17 +2395,17 @@
           <t>Scenario</t>
         </is>
       </c>
-      <c r="C5" s="22" t="inlineStr">
+      <c r="C5" s="23" t="inlineStr">
         <is>
           <t>NOI achieved</t>
         </is>
       </c>
-      <c r="D5" s="22" t="inlineStr">
+      <c r="D5" s="23" t="inlineStr">
         <is>
           <t>Exit cap</t>
         </is>
       </c>
-      <c r="E5" s="22" t="inlineStr">
+      <c r="E5" s="23" t="inlineStr">
         <is>
           <t>Senior rate</t>
         </is>
@@ -2225,16 +2460,16 @@
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
-      <c r="B9" s="15" t="inlineStr">
+      <c r="B9" s="16" t="inlineStr">
         <is>
           <t>Base income price (fixed basis)</t>
         </is>
       </c>
-      <c r="C9" s="23">
+      <c r="C9" s="24">
         <f>'Income Valuation'!C61</f>
         <v/>
       </c>
-      <c r="E9" s="15" t="inlineStr">
+      <c r="E9" s="16" t="inlineStr">
         <is>
           <t>loan &amp; equity held fixed; only the senior rate varies debt service across cases</t>
         </is>
@@ -2273,7 +2508,7 @@
           <t>Year</t>
         </is>
       </c>
-      <c r="C12" s="22" t="inlineStr">
+      <c r="C12" s="23" t="inlineStr">
         <is>
           <t>0/Acq</t>
         </is>
@@ -2310,7 +2545,7 @@
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
-      <c r="B13" s="15" t="inlineStr">
+      <c r="B13" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  Downside — unlevered CF</t>
         </is>
@@ -2361,7 +2596,7 @@
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
-      <c r="B14" s="15" t="inlineStr">
+      <c r="B14" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  Downside — levered CF</t>
         </is>
@@ -2412,7 +2647,7 @@
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
-      <c r="B15" s="15" t="inlineStr">
+      <c r="B15" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  Base — unlevered CF</t>
         </is>
@@ -2463,7 +2698,7 @@
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
-      <c r="B16" s="15" t="inlineStr">
+      <c r="B16" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  Base — levered CF</t>
         </is>
@@ -2514,7 +2749,7 @@
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
-      <c r="B17" s="15" t="inlineStr">
+      <c r="B17" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  Upside — unlevered CF</t>
         </is>
@@ -2565,7 +2800,7 @@
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
-      <c r="B18" s="15" t="inlineStr">
+      <c r="B18" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  Upside — levered CF</t>
         </is>
@@ -2640,33 +2875,33 @@
           <t>Scenario</t>
         </is>
       </c>
-      <c r="D21" s="22" t="inlineStr">
+      <c r="D21" s="23" t="inlineStr">
         <is>
           <t>Income value</t>
         </is>
       </c>
       <c r="E21" s="9" t="n"/>
-      <c r="F21" s="22" t="inlineStr">
+      <c r="F21" s="23" t="inlineStr">
         <is>
           <t>Unlev IRR</t>
         </is>
       </c>
-      <c r="G21" s="22" t="inlineStr">
+      <c r="G21" s="23" t="inlineStr">
         <is>
           <t>Lev IRR</t>
         </is>
       </c>
-      <c r="H21" s="22" t="inlineStr">
+      <c r="H21" s="23" t="inlineStr">
         <is>
           <t>Lev EM</t>
         </is>
       </c>
-      <c r="I21" s="22" t="inlineStr">
+      <c r="I21" s="23" t="inlineStr">
         <is>
           <t>Yr-1 DSCR</t>
         </is>
       </c>
-      <c r="J21" s="22" t="inlineStr">
+      <c r="J21" s="23" t="inlineStr">
         <is>
           <t>Avg CoC</t>
         </is>
@@ -2708,7 +2943,7 @@
       <c r="M22" s="9" t="n"/>
     </row>
     <row r="23" ht="15" customHeight="1">
-      <c r="B23" s="27" t="inlineStr">
+      <c r="B23" s="28" t="inlineStr">
         <is>
           <t>Base</t>
         </is>
@@ -2718,11 +2953,11 @@
         <v/>
       </c>
       <c r="E23" s="9" t="n"/>
-      <c r="F23" s="32">
+      <c r="F23" s="33">
         <f>IRR(C15:M15)</f>
         <v/>
       </c>
-      <c r="G23" s="32">
+      <c r="G23" s="33">
         <f>IRR(C16:M16)</f>
         <v/>
       </c>
@@ -2734,7 +2969,7 @@
         <f>'Income Valuation'!C25*C7/('Income Valuation'!C67*((E7/12)/(1-(1+(E7/12))^(-'Income Valuation'!C44*12))*12))</f>
         <v/>
       </c>
-      <c r="J23" s="32">
+      <c r="J23" s="33">
         <f>('Income Valuation'!C50*C7-'Income Valuation'!C34*('Income Valuation'!C67*((E7/12)/(1-(1+(E7/12))^(-'Income Valuation'!C44*12))*12)))/'Income Valuation'!C34/('Income Valuation'!C61*(1+'Income Valuation'!C49)+'Income Valuation'!C39*'Income Valuation'!C67-'Income Valuation'!C67)</f>
         <v/>
       </c>
@@ -2779,12 +3014,12 @@
     </row>
     <row r="25"/>
     <row r="26" ht="27" customHeight="1">
-      <c r="B26" s="37" t="inlineStr">
+      <c r="B26" s="15" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
-      <c r="D26" s="37" t="inlineStr">
+      <c r="D26" s="15" t="inlineStr">
         <is>
           <t>Downside stresses NOI −8%, exit cap +50 bps, and rate +75 bps simultaneously (a compound recession case). The base case is highlighted; the levered IRR range brackets the deal for the investment committee.</t>
         </is>
@@ -3011,37 +3246,37 @@
           <t>Asset</t>
         </is>
       </c>
-      <c r="C11" s="22" t="inlineStr">
+      <c r="C11" s="23" t="inlineStr">
         <is>
           <t>Control cost</t>
         </is>
       </c>
-      <c r="D11" s="22" t="inlineStr">
+      <c r="D11" s="23" t="inlineStr">
         <is>
           <t>In-place NOI</t>
         </is>
       </c>
-      <c r="E11" s="22" t="inlineStr">
+      <c r="E11" s="23" t="inlineStr">
         <is>
           <t>Going-in cap</t>
         </is>
       </c>
-      <c r="F11" s="22" t="inlineStr">
+      <c r="F11" s="23" t="inlineStr">
         <is>
           <t>Land SF</t>
         </is>
       </c>
-      <c r="G11" s="22" t="inlineStr">
+      <c r="G11" s="23" t="inlineStr">
         <is>
           <t>Land value</t>
         </is>
       </c>
-      <c r="H11" s="22" t="inlineStr">
+      <c r="H11" s="23" t="inlineStr">
         <is>
           <t>Unlev IRR</t>
         </is>
       </c>
-      <c r="I11" s="22" t="inlineStr">
+      <c r="I11" s="23" t="inlineStr">
         <is>
           <t>Lev IRR</t>
         </is>
@@ -3061,11 +3296,11 @@
           <t>Shahidi Retail (Galleria Plaza)</t>
         </is>
       </c>
-      <c r="C12" s="23">
+      <c r="C12" s="24">
         <f>'Shahidi Retail'!C57</f>
         <v/>
       </c>
-      <c r="D12" s="23">
+      <c r="D12" s="24">
         <f>'Shahidi Retail'!C122</f>
         <v/>
       </c>
@@ -3077,15 +3312,15 @@
         <f>'Shahidi Retail'!C36</f>
         <v/>
       </c>
-      <c r="G12" s="23">
+      <c r="G12" s="24">
         <f>'Shahidi Retail'!C80</f>
         <v/>
       </c>
-      <c r="H12" s="33">
+      <c r="H12" s="34">
         <f>'Shahidi Retail'!C117</f>
         <v/>
       </c>
-      <c r="I12" s="33">
+      <c r="I12" s="34">
         <f>'Shahidi Retail'!C120</f>
         <v/>
       </c>
@@ -3104,11 +3339,11 @@
           <t>Publix + Starbucks</t>
         </is>
       </c>
-      <c r="C13" s="23">
+      <c r="C13" s="24">
         <f>'Publix &amp; Starbucks'!C44</f>
         <v/>
       </c>
-      <c r="D13" s="23">
+      <c r="D13" s="24">
         <f>'Publix &amp; Starbucks'!C109</f>
         <v/>
       </c>
@@ -3120,15 +3355,15 @@
         <f>'Publix &amp; Starbucks'!C25</f>
         <v/>
       </c>
-      <c r="G13" s="23">
+      <c r="G13" s="24">
         <f>'Publix &amp; Starbucks'!C67</f>
         <v/>
       </c>
-      <c r="H13" s="33">
+      <c r="H13" s="34">
         <f>'Publix &amp; Starbucks'!C104</f>
         <v/>
       </c>
-      <c r="I13" s="33">
+      <c r="I13" s="34">
         <f>'Publix &amp; Starbucks'!C107</f>
         <v/>
       </c>
@@ -3147,11 +3382,11 @@
           <t>Sunrise Plaza (Kar Luen)</t>
         </is>
       </c>
-      <c r="C14" s="23">
+      <c r="C14" s="24">
         <f>'Sunrise Plaza'!C47</f>
         <v/>
       </c>
-      <c r="D14" s="23">
+      <c r="D14" s="24">
         <f>'Sunrise Plaza'!C112</f>
         <v/>
       </c>
@@ -3163,15 +3398,15 @@
         <f>'Sunrise Plaza'!C28</f>
         <v/>
       </c>
-      <c r="G14" s="23">
+      <c r="G14" s="24">
         <f>'Sunrise Plaza'!C70</f>
         <v/>
       </c>
-      <c r="H14" s="33">
+      <c r="H14" s="34">
         <f>'Sunrise Plaza'!C107</f>
         <v/>
       </c>
-      <c r="I14" s="33">
+      <c r="I14" s="34">
         <f>'Sunrise Plaza'!C110</f>
         <v/>
       </c>
@@ -3190,11 +3425,11 @@
           <t>Galleria Corporate Centre (office)</t>
         </is>
       </c>
-      <c r="C15" s="23">
+      <c r="C15" s="24">
         <f>'Office Condo'!I99</f>
         <v/>
       </c>
-      <c r="D15" s="23">
+      <c r="D15" s="24">
         <f>'Office Condo'!C79</f>
         <v/>
       </c>
@@ -3209,11 +3444,11 @@
         <f>0</f>
         <v/>
       </c>
-      <c r="H15" s="33">
+      <c r="H15" s="34">
         <f>'Office Condo'!C74</f>
         <v/>
       </c>
-      <c r="I15" s="33">
+      <c r="I15" s="34">
         <f>'Office Condo'!C77</f>
         <v/>
       </c>
@@ -3232,11 +3467,11 @@
           <t>1040 Bayview (covered land)</t>
         </is>
       </c>
-      <c r="C16" s="23">
+      <c r="C16" s="24">
         <f>'Land'!E43</f>
         <v/>
       </c>
-      <c r="D16" s="23">
+      <c r="D16" s="24">
         <f>'Land'!C50</f>
         <v/>
       </c>
@@ -3248,15 +3483,15 @@
         <f>'Land'!C18</f>
         <v/>
       </c>
-      <c r="G16" s="23">
+      <c r="G16" s="24">
         <f>'Land'!E43</f>
         <v/>
       </c>
-      <c r="H16" s="33">
+      <c r="H16" s="34">
         <f>'Land'!C68</f>
         <v/>
       </c>
-      <c r="I16" s="33">
+      <c r="I16" s="34">
         <f>'Land'!C71</f>
         <v/>
       </c>
@@ -3270,16 +3505,16 @@
       <c r="M16" s="9" t="n"/>
     </row>
     <row r="17" ht="15" customHeight="1">
-      <c r="B17" s="27" t="inlineStr">
+      <c r="B17" s="28" t="inlineStr">
         <is>
           <t>ASSEMBLAGE TOTAL (pre-premium)</t>
         </is>
       </c>
-      <c r="C17" s="30">
+      <c r="C17" s="31">
         <f>SUM(C12:C16)</f>
         <v/>
       </c>
-      <c r="D17" s="30">
+      <c r="D17" s="31">
         <f>SUM(D12:D16)</f>
         <v/>
       </c>
@@ -3291,21 +3526,21 @@
         <f>SUM(F12:F16)</f>
         <v/>
       </c>
-      <c r="G17" s="30">
+      <c r="G17" s="31">
         <f>SUM(G12:G16)</f>
         <v/>
       </c>
-      <c r="H17" s="28" t="inlineStr">
+      <c r="H17" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I17" s="28" t="inlineStr">
+      <c r="I17" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J17" s="27" t="inlineStr">
+      <c r="J17" s="28" t="inlineStr">
         <is>
           <t>blended going-in cap covers carry</t>
         </is>
@@ -3343,7 +3578,7 @@
         <f>341501</f>
         <v/>
       </c>
-      <c r="D20" s="15" t="inlineStr">
+      <c r="D20" s="16" t="inlineStr">
         <is>
           <t>existing improvements across all five</t>
         </is>
@@ -3368,7 +3603,7 @@
         <f>F17/43560</f>
         <v/>
       </c>
-      <c r="D21" s="15" t="inlineStr">
+      <c r="D21" s="16" t="inlineStr">
         <is>
           <t>≈ 7+ acres of E Sunrise frontage</t>
         </is>
@@ -3393,7 +3628,7 @@
         <f>G17/F17</f>
         <v/>
       </c>
-      <c r="D22" s="15" t="inlineStr">
+      <c r="D22" s="16" t="inlineStr">
         <is>
           <t>vs. subject comps $228–255/SF; Galleria bulk $53/SF</t>
         </is>
@@ -3418,7 +3653,7 @@
         <f>D17/C17</f>
         <v/>
       </c>
-      <c r="D23" s="15" t="inlineStr">
+      <c r="D23" s="16" t="inlineStr">
         <is>
           <t>covered-land range ~3–5% — income covers carry, not a yield play</t>
         </is>
@@ -3462,7 +3697,7 @@
         <f>C17*(1+'Assumptions'!C39)</f>
         <v/>
       </c>
-      <c r="D26" s="33">
+      <c r="D26" s="34">
         <f>'Assumptions'!C39</f>
         <v/>
       </c>
@@ -3477,7 +3712,7 @@
         <f>C17*(1+'Assumptions'!C40)</f>
         <v/>
       </c>
-      <c r="D27" s="33">
+      <c r="D27" s="34">
         <f>'Assumptions'!C40</f>
         <v/>
       </c>
@@ -3492,22 +3727,22 @@
         <f>C17*(1+'Assumptions'!C41)</f>
         <v/>
       </c>
-      <c r="D28" s="33">
+      <c r="D28" s="34">
         <f>'Assumptions'!C41</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="16" customHeight="1">
-      <c r="B29" s="20" t="inlineStr">
+      <c r="B29" s="21" t="inlineStr">
         <is>
           <t>TOTAL ASSEMBLAGE ACQUISITION COST (base)</t>
         </is>
       </c>
-      <c r="C29" s="21">
+      <c r="C29" s="22">
         <f>C27</f>
         <v/>
       </c>
-      <c r="D29" s="15" t="inlineStr">
+      <c r="D29" s="16" t="inlineStr">
         <is>
           <t>🔶 base premium (Assumptions tab) on the summed control cost</t>
         </is>
@@ -3547,13 +3782,13 @@
           <t>Redevelopment residual — 1040 Bayview (per Land tab)</t>
         </is>
       </c>
-      <c r="C32" s="19">
+      <c r="C32" s="20">
         <f>'Land'!C81</f>
         <v/>
       </c>
     </row>
     <row r="33" ht="27" customHeight="1">
-      <c r="B33" s="37" t="inlineStr">
+      <c r="B33" s="15" t="inlineStr">
         <is>
           <t>Redevelopment verdict</t>
         </is>
@@ -3563,7 +3798,7 @@
           <t>HOLD</t>
         </is>
       </c>
-      <c r="D33" s="37" t="inlineStr">
+      <c r="D33" s="15" t="inlineStr">
         <is>
           <t>Residual runs NEGATIVE in the AE flood zone at current coastal hard costs — do not force it positive. Best use today = hold the income-covered land + Live Local density option until costs/rents support redevelopment.</t>
         </is>
@@ -3620,12 +3855,12 @@
       </c>
     </row>
     <row r="38" ht="27" customHeight="1">
-      <c r="B38" s="37" t="inlineStr">
+      <c r="B38" s="15" t="inlineStr">
         <is>
           <t>Portfolio IRR (unlevered / levered)</t>
         </is>
       </c>
-      <c r="D38" s="37" t="inlineStr">
+      <c r="D38" s="15" t="inlineStr">
         <is>
           <t>Computed from the CONSOLIDATED cash flows on the Income Valuation tab — never by averaging asset IRRs (mathematically invalid). See that tab for portfolio returns at both the income and covered-land prices.</t>
         </is>
@@ -3761,7 +3996,7 @@
           <t>Component</t>
         </is>
       </c>
-      <c r="C5" s="22" t="inlineStr">
+      <c r="C5" s="23" t="inlineStr">
         <is>
           <t>Independent price</t>
         </is>
@@ -3786,11 +4021,11 @@
           <t>Shahidi Retail (Galleria Plaza)</t>
         </is>
       </c>
-      <c r="C6" s="23">
+      <c r="C6" s="24">
         <f>'Shahidi Retail'!C57</f>
         <v/>
       </c>
-      <c r="E6" s="15" t="inlineStr">
+      <c r="E6" s="16" t="inlineStr">
         <is>
           <t>acquire fee · value-add retail</t>
         </is>
@@ -3810,11 +4045,11 @@
           <t>Publix + Starbucks</t>
         </is>
       </c>
-      <c r="C7" s="23">
+      <c r="C7" s="24">
         <f>'Publix &amp; Starbucks'!C44</f>
         <v/>
       </c>
-      <c r="E7" s="15" t="inlineStr">
+      <c r="E7" s="16" t="inlineStr">
         <is>
           <t>sale-leaseback (acquire fee)</t>
         </is>
@@ -3834,11 +4069,11 @@
           <t>Sunrise Plaza (Kar Luen)</t>
         </is>
       </c>
-      <c r="C8" s="23">
+      <c r="C8" s="24">
         <f>'Sunrise Plaza'!C47</f>
         <v/>
       </c>
-      <c r="E8" s="15" t="inlineStr">
+      <c r="E8" s="16" t="inlineStr">
         <is>
           <t>acquire fee · restaurant value-add</t>
         </is>
@@ -3858,11 +4093,11 @@
           <t>Galleria Corp Centre (full buy-out)</t>
         </is>
       </c>
-      <c r="C9" s="23">
+      <c r="C9" s="24">
         <f>'Office Condo'!I99</f>
         <v/>
       </c>
-      <c r="E9" s="15" t="inlineStr">
+      <c r="E9" s="16" t="inlineStr">
         <is>
           <t>buy out BOTH condo owners</t>
         </is>
@@ -3882,11 +4117,11 @@
           <t>1040 Bayview (entitled land)</t>
         </is>
       </c>
-      <c r="C10" s="23">
+      <c r="C10" s="24">
         <f>'Land'!E43</f>
         <v/>
       </c>
-      <c r="E10" s="15" t="inlineStr">
+      <c r="E10" s="16" t="inlineStr">
         <is>
           <t>covered land · hold for redevelopment</t>
         </is>
@@ -3910,7 +4145,7 @@
         <f>SUM(C6:C10)</f>
         <v/>
       </c>
-      <c r="E11" s="15" t="inlineStr">
+      <c r="E11" s="16" t="inlineStr">
         <is>
           <t>what you'd pay buying each one at a time</t>
         </is>
@@ -3934,11 +4169,11 @@
         <f>C11*'Assumptions'!C40</f>
         <v/>
       </c>
-      <c r="D12" s="33">
+      <c r="D12" s="34">
         <f>'Assumptions'!C40</f>
         <v/>
       </c>
-      <c r="E12" s="15" t="inlineStr">
+      <c r="E12" s="16" t="inlineStr">
         <is>
           <t>5 owners · a sale-leaseback · a fractured condo · holdout risk</t>
         </is>
@@ -3953,16 +4188,16 @@
       <c r="M12" s="9" t="n"/>
     </row>
     <row r="13" ht="16" customHeight="1">
-      <c r="B13" s="20" t="inlineStr">
+      <c r="B13" s="21" t="inlineStr">
         <is>
           <t>PRICED AS AN ASSEMBLAGE (base)</t>
         </is>
       </c>
-      <c r="C13" s="21">
+      <c r="C13" s="22">
         <f>C11+C12</f>
         <v/>
       </c>
-      <c r="E13" s="15" t="inlineStr">
+      <c r="E13" s="16" t="inlineStr">
         <is>
           <t>total to control the whole block</t>
         </is>
@@ -4001,17 +4236,17 @@
           <t>Component / owner</t>
         </is>
       </c>
-      <c r="C16" s="22" t="inlineStr">
+      <c r="C16" s="23" t="inlineStr">
         <is>
           <t>Bought</t>
         </is>
       </c>
-      <c r="D16" s="22" t="inlineStr">
+      <c r="D16" s="23" t="inlineStr">
         <is>
           <t>For</t>
         </is>
       </c>
-      <c r="E16" s="22" t="inlineStr">
+      <c r="E16" s="23" t="inlineStr">
         <is>
           <t>Our modeled price</t>
         </is>
@@ -4040,15 +4275,15 @@
           <t>11/09/2021</t>
         </is>
       </c>
-      <c r="D17" s="23">
+      <c r="D17" s="24">
         <f>'Assumptions'!C27</f>
         <v/>
       </c>
-      <c r="E17" s="23">
+      <c r="E17" s="24">
         <f>'Shahidi Retail'!C57</f>
         <v/>
       </c>
-      <c r="F17" s="15" t="inlineStr">
+      <c r="F17" s="16" t="inlineStr">
         <is>
           <t>Special Warranty Deed (flagged disqualified sale)</t>
         </is>
@@ -4072,15 +4307,15 @@
           <t>03/14/2025</t>
         </is>
       </c>
-      <c r="D18" s="23">
+      <c r="D18" s="24">
         <f>'Assumptions'!C29</f>
         <v/>
       </c>
-      <c r="E18" s="23">
+      <c r="E18" s="24">
         <f>'Publix &amp; Starbucks'!C44</f>
         <v/>
       </c>
-      <c r="F18" s="15" t="inlineStr">
+      <c r="F18" s="16" t="inlineStr">
         <is>
           <t>Trustee's Deed · $679/SF bldg</t>
         </is>
@@ -4104,15 +4339,15 @@
           <t>Oct 2000</t>
         </is>
       </c>
-      <c r="D19" s="23">
+      <c r="D19" s="24">
         <f>'Assumptions'!C31</f>
         <v/>
       </c>
-      <c r="E19" s="23">
+      <c r="E19" s="24">
         <f>'Sunrise Plaza'!C47</f>
         <v/>
       </c>
-      <c r="F19" s="15" t="inlineStr">
+      <c r="F19" s="16" t="inlineStr">
         <is>
           <t>stale/nominal — held since; no recent arm's-length</t>
         </is>
@@ -4136,15 +4371,15 @@
           <t>09/23/2019</t>
         </is>
       </c>
-      <c r="D20" s="23">
+      <c r="D20" s="24">
         <f>'Assumptions'!C33</f>
         <v/>
       </c>
-      <c r="E20" s="23">
+      <c r="E20" s="24">
         <f>'Office Condo'!I91</f>
         <v/>
       </c>
-      <c r="F20" s="15" t="inlineStr">
+      <c r="F20" s="16" t="inlineStr">
         <is>
           <t>$103/SF from Intl Sunrise (dissolved 2020); now reselling units $270–381/SF</t>
         </is>
@@ -4178,7 +4413,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F21" s="15" t="inlineStr">
+      <c r="F21" s="16" t="inlineStr">
         <is>
           <t>~40 small owners (Merrimac, Cosmo, Jorgensen, Hublot); un-itemizable without BCPA</t>
         </is>
@@ -4202,15 +4437,15 @@
           <t>2014 (JV)</t>
         </is>
       </c>
-      <c r="D22" s="23">
+      <c r="D22" s="24">
         <f>'Assumptions'!C35</f>
         <v/>
       </c>
-      <c r="E22" s="23">
+      <c r="E22" s="24">
         <f>'Land'!E43</f>
         <v/>
       </c>
-      <c r="F22" s="15" t="inlineStr">
+      <c r="F22" s="16" t="inlineStr">
         <is>
           <t>Procacci/BBX bought 2014 ~$7.9M; BBX exited to Procacci 2022</t>
         </is>
@@ -4248,17 +4483,17 @@
           <t>Parcel</t>
         </is>
       </c>
-      <c r="C25" s="22" t="inlineStr">
+      <c r="C25" s="23" t="inlineStr">
         <is>
           <t>Land SF</t>
         </is>
       </c>
-      <c r="D25" s="22" t="inlineStr">
+      <c r="D25" s="23" t="inlineStr">
         <is>
           <t>$/SF</t>
         </is>
       </c>
-      <c r="E25" s="22" t="inlineStr">
+      <c r="E25" s="23" t="inlineStr">
         <is>
           <t>Land value</t>
         </is>
@@ -4286,15 +4521,15 @@
         <f>'Shahidi Retail'!C36</f>
         <v/>
       </c>
-      <c r="D26" s="35">
+      <c r="D26" s="36">
         <f>'Shahidi Retail'!C79</f>
         <v/>
       </c>
-      <c r="E26" s="23">
+      <c r="E26" s="24">
         <f>'Shahidi Retail'!C80</f>
         <v/>
       </c>
-      <c r="F26" s="15" t="inlineStr">
+      <c r="F26" s="16" t="inlineStr">
         <is>
           <t>standalone parcel</t>
         </is>
@@ -4317,15 +4552,15 @@
         <f>'Publix &amp; Starbucks'!C25</f>
         <v/>
       </c>
-      <c r="D27" s="35">
+      <c r="D27" s="36">
         <f>'Publix &amp; Starbucks'!C55</f>
         <v/>
       </c>
-      <c r="E27" s="23">
+      <c r="E27" s="24">
         <f>'Publix &amp; Starbucks'!C67</f>
         <v/>
       </c>
-      <c r="F27" s="15" t="inlineStr">
+      <c r="F27" s="16" t="inlineStr">
         <is>
           <t>standalone parcel</t>
         </is>
@@ -4348,15 +4583,15 @@
         <f>'Sunrise Plaza'!C28</f>
         <v/>
       </c>
-      <c r="D28" s="35">
+      <c r="D28" s="36">
         <f>'Sunrise Plaza'!C58</f>
         <v/>
       </c>
-      <c r="E28" s="23">
+      <c r="E28" s="24">
         <f>'Sunrise Plaza'!C70</f>
         <v/>
       </c>
-      <c r="F28" s="15" t="inlineStr">
+      <c r="F28" s="16" t="inlineStr">
         <is>
           <t>standalone parcel</t>
         </is>
@@ -4383,11 +4618,11 @@
         <f>'Land'!E43/'Land'!C18</f>
         <v/>
       </c>
-      <c r="E29" s="23">
+      <c r="E29" s="24">
         <f>'Land'!E43</f>
         <v/>
       </c>
-      <c r="F29" s="15" t="inlineStr">
+      <c r="F29" s="16" t="inlineStr">
         <is>
           <t>standalone parcel</t>
         </is>
@@ -4418,7 +4653,7 @@
         <f>SUM(E26:E29)</f>
         <v/>
       </c>
-      <c r="F30" s="15" t="inlineStr">
+      <c r="F30" s="16" t="inlineStr">
         <is>
           <t>office excluded — building, not land (buy-out below)</t>
         </is>
@@ -4459,7 +4694,7 @@
         <f>C30</f>
         <v/>
       </c>
-      <c r="E32" s="15" t="inlineStr">
+      <c r="E32" s="16" t="inlineStr">
         <is>
           <t>4 contiguous land parcels, one plat block</t>
         </is>
@@ -4494,7 +4729,7 @@
         <f>'Assumptions'!C40</f>
         <v/>
       </c>
-      <c r="E34" s="15" t="inlineStr">
+      <c r="E34" s="16" t="inlineStr">
         <is>
           <t>uplift for a large contiguous development site</t>
         </is>
@@ -4520,12 +4755,12 @@
       </c>
     </row>
     <row r="36" ht="16" customHeight="1">
-      <c r="B36" s="20" t="inlineStr">
+      <c r="B36" s="21" t="inlineStr">
         <is>
           <t>Assembled land value — BASE</t>
         </is>
       </c>
-      <c r="C36" s="21">
+      <c r="C36" s="22">
         <f>E30*(1+'Assumptions'!C40)</f>
         <v/>
       </c>
@@ -4551,7 +4786,7 @@
         <f>C36/C30</f>
         <v/>
       </c>
-      <c r="E38" s="15" t="inlineStr">
+      <c r="E38" s="16" t="inlineStr">
         <is>
           <t>vs. fragmented blend above</t>
         </is>
@@ -4575,7 +4810,7 @@
         <f>C36-E30</f>
         <v/>
       </c>
-      <c r="E39" s="15" t="inlineStr">
+      <c r="E39" s="16" t="inlineStr">
         <is>
           <t>the value created / cost incurred by assembling the hard-to-put-together block</t>
         </is>
@@ -4599,7 +4834,7 @@
         <f>'Assumptions'!C44</f>
         <v/>
       </c>
-      <c r="E40" s="15" t="inlineStr">
+      <c r="E40" s="16" t="inlineStr">
         <is>
           <t>value bump once entitled for Live Local density</t>
         </is>
@@ -4614,16 +4849,16 @@
       <c r="M40" s="9" t="n"/>
     </row>
     <row r="41" ht="16" customHeight="1">
-      <c r="B41" s="20" t="inlineStr">
+      <c r="B41" s="21" t="inlineStr">
         <is>
           <t>POST-APPROVAL assembled land value</t>
         </is>
       </c>
-      <c r="C41" s="21">
+      <c r="C41" s="22">
         <f>C36*(1+'Assumptions'!C44)</f>
         <v/>
       </c>
-      <c r="E41" s="15" t="inlineStr">
+      <c r="E41" s="16" t="inlineStr">
         <is>
           <t>what the ENTITLED dirt is worth — the redevelopment upside the premium buys you the option on</t>
         </is>
@@ -4662,11 +4897,11 @@
           <t>Main Street Fund LLC (Grove Gate, 57.4%)</t>
         </is>
       </c>
-      <c r="C44" s="23">
+      <c r="C44" s="24">
         <f>'Office Condo'!I91</f>
         <v/>
       </c>
-      <c r="E44" s="15" t="inlineStr">
+      <c r="E44" s="16" t="inlineStr">
         <is>
           <t>bought 96,930 SF + 2 parking lots for $10M (2019)</t>
         </is>
@@ -4686,11 +4921,11 @@
           <t>International Sunrise Partners LLC (42.6%)</t>
         </is>
       </c>
-      <c r="C45" s="23">
+      <c r="C45" s="24">
         <f>'Office Condo'!I92</f>
         <v/>
       </c>
-      <c r="E45" s="15" t="inlineStr">
+      <c r="E45" s="16" t="inlineStr">
         <is>
           <t>prior bulk owner (2011 condo-conversion sponsor)</t>
         </is>
@@ -4705,16 +4940,16 @@
       <c r="M45" s="9" t="n"/>
     </row>
     <row r="46" ht="16" customHeight="1">
-      <c r="B46" s="20" t="inlineStr">
+      <c r="B46" s="21" t="inlineStr">
         <is>
           <t>FULL BUY-OUT VALUE (both owners)</t>
         </is>
       </c>
-      <c r="C46" s="21">
+      <c r="C46" s="22">
         <f>'Office Condo'!I99</f>
         <v/>
       </c>
-      <c r="E46" s="15" t="inlineStr">
+      <c r="E46" s="16" t="inlineStr">
         <is>
           <t>income value + buy-out premium; adjust the premium on the Office Condo tab</t>
         </is>
@@ -4756,7 +4991,7 @@
       <c r="C49" s="92" t="n">
         <v>100</v>
       </c>
-      <c r="D49" s="15" t="inlineStr">
+      <c r="D49" s="16" t="inlineStr">
         <is>
           <t>🔵 Live Local target</t>
         </is>
@@ -4781,7 +5016,7 @@
         <f>C30/43560*C49</f>
         <v/>
       </c>
-      <c r="E50" s="15" t="inlineStr">
+      <c r="E50" s="16" t="inlineStr">
         <is>
           <t>acres × density</t>
         </is>
@@ -4805,7 +5040,7 @@
         <f>C50*'Assumptions'!C51</f>
         <v/>
       </c>
-      <c r="E51" s="15" t="inlineStr">
+      <c r="E51" s="16" t="inlineStr">
         <is>
           <t>units × achievable value/unit (Assumptions)</t>
         </is>
@@ -4864,18 +5099,18 @@
       </c>
     </row>
     <row r="56" ht="16" customHeight="1">
-      <c r="B56" s="20" t="inlineStr">
+      <c r="B56" s="21" t="inlineStr">
         <is>
           <t>RESIDUAL LAND VALUE (supports acquisition?)</t>
         </is>
       </c>
-      <c r="C56" s="21">
+      <c r="C56" s="22">
         <f>C51+C53-C52*'Assumptions'!C52*'Assumptions'!C54-C51*'Assumptions'!C55</f>
         <v/>
       </c>
     </row>
     <row r="57" ht="27" customHeight="1">
-      <c r="B57" s="37" t="inlineStr">
+      <c r="B57" s="15" t="inlineStr">
         <is>
           <t>HBU verdict</t>
         </is>
@@ -4885,7 +5120,7 @@
           <t>HOLD</t>
         </is>
       </c>
-      <c r="D57" s="37" t="inlineStr">
+      <c r="D57" s="15" t="inlineStr">
         <is>
           <t>Residual runs NEGATIVE at coastal AE-zone hard costs — redevelopment does not pencil today. Highest &amp; best use = acquire and HOLD the income-covered assemblage; redevelop when achievable rents / hard costs support Live Local density.</t>
         </is>
@@ -5400,7 +5635,7 @@
       <c r="M18" s="3" t="n"/>
     </row>
     <row r="19" ht="15" customHeight="1">
-      <c r="B19" s="22" t="inlineStr">
+      <c r="B19" s="23" t="inlineStr">
         <is>
           <t>Suite</t>
         </is>
@@ -5416,24 +5651,24 @@
         </is>
       </c>
       <c r="E19" s="9" t="n"/>
-      <c r="F19" s="22" t="inlineStr">
+      <c r="F19" s="23" t="inlineStr">
         <is>
           <t>SF</t>
         </is>
       </c>
-      <c r="G19" s="22" t="inlineStr">
+      <c r="G19" s="23" t="inlineStr">
         <is>
           <t>$/SF NNN</t>
         </is>
       </c>
-      <c r="H19" s="22" t="inlineStr">
+      <c r="H19" s="23" t="inlineStr">
         <is>
           <t>Annual rent</t>
         </is>
       </c>
       <c r="I19" s="8" t="n"/>
       <c r="J19" s="9" t="n"/>
-      <c r="K19" s="22" t="inlineStr">
+      <c r="K19" s="23" t="inlineStr">
         <is>
           <t>Tenant type</t>
         </is>
@@ -5780,12 +6015,12 @@
           <t>—</t>
         </is>
       </c>
-      <c r="C29" s="37" t="inlineStr">
+      <c r="C29" s="15" t="inlineStr">
         <is>
           <t>VACANT / available (mid-strip)</t>
         </is>
       </c>
-      <c r="D29" s="37" t="inlineStr">
+      <c r="D29" s="15" t="inlineStr">
         <is>
           <t>Lease-up target to 95%</t>
         </is>
@@ -5806,7 +6041,7 @@
       </c>
       <c r="I29" s="8" t="n"/>
       <c r="J29" s="9" t="n"/>
-      <c r="K29" s="37" t="inlineStr">
+      <c r="K29" s="15" t="inlineStr">
         <is>
           <t>value-add upside</t>
         </is>
@@ -5815,17 +6050,17 @@
       <c r="M29" s="9" t="n"/>
     </row>
     <row r="30" ht="27" customHeight="1">
-      <c r="B30" s="27" t="inlineStr">
+      <c r="B30" s="28" t="inlineStr">
         <is>
           <t>TOTAL / WEIGHTED AVG</t>
         </is>
       </c>
-      <c r="C30" s="27" t="inlineStr">
+      <c r="C30" s="28" t="inlineStr">
         <is>
           <t>9 tenants + vacancy</t>
         </is>
       </c>
-      <c r="D30" s="29" t="inlineStr"/>
+      <c r="D30" s="30" t="inlineStr"/>
       <c r="E30" s="9" t="n"/>
       <c r="F30" s="85">
         <f>SUM(F20:F29)</f>
@@ -5835,13 +6070,13 @@
         <f>IFERROR(SUM(H20:H28)/SUM(F20:F28),0)</f>
         <v/>
       </c>
-      <c r="H30" s="30">
+      <c r="H30" s="31">
         <f>SUM(H20:H28)</f>
         <v/>
       </c>
       <c r="I30" s="8" t="n"/>
       <c r="J30" s="9" t="n"/>
-      <c r="K30" s="27" t="inlineStr">
+      <c r="K30" s="28" t="inlineStr">
         <is>
           <t>Wells Fargo + Verizon = credit</t>
         </is>
@@ -5895,7 +6130,7 @@
       <c r="C34" s="92" t="n">
         <v>26272</v>
       </c>
-      <c r="D34" s="15" t="inlineStr">
+      <c r="D34" s="16" t="inlineStr">
         <is>
           <t>✅ BCPA</t>
         </is>
@@ -5916,11 +6151,11 @@
           <t>In-place occupancy</t>
         </is>
       </c>
-      <c r="C35" s="36">
+      <c r="C35" s="37">
         <f>'Assumptions'!C63</f>
         <v/>
       </c>
-      <c r="D35" s="15" t="inlineStr">
+      <c r="D35" s="16" t="inlineStr">
         <is>
           <t>🟢 Assumptions</t>
         </is>
@@ -5945,7 +6180,7 @@
         <f>'Assumptions'!C60</f>
         <v/>
       </c>
-      <c r="D36" s="15" t="inlineStr">
+      <c r="D36" s="16" t="inlineStr">
         <is>
           <t>🟢 Assumptions</t>
         </is>
@@ -5969,7 +6204,7 @@
       <c r="C37" s="97" t="n">
         <v>0.0191</v>
       </c>
-      <c r="D37" s="15" t="inlineStr">
+      <c r="D37" s="16" t="inlineStr">
         <is>
           <t>✅ 2025 tax ÷ just value</t>
         </is>
@@ -6011,7 +6246,7 @@
       <c r="C39" s="93" t="n">
         <v>55</v>
       </c>
-      <c r="D39" s="15" t="inlineStr">
+      <c r="D39" s="16" t="inlineStr">
         <is>
           <t>🔶 owner says $60; corridor $45–60</t>
         </is>
@@ -6032,11 +6267,11 @@
           <t>Market rent ($/SF NNN)</t>
         </is>
       </c>
-      <c r="C40" s="35">
+      <c r="C40" s="36">
         <f>'Assumptions'!C62</f>
         <v/>
       </c>
-      <c r="D40" s="15" t="inlineStr">
+      <c r="D40" s="16" t="inlineStr">
         <is>
           <t>🟢 Assumptions</t>
         </is>
@@ -6060,7 +6295,7 @@
       <c r="C41" s="98" t="n">
         <v>0.03</v>
       </c>
-      <c r="D41" s="15" t="inlineStr">
+      <c r="D41" s="16" t="inlineStr">
         <is>
           <t>🔶</t>
         </is>
@@ -6081,11 +6316,11 @@
           <t>Stabilized occupancy</t>
         </is>
       </c>
-      <c r="C42" s="33">
+      <c r="C42" s="34">
         <f>'Assumptions'!C64</f>
         <v/>
       </c>
-      <c r="D42" s="15" t="inlineStr">
+      <c r="D42" s="16" t="inlineStr">
         <is>
           <t>🟢 Assumptions</t>
         </is>
@@ -6109,7 +6344,7 @@
       <c r="C43" s="98" t="n">
         <v>0.02</v>
       </c>
-      <c r="D43" s="15" t="inlineStr">
+      <c r="D43" s="16" t="inlineStr">
         <is>
           <t>🔶</t>
         </is>
@@ -6151,7 +6386,7 @@
       <c r="C45" s="47" t="n">
         <v>17100000</v>
       </c>
-      <c r="D45" s="15" t="inlineStr">
+      <c r="D45" s="16" t="inlineStr">
         <is>
           <t>🔶 FL reassess-to-price</t>
         </is>
@@ -6172,11 +6407,11 @@
           <t>Insurance ($/yr)</t>
         </is>
       </c>
-      <c r="C46" s="19">
+      <c r="C46" s="20">
         <f>'Assumptions'!C65</f>
         <v/>
       </c>
-      <c r="D46" s="15" t="inlineStr">
+      <c r="D46" s="16" t="inlineStr">
         <is>
           <t>🟢 Assumptions</t>
         </is>
@@ -6197,11 +6432,11 @@
           <t>CAM ($/yr, recoverable)</t>
         </is>
       </c>
-      <c r="C47" s="19">
+      <c r="C47" s="20">
         <f>'Assumptions'!C66</f>
         <v/>
       </c>
-      <c r="D47" s="15" t="inlineStr">
+      <c r="D47" s="16" t="inlineStr">
         <is>
           <t>🟢 Assumptions</t>
         </is>
@@ -6222,11 +6457,11 @@
           <t>Repairs &amp; maintenance ($/yr)</t>
         </is>
       </c>
-      <c r="C48" s="19">
+      <c r="C48" s="20">
         <f>'Assumptions'!C67</f>
         <v/>
       </c>
-      <c r="D48" s="15" t="inlineStr">
+      <c r="D48" s="16" t="inlineStr">
         <is>
           <t>🟢 Assumptions</t>
         </is>
@@ -6247,11 +6482,11 @@
           <t>Management fee (% EGR)</t>
         </is>
       </c>
-      <c r="C49" s="33">
+      <c r="C49" s="34">
         <f>'Assumptions'!C68</f>
         <v/>
       </c>
-      <c r="D49" s="15" t="inlineStr">
+      <c r="D49" s="16" t="inlineStr">
         <is>
           <t>🟢 Assumptions</t>
         </is>
@@ -6275,7 +6510,7 @@
       <c r="C50" s="98" t="n">
         <v>0.03</v>
       </c>
-      <c r="D50" s="15" t="inlineStr">
+      <c r="D50" s="16" t="inlineStr">
         <is>
           <t>🔶</t>
         </is>
@@ -6317,7 +6552,7 @@
       <c r="C52" s="93" t="n">
         <v>30</v>
       </c>
-      <c r="D52" s="15" t="inlineStr">
+      <c r="D52" s="16" t="inlineStr">
         <is>
           <t>🔶 on leased-up SF</t>
         </is>
@@ -6341,7 +6576,7 @@
       <c r="C53" s="93" t="n">
         <v>20</v>
       </c>
-      <c r="D53" s="15" t="inlineStr">
+      <c r="D53" s="16" t="inlineStr">
         <is>
           <t>🔶 on leased-up SF</t>
         </is>
@@ -6365,7 +6600,7 @@
       <c r="C54" s="93" t="n">
         <v>0.15</v>
       </c>
-      <c r="D54" s="15" t="inlineStr">
+      <c r="D54" s="16" t="inlineStr">
         <is>
           <t>🔶</t>
         </is>
@@ -6389,7 +6624,7 @@
       <c r="C55" s="93" t="n">
         <v>0.75</v>
       </c>
-      <c r="D55" s="15" t="inlineStr">
+      <c r="D55" s="16" t="inlineStr">
         <is>
           <t>🔶</t>
         </is>
@@ -6428,11 +6663,11 @@
           <t>Purchase price</t>
         </is>
       </c>
-      <c r="C57" s="19">
+      <c r="C57" s="20">
         <f>'Assumptions'!C59</f>
         <v/>
       </c>
-      <c r="D57" s="15" t="inlineStr">
+      <c r="D57" s="16" t="inlineStr">
         <is>
           <t>🟢 Assumptions</t>
         </is>
@@ -6456,7 +6691,7 @@
       <c r="C58" s="98" t="n">
         <v>0.025</v>
       </c>
-      <c r="D58" s="15" t="inlineStr">
+      <c r="D58" s="16" t="inlineStr">
         <is>
           <t>🔶</t>
         </is>
@@ -6477,11 +6712,11 @@
           <t>Senior loan LTV</t>
         </is>
       </c>
-      <c r="C59" s="33">
+      <c r="C59" s="34">
         <f>'Assumptions'!C71</f>
         <v/>
       </c>
-      <c r="D59" s="15" t="inlineStr">
+      <c r="D59" s="16" t="inlineStr">
         <is>
           <t>🟢 Assumptions</t>
         </is>
@@ -6502,11 +6737,11 @@
           <t>Senior loan rate</t>
         </is>
       </c>
-      <c r="C60" s="36">
+      <c r="C60" s="37">
         <f>'Assumptions'!C72</f>
         <v/>
       </c>
-      <c r="D60" s="15" t="inlineStr">
+      <c r="D60" s="16" t="inlineStr">
         <is>
           <t>🟢 Assumptions</t>
         </is>
@@ -6530,7 +6765,7 @@
       <c r="C61" s="99" t="n">
         <v>30</v>
       </c>
-      <c r="D61" s="15" t="inlineStr">
+      <c r="D61" s="16" t="inlineStr">
         <is>
           <t>🔶</t>
         </is>
@@ -6569,11 +6804,11 @@
           <t>Going-in cap (reference)</t>
         </is>
       </c>
-      <c r="C63" s="33">
+      <c r="C63" s="34">
         <f>'Assumptions'!C69</f>
         <v/>
       </c>
-      <c r="D63" s="15" t="inlineStr">
+      <c r="D63" s="16" t="inlineStr">
         <is>
           <t>🟢 Assumptions</t>
         </is>
@@ -6594,11 +6829,11 @@
           <t>Exit / reversion cap</t>
         </is>
       </c>
-      <c r="C64" s="33">
+      <c r="C64" s="34">
         <f>'Assumptions'!C70</f>
         <v/>
       </c>
-      <c r="D64" s="15" t="inlineStr">
+      <c r="D64" s="16" t="inlineStr">
         <is>
           <t>🟢 Assumptions</t>
         </is>
@@ -6622,7 +6857,7 @@
       <c r="C65" s="98" t="n">
         <v>0.02</v>
       </c>
-      <c r="D65" s="15" t="inlineStr">
+      <c r="D65" s="16" t="inlineStr">
         <is>
           <t>🔶</t>
         </is>
@@ -6646,7 +6881,7 @@
       <c r="C66" s="99" t="n">
         <v>5</v>
       </c>
-      <c r="D66" s="15" t="inlineStr">
+      <c r="D66" s="16" t="inlineStr">
         <is>
           <t>🔶 reversion in this year</t>
         </is>
@@ -6670,7 +6905,7 @@
       <c r="C67" s="98" t="n">
         <v>0.09</v>
       </c>
-      <c r="D67" s="15" t="inlineStr">
+      <c r="D67" s="16" t="inlineStr">
         <is>
           <t>🔶 target unlevered yield</t>
         </is>
@@ -6714,7 +6949,7 @@
         <f>C57*C59</f>
         <v/>
       </c>
-      <c r="D70" s="15" t="inlineStr">
+      <c r="D70" s="16" t="inlineStr">
         <is>
           <t>price × LTV</t>
         </is>
@@ -6772,7 +7007,7 @@
         <f>C57*(1+C58)-C70</f>
         <v/>
       </c>
-      <c r="D74" s="15" t="inlineStr">
+      <c r="D74" s="16" t="inlineStr">
         <is>
           <t>price×(1+closing) − loan</t>
         </is>
@@ -6837,11 +7072,11 @@
           <t>Land value ($/SF)</t>
         </is>
       </c>
-      <c r="C79" s="35">
+      <c r="C79" s="36">
         <f>'Assumptions'!C61</f>
         <v/>
       </c>
-      <c r="D79" s="15" t="inlineStr">
+      <c r="D79" s="16" t="inlineStr">
         <is>
           <t>🟢 Assumptions</t>
         </is>
@@ -6866,7 +7101,7 @@
         <f>C36*C79</f>
         <v/>
       </c>
-      <c r="D80" s="15" t="inlineStr">
+      <c r="D80" s="16" t="inlineStr">
         <is>
           <t>both blue inputs above</t>
         </is>
@@ -6906,7 +7141,7 @@
           <t>Year</t>
         </is>
       </c>
-      <c r="C83" s="22" t="inlineStr">
+      <c r="C83" s="23" t="inlineStr">
         <is>
           <t>0 / Acq</t>
         </is>
@@ -6943,7 +7178,7 @@
       </c>
     </row>
     <row r="84" ht="15" customHeight="1">
-      <c r="B84" s="15" t="inlineStr">
+      <c r="B84" s="16" t="inlineStr">
         <is>
           <t>Year ending</t>
         </is>
@@ -9312,17 +9547,17 @@
         </is>
       </c>
       <c r="F17" s="9" t="n"/>
-      <c r="G17" s="22" t="inlineStr">
+      <c r="G17" s="23" t="inlineStr">
         <is>
           <t>SF</t>
         </is>
       </c>
-      <c r="H17" s="22" t="inlineStr">
+      <c r="H17" s="23" t="inlineStr">
         <is>
           <t>$/SF NNN</t>
         </is>
       </c>
-      <c r="I17" s="22" t="inlineStr">
+      <c r="I17" s="23" t="inlineStr">
         <is>
           <t>Annual rent</t>
         </is>
@@ -9403,14 +9638,14 @@
       <c r="M19" s="9" t="n"/>
     </row>
     <row r="20" ht="27" customHeight="1">
-      <c r="B20" s="27" t="inlineStr">
+      <c r="B20" s="28" t="inlineStr">
         <is>
           <t>TOTAL / WTD AVG</t>
         </is>
       </c>
       <c r="C20" s="8" t="n"/>
       <c r="D20" s="9" t="n"/>
-      <c r="E20" s="29" t="inlineStr"/>
+      <c r="E20" s="30" t="inlineStr"/>
       <c r="F20" s="9" t="n"/>
       <c r="G20" s="85">
         <f>SUM(G18:G19)</f>
@@ -9420,13 +9655,13 @@
         <f>IFERROR(SUM(I18:I19)/SUM(G18:G19),0)</f>
         <v/>
       </c>
-      <c r="I20" s="30">
+      <c r="I20" s="31">
         <f>SUM(I18:I19)</f>
         <v/>
       </c>
       <c r="J20" s="8" t="n"/>
       <c r="K20" s="9" t="n"/>
-      <c r="L20" s="27" t="inlineStr">
+      <c r="L20" s="28" t="inlineStr">
         <is>
           <t>100% occ · credit tenants · sale-leaseback</t>
         </is>
@@ -9479,7 +9714,7 @@
       <c r="C24" s="92" t="n">
         <v>36822</v>
       </c>
-      <c r="D24" s="15" t="inlineStr">
+      <c r="D24" s="16" t="inlineStr">
         <is>
           <t>✅ BCPA (36,822 SF)</t>
         </is>
@@ -9504,7 +9739,7 @@
         <f>'Assumptions'!C76</f>
         <v/>
       </c>
-      <c r="D25" s="15" t="inlineStr">
+      <c r="D25" s="16" t="inlineStr">
         <is>
           <t>🟢 Assumptions</t>
         </is>
@@ -9525,11 +9760,11 @@
           <t>In-place occupancy</t>
         </is>
       </c>
-      <c r="C26" s="33">
+      <c r="C26" s="34">
         <f>'Assumptions'!C83</f>
         <v/>
       </c>
-      <c r="D26" s="15" t="inlineStr">
+      <c r="D26" s="16" t="inlineStr">
         <is>
           <t>🟢 Assumptions</t>
         </is>
@@ -9550,11 +9785,11 @@
           <t>Stabilized occupancy</t>
         </is>
       </c>
-      <c r="C27" s="33">
+      <c r="C27" s="34">
         <f>'Assumptions'!C84</f>
         <v/>
       </c>
-      <c r="D27" s="15" t="inlineStr">
+      <c r="D27" s="16" t="inlineStr">
         <is>
           <t>🟢 Assumptions</t>
         </is>
@@ -9575,11 +9810,11 @@
           <t>Blended NNN rent ($/SF) — leaseback + pad</t>
         </is>
       </c>
-      <c r="C28" s="35">
+      <c r="C28" s="36">
         <f>('Assumptions'!C79*'Assumptions'!C78+'Assumptions'!C81*'Assumptions'!C80)/C24</f>
         <v/>
       </c>
-      <c r="D28" s="15" t="inlineStr">
+      <c r="D28" s="16" t="inlineStr">
         <is>
           <t>🟢 computed from Publix leaseback + Starbucks pad (Assumptions)</t>
         </is>
@@ -9603,7 +9838,7 @@
       <c r="C29" s="98" t="n">
         <v>0.02</v>
       </c>
-      <c r="D29" s="15" t="inlineStr">
+      <c r="D29" s="16" t="inlineStr">
         <is>
           <t>🔶</t>
         </is>
@@ -9627,7 +9862,7 @@
       <c r="C30" s="98" t="n">
         <v>0.01</v>
       </c>
-      <c r="D30" s="15" t="inlineStr">
+      <c r="D30" s="16" t="inlineStr">
         <is>
           <t>🔶</t>
         </is>
@@ -9651,7 +9886,7 @@
       <c r="C31" s="97" t="n">
         <v>0.0191</v>
       </c>
-      <c r="D31" s="15" t="inlineStr">
+      <c r="D31" s="16" t="inlineStr">
         <is>
           <t>✅ 2025</t>
         </is>
@@ -9690,11 +9925,11 @@
           <t>Insurance ($/yr)</t>
         </is>
       </c>
-      <c r="C33" s="19">
+      <c r="C33" s="20">
         <f>'Assumptions'!C85</f>
         <v/>
       </c>
-      <c r="D33" s="15" t="inlineStr">
+      <c r="D33" s="16" t="inlineStr">
         <is>
           <t>🟢 Assumptions</t>
         </is>
@@ -9715,11 +9950,11 @@
           <t>CAM ($/yr, recoverable)</t>
         </is>
       </c>
-      <c r="C34" s="19">
+      <c r="C34" s="20">
         <f>'Assumptions'!C86</f>
         <v/>
       </c>
-      <c r="D34" s="15" t="inlineStr">
+      <c r="D34" s="16" t="inlineStr">
         <is>
           <t>🟢 Assumptions</t>
         </is>
@@ -9740,11 +9975,11 @@
           <t>Repairs &amp; maintenance ($/yr)</t>
         </is>
       </c>
-      <c r="C35" s="19">
+      <c r="C35" s="20">
         <f>'Assumptions'!C87</f>
         <v/>
       </c>
-      <c r="D35" s="15" t="inlineStr">
+      <c r="D35" s="16" t="inlineStr">
         <is>
           <t>🟢 Assumptions</t>
         </is>
@@ -9765,11 +10000,11 @@
           <t>Management fee (% EGR)</t>
         </is>
       </c>
-      <c r="C36" s="33">
+      <c r="C36" s="34">
         <f>'Assumptions'!C88</f>
         <v/>
       </c>
-      <c r="D36" s="15" t="inlineStr">
+      <c r="D36" s="16" t="inlineStr">
         <is>
           <t>🟢 Assumptions</t>
         </is>
@@ -9793,7 +10028,7 @@
       <c r="C37" s="98" t="n">
         <v>0.03</v>
       </c>
-      <c r="D37" s="15" t="inlineStr">
+      <c r="D37" s="16" t="inlineStr">
         <is>
           <t>🔶</t>
         </is>
@@ -9835,7 +10070,7 @@
       <c r="C39" s="93" t="n">
         <v>0</v>
       </c>
-      <c r="D39" s="15" t="inlineStr">
+      <c r="D39" s="16" t="inlineStr">
         <is>
           <t>🔶 on leased-up SF</t>
         </is>
@@ -9859,7 +10094,7 @@
       <c r="C40" s="93" t="n">
         <v>0</v>
       </c>
-      <c r="D40" s="15" t="inlineStr">
+      <c r="D40" s="16" t="inlineStr">
         <is>
           <t>🔶 on leased-up SF</t>
         </is>
@@ -9883,7 +10118,7 @@
       <c r="C41" s="93" t="n">
         <v>0.15</v>
       </c>
-      <c r="D41" s="15" t="inlineStr">
+      <c r="D41" s="16" t="inlineStr">
         <is>
           <t>🔶</t>
         </is>
@@ -9907,7 +10142,7 @@
       <c r="C42" s="93" t="n">
         <v>0.15</v>
       </c>
-      <c r="D42" s="15" t="inlineStr">
+      <c r="D42" s="16" t="inlineStr">
         <is>
           <t>🔶</t>
         </is>
@@ -9946,11 +10181,11 @@
           <t>Purchase price / basis</t>
         </is>
       </c>
-      <c r="C44" s="19">
+      <c r="C44" s="20">
         <f>'Assumptions'!C75</f>
         <v/>
       </c>
-      <c r="D44" s="15" t="inlineStr">
+      <c r="D44" s="16" t="inlineStr">
         <is>
           <t>🟢 Assumptions</t>
         </is>
@@ -9974,7 +10209,7 @@
       <c r="C45" s="98" t="n">
         <v>0.02</v>
       </c>
-      <c r="D45" s="15" t="inlineStr">
+      <c r="D45" s="16" t="inlineStr">
         <is>
           <t>🔶</t>
         </is>
@@ -9995,11 +10230,11 @@
           <t>Senior loan LTV</t>
         </is>
       </c>
-      <c r="C46" s="33">
+      <c r="C46" s="34">
         <f>'Assumptions'!C91</f>
         <v/>
       </c>
-      <c r="D46" s="15" t="inlineStr">
+      <c r="D46" s="16" t="inlineStr">
         <is>
           <t>🟢 Assumptions</t>
         </is>
@@ -10020,11 +10255,11 @@
           <t>Senior loan rate</t>
         </is>
       </c>
-      <c r="C47" s="36">
+      <c r="C47" s="37">
         <f>'Assumptions'!C92</f>
         <v/>
       </c>
-      <c r="D47" s="15" t="inlineStr">
+      <c r="D47" s="16" t="inlineStr">
         <is>
           <t>🟢 Assumptions</t>
         </is>
@@ -10048,7 +10283,7 @@
       <c r="C48" s="99" t="n">
         <v>30</v>
       </c>
-      <c r="D48" s="15" t="inlineStr">
+      <c r="D48" s="16" t="inlineStr">
         <is>
           <t>🔶</t>
         </is>
@@ -10087,11 +10322,11 @@
           <t>Going-in cap</t>
         </is>
       </c>
-      <c r="C50" s="36">
+      <c r="C50" s="37">
         <f>'Assumptions'!C89</f>
         <v/>
       </c>
-      <c r="D50" s="15" t="inlineStr">
+      <c r="D50" s="16" t="inlineStr">
         <is>
           <t>🟢 Assumptions</t>
         </is>
@@ -10112,11 +10347,11 @@
           <t>Exit / reversion cap</t>
         </is>
       </c>
-      <c r="C51" s="36">
+      <c r="C51" s="37">
         <f>'Assumptions'!C90</f>
         <v/>
       </c>
-      <c r="D51" s="15" t="inlineStr">
+      <c r="D51" s="16" t="inlineStr">
         <is>
           <t>🟢 Assumptions</t>
         </is>
@@ -10140,7 +10375,7 @@
       <c r="C52" s="98" t="n">
         <v>0.02</v>
       </c>
-      <c r="D52" s="15" t="inlineStr">
+      <c r="D52" s="16" t="inlineStr">
         <is>
           <t>🔶</t>
         </is>
@@ -10164,7 +10399,7 @@
       <c r="C53" s="99" t="n">
         <v>5</v>
       </c>
-      <c r="D53" s="15" t="inlineStr">
+      <c r="D53" s="16" t="inlineStr">
         <is>
           <t>🔶</t>
         </is>
@@ -10188,7 +10423,7 @@
       <c r="C54" s="98" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="D54" s="15" t="inlineStr">
+      <c r="D54" s="16" t="inlineStr">
         <is>
           <t>🔶</t>
         </is>
@@ -10209,11 +10444,11 @@
           <t>Land value ($/SF)</t>
         </is>
       </c>
-      <c r="C55" s="35">
+      <c r="C55" s="36">
         <f>'Assumptions'!C77</f>
         <v/>
       </c>
-      <c r="D55" s="15" t="inlineStr">
+      <c r="D55" s="16" t="inlineStr">
         <is>
           <t>🟢 Assumptions</t>
         </is>
@@ -10257,7 +10492,7 @@
         <f>C44*C46</f>
         <v/>
       </c>
-      <c r="D58" s="15" t="inlineStr">
+      <c r="D58" s="16" t="inlineStr">
         <is>
           <t>price × LTV</t>
         </is>
@@ -10359,7 +10594,7 @@
         <f>D87/C50</f>
         <v/>
       </c>
-      <c r="D66" s="15" t="inlineStr">
+      <c r="D66" s="16" t="inlineStr">
         <is>
           <t>computed below</t>
         </is>
@@ -10384,7 +10619,7 @@
         <f>C25*C55</f>
         <v/>
       </c>
-      <c r="D67" s="15" t="inlineStr">
+      <c r="D67" s="16" t="inlineStr">
         <is>
           <t>land SF × land $/SF (both blue inputs above)</t>
         </is>
@@ -10424,7 +10659,7 @@
           <t>Year</t>
         </is>
       </c>
-      <c r="C70" s="22" t="inlineStr">
+      <c r="C70" s="23" t="inlineStr">
         <is>
           <t>0 / Acq</t>
         </is>
@@ -10461,7 +10696,7 @@
       </c>
     </row>
     <row r="71" ht="15" customHeight="1">
-      <c r="B71" s="15" t="inlineStr">
+      <c r="B71" s="16" t="inlineStr">
         <is>
           <t>Year ending</t>
         </is>
@@ -11972,7 +12207,7 @@
       <c r="C119" s="102" t="n">
         <v>1.2</v>
       </c>
-      <c r="D119" s="15" t="inlineStr">
+      <c r="D119" s="16" t="inlineStr">
         <is>
           <t>🔵 your coverage target</t>
         </is>
@@ -11996,7 +12231,7 @@
       <c r="C120" s="97" t="n">
         <v>0.05</v>
       </c>
-      <c r="D120" s="15" t="inlineStr">
+      <c r="D120" s="16" t="inlineStr">
         <is>
           <t>🔵 your yield target</t>
         </is>
@@ -12043,7 +12278,7 @@
         <f>(((C119*C60+C122*C36+C35)/C121)-'Assumptions'!C81*'Assumptions'!C80)/'Assumptions'!C79</f>
         <v/>
       </c>
-      <c r="D123" s="15" t="inlineStr">
+      <c r="D123" s="16" t="inlineStr">
         <is>
           <t>$/SF NNN — set Publix leaseback rent (Assumptions) to this</t>
         </is>
@@ -12068,7 +12303,7 @@
         <f>(((C120*C44+C122*C36+C35)/C121)-'Assumptions'!C81*'Assumptions'!C80)/'Assumptions'!C79</f>
         <v/>
       </c>
-      <c r="D124" s="15" t="inlineStr">
+      <c r="D124" s="16" t="inlineStr">
         <is>
           <t>$/SF NNN — set Publix leaseback rent (Assumptions) to this</t>
         </is>
@@ -12108,13 +12343,13 @@
           <t>Case</t>
         </is>
       </c>
-      <c r="E127" s="22" t="inlineStr">
+      <c r="E127" s="23" t="inlineStr">
         <is>
           <t>Leaseback</t>
         </is>
       </c>
       <c r="F127" s="9" t="n"/>
-      <c r="G127" s="22" t="inlineStr">
+      <c r="G127" s="23" t="inlineStr">
         <is>
           <t>Dark (Publix out)</t>
         </is>
@@ -12136,7 +12371,7 @@
           <t>Year-1 NOI</t>
         </is>
       </c>
-      <c r="E128" s="19">
+      <c r="E128" s="20">
         <f>C109</f>
         <v/>
       </c>
@@ -12146,7 +12381,7 @@
         <v/>
       </c>
       <c r="H128" s="9" t="n"/>
-      <c r="I128" s="15" t="inlineStr">
+      <c r="I128" s="16" t="inlineStr">
         <is>
           <t>dark = Starbucks pad only; you carry Publix's taxes &amp; insurance</t>
         </is>
@@ -12167,7 +12402,7 @@
         <v/>
       </c>
       <c r="F129" s="9" t="n"/>
-      <c r="G129" s="15" t="inlineStr">
+      <c r="G129" s="16" t="inlineStr">
         <is>
           <t>per year of vacancy</t>
         </is>
@@ -12185,7 +12420,7 @@
           <t>Entitlement term (yrs)</t>
         </is>
       </c>
-      <c r="E130" s="24">
+      <c r="E130" s="25">
         <f>'Assumptions'!C82</f>
         <v/>
       </c>
@@ -12202,7 +12437,7 @@
         <v/>
       </c>
       <c r="F131" s="9" t="n"/>
-      <c r="G131" s="37" t="inlineStr">
+      <c r="G131" s="15" t="inlineStr">
         <is>
           <t>cumulative over the entitlement term — funded by equity</t>
         </is>
@@ -12215,12 +12450,12 @@
       <c r="M131" s="9" t="n"/>
     </row>
     <row r="132" ht="27" customHeight="1">
-      <c r="B132" s="37" t="inlineStr">
+      <c r="B132" s="15" t="inlineStr">
         <is>
           <t>Deal note</t>
         </is>
       </c>
-      <c r="D132" s="37" t="inlineStr">
+      <c r="D132" s="15" t="inlineStr">
         <is>
           <t>The sale-leaseback is DEAL-CRITICAL — Publix is a fee owner, not a seller. Confirm leaseback appetite &amp; rent BEFORE hard money. If it goes dark you fund the carry above and lean entirely on land value; the covered-land exit is unchanged.</t>
         </is>
@@ -13093,17 +13328,17 @@
         </is>
       </c>
       <c r="F16" s="9" t="n"/>
-      <c r="G16" s="22" t="inlineStr">
+      <c r="G16" s="23" t="inlineStr">
         <is>
           <t>SF</t>
         </is>
       </c>
-      <c r="H16" s="22" t="inlineStr">
+      <c r="H16" s="23" t="inlineStr">
         <is>
           <t>$/SF NNN</t>
         </is>
       </c>
-      <c r="I16" s="22" t="inlineStr">
+      <c r="I16" s="23" t="inlineStr">
         <is>
           <t>Annual rent</t>
         </is>
@@ -13283,14 +13518,14 @@
       <c r="M21" s="9" t="n"/>
     </row>
     <row r="22" ht="15" customHeight="1">
-      <c r="B22" s="37" t="inlineStr">
+      <c r="B22" s="15" t="inlineStr">
         <is>
           <t>VACANT / available</t>
         </is>
       </c>
       <c r="C22" s="8" t="n"/>
       <c r="D22" s="9" t="n"/>
-      <c r="E22" s="37" t="inlineStr">
+      <c r="E22" s="15" t="inlineStr">
         <is>
           <t>Lease-up upside</t>
         </is>
@@ -13311,7 +13546,7 @@
       </c>
       <c r="J22" s="8" t="n"/>
       <c r="K22" s="9" t="n"/>
-      <c r="L22" s="37" t="inlineStr">
+      <c r="L22" s="15" t="inlineStr">
         <is>
           <t>value-add</t>
         </is>
@@ -13319,14 +13554,14 @@
       <c r="M22" s="9" t="n"/>
     </row>
     <row r="23" ht="15" customHeight="1">
-      <c r="B23" s="27" t="inlineStr">
+      <c r="B23" s="28" t="inlineStr">
         <is>
           <t>TOTAL / WTD AVG</t>
         </is>
       </c>
       <c r="C23" s="8" t="n"/>
       <c r="D23" s="9" t="n"/>
-      <c r="E23" s="29" t="inlineStr"/>
+      <c r="E23" s="30" t="inlineStr"/>
       <c r="F23" s="9" t="n"/>
       <c r="G23" s="85">
         <f>SUM(G17:G22)</f>
@@ -13336,13 +13571,13 @@
         <f>IFERROR(SUM(I17:I21)/SUM(G17:G21),0)</f>
         <v/>
       </c>
-      <c r="I23" s="30">
+      <c r="I23" s="31">
         <f>SUM(I17:I21)</f>
         <v/>
       </c>
       <c r="J23" s="8" t="n"/>
       <c r="K23" s="9" t="n"/>
-      <c r="L23" s="27" t="inlineStr">
+      <c r="L23" s="28" t="inlineStr">
         <is>
           <t>Daoud's = anchor; ~20% vacant</t>
         </is>
@@ -13395,7 +13630,7 @@
       <c r="C27" s="92" t="n">
         <v>25105</v>
       </c>
-      <c r="D27" s="15" t="inlineStr">
+      <c r="D27" s="16" t="inlineStr">
         <is>
           <t>⚠️ LoopNet (25,105 SF)</t>
         </is>
@@ -13420,7 +13655,7 @@
         <f>'Assumptions'!C96</f>
         <v/>
       </c>
-      <c r="D28" s="15" t="inlineStr">
+      <c r="D28" s="16" t="inlineStr">
         <is>
           <t>🟢 Assumptions</t>
         </is>
@@ -13441,11 +13676,11 @@
           <t>In-place occupancy</t>
         </is>
       </c>
-      <c r="C29" s="33">
+      <c r="C29" s="34">
         <f>'Assumptions'!C99</f>
         <v/>
       </c>
-      <c r="D29" s="15" t="inlineStr">
+      <c r="D29" s="16" t="inlineStr">
         <is>
           <t>🟢 Assumptions</t>
         </is>
@@ -13466,11 +13701,11 @@
           <t>Stabilized occupancy</t>
         </is>
       </c>
-      <c r="C30" s="33">
+      <c r="C30" s="34">
         <f>'Assumptions'!C100</f>
         <v/>
       </c>
-      <c r="D30" s="15" t="inlineStr">
+      <c r="D30" s="16" t="inlineStr">
         <is>
           <t>🟢 Assumptions</t>
         </is>
@@ -13491,11 +13726,11 @@
           <t>Market rent ($/SF NNN)</t>
         </is>
       </c>
-      <c r="C31" s="35">
+      <c r="C31" s="36">
         <f>'Assumptions'!C98</f>
         <v/>
       </c>
-      <c r="D31" s="15" t="inlineStr">
+      <c r="D31" s="16" t="inlineStr">
         <is>
           <t>🟢 Assumptions</t>
         </is>
@@ -13519,7 +13754,7 @@
       <c r="C32" s="98" t="n">
         <v>0.03</v>
       </c>
-      <c r="D32" s="15" t="inlineStr">
+      <c r="D32" s="16" t="inlineStr">
         <is>
           <t>🔶</t>
         </is>
@@ -13543,7 +13778,7 @@
       <c r="C33" s="98" t="n">
         <v>0.03</v>
       </c>
-      <c r="D33" s="15" t="inlineStr">
+      <c r="D33" s="16" t="inlineStr">
         <is>
           <t>🔶</t>
         </is>
@@ -13567,7 +13802,7 @@
       <c r="C34" s="97" t="n">
         <v>0.0191</v>
       </c>
-      <c r="D34" s="15" t="inlineStr">
+      <c r="D34" s="16" t="inlineStr">
         <is>
           <t>✅ 2025 area millage</t>
         </is>
@@ -13606,11 +13841,11 @@
           <t>Insurance ($/yr)</t>
         </is>
       </c>
-      <c r="C36" s="19">
+      <c r="C36" s="20">
         <f>'Assumptions'!C101</f>
         <v/>
       </c>
-      <c r="D36" s="15" t="inlineStr">
+      <c r="D36" s="16" t="inlineStr">
         <is>
           <t>🟢 Assumptions</t>
         </is>
@@ -13631,11 +13866,11 @@
           <t>CAM ($/yr, recoverable)</t>
         </is>
       </c>
-      <c r="C37" s="19">
+      <c r="C37" s="20">
         <f>'Assumptions'!C102</f>
         <v/>
       </c>
-      <c r="D37" s="15" t="inlineStr">
+      <c r="D37" s="16" t="inlineStr">
         <is>
           <t>🟢 Assumptions</t>
         </is>
@@ -13656,11 +13891,11 @@
           <t>Repairs &amp; maintenance ($/yr)</t>
         </is>
       </c>
-      <c r="C38" s="19">
+      <c r="C38" s="20">
         <f>'Assumptions'!C103</f>
         <v/>
       </c>
-      <c r="D38" s="15" t="inlineStr">
+      <c r="D38" s="16" t="inlineStr">
         <is>
           <t>🟢 Assumptions</t>
         </is>
@@ -13681,11 +13916,11 @@
           <t>Management fee (% EGR)</t>
         </is>
       </c>
-      <c r="C39" s="33">
+      <c r="C39" s="34">
         <f>'Assumptions'!C104</f>
         <v/>
       </c>
-      <c r="D39" s="15" t="inlineStr">
+      <c r="D39" s="16" t="inlineStr">
         <is>
           <t>🟢 Assumptions</t>
         </is>
@@ -13709,7 +13944,7 @@
       <c r="C40" s="98" t="n">
         <v>0.03</v>
       </c>
-      <c r="D40" s="15" t="inlineStr">
+      <c r="D40" s="16" t="inlineStr">
         <is>
           <t>🔶</t>
         </is>
@@ -13751,7 +13986,7 @@
       <c r="C42" s="93" t="n">
         <v>30</v>
       </c>
-      <c r="D42" s="15" t="inlineStr">
+      <c r="D42" s="16" t="inlineStr">
         <is>
           <t>🔶 on leased-up SF</t>
         </is>
@@ -13775,7 +14010,7 @@
       <c r="C43" s="93" t="n">
         <v>20</v>
       </c>
-      <c r="D43" s="15" t="inlineStr">
+      <c r="D43" s="16" t="inlineStr">
         <is>
           <t>🔶 on leased-up SF</t>
         </is>
@@ -13799,7 +14034,7 @@
       <c r="C44" s="93" t="n">
         <v>0.15</v>
       </c>
-      <c r="D44" s="15" t="inlineStr">
+      <c r="D44" s="16" t="inlineStr">
         <is>
           <t>🔶</t>
         </is>
@@ -13823,7 +14058,7 @@
       <c r="C45" s="93" t="n">
         <v>0.75</v>
       </c>
-      <c r="D45" s="15" t="inlineStr">
+      <c r="D45" s="16" t="inlineStr">
         <is>
           <t>🔶</t>
         </is>
@@ -13862,11 +14097,11 @@
           <t>Purchase price / basis</t>
         </is>
       </c>
-      <c r="C47" s="19">
+      <c r="C47" s="20">
         <f>'Assumptions'!C95</f>
         <v/>
       </c>
-      <c r="D47" s="15" t="inlineStr">
+      <c r="D47" s="16" t="inlineStr">
         <is>
           <t>🟢 Assumptions</t>
         </is>
@@ -13890,7 +14125,7 @@
       <c r="C48" s="98" t="n">
         <v>0.025</v>
       </c>
-      <c r="D48" s="15" t="inlineStr">
+      <c r="D48" s="16" t="inlineStr">
         <is>
           <t>🔶</t>
         </is>
@@ -13911,11 +14146,11 @@
           <t>Senior loan LTV</t>
         </is>
       </c>
-      <c r="C49" s="33">
+      <c r="C49" s="34">
         <f>'Assumptions'!C107</f>
         <v/>
       </c>
-      <c r="D49" s="15" t="inlineStr">
+      <c r="D49" s="16" t="inlineStr">
         <is>
           <t>🟢 Assumptions</t>
         </is>
@@ -13936,11 +14171,11 @@
           <t>Senior loan rate</t>
         </is>
       </c>
-      <c r="C50" s="36">
+      <c r="C50" s="37">
         <f>'Assumptions'!C108</f>
         <v/>
       </c>
-      <c r="D50" s="15" t="inlineStr">
+      <c r="D50" s="16" t="inlineStr">
         <is>
           <t>🟢 Assumptions</t>
         </is>
@@ -13964,7 +14199,7 @@
       <c r="C51" s="99" t="n">
         <v>30</v>
       </c>
-      <c r="D51" s="15" t="inlineStr">
+      <c r="D51" s="16" t="inlineStr">
         <is>
           <t>🔶</t>
         </is>
@@ -14003,11 +14238,11 @@
           <t>Going-in cap</t>
         </is>
       </c>
-      <c r="C53" s="36">
+      <c r="C53" s="37">
         <f>'Assumptions'!C105</f>
         <v/>
       </c>
-      <c r="D53" s="15" t="inlineStr">
+      <c r="D53" s="16" t="inlineStr">
         <is>
           <t>🟢 Assumptions</t>
         </is>
@@ -14028,11 +14263,11 @@
           <t>Exit / reversion cap</t>
         </is>
       </c>
-      <c r="C54" s="36">
+      <c r="C54" s="37">
         <f>'Assumptions'!C106</f>
         <v/>
       </c>
-      <c r="D54" s="15" t="inlineStr">
+      <c r="D54" s="16" t="inlineStr">
         <is>
           <t>🟢 Assumptions</t>
         </is>
@@ -14056,7 +14291,7 @@
       <c r="C55" s="98" t="n">
         <v>0.02</v>
       </c>
-      <c r="D55" s="15" t="inlineStr">
+      <c r="D55" s="16" t="inlineStr">
         <is>
           <t>🔶</t>
         </is>
@@ -14080,7 +14315,7 @@
       <c r="C56" s="99" t="n">
         <v>5</v>
       </c>
-      <c r="D56" s="15" t="inlineStr">
+      <c r="D56" s="16" t="inlineStr">
         <is>
           <t>🔶</t>
         </is>
@@ -14104,7 +14339,7 @@
       <c r="C57" s="98" t="n">
         <v>0.09</v>
       </c>
-      <c r="D57" s="15" t="inlineStr">
+      <c r="D57" s="16" t="inlineStr">
         <is>
           <t>🔶</t>
         </is>
@@ -14125,11 +14360,11 @@
           <t>Land value ($/SF)</t>
         </is>
       </c>
-      <c r="C58" s="35">
+      <c r="C58" s="36">
         <f>'Assumptions'!C97</f>
         <v/>
       </c>
-      <c r="D58" s="15" t="inlineStr">
+      <c r="D58" s="16" t="inlineStr">
         <is>
           <t>🟢 Assumptions</t>
         </is>
@@ -14173,7 +14408,7 @@
         <f>C47*C49</f>
         <v/>
       </c>
-      <c r="D61" s="15" t="inlineStr">
+      <c r="D61" s="16" t="inlineStr">
         <is>
           <t>price × LTV</t>
         </is>
@@ -14275,7 +14510,7 @@
         <f>D90/C53</f>
         <v/>
       </c>
-      <c r="D69" s="15" t="inlineStr">
+      <c r="D69" s="16" t="inlineStr">
         <is>
           <t>computed below</t>
         </is>
@@ -14300,7 +14535,7 @@
         <f>C28*C58</f>
         <v/>
       </c>
-      <c r="D70" s="15" t="inlineStr">
+      <c r="D70" s="16" t="inlineStr">
         <is>
           <t>land SF × land $/SF (both blue inputs above)</t>
         </is>
@@ -14340,7 +14575,7 @@
           <t>Year</t>
         </is>
       </c>
-      <c r="C73" s="22" t="inlineStr">
+      <c r="C73" s="23" t="inlineStr">
         <is>
           <t>0 / Acq</t>
         </is>
@@ -14377,7 +14612,7 @@
       </c>
     </row>
     <row r="74" ht="15" customHeight="1">
-      <c r="B74" s="15" t="inlineStr">
+      <c r="B74" s="16" t="inlineStr">
         <is>
           <t>Year ending</t>
         </is>
@@ -16752,7 +16987,7 @@
       <c r="C18" s="92" t="n">
         <v>168807</v>
       </c>
-      <c r="D18" s="15" t="inlineStr">
+      <c r="D18" s="16" t="inlineStr">
         <is>
           <t>⚠️ ~168,807 SF</t>
         </is>
@@ -16773,11 +17008,11 @@
           <t>In-place occupancy</t>
         </is>
       </c>
-      <c r="C19" s="33">
+      <c r="C19" s="34">
         <f>'Assumptions'!C113</f>
         <v/>
       </c>
-      <c r="D19" s="15" t="inlineStr">
+      <c r="D19" s="16" t="inlineStr">
         <is>
           <t>🟢 Assumptions</t>
         </is>
@@ -16798,11 +17033,11 @@
           <t>Stabilized occupancy</t>
         </is>
       </c>
-      <c r="C20" s="33">
+      <c r="C20" s="34">
         <f>'Assumptions'!C114</f>
         <v/>
       </c>
-      <c r="D20" s="15" t="inlineStr">
+      <c r="D20" s="16" t="inlineStr">
         <is>
           <t>🟢 Assumptions</t>
         </is>
@@ -16823,11 +17058,11 @@
           <t>Market rent ($/SF Modified Gross)</t>
         </is>
       </c>
-      <c r="C21" s="35">
+      <c r="C21" s="36">
         <f>'Assumptions'!C112</f>
         <v/>
       </c>
-      <c r="D21" s="15" t="inlineStr">
+      <c r="D21" s="16" t="inlineStr">
         <is>
           <t>🟢 Assumptions</t>
         </is>
@@ -16851,7 +17086,7 @@
       <c r="C22" s="98" t="n">
         <v>0.03</v>
       </c>
-      <c r="D22" s="15" t="inlineStr">
+      <c r="D22" s="16" t="inlineStr">
         <is>
           <t>🔶</t>
         </is>
@@ -16875,7 +17110,7 @@
       <c r="C23" s="98" t="n">
         <v>0.03</v>
       </c>
-      <c r="D23" s="15" t="inlineStr">
+      <c r="D23" s="16" t="inlineStr">
         <is>
           <t>🔶</t>
         </is>
@@ -16899,7 +17134,7 @@
       <c r="C24" s="97" t="n">
         <v>0.0191</v>
       </c>
-      <c r="D24" s="15" t="inlineStr">
+      <c r="D24" s="16" t="inlineStr">
         <is>
           <t>✅ area millage</t>
         </is>
@@ -16920,11 +17155,11 @@
           <t>Office opex ex-taxes ($/SF, landlord)</t>
         </is>
       </c>
-      <c r="C25" s="35">
+      <c r="C25" s="36">
         <f>'Assumptions'!C115</f>
         <v/>
       </c>
-      <c r="D25" s="15" t="inlineStr">
+      <c r="D25" s="16" t="inlineStr">
         <is>
           <t>🟢 Assumptions</t>
         </is>
@@ -16945,11 +17180,11 @@
           <t>Management fee (% EGR)</t>
         </is>
       </c>
-      <c r="C26" s="33">
+      <c r="C26" s="34">
         <f>'Assumptions'!C116</f>
         <v/>
       </c>
-      <c r="D26" s="15" t="inlineStr">
+      <c r="D26" s="16" t="inlineStr">
         <is>
           <t>🟢 Assumptions</t>
         </is>
@@ -16973,7 +17208,7 @@
       <c r="C27" s="98" t="n">
         <v>0.03</v>
       </c>
-      <c r="D27" s="15" t="inlineStr">
+      <c r="D27" s="16" t="inlineStr">
         <is>
           <t>🔶</t>
         </is>
@@ -16997,7 +17232,7 @@
       <c r="C28" s="93" t="n">
         <v>0.2</v>
       </c>
-      <c r="D28" s="15" t="inlineStr">
+      <c r="D28" s="16" t="inlineStr">
         <is>
           <t>🔶</t>
         </is>
@@ -17018,11 +17253,11 @@
           <t>Acquisition basis (income value)</t>
         </is>
       </c>
-      <c r="C29" s="19">
+      <c r="C29" s="20">
         <f>'Assumptions'!C111</f>
         <v/>
       </c>
-      <c r="D29" s="15" t="inlineStr">
+      <c r="D29" s="16" t="inlineStr">
         <is>
           <t>🟢 Assumptions</t>
         </is>
@@ -17046,7 +17281,7 @@
       <c r="C30" s="98" t="n">
         <v>0.02</v>
       </c>
-      <c r="D30" s="15" t="inlineStr">
+      <c r="D30" s="16" t="inlineStr">
         <is>
           <t>🔶</t>
         </is>
@@ -17067,11 +17302,11 @@
           <t>Senior loan LTV</t>
         </is>
       </c>
-      <c r="C31" s="33">
+      <c r="C31" s="34">
         <f>'Assumptions'!C119</f>
         <v/>
       </c>
-      <c r="D31" s="15" t="inlineStr">
+      <c r="D31" s="16" t="inlineStr">
         <is>
           <t>🟢 Assumptions</t>
         </is>
@@ -17092,11 +17327,11 @@
           <t>Senior loan rate</t>
         </is>
       </c>
-      <c r="C32" s="36">
+      <c r="C32" s="37">
         <f>'Assumptions'!C120</f>
         <v/>
       </c>
-      <c r="D32" s="15" t="inlineStr">
+      <c r="D32" s="16" t="inlineStr">
         <is>
           <t>🟢 Assumptions</t>
         </is>
@@ -17120,7 +17355,7 @@
       <c r="C33" s="99" t="n">
         <v>30</v>
       </c>
-      <c r="D33" s="15" t="inlineStr">
+      <c r="D33" s="16" t="inlineStr">
         <is>
           <t>🔶</t>
         </is>
@@ -17141,11 +17376,11 @@
           <t>Going-in cap</t>
         </is>
       </c>
-      <c r="C34" s="36">
+      <c r="C34" s="37">
         <f>'Assumptions'!C117</f>
         <v/>
       </c>
-      <c r="D34" s="15" t="inlineStr">
+      <c r="D34" s="16" t="inlineStr">
         <is>
           <t>🟢 Assumptions</t>
         </is>
@@ -17166,11 +17401,11 @@
           <t>Exit cap</t>
         </is>
       </c>
-      <c r="C35" s="36">
+      <c r="C35" s="37">
         <f>'Assumptions'!C118</f>
         <v/>
       </c>
-      <c r="D35" s="15" t="inlineStr">
+      <c r="D35" s="16" t="inlineStr">
         <is>
           <t>🟢 Assumptions</t>
         </is>
@@ -17194,7 +17429,7 @@
       <c r="C36" s="98" t="n">
         <v>0.02</v>
       </c>
-      <c r="D36" s="15" t="inlineStr">
+      <c r="D36" s="16" t="inlineStr">
         <is>
           <t>🔶</t>
         </is>
@@ -17218,7 +17453,7 @@
       <c r="C37" s="99" t="n">
         <v>5</v>
       </c>
-      <c r="D37" s="15" t="inlineStr">
+      <c r="D37" s="16" t="inlineStr">
         <is>
           <t>🔶</t>
         </is>
@@ -17242,7 +17477,7 @@
       <c r="C38" s="98" t="n">
         <v>0.1</v>
       </c>
-      <c r="D38" s="15" t="inlineStr">
+      <c r="D38" s="16" t="inlineStr">
         <is>
           <t>🔶</t>
         </is>
@@ -17266,7 +17501,7 @@
       <c r="C39" s="93" t="n">
         <v>300</v>
       </c>
-      <c r="D39" s="15" t="inlineStr">
+      <c r="D39" s="16" t="inlineStr">
         <is>
           <t>⚠️ historical ~$300/SF</t>
         </is>
@@ -17310,7 +17545,7 @@
         <f>C29*C31</f>
         <v/>
       </c>
-      <c r="D42" s="15" t="inlineStr">
+      <c r="D42" s="16" t="inlineStr">
         <is>
           <t>price × LTV</t>
         </is>
@@ -17405,7 +17640,7 @@
           <t>Year</t>
         </is>
       </c>
-      <c r="C50" s="22" t="inlineStr">
+      <c r="C50" s="23" t="inlineStr">
         <is>
           <t>0 / Acq</t>
         </is>
@@ -17442,7 +17677,7 @@
       </c>
     </row>
     <row r="51" ht="15" customHeight="1">
-      <c r="B51" s="15" t="inlineStr">
+      <c r="B51" s="16" t="inlineStr">
         <is>
           <t>Year ending</t>
         </is>
@@ -18541,7 +18776,7 @@
       <c r="C89" s="93" t="n">
         <v>250</v>
       </c>
-      <c r="D89" s="15" t="inlineStr">
+      <c r="D89" s="16" t="inlineStr">
         <is>
           <t>🔵 closed unit comps: Ste 805 $238 · #401 $381 (2024); Grove Gate asking $367–475/SF; $250 = a bulk buy-out discount to those</t>
         </is>
@@ -18563,32 +18798,32 @@
         </is>
       </c>
       <c r="C90" s="9" t="n"/>
-      <c r="D90" s="22" t="inlineStr">
+      <c r="D90" s="23" t="inlineStr">
         <is>
           <t>SF</t>
         </is>
       </c>
-      <c r="E90" s="22" t="inlineStr">
+      <c r="E90" s="23" t="inlineStr">
         <is>
           <t>% bldg</t>
         </is>
       </c>
-      <c r="F90" s="22" t="inlineStr">
+      <c r="F90" s="23" t="inlineStr">
         <is>
           <t>Orig basis</t>
         </is>
       </c>
-      <c r="G90" s="22" t="inlineStr">
+      <c r="G90" s="23" t="inlineStr">
         <is>
           <t>Bought</t>
         </is>
       </c>
-      <c r="H90" s="22" t="inlineStr">
+      <c r="H90" s="23" t="inlineStr">
         <is>
           <t>Income value</t>
         </is>
       </c>
-      <c r="I90" s="22" t="inlineStr">
+      <c r="I90" s="23" t="inlineStr">
         <is>
           <t>Buy-out ($/SF)</t>
         </is>
@@ -18923,7 +19158,7 @@
       <c r="M98" s="9" t="n"/>
     </row>
     <row r="99" ht="16" customHeight="1">
-      <c r="B99" s="20" t="inlineStr">
+      <c r="B99" s="21" t="inlineStr">
         <is>
           <t>TOTAL BUILDING — FULL BUY-OUT</t>
         </is>
@@ -18947,15 +19182,15 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H99" s="21">
+      <c r="H99" s="22">
         <f>SUM(H91:H98)</f>
         <v/>
       </c>
-      <c r="I99" s="21">
+      <c r="I99" s="22">
         <f>SUM(I91:I98)</f>
         <v/>
       </c>
-      <c r="J99" s="20" t="inlineStr">
+      <c r="J99" s="21" t="inlineStr">
         <is>
           <t>cost to control the whole building</t>
         </is>
@@ -18976,16 +19211,16 @@
       </c>
     </row>
     <row r="101" ht="29" customHeight="1">
-      <c r="B101" s="20" t="inlineStr">
+      <c r="B101" s="21" t="inlineStr">
         <is>
           <t>FRAGMENTATION PREMIUM (buy-out − income value)</t>
         </is>
       </c>
-      <c r="C101" s="21">
+      <c r="C101" s="22">
         <f>I99-H99</f>
         <v/>
       </c>
-      <c r="D101" s="37" t="inlineStr">
+      <c r="D101" s="15" t="inlineStr">
         <is>
           <t>the office trades higher as fragmented condos than as one income asset — you overpay ~2× income value to re-assemble it</t>
         </is>
@@ -19761,7 +19996,7 @@
       <c r="C18" s="92" t="n">
         <v>104108</v>
       </c>
-      <c r="D18" s="15" t="inlineStr">
+      <c r="D18" s="16" t="inlineStr">
         <is>
           <t>⚠️ 2.39 ac</t>
         </is>
@@ -19785,7 +20020,7 @@
       <c r="C19" s="92" t="n">
         <v>84495</v>
       </c>
-      <c r="D19" s="15" t="inlineStr">
+      <c r="D19" s="16" t="inlineStr">
         <is>
           <t>⚠️ 1967 bldg</t>
         </is>
@@ -19809,7 +20044,7 @@
       <c r="C20" s="92" t="n">
         <v>259</v>
       </c>
-      <c r="D20" s="15" t="inlineStr">
+      <c r="D20" s="16" t="inlineStr">
         <is>
           <t>⚠️ approved 259</t>
         </is>
@@ -19833,7 +20068,7 @@
       <c r="C21" s="47" t="n">
         <v>6685580</v>
       </c>
-      <c r="D21" s="15" t="inlineStr">
+      <c r="D21" s="16" t="inlineStr">
         <is>
           <t>⚠️ reported</t>
         </is>
@@ -19854,11 +20089,11 @@
           <t>Interim office occupancy</t>
         </is>
       </c>
-      <c r="C22" s="33">
+      <c r="C22" s="34">
         <f>'Assumptions'!C124</f>
         <v/>
       </c>
-      <c r="D22" s="15" t="inlineStr">
+      <c r="D22" s="16" t="inlineStr">
         <is>
           <t>🟢 Assumptions</t>
         </is>
@@ -19879,11 +20114,11 @@
           <t>Interim office rent ($/SF MG)</t>
         </is>
       </c>
-      <c r="C23" s="35">
+      <c r="C23" s="36">
         <f>'Assumptions'!C125</f>
         <v/>
       </c>
-      <c r="D23" s="15" t="inlineStr">
+      <c r="D23" s="16" t="inlineStr">
         <is>
           <t>🟢 Assumptions</t>
         </is>
@@ -19904,11 +20139,11 @@
           <t>Interim office opex ($/SF)</t>
         </is>
       </c>
-      <c r="C24" s="35">
+      <c r="C24" s="36">
         <f>'Assumptions'!C126</f>
         <v/>
       </c>
-      <c r="D24" s="15" t="inlineStr">
+      <c r="D24" s="16" t="inlineStr">
         <is>
           <t>🟢 Assumptions</t>
         </is>
@@ -19929,11 +20164,11 @@
           <t>Management fee (% EGR)</t>
         </is>
       </c>
-      <c r="C25" s="33">
+      <c r="C25" s="34">
         <f>'Assumptions'!C127</f>
         <v/>
       </c>
-      <c r="D25" s="15" t="inlineStr">
+      <c r="D25" s="16" t="inlineStr">
         <is>
           <t>🟢 Assumptions</t>
         </is>
@@ -19957,7 +20192,7 @@
       <c r="C26" s="97" t="n">
         <v>0.0191</v>
       </c>
-      <c r="D26" s="15" t="inlineStr">
+      <c r="D26" s="16" t="inlineStr">
         <is>
           <t>✅ area</t>
         </is>
@@ -19978,11 +20213,11 @@
           <t>Acquisition basis (entitled land)</t>
         </is>
       </c>
-      <c r="C27" s="19">
+      <c r="C27" s="20">
         <f>'Assumptions'!C123</f>
         <v/>
       </c>
-      <c r="D27" s="15" t="inlineStr">
+      <c r="D27" s="16" t="inlineStr">
         <is>
           <t>🟢 Assumptions</t>
         </is>
@@ -20006,7 +20241,7 @@
       <c r="C28" s="98" t="n">
         <v>0.02</v>
       </c>
-      <c r="D28" s="15" t="inlineStr">
+      <c r="D28" s="16" t="inlineStr">
         <is>
           <t>🔶</t>
         </is>
@@ -20030,7 +20265,7 @@
       <c r="C29" s="98" t="n">
         <v>0.04</v>
       </c>
-      <c r="D29" s="15" t="inlineStr">
+      <c r="D29" s="16" t="inlineStr">
         <is>
           <t>🔶</t>
         </is>
@@ -20054,7 +20289,7 @@
       <c r="C30" s="99" t="n">
         <v>5</v>
       </c>
-      <c r="D30" s="15" t="inlineStr">
+      <c r="D30" s="16" t="inlineStr">
         <is>
           <t>🔶 to redevelopment</t>
         </is>
@@ -20075,11 +20310,11 @@
           <t>Land loan LTV (IO)</t>
         </is>
       </c>
-      <c r="C31" s="33">
+      <c r="C31" s="34">
         <f>'Assumptions'!C128</f>
         <v/>
       </c>
-      <c r="D31" s="15" t="inlineStr">
+      <c r="D31" s="16" t="inlineStr">
         <is>
           <t>🟢 Assumptions</t>
         </is>
@@ -20100,11 +20335,11 @@
           <t>Land loan rate (IO)</t>
         </is>
       </c>
-      <c r="C32" s="36">
+      <c r="C32" s="37">
         <f>'Assumptions'!C129</f>
         <v/>
       </c>
-      <c r="D32" s="15" t="inlineStr">
+      <c r="D32" s="16" t="inlineStr">
         <is>
           <t>🟢 Assumptions</t>
         </is>
@@ -20128,7 +20363,7 @@
       <c r="C33" s="98" t="n">
         <v>0.02</v>
       </c>
-      <c r="D33" s="15" t="inlineStr">
+      <c r="D33" s="16" t="inlineStr">
         <is>
           <t>🔶</t>
         </is>
@@ -20152,7 +20387,7 @@
       <c r="C34" s="98" t="n">
         <v>0.1</v>
       </c>
-      <c r="D34" s="15" t="inlineStr">
+      <c r="D34" s="16" t="inlineStr">
         <is>
           <t>🔶</t>
         </is>
@@ -20176,7 +20411,7 @@
       <c r="C35" s="98" t="n">
         <v>0.03</v>
       </c>
-      <c r="D35" s="15" t="inlineStr">
+      <c r="D35" s="16" t="inlineStr">
         <is>
           <t>🔶</t>
         </is>
@@ -20261,7 +20496,7 @@
         <f>C18*'Assumptions'!C47</f>
         <v/>
       </c>
-      <c r="G39" s="15" t="inlineStr">
+      <c r="G39" s="16" t="inlineStr">
         <is>
           <t>land SF × $/SF (low/base/high on Assumptions tab)</t>
         </is>
@@ -20291,7 +20526,7 @@
         <f>C20*'Assumptions'!C50</f>
         <v/>
       </c>
-      <c r="G40" s="15" t="inlineStr">
+      <c r="G40" s="16" t="inlineStr">
         <is>
           <t>units × $/unit (low/base/high on Assumptions tab)</t>
         </is>
@@ -20321,7 +20556,7 @@
         <f>C21</f>
         <v/>
       </c>
-      <c r="G41" s="15" t="inlineStr">
+      <c r="G41" s="16" t="inlineStr">
         <is>
           <t>assessed just value — conservative floor</t>
         </is>
@@ -20351,7 +20586,7 @@
         <f>C51</f>
         <v/>
       </c>
-      <c r="G42" s="15" t="inlineStr">
+      <c r="G42" s="16" t="inlineStr">
         <is>
           <t>existing office NOI ÷ 8% cap (income the land throws off)</t>
         </is>
@@ -20373,7 +20608,7 @@
         <f>C27</f>
         <v/>
       </c>
-      <c r="G43" s="15" t="inlineStr">
+      <c r="G43" s="16" t="inlineStr">
         <is>
           <t>🔶 entitled-land basis used in the hold model &amp; assemblage</t>
         </is>
@@ -20481,7 +20716,7 @@
         <f>C27*C31</f>
         <v/>
       </c>
-      <c r="D53" s="15" t="inlineStr">
+      <c r="D53" s="16" t="inlineStr">
         <is>
           <t>price × LTV</t>
         </is>
@@ -20528,7 +20763,7 @@
         <f>C50-C54</f>
         <v/>
       </c>
-      <c r="D56" s="15" t="inlineStr">
+      <c r="D56" s="16" t="inlineStr">
         <is>
           <t>covered-land carry</t>
         </is>
@@ -20568,7 +20803,7 @@
           <t>Year</t>
         </is>
       </c>
-      <c r="C59" s="22" t="inlineStr">
+      <c r="C59" s="23" t="inlineStr">
         <is>
           <t>0 / Acq</t>
         </is>
@@ -21008,7 +21243,7 @@
         <f>C20*'Assumptions'!C51</f>
         <v/>
       </c>
-      <c r="D76" s="15" t="inlineStr">
+      <c r="D76" s="16" t="inlineStr">
         <is>
           <t>units × achievable value/unit (Assumptions tab)</t>
         </is>
@@ -21033,7 +21268,7 @@
         <f>C20*'Assumptions'!C53</f>
         <v/>
       </c>
-      <c r="D77" s="15" t="inlineStr">
+      <c r="D77" s="16" t="inlineStr">
         <is>
           <t>units × GBA/unit (Assumptions tab)</t>
         </is>
@@ -21058,7 +21293,7 @@
         <f>-C77*'Assumptions'!C52</f>
         <v/>
       </c>
-      <c r="D78" s="15" t="inlineStr">
+      <c r="D78" s="16" t="inlineStr">
         <is>
           <t>$/GBA SF (AE-zone coastal, Assumptions tab)</t>
         </is>
@@ -21083,7 +21318,7 @@
         <f>-C77*'Assumptions'!C52*'Assumptions'!C54</f>
         <v/>
       </c>
-      <c r="D79" s="15" t="inlineStr">
+      <c r="D79" s="16" t="inlineStr">
         <is>
           <t>% of hard (Assumptions tab)</t>
         </is>
@@ -21108,7 +21343,7 @@
         <f>-C76*'Assumptions'!C55</f>
         <v/>
       </c>
-      <c r="D80" s="15" t="inlineStr">
+      <c r="D80" s="16" t="inlineStr">
         <is>
           <t>% of GDV (Assumptions tab)</t>
         </is>
@@ -21135,7 +21370,7 @@
       </c>
     </row>
     <row r="82" ht="39" customHeight="1">
-      <c r="B82" s="37" t="inlineStr">
+      <c r="B82" s="15" t="inlineStr">
         <is>
           <t>Conclusion</t>
         </is>
@@ -21145,7 +21380,7 @@
           <t>HOLD</t>
         </is>
       </c>
-      <c r="D82" s="37" t="inlineStr">
+      <c r="D82" s="15" t="inlineStr">
         <is>
           <t>Residual &lt; entitled-land basis at the modeled $500/SF hard cost → redevelopment does not pencil TODAY; hold as covered land. But note: mid-2026 research puts defensible AE-coastal concrete at $300–450/SF — dial the hard cost toward that on the Assumptions tab and the residual approaches break-even. The option is closer to the money than a single point implies.</t>
         </is>
@@ -21996,7 +22231,7 @@
       <c r="M43" s="3" t="n"/>
     </row>
     <row r="44" ht="15" customHeight="1">
-      <c r="B44" s="22" t="inlineStr">
+      <c r="B44" s="23" t="inlineStr">
         <is>
           <t>Flag</t>
         </is>
@@ -22090,7 +22325,7 @@
           <t>Asset</t>
         </is>
       </c>
-      <c r="D49" s="22" t="inlineStr">
+      <c r="D49" s="23" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
@@ -22235,7 +22470,7 @@
       <c r="M54" s="9" t="n"/>
     </row>
     <row r="55" ht="15" customHeight="1">
-      <c r="B55" s="37" t="inlineStr">
+      <c r="B55" s="15" t="inlineStr">
         <is>
           <t>BCPA (bcpa.net) was blocked from the build environment; ⚠️ items were sourced from web mirrors of the tax roll and must be confirmed at the county before close.</t>
         </is>
@@ -22857,7 +23092,7 @@
       <c r="M2" s="3" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1">
-      <c r="B3" s="16" t="inlineStr">
+      <c r="B3" s="17" t="inlineStr">
         <is>
           <t>Fort Lauderdale FL 33304 · Galleria hard corner · 5 contiguous assets · plat 49-42-36-12 · ~7.2 ac / 341,501 SF bldg · CONFIDENTIAL</t>
         </is>
@@ -22924,7 +23159,7 @@
         <v/>
       </c>
       <c r="E6" s="3" t="n"/>
-      <c r="F6" s="17">
+      <c r="F6" s="18">
         <f>'Assemblage'!C23</f>
         <v/>
       </c>
@@ -22939,7 +23174,7 @@
         <v/>
       </c>
       <c r="K6" s="3" t="n"/>
-      <c r="L6" s="18">
+      <c r="L6" s="19">
         <f>'Assemblage'!C21</f>
         <v/>
       </c>
@@ -22972,12 +23207,12 @@
       </c>
       <c r="C9" s="8" t="n"/>
       <c r="D9" s="9" t="n"/>
-      <c r="E9" s="19">
+      <c r="E9" s="20">
         <f>'Income Valuation'!C122</f>
         <v/>
       </c>
       <c r="F9" s="9" t="n"/>
-      <c r="G9" s="15" t="inlineStr">
+      <c r="G9" s="16" t="inlineStr">
         <is>
           <t>direct cap on consolidated in-place NOI — what the rent supports</t>
         </is>
@@ -22997,12 +23232,12 @@
       </c>
       <c r="C10" s="8" t="n"/>
       <c r="D10" s="9" t="n"/>
-      <c r="E10" s="19">
+      <c r="E10" s="20">
         <f>'Highest &amp; Best Use'!C11</f>
         <v/>
       </c>
       <c r="F10" s="9" t="n"/>
-      <c r="G10" s="15" t="inlineStr">
+      <c r="G10" s="16" t="inlineStr">
         <is>
           <t>buy each component independently</t>
         </is>
@@ -23015,19 +23250,19 @@
       <c r="M10" s="9" t="n"/>
     </row>
     <row r="11" ht="16" customHeight="1">
-      <c r="B11" s="20" t="inlineStr">
+      <c r="B11" s="21" t="inlineStr">
         <is>
           <t>③ COVERED-LAND / HBU (assembled)</t>
         </is>
       </c>
       <c r="C11" s="8" t="n"/>
       <c r="D11" s="9" t="n"/>
-      <c r="E11" s="21">
+      <c r="E11" s="22">
         <f>'Assemblage'!C29</f>
         <v/>
       </c>
       <c r="F11" s="9" t="n"/>
-      <c r="G11" s="15" t="inlineStr">
+      <c r="G11" s="16" t="inlineStr">
         <is>
           <t>sum of parts + assemblage premium — control the whole block</t>
         </is>
@@ -23047,12 +23282,12 @@
       </c>
       <c r="C12" s="8" t="n"/>
       <c r="D12" s="9" t="n"/>
-      <c r="E12" s="19">
+      <c r="E12" s="20">
         <f>'Income Valuation'!C124</f>
         <v/>
       </c>
       <c r="F12" s="9" t="n"/>
-      <c r="G12" s="15" t="inlineStr">
+      <c r="G12" s="16" t="inlineStr">
         <is>
           <t>③ − ① = what you pay for the land / Live Local option</t>
         </is>
@@ -23072,12 +23307,12 @@
       </c>
       <c r="C13" s="8" t="n"/>
       <c r="D13" s="9" t="n"/>
-      <c r="E13" s="19">
+      <c r="E13" s="20">
         <f>'Highest &amp; Best Use'!C41</f>
         <v/>
       </c>
       <c r="F13" s="9" t="n"/>
-      <c r="G13" s="15" t="inlineStr">
+      <c r="G13" s="16" t="inlineStr">
         <is>
           <t>entitled dirt once Live Local is approved</t>
         </is>
@@ -23114,37 +23349,37 @@
           <t>Component</t>
         </is>
       </c>
-      <c r="C16" s="22" t="inlineStr">
+      <c r="C16" s="23" t="inlineStr">
         <is>
           <t>Size</t>
         </is>
       </c>
-      <c r="D16" s="22" t="inlineStr">
+      <c r="D16" s="23" t="inlineStr">
         <is>
           <t>They paid</t>
         </is>
       </c>
-      <c r="E16" s="22" t="inlineStr">
+      <c r="E16" s="23" t="inlineStr">
         <is>
           <t>Yr</t>
         </is>
       </c>
-      <c r="F16" s="22" t="inlineStr">
+      <c r="F16" s="23" t="inlineStr">
         <is>
           <t>Our price</t>
         </is>
       </c>
-      <c r="G16" s="22" t="inlineStr">
+      <c r="G16" s="23" t="inlineStr">
         <is>
           <t>In-place NOI</t>
         </is>
       </c>
-      <c r="H16" s="22" t="inlineStr">
+      <c r="H16" s="23" t="inlineStr">
         <is>
           <t>Cap</t>
         </is>
       </c>
-      <c r="I16" s="22" t="inlineStr">
+      <c r="I16" s="23" t="inlineStr">
         <is>
           <t>Lev IRR</t>
         </is>
@@ -23164,36 +23399,36 @@
           <t>Shahidi Retail (Galleria Plaza)</t>
         </is>
       </c>
-      <c r="C17" s="15" t="inlineStr">
+      <c r="C17" s="16" t="inlineStr">
         <is>
           <t>26,272 SF retail</t>
         </is>
       </c>
-      <c r="D17" s="23">
+      <c r="D17" s="24">
         <f>'Assumptions'!C27</f>
         <v/>
       </c>
-      <c r="E17" s="24">
+      <c r="E17" s="25">
         <f>'Assumptions'!C28</f>
         <v/>
       </c>
-      <c r="F17" s="23">
+      <c r="F17" s="24">
         <f>'Shahidi Retail'!C57</f>
         <v/>
       </c>
-      <c r="G17" s="23">
+      <c r="G17" s="24">
         <f>'Shahidi Retail'!C122</f>
         <v/>
       </c>
-      <c r="H17" s="25">
+      <c r="H17" s="26">
         <f>G17/F17</f>
         <v/>
       </c>
-      <c r="I17" s="26">
+      <c r="I17" s="27">
         <f>'Shahidi Retail'!C120</f>
         <v/>
       </c>
-      <c r="J17" s="15" t="inlineStr">
+      <c r="J17" s="16" t="inlineStr">
         <is>
           <t>acquire fee</t>
         </is>
@@ -23208,36 +23443,36 @@
           <t>Publix + Starbucks (SLB)</t>
         </is>
       </c>
-      <c r="C18" s="15" t="inlineStr">
+      <c r="C18" s="16" t="inlineStr">
         <is>
           <t>36,822 SF grocery+pad</t>
         </is>
       </c>
-      <c r="D18" s="23">
+      <c r="D18" s="24">
         <f>'Assumptions'!C29</f>
         <v/>
       </c>
-      <c r="E18" s="24">
+      <c r="E18" s="25">
         <f>'Assumptions'!C30</f>
         <v/>
       </c>
-      <c r="F18" s="23">
+      <c r="F18" s="24">
         <f>'Publix &amp; Starbucks'!C44</f>
         <v/>
       </c>
-      <c r="G18" s="23">
+      <c r="G18" s="24">
         <f>'Publix &amp; Starbucks'!C109</f>
         <v/>
       </c>
-      <c r="H18" s="25">
+      <c r="H18" s="26">
         <f>G18/F18</f>
         <v/>
       </c>
-      <c r="I18" s="26">
+      <c r="I18" s="27">
         <f>'Publix &amp; Starbucks'!C107</f>
         <v/>
       </c>
-      <c r="J18" s="15" t="inlineStr">
+      <c r="J18" s="16" t="inlineStr">
         <is>
           <t>sale-leaseback · land exit</t>
         </is>
@@ -23252,36 +23487,36 @@
           <t>Sunrise Plaza (Kar Luen)</t>
         </is>
       </c>
-      <c r="C19" s="15" t="inlineStr">
+      <c r="C19" s="16" t="inlineStr">
         <is>
           <t>25,105 SF retail</t>
         </is>
       </c>
-      <c r="D19" s="23">
+      <c r="D19" s="24">
         <f>'Assumptions'!C31</f>
         <v/>
       </c>
-      <c r="E19" s="24">
+      <c r="E19" s="25">
         <f>'Assumptions'!C32</f>
         <v/>
       </c>
-      <c r="F19" s="23">
+      <c r="F19" s="24">
         <f>'Sunrise Plaza'!C47</f>
         <v/>
       </c>
-      <c r="G19" s="23">
+      <c r="G19" s="24">
         <f>'Sunrise Plaza'!C112</f>
         <v/>
       </c>
-      <c r="H19" s="25">
+      <c r="H19" s="26">
         <f>G19/F19</f>
         <v/>
       </c>
-      <c r="I19" s="26">
+      <c r="I19" s="27">
         <f>'Sunrise Plaza'!C110</f>
         <v/>
       </c>
-      <c r="J19" s="15" t="inlineStr">
+      <c r="J19" s="16" t="inlineStr">
         <is>
           <t>acquire fee</t>
         </is>
@@ -23296,36 +23531,36 @@
           <t>Galleria Corp Centre (buy-out)</t>
         </is>
       </c>
-      <c r="C20" s="15" t="inlineStr">
+      <c r="C20" s="16" t="inlineStr">
         <is>
           <t>168,807 SF office condo</t>
         </is>
       </c>
-      <c r="D20" s="23">
+      <c r="D20" s="24">
         <f>'Assumptions'!C33</f>
         <v/>
       </c>
-      <c r="E20" s="24">
+      <c r="E20" s="25">
         <f>'Assumptions'!C34</f>
         <v/>
       </c>
-      <c r="F20" s="23">
+      <c r="F20" s="24">
         <f>'Office Condo'!I99</f>
         <v/>
       </c>
-      <c r="G20" s="23">
+      <c r="G20" s="24">
         <f>'Office Condo'!C79</f>
         <v/>
       </c>
-      <c r="H20" s="25">
+      <c r="H20" s="26">
         <f>G20/F20</f>
         <v/>
       </c>
-      <c r="I20" s="26">
+      <c r="I20" s="27">
         <f>'Office Condo'!C77</f>
         <v/>
       </c>
-      <c r="J20" s="15" t="inlineStr">
+      <c r="J20" s="16" t="inlineStr">
         <is>
           <t>unit-market buy-out; fractured condo</t>
         </is>
@@ -23340,36 +23575,36 @@
           <t>1040 Bayview (covered land)</t>
         </is>
       </c>
-      <c r="C21" s="15" t="inlineStr">
+      <c r="C21" s="16" t="inlineStr">
         <is>
           <t>2.39 ac · 259 units</t>
         </is>
       </c>
-      <c r="D21" s="23">
+      <c r="D21" s="24">
         <f>'Assumptions'!C35</f>
         <v/>
       </c>
-      <c r="E21" s="24">
+      <c r="E21" s="25">
         <f>'Assumptions'!C36</f>
         <v/>
       </c>
-      <c r="F21" s="23">
+      <c r="F21" s="24">
         <f>'Land'!E43</f>
         <v/>
       </c>
-      <c r="G21" s="23">
+      <c r="G21" s="24">
         <f>'Land'!C50</f>
         <v/>
       </c>
-      <c r="H21" s="25">
+      <c r="H21" s="26">
         <f>G21/F21</f>
         <v/>
       </c>
-      <c r="I21" s="26">
+      <c r="I21" s="27">
         <f>'Land'!C71</f>
         <v/>
       </c>
-      <c r="J21" s="15" t="inlineStr">
+      <c r="J21" s="16" t="inlineStr">
         <is>
           <t>entitled 259 units · covered land</t>
         </is>
@@ -23379,39 +23614,39 @@
       <c r="M21" s="9" t="n"/>
     </row>
     <row r="22" ht="15" customHeight="1">
-      <c r="B22" s="27" t="inlineStr">
+      <c r="B22" s="28" t="inlineStr">
         <is>
           <t>ASSEMBLAGE — priced independently</t>
         </is>
       </c>
-      <c r="C22" s="27" t="inlineStr">
+      <c r="C22" s="28" t="inlineStr">
         <is>
           <t>5 assets</t>
         </is>
       </c>
-      <c r="D22" s="28" t="inlineStr">
+      <c r="D22" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E22" s="29" t="inlineStr"/>
-      <c r="F22" s="30">
+      <c r="E22" s="30" t="inlineStr"/>
+      <c r="F22" s="31">
         <f>'Assemblage'!C17</f>
         <v/>
       </c>
-      <c r="G22" s="30">
+      <c r="G22" s="31">
         <f>'Assemblage'!D17</f>
         <v/>
       </c>
-      <c r="H22" s="31">
+      <c r="H22" s="32">
         <f>'Assemblage'!C23</f>
         <v/>
       </c>
-      <c r="I22" s="32">
+      <c r="I22" s="33">
         <f>'Income Valuation'!C94</f>
         <v/>
       </c>
-      <c r="J22" s="27" t="inlineStr">
+      <c r="J22" s="28" t="inlineStr">
         <is>
           <t>portfolio lev IRR = consolidated cash-flow IRR</t>
         </is>
@@ -23450,7 +23685,7 @@
         </is>
       </c>
       <c r="C25" s="9" t="n"/>
-      <c r="D25" s="23">
+      <c r="D25" s="24">
         <f>'Highest &amp; Best Use'!E30</f>
         <v/>
       </c>
@@ -23463,7 +23698,7 @@
       </c>
       <c r="H25" s="8" t="n"/>
       <c r="I25" s="9" t="n"/>
-      <c r="J25" s="33">
+      <c r="J25" s="34">
         <f>'Income Valuation'!C92</f>
         <v/>
       </c>
@@ -23478,7 +23713,7 @@
         </is>
       </c>
       <c r="C26" s="9" t="n"/>
-      <c r="D26" s="23">
+      <c r="D26" s="24">
         <f>'Highest &amp; Best Use'!C36</f>
         <v/>
       </c>
@@ -23491,7 +23726,7 @@
       </c>
       <c r="H26" s="8" t="n"/>
       <c r="I26" s="9" t="n"/>
-      <c r="J26" s="34">
+      <c r="J26" s="35">
         <f>'Income Valuation'!C95</f>
         <v/>
       </c>
@@ -23506,7 +23741,7 @@
         </is>
       </c>
       <c r="C27" s="9" t="n"/>
-      <c r="D27" s="23">
+      <c r="D27" s="24">
         <f>'Highest &amp; Best Use'!C39</f>
         <v/>
       </c>
@@ -23519,7 +23754,7 @@
       </c>
       <c r="H27" s="8" t="n"/>
       <c r="I27" s="9" t="n"/>
-      <c r="J27" s="33">
+      <c r="J27" s="34">
         <f>'Income Valuation'!C98</f>
         <v/>
       </c>
@@ -23534,7 +23769,7 @@
         </is>
       </c>
       <c r="C28" s="9" t="n"/>
-      <c r="D28" s="23">
+      <c r="D28" s="24">
         <f>'Office Condo'!I99</f>
         <v/>
       </c>
@@ -23547,7 +23782,7 @@
       </c>
       <c r="H28" s="8" t="n"/>
       <c r="I28" s="9" t="n"/>
-      <c r="J28" s="34">
+      <c r="J28" s="35">
         <f>'Income Valuation'!C96</f>
         <v/>
       </c>
@@ -23562,7 +23797,7 @@
         </is>
       </c>
       <c r="C29" s="9" t="n"/>
-      <c r="D29" s="35">
+      <c r="D29" s="36">
         <f>'Assemblage'!C22</f>
         <v/>
       </c>
@@ -23575,7 +23810,7 @@
       </c>
       <c r="H29" s="8" t="n"/>
       <c r="I29" s="9" t="n"/>
-      <c r="J29" s="36">
+      <c r="J29" s="37">
         <f>'Income Valuation'!C118</f>
         <v/>
       </c>
@@ -23590,7 +23825,7 @@
         </is>
       </c>
       <c r="C30" s="9" t="n"/>
-      <c r="D30" s="23">
+      <c r="D30" s="24">
         <f>'Land'!C81</f>
         <v/>
       </c>
@@ -23603,7 +23838,7 @@
       </c>
       <c r="H30" s="8" t="n"/>
       <c r="I30" s="9" t="n"/>
-      <c r="J30" s="23">
+      <c r="J30" s="24">
         <f>'Income Valuation'!C67</f>
         <v/>
       </c>
@@ -23612,13 +23847,13 @@
       <c r="M30" s="9" t="n"/>
     </row>
     <row r="31" ht="15" customHeight="1">
-      <c r="B31" s="37" t="inlineStr">
+      <c r="B31" s="15" t="inlineStr">
         <is>
           <t>HBU verdict</t>
         </is>
       </c>
       <c r="C31" s="9" t="n"/>
-      <c r="D31" s="37" t="inlineStr">
+      <c r="D31" s="15" t="inlineStr">
         <is>
           <t>HOLD — residual negative</t>
         </is>
@@ -23632,15 +23867,15 @@
       </c>
       <c r="H31" s="8" t="n"/>
       <c r="I31" s="9" t="n"/>
-      <c r="J31" s="26">
+      <c r="J31" s="27">
         <f>'Scenarios'!G22</f>
         <v/>
       </c>
-      <c r="K31" s="26">
+      <c r="K31" s="27">
         <f>'Income Valuation'!C94</f>
         <v/>
       </c>
-      <c r="L31" s="26">
+      <c r="L31" s="27">
         <f>'Scenarios'!G24</f>
         <v/>
       </c>
@@ -23739,13 +23974,13 @@
     </row>
     <row r="38"/>
     <row r="39" ht="25" customHeight="1">
-      <c r="B39" s="15" t="inlineStr">
+      <c r="B39" s="16" t="inlineStr">
         <is>
           <t>Confidence</t>
         </is>
       </c>
       <c r="C39" s="9" t="n"/>
-      <c r="D39" s="15" t="inlineStr">
+      <c r="D39" s="16" t="inlineStr">
         <is>
           <t>✅ Shahidi &amp; Publix = BCPA-verified · ⚠️ Sunrise, Office, Land = web-sourced (BCPA/Clerk/Sunbiz egress-blocked — verify at county) · 🔶 all rents/caps/premiums modeled on the Assumptions tab</t>
         </is>
@@ -23933,7 +24168,7 @@
       </c>
       <c r="C5" s="9" t="n"/>
       <c r="D5" s="38" t="inlineStr"/>
-      <c r="E5" s="22" t="inlineStr">
+      <c r="E5" s="23" t="inlineStr">
         <is>
           <t>flag</t>
         </is>
@@ -24076,15 +24311,15 @@
         </is>
       </c>
       <c r="C11" s="42" t="n"/>
-      <c r="D11" s="19">
+      <c r="D11" s="20">
         <f>'Shahidi Retail'!C57</f>
         <v/>
       </c>
-      <c r="F11" s="23">
+      <c r="F11" s="24">
         <f>'Shahidi Retail'!C122/'Shahidi Retail'!C63</f>
         <v/>
       </c>
-      <c r="G11" s="15" t="inlineStr">
+      <c r="G11" s="16" t="inlineStr">
         <is>
           <t>← income value (cross-check)</t>
         </is>
@@ -24111,7 +24346,7 @@
       <c r="E12" s="8" t="n"/>
       <c r="F12" s="8" t="n"/>
       <c r="G12" s="9" t="n"/>
-      <c r="H12" s="22" t="inlineStr">
+      <c r="H12" s="23" t="inlineStr">
         <is>
           <t>Figure</t>
         </is>
@@ -24147,7 +24382,7 @@
         </is>
       </c>
       <c r="I13" s="9" t="n"/>
-      <c r="J13" s="15" t="inlineStr">
+      <c r="J13" s="16" t="inlineStr">
         <is>
           <t>📰 Shopping Center Business / Traded · 11/2021</t>
         </is>
@@ -24177,7 +24412,7 @@
         </is>
       </c>
       <c r="I14" s="9" t="n"/>
-      <c r="J14" s="15" t="inlineStr">
+      <c r="J14" s="16" t="inlineStr">
         <is>
           <t>📰 The Real Deal · 9/2025</t>
         </is>
@@ -24207,7 +24442,7 @@
         </is>
       </c>
       <c r="I15" s="9" t="n"/>
-      <c r="J15" s="15" t="inlineStr">
+      <c r="J15" s="16" t="inlineStr">
         <is>
           <t>📰 Traded.co · 2024</t>
         </is>
@@ -24237,7 +24472,7 @@
         </is>
       </c>
       <c r="I16" s="9" t="n"/>
-      <c r="J16" s="15" t="inlineStr">
+      <c r="J16" s="16" t="inlineStr">
         <is>
           <t>📊 Matthews Retail Report · Q3'25</t>
         </is>
@@ -24267,7 +24502,7 @@
         </is>
       </c>
       <c r="I17" s="9" t="n"/>
-      <c r="J17" s="15" t="inlineStr">
+      <c r="J17" s="16" t="inlineStr">
         <is>
           <t>📊 Native Realty / Justin Crow CRE · 2025-26</t>
         </is>
@@ -24297,7 +24532,7 @@
         </is>
       </c>
       <c r="I18" s="9" t="n"/>
-      <c r="J18" s="15" t="inlineStr">
+      <c r="J18" s="16" t="inlineStr">
         <is>
           <t>📊 Matthews · 2025</t>
         </is>
@@ -24327,7 +24562,7 @@
         </is>
       </c>
       <c r="I19" s="9" t="n"/>
-      <c r="J19" s="15" t="inlineStr">
+      <c r="J19" s="16" t="inlineStr">
         <is>
           <t>📊 Broker One / market · 2025-26</t>
         </is>
@@ -24337,7 +24572,7 @@
       <c r="M19" s="9" t="n"/>
     </row>
     <row r="20" ht="27" customHeight="1">
-      <c r="B20" s="37" t="inlineStr">
+      <c r="B20" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">  Read</t>
         </is>
@@ -24385,7 +24620,7 @@
       </c>
       <c r="C23" s="9" t="n"/>
       <c r="D23" s="38" t="inlineStr"/>
-      <c r="E23" s="22" t="inlineStr">
+      <c r="E23" s="23" t="inlineStr">
         <is>
           <t>flag</t>
         </is>
@@ -24502,15 +24737,15 @@
         </is>
       </c>
       <c r="C28" s="42" t="n"/>
-      <c r="D28" s="19">
+      <c r="D28" s="20">
         <f>'Publix &amp; Starbucks'!C44</f>
         <v/>
       </c>
-      <c r="F28" s="23">
+      <c r="F28" s="24">
         <f>'Publix &amp; Starbucks'!C110/'Publix &amp; Starbucks'!C50</f>
         <v/>
       </c>
-      <c r="G28" s="15" t="inlineStr">
+      <c r="G28" s="16" t="inlineStr">
         <is>
           <t>← income value (cross-check)</t>
         </is>
@@ -24537,7 +24772,7 @@
       <c r="E29" s="8" t="n"/>
       <c r="F29" s="8" t="n"/>
       <c r="G29" s="9" t="n"/>
-      <c r="H29" s="22" t="inlineStr">
+      <c r="H29" s="23" t="inlineStr">
         <is>
           <t>Figure</t>
         </is>
@@ -24573,7 +24808,7 @@
         </is>
       </c>
       <c r="I30" s="9" t="n"/>
-      <c r="J30" s="15" t="inlineStr">
+      <c r="J30" s="16" t="inlineStr">
         <is>
           <t>📊 Boulder Group / investmentgrade.com · 2025-26</t>
         </is>
@@ -24603,7 +24838,7 @@
         </is>
       </c>
       <c r="I31" s="9" t="n"/>
-      <c r="J31" s="15" t="inlineStr">
+      <c r="J31" s="16" t="inlineStr">
         <is>
           <t>📊 apers.app / net-lease research · 2026</t>
         </is>
@@ -24633,7 +24868,7 @@
         </is>
       </c>
       <c r="I32" s="9" t="n"/>
-      <c r="J32" s="15" t="inlineStr">
+      <c r="J32" s="16" t="inlineStr">
         <is>
           <t>📊 The Boulder Group · 2025</t>
         </is>
@@ -24663,7 +24898,7 @@
         </is>
       </c>
       <c r="I33" s="9" t="n"/>
-      <c r="J33" s="15" t="inlineStr">
+      <c r="J33" s="16" t="inlineStr">
         <is>
           <t>📊 Boulder Group / LoopNet · 2025</t>
         </is>
@@ -24673,7 +24908,7 @@
       <c r="M33" s="9" t="n"/>
     </row>
     <row r="34" ht="27" customHeight="1">
-      <c r="B34" s="37" t="inlineStr">
+      <c r="B34" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">  Read</t>
         </is>
@@ -24721,7 +24956,7 @@
       </c>
       <c r="C37" s="9" t="n"/>
       <c r="D37" s="38" t="inlineStr"/>
-      <c r="E37" s="22" t="inlineStr">
+      <c r="E37" s="23" t="inlineStr">
         <is>
           <t>flag</t>
         </is>
@@ -24838,15 +25073,15 @@
         </is>
       </c>
       <c r="C42" s="42" t="n"/>
-      <c r="D42" s="19">
+      <c r="D42" s="20">
         <f>'Sunrise Plaza'!C47</f>
         <v/>
       </c>
-      <c r="F42" s="23">
+      <c r="F42" s="24">
         <f>'Sunrise Plaza'!C113/'Sunrise Plaza'!C53</f>
         <v/>
       </c>
-      <c r="G42" s="15" t="inlineStr">
+      <c r="G42" s="16" t="inlineStr">
         <is>
           <t>← income value (cross-check)</t>
         </is>
@@ -24873,7 +25108,7 @@
       <c r="E43" s="8" t="n"/>
       <c r="F43" s="8" t="n"/>
       <c r="G43" s="9" t="n"/>
-      <c r="H43" s="22" t="inlineStr">
+      <c r="H43" s="23" t="inlineStr">
         <is>
           <t>Figure</t>
         </is>
@@ -24909,7 +25144,7 @@
         </is>
       </c>
       <c r="I44" s="9" t="n"/>
-      <c r="J44" s="15" t="inlineStr">
+      <c r="J44" s="16" t="inlineStr">
         <is>
           <t>⚠️ LoopNet / broker · unverified</t>
         </is>
@@ -24939,7 +25174,7 @@
         </is>
       </c>
       <c r="I45" s="9" t="n"/>
-      <c r="J45" s="15" t="inlineStr">
+      <c r="J45" s="16" t="inlineStr">
         <is>
           <t>📊 Native Realty / Matthews · 2025</t>
         </is>
@@ -24969,7 +25204,7 @@
         </is>
       </c>
       <c r="I46" s="9" t="n"/>
-      <c r="J46" s="15" t="inlineStr">
+      <c r="J46" s="16" t="inlineStr">
         <is>
           <t>📊 Matthews · 2025</t>
         </is>
@@ -24979,7 +25214,7 @@
       <c r="M46" s="9" t="n"/>
     </row>
     <row r="47" ht="27" customHeight="1">
-      <c r="B47" s="37" t="inlineStr">
+      <c r="B47" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">  Read</t>
         </is>
@@ -25027,7 +25262,7 @@
       </c>
       <c r="C50" s="9" t="n"/>
       <c r="D50" s="38" t="inlineStr"/>
-      <c r="E50" s="22" t="inlineStr">
+      <c r="E50" s="23" t="inlineStr">
         <is>
           <t>flag</t>
         </is>
@@ -25144,15 +25379,15 @@
         </is>
       </c>
       <c r="C55" s="42" t="n"/>
-      <c r="D55" s="19">
+      <c r="D55" s="20">
         <f>'Office Condo'!I99</f>
         <v/>
       </c>
-      <c r="F55" s="23">
+      <c r="F55" s="24">
         <f>'Office Condo'!C80/'Office Condo'!C34</f>
         <v/>
       </c>
-      <c r="G55" s="15" t="inlineStr">
+      <c r="G55" s="16" t="inlineStr">
         <is>
           <t>← income value (cross-check)</t>
         </is>
@@ -25179,7 +25414,7 @@
       <c r="E56" s="8" t="n"/>
       <c r="F56" s="8" t="n"/>
       <c r="G56" s="9" t="n"/>
-      <c r="H56" s="22" t="inlineStr">
+      <c r="H56" s="23" t="inlineStr">
         <is>
           <t>Figure</t>
         </is>
@@ -25215,7 +25450,7 @@
         </is>
       </c>
       <c r="I57" s="9" t="n"/>
-      <c r="J57" s="15" t="inlineStr">
+      <c r="J57" s="16" t="inlineStr">
         <is>
           <t>📰 MLS A11438689 · 6/2024</t>
         </is>
@@ -25245,7 +25480,7 @@
         </is>
       </c>
       <c r="I58" s="9" t="n"/>
-      <c r="J58" s="15" t="inlineStr">
+      <c r="J58" s="16" t="inlineStr">
         <is>
           <t>📰 Berger Commercial · 11/2019</t>
         </is>
@@ -25275,7 +25510,7 @@
         </is>
       </c>
       <c r="I59" s="9" t="n"/>
-      <c r="J59" s="15" t="inlineStr">
+      <c r="J59" s="16" t="inlineStr">
         <is>
           <t>⚠️ LoopNet / CommercialSearch · 2025</t>
         </is>
@@ -25305,7 +25540,7 @@
         </is>
       </c>
       <c r="I60" s="9" t="n"/>
-      <c r="J60" s="15" t="inlineStr">
+      <c r="J60" s="16" t="inlineStr">
         <is>
           <t>📰 LoopNet listing · 2024-26</t>
         </is>
@@ -25335,7 +25570,7 @@
         </is>
       </c>
       <c r="I61" s="9" t="n"/>
-      <c r="J61" s="15" t="inlineStr">
+      <c r="J61" s="16" t="inlineStr">
         <is>
           <t>📊 Colliers 4Q25 / CBRE</t>
         </is>
@@ -25345,7 +25580,7 @@
       <c r="M61" s="9" t="n"/>
     </row>
     <row r="62" ht="27" customHeight="1">
-      <c r="B62" s="37" t="inlineStr">
+      <c r="B62" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">  Read</t>
         </is>
@@ -25393,7 +25628,7 @@
       </c>
       <c r="C65" s="9" t="n"/>
       <c r="D65" s="38" t="inlineStr"/>
-      <c r="E65" s="22" t="inlineStr">
+      <c r="E65" s="23" t="inlineStr">
         <is>
           <t>flag</t>
         </is>
@@ -25510,15 +25745,15 @@
         </is>
       </c>
       <c r="C70" s="42" t="n"/>
-      <c r="D70" s="19">
+      <c r="D70" s="20">
         <f>'Land'!E43</f>
         <v/>
       </c>
-      <c r="F70" s="23">
+      <c r="F70" s="24">
         <f>'Land'!C51</f>
         <v/>
       </c>
-      <c r="G70" s="15" t="inlineStr">
+      <c r="G70" s="16" t="inlineStr">
         <is>
           <t>← income value (cross-check)</t>
         </is>
@@ -25545,7 +25780,7 @@
       <c r="E71" s="8" t="n"/>
       <c r="F71" s="8" t="n"/>
       <c r="G71" s="9" t="n"/>
-      <c r="H71" s="22" t="inlineStr">
+      <c r="H71" s="23" t="inlineStr">
         <is>
           <t>Figure</t>
         </is>
@@ -25581,7 +25816,7 @@
         </is>
       </c>
       <c r="I72" s="9" t="n"/>
-      <c r="J72" s="15" t="inlineStr">
+      <c r="J72" s="16" t="inlineStr">
         <is>
           <t>📰 The Real Deal · 2/2024</t>
         </is>
@@ -25611,7 +25846,7 @@
         </is>
       </c>
       <c r="I73" s="9" t="n"/>
-      <c r="J73" s="15" t="inlineStr">
+      <c r="J73" s="16" t="inlineStr">
         <is>
           <t>⚠️ The Real Deal · 2/2025</t>
         </is>
@@ -25641,7 +25876,7 @@
         </is>
       </c>
       <c r="I74" s="9" t="n"/>
-      <c r="J74" s="15" t="inlineStr">
+      <c r="J74" s="16" t="inlineStr">
         <is>
           <t>📊 Redfin / broker aggregate · 2025</t>
         </is>
@@ -25651,7 +25886,7 @@
       <c r="M74" s="9" t="n"/>
     </row>
     <row r="75" ht="27" customHeight="1">
-      <c r="B75" s="37" t="inlineStr">
+      <c r="B75" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">  Read</t>
         </is>
@@ -25699,12 +25934,12 @@
       </c>
       <c r="C78" s="8" t="n"/>
       <c r="D78" s="9" t="n"/>
-      <c r="E78" s="23">
+      <c r="E78" s="24">
         <f>'Shahidi Retail'!C57</f>
         <v/>
       </c>
       <c r="F78" s="9" t="n"/>
-      <c r="G78" s="15" t="inlineStr">
+      <c r="G78" s="16" t="inlineStr">
         <is>
           <t>concluded individual price</t>
         </is>
@@ -25724,12 +25959,12 @@
       </c>
       <c r="C79" s="8" t="n"/>
       <c r="D79" s="9" t="n"/>
-      <c r="E79" s="23">
+      <c r="E79" s="24">
         <f>'Publix &amp; Starbucks'!C44</f>
         <v/>
       </c>
       <c r="F79" s="9" t="n"/>
-      <c r="G79" s="15" t="inlineStr">
+      <c r="G79" s="16" t="inlineStr">
         <is>
           <t>concluded individual price</t>
         </is>
@@ -25749,12 +25984,12 @@
       </c>
       <c r="C80" s="8" t="n"/>
       <c r="D80" s="9" t="n"/>
-      <c r="E80" s="23">
+      <c r="E80" s="24">
         <f>'Sunrise Plaza'!C47</f>
         <v/>
       </c>
       <c r="F80" s="9" t="n"/>
-      <c r="G80" s="15" t="inlineStr">
+      <c r="G80" s="16" t="inlineStr">
         <is>
           <t>concluded individual price</t>
         </is>
@@ -25774,12 +26009,12 @@
       </c>
       <c r="C81" s="8" t="n"/>
       <c r="D81" s="9" t="n"/>
-      <c r="E81" s="23">
+      <c r="E81" s="24">
         <f>'Office Condo'!I99</f>
         <v/>
       </c>
       <c r="F81" s="9" t="n"/>
-      <c r="G81" s="15" t="inlineStr">
+      <c r="G81" s="16" t="inlineStr">
         <is>
           <t>concluded individual price</t>
         </is>
@@ -25799,12 +26034,12 @@
       </c>
       <c r="C82" s="8" t="n"/>
       <c r="D82" s="9" t="n"/>
-      <c r="E82" s="23">
+      <c r="E82" s="24">
         <f>'Land'!E43</f>
         <v/>
       </c>
       <c r="F82" s="9" t="n"/>
-      <c r="G82" s="15" t="inlineStr">
+      <c r="G82" s="16" t="inlineStr">
         <is>
           <t>concluded individual price</t>
         </is>
@@ -25824,12 +26059,12 @@
       </c>
       <c r="C83" s="43" t="n"/>
       <c r="D83" s="42" t="n"/>
-      <c r="E83" s="19">
+      <c r="E83" s="20">
         <f>'Assemblage'!C17</f>
         <v/>
       </c>
       <c r="F83" s="9" t="n"/>
-      <c r="G83" s="15" t="inlineStr">
+      <c r="G83" s="16" t="inlineStr">
         <is>
           <t>what you pay buying each owner out</t>
         </is>
@@ -25849,12 +26084,12 @@
       </c>
       <c r="C84" s="8" t="n"/>
       <c r="D84" s="9" t="n"/>
-      <c r="E84" s="23">
+      <c r="E84" s="24">
         <f>'Assemblage'!C29-'Assemblage'!C17</f>
         <v/>
       </c>
       <c r="F84" s="9" t="n"/>
-      <c r="G84" s="15" t="inlineStr">
+      <c r="G84" s="16" t="inlineStr">
         <is>
           <t>hard-to-assemble · holdout risk (20% base)</t>
         </is>
@@ -25867,19 +26102,19 @@
       <c r="M84" s="9" t="n"/>
     </row>
     <row r="85" ht="16" customHeight="1">
-      <c r="B85" s="20" t="inlineStr">
+      <c r="B85" s="21" t="inlineStr">
         <is>
           <t>COVERED-LAND PRICE — controlled as one block</t>
         </is>
       </c>
       <c r="C85" s="8" t="n"/>
       <c r="D85" s="9" t="n"/>
-      <c r="E85" s="21">
+      <c r="E85" s="22">
         <f>'Assemblage'!C29</f>
         <v/>
       </c>
       <c r="F85" s="9" t="n"/>
-      <c r="G85" s="15" t="inlineStr">
+      <c r="G85" s="16" t="inlineStr">
         <is>
           <t>the ceiling — highest &amp; best use</t>
         </is>
@@ -25899,12 +26134,12 @@
       </c>
       <c r="C86" s="8" t="n"/>
       <c r="D86" s="9" t="n"/>
-      <c r="E86" s="19">
+      <c r="E86" s="20">
         <f>'Income Valuation'!C122</f>
         <v/>
       </c>
       <c r="F86" s="9" t="n"/>
-      <c r="G86" s="15" t="inlineStr">
+      <c r="G86" s="16" t="inlineStr">
         <is>
           <t>valuation floor — direct-cap on the combined rent</t>
         </is>
@@ -25924,12 +26159,12 @@
       </c>
       <c r="C87" s="8" t="n"/>
       <c r="D87" s="9" t="n"/>
-      <c r="E87" s="23">
+      <c r="E87" s="24">
         <f>'Highest &amp; Best Use'!C41</f>
         <v/>
       </c>
       <c r="F87" s="9" t="n"/>
-      <c r="G87" s="15" t="inlineStr">
+      <c r="G87" s="16" t="inlineStr">
         <is>
           <t>once density is approved</t>
         </is>
@@ -25943,13 +26178,13 @@
     </row>
     <row r="88"/>
     <row r="89" ht="27" customHeight="1">
-      <c r="B89" s="37" t="inlineStr">
+      <c r="B89" s="15" t="inlineStr">
         <is>
           <t>How to quote this</t>
         </is>
       </c>
       <c r="C89" s="9" t="n"/>
-      <c r="D89" s="37" t="inlineStr">
+      <c r="D89" s="15" t="inlineStr">
         <is>
           <t>Quote ✅ items freely (public record). Attribute 📰/📊 to the named source and date, and say “reported / market” — they are research, not the county roll. Confirm every ⚠️ before it goes in an LOI or an offering memo.</t>
         </is>
@@ -26281,7 +26516,7 @@
         <v/>
       </c>
       <c r="F5" s="9" t="n"/>
-      <c r="G5" s="15" t="inlineStr">
+      <c r="G5" s="16" t="inlineStr">
         <is>
           <t>acres · 5 contiguous assets · Galleria hard corner · plat 49-42-36-12</t>
         </is>
@@ -26301,12 +26536,12 @@
       </c>
       <c r="C6" s="8" t="n"/>
       <c r="D6" s="9" t="n"/>
-      <c r="E6" s="19">
+      <c r="E6" s="20">
         <f>'Income Valuation'!C122</f>
         <v/>
       </c>
       <c r="F6" s="9" t="n"/>
-      <c r="G6" s="15" t="inlineStr">
+      <c r="G6" s="16" t="inlineStr">
         <is>
           <t>what the combined rent supports</t>
         </is>
@@ -26326,12 +26561,12 @@
       </c>
       <c r="C7" s="8" t="n"/>
       <c r="D7" s="9" t="n"/>
-      <c r="E7" s="19">
+      <c r="E7" s="20">
         <f>'Highest &amp; Best Use'!C11</f>
         <v/>
       </c>
       <c r="F7" s="9" t="n"/>
-      <c r="G7" s="15" t="inlineStr">
+      <c r="G7" s="16" t="inlineStr">
         <is>
           <t>each component bought independently</t>
         </is>
@@ -26351,12 +26586,12 @@
       </c>
       <c r="C8" s="8" t="n"/>
       <c r="D8" s="9" t="n"/>
-      <c r="E8" s="21">
+      <c r="E8" s="22">
         <f>'Assemblage'!C29</f>
         <v/>
       </c>
       <c r="F8" s="9" t="n"/>
-      <c r="G8" s="15" t="inlineStr">
+      <c r="G8" s="16" t="inlineStr">
         <is>
           <t>control the whole block — sum-of-parts + assemblage premium</t>
         </is>
@@ -26376,12 +26611,12 @@
       </c>
       <c r="C9" s="8" t="n"/>
       <c r="D9" s="9" t="n"/>
-      <c r="E9" s="23">
+      <c r="E9" s="24">
         <f>'Assemblage'!D17</f>
         <v/>
       </c>
       <c r="F9" s="9" t="n"/>
-      <c r="G9" s="15" t="inlineStr">
+      <c r="G9" s="16" t="inlineStr">
         <is>
           <t>covers carry; blended cap on next line</t>
         </is>
@@ -26401,12 +26636,12 @@
       </c>
       <c r="C10" s="8" t="n"/>
       <c r="D10" s="9" t="n"/>
-      <c r="E10" s="36">
+      <c r="E10" s="37">
         <f>'Assemblage'!C23</f>
         <v/>
       </c>
       <c r="F10" s="9" t="n"/>
-      <c r="G10" s="15" t="inlineStr">
+      <c r="G10" s="16" t="inlineStr">
         <is>
           <t>covered-land range ~3–5% — income covers carry, not a yield play</t>
         </is>
@@ -26426,12 +26661,12 @@
       </c>
       <c r="C11" s="8" t="n"/>
       <c r="D11" s="9" t="n"/>
-      <c r="E11" s="19">
+      <c r="E11" s="20">
         <f>'Income Valuation'!E85</f>
         <v/>
       </c>
       <c r="F11" s="9" t="n"/>
-      <c r="G11" s="15" t="inlineStr">
+      <c r="G11" s="16" t="inlineStr">
         <is>
           <t>sized lesser-of; income-limited at this price</t>
         </is>
@@ -26451,12 +26686,12 @@
       </c>
       <c r="C12" s="8" t="n"/>
       <c r="D12" s="9" t="n"/>
-      <c r="E12" s="21">
+      <c r="E12" s="22">
         <f>'Income Valuation'!E86</f>
         <v/>
       </c>
       <c r="F12" s="9" t="n"/>
-      <c r="G12" s="15" t="inlineStr">
+      <c r="G12" s="16" t="inlineStr">
         <is>
           <t>the sponsor + LP check; full Sources &amp; Uses in §3</t>
         </is>
@@ -26469,7 +26704,7 @@
       <c r="M12" s="9" t="n"/>
     </row>
     <row r="13" ht="15" customHeight="1">
-      <c r="B13" s="37" t="inlineStr">
+      <c r="B13" s="15" t="inlineStr">
         <is>
           <t>Recommendation</t>
         </is>
@@ -26482,7 +26717,7 @@
         </is>
       </c>
       <c r="F13" s="9" t="n"/>
-      <c r="G13" s="37" t="inlineStr">
+      <c r="G13" s="15" t="inlineStr">
         <is>
           <t>covered land play — buy the income, control the dirt, hold the Live Local density option</t>
         </is>
@@ -26520,12 +26755,12 @@
         </is>
       </c>
       <c r="C16" s="9" t="n"/>
-      <c r="D16" s="22" t="inlineStr">
+      <c r="D16" s="23" t="inlineStr">
         <is>
           <t>They paid</t>
         </is>
       </c>
-      <c r="E16" s="22" t="inlineStr">
+      <c r="E16" s="23" t="inlineStr">
         <is>
           <t>Our basis</t>
         </is>
@@ -26554,11 +26789,11 @@
         </is>
       </c>
       <c r="C17" s="9" t="n"/>
-      <c r="D17" s="23">
+      <c r="D17" s="24">
         <f>'Assumptions'!C27</f>
         <v/>
       </c>
-      <c r="E17" s="23">
+      <c r="E17" s="24">
         <f>'Shahidi Retail'!C57</f>
         <v/>
       </c>
@@ -26586,11 +26821,11 @@
         </is>
       </c>
       <c r="C18" s="9" t="n"/>
-      <c r="D18" s="23">
+      <c r="D18" s="24">
         <f>'Assumptions'!C29</f>
         <v/>
       </c>
-      <c r="E18" s="23">
+      <c r="E18" s="24">
         <f>'Publix &amp; Starbucks'!C44</f>
         <v/>
       </c>
@@ -26618,11 +26853,11 @@
         </is>
       </c>
       <c r="C19" s="9" t="n"/>
-      <c r="D19" s="23">
+      <c r="D19" s="24">
         <f>'Assumptions'!C31</f>
         <v/>
       </c>
-      <c r="E19" s="23">
+      <c r="E19" s="24">
         <f>'Sunrise Plaza'!C47</f>
         <v/>
       </c>
@@ -26650,11 +26885,11 @@
         </is>
       </c>
       <c r="C20" s="9" t="n"/>
-      <c r="D20" s="23">
+      <c r="D20" s="24">
         <f>'Assumptions'!C33</f>
         <v/>
       </c>
-      <c r="E20" s="23">
+      <c r="E20" s="24">
         <f>'Office Condo'!I99</f>
         <v/>
       </c>
@@ -26682,11 +26917,11 @@
         </is>
       </c>
       <c r="C21" s="9" t="n"/>
-      <c r="D21" s="23">
+      <c r="D21" s="24">
         <f>'Assumptions'!C35</f>
         <v/>
       </c>
-      <c r="E21" s="23">
+      <c r="E21" s="24">
         <f>'Land'!E43</f>
         <v/>
       </c>
@@ -26708,28 +26943,28 @@
       <c r="M21" s="9" t="n"/>
     </row>
     <row r="22" ht="15" customHeight="1">
-      <c r="B22" s="27" t="inlineStr">
+      <c r="B22" s="28" t="inlineStr">
         <is>
           <t>Total to control (independently)</t>
         </is>
       </c>
       <c r="C22" s="9" t="n"/>
-      <c r="D22" s="28" t="inlineStr">
+      <c r="D22" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E22" s="30">
+      <c r="E22" s="31">
         <f>'Assemblage'!C17</f>
         <v/>
       </c>
-      <c r="F22" s="27" t="inlineStr">
+      <c r="F22" s="28" t="inlineStr">
         <is>
           <t>sum of the parts</t>
         </is>
       </c>
       <c r="G22" s="9" t="n"/>
-      <c r="H22" s="27" t="inlineStr">
+      <c r="H22" s="28" t="inlineStr">
         <is>
           <t>＋ assemblage premium → covered-land price (§3)</t>
         </is>
@@ -26771,7 +27006,7 @@
         <v>2000000</v>
       </c>
       <c r="F25" s="9" t="n"/>
-      <c r="G25" s="15" t="inlineStr">
+      <c r="G25" s="16" t="inlineStr">
         <is>
           <t>🔵 sized cushion for lease-up &amp; capex</t>
         </is>
@@ -26795,7 +27030,7 @@
         <v>3000000</v>
       </c>
       <c r="F26" s="9" t="n"/>
-      <c r="G26" s="15" t="inlineStr">
+      <c r="G26" s="16" t="inlineStr">
         <is>
           <t>🔵 funds negative carry while entitling (covered-land)</t>
         </is>
@@ -26819,7 +27054,7 @@
         <v>0</v>
       </c>
       <c r="F27" s="9" t="n"/>
-      <c r="G27" s="15" t="inlineStr">
+      <c r="G27" s="16" t="inlineStr">
         <is>
           <t>🔵 optional second debt layer (0 = none)</t>
         </is>
@@ -27006,7 +27241,7 @@
       </c>
     </row>
     <row r="39" ht="16" customHeight="1">
-      <c r="B39" s="20" t="inlineStr">
+      <c r="B39" s="21" t="inlineStr">
         <is>
           <t>TOTAL USES</t>
         </is>
@@ -27014,7 +27249,7 @@
       <c r="C39" s="8" t="n"/>
       <c r="D39" s="8" t="n"/>
       <c r="E39" s="9" t="n"/>
-      <c r="F39" s="21">
+      <c r="F39" s="22">
         <f>'Assemblage'!C29*(1+'Income Valuation'!C36+'Income Valuation'!C37+'Income Valuation'!C38)+'Income Valuation'!C39*'Income Valuation'!E85+E25+E26</f>
         <v/>
       </c>
@@ -27033,7 +27268,7 @@
       <c r="M39" s="9" t="n"/>
     </row>
     <row r="40" ht="16" customHeight="1">
-      <c r="B40" s="15" t="inlineStr">
+      <c r="B40" s="16" t="inlineStr">
         <is>
           <t>Check (sources − uses)</t>
         </is>
@@ -27045,7 +27280,7 @@
         <f>(L30+L31+L39)-F39</f>
         <v/>
       </c>
-      <c r="H40" s="20" t="inlineStr">
+      <c r="H40" s="21" t="inlineStr">
         <is>
           <t>TOTAL SOURCES</t>
         </is>
@@ -27053,14 +27288,14 @@
       <c r="I40" s="8" t="n"/>
       <c r="J40" s="8" t="n"/>
       <c r="K40" s="9" t="n"/>
-      <c r="L40" s="21">
+      <c r="L40" s="22">
         <f>L30+L31+L39</f>
         <v/>
       </c>
       <c r="M40" s="9" t="n"/>
     </row>
     <row r="41" ht="15" customHeight="1">
-      <c r="B41" s="15" t="inlineStr">
+      <c r="B41" s="16" t="inlineStr">
         <is>
           <t>Loan-to-cost  ·  equity as % of cost</t>
         </is>
@@ -27109,7 +27344,7 @@
       </c>
       <c r="C44" s="8" t="n"/>
       <c r="D44" s="9" t="n"/>
-      <c r="E44" s="36">
+      <c r="E44" s="37">
         <f>'Income Valuation'!C43</f>
         <v/>
       </c>
@@ -27121,7 +27356,7 @@
       </c>
       <c r="H44" s="8" t="n"/>
       <c r="I44" s="9" t="n"/>
-      <c r="J44" s="34">
+      <c r="J44" s="35">
         <f>'Income Valuation'!E96</f>
         <v/>
       </c>
@@ -27137,7 +27372,7 @@
       </c>
       <c r="C45" s="8" t="n"/>
       <c r="D45" s="9" t="n"/>
-      <c r="E45" s="33">
+      <c r="E45" s="34">
         <f>'Income Valuation'!C40</f>
         <v/>
       </c>
@@ -27149,7 +27384,7 @@
       </c>
       <c r="H45" s="8" t="n"/>
       <c r="I45" s="9" t="n"/>
-      <c r="J45" s="36">
+      <c r="J45" s="37">
         <f>'Income Valuation'!C118</f>
         <v/>
       </c>
@@ -27165,7 +27400,7 @@
       </c>
       <c r="C46" s="8" t="n"/>
       <c r="D46" s="9" t="n"/>
-      <c r="E46" s="33">
+      <c r="E46" s="34">
         <f>'Income Valuation'!C94</f>
         <v/>
       </c>
@@ -27177,7 +27412,7 @@
       </c>
       <c r="H46" s="8" t="n"/>
       <c r="I46" s="9" t="n"/>
-      <c r="J46" s="33">
+      <c r="J46" s="34">
         <f>'Income Valuation'!E94</f>
         <v/>
       </c>
@@ -27193,7 +27428,7 @@
       </c>
       <c r="C47" s="8" t="n"/>
       <c r="D47" s="9" t="n"/>
-      <c r="E47" s="33">
+      <c r="E47" s="34">
         <f>'Income Valuation'!C92</f>
         <v/>
       </c>
@@ -27205,7 +27440,7 @@
       </c>
       <c r="H47" s="8" t="n"/>
       <c r="I47" s="9" t="n"/>
-      <c r="J47" s="34">
+      <c r="J47" s="35">
         <f>'Income Valuation'!C95</f>
         <v/>
       </c>
@@ -27221,7 +27456,7 @@
       </c>
       <c r="C48" s="8" t="n"/>
       <c r="D48" s="9" t="n"/>
-      <c r="E48" s="33">
+      <c r="E48" s="34">
         <f>'Income Valuation'!C102</f>
         <v/>
       </c>
@@ -27233,7 +27468,7 @@
       </c>
       <c r="H48" s="8" t="n"/>
       <c r="I48" s="9" t="n"/>
-      <c r="J48" s="19">
+      <c r="J48" s="20">
         <f>'Highest &amp; Best Use'!C41</f>
         <v/>
       </c>
@@ -27242,14 +27477,14 @@
       <c r="M48" s="9" t="n"/>
     </row>
     <row r="49" ht="27" customHeight="1">
-      <c r="B49" s="37" t="inlineStr">
+      <c r="B49" s="15" t="inlineStr">
         <is>
           <t>The thesis</t>
         </is>
       </c>
       <c r="C49" s="8" t="n"/>
       <c r="D49" s="9" t="n"/>
-      <c r="E49" s="37" t="inlineStr">
+      <c r="E49" s="15" t="inlineStr">
         <is>
           <t>Income covers the carry; the return is the dirt + the Live Local option. At the covered-land price the going-in income return is negative by design — equity buys optionality, underwritten to a HOLD, and pays off if land compounds at ≥ the CAGR at left.</t>
         </is>
@@ -27290,7 +27525,7 @@
       </c>
       <c r="C52" s="8" t="n"/>
       <c r="D52" s="9" t="n"/>
-      <c r="E52" s="22" t="inlineStr">
+      <c r="E52" s="23" t="inlineStr">
         <is>
           <t>L / I</t>
         </is>
@@ -27543,7 +27778,7 @@
       </c>
       <c r="C63" s="8" t="n"/>
       <c r="D63" s="9" t="n"/>
-      <c r="E63" s="22" t="inlineStr">
+      <c r="E63" s="23" t="inlineStr">
         <is>
           <t>Window</t>
         </is>
@@ -27957,7 +28192,7 @@
       <c r="C5" s="53" t="n">
         <v>0.9</v>
       </c>
-      <c r="D5" s="15" t="inlineStr">
+      <c r="D5" s="16" t="inlineStr">
         <is>
           <t>limited partner / investors</t>
         </is>
@@ -27981,7 +28216,7 @@
       <c r="C6" s="53" t="n">
         <v>0.1</v>
       </c>
-      <c r="D6" s="15" t="inlineStr">
+      <c r="D6" s="16" t="inlineStr">
         <is>
           <t>sponsor co-invest</t>
         </is>
@@ -28005,7 +28240,7 @@
       <c r="C7" s="53" t="n">
         <v>0.08</v>
       </c>
-      <c r="D7" s="15" t="inlineStr">
+      <c r="D7" s="16" t="inlineStr">
         <is>
           <t>8% pref, compounded, before promote</t>
         </is>
@@ -28029,7 +28264,7 @@
       <c r="C8" s="53" t="n">
         <v>0.7</v>
       </c>
-      <c r="D8" s="15" t="inlineStr">
+      <c r="D8" s="16" t="inlineStr">
         <is>
           <t>LP keeps 70% of the excess</t>
         </is>
@@ -28053,7 +28288,7 @@
       <c r="C9" s="53" t="n">
         <v>0.3</v>
       </c>
-      <c r="D9" s="15" t="inlineStr">
+      <c r="D9" s="16" t="inlineStr">
         <is>
           <t>sponsor carry on the excess</t>
         </is>
@@ -28078,7 +28313,7 @@
         <f>'Income Valuation'!C86</f>
         <v/>
       </c>
-      <c r="D10" s="15" t="inlineStr">
+      <c r="D10" s="16" t="inlineStr">
         <is>
           <t>🟢 from the Income Valuation Sources &amp; Uses</t>
         </is>
@@ -28118,7 +28353,7 @@
           <t>Year</t>
         </is>
       </c>
-      <c r="C13" s="22" t="inlineStr">
+      <c r="C13" s="23" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -28160,47 +28395,47 @@
           <t>Total equity cash flow (levered)</t>
         </is>
       </c>
-      <c r="C14" s="19">
+      <c r="C14" s="20">
         <f>'Income Valuation'!C90</f>
         <v/>
       </c>
-      <c r="D14" s="23">
+      <c r="D14" s="24">
         <f>'Income Valuation'!D90</f>
         <v/>
       </c>
-      <c r="E14" s="23">
+      <c r="E14" s="24">
         <f>'Income Valuation'!E90</f>
         <v/>
       </c>
-      <c r="F14" s="23">
+      <c r="F14" s="24">
         <f>'Income Valuation'!F90</f>
         <v/>
       </c>
-      <c r="G14" s="23">
+      <c r="G14" s="24">
         <f>'Income Valuation'!G90</f>
         <v/>
       </c>
-      <c r="H14" s="23">
+      <c r="H14" s="24">
         <f>'Income Valuation'!H90</f>
         <v/>
       </c>
-      <c r="I14" s="23">
+      <c r="I14" s="24">
         <f>'Income Valuation'!I90</f>
         <v/>
       </c>
-      <c r="J14" s="23">
+      <c r="J14" s="24">
         <f>'Income Valuation'!J90</f>
         <v/>
       </c>
-      <c r="K14" s="23">
+      <c r="K14" s="24">
         <f>'Income Valuation'!K90</f>
         <v/>
       </c>
-      <c r="L14" s="23">
+      <c r="L14" s="24">
         <f>'Income Valuation'!L90</f>
         <v/>
       </c>
-      <c r="M14" s="23">
+      <c r="M14" s="24">
         <f>'Income Valuation'!M90</f>
         <v/>
       </c>
@@ -28524,17 +28759,17 @@
           <t>Metric</t>
         </is>
       </c>
-      <c r="E23" s="22" t="inlineStr">
+      <c r="E23" s="23" t="inlineStr">
         <is>
           <t>LP</t>
         </is>
       </c>
-      <c r="G23" s="22" t="inlineStr">
+      <c r="G23" s="23" t="inlineStr">
         <is>
           <t>GP / sponsor</t>
         </is>
       </c>
-      <c r="I23" s="22" t="inlineStr">
+      <c r="I23" s="23" t="inlineStr">
         <is>
           <t>Project</t>
         </is>
@@ -28555,7 +28790,7 @@
         <f>IFERROR(IRR(C20:M20),"n/m")</f>
         <v/>
       </c>
-      <c r="I24" s="33">
+      <c r="I24" s="34">
         <f>'Income Valuation'!C94</f>
         <v/>
       </c>
@@ -28575,7 +28810,7 @@
         <f>SUM(D20:M20)/(C6*C10)</f>
         <v/>
       </c>
-      <c r="I25" s="34">
+      <c r="I25" s="35">
         <f>'Income Valuation'!C95</f>
         <v/>
       </c>
@@ -28595,7 +28830,7 @@
         <f>C6*C10</f>
         <v/>
       </c>
-      <c r="I26" s="23">
+      <c r="I26" s="24">
         <f>C10</f>
         <v/>
       </c>
@@ -28615,7 +28850,7 @@
         <f>SUM(D20:M20)</f>
         <v/>
       </c>
-      <c r="I27" s="23">
+      <c r="I27" s="24">
         <f>SUM(D15:M15)</f>
         <v/>
       </c>
@@ -28631,7 +28866,7 @@
         <f>C9*SUM(D18:M18)</f>
         <v/>
       </c>
-      <c r="G28" s="15" t="inlineStr">
+      <c r="G28" s="16" t="inlineStr">
         <is>
           <t>the sponsor's incentive fee for outperformance above the pref</t>
         </is>
@@ -28668,19 +28903,19 @@
           <t>Project levered IRR — down / base / up</t>
         </is>
       </c>
-      <c r="F31" s="26">
+      <c r="F31" s="27">
         <f>'Scenarios'!G22</f>
         <v/>
       </c>
-      <c r="G31" s="26">
+      <c r="G31" s="27">
         <f>'Income Valuation'!C94</f>
         <v/>
       </c>
-      <c r="H31" s="26">
+      <c r="H31" s="27">
         <f>'Scenarios'!G24</f>
         <v/>
       </c>
-      <c r="I31" s="15" t="inlineStr">
+      <c r="I31" s="16" t="inlineStr">
         <is>
           <t>full consolidated cash flows on the Scenarios tab</t>
         </is>
@@ -28725,7 +28960,7 @@
         <v/>
       </c>
       <c r="F34" s="9" t="n"/>
-      <c r="G34" s="15" t="inlineStr">
+      <c r="G34" s="16" t="inlineStr">
         <is>
           <t>LP sits ahead of the GP promote: the sponsor earns carry only after the LP's capital + 8% pref is returned</t>
         </is>
@@ -28738,12 +28973,12 @@
       <c r="M34" s="9" t="n"/>
     </row>
     <row r="35" ht="27" customHeight="1">
-      <c r="B35" s="37" t="inlineStr">
+      <c r="B35" s="15" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
-      <c r="D35" s="37" t="inlineStr">
+      <c r="D35" s="15" t="inlineStr">
         <is>
           <t>At the income price the LP earns its pref with room to spare; the GP's upside is the promote. The covered-land price is a separate, land-appreciation bet (negative going-in income return) — raise LP equity against the income case, not the covered-land case.</t>
         </is>
@@ -28963,7 +29198,7 @@
         <v/>
       </c>
       <c r="O6" s="3" t="n"/>
-      <c r="P6" s="17">
+      <c r="P6" s="18">
         <f>'Income Valuation'!C118</f>
         <v/>
       </c>
@@ -28995,7 +29230,7 @@
           <t>Lever</t>
         </is>
       </c>
-      <c r="D9" s="22" t="inlineStr">
+      <c r="D9" s="23" t="inlineStr">
         <is>
           <t>Now</t>
         </is>
@@ -29024,7 +29259,7 @@
         <f>'Assumptions'!C6</f>
         <v/>
       </c>
-      <c r="E10" s="15" t="inlineStr">
+      <c r="E10" s="16" t="inlineStr">
         <is>
           <t>income price = as-is NOI ÷ this</t>
         </is>
@@ -29048,7 +29283,7 @@
         <f>'Assumptions'!C7</f>
         <v/>
       </c>
-      <c r="E11" s="15" t="inlineStr">
+      <c r="E11" s="16" t="inlineStr">
         <is>
           <t>reversion &amp; exit value</t>
         </is>
@@ -29068,11 +29303,11 @@
           <t>NOI growth</t>
         </is>
       </c>
-      <c r="D12" s="26">
+      <c r="D12" s="27">
         <f>'Assumptions'!C9</f>
         <v/>
       </c>
-      <c r="E12" s="15" t="inlineStr">
+      <c r="E12" s="16" t="inlineStr">
         <is>
           <t>forward NOI, reversion</t>
         </is>
@@ -29096,7 +29331,7 @@
         <f>'Assumptions'!C17</f>
         <v/>
       </c>
-      <c r="E13" s="15" t="inlineStr">
+      <c r="E13" s="16" t="inlineStr">
         <is>
           <t>debt service, levered return</t>
         </is>
@@ -29116,11 +29351,11 @@
           <t>Max senior LTV</t>
         </is>
       </c>
-      <c r="D14" s="26">
+      <c r="D14" s="27">
         <f>'Assumptions'!C14</f>
         <v/>
       </c>
-      <c r="E14" s="15" t="inlineStr">
+      <c r="E14" s="16" t="inlineStr">
         <is>
           <t>leverage / equity check</t>
         </is>
@@ -29140,11 +29375,11 @@
           <t>Hold (yrs)</t>
         </is>
       </c>
-      <c r="D15" s="24">
+      <c r="D15" s="25">
         <f>'Assumptions'!C10</f>
         <v/>
       </c>
-      <c r="E15" s="15" t="inlineStr">
+      <c r="E15" s="16" t="inlineStr">
         <is>
           <t>exit year</t>
         </is>
@@ -29164,11 +29399,11 @@
           <t>Assemblage premium (base)</t>
         </is>
       </c>
-      <c r="D16" s="26">
+      <c r="D16" s="27">
         <f>'Assumptions'!C40</f>
         <v/>
       </c>
-      <c r="E16" s="15" t="inlineStr">
+      <c r="E16" s="16" t="inlineStr">
         <is>
           <t>covered-land price over sum-of-parts</t>
         </is>
@@ -29188,11 +29423,11 @@
           <t>Target unlevered yield (DCF)</t>
         </is>
       </c>
-      <c r="D17" s="26">
+      <c r="D17" s="27">
         <f>'Assumptions'!C8</f>
         <v/>
       </c>
-      <c r="E17" s="15" t="inlineStr">
+      <c r="E17" s="16" t="inlineStr">
         <is>
           <t>DCF cross-check value</t>
         </is>
@@ -29261,7 +29496,7 @@
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
-      <c r="B22" s="15" t="inlineStr">
+      <c r="B22" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  price</t>
         </is>
@@ -29324,7 +29559,7 @@
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
-      <c r="B26" s="15" t="inlineStr">
+      <c r="B26" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  price</t>
         </is>
@@ -29387,7 +29622,7 @@
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
-      <c r="B30" s="15" t="inlineStr">
+      <c r="B30" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  EM</t>
         </is>
@@ -29433,7 +29668,7 @@
       <c r="M32" s="3" t="n"/>
     </row>
     <row r="33" ht="15" customHeight="1">
-      <c r="B33" s="22" t="inlineStr">
+      <c r="B33" s="23" t="inlineStr">
         <is>
           <t>Price ╲ exit cap</t>
         </is>
@@ -29580,7 +29815,7 @@
       </c>
     </row>
     <row r="39" ht="15" customHeight="1">
-      <c r="B39" s="15" t="inlineStr">
+      <c r="B39" s="16" t="inlineStr">
         <is>
           <t>income price ≈ row 2 · covered-land price ≈ row 5 · reversion anchored to actual (incl. land-value exits)</t>
         </is>
@@ -29622,32 +29857,32 @@
           <t>Lever</t>
         </is>
       </c>
-      <c r="D42" s="22" t="inlineStr">
+      <c r="D42" s="23" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E42" s="22" t="inlineStr">
+      <c r="E42" s="23" t="inlineStr">
         <is>
           <t>EM@Low</t>
         </is>
       </c>
-      <c r="F42" s="22" t="inlineStr">
+      <c r="F42" s="23" t="inlineStr">
         <is>
           <t>EM@Base</t>
         </is>
       </c>
-      <c r="G42" s="22" t="inlineStr">
+      <c r="G42" s="23" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H42" s="22" t="inlineStr">
+      <c r="H42" s="23" t="inlineStr">
         <is>
           <t>EM@High</t>
         </is>
       </c>
-      <c r="I42" s="22" t="inlineStr">
+      <c r="I42" s="23" t="inlineStr">
         <is>
           <t>Swing</t>
         </is>
@@ -29689,7 +29924,7 @@
         <f>ABS(H43-E43)</f>
         <v/>
       </c>
-      <c r="J43" s="15" t="inlineStr">
+      <c r="J43" s="16" t="inlineStr">
         <is>
           <t>softer exit → reversion falls (incl. land)</t>
         </is>
@@ -29726,7 +29961,7 @@
         <f>ABS(H44-E44)</f>
         <v/>
       </c>
-      <c r="J44" s="15" t="inlineStr">
+      <c r="J44" s="16" t="inlineStr">
         <is>
           <t>pay less → higher multiple</t>
         </is>
@@ -29763,7 +29998,7 @@
         <f>ABS(H45-E45)</f>
         <v/>
       </c>
-      <c r="J45" s="15" t="inlineStr">
+      <c r="J45" s="16" t="inlineStr">
         <is>
           <t>cost of debt</t>
         </is>
@@ -29800,7 +30035,7 @@
         <f>ABS(H46-E46)</f>
         <v/>
       </c>
-      <c r="J46" s="15" t="inlineStr">
+      <c r="J46" s="16" t="inlineStr">
         <is>
           <t>more debt → more levered</t>
         </is>
@@ -29837,7 +30072,7 @@
         <f>ABS(H47-E47)</f>
         <v/>
       </c>
-      <c r="J47" s="15" t="inlineStr">
+      <c r="J47" s="16" t="inlineStr">
         <is>
           <t>NOI / carry achievement ±10%</t>
         </is>
@@ -29871,17 +30106,17 @@
           <t>Levered IRR (income price)</t>
         </is>
       </c>
-      <c r="E50" s="22" t="inlineStr">
+      <c r="E50" s="23" t="inlineStr">
         <is>
           <t>Downside</t>
         </is>
       </c>
-      <c r="F50" s="22" t="inlineStr">
+      <c r="F50" s="23" t="inlineStr">
         <is>
           <t>Base</t>
         </is>
       </c>
-      <c r="G50" s="22" t="inlineStr">
+      <c r="G50" s="23" t="inlineStr">
         <is>
           <t>Upside</t>
         </is>
@@ -29889,27 +30124,27 @@
       <c r="H50" s="9" t="n"/>
     </row>
     <row r="51" ht="15" customHeight="1">
-      <c r="B51" s="15" t="inlineStr">
+      <c r="B51" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  IRR</t>
         </is>
       </c>
-      <c r="E51" s="26">
+      <c r="E51" s="27">
         <f>'Scenarios'!G22</f>
         <v/>
       </c>
-      <c r="F51" s="26">
+      <c r="F51" s="27">
         <f>'Income Valuation'!C94</f>
         <v/>
       </c>
-      <c r="G51" s="26">
+      <c r="G51" s="27">
         <f>'Scenarios'!G24</f>
         <v/>
       </c>
       <c r="H51" s="9" t="n"/>
     </row>
     <row r="52" ht="15" customHeight="1">
-      <c r="B52" s="37" t="inlineStr">
+      <c r="B52" s="15" t="inlineStr">
         <is>
           <t>At the COVERED-LAND price</t>
         </is>
@@ -29918,7 +30153,7 @@
         <f>'Income Valuation'!E94</f>
         <v/>
       </c>
-      <c r="E52" s="37">
+      <c r="E52" s="15">
         <f>IF('Income Valuation'!E94&lt;0,"income case loses money at this price — the return is land appreciation / redevelopment only","thin income return — land optionality drives it")</f>
         <v/>
       </c>
@@ -29937,11 +30172,11 @@
           <t>Land CAGR needed to justify the premium</t>
         </is>
       </c>
-      <c r="D53" s="26">
+      <c r="D53" s="27">
         <f>'Income Valuation'!C102</f>
         <v/>
       </c>
-      <c r="E53" s="15" t="inlineStr">
+      <c r="E53" s="16" t="inlineStr">
         <is>
           <t>annual land-value growth over the hold to break even on the dirt premium</t>
         </is>
@@ -29957,12 +30192,12 @@
     </row>
     <row r="54"/>
     <row r="55" ht="25" customHeight="1">
-      <c r="B55" s="15" t="inlineStr">
+      <c r="B55" s="16" t="inlineStr">
         <is>
           <t>How to read</t>
         </is>
       </c>
-      <c r="D55" s="15" t="inlineStr">
+      <c r="D55" s="16" t="inlineStr">
         <is>
           <t>Every grid is closed-form and live, anchored so the base case reproduces the headline multiple. Edit a 🔵 blue axis/band cell to reshape a table, or change the underlying lever on the Assumptions tab to move the whole board (and the model) at once.</t>
         </is>
@@ -30180,12 +30415,12 @@
           <t>Lever</t>
         </is>
       </c>
-      <c r="C5" s="22" t="inlineStr">
+      <c r="C5" s="23" t="inlineStr">
         <is>
           <t>You</t>
         </is>
       </c>
-      <c r="D5" s="22" t="inlineStr">
+      <c r="D5" s="23" t="inlineStr">
         <is>
           <t>Model now</t>
         </is>
@@ -30231,11 +30466,11 @@
       <c r="C7" s="53" t="n">
         <v>0.6</v>
       </c>
-      <c r="D7" s="26">
+      <c r="D7" s="27">
         <f>'Income Valuation'!C40</f>
         <v/>
       </c>
-      <c r="E7" s="15" t="inlineStr">
+      <c r="E7" s="16" t="inlineStr">
         <is>
           <t>sizing constraint 1</t>
         </is>
@@ -30262,7 +30497,7 @@
         <f>'Income Valuation'!C43</f>
         <v/>
       </c>
-      <c r="E8" s="15" t="inlineStr">
+      <c r="E8" s="16" t="inlineStr">
         <is>
           <t>annual</t>
         </is>
@@ -30285,11 +30520,11 @@
       <c r="C9" s="67" t="n">
         <v>30</v>
       </c>
-      <c r="D9" s="24">
+      <c r="D9" s="25">
         <f>'Income Valuation'!C44</f>
         <v/>
       </c>
-      <c r="E9" s="15" t="inlineStr">
+      <c r="E9" s="16" t="inlineStr">
         <is>
           <t>0 = interest-only</t>
         </is>
@@ -30316,7 +30551,7 @@
         <f>'Income Valuation'!C41</f>
         <v/>
       </c>
-      <c r="E10" s="15" t="inlineStr">
+      <c r="E10" s="16" t="inlineStr">
         <is>
           <t>sizing constraint 2</t>
         </is>
@@ -30339,11 +30574,11 @@
       <c r="C11" s="53" t="n">
         <v>0.08500000000000001</v>
       </c>
-      <c r="D11" s="26">
+      <c r="D11" s="27">
         <f>'Income Valuation'!C42</f>
         <v/>
       </c>
-      <c r="E11" s="15" t="inlineStr">
+      <c r="E11" s="16" t="inlineStr">
         <is>
           <t>sizing constraint 3</t>
         </is>
@@ -30389,7 +30624,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="E13" s="15" t="inlineStr">
+      <c r="E13" s="16" t="inlineStr">
         <is>
           <t>0 = none; a second debt layer</t>
         </is>
@@ -30417,7 +30652,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="E14" s="15" t="inlineStr">
+      <c r="E14" s="16" t="inlineStr">
         <is>
           <t>typically higher than senior</t>
         </is>
@@ -30462,7 +30697,7 @@
         <f>'Income Valuation'!C86</f>
         <v/>
       </c>
-      <c r="E16" s="15" t="inlineStr">
+      <c r="E16" s="16" t="inlineStr">
         <is>
           <t>your check size — drives affordability</t>
         </is>
@@ -30490,7 +30725,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="E17" s="15" t="inlineStr">
+      <c r="E17" s="16" t="inlineStr">
         <is>
           <t>LP takes the balance</t>
         </is>
@@ -30518,7 +30753,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="E18" s="15" t="inlineStr">
+      <c r="E18" s="16" t="inlineStr">
         <is>
           <t>hurdle before promote (reference)</t>
         </is>
@@ -30557,7 +30792,7 @@
           <t>Senior monthly rate</t>
         </is>
       </c>
-      <c r="C21" s="25">
+      <c r="C21" s="26">
         <f>C8/12</f>
         <v/>
       </c>
@@ -30568,11 +30803,11 @@
           <t>Senior mortgage constant (annual)</t>
         </is>
       </c>
-      <c r="C22" s="25">
+      <c r="C22" s="26">
         <f>IF(C9=0,C8,(C21/(1-(1+C21)^(-C9*12)))*12)</f>
         <v/>
       </c>
-      <c r="D22" s="15" t="inlineStr">
+      <c r="D22" s="16" t="inlineStr">
         <is>
           <t>debt service ÷ loan (IO if amort = 0)</t>
         </is>
@@ -30608,13 +30843,13 @@
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="B25" s="14" t="inlineStr"/>
-      <c r="D25" s="22" t="inlineStr">
+      <c r="D25" s="23" t="inlineStr">
         <is>
           <t>INCOME PRICE</t>
         </is>
       </c>
       <c r="E25" s="9" t="n"/>
-      <c r="G25" s="22" t="inlineStr">
+      <c r="G25" s="23" t="inlineStr">
         <is>
           <t>COVERED-LAND PRICE</t>
         </is>
@@ -30627,22 +30862,22 @@
           <t>Component</t>
         </is>
       </c>
-      <c r="D26" s="22" t="inlineStr">
+      <c r="D26" s="23" t="inlineStr">
         <is>
           <t>$</t>
         </is>
       </c>
-      <c r="E26" s="22" t="inlineStr">
+      <c r="E26" s="23" t="inlineStr">
         <is>
           <t>% cost</t>
         </is>
       </c>
-      <c r="G26" s="22" t="inlineStr">
+      <c r="G26" s="23" t="inlineStr">
         <is>
           <t>$</t>
         </is>
       </c>
-      <c r="H26" s="22" t="inlineStr">
+      <c r="H26" s="23" t="inlineStr">
         <is>
           <t>% cost</t>
         </is>
@@ -30824,7 +31059,7 @@
       </c>
     </row>
     <row r="38" ht="15" customHeight="1">
-      <c r="B38" s="15" t="inlineStr">
+      <c r="B38" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  GP / sponsor equity</t>
         </is>
@@ -30839,7 +31074,7 @@
       </c>
     </row>
     <row r="39" ht="15" customHeight="1">
-      <c r="B39" s="15" t="inlineStr">
+      <c r="B39" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  LP equity</t>
         </is>
@@ -30859,11 +31094,11 @@
           <t>Levered IRR at this price (from model)</t>
         </is>
       </c>
-      <c r="D40" s="33">
+      <c r="D40" s="34">
         <f>'Income Valuation'!C94</f>
         <v/>
       </c>
-      <c r="G40" s="33">
+      <c r="G40" s="34">
         <f>'Income Valuation'!E94</f>
         <v/>
       </c>
@@ -30921,7 +31156,7 @@
       </c>
     </row>
     <row r="46" ht="16" customHeight="1">
-      <c r="B46" s="20" t="inlineStr">
+      <c r="B46" s="21" t="inlineStr">
         <is>
           <t>→ MAX PURCHASE PRICE</t>
         </is>
@@ -30930,7 +31165,7 @@
         <f>C45/(1+'Income Valuation'!C49)</f>
         <v/>
       </c>
-      <c r="D46" s="15" t="inlineStr">
+      <c r="D46" s="16" t="inlineStr">
         <is>
           <t>the biggest price your equity + this leverage supports</t>
         </is>
@@ -30973,23 +31208,23 @@
           <t>Assemblage capacity</t>
         </is>
       </c>
-      <c r="C49" s="22" t="inlineStr">
+      <c r="C49" s="23" t="inlineStr">
         <is>
           <t>Price</t>
         </is>
       </c>
-      <c r="D49" s="22" t="inlineStr">
+      <c r="D49" s="23" t="inlineStr">
         <is>
           <t>Your max vs it</t>
         </is>
       </c>
-      <c r="F49" s="22" t="inlineStr">
+      <c r="F49" s="23" t="inlineStr">
         <is>
           <t>Equity to control it</t>
         </is>
       </c>
       <c r="G49" s="9" t="n"/>
-      <c r="H49" s="22" t="inlineStr">
+      <c r="H49" s="23" t="inlineStr">
         <is>
           <t>Equity gap</t>
         </is>
@@ -31072,12 +31307,12 @@
       <c r="I52" s="9" t="n"/>
     </row>
     <row r="53" ht="15" customHeight="1">
-      <c r="B53" s="15" t="inlineStr">
+      <c r="B53" s="16" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
-      <c r="D53" s="15" t="inlineStr">
+      <c r="D53" s="16" t="inlineStr">
         <is>
           <t>‘Your max vs it’ = what share of that price your equity covers at this leverage. ‘Equity gap’ &gt; 0 = additional equity needed to control it; &lt; 0 = headroom.</t>
         </is>
@@ -31112,7 +31347,7 @@
       <c r="M55" s="3" t="n"/>
     </row>
     <row r="56" ht="15" customHeight="1">
-      <c r="B56" s="22" t="inlineStr">
+      <c r="B56" s="23" t="inlineStr">
         <is>
           <t>Equity ╲ leverage</t>
         </is>
@@ -31259,7 +31494,7 @@
       </c>
     </row>
     <row r="62" ht="15" customHeight="1">
-      <c r="B62" s="15" t="inlineStr">
+      <c r="B62" s="16" t="inlineStr">
         <is>
           <t>Max purchase price ($M) = equity ÷ (1 − leverage) ÷ (1 + closing). Green = more buying power.</t>
         </is>
@@ -31437,12 +31672,12 @@
           <t>Driver</t>
         </is>
       </c>
-      <c r="C5" s="22" t="inlineStr">
+      <c r="C5" s="23" t="inlineStr">
         <is>
           <t>Input</t>
         </is>
       </c>
-      <c r="D5" s="22" t="inlineStr">
+      <c r="D5" s="23" t="inlineStr">
         <is>
           <t>Flag</t>
         </is>
@@ -31475,7 +31710,7 @@
           <t>🔶</t>
         </is>
       </c>
-      <c r="E6" s="15" t="inlineStr">
+      <c r="E6" s="16" t="inlineStr">
         <is>
           <t>income price = as-is NOI ÷ this</t>
         </is>
@@ -31503,7 +31738,7 @@
           <t>🔶</t>
         </is>
       </c>
-      <c r="E7" s="15" t="inlineStr">
+      <c r="E7" s="16" t="inlineStr">
         <is>
           <t>reversion &amp; stabilized value</t>
         </is>
@@ -31531,7 +31766,7 @@
           <t>🔶</t>
         </is>
       </c>
-      <c r="E8" s="15" t="inlineStr">
+      <c r="E8" s="16" t="inlineStr">
         <is>
           <t>DCF value; NPV hurdle</t>
         </is>
@@ -31559,7 +31794,7 @@
           <t>🔶</t>
         </is>
       </c>
-      <c r="E9" s="15" t="inlineStr">
+      <c r="E9" s="16" t="inlineStr">
         <is>
           <t>reversion &amp; sensitivities</t>
         </is>
@@ -31587,7 +31822,7 @@
           <t>🔶</t>
         </is>
       </c>
-      <c r="E10" s="15" t="inlineStr">
+      <c r="E10" s="16" t="inlineStr">
         <is>
           <t>exit year for all assets</t>
         </is>
@@ -31615,7 +31850,7 @@
           <t>🔶</t>
         </is>
       </c>
-      <c r="E11" s="15" t="inlineStr">
+      <c r="E11" s="16" t="inlineStr">
         <is>
           <t>net reversion</t>
         </is>
@@ -31653,12 +31888,12 @@
           <t>Driver</t>
         </is>
       </c>
-      <c r="C13" s="22" t="inlineStr">
+      <c r="C13" s="23" t="inlineStr">
         <is>
           <t>Input</t>
         </is>
       </c>
-      <c r="D13" s="22" t="inlineStr">
+      <c r="D13" s="23" t="inlineStr">
         <is>
           <t>Flag</t>
         </is>
@@ -31691,7 +31926,7 @@
           <t>🔶</t>
         </is>
       </c>
-      <c r="E14" s="15" t="inlineStr">
+      <c r="E14" s="16" t="inlineStr">
         <is>
           <t>debt sizing constraint 1</t>
         </is>
@@ -31719,7 +31954,7 @@
           <t>🔶</t>
         </is>
       </c>
-      <c r="E15" s="15" t="inlineStr">
+      <c r="E15" s="16" t="inlineStr">
         <is>
           <t>debt sizing constraint 2</t>
         </is>
@@ -31747,7 +31982,7 @@
           <t>🔶</t>
         </is>
       </c>
-      <c r="E16" s="15" t="inlineStr">
+      <c r="E16" s="16" t="inlineStr">
         <is>
           <t>debt sizing constraint 3</t>
         </is>
@@ -31775,7 +32010,7 @@
           <t>🔶</t>
         </is>
       </c>
-      <c r="E17" s="15" t="inlineStr">
+      <c r="E17" s="16" t="inlineStr">
         <is>
           <t>debt service</t>
         </is>
@@ -31803,7 +32038,7 @@
           <t>🔶</t>
         </is>
       </c>
-      <c r="E18" s="15" t="inlineStr">
+      <c r="E18" s="16" t="inlineStr">
         <is>
           <t>mortgage constant</t>
         </is>
@@ -31841,12 +32076,12 @@
           <t>Driver</t>
         </is>
       </c>
-      <c r="C20" s="22" t="inlineStr">
+      <c r="C20" s="23" t="inlineStr">
         <is>
           <t>Input</t>
         </is>
       </c>
-      <c r="D20" s="22" t="inlineStr">
+      <c r="D20" s="23" t="inlineStr">
         <is>
           <t>Flag</t>
         </is>
@@ -31879,7 +32114,7 @@
           <t>🔶</t>
         </is>
       </c>
-      <c r="E21" s="15" t="inlineStr">
+      <c r="E21" s="16" t="inlineStr">
         <is>
           <t>FL Broward $0.70/$100</t>
         </is>
@@ -31907,7 +32142,7 @@
           <t>🔶</t>
         </is>
       </c>
-      <c r="E22" s="15" t="inlineStr">
+      <c r="E22" s="16" t="inlineStr">
         <is>
           <t>closing cost</t>
         </is>
@@ -31935,7 +32170,7 @@
           <t>🔶</t>
         </is>
       </c>
-      <c r="E23" s="15" t="inlineStr">
+      <c r="E23" s="16" t="inlineStr">
         <is>
           <t>closing cost</t>
         </is>
@@ -31963,7 +32198,7 @@
           <t>🔶</t>
         </is>
       </c>
-      <c r="E24" s="15" t="inlineStr">
+      <c r="E24" s="16" t="inlineStr">
         <is>
           <t>financing cost → equity</t>
         </is>
@@ -32001,12 +32236,12 @@
           <t>Driver</t>
         </is>
       </c>
-      <c r="C26" s="22" t="inlineStr">
+      <c r="C26" s="23" t="inlineStr">
         <is>
           <t>Input</t>
         </is>
       </c>
-      <c r="D26" s="22" t="inlineStr">
+      <c r="D26" s="23" t="inlineStr">
         <is>
           <t>Flag</t>
         </is>
@@ -32039,7 +32274,7 @@
           <t>✅</t>
         </is>
       </c>
-      <c r="E27" s="15" t="inlineStr">
+      <c r="E27" s="16" t="inlineStr">
         <is>
           <t>Shawnick Galleria LLC, 11/2021 (disqualified deed)</t>
         </is>
@@ -32067,7 +32302,7 @@
           <t>✅</t>
         </is>
       </c>
-      <c r="E28" s="15" t="inlineStr">
+      <c r="E28" s="16" t="inlineStr">
         <is>
           <t>→ scorecard 'they paid' year</t>
         </is>
@@ -32095,7 +32330,7 @@
           <t>✅</t>
         </is>
       </c>
-      <c r="E29" s="15" t="inlineStr">
+      <c r="E29" s="16" t="inlineStr">
         <is>
           <t>REAL SUB LLC Trustee's Deed, 03/2025 ($679/SF)</t>
         </is>
@@ -32123,7 +32358,7 @@
           <t>✅</t>
         </is>
       </c>
-      <c r="E30" s="15" t="inlineStr">
+      <c r="E30" s="16" t="inlineStr">
         <is>
           <t>→ scorecard 'they paid' year</t>
         </is>
@@ -32151,7 +32386,7 @@
           <t>⚠️</t>
         </is>
       </c>
-      <c r="E31" s="15" t="inlineStr">
+      <c r="E31" s="16" t="inlineStr">
         <is>
           <t>Kar Luen Inc, Oct 2000 — stale/nominal</t>
         </is>
@@ -32179,7 +32414,7 @@
           <t>⚠️</t>
         </is>
       </c>
-      <c r="E32" s="15" t="inlineStr">
+      <c r="E32" s="16" t="inlineStr">
         <is>
           <t>→ scorecard 'they paid' year</t>
         </is>
@@ -32207,7 +32442,7 @@
           <t>✅</t>
         </is>
       </c>
-      <c r="E33" s="15" t="inlineStr">
+      <c r="E33" s="16" t="inlineStr">
         <is>
           <t>Main St Fund from Intl Sunrise 09/2019 (~$103/SF) — Daily Business Review</t>
         </is>
@@ -32235,7 +32470,7 @@
           <t>✅</t>
         </is>
       </c>
-      <c r="E34" s="15" t="inlineStr">
+      <c r="E34" s="16" t="inlineStr">
         <is>
           <t>→ scorecard 'they paid' year</t>
         </is>
@@ -32263,7 +32498,7 @@
           <t>✅</t>
         </is>
       </c>
-      <c r="E35" s="15" t="inlineStr">
+      <c r="E35" s="16" t="inlineStr">
         <is>
           <t>Procacci/BBX JV bought 2014 for ~$7.9–8.0M; BBX exited 2022 (Florida YIMBY)</t>
         </is>
@@ -32291,7 +32526,7 @@
           <t>✅</t>
         </is>
       </c>
-      <c r="E36" s="15" t="inlineStr">
+      <c r="E36" s="16" t="inlineStr">
         <is>
           <t>→ scorecard 'they paid' year</t>
         </is>
@@ -32329,12 +32564,12 @@
           <t>Driver</t>
         </is>
       </c>
-      <c r="C38" s="22" t="inlineStr">
+      <c r="C38" s="23" t="inlineStr">
         <is>
           <t>Input</t>
         </is>
       </c>
-      <c r="D38" s="22" t="inlineStr">
+      <c r="D38" s="23" t="inlineStr">
         <is>
           <t>Flag</t>
         </is>
@@ -32367,7 +32602,7 @@
           <t>🔶</t>
         </is>
       </c>
-      <c r="E39" s="15" t="inlineStr">
+      <c r="E39" s="16" t="inlineStr">
         <is>
           <t>control-cost premium</t>
         </is>
@@ -32395,7 +32630,7 @@
           <t>🔶</t>
         </is>
       </c>
-      <c r="E40" s="15" t="inlineStr">
+      <c r="E40" s="16" t="inlineStr">
         <is>
           <t>headline covered-land price</t>
         </is>
@@ -32423,7 +32658,7 @@
           <t>🔶</t>
         </is>
       </c>
-      <c r="E41" s="15" t="inlineStr">
+      <c r="E41" s="16" t="inlineStr">
         <is>
           <t>aggressive case</t>
         </is>
@@ -32461,12 +32696,12 @@
           <t>Driver</t>
         </is>
       </c>
-      <c r="C43" s="22" t="inlineStr">
+      <c r="C43" s="23" t="inlineStr">
         <is>
           <t>Input</t>
         </is>
       </c>
-      <c r="D43" s="22" t="inlineStr">
+      <c r="D43" s="23" t="inlineStr">
         <is>
           <t>Flag</t>
         </is>
@@ -32499,7 +32734,7 @@
           <t>🔶</t>
         </is>
       </c>
-      <c r="E44" s="15" t="inlineStr">
+      <c r="E44" s="16" t="inlineStr">
         <is>
           <t>assembled land value bump once entitled</t>
         </is>
@@ -32527,7 +32762,7 @@
           <t>🔶</t>
         </is>
       </c>
-      <c r="E45" s="15" t="inlineStr">
+      <c r="E45" s="16" t="inlineStr">
         <is>
           <t>BCPA-implied floor</t>
         </is>
@@ -32555,7 +32790,7 @@
           <t>🔶</t>
         </is>
       </c>
-      <c r="E46" s="15" t="inlineStr">
+      <c r="E46" s="16" t="inlineStr">
         <is>
           <t>mid-block corridor</t>
         </is>
@@ -32583,7 +32818,7 @@
           <t>🔶</t>
         </is>
       </c>
-      <c r="E47" s="15" t="inlineStr">
+      <c r="E47" s="16" t="inlineStr">
         <is>
           <t>toward hard-corner comps</t>
         </is>
@@ -32611,7 +32846,7 @@
           <t>🔶</t>
         </is>
       </c>
-      <c r="E48" s="15" t="inlineStr">
+      <c r="E48" s="16" t="inlineStr">
         <is>
           <t>259 units</t>
         </is>
@@ -32639,7 +32874,7 @@
           <t>🔶</t>
         </is>
       </c>
-      <c r="E49" s="15" t="inlineStr">
+      <c r="E49" s="16" t="inlineStr">
         <is>
           <t>entitled-land value</t>
         </is>
@@ -32667,7 +32902,7 @@
           <t>🔶</t>
         </is>
       </c>
-      <c r="E50" s="15" t="inlineStr">
+      <c r="E50" s="16" t="inlineStr">
         <is>
           <t>strong entitlement</t>
         </is>
@@ -32695,7 +32930,7 @@
           <t>🔶</t>
         </is>
       </c>
-      <c r="E51" s="15" t="inlineStr">
+      <c r="E51" s="16" t="inlineStr">
         <is>
           <t>sellout / cap'd rental</t>
         </is>
@@ -32723,7 +32958,7 @@
           <t>🔶</t>
         </is>
       </c>
-      <c r="E52" s="15" t="inlineStr">
+      <c r="E52" s="16" t="inlineStr">
         <is>
           <t>AE-zone coastal</t>
         </is>
@@ -32751,7 +32986,7 @@
           <t>🔶</t>
         </is>
       </c>
-      <c r="E53" s="15" t="inlineStr">
+      <c r="E53" s="16" t="inlineStr">
         <is>
           <t>gross buildable/unit</t>
         </is>
@@ -32779,7 +33014,7 @@
           <t>🔶</t>
         </is>
       </c>
-      <c r="E54" s="15" t="inlineStr">
+      <c r="E54" s="16" t="inlineStr">
         <is>
           <t>A&amp;E, financing, fees</t>
         </is>
@@ -32807,7 +33042,7 @@
           <t>🔶</t>
         </is>
       </c>
-      <c r="E55" s="15" t="inlineStr">
+      <c r="E55" s="16" t="inlineStr">
         <is>
           <t>required margin</t>
         </is>
@@ -33589,12 +33824,12 @@
           <t>Figure</t>
         </is>
       </c>
-      <c r="C132" s="22" t="inlineStr">
+      <c r="C132" s="23" t="inlineStr">
         <is>
           <t>Current</t>
         </is>
       </c>
-      <c r="D132" s="22" t="inlineStr">
+      <c r="D132" s="23" t="inlineStr">
         <is>
           <t>Flag</t>
         </is>
@@ -33628,7 +33863,7 @@
           <t>⚠️</t>
         </is>
       </c>
-      <c r="E133" s="15" t="inlineStr">
+      <c r="E133" s="16" t="inlineStr">
         <is>
           <t>Assumptions · Sunrise block</t>
         </is>
@@ -33657,7 +33892,7 @@
           <t>⚠️</t>
         </is>
       </c>
-      <c r="E134" s="15" t="inlineStr">
+      <c r="E134" s="16" t="inlineStr">
         <is>
           <t>Sunrise Plaza tab</t>
         </is>
@@ -33686,7 +33921,7 @@
           <t>⚠️</t>
         </is>
       </c>
-      <c r="E135" s="15" t="inlineStr">
+      <c r="E135" s="16" t="inlineStr">
         <is>
           <t>Assumptions · Sunrise block</t>
         </is>
@@ -33715,7 +33950,7 @@
           <t>⚠️</t>
         </is>
       </c>
-      <c r="E136" s="15" t="inlineStr">
+      <c r="E136" s="16" t="inlineStr">
         <is>
           <t>Office Condo tab</t>
         </is>
@@ -33744,7 +33979,7 @@
           <t>⚠️</t>
         </is>
       </c>
-      <c r="E137" s="15" t="inlineStr">
+      <c r="E137" s="16" t="inlineStr">
         <is>
           <t>Office Condo tab</t>
         </is>
@@ -33773,7 +34008,7 @@
           <t>⚠️</t>
         </is>
       </c>
-      <c r="E138" s="15" t="inlineStr">
+      <c r="E138" s="16" t="inlineStr">
         <is>
           <t>Office Condo tab</t>
         </is>
@@ -33802,7 +34037,7 @@
           <t>🔶</t>
         </is>
       </c>
-      <c r="E139" s="15" t="inlineStr">
+      <c r="E139" s="16" t="inlineStr">
         <is>
           <t>Assumptions · Office block</t>
         </is>
@@ -33831,7 +34066,7 @@
           <t>⚠️</t>
         </is>
       </c>
-      <c r="E140" s="15" t="inlineStr">
+      <c r="E140" s="16" t="inlineStr">
         <is>
           <t>Land tab</t>
         </is>
@@ -33860,7 +34095,7 @@
           <t>⚠️</t>
         </is>
       </c>
-      <c r="E141" s="15" t="inlineStr">
+      <c r="E141" s="16" t="inlineStr">
         <is>
           <t>Land tab</t>
         </is>
@@ -33889,7 +34124,7 @@
           <t>⚠️</t>
         </is>
       </c>
-      <c r="E142" s="15" t="inlineStr">
+      <c r="E142" s="16" t="inlineStr">
         <is>
           <t>Land tab</t>
         </is>
@@ -33918,7 +34153,7 @@
           <t>⚠️</t>
         </is>
       </c>
-      <c r="E143" s="15" t="inlineStr">
+      <c r="E143" s="16" t="inlineStr">
         <is>
           <t>Land tab</t>
         </is>
@@ -33934,12 +34169,12 @@
     </row>
     <row r="144"/>
     <row r="145" ht="39" customHeight="1">
-      <c r="B145" s="37" t="inlineStr">
+      <c r="B145" s="15" t="inlineStr">
         <is>
           <t>How to use</t>
         </is>
       </c>
-      <c r="D145" s="37" t="inlineStr">
+      <c r="D145" s="15" t="inlineStr">
         <is>
           <t>Everything you tune is on THIS tab: global drivers up top, then a block per asset (price · rents · occupancy · operating expenses · caps · debt). Standard modeling params (rent/expense growth, TI/LC, reserves, closing detail) remain blue on each asset tab. ⚠️ = reported, verify at bcpa.net. Change any blue cell → the model recalculates.</t>
         </is>
@@ -33955,12 +34190,12 @@
       <c r="M145" s="9" t="n"/>
     </row>
     <row r="146" ht="27" customHeight="1">
-      <c r="B146" s="37" t="inlineStr">
+      <c r="B146" s="15" t="inlineStr">
         <is>
           <t>Filling in real data</t>
         </is>
       </c>
-      <c r="D146" s="37" t="inlineStr">
+      <c r="D146" s="15" t="inlineStr">
         <is>
           <t>As you confirm real numbers, put them in overrides.json (pre-listed with every gap + where to source it) and rerun build_model.py — the value flows through every tab. See the developer README and MODEL_AUDIT.md for the full data-gap list.</t>
         </is>
@@ -34268,7 +34503,7 @@
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
-      <c r="B12" s="15" t="inlineStr">
+      <c r="B12" s="16" t="inlineStr">
         <is>
           <t>Year ending</t>
         </is>
@@ -34348,43 +34583,43 @@
           <t xml:space="preserve">  Shahidi Retail (Galleria Plaza)</t>
         </is>
       </c>
-      <c r="D14" s="19">
+      <c r="D14" s="20">
         <f>'Shahidi Retail'!D100</f>
         <v/>
       </c>
-      <c r="E14" s="23">
+      <c r="E14" s="24">
         <f>'Shahidi Retail'!E100</f>
         <v/>
       </c>
-      <c r="F14" s="23">
+      <c r="F14" s="24">
         <f>'Shahidi Retail'!F100</f>
         <v/>
       </c>
-      <c r="G14" s="23">
+      <c r="G14" s="24">
         <f>'Shahidi Retail'!G100</f>
         <v/>
       </c>
-      <c r="H14" s="23">
+      <c r="H14" s="24">
         <f>'Shahidi Retail'!H100</f>
         <v/>
       </c>
-      <c r="I14" s="23">
+      <c r="I14" s="24">
         <f>'Shahidi Retail'!I100</f>
         <v/>
       </c>
-      <c r="J14" s="23">
+      <c r="J14" s="24">
         <f>'Shahidi Retail'!J100</f>
         <v/>
       </c>
-      <c r="K14" s="23">
+      <c r="K14" s="24">
         <f>'Shahidi Retail'!K100</f>
         <v/>
       </c>
-      <c r="L14" s="23">
+      <c r="L14" s="24">
         <f>'Shahidi Retail'!L100</f>
         <v/>
       </c>
-      <c r="M14" s="23">
+      <c r="M14" s="24">
         <f>'Shahidi Retail'!M100</f>
         <v/>
       </c>
@@ -34395,43 +34630,43 @@
           <t xml:space="preserve">  Publix + Starbucks</t>
         </is>
       </c>
-      <c r="D15" s="19">
+      <c r="D15" s="20">
         <f>'Publix &amp; Starbucks'!D87</f>
         <v/>
       </c>
-      <c r="E15" s="23">
+      <c r="E15" s="24">
         <f>'Publix &amp; Starbucks'!E87</f>
         <v/>
       </c>
-      <c r="F15" s="23">
+      <c r="F15" s="24">
         <f>'Publix &amp; Starbucks'!F87</f>
         <v/>
       </c>
-      <c r="G15" s="23">
+      <c r="G15" s="24">
         <f>'Publix &amp; Starbucks'!G87</f>
         <v/>
       </c>
-      <c r="H15" s="23">
+      <c r="H15" s="24">
         <f>'Publix &amp; Starbucks'!H87</f>
         <v/>
       </c>
-      <c r="I15" s="23">
+      <c r="I15" s="24">
         <f>'Publix &amp; Starbucks'!I87</f>
         <v/>
       </c>
-      <c r="J15" s="23">
+      <c r="J15" s="24">
         <f>'Publix &amp; Starbucks'!J87</f>
         <v/>
       </c>
-      <c r="K15" s="23">
+      <c r="K15" s="24">
         <f>'Publix &amp; Starbucks'!K87</f>
         <v/>
       </c>
-      <c r="L15" s="23">
+      <c r="L15" s="24">
         <f>'Publix &amp; Starbucks'!L87</f>
         <v/>
       </c>
-      <c r="M15" s="23">
+      <c r="M15" s="24">
         <f>'Publix &amp; Starbucks'!M87</f>
         <v/>
       </c>
@@ -34442,43 +34677,43 @@
           <t xml:space="preserve">  Sunrise Plaza (Kar Luen)</t>
         </is>
       </c>
-      <c r="D16" s="19">
+      <c r="D16" s="20">
         <f>'Sunrise Plaza'!D90</f>
         <v/>
       </c>
-      <c r="E16" s="23">
+      <c r="E16" s="24">
         <f>'Sunrise Plaza'!E90</f>
         <v/>
       </c>
-      <c r="F16" s="23">
+      <c r="F16" s="24">
         <f>'Sunrise Plaza'!F90</f>
         <v/>
       </c>
-      <c r="G16" s="23">
+      <c r="G16" s="24">
         <f>'Sunrise Plaza'!G90</f>
         <v/>
       </c>
-      <c r="H16" s="23">
+      <c r="H16" s="24">
         <f>'Sunrise Plaza'!H90</f>
         <v/>
       </c>
-      <c r="I16" s="23">
+      <c r="I16" s="24">
         <f>'Sunrise Plaza'!I90</f>
         <v/>
       </c>
-      <c r="J16" s="23">
+      <c r="J16" s="24">
         <f>'Sunrise Plaza'!J90</f>
         <v/>
       </c>
-      <c r="K16" s="23">
+      <c r="K16" s="24">
         <f>'Sunrise Plaza'!K90</f>
         <v/>
       </c>
-      <c r="L16" s="23">
+      <c r="L16" s="24">
         <f>'Sunrise Plaza'!L90</f>
         <v/>
       </c>
-      <c r="M16" s="23">
+      <c r="M16" s="24">
         <f>'Sunrise Plaza'!M90</f>
         <v/>
       </c>
@@ -34489,43 +34724,43 @@
           <t xml:space="preserve">  Galleria Corporate Centre (office)</t>
         </is>
       </c>
-      <c r="D17" s="19">
+      <c r="D17" s="20">
         <f>'Office Condo'!D62</f>
         <v/>
       </c>
-      <c r="E17" s="23">
+      <c r="E17" s="24">
         <f>'Office Condo'!E62</f>
         <v/>
       </c>
-      <c r="F17" s="23">
+      <c r="F17" s="24">
         <f>'Office Condo'!F62</f>
         <v/>
       </c>
-      <c r="G17" s="23">
+      <c r="G17" s="24">
         <f>'Office Condo'!G62</f>
         <v/>
       </c>
-      <c r="H17" s="23">
+      <c r="H17" s="24">
         <f>'Office Condo'!H62</f>
         <v/>
       </c>
-      <c r="I17" s="23">
+      <c r="I17" s="24">
         <f>'Office Condo'!I62</f>
         <v/>
       </c>
-      <c r="J17" s="23">
+      <c r="J17" s="24">
         <f>'Office Condo'!J62</f>
         <v/>
       </c>
-      <c r="K17" s="23">
+      <c r="K17" s="24">
         <f>'Office Condo'!K62</f>
         <v/>
       </c>
-      <c r="L17" s="23">
+      <c r="L17" s="24">
         <f>'Office Condo'!L62</f>
         <v/>
       </c>
-      <c r="M17" s="23">
+      <c r="M17" s="24">
         <f>'Office Condo'!M62</f>
         <v/>
       </c>
@@ -34536,43 +34771,43 @@
           <t xml:space="preserve">  1040 Bayview (interim office)</t>
         </is>
       </c>
-      <c r="D18" s="19">
+      <c r="D18" s="20">
         <f>'Land'!D61</f>
         <v/>
       </c>
-      <c r="E18" s="23">
+      <c r="E18" s="24">
         <f>'Land'!E61</f>
         <v/>
       </c>
-      <c r="F18" s="23">
+      <c r="F18" s="24">
         <f>'Land'!F61</f>
         <v/>
       </c>
-      <c r="G18" s="23">
+      <c r="G18" s="24">
         <f>'Land'!G61</f>
         <v/>
       </c>
-      <c r="H18" s="23">
+      <c r="H18" s="24">
         <f>'Land'!H61</f>
         <v/>
       </c>
-      <c r="I18" s="23">
+      <c r="I18" s="24">
         <f>'Land'!I61</f>
         <v/>
       </c>
-      <c r="J18" s="23">
+      <c r="J18" s="24">
         <f>'Land'!J61</f>
         <v/>
       </c>
-      <c r="K18" s="23">
+      <c r="K18" s="24">
         <f>'Land'!K61</f>
         <v/>
       </c>
-      <c r="L18" s="23">
+      <c r="L18" s="24">
         <f>'Land'!L61</f>
         <v/>
       </c>
-      <c r="M18" s="23">
+      <c r="M18" s="24">
         <f>'Land'!M61</f>
         <v/>
       </c>
@@ -34630,43 +34865,43 @@
           <t>Less: consolidated capital (reserves + leasing)</t>
         </is>
       </c>
-      <c r="D20" s="23">
+      <c r="D20" s="24">
         <f>-('Shahidi Retail'!D104+'Publix &amp; Starbucks'!D91+'Sunrise Plaza'!D94+'Office Condo'!D63)</f>
         <v/>
       </c>
-      <c r="E20" s="23">
+      <c r="E20" s="24">
         <f>-('Shahidi Retail'!E104+'Publix &amp; Starbucks'!E91+'Sunrise Plaza'!E94+'Office Condo'!E63)</f>
         <v/>
       </c>
-      <c r="F20" s="23">
+      <c r="F20" s="24">
         <f>-('Shahidi Retail'!F104+'Publix &amp; Starbucks'!F91+'Sunrise Plaza'!F94+'Office Condo'!F63)</f>
         <v/>
       </c>
-      <c r="G20" s="23">
+      <c r="G20" s="24">
         <f>-('Shahidi Retail'!G104+'Publix &amp; Starbucks'!G91+'Sunrise Plaza'!G94+'Office Condo'!G63)</f>
         <v/>
       </c>
-      <c r="H20" s="23">
+      <c r="H20" s="24">
         <f>-('Shahidi Retail'!H104+'Publix &amp; Starbucks'!H91+'Sunrise Plaza'!H94+'Office Condo'!H63)</f>
         <v/>
       </c>
-      <c r="I20" s="23">
+      <c r="I20" s="24">
         <f>-('Shahidi Retail'!I104+'Publix &amp; Starbucks'!I91+'Sunrise Plaza'!I94+'Office Condo'!I63)</f>
         <v/>
       </c>
-      <c r="J20" s="23">
+      <c r="J20" s="24">
         <f>-('Shahidi Retail'!J104+'Publix &amp; Starbucks'!J91+'Sunrise Plaza'!J94+'Office Condo'!J63)</f>
         <v/>
       </c>
-      <c r="K20" s="23">
+      <c r="K20" s="24">
         <f>-('Shahidi Retail'!K104+'Publix &amp; Starbucks'!K91+'Sunrise Plaza'!K94+'Office Condo'!K63)</f>
         <v/>
       </c>
-      <c r="L20" s="23">
+      <c r="L20" s="24">
         <f>-('Shahidi Retail'!L104+'Publix &amp; Starbucks'!L91+'Sunrise Plaza'!L94+'Office Condo'!L63)</f>
         <v/>
       </c>
-      <c r="M20" s="23">
+      <c r="M20" s="24">
         <f>-('Shahidi Retail'!M104+'Publix &amp; Starbucks'!M91+'Sunrise Plaza'!M94+'Office Condo'!M63)</f>
         <v/>
       </c>
@@ -34724,43 +34959,43 @@
           <t>Consolidated reversion (net sale, exit yr)</t>
         </is>
       </c>
-      <c r="D22" s="23">
+      <c r="D22" s="24">
         <f>'Shahidi Retail'!D108+'Publix &amp; Starbucks'!D95+'Sunrise Plaza'!D98+'Office Condo'!D67+'Land'!D62</f>
         <v/>
       </c>
-      <c r="E22" s="23">
+      <c r="E22" s="24">
         <f>'Shahidi Retail'!E108+'Publix &amp; Starbucks'!E95+'Sunrise Plaza'!E98+'Office Condo'!E67+'Land'!E62</f>
         <v/>
       </c>
-      <c r="F22" s="23">
+      <c r="F22" s="24">
         <f>'Shahidi Retail'!F108+'Publix &amp; Starbucks'!F95+'Sunrise Plaza'!F98+'Office Condo'!F67+'Land'!F62</f>
         <v/>
       </c>
-      <c r="G22" s="23">
+      <c r="G22" s="24">
         <f>'Shahidi Retail'!G108+'Publix &amp; Starbucks'!G95+'Sunrise Plaza'!G98+'Office Condo'!G67+'Land'!G62</f>
         <v/>
       </c>
-      <c r="H22" s="23">
+      <c r="H22" s="24">
         <f>'Shahidi Retail'!H108+'Publix &amp; Starbucks'!H95+'Sunrise Plaza'!H98+'Office Condo'!H67+'Land'!H62</f>
         <v/>
       </c>
-      <c r="I22" s="23">
+      <c r="I22" s="24">
         <f>'Shahidi Retail'!I108+'Publix &amp; Starbucks'!I95+'Sunrise Plaza'!I98+'Office Condo'!I67+'Land'!I62</f>
         <v/>
       </c>
-      <c r="J22" s="23">
+      <c r="J22" s="24">
         <f>'Shahidi Retail'!J108+'Publix &amp; Starbucks'!J95+'Sunrise Plaza'!J98+'Office Condo'!J67+'Land'!J62</f>
         <v/>
       </c>
-      <c r="K22" s="23">
+      <c r="K22" s="24">
         <f>'Shahidi Retail'!K108+'Publix &amp; Starbucks'!K95+'Sunrise Plaza'!K98+'Office Condo'!K67+'Land'!K62</f>
         <v/>
       </c>
-      <c r="L22" s="23">
+      <c r="L22" s="24">
         <f>'Shahidi Retail'!L108+'Publix &amp; Starbucks'!L95+'Sunrise Plaza'!L98+'Office Condo'!L67+'Land'!L62</f>
         <v/>
       </c>
-      <c r="M22" s="23">
+      <c r="M22" s="24">
         <f>'Shahidi Retail'!M108+'Publix &amp; Starbucks'!M95+'Sunrise Plaza'!M98+'Office Condo'!M67+'Land'!M62</f>
         <v/>
       </c>
@@ -34794,7 +35029,7 @@
         <f>'Shahidi Retail'!C122+'Publix &amp; Starbucks'!C110+'Sunrise Plaza'!C113+'Office Condo'!C80+'Land'!C50</f>
         <v/>
       </c>
-      <c r="D25" s="15" t="inlineStr">
+      <c r="D25" s="16" t="inlineStr">
         <is>
           <t>current occupancy, no lease-up (going-in)</t>
         </is>
@@ -34819,7 +35054,7 @@
         <f>'Shahidi Retail'!C124+'Publix &amp; Starbucks'!C112+'Sunrise Plaza'!C115+'Office Condo'!C82+'Land'!C50</f>
         <v/>
       </c>
-      <c r="D26" s="15" t="inlineStr">
+      <c r="D26" s="16" t="inlineStr">
         <is>
           <t>post lease-up (Shahidi to 95%, Sunrise to 95%, office to 88%)</t>
         </is>
@@ -34870,11 +35105,11 @@
           <t>Blended going-in cap (as-is)</t>
         </is>
       </c>
-      <c r="C30" s="36">
+      <c r="C30" s="37">
         <f>'Assumptions'!C6</f>
         <v/>
       </c>
-      <c r="D30" s="15" t="inlineStr">
+      <c r="D30" s="16" t="inlineStr">
         <is>
           <t>🟢 Assumptions tab</t>
         </is>
@@ -34895,11 +35130,11 @@
           <t>Blended stabilized / exit cap</t>
         </is>
       </c>
-      <c r="C31" s="36">
+      <c r="C31" s="37">
         <f>'Assumptions'!C7</f>
         <v/>
       </c>
-      <c r="D31" s="15" t="inlineStr">
+      <c r="D31" s="16" t="inlineStr">
         <is>
           <t>🟢 Assumptions tab</t>
         </is>
@@ -34920,11 +35155,11 @@
           <t>Target unlevered yield (DCF discount)</t>
         </is>
       </c>
-      <c r="C32" s="33">
+      <c r="C32" s="34">
         <f>'Assumptions'!C8</f>
         <v/>
       </c>
-      <c r="D32" s="15" t="inlineStr">
+      <c r="D32" s="16" t="inlineStr">
         <is>
           <t>🟢 Assumptions tab</t>
         </is>
@@ -34945,11 +35180,11 @@
           <t>Blended NOI growth</t>
         </is>
       </c>
-      <c r="C33" s="33">
+      <c r="C33" s="34">
         <f>'Assumptions'!C9</f>
         <v/>
       </c>
-      <c r="D33" s="15" t="inlineStr">
+      <c r="D33" s="16" t="inlineStr">
         <is>
           <t>🟢 Assumptions tab</t>
         </is>
@@ -34974,7 +35209,7 @@
         <f>'Assumptions'!C10</f>
         <v/>
       </c>
-      <c r="D34" s="15" t="inlineStr">
+      <c r="D34" s="16" t="inlineStr">
         <is>
           <t>🟢 Assumptions tab</t>
         </is>
@@ -34995,11 +35230,11 @@
           <t>Cost of sale at exit</t>
         </is>
       </c>
-      <c r="C35" s="33">
+      <c r="C35" s="34">
         <f>'Assumptions'!C11</f>
         <v/>
       </c>
-      <c r="D35" s="15" t="inlineStr">
+      <c r="D35" s="16" t="inlineStr">
         <is>
           <t>🟢 Assumptions tab</t>
         </is>
@@ -35020,11 +35255,11 @@
           <t>Doc-stamp / transfer tax (% price)</t>
         </is>
       </c>
-      <c r="C36" s="36">
+      <c r="C36" s="37">
         <f>'Assumptions'!C21</f>
         <v/>
       </c>
-      <c r="D36" s="15" t="inlineStr">
+      <c r="D36" s="16" t="inlineStr">
         <is>
           <t>🟢 Assumptions tab</t>
         </is>
@@ -35045,11 +35280,11 @@
           <t>Title insurance (% price)</t>
         </is>
       </c>
-      <c r="C37" s="36">
+      <c r="C37" s="37">
         <f>'Assumptions'!C22</f>
         <v/>
       </c>
-      <c r="D37" s="15" t="inlineStr">
+      <c r="D37" s="16" t="inlineStr">
         <is>
           <t>🟢 Assumptions tab</t>
         </is>
@@ -35070,11 +35305,11 @@
           <t>Legal &amp; due diligence (% price)</t>
         </is>
       </c>
-      <c r="C38" s="36">
+      <c r="C38" s="37">
         <f>'Assumptions'!C23</f>
         <v/>
       </c>
-      <c r="D38" s="15" t="inlineStr">
+      <c r="D38" s="16" t="inlineStr">
         <is>
           <t>🟢 Assumptions tab</t>
         </is>
@@ -35095,11 +35330,11 @@
           <t>Loan origination fee (% loan)</t>
         </is>
       </c>
-      <c r="C39" s="36">
+      <c r="C39" s="37">
         <f>'Assumptions'!C24</f>
         <v/>
       </c>
-      <c r="D39" s="15" t="inlineStr">
+      <c r="D39" s="16" t="inlineStr">
         <is>
           <t>🟢 Assumptions tab</t>
         </is>
@@ -35120,11 +35355,11 @@
           <t>Max senior LTV</t>
         </is>
       </c>
-      <c r="C40" s="33">
+      <c r="C40" s="34">
         <f>'Assumptions'!C14</f>
         <v/>
       </c>
-      <c r="D40" s="15" t="inlineStr">
+      <c r="D40" s="16" t="inlineStr">
         <is>
           <t>🟢 Assumptions tab</t>
         </is>
@@ -35145,11 +35380,11 @@
           <t>Min DSCR (sizing constraint)</t>
         </is>
       </c>
-      <c r="C41" s="34">
+      <c r="C41" s="35">
         <f>'Assumptions'!C15</f>
         <v/>
       </c>
-      <c r="D41" s="15" t="inlineStr">
+      <c r="D41" s="16" t="inlineStr">
         <is>
           <t>🟢 Assumptions tab</t>
         </is>
@@ -35170,11 +35405,11 @@
           <t>Min debt yield (sizing constraint)</t>
         </is>
       </c>
-      <c r="C42" s="33">
+      <c r="C42" s="34">
         <f>'Assumptions'!C16</f>
         <v/>
       </c>
-      <c r="D42" s="15" t="inlineStr">
+      <c r="D42" s="16" t="inlineStr">
         <is>
           <t>🟢 Assumptions tab</t>
         </is>
@@ -35195,11 +35430,11 @@
           <t>Senior rate</t>
         </is>
       </c>
-      <c r="C43" s="36">
+      <c r="C43" s="37">
         <f>'Assumptions'!C17</f>
         <v/>
       </c>
-      <c r="D43" s="15" t="inlineStr">
+      <c r="D43" s="16" t="inlineStr">
         <is>
           <t>🟢 Assumptions tab</t>
         </is>
@@ -35224,7 +35459,7 @@
         <f>'Assumptions'!C18</f>
         <v/>
       </c>
-      <c r="D44" s="15" t="inlineStr">
+      <c r="D44" s="16" t="inlineStr">
         <is>
           <t>🟢 Assumptions tab</t>
         </is>
@@ -35279,7 +35514,7 @@
         <f>(C47/(1-(1+C47)^(-C44*12)))*12</f>
         <v/>
       </c>
-      <c r="D48" s="15" t="inlineStr">
+      <c r="D48" s="16" t="inlineStr">
         <is>
           <t>DS ÷ loan</t>
         </is>
@@ -35304,7 +35539,7 @@
         <f>C36+C37+C38</f>
         <v/>
       </c>
-      <c r="D49" s="15" t="inlineStr">
+      <c r="D49" s="16" t="inlineStr">
         <is>
           <t>doc stamps + title + legal/DD</t>
         </is>
@@ -35351,7 +35586,7 @@
         <f>INDEX(D22:M22,C34)</f>
         <v/>
       </c>
-      <c r="D52" s="15" t="inlineStr">
+      <c r="D52" s="16" t="inlineStr">
         <is>
           <t>sum of asset reversions</t>
         </is>
@@ -35395,7 +35630,7 @@
         <f>('Shahidi Retail'!C122/'Shahidi Retail'!C63)+('Publix &amp; Starbucks'!C110/'Publix &amp; Starbucks'!C50)+('Sunrise Plaza'!C113/'Sunrise Plaza'!C53)+('Office Condo'!C80/'Office Condo'!C34)+'Land'!C51</f>
         <v/>
       </c>
-      <c r="D55" s="15" t="inlineStr">
+      <c r="D55" s="16" t="inlineStr">
         <is>
           <t>reconciles to the asset tabs — the concluded income basis</t>
         </is>
@@ -35420,7 +35655,7 @@
         <f>C25/C55</f>
         <v/>
       </c>
-      <c r="D56" s="15" t="inlineStr">
+      <c r="D56" s="16" t="inlineStr">
         <is>
           <t>as-is NOI ÷ sum-of-parts value — the TRUE weighted cap (an output, not a guess)</t>
         </is>
@@ -35445,7 +35680,7 @@
         <f>C25/C30</f>
         <v/>
       </c>
-      <c r="D57" s="15" t="inlineStr">
+      <c r="D57" s="16" t="inlineStr">
         <is>
           <t>cross-check at the single blended-cap input — an alternative view, not the conclusion</t>
         </is>
@@ -35470,7 +35705,7 @@
         <f>C26/C31</f>
         <v/>
       </c>
-      <c r="D58" s="15" t="inlineStr">
+      <c r="D58" s="16" t="inlineStr">
         <is>
           <t>post lease-up</t>
         </is>
@@ -35542,7 +35777,7 @@
         <f>NPV(C32,D59:M59)</f>
         <v/>
       </c>
-      <c r="D60" s="15" t="inlineStr">
+      <c r="D60" s="16" t="inlineStr">
         <is>
           <t>price where unlevered IRR = target</t>
         </is>
@@ -35567,7 +35802,7 @@
         <f>C55</f>
         <v/>
       </c>
-      <c r="D61" s="15" t="inlineStr">
+      <c r="D61" s="16" t="inlineStr">
         <is>
           <t>sum of the parts — each asset at its own cap; reconciles to the components</t>
         </is>
@@ -35644,7 +35879,7 @@
         <f>MIN(C64,C65,C66)</f>
         <v/>
       </c>
-      <c r="D67" s="15">
+      <c r="D67" s="16">
         <f>IF(C67=C64,"LTV-constrained",IF(C67=C65,"DSCR-constrained","Debt-yield-constrained"))</f>
         <v/>
       </c>
@@ -35818,7 +36053,7 @@
       </c>
     </row>
     <row r="80" ht="15" customHeight="1">
-      <c r="B80" s="15" t="inlineStr">
+      <c r="B80" s="16" t="inlineStr">
         <is>
           <t>Check (sources − uses)</t>
         </is>
@@ -35827,7 +36062,7 @@
         <f>F79-C79</f>
         <v/>
       </c>
-      <c r="E80" s="15" t="inlineStr">
+      <c r="E80" s="16" t="inlineStr">
         <is>
           <t>Loan-to-cost (LTC)</t>
         </is>
@@ -35862,12 +36097,12 @@
           <t>Scenario</t>
         </is>
       </c>
-      <c r="C83" s="22" t="inlineStr">
+      <c r="C83" s="23" t="inlineStr">
         <is>
           <t>① Income price</t>
         </is>
       </c>
-      <c r="E83" s="22" t="inlineStr">
+      <c r="E83" s="23" t="inlineStr">
         <is>
           <t>② Covered-land (HBU)</t>
         </is>
@@ -35939,7 +36174,7 @@
       <c r="F87" s="9" t="n"/>
     </row>
     <row r="88" ht="15" customHeight="1">
-      <c r="B88" s="15" t="inlineStr">
+      <c r="B88" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  Unlevered CF ① (acq + valuation CF)</t>
         </is>
@@ -35990,7 +36225,7 @@
       </c>
     </row>
     <row r="89" ht="15" customHeight="1">
-      <c r="B89" s="15" t="inlineStr">
+      <c r="B89" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  Unlevered CF ② (acq + valuation CF)</t>
         </is>
@@ -36041,7 +36276,7 @@
       </c>
     </row>
     <row r="90" ht="15" customHeight="1">
-      <c r="B90" s="15" t="inlineStr">
+      <c r="B90" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  Levered CF ① (equity)</t>
         </is>
@@ -36092,7 +36327,7 @@
       </c>
     </row>
     <row r="91" ht="15" customHeight="1">
-      <c r="B91" s="15" t="inlineStr">
+      <c r="B91" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  Levered CF ② (equity)</t>
         </is>
@@ -36223,7 +36458,7 @@
       <c r="F96" s="9" t="n"/>
     </row>
     <row r="97" ht="15" customHeight="1">
-      <c r="B97" s="15" t="inlineStr">
+      <c r="B97" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  Cash-on-cash ① by year (levered)</t>
         </is>
@@ -36314,7 +36549,7 @@
         <f>'Assemblage'!C29-C61</f>
         <v/>
       </c>
-      <c r="D101" s="15" t="inlineStr">
+      <c r="D101" s="16" t="inlineStr">
         <is>
           <t>the dirt / optionality cost</t>
         </is>
@@ -36339,7 +36574,7 @@
         <f>((C61+C101)/C61)^(1/C34)-1</f>
         <v/>
       </c>
-      <c r="D102" s="15" t="inlineStr">
+      <c r="D102" s="16" t="inlineStr">
         <is>
           <t>annual land-value growth needed just to break even on the premium at exit</t>
         </is>
@@ -36355,12 +36590,12 @@
       <c r="M102" s="9" t="n"/>
     </row>
     <row r="103" ht="27" customHeight="1">
-      <c r="B103" s="37" t="inlineStr">
+      <c r="B103" s="15" t="inlineStr">
         <is>
           <t>Read</t>
         </is>
       </c>
-      <c r="D103" s="37" t="inlineStr">
+      <c r="D103" s="15" t="inlineStr">
         <is>
           <t>At the covered-land price the income IRR is thin — the return thesis is land appreciation / redevelopment, not current yield. The premium only pencils if land compounds at ≥ the rate above over the hold.</t>
         </is>
@@ -36483,7 +36718,7 @@
       </c>
     </row>
     <row r="114" ht="15" customHeight="1">
-      <c r="B114" s="15" t="inlineStr">
+      <c r="B114" s="16" t="inlineStr">
         <is>
           <t>Check: Σ unlevered cash flow (income scenario)</t>
         </is>
@@ -36492,7 +36727,7 @@
         <f>SUM(C88:M88)</f>
         <v/>
       </c>
-      <c r="D114" s="15" t="inlineStr">
+      <c r="D114" s="16" t="inlineStr">
         <is>
           <t>ties to unlevered profit above</t>
         </is>
@@ -36547,7 +36782,7 @@
         <f>C106*(1-C35)/(C86-C117+C69)</f>
         <v/>
       </c>
-      <c r="D118" s="15" t="inlineStr">
+      <c r="D118" s="16" t="inlineStr">
         <is>
           <t>max exit cap before levered equity &lt; 1.0x</t>
         </is>
@@ -36572,7 +36807,7 @@
         <f>C118-C31</f>
         <v/>
       </c>
-      <c r="D119" s="15" t="inlineStr">
+      <c r="D119" s="16" t="inlineStr">
         <is>
           <t>bps of exit-cap softening tolerable</t>
         </is>
@@ -36616,7 +36851,7 @@
         <f>C61</f>
         <v/>
       </c>
-      <c r="D122" s="15" t="inlineStr">
+      <c r="D122" s="16" t="inlineStr">
         <is>
           <t>what the combined cash flows support</t>
         </is>
@@ -36637,11 +36872,11 @@
           <t>HBU covered-land acquisition (Assemblage tab)</t>
         </is>
       </c>
-      <c r="C123" s="19">
+      <c r="C123" s="20">
         <f>'Assemblage'!C29</f>
         <v/>
       </c>
-      <c r="D123" s="15" t="inlineStr">
+      <c r="D123" s="16" t="inlineStr">
         <is>
           <t>land value + 20% assemblage premium to control</t>
         </is>
@@ -36657,12 +36892,12 @@
       <c r="M123" s="9" t="n"/>
     </row>
     <row r="124" ht="29" customHeight="1">
-      <c r="B124" s="20" t="inlineStr">
+      <c r="B124" s="21" t="inlineStr">
         <is>
           <t>PREMIUM OVER INCOME VALUE (dirt + optionality)</t>
         </is>
       </c>
-      <c r="C124" s="21">
+      <c r="C124" s="22">
         <f>C123-C122</f>
         <v/>
       </c>
@@ -36698,7 +36933,7 @@
       <c r="M127" s="3" t="n"/>
     </row>
     <row r="128" ht="15" customHeight="1">
-      <c r="B128" s="22" t="inlineStr">
+      <c r="B128" s="23" t="inlineStr">
         <is>
           <t>Cap  ╲  NOI</t>
         </is>
@@ -36864,7 +37099,7 @@
       <c r="M135" s="3" t="n"/>
     </row>
     <row r="136" ht="15" customHeight="1">
-      <c r="B136" s="22" t="inlineStr">
+      <c r="B136" s="23" t="inlineStr">
         <is>
           <t>Price ╲ exit cap</t>
         </is>
@@ -37012,12 +37247,12 @@
     </row>
     <row r="142"/>
     <row r="143" ht="25" customHeight="1">
-      <c r="B143" s="15" t="inlineStr">
+      <c r="B143" s="16" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
       </c>
-      <c r="D143" s="15" t="inlineStr">
+      <c r="D143" s="16" t="inlineStr">
         <is>
           <t>Sensitivity ② anchors the reversion to the ACTUAL consolidated exit proceeds (which include the Publix and Land land-value exits, not just an income cap), scaled by exit cap, and sizes debt lesser-of at each price; operating cash flows are held at the underwritten level. The base row/col reproduces the headline levered multiple. Green = higher.</t>
         </is>

--- a/Shahidi_Assemblage_Model.xlsx
+++ b/Shahidi_Assemblage_Model.xlsx
@@ -24,7 +24,7 @@
     <sheet name="Publix &amp; Starbucks" sheetId="15" state="visible" r:id="rId15"/>
     <sheet name="Sunrise Plaza" sheetId="16" state="visible" r:id="rId16"/>
     <sheet name="Office Condo" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="Land" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="Bayview JV" sheetId="18" state="visible" r:id="rId18"/>
     <sheet name="Notes &amp; Sources" sheetId="19" state="visible" r:id="rId19"/>
   </sheets>
   <definedNames/>
@@ -357,7 +357,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="111">
+  <cellXfs count="113">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -567,6 +567,12 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="11" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="7" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="1" fontId="4" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1043,7 +1049,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M58"/>
+  <dimension ref="A1:M59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -1146,7 +1152,7 @@
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>The rent supports about $65M (income basis); controlling the whole block costs about $127M (covered-land) — the gap is the land + density option.</t>
+          <t>The rent supports about $60M (income basis); controlling the four-parcel corner costs about $111M (covered-land) — the gap is the land + the density option.</t>
         </is>
       </c>
       <c r="D6" s="8" t="n"/>
@@ -1725,14 +1731,14 @@
     <row r="35" ht="15" customHeight="1">
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>Shahidi · Publix · Sunrise · Office · Land</t>
+          <t>Shahidi · Publix · Sunrise · Office</t>
         </is>
       </c>
       <c r="C35" s="8" t="n"/>
       <c r="D35" s="9" t="n"/>
       <c r="E35" s="7" t="inlineStr">
         <is>
-          <t>The full underwrite of each property — rent roll, cash flow, P&amp;L.</t>
+          <t>The full underwrite of each core property — rent roll, cash flow, P&amp;L.</t>
         </is>
       </c>
       <c r="F35" s="8" t="n"/>
@@ -1745,14 +1751,18 @@
       <c r="M35" s="9" t="n"/>
     </row>
     <row r="36" ht="15" customHeight="1">
-      <c r="B36" s="14" t="inlineStr">
-        <is>
-          <t>⑦ WHERE IT COMES FROM</t>
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>Bayview JV</t>
         </is>
       </c>
       <c r="C36" s="8" t="n"/>
-      <c r="D36" s="8" t="n"/>
-      <c r="E36" s="8" t="n"/>
+      <c r="D36" s="9" t="n"/>
+      <c r="E36" s="7" t="inlineStr">
+        <is>
+          <t>The 5th parcel — sold to Willow Bridge; modeled as a JV-upside case, not part of the core.</t>
+        </is>
+      </c>
       <c r="F36" s="8" t="n"/>
       <c r="G36" s="8" t="n"/>
       <c r="H36" s="8" t="n"/>
@@ -1763,18 +1773,14 @@
       <c r="M36" s="9" t="n"/>
     </row>
     <row r="37" ht="15" customHeight="1">
-      <c r="B37" s="6" t="inlineStr">
-        <is>
-          <t>Notes &amp; Sources</t>
+      <c r="B37" s="14" t="inlineStr">
+        <is>
+          <t>⑦ WHERE IT COMES FROM</t>
         </is>
       </c>
       <c r="C37" s="8" t="n"/>
-      <c r="D37" s="9" t="n"/>
-      <c r="E37" s="7" t="inlineStr">
-        <is>
-          <t>Where every number came from, what's verified vs. still to confirm, and the methodology.</t>
-        </is>
-      </c>
+      <c r="D37" s="8" t="n"/>
+      <c r="E37" s="8" t="n"/>
       <c r="F37" s="8" t="n"/>
       <c r="G37" s="8" t="n"/>
       <c r="H37" s="8" t="n"/>
@@ -1784,89 +1790,85 @@
       <c r="L37" s="8" t="n"/>
       <c r="M37" s="9" t="n"/>
     </row>
-    <row r="38"/>
-    <row r="39">
-      <c r="B39" s="5" t="inlineStr">
+    <row r="38" ht="15" customHeight="1">
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>Notes &amp; Sources</t>
+        </is>
+      </c>
+      <c r="C38" s="8" t="n"/>
+      <c r="D38" s="9" t="n"/>
+      <c r="E38" s="7" t="inlineStr">
+        <is>
+          <t>Where every number came from, what's verified vs. still to confirm, and the methodology.</t>
+        </is>
+      </c>
+      <c r="F38" s="8" t="n"/>
+      <c r="G38" s="8" t="n"/>
+      <c r="H38" s="8" t="n"/>
+      <c r="I38" s="8" t="n"/>
+      <c r="J38" s="8" t="n"/>
+      <c r="K38" s="8" t="n"/>
+      <c r="L38" s="8" t="n"/>
+      <c r="M38" s="9" t="n"/>
+    </row>
+    <row r="39"/>
+    <row r="40">
+      <c r="B40" s="5" t="inlineStr">
         <is>
           <t>PLAY WITH IT  —  it's a live model: change a BLUE cell and everything recalculates</t>
         </is>
       </c>
-      <c r="C39" s="2" t="n"/>
-      <c r="D39" s="2" t="n"/>
-      <c r="E39" s="2" t="n"/>
-      <c r="F39" s="2" t="n"/>
-      <c r="G39" s="2" t="n"/>
-      <c r="H39" s="2" t="n"/>
-      <c r="I39" s="2" t="n"/>
-      <c r="J39" s="2" t="n"/>
-      <c r="K39" s="2" t="n"/>
-      <c r="L39" s="2" t="n"/>
-      <c r="M39" s="3" t="n"/>
-    </row>
-    <row r="40" ht="15" customHeight="1">
-      <c r="B40" s="15" t="inlineStr">
+      <c r="C40" s="2" t="n"/>
+      <c r="D40" s="2" t="n"/>
+      <c r="E40" s="2" t="n"/>
+      <c r="F40" s="2" t="n"/>
+      <c r="G40" s="2" t="n"/>
+      <c r="H40" s="2" t="n"/>
+      <c r="I40" s="2" t="n"/>
+      <c r="J40" s="2" t="n"/>
+      <c r="K40" s="2" t="n"/>
+      <c r="L40" s="2" t="n"/>
+      <c r="M40" s="3" t="n"/>
+    </row>
+    <row r="41" ht="15" customHeight="1">
+      <c r="B41" s="15" t="inlineStr">
         <is>
           <t>Open it in Excel or Google Sheets (a preview is read-only). Blue cells are the only ones you touch — the rest updates on its own.</t>
         </is>
       </c>
-      <c r="C40" s="8" t="n"/>
-      <c r="D40" s="8" t="n"/>
-      <c r="E40" s="8" t="n"/>
-      <c r="F40" s="8" t="n"/>
-      <c r="G40" s="8" t="n"/>
-      <c r="H40" s="8" t="n"/>
-      <c r="I40" s="8" t="n"/>
-      <c r="J40" s="8" t="n"/>
-      <c r="K40" s="8" t="n"/>
-      <c r="L40" s="8" t="n"/>
-      <c r="M40" s="9" t="n"/>
-    </row>
-    <row r="41" ht="15" customHeight="1">
-      <c r="B41" s="14" t="inlineStr">
-        <is>
-          <t>To change…</t>
-        </is>
-      </c>
       <c r="C41" s="8" t="n"/>
-      <c r="D41" s="9" t="n"/>
-      <c r="E41" s="14" t="inlineStr">
-        <is>
-          <t>Go here and edit the blue cell</t>
-        </is>
-      </c>
+      <c r="D41" s="8" t="n"/>
+      <c r="E41" s="8" t="n"/>
       <c r="F41" s="8" t="n"/>
       <c r="G41" s="8" t="n"/>
       <c r="H41" s="8" t="n"/>
-      <c r="I41" s="9" t="n"/>
-      <c r="J41" s="14" t="inlineStr">
-        <is>
-          <t>…and watch this update</t>
-        </is>
-      </c>
+      <c r="I41" s="8" t="n"/>
+      <c r="J41" s="8" t="n"/>
       <c r="K41" s="8" t="n"/>
       <c r="L41" s="8" t="n"/>
       <c r="M41" s="9" t="n"/>
     </row>
     <row r="42" ht="15" customHeight="1">
-      <c r="B42" s="6" t="inlineStr">
-        <is>
-          <t>What you pay for an asset</t>
+      <c r="B42" s="14" t="inlineStr">
+        <is>
+          <t>To change…</t>
         </is>
       </c>
       <c r="C42" s="8" t="n"/>
       <c r="D42" s="9" t="n"/>
-      <c r="E42" s="7" t="inlineStr">
-        <is>
-          <t>Assumptions → that asset's block → 'Purchase price / basis'</t>
+      <c r="E42" s="14" t="inlineStr">
+        <is>
+          <t>Go here and edit the blue cell</t>
         </is>
       </c>
       <c r="F42" s="8" t="n"/>
       <c r="G42" s="8" t="n"/>
       <c r="H42" s="8" t="n"/>
       <c r="I42" s="9" t="n"/>
-      <c r="J42" s="16" t="inlineStr">
-        <is>
-          <t>income price, returns, Comps &amp; Pricing</t>
+      <c r="J42" s="14" t="inlineStr">
+        <is>
+          <t>…and watch this update</t>
         </is>
       </c>
       <c r="K42" s="8" t="n"/>
@@ -1876,14 +1878,14 @@
     <row r="43" ht="15" customHeight="1">
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>A cap rate</t>
+          <t>What you pay for an asset</t>
         </is>
       </c>
       <c r="C43" s="8" t="n"/>
       <c r="D43" s="9" t="n"/>
       <c r="E43" s="7" t="inlineStr">
         <is>
-          <t>Assumptions → 'Blended going-in cap' (or an asset's going-in / exit cap)</t>
+          <t>Assumptions → that asset's block → 'Purchase price / basis'</t>
         </is>
       </c>
       <c r="F43" s="8" t="n"/>
@@ -1892,7 +1894,7 @@
       <c r="I43" s="9" t="n"/>
       <c r="J43" s="16" t="inlineStr">
         <is>
-          <t>the value and the price</t>
+          <t>income price, returns, Comps &amp; Pricing</t>
         </is>
       </c>
       <c r="K43" s="8" t="n"/>
@@ -1902,14 +1904,14 @@
     <row r="44" ht="15" customHeight="1">
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>Rents</t>
+          <t>A cap rate</t>
         </is>
       </c>
       <c r="C44" s="8" t="n"/>
       <c r="D44" s="9" t="n"/>
       <c r="E44" s="7" t="inlineStr">
         <is>
-          <t>Assumptions → an asset's 'Market rent' (or the Publix leaseback rent)</t>
+          <t>Assumptions → 'Blended going-in cap' (or an asset's going-in / exit cap)</t>
         </is>
       </c>
       <c r="F44" s="8" t="n"/>
@@ -1918,7 +1920,7 @@
       <c r="I44" s="9" t="n"/>
       <c r="J44" s="16" t="inlineStr">
         <is>
-          <t>NOI → value → returns</t>
+          <t>the value and the price</t>
         </is>
       </c>
       <c r="K44" s="8" t="n"/>
@@ -1928,14 +1930,14 @@
     <row r="45" ht="15" customHeight="1">
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>How much you borrow</t>
+          <t>Rents</t>
         </is>
       </c>
       <c r="C45" s="8" t="n"/>
       <c r="D45" s="9" t="n"/>
       <c r="E45" s="7" t="inlineStr">
         <is>
-          <t>Assumptions → 'Max senior LTV' and 'Senior rate'</t>
+          <t>Assumptions → an asset's 'Market rent' (or the Publix leaseback rent)</t>
         </is>
       </c>
       <c r="F45" s="8" t="n"/>
@@ -1944,7 +1946,7 @@
       <c r="I45" s="9" t="n"/>
       <c r="J45" s="16" t="inlineStr">
         <is>
-          <t>debt, equity, DSCR, returns</t>
+          <t>NOI → value → returns</t>
         </is>
       </c>
       <c r="K45" s="8" t="n"/>
@@ -1954,14 +1956,14 @@
     <row r="46" ht="15" customHeight="1">
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>The assemblage premium</t>
+          <t>How much you borrow</t>
         </is>
       </c>
       <c r="C46" s="8" t="n"/>
       <c r="D46" s="9" t="n"/>
       <c r="E46" s="7" t="inlineStr">
         <is>
-          <t>Assumptions → 'Assemblage premium — base'</t>
+          <t>Assumptions → 'Max senior LTV' and 'Senior rate'</t>
         </is>
       </c>
       <c r="F46" s="8" t="n"/>
@@ -1970,7 +1972,7 @@
       <c r="I46" s="9" t="n"/>
       <c r="J46" s="16" t="inlineStr">
         <is>
-          <t>the covered-land price</t>
+          <t>debt, equity, DSCR, returns</t>
         </is>
       </c>
       <c r="K46" s="8" t="n"/>
@@ -1980,14 +1982,14 @@
     <row r="47" ht="15" customHeight="1">
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>The office buy-out price</t>
+          <t>The assemblage premium</t>
         </is>
       </c>
       <c r="C47" s="8" t="n"/>
       <c r="D47" s="9" t="n"/>
       <c r="E47" s="7" t="inlineStr">
         <is>
-          <t>Office Condo tab → 'Buy-out $/SF (unit market)'</t>
+          <t>Assumptions → 'Assemblage premium — base'</t>
         </is>
       </c>
       <c r="F47" s="8" t="n"/>
@@ -1996,7 +1998,7 @@
       <c r="I47" s="9" t="n"/>
       <c r="J47" s="16" t="inlineStr">
         <is>
-          <t>office price → covered-land</t>
+          <t>the covered-land price</t>
         </is>
       </c>
       <c r="K47" s="8" t="n"/>
@@ -2006,14 +2008,14 @@
     <row r="48" ht="15" customHeight="1">
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>A sensitivity (without touching the model)</t>
+          <t>The office buy-out price</t>
         </is>
       </c>
       <c r="C48" s="8" t="n"/>
       <c r="D48" s="9" t="n"/>
       <c r="E48" s="7" t="inlineStr">
         <is>
-          <t>Review Board → the blue axis cells on any grid</t>
+          <t>Office Condo tab → 'Buy-out $/SF (unit market)'</t>
         </is>
       </c>
       <c r="F48" s="8" t="n"/>
@@ -2022,7 +2024,7 @@
       <c r="I48" s="9" t="n"/>
       <c r="J48" s="16" t="inlineStr">
         <is>
-          <t>the grid + driver tornado, live</t>
+          <t>office price → covered-land</t>
         </is>
       </c>
       <c r="K48" s="8" t="n"/>
@@ -2032,14 +2034,14 @@
     <row r="49" ht="15" customHeight="1">
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>What you can afford</t>
+          <t>A sensitivity (without touching the model)</t>
         </is>
       </c>
       <c r="C49" s="8" t="n"/>
       <c r="D49" s="9" t="n"/>
       <c r="E49" s="7" t="inlineStr">
         <is>
-          <t>Capital Stack → 'Equity available'</t>
+          <t>Review Board → the blue axis cells on any grid</t>
         </is>
       </c>
       <c r="F49" s="8" t="n"/>
@@ -2048,86 +2050,90 @@
       <c r="I49" s="9" t="n"/>
       <c r="J49" s="16" t="inlineStr">
         <is>
-          <t>max price + assemblage capacity</t>
+          <t>the grid + driver tornado, live</t>
         </is>
       </c>
       <c r="K49" s="8" t="n"/>
       <c r="L49" s="8" t="n"/>
       <c r="M49" s="9" t="n"/>
     </row>
-    <row r="50"/>
-    <row r="51" ht="27" customHeight="1">
-      <c r="B51" s="6" t="inlineStr">
+    <row r="50" ht="15" customHeight="1">
+      <c r="B50" s="6" t="inlineStr">
+        <is>
+          <t>What you can afford</t>
+        </is>
+      </c>
+      <c r="C50" s="8" t="n"/>
+      <c r="D50" s="9" t="n"/>
+      <c r="E50" s="7" t="inlineStr">
+        <is>
+          <t>Capital Stack → 'Equity available'</t>
+        </is>
+      </c>
+      <c r="F50" s="8" t="n"/>
+      <c r="G50" s="8" t="n"/>
+      <c r="H50" s="8" t="n"/>
+      <c r="I50" s="9" t="n"/>
+      <c r="J50" s="16" t="inlineStr">
+        <is>
+          <t>max price + assemblage capacity</t>
+        </is>
+      </c>
+      <c r="K50" s="8" t="n"/>
+      <c r="L50" s="8" t="n"/>
+      <c r="M50" s="9" t="n"/>
+    </row>
+    <row r="51"/>
+    <row r="52" ht="27" customHeight="1">
+      <c r="B52" s="6" t="inlineStr">
         <is>
           <t>Confirming real data</t>
         </is>
       </c>
-      <c r="C51" s="8" t="n"/>
-      <c r="D51" s="9" t="n"/>
-      <c r="E51" s="7" t="inlineStr">
+      <c r="C52" s="8" t="n"/>
+      <c r="D52" s="9" t="n"/>
+      <c r="E52" s="7" t="inlineStr">
         <is>
           <t>As you get real facts (a sale price, a rent, a lender quote), put them in the overrides.json file and rebuild — it lists every gap and where to source it. Or just edit the blue cell directly and keep the file.</t>
         </is>
       </c>
-      <c r="F51" s="8" t="n"/>
-      <c r="G51" s="8" t="n"/>
-      <c r="H51" s="8" t="n"/>
-      <c r="I51" s="8" t="n"/>
-      <c r="J51" s="8" t="n"/>
-      <c r="K51" s="8" t="n"/>
-      <c r="L51" s="8" t="n"/>
-      <c r="M51" s="9" t="n"/>
-    </row>
-    <row r="52">
-      <c r="B52" s="5" t="inlineStr">
+      <c r="F52" s="8" t="n"/>
+      <c r="G52" s="8" t="n"/>
+      <c r="H52" s="8" t="n"/>
+      <c r="I52" s="8" t="n"/>
+      <c r="J52" s="8" t="n"/>
+      <c r="K52" s="8" t="n"/>
+      <c r="L52" s="8" t="n"/>
+      <c r="M52" s="9" t="n"/>
+    </row>
+    <row r="53">
+      <c r="B53" s="5" t="inlineStr">
         <is>
           <t>THE COLOR CODE</t>
         </is>
       </c>
-      <c r="C52" s="2" t="n"/>
-      <c r="D52" s="2" t="n"/>
-      <c r="E52" s="2" t="n"/>
-      <c r="F52" s="2" t="n"/>
-      <c r="G52" s="2" t="n"/>
-      <c r="H52" s="2" t="n"/>
-      <c r="I52" s="2" t="n"/>
-      <c r="J52" s="2" t="n"/>
-      <c r="K52" s="2" t="n"/>
-      <c r="L52" s="2" t="n"/>
-      <c r="M52" s="3" t="n"/>
-    </row>
-    <row r="53" ht="15" customHeight="1">
-      <c r="B53" s="6" t="inlineStr">
-        <is>
-          <t>Blue on yellow</t>
-        </is>
-      </c>
-      <c r="C53" s="9" t="n"/>
-      <c r="D53" s="7" t="inlineStr">
-        <is>
-          <t>an input — the only cells you change</t>
-        </is>
-      </c>
-      <c r="E53" s="8" t="n"/>
-      <c r="F53" s="8" t="n"/>
-      <c r="G53" s="8" t="n"/>
-      <c r="H53" s="8" t="n"/>
-      <c r="I53" s="8" t="n"/>
-      <c r="J53" s="8" t="n"/>
-      <c r="K53" s="8" t="n"/>
-      <c r="L53" s="8" t="n"/>
-      <c r="M53" s="9" t="n"/>
+      <c r="C53" s="2" t="n"/>
+      <c r="D53" s="2" t="n"/>
+      <c r="E53" s="2" t="n"/>
+      <c r="F53" s="2" t="n"/>
+      <c r="G53" s="2" t="n"/>
+      <c r="H53" s="2" t="n"/>
+      <c r="I53" s="2" t="n"/>
+      <c r="J53" s="2" t="n"/>
+      <c r="K53" s="2" t="n"/>
+      <c r="L53" s="2" t="n"/>
+      <c r="M53" s="3" t="n"/>
     </row>
     <row r="54" ht="15" customHeight="1">
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>Black</t>
+          <t>Blue on yellow</t>
         </is>
       </c>
       <c r="C54" s="9" t="n"/>
       <c r="D54" s="7" t="inlineStr">
         <is>
-          <t>a formula / calculation (leave it)</t>
+          <t>an input — the only cells you change</t>
         </is>
       </c>
       <c r="E54" s="8" t="n"/>
@@ -2143,13 +2149,13 @@
     <row r="55" ht="15" customHeight="1">
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>Green</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="C55" s="9" t="n"/>
       <c r="D55" s="7" t="inlineStr">
         <is>
-          <t>a verified fact, or a live link pulling from another tab</t>
+          <t>a formula / calculation (leave it)</t>
         </is>
       </c>
       <c r="E55" s="8" t="n"/>
@@ -2165,13 +2171,13 @@
     <row r="56" ht="15" customHeight="1">
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>Gold on navy</t>
+          <t>Green</t>
         </is>
       </c>
       <c r="C56" s="9" t="n"/>
       <c r="D56" s="7" t="inlineStr">
         <is>
-          <t>a header, total, or key number</t>
+          <t>a verified fact, or a live link pulling from another tab</t>
         </is>
       </c>
       <c r="E56" s="8" t="n"/>
@@ -2187,13 +2193,13 @@
     <row r="57" ht="15" customHeight="1">
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t>Orange</t>
+          <t>Gold on navy</t>
         </is>
       </c>
       <c r="C57" s="9" t="n"/>
       <c r="D57" s="7" t="inlineStr">
         <is>
-          <t>a warning, a flag, or something to confirm</t>
+          <t>a header, total, or key number</t>
         </is>
       </c>
       <c r="E57" s="8" t="n"/>
@@ -2209,13 +2215,13 @@
     <row r="58" ht="15" customHeight="1">
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t>Confidence</t>
+          <t>Orange</t>
         </is>
       </c>
       <c r="C58" s="9" t="n"/>
-      <c r="D58" s="16" t="inlineStr">
-        <is>
-          <t>✅ verified (public record)   ·   ⚠️ reported (confirm at the county)   ·   🔶 modeled (a market assumption)</t>
+      <c r="D58" s="7" t="inlineStr">
+        <is>
+          <t>a warning, a flag, or something to confirm</t>
         </is>
       </c>
       <c r="E58" s="8" t="n"/>
@@ -2228,21 +2234,45 @@
       <c r="L58" s="8" t="n"/>
       <c r="M58" s="9" t="n"/>
     </row>
+    <row r="59" ht="15" customHeight="1">
+      <c r="B59" s="6" t="inlineStr">
+        <is>
+          <t>Confidence</t>
+        </is>
+      </c>
+      <c r="C59" s="9" t="n"/>
+      <c r="D59" s="16" t="inlineStr">
+        <is>
+          <t>✅ verified (public record)   ·   ⚠️ reported (confirm at the county)   ·   🔶 modeled (a market assumption)</t>
+        </is>
+      </c>
+      <c r="E59" s="8" t="n"/>
+      <c r="F59" s="8" t="n"/>
+      <c r="G59" s="8" t="n"/>
+      <c r="H59" s="8" t="n"/>
+      <c r="I59" s="8" t="n"/>
+      <c r="J59" s="8" t="n"/>
+      <c r="K59" s="8" t="n"/>
+      <c r="L59" s="8" t="n"/>
+      <c r="M59" s="9" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="103">
+  <mergeCells count="105">
     <mergeCell ref="B11:D11"/>
     <mergeCell ref="B2:M2"/>
     <mergeCell ref="B42:D42"/>
     <mergeCell ref="C6:M6"/>
     <mergeCell ref="J43:M43"/>
     <mergeCell ref="B44:D44"/>
+    <mergeCell ref="B53:M53"/>
     <mergeCell ref="H11:J11"/>
     <mergeCell ref="E48:I48"/>
     <mergeCell ref="J42:M42"/>
     <mergeCell ref="B34:M34"/>
-    <mergeCell ref="B37:D37"/>
     <mergeCell ref="B28:M28"/>
     <mergeCell ref="E27:M27"/>
+    <mergeCell ref="B37:M37"/>
+    <mergeCell ref="E36:M36"/>
     <mergeCell ref="B30:D30"/>
     <mergeCell ref="J44:M44"/>
     <mergeCell ref="B20:D20"/>
@@ -2253,6 +2283,8 @@
     <mergeCell ref="B55:C55"/>
     <mergeCell ref="B43:D43"/>
     <mergeCell ref="K11:M11"/>
+    <mergeCell ref="E38:M38"/>
+    <mergeCell ref="E50:I50"/>
     <mergeCell ref="J47:M47"/>
     <mergeCell ref="E42:I42"/>
     <mergeCell ref="B17:D17"/>
@@ -2264,8 +2296,8 @@
     <mergeCell ref="B19:D19"/>
     <mergeCell ref="D54:M54"/>
     <mergeCell ref="B9:M9"/>
-    <mergeCell ref="B53:C53"/>
     <mergeCell ref="E25:M25"/>
+    <mergeCell ref="B36:D36"/>
     <mergeCell ref="B45:D45"/>
     <mergeCell ref="E46:I46"/>
     <mergeCell ref="E18:M18"/>
@@ -2274,11 +2306,10 @@
     <mergeCell ref="J49:M49"/>
     <mergeCell ref="B31:D31"/>
     <mergeCell ref="B46:D46"/>
-    <mergeCell ref="E41:I41"/>
+    <mergeCell ref="E52:M52"/>
     <mergeCell ref="B21:M21"/>
     <mergeCell ref="E47:I47"/>
     <mergeCell ref="B48:D48"/>
-    <mergeCell ref="B39:M39"/>
     <mergeCell ref="E20:M20"/>
     <mergeCell ref="E10:G10"/>
     <mergeCell ref="E29:M29"/>
@@ -2294,12 +2325,11 @@
     <mergeCell ref="E11:G11"/>
     <mergeCell ref="J48:M48"/>
     <mergeCell ref="B49:D49"/>
+    <mergeCell ref="D59:M59"/>
     <mergeCell ref="B57:C57"/>
-    <mergeCell ref="B51:D51"/>
     <mergeCell ref="E32:M32"/>
-    <mergeCell ref="B41:D41"/>
     <mergeCell ref="B35:D35"/>
-    <mergeCell ref="B36:M36"/>
+    <mergeCell ref="B50:D50"/>
     <mergeCell ref="E12:G12"/>
     <mergeCell ref="E45:I45"/>
     <mergeCell ref="B25:D25"/>
@@ -2313,26 +2343,26 @@
     <mergeCell ref="E35:M35"/>
     <mergeCell ref="E19:M19"/>
     <mergeCell ref="D56:M56"/>
+    <mergeCell ref="B59:C59"/>
     <mergeCell ref="B14:M14"/>
+    <mergeCell ref="J50:M50"/>
     <mergeCell ref="B1:M1"/>
     <mergeCell ref="B29:D29"/>
+    <mergeCell ref="B38:D38"/>
     <mergeCell ref="E30:M30"/>
     <mergeCell ref="H12:J12"/>
     <mergeCell ref="B40:M40"/>
     <mergeCell ref="B15:D15"/>
     <mergeCell ref="B24:D24"/>
     <mergeCell ref="B33:D33"/>
-    <mergeCell ref="E37:M37"/>
     <mergeCell ref="B32:D32"/>
     <mergeCell ref="E49:I49"/>
     <mergeCell ref="B26:M26"/>
+    <mergeCell ref="B41:M41"/>
     <mergeCell ref="B16:M16"/>
     <mergeCell ref="B18:D18"/>
     <mergeCell ref="B27:D27"/>
-    <mergeCell ref="D53:M53"/>
-    <mergeCell ref="B52:M52"/>
-    <mergeCell ref="J41:M41"/>
-    <mergeCell ref="E51:M51"/>
+    <mergeCell ref="B52:D52"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
@@ -2347,7 +2377,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M61"/>
+  <dimension ref="A1:M62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.5" customWidth="1" min="1" max="1"/>
@@ -2676,7 +2706,7 @@
           <t>Shahidi Retail — Shawnick Galleria LLC (Shahidi)</t>
         </is>
       </c>
-      <c r="C16" s="88" t="inlineStr">
+      <c r="C16" s="90" t="inlineStr">
         <is>
           <t>11/09/2021</t>
         </is>
@@ -2708,7 +2738,7 @@
           <t>Publix + Starbucks — REAL SUB LLC (Publix)</t>
         </is>
       </c>
-      <c r="C17" s="88" t="inlineStr">
+      <c r="C17" s="90" t="inlineStr">
         <is>
           <t>03/14/2025</t>
         </is>
@@ -2809,12 +2839,12 @@
           <t>2011→2026</t>
         </is>
       </c>
-      <c r="D20" s="89" t="inlineStr">
+      <c r="D20" s="91" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E20" s="89" t="inlineStr">
+      <c r="E20" s="91" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -2838,7 +2868,7 @@
           <t>1040 Bayview — SOLD to Willow Bridge (~Aug 2026)</t>
         </is>
       </c>
-      <c r="C21" s="88" t="inlineStr">
+      <c r="C21" s="90" t="inlineStr">
         <is>
           <t>8/2026</t>
         </is>
@@ -2847,7 +2877,7 @@
         <f>'Assumptions'!C35</f>
         <v/>
       </c>
-      <c r="E21" s="89" t="inlineStr">
+      <c r="E21" s="91" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -2924,7 +2954,7 @@
           <t>Shahidi Retail</t>
         </is>
       </c>
-      <c r="C25" s="85">
+      <c r="C25" s="87">
         <f>'Shahidi Retail'!C36</f>
         <v/>
       </c>
@@ -2955,7 +2985,7 @@
           <t>Publix + Starbucks</t>
         </is>
       </c>
-      <c r="C26" s="85">
+      <c r="C26" s="87">
         <f>'Publix &amp; Starbucks'!C25</f>
         <v/>
       </c>
@@ -2986,7 +3016,7 @@
           <t>Sunrise Plaza (Kar Luen)</t>
         </is>
       </c>
-      <c r="C27" s="85">
+      <c r="C27" s="87">
         <f>'Sunrise Plaza'!C28</f>
         <v/>
       </c>
@@ -3017,15 +3047,15 @@
           <t>SUM OF THE PARTS  (fragmented land)</t>
         </is>
       </c>
-      <c r="C28" s="90">
+      <c r="C28" s="92">
         <f>SUM(C25:C27)</f>
         <v/>
       </c>
-      <c r="D28" s="91">
+      <c r="D28" s="93">
         <f>SUM(E25:E27)/SUM(C25:C27)</f>
         <v/>
       </c>
-      <c r="E28" s="92">
+      <c r="E28" s="94">
         <f>SUM(E25:E27)</f>
         <v/>
       </c>
@@ -3343,7 +3373,7 @@
     <row r="46">
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>④  REDEVELOPMENT — LIVE LOCAL RESIDUAL  (assemblage scale · ⚠️ negative → HOLD)</t>
+          <t>④  REDEVELOPMENT — QUICK RESIDUAL CHECK  (⚠️ negative → HOLD · full pro forma on the DEVELOPMENT PRO FORMA tab)</t>
         </is>
       </c>
       <c r="C46" s="2" t="n"/>
@@ -3359,20 +3389,18 @@
       <c r="M46" s="3" t="n"/>
     </row>
     <row r="47" ht="15" customHeight="1">
-      <c r="B47" s="7" t="inlineStr">
-        <is>
-          <t>Buildable density (units/acre)</t>
-        </is>
-      </c>
-      <c r="C47" s="45" t="n">
-        <v>100</v>
-      </c>
-      <c r="D47" s="16" t="inlineStr">
-        <is>
-          <t>🔵 Live Local target</t>
-        </is>
-      </c>
-      <c r="E47" s="8" t="n"/>
+      <c r="B47" s="16" t="inlineStr">
+        <is>
+          <t>→ See the DEVELOPMENT PRO FORMA tab for the full vision</t>
+        </is>
+      </c>
+      <c r="C47" s="8" t="n"/>
+      <c r="D47" s="9" t="n"/>
+      <c r="E47" s="16" t="inlineStr">
+        <is>
+          <t>density · product · cost stack · rental vs condo · residual land value · sensitivity</t>
+        </is>
+      </c>
       <c r="F47" s="8" t="n"/>
       <c r="G47" s="8" t="n"/>
       <c r="H47" s="8" t="n"/>
@@ -3385,18 +3413,18 @@
     <row r="48" ht="15" customHeight="1">
       <c r="B48" s="7" t="inlineStr">
         <is>
-          <t>Assemblage buildable units</t>
-        </is>
-      </c>
-      <c r="C48" s="48">
-        <f>C28/43560*C47</f>
-        <v/>
-      </c>
-      <c r="E48" s="16" t="inlineStr">
-        <is>
-          <t>acres × density</t>
-        </is>
-      </c>
+          <t>Buildable density (units/acre)</t>
+        </is>
+      </c>
+      <c r="C48" s="45" t="n">
+        <v>100</v>
+      </c>
+      <c r="D48" s="16" t="inlineStr">
+        <is>
+          <t>🔵 Live Local target</t>
+        </is>
+      </c>
+      <c r="E48" s="8" t="n"/>
       <c r="F48" s="8" t="n"/>
       <c r="G48" s="8" t="n"/>
       <c r="H48" s="8" t="n"/>
@@ -3409,16 +3437,16 @@
     <row r="49" ht="15" customHeight="1">
       <c r="B49" s="7" t="inlineStr">
         <is>
-          <t>Gross development value (GDV)</t>
-        </is>
-      </c>
-      <c r="C49" s="57">
-        <f>C48*'Assumptions'!C51</f>
+          <t>Assemblage buildable units</t>
+        </is>
+      </c>
+      <c r="C49" s="48">
+        <f>C28/43560*C48</f>
         <v/>
       </c>
       <c r="E49" s="16" t="inlineStr">
         <is>
-          <t>units × achievable value/unit (Assumptions)</t>
+          <t>acres × density</t>
         </is>
       </c>
       <c r="F49" s="8" t="n"/>
@@ -3433,125 +3461,131 @@
     <row r="50" ht="15" customHeight="1">
       <c r="B50" s="7" t="inlineStr">
         <is>
-          <t>Buildable GBA (SF)</t>
-        </is>
-      </c>
-      <c r="C50" s="48">
-        <f>C48*'Assumptions'!C53</f>
-        <v/>
-      </c>
+          <t>Gross development value (GDV)</t>
+        </is>
+      </c>
+      <c r="C50" s="57">
+        <f>C49*'Assumptions'!C51</f>
+        <v/>
+      </c>
+      <c r="E50" s="16" t="inlineStr">
+        <is>
+          <t>units × achievable value/unit (Assumptions)</t>
+        </is>
+      </c>
+      <c r="F50" s="8" t="n"/>
+      <c r="G50" s="8" t="n"/>
+      <c r="H50" s="8" t="n"/>
+      <c r="I50" s="8" t="n"/>
+      <c r="J50" s="8" t="n"/>
+      <c r="K50" s="8" t="n"/>
+      <c r="L50" s="8" t="n"/>
+      <c r="M50" s="9" t="n"/>
     </row>
     <row r="51" ht="15" customHeight="1">
       <c r="B51" s="7" t="inlineStr">
         <is>
-          <t>− Hard cost</t>
-        </is>
-      </c>
-      <c r="C51" s="53">
-        <f>-C50*'Assumptions'!C52</f>
+          <t>Buildable GBA (SF)</t>
+        </is>
+      </c>
+      <c r="C51" s="48">
+        <f>C49*'Assumptions'!C53</f>
         <v/>
       </c>
     </row>
     <row r="52" ht="15" customHeight="1">
       <c r="B52" s="7" t="inlineStr">
         <is>
-          <t>− Soft cost</t>
+          <t>− Hard cost</t>
         </is>
       </c>
       <c r="C52" s="53">
-        <f>-C50*'Assumptions'!C52*'Assumptions'!C54</f>
+        <f>-C51*'Assumptions'!C52</f>
         <v/>
       </c>
     </row>
     <row r="53" ht="15" customHeight="1">
       <c r="B53" s="7" t="inlineStr">
         <is>
+          <t>− Soft cost</t>
+        </is>
+      </c>
+      <c r="C53" s="53">
+        <f>-C51*'Assumptions'!C52*'Assumptions'!C54</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54" ht="15" customHeight="1">
+      <c r="B54" s="7" t="inlineStr">
+        <is>
           <t>− Developer profit</t>
         </is>
       </c>
-      <c r="C53" s="53">
-        <f>-C49*'Assumptions'!C55</f>
-        <v/>
-      </c>
-    </row>
-    <row r="54" ht="16" customHeight="1">
-      <c r="B54" s="21" t="inlineStr">
+      <c r="C54" s="53">
+        <f>-C50*'Assumptions'!C55</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55" ht="16" customHeight="1">
+      <c r="B55" s="21" t="inlineStr">
         <is>
           <t>RESIDUAL LAND VALUE (supports acquisition?)</t>
         </is>
       </c>
-      <c r="C54" s="22">
-        <f>C49+C51-C50*'Assumptions'!C52*'Assumptions'!C54-C49*'Assumptions'!C55</f>
-        <v/>
-      </c>
-    </row>
-    <row r="55" ht="27" customHeight="1">
-      <c r="B55" s="15" t="inlineStr">
+      <c r="C55" s="22">
+        <f>C50+C52-C51*'Assumptions'!C52*'Assumptions'!C54-C50*'Assumptions'!C55</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56" ht="27" customHeight="1">
+      <c r="B56" s="15" t="inlineStr">
         <is>
           <t>HBU verdict</t>
         </is>
       </c>
-      <c r="C55" s="63" t="inlineStr">
+      <c r="C56" s="63" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="D55" s="15" t="inlineStr">
+      <c r="D56" s="15" t="inlineStr">
         <is>
           <t>Residual runs NEGATIVE at coastal AE-zone hard costs — redevelopment does not pencil today. Highest &amp; best use = acquire and HOLD the income-covered assemblage; redevelop when achievable rents / hard costs support Live Local density.</t>
         </is>
       </c>
-      <c r="E55" s="8" t="n"/>
-      <c r="F55" s="8" t="n"/>
-      <c r="G55" s="8" t="n"/>
-      <c r="H55" s="8" t="n"/>
-      <c r="I55" s="8" t="n"/>
-      <c r="J55" s="8" t="n"/>
-      <c r="K55" s="8" t="n"/>
-      <c r="L55" s="8" t="n"/>
-      <c r="M55" s="9" t="n"/>
-    </row>
-    <row r="56"/>
-    <row r="57">
-      <c r="B57" s="5" t="inlineStr">
+      <c r="E56" s="8" t="n"/>
+      <c r="F56" s="8" t="n"/>
+      <c r="G56" s="8" t="n"/>
+      <c r="H56" s="8" t="n"/>
+      <c r="I56" s="8" t="n"/>
+      <c r="J56" s="8" t="n"/>
+      <c r="K56" s="8" t="n"/>
+      <c r="L56" s="8" t="n"/>
+      <c r="M56" s="9" t="n"/>
+    </row>
+    <row r="57"/>
+    <row r="58">
+      <c r="B58" s="5" t="inlineStr">
         <is>
           <t>⑤  CONCLUSION</t>
         </is>
       </c>
-      <c r="C57" s="2" t="n"/>
-      <c r="D57" s="2" t="n"/>
-      <c r="E57" s="2" t="n"/>
-      <c r="F57" s="2" t="n"/>
-      <c r="G57" s="2" t="n"/>
-      <c r="H57" s="2" t="n"/>
-      <c r="I57" s="2" t="n"/>
-      <c r="J57" s="2" t="n"/>
-      <c r="K57" s="2" t="n"/>
-      <c r="L57" s="2" t="n"/>
-      <c r="M57" s="3" t="n"/>
-    </row>
-    <row r="58" ht="15" customHeight="1">
-      <c r="B58" s="7" t="inlineStr">
-        <is>
-          <t>• Priced independently, the components sum to ~$86M; as an assemblage (base premium) ~$103M — the premium is the cost of controlling</t>
-        </is>
-      </c>
-      <c r="C58" s="8" t="n"/>
-      <c r="D58" s="8" t="n"/>
-      <c r="E58" s="8" t="n"/>
-      <c r="F58" s="8" t="n"/>
-      <c r="G58" s="8" t="n"/>
-      <c r="H58" s="8" t="n"/>
-      <c r="I58" s="8" t="n"/>
-      <c r="J58" s="8" t="n"/>
-      <c r="K58" s="8" t="n"/>
-      <c r="L58" s="8" t="n"/>
-      <c r="M58" s="9" t="n"/>
+      <c r="C58" s="2" t="n"/>
+      <c r="D58" s="2" t="n"/>
+      <c r="E58" s="2" t="n"/>
+      <c r="F58" s="2" t="n"/>
+      <c r="G58" s="2" t="n"/>
+      <c r="H58" s="2" t="n"/>
+      <c r="I58" s="2" t="n"/>
+      <c r="J58" s="2" t="n"/>
+      <c r="K58" s="2" t="n"/>
+      <c r="L58" s="2" t="n"/>
+      <c r="M58" s="3" t="n"/>
     </row>
     <row r="59" ht="15" customHeight="1">
       <c r="B59" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">  a contiguous block held by five owners (a sale-leaseback, a fractured condo, and holdout risk).</t>
+          <t>• Priced independently, the components sum to ~$86M; as an assemblage (base premium) ~$103M — the premium is the cost of controlling</t>
         </is>
       </c>
       <c r="C59" s="8" t="n"/>
@@ -3569,7 +3603,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="B60" s="7" t="inlineStr">
         <is>
-          <t>• The land alone is worth more assembled (plottage) than as fragmented parcels — but redevelopment does not yet pencil, so the</t>
+          <t xml:space="preserve">  a contiguous block held by five owners (a sale-leaseback, a fractured condo, and holdout risk).</t>
         </is>
       </c>
       <c r="C60" s="8" t="n"/>
@@ -3587,7 +3621,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="B61" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">  return today is income-covered land banking, with the Live Local density as the option you are paying the premium to hold.</t>
+          <t>• The land alone is worth more assembled (plottage) than as fragmented parcels — but redevelopment does not yet pencil, so the</t>
         </is>
       </c>
       <c r="C61" s="8" t="n"/>
@@ -3602,10 +3636,29 @@
       <c r="L61" s="8" t="n"/>
       <c r="M61" s="9" t="n"/>
     </row>
+    <row r="62" ht="15" customHeight="1">
+      <c r="B62" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  return today is income-covered land banking, with the Live Local density as the option you are paying the premium to hold.</t>
+        </is>
+      </c>
+      <c r="C62" s="8" t="n"/>
+      <c r="D62" s="8" t="n"/>
+      <c r="E62" s="8" t="n"/>
+      <c r="F62" s="8" t="n"/>
+      <c r="G62" s="8" t="n"/>
+      <c r="H62" s="8" t="n"/>
+      <c r="I62" s="8" t="n"/>
+      <c r="J62" s="8" t="n"/>
+      <c r="K62" s="8" t="n"/>
+      <c r="L62" s="8" t="n"/>
+      <c r="M62" s="9" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="46">
+  <mergeCells count="48">
     <mergeCell ref="B2:M2"/>
     <mergeCell ref="E10:M10"/>
+    <mergeCell ref="D56:M56"/>
     <mergeCell ref="B60:M60"/>
     <mergeCell ref="F19:M19"/>
     <mergeCell ref="B23:M23"/>
@@ -3615,8 +3668,6 @@
     <mergeCell ref="B61:M61"/>
     <mergeCell ref="E9:M9"/>
     <mergeCell ref="B1:M1"/>
-    <mergeCell ref="D55:M55"/>
-    <mergeCell ref="B57:M57"/>
     <mergeCell ref="B29:M29"/>
     <mergeCell ref="E6:M6"/>
     <mergeCell ref="E30:M30"/>
@@ -3636,18 +3687,21 @@
     <mergeCell ref="E37:M37"/>
     <mergeCell ref="F28:M28"/>
     <mergeCell ref="B41:M41"/>
+    <mergeCell ref="E47:M47"/>
     <mergeCell ref="B4:M4"/>
     <mergeCell ref="E12:M12"/>
     <mergeCell ref="F27:M27"/>
     <mergeCell ref="E43:M43"/>
+    <mergeCell ref="B47:D47"/>
+    <mergeCell ref="E50:M50"/>
+    <mergeCell ref="B62:M62"/>
     <mergeCell ref="B59:M59"/>
     <mergeCell ref="E5:M5"/>
     <mergeCell ref="E42:M42"/>
+    <mergeCell ref="D48:M48"/>
     <mergeCell ref="B46:M46"/>
-    <mergeCell ref="E48:M48"/>
     <mergeCell ref="E39:M39"/>
     <mergeCell ref="E8:M8"/>
-    <mergeCell ref="D47:M47"/>
     <mergeCell ref="B58:M58"/>
     <mergeCell ref="E38:M38"/>
   </mergeCells>
@@ -3819,12 +3873,12 @@
         <v/>
       </c>
       <c r="K6" s="3" t="n"/>
-      <c r="L6" s="93">
+      <c r="L6" s="95">
         <f>'Income Valuation'!C94</f>
         <v/>
       </c>
       <c r="M6" s="3" t="n"/>
-      <c r="N6" s="93">
+      <c r="N6" s="95">
         <f>'Income Valuation'!C95</f>
         <v/>
       </c>
@@ -3886,7 +3940,7 @@
           <t>Blended going-in cap (as-is)</t>
         </is>
       </c>
-      <c r="D10" s="94">
+      <c r="D10" s="96">
         <f>'Assumptions'!C6</f>
         <v/>
       </c>
@@ -3910,7 +3964,7 @@
           <t>Stabilized / exit cap</t>
         </is>
       </c>
-      <c r="D11" s="94">
+      <c r="D11" s="96">
         <f>'Assumptions'!C7</f>
         <v/>
       </c>
@@ -3958,7 +4012,7 @@
           <t>Senior rate</t>
         </is>
       </c>
-      <c r="D13" s="94">
+      <c r="D13" s="96">
         <f>'Assumptions'!C17</f>
         <v/>
       </c>
@@ -4258,23 +4312,23 @@
           <t xml:space="preserve">  EM</t>
         </is>
       </c>
-      <c r="D30" s="81">
+      <c r="D30" s="83">
         <f>('Income Valuation'!C49-'Income Valuation'!C33*'Income Valuation'!C67+('Income Valuation'!C51*'Income Valuation'!C30/D29)-'Income Valuation'!C68)/'Income Valuation'!C85</f>
         <v/>
       </c>
-      <c r="E30" s="81">
+      <c r="E30" s="83">
         <f>('Income Valuation'!C49-'Income Valuation'!C33*'Income Valuation'!C67+('Income Valuation'!C51*'Income Valuation'!C30/E29)-'Income Valuation'!C68)/'Income Valuation'!C85</f>
         <v/>
       </c>
-      <c r="F30" s="81">
+      <c r="F30" s="83">
         <f>('Income Valuation'!C49-'Income Valuation'!C33*'Income Valuation'!C67+('Income Valuation'!C51*'Income Valuation'!C30/F29)-'Income Valuation'!C68)/'Income Valuation'!C85</f>
         <v/>
       </c>
-      <c r="G30" s="81">
+      <c r="G30" s="83">
         <f>('Income Valuation'!C49-'Income Valuation'!C33*'Income Valuation'!C67+('Income Valuation'!C51*'Income Valuation'!C30/G29)-'Income Valuation'!C68)/'Income Valuation'!C85</f>
         <v/>
       </c>
-      <c r="H30" s="81">
+      <c r="H30" s="83">
         <f>('Income Valuation'!C49-'Income Valuation'!C33*'Income Valuation'!C67+('Income Valuation'!C51*'Income Valuation'!C30/H29)-'Income Valuation'!C68)/'Income Valuation'!C85</f>
         <v/>
       </c>
@@ -4324,23 +4378,23 @@
       <c r="B34" s="70" t="n">
         <v>60000000</v>
       </c>
-      <c r="D34" s="81">
+      <c r="D34" s="83">
         <f>('Income Valuation'!C49-'Income Valuation'!C33*(MIN(B34*'Income Valuation'!C39,'Income Valuation'!C64,'Income Valuation'!C65)*'Income Valuation'!C47)+('Income Valuation'!C51*'Income Valuation'!C30/D33)-(MIN(B34*'Income Valuation'!C39,'Income Valuation'!C64,'Income Valuation'!C65)*(1+'Income Valuation'!C46)^(12*'Income Valuation'!C33)-((MIN(B34*'Income Valuation'!C39,'Income Valuation'!C64,'Income Valuation'!C65)*'Income Valuation'!C47)/12)*((1+'Income Valuation'!C46)^(12*'Income Valuation'!C33)-1)/'Income Valuation'!C46))/(B34*(1+'Income Valuation'!C48)-MIN(B34*'Income Valuation'!C39,'Income Valuation'!C64,'Income Valuation'!C65))</f>
         <v/>
       </c>
-      <c r="E34" s="81">
+      <c r="E34" s="83">
         <f>('Income Valuation'!C49-'Income Valuation'!C33*(MIN(B34*'Income Valuation'!C39,'Income Valuation'!C64,'Income Valuation'!C65)*'Income Valuation'!C47)+('Income Valuation'!C51*'Income Valuation'!C30/E33)-(MIN(B34*'Income Valuation'!C39,'Income Valuation'!C64,'Income Valuation'!C65)*(1+'Income Valuation'!C46)^(12*'Income Valuation'!C33)-((MIN(B34*'Income Valuation'!C39,'Income Valuation'!C64,'Income Valuation'!C65)*'Income Valuation'!C47)/12)*((1+'Income Valuation'!C46)^(12*'Income Valuation'!C33)-1)/'Income Valuation'!C46))/(B34*(1+'Income Valuation'!C48)-MIN(B34*'Income Valuation'!C39,'Income Valuation'!C64,'Income Valuation'!C65))</f>
         <v/>
       </c>
-      <c r="F34" s="81">
+      <c r="F34" s="83">
         <f>('Income Valuation'!C49-'Income Valuation'!C33*(MIN(B34*'Income Valuation'!C39,'Income Valuation'!C64,'Income Valuation'!C65)*'Income Valuation'!C47)+('Income Valuation'!C51*'Income Valuation'!C30/F33)-(MIN(B34*'Income Valuation'!C39,'Income Valuation'!C64,'Income Valuation'!C65)*(1+'Income Valuation'!C46)^(12*'Income Valuation'!C33)-((MIN(B34*'Income Valuation'!C39,'Income Valuation'!C64,'Income Valuation'!C65)*'Income Valuation'!C47)/12)*((1+'Income Valuation'!C46)^(12*'Income Valuation'!C33)-1)/'Income Valuation'!C46))/(B34*(1+'Income Valuation'!C48)-MIN(B34*'Income Valuation'!C39,'Income Valuation'!C64,'Income Valuation'!C65))</f>
         <v/>
       </c>
-      <c r="G34" s="81">
+      <c r="G34" s="83">
         <f>('Income Valuation'!C49-'Income Valuation'!C33*(MIN(B34*'Income Valuation'!C39,'Income Valuation'!C64,'Income Valuation'!C65)*'Income Valuation'!C47)+('Income Valuation'!C51*'Income Valuation'!C30/G33)-(MIN(B34*'Income Valuation'!C39,'Income Valuation'!C64,'Income Valuation'!C65)*(1+'Income Valuation'!C46)^(12*'Income Valuation'!C33)-((MIN(B34*'Income Valuation'!C39,'Income Valuation'!C64,'Income Valuation'!C65)*'Income Valuation'!C47)/12)*((1+'Income Valuation'!C46)^(12*'Income Valuation'!C33)-1)/'Income Valuation'!C46))/(B34*(1+'Income Valuation'!C48)-MIN(B34*'Income Valuation'!C39,'Income Valuation'!C64,'Income Valuation'!C65))</f>
         <v/>
       </c>
-      <c r="H34" s="81">
+      <c r="H34" s="83">
         <f>('Income Valuation'!C49-'Income Valuation'!C33*(MIN(B34*'Income Valuation'!C39,'Income Valuation'!C64,'Income Valuation'!C65)*'Income Valuation'!C47)+('Income Valuation'!C51*'Income Valuation'!C30/H33)-(MIN(B34*'Income Valuation'!C39,'Income Valuation'!C64,'Income Valuation'!C65)*(1+'Income Valuation'!C46)^(12*'Income Valuation'!C33)-((MIN(B34*'Income Valuation'!C39,'Income Valuation'!C64,'Income Valuation'!C65)*'Income Valuation'!C47)/12)*((1+'Income Valuation'!C46)^(12*'Income Valuation'!C33)-1)/'Income Valuation'!C46))/(B34*(1+'Income Valuation'!C48)-MIN(B34*'Income Valuation'!C39,'Income Valuation'!C64,'Income Valuation'!C65))</f>
         <v/>
       </c>
@@ -4349,23 +4403,23 @@
       <c r="B35" s="70" t="n">
         <v>70000000</v>
       </c>
-      <c r="D35" s="81">
+      <c r="D35" s="83">
         <f>('Income Valuation'!C49-'Income Valuation'!C33*(MIN(B35*'Income Valuation'!C39,'Income Valuation'!C64,'Income Valuation'!C65)*'Income Valuation'!C47)+('Income Valuation'!C51*'Income Valuation'!C30/D33)-(MIN(B35*'Income Valuation'!C39,'Income Valuation'!C64,'Income Valuation'!C65)*(1+'Income Valuation'!C46)^(12*'Income Valuation'!C33)-((MIN(B35*'Income Valuation'!C39,'Income Valuation'!C64,'Income Valuation'!C65)*'Income Valuation'!C47)/12)*((1+'Income Valuation'!C46)^(12*'Income Valuation'!C33)-1)/'Income Valuation'!C46))/(B35*(1+'Income Valuation'!C48)-MIN(B35*'Income Valuation'!C39,'Income Valuation'!C64,'Income Valuation'!C65))</f>
         <v/>
       </c>
-      <c r="E35" s="81">
+      <c r="E35" s="83">
         <f>('Income Valuation'!C49-'Income Valuation'!C33*(MIN(B35*'Income Valuation'!C39,'Income Valuation'!C64,'Income Valuation'!C65)*'Income Valuation'!C47)+('Income Valuation'!C51*'Income Valuation'!C30/E33)-(MIN(B35*'Income Valuation'!C39,'Income Valuation'!C64,'Income Valuation'!C65)*(1+'Income Valuation'!C46)^(12*'Income Valuation'!C33)-((MIN(B35*'Income Valuation'!C39,'Income Valuation'!C64,'Income Valuation'!C65)*'Income Valuation'!C47)/12)*((1+'Income Valuation'!C46)^(12*'Income Valuation'!C33)-1)/'Income Valuation'!C46))/(B35*(1+'Income Valuation'!C48)-MIN(B35*'Income Valuation'!C39,'Income Valuation'!C64,'Income Valuation'!C65))</f>
         <v/>
       </c>
-      <c r="F35" s="81">
+      <c r="F35" s="83">
         <f>('Income Valuation'!C49-'Income Valuation'!C33*(MIN(B35*'Income Valuation'!C39,'Income Valuation'!C64,'Income Valuation'!C65)*'Income Valuation'!C47)+('Income Valuation'!C51*'Income Valuation'!C30/F33)-(MIN(B35*'Income Valuation'!C39,'Income Valuation'!C64,'Income Valuation'!C65)*(1+'Income Valuation'!C46)^(12*'Income Valuation'!C33)-((MIN(B35*'Income Valuation'!C39,'Income Valuation'!C64,'Income Valuation'!C65)*'Income Valuation'!C47)/12)*((1+'Income Valuation'!C46)^(12*'Income Valuation'!C33)-1)/'Income Valuation'!C46))/(B35*(1+'Income Valuation'!C48)-MIN(B35*'Income Valuation'!C39,'Income Valuation'!C64,'Income Valuation'!C65))</f>
         <v/>
       </c>
-      <c r="G35" s="81">
+      <c r="G35" s="83">
         <f>('Income Valuation'!C49-'Income Valuation'!C33*(MIN(B35*'Income Valuation'!C39,'Income Valuation'!C64,'Income Valuation'!C65)*'Income Valuation'!C47)+('Income Valuation'!C51*'Income Valuation'!C30/G33)-(MIN(B35*'Income Valuation'!C39,'Income Valuation'!C64,'Income Valuation'!C65)*(1+'Income Valuation'!C46)^(12*'Income Valuation'!C33)-((MIN(B35*'Income Valuation'!C39,'Income Valuation'!C64,'Income Valuation'!C65)*'Income Valuation'!C47)/12)*((1+'Income Valuation'!C46)^(12*'Income Valuation'!C33)-1)/'Income Valuation'!C46))/(B35*(1+'Income Valuation'!C48)-MIN(B35*'Income Valuation'!C39,'Income Valuation'!C64,'Income Valuation'!C65))</f>
         <v/>
       </c>
-      <c r="H35" s="81">
+      <c r="H35" s="83">
         <f>('Income Valuation'!C49-'Income Valuation'!C33*(MIN(B35*'Income Valuation'!C39,'Income Valuation'!C64,'Income Valuation'!C65)*'Income Valuation'!C47)+('Income Valuation'!C51*'Income Valuation'!C30/H33)-(MIN(B35*'Income Valuation'!C39,'Income Valuation'!C64,'Income Valuation'!C65)*(1+'Income Valuation'!C46)^(12*'Income Valuation'!C33)-((MIN(B35*'Income Valuation'!C39,'Income Valuation'!C64,'Income Valuation'!C65)*'Income Valuation'!C47)/12)*((1+'Income Valuation'!C46)^(12*'Income Valuation'!C33)-1)/'Income Valuation'!C46))/(B35*(1+'Income Valuation'!C48)-MIN(B35*'Income Valuation'!C39,'Income Valuation'!C64,'Income Valuation'!C65))</f>
         <v/>
       </c>
@@ -4374,23 +4428,23 @@
       <c r="B36" s="70" t="n">
         <v>85000000</v>
       </c>
-      <c r="D36" s="81">
+      <c r="D36" s="83">
         <f>('Income Valuation'!C49-'Income Valuation'!C33*(MIN(B36*'Income Valuation'!C39,'Income Valuation'!C64,'Income Valuation'!C65)*'Income Valuation'!C47)+('Income Valuation'!C51*'Income Valuation'!C30/D33)-(MIN(B36*'Income Valuation'!C39,'Income Valuation'!C64,'Income Valuation'!C65)*(1+'Income Valuation'!C46)^(12*'Income Valuation'!C33)-((MIN(B36*'Income Valuation'!C39,'Income Valuation'!C64,'Income Valuation'!C65)*'Income Valuation'!C47)/12)*((1+'Income Valuation'!C46)^(12*'Income Valuation'!C33)-1)/'Income Valuation'!C46))/(B36*(1+'Income Valuation'!C48)-MIN(B36*'Income Valuation'!C39,'Income Valuation'!C64,'Income Valuation'!C65))</f>
         <v/>
       </c>
-      <c r="E36" s="81">
+      <c r="E36" s="83">
         <f>('Income Valuation'!C49-'Income Valuation'!C33*(MIN(B36*'Income Valuation'!C39,'Income Valuation'!C64,'Income Valuation'!C65)*'Income Valuation'!C47)+('Income Valuation'!C51*'Income Valuation'!C30/E33)-(MIN(B36*'Income Valuation'!C39,'Income Valuation'!C64,'Income Valuation'!C65)*(1+'Income Valuation'!C46)^(12*'Income Valuation'!C33)-((MIN(B36*'Income Valuation'!C39,'Income Valuation'!C64,'Income Valuation'!C65)*'Income Valuation'!C47)/12)*((1+'Income Valuation'!C46)^(12*'Income Valuation'!C33)-1)/'Income Valuation'!C46))/(B36*(1+'Income Valuation'!C48)-MIN(B36*'Income Valuation'!C39,'Income Valuation'!C64,'Income Valuation'!C65))</f>
         <v/>
       </c>
-      <c r="F36" s="81">
+      <c r="F36" s="83">
         <f>('Income Valuation'!C49-'Income Valuation'!C33*(MIN(B36*'Income Valuation'!C39,'Income Valuation'!C64,'Income Valuation'!C65)*'Income Valuation'!C47)+('Income Valuation'!C51*'Income Valuation'!C30/F33)-(MIN(B36*'Income Valuation'!C39,'Income Valuation'!C64,'Income Valuation'!C65)*(1+'Income Valuation'!C46)^(12*'Income Valuation'!C33)-((MIN(B36*'Income Valuation'!C39,'Income Valuation'!C64,'Income Valuation'!C65)*'Income Valuation'!C47)/12)*((1+'Income Valuation'!C46)^(12*'Income Valuation'!C33)-1)/'Income Valuation'!C46))/(B36*(1+'Income Valuation'!C48)-MIN(B36*'Income Valuation'!C39,'Income Valuation'!C64,'Income Valuation'!C65))</f>
         <v/>
       </c>
-      <c r="G36" s="81">
+      <c r="G36" s="83">
         <f>('Income Valuation'!C49-'Income Valuation'!C33*(MIN(B36*'Income Valuation'!C39,'Income Valuation'!C64,'Income Valuation'!C65)*'Income Valuation'!C47)+('Income Valuation'!C51*'Income Valuation'!C30/G33)-(MIN(B36*'Income Valuation'!C39,'Income Valuation'!C64,'Income Valuation'!C65)*(1+'Income Valuation'!C46)^(12*'Income Valuation'!C33)-((MIN(B36*'Income Valuation'!C39,'Income Valuation'!C64,'Income Valuation'!C65)*'Income Valuation'!C47)/12)*((1+'Income Valuation'!C46)^(12*'Income Valuation'!C33)-1)/'Income Valuation'!C46))/(B36*(1+'Income Valuation'!C48)-MIN(B36*'Income Valuation'!C39,'Income Valuation'!C64,'Income Valuation'!C65))</f>
         <v/>
       </c>
-      <c r="H36" s="81">
+      <c r="H36" s="83">
         <f>('Income Valuation'!C49-'Income Valuation'!C33*(MIN(B36*'Income Valuation'!C39,'Income Valuation'!C64,'Income Valuation'!C65)*'Income Valuation'!C47)+('Income Valuation'!C51*'Income Valuation'!C30/H33)-(MIN(B36*'Income Valuation'!C39,'Income Valuation'!C64,'Income Valuation'!C65)*(1+'Income Valuation'!C46)^(12*'Income Valuation'!C33)-((MIN(B36*'Income Valuation'!C39,'Income Valuation'!C64,'Income Valuation'!C65)*'Income Valuation'!C47)/12)*((1+'Income Valuation'!C46)^(12*'Income Valuation'!C33)-1)/'Income Valuation'!C46))/(B36*(1+'Income Valuation'!C48)-MIN(B36*'Income Valuation'!C39,'Income Valuation'!C64,'Income Valuation'!C65))</f>
         <v/>
       </c>
@@ -4399,23 +4453,23 @@
       <c r="B37" s="70" t="n">
         <v>100000000</v>
       </c>
-      <c r="D37" s="81">
+      <c r="D37" s="83">
         <f>('Income Valuation'!C49-'Income Valuation'!C33*(MIN(B37*'Income Valuation'!C39,'Income Valuation'!C64,'Income Valuation'!C65)*'Income Valuation'!C47)+('Income Valuation'!C51*'Income Valuation'!C30/D33)-(MIN(B37*'Income Valuation'!C39,'Income Valuation'!C64,'Income Valuation'!C65)*(1+'Income Valuation'!C46)^(12*'Income Valuation'!C33)-((MIN(B37*'Income Valuation'!C39,'Income Valuation'!C64,'Income Valuation'!C65)*'Income Valuation'!C47)/12)*((1+'Income Valuation'!C46)^(12*'Income Valuation'!C33)-1)/'Income Valuation'!C46))/(B37*(1+'Income Valuation'!C48)-MIN(B37*'Income Valuation'!C39,'Income Valuation'!C64,'Income Valuation'!C65))</f>
         <v/>
       </c>
-      <c r="E37" s="81">
+      <c r="E37" s="83">
         <f>('Income Valuation'!C49-'Income Valuation'!C33*(MIN(B37*'Income Valuation'!C39,'Income Valuation'!C64,'Income Valuation'!C65)*'Income Valuation'!C47)+('Income Valuation'!C51*'Income Valuation'!C30/E33)-(MIN(B37*'Income Valuation'!C39,'Income Valuation'!C64,'Income Valuation'!C65)*(1+'Income Valuation'!C46)^(12*'Income Valuation'!C33)-((MIN(B37*'Income Valuation'!C39,'Income Valuation'!C64,'Income Valuation'!C65)*'Income Valuation'!C47)/12)*((1+'Income Valuation'!C46)^(12*'Income Valuation'!C33)-1)/'Income Valuation'!C46))/(B37*(1+'Income Valuation'!C48)-MIN(B37*'Income Valuation'!C39,'Income Valuation'!C64,'Income Valuation'!C65))</f>
         <v/>
       </c>
-      <c r="F37" s="81">
+      <c r="F37" s="83">
         <f>('Income Valuation'!C49-'Income Valuation'!C33*(MIN(B37*'Income Valuation'!C39,'Income Valuation'!C64,'Income Valuation'!C65)*'Income Valuation'!C47)+('Income Valuation'!C51*'Income Valuation'!C30/F33)-(MIN(B37*'Income Valuation'!C39,'Income Valuation'!C64,'Income Valuation'!C65)*(1+'Income Valuation'!C46)^(12*'Income Valuation'!C33)-((MIN(B37*'Income Valuation'!C39,'Income Valuation'!C64,'Income Valuation'!C65)*'Income Valuation'!C47)/12)*((1+'Income Valuation'!C46)^(12*'Income Valuation'!C33)-1)/'Income Valuation'!C46))/(B37*(1+'Income Valuation'!C48)-MIN(B37*'Income Valuation'!C39,'Income Valuation'!C64,'Income Valuation'!C65))</f>
         <v/>
       </c>
-      <c r="G37" s="81">
+      <c r="G37" s="83">
         <f>('Income Valuation'!C49-'Income Valuation'!C33*(MIN(B37*'Income Valuation'!C39,'Income Valuation'!C64,'Income Valuation'!C65)*'Income Valuation'!C47)+('Income Valuation'!C51*'Income Valuation'!C30/G33)-(MIN(B37*'Income Valuation'!C39,'Income Valuation'!C64,'Income Valuation'!C65)*(1+'Income Valuation'!C46)^(12*'Income Valuation'!C33)-((MIN(B37*'Income Valuation'!C39,'Income Valuation'!C64,'Income Valuation'!C65)*'Income Valuation'!C47)/12)*((1+'Income Valuation'!C46)^(12*'Income Valuation'!C33)-1)/'Income Valuation'!C46))/(B37*(1+'Income Valuation'!C48)-MIN(B37*'Income Valuation'!C39,'Income Valuation'!C64,'Income Valuation'!C65))</f>
         <v/>
       </c>
-      <c r="H37" s="81">
+      <c r="H37" s="83">
         <f>('Income Valuation'!C49-'Income Valuation'!C33*(MIN(B37*'Income Valuation'!C39,'Income Valuation'!C64,'Income Valuation'!C65)*'Income Valuation'!C47)+('Income Valuation'!C51*'Income Valuation'!C30/H33)-(MIN(B37*'Income Valuation'!C39,'Income Valuation'!C64,'Income Valuation'!C65)*(1+'Income Valuation'!C46)^(12*'Income Valuation'!C33)-((MIN(B37*'Income Valuation'!C39,'Income Valuation'!C64,'Income Valuation'!C65)*'Income Valuation'!C47)/12)*((1+'Income Valuation'!C46)^(12*'Income Valuation'!C33)-1)/'Income Valuation'!C46))/(B37*(1+'Income Valuation'!C48)-MIN(B37*'Income Valuation'!C39,'Income Valuation'!C64,'Income Valuation'!C65))</f>
         <v/>
       </c>
@@ -4424,23 +4478,23 @@
       <c r="B38" s="70" t="n">
         <v>122000000</v>
       </c>
-      <c r="D38" s="81">
+      <c r="D38" s="83">
         <f>('Income Valuation'!C49-'Income Valuation'!C33*(MIN(B38*'Income Valuation'!C39,'Income Valuation'!C64,'Income Valuation'!C65)*'Income Valuation'!C47)+('Income Valuation'!C51*'Income Valuation'!C30/D33)-(MIN(B38*'Income Valuation'!C39,'Income Valuation'!C64,'Income Valuation'!C65)*(1+'Income Valuation'!C46)^(12*'Income Valuation'!C33)-((MIN(B38*'Income Valuation'!C39,'Income Valuation'!C64,'Income Valuation'!C65)*'Income Valuation'!C47)/12)*((1+'Income Valuation'!C46)^(12*'Income Valuation'!C33)-1)/'Income Valuation'!C46))/(B38*(1+'Income Valuation'!C48)-MIN(B38*'Income Valuation'!C39,'Income Valuation'!C64,'Income Valuation'!C65))</f>
         <v/>
       </c>
-      <c r="E38" s="81">
+      <c r="E38" s="83">
         <f>('Income Valuation'!C49-'Income Valuation'!C33*(MIN(B38*'Income Valuation'!C39,'Income Valuation'!C64,'Income Valuation'!C65)*'Income Valuation'!C47)+('Income Valuation'!C51*'Income Valuation'!C30/E33)-(MIN(B38*'Income Valuation'!C39,'Income Valuation'!C64,'Income Valuation'!C65)*(1+'Income Valuation'!C46)^(12*'Income Valuation'!C33)-((MIN(B38*'Income Valuation'!C39,'Income Valuation'!C64,'Income Valuation'!C65)*'Income Valuation'!C47)/12)*((1+'Income Valuation'!C46)^(12*'Income Valuation'!C33)-1)/'Income Valuation'!C46))/(B38*(1+'Income Valuation'!C48)-MIN(B38*'Income Valuation'!C39,'Income Valuation'!C64,'Income Valuation'!C65))</f>
         <v/>
       </c>
-      <c r="F38" s="81">
+      <c r="F38" s="83">
         <f>('Income Valuation'!C49-'Income Valuation'!C33*(MIN(B38*'Income Valuation'!C39,'Income Valuation'!C64,'Income Valuation'!C65)*'Income Valuation'!C47)+('Income Valuation'!C51*'Income Valuation'!C30/F33)-(MIN(B38*'Income Valuation'!C39,'Income Valuation'!C64,'Income Valuation'!C65)*(1+'Income Valuation'!C46)^(12*'Income Valuation'!C33)-((MIN(B38*'Income Valuation'!C39,'Income Valuation'!C64,'Income Valuation'!C65)*'Income Valuation'!C47)/12)*((1+'Income Valuation'!C46)^(12*'Income Valuation'!C33)-1)/'Income Valuation'!C46))/(B38*(1+'Income Valuation'!C48)-MIN(B38*'Income Valuation'!C39,'Income Valuation'!C64,'Income Valuation'!C65))</f>
         <v/>
       </c>
-      <c r="G38" s="81">
+      <c r="G38" s="83">
         <f>('Income Valuation'!C49-'Income Valuation'!C33*(MIN(B38*'Income Valuation'!C39,'Income Valuation'!C64,'Income Valuation'!C65)*'Income Valuation'!C47)+('Income Valuation'!C51*'Income Valuation'!C30/G33)-(MIN(B38*'Income Valuation'!C39,'Income Valuation'!C64,'Income Valuation'!C65)*(1+'Income Valuation'!C46)^(12*'Income Valuation'!C33)-((MIN(B38*'Income Valuation'!C39,'Income Valuation'!C64,'Income Valuation'!C65)*'Income Valuation'!C47)/12)*((1+'Income Valuation'!C46)^(12*'Income Valuation'!C33)-1)/'Income Valuation'!C46))/(B38*(1+'Income Valuation'!C48)-MIN(B38*'Income Valuation'!C39,'Income Valuation'!C64,'Income Valuation'!C65))</f>
         <v/>
       </c>
-      <c r="H38" s="81">
+      <c r="H38" s="83">
         <f>('Income Valuation'!C49-'Income Valuation'!C33*(MIN(B38*'Income Valuation'!C39,'Income Valuation'!C64,'Income Valuation'!C65)*'Income Valuation'!C47)+('Income Valuation'!C51*'Income Valuation'!C30/H33)-(MIN(B38*'Income Valuation'!C39,'Income Valuation'!C64,'Income Valuation'!C65)*(1+'Income Valuation'!C46)^(12*'Income Valuation'!C33)-((MIN(B38*'Income Valuation'!C39,'Income Valuation'!C64,'Income Valuation'!C65)*'Income Valuation'!C47)/12)*((1+'Income Valuation'!C46)^(12*'Income Valuation'!C33)-1)/'Income Valuation'!C46))/(B38*(1+'Income Valuation'!C48)-MIN(B38*'Income Valuation'!C39,'Income Valuation'!C64,'Income Valuation'!C65))</f>
         <v/>
       </c>
@@ -4536,22 +4590,22 @@
       <c r="D43" s="66" t="n">
         <v>0.06</v>
       </c>
-      <c r="E43" s="81">
+      <c r="E43" s="83">
         <f>('Income Valuation'!C49-'Income Valuation'!C33*'Income Valuation'!C67+('Income Valuation'!C51*'Income Valuation'!C30/D43)-'Income Valuation'!C68)/'Income Valuation'!C85</f>
         <v/>
       </c>
-      <c r="F43" s="95">
+      <c r="F43" s="97">
         <f>'Income Valuation'!C94</f>
         <v/>
       </c>
       <c r="G43" s="66" t="n">
         <v>0.08</v>
       </c>
-      <c r="H43" s="81">
+      <c r="H43" s="83">
         <f>('Income Valuation'!C49-'Income Valuation'!C33*'Income Valuation'!C67+('Income Valuation'!C51*'Income Valuation'!C30/G43)-'Income Valuation'!C68)/'Income Valuation'!C85</f>
         <v/>
       </c>
-      <c r="I43" s="81">
+      <c r="I43" s="83">
         <f>ABS(H43-E43)</f>
         <v/>
       </c>
@@ -4573,22 +4627,22 @@
       <c r="D44" s="70" t="n">
         <v>60000000</v>
       </c>
-      <c r="E44" s="81">
+      <c r="E44" s="83">
         <f>('Income Valuation'!C49-'Income Valuation'!C33*(MIN(D44*'Income Valuation'!C39,'Income Valuation'!C64,'Income Valuation'!C65)*'Income Valuation'!C47)+'Income Valuation'!C51-(MIN(D44*'Income Valuation'!C39,'Income Valuation'!C64,'Income Valuation'!C65)*(1+'Income Valuation'!C46)^(12*'Income Valuation'!C33)-((MIN(D44*'Income Valuation'!C39,'Income Valuation'!C64,'Income Valuation'!C65)*'Income Valuation'!C47)/12)*((1+'Income Valuation'!C46)^(12*'Income Valuation'!C33)-1)/'Income Valuation'!C46))/(D44*(1+'Income Valuation'!C48)-MIN(D44*'Income Valuation'!C39,'Income Valuation'!C64,'Income Valuation'!C65))</f>
         <v/>
       </c>
-      <c r="F44" s="95">
+      <c r="F44" s="97">
         <f>'Income Valuation'!C94</f>
         <v/>
       </c>
       <c r="G44" s="70" t="n">
         <v>85000000</v>
       </c>
-      <c r="H44" s="81">
+      <c r="H44" s="83">
         <f>('Income Valuation'!C49-'Income Valuation'!C33*(MIN(G44*'Income Valuation'!C39,'Income Valuation'!C64,'Income Valuation'!C65)*'Income Valuation'!C47)+'Income Valuation'!C51-(MIN(G44*'Income Valuation'!C39,'Income Valuation'!C64,'Income Valuation'!C65)*(1+'Income Valuation'!C46)^(12*'Income Valuation'!C33)-((MIN(G44*'Income Valuation'!C39,'Income Valuation'!C64,'Income Valuation'!C65)*'Income Valuation'!C47)/12)*((1+'Income Valuation'!C46)^(12*'Income Valuation'!C33)-1)/'Income Valuation'!C46))/(G44*(1+'Income Valuation'!C48)-MIN(G44*'Income Valuation'!C39,'Income Valuation'!C64,'Income Valuation'!C65))</f>
         <v/>
       </c>
-      <c r="I44" s="81">
+      <c r="I44" s="83">
         <f>ABS(H44-E44)</f>
         <v/>
       </c>
@@ -4610,22 +4664,22 @@
       <c r="D45" s="66" t="n">
         <v>0.055</v>
       </c>
-      <c r="E45" s="81">
+      <c r="E45" s="83">
         <f>('Income Valuation'!C49-'Income Valuation'!C33*('Income Valuation'!C66*((D45/12)/(1-(1+(D45/12))^(-'Income Valuation'!C43*12))*12))+'Income Valuation'!C51-('Income Valuation'!C66*(1+(D45/12))^(12*'Income Valuation'!C33)-(('Income Valuation'!C66*((D45/12)/(1-(1+(D45/12))^(-'Income Valuation'!C43*12))*12))/12)*((1+(D45/12))^(12*'Income Valuation'!C33)-1)/(D45/12)))/'Income Valuation'!C85</f>
         <v/>
       </c>
-      <c r="F45" s="95">
+      <c r="F45" s="97">
         <f>'Income Valuation'!C94</f>
         <v/>
       </c>
       <c r="G45" s="66" t="n">
         <v>0.08</v>
       </c>
-      <c r="H45" s="81">
+      <c r="H45" s="83">
         <f>('Income Valuation'!C49-'Income Valuation'!C33*('Income Valuation'!C66*((G45/12)/(1-(1+(G45/12))^(-'Income Valuation'!C43*12))*12))+'Income Valuation'!C51-('Income Valuation'!C66*(1+(G45/12))^(12*'Income Valuation'!C33)-(('Income Valuation'!C66*((G45/12)/(1-(1+(G45/12))^(-'Income Valuation'!C43*12))*12))/12)*((1+(G45/12))^(12*'Income Valuation'!C33)-1)/(G45/12)))/'Income Valuation'!C85</f>
         <v/>
       </c>
-      <c r="I45" s="81">
+      <c r="I45" s="83">
         <f>ABS(H45-E45)</f>
         <v/>
       </c>
@@ -4647,22 +4701,22 @@
       <c r="D46" s="67" t="n">
         <v>0.5</v>
       </c>
-      <c r="E46" s="81">
+      <c r="E46" s="83">
         <f>('Income Valuation'!C49-'Income Valuation'!C33*(MIN('Income Valuation'!C60*D46,'Income Valuation'!C64,'Income Valuation'!C65)*'Income Valuation'!C47)+'Income Valuation'!C51-(MIN('Income Valuation'!C60*D46,'Income Valuation'!C64,'Income Valuation'!C65)*(1+'Income Valuation'!C46)^(12*'Income Valuation'!C33)-((MIN('Income Valuation'!C60*D46,'Income Valuation'!C64,'Income Valuation'!C65)*'Income Valuation'!C47)/12)*((1+'Income Valuation'!C46)^(12*'Income Valuation'!C33)-1)/'Income Valuation'!C46))/('Income Valuation'!C60*(1+'Income Valuation'!C48)-MIN('Income Valuation'!C60*D46,'Income Valuation'!C64,'Income Valuation'!C65))</f>
         <v/>
       </c>
-      <c r="F46" s="95">
+      <c r="F46" s="97">
         <f>'Income Valuation'!C94</f>
         <v/>
       </c>
       <c r="G46" s="67" t="n">
         <v>0.7</v>
       </c>
-      <c r="H46" s="81">
+      <c r="H46" s="83">
         <f>('Income Valuation'!C49-'Income Valuation'!C33*(MIN('Income Valuation'!C60*G46,'Income Valuation'!C64,'Income Valuation'!C65)*'Income Valuation'!C47)+'Income Valuation'!C51-(MIN('Income Valuation'!C60*G46,'Income Valuation'!C64,'Income Valuation'!C65)*(1+'Income Valuation'!C46)^(12*'Income Valuation'!C33)-((MIN('Income Valuation'!C60*G46,'Income Valuation'!C64,'Income Valuation'!C65)*'Income Valuation'!C47)/12)*((1+'Income Valuation'!C46)^(12*'Income Valuation'!C33)-1)/'Income Valuation'!C46))/('Income Valuation'!C60*(1+'Income Valuation'!C48)-MIN('Income Valuation'!C60*G46,'Income Valuation'!C64,'Income Valuation'!C65))</f>
         <v/>
       </c>
-      <c r="I46" s="81">
+      <c r="I46" s="83">
         <f>ABS(H46-E46)</f>
         <v/>
       </c>
@@ -4684,22 +4738,22 @@
       <c r="D47" s="69" t="n">
         <v>0.9</v>
       </c>
-      <c r="E47" s="81">
+      <c r="E47" s="83">
         <f>((D47*'Income Valuation'!C49)-'Income Valuation'!C33*'Income Valuation'!C67+'Income Valuation'!C51-'Income Valuation'!C68)/'Income Valuation'!C85</f>
         <v/>
       </c>
-      <c r="F47" s="95">
+      <c r="F47" s="97">
         <f>'Income Valuation'!C94</f>
         <v/>
       </c>
       <c r="G47" s="69" t="n">
         <v>1.1</v>
       </c>
-      <c r="H47" s="81">
+      <c r="H47" s="83">
         <f>((G47*'Income Valuation'!C49)-'Income Valuation'!C33*'Income Valuation'!C67+'Income Valuation'!C51-'Income Valuation'!C68)/'Income Valuation'!C85</f>
         <v/>
       </c>
-      <c r="I47" s="81">
+      <c r="I47" s="83">
         <f>ABS(H47-E47)</f>
         <v/>
       </c>
@@ -4780,7 +4834,7 @@
           <t>At the COVERED-LAND price</t>
         </is>
       </c>
-      <c r="D52" s="96">
+      <c r="D52" s="98">
         <f>'Income Valuation'!E93</f>
         <v/>
       </c>
@@ -5124,7 +5178,7 @@
       <c r="C8" s="66" t="n">
         <v>0.065</v>
       </c>
-      <c r="D8" s="94">
+      <c r="D8" s="96">
         <f>'Income Valuation'!C42</f>
         <v/>
       </c>
@@ -5178,7 +5232,7 @@
       <c r="C10" s="69" t="n">
         <v>1.3</v>
       </c>
-      <c r="D10" s="95">
+      <c r="D10" s="97">
         <f>'Income Valuation'!C40</f>
         <v/>
       </c>
@@ -5324,7 +5378,7 @@
       <c r="C16" s="72" t="n">
         <v>30000000</v>
       </c>
-      <c r="D16" s="97">
+      <c r="D16" s="99">
         <f>'Income Valuation'!C85</f>
         <v/>
       </c>
@@ -5569,7 +5623,7 @@
         <f>MIN(C7*'Income Valuation'!C121,'Income Valuation'!C24/(C10*C22),'Income Valuation'!C24/C11)</f>
         <v/>
       </c>
-      <c r="E30" s="82">
+      <c r="E30" s="84">
         <f>MIN(C7*'Income Valuation'!C121,'Income Valuation'!C24/(C10*C22),'Income Valuation'!C24/C11)/D29</f>
         <v/>
       </c>
@@ -5577,7 +5631,7 @@
         <f>MIN(C7*'Assemblage'!C28,'Income Valuation'!C24/(C10*C22),'Income Valuation'!C24/C11)</f>
         <v/>
       </c>
-      <c r="H30" s="82">
+      <c r="H30" s="84">
         <f>MIN(C7*'Assemblage'!C28,'Income Valuation'!C24/(C10*C22),'Income Valuation'!C24/C11)/G29</f>
         <v/>
       </c>
@@ -5592,7 +5646,7 @@
         <f>(C13*'Income Valuation'!C121)</f>
         <v/>
       </c>
-      <c r="E31" s="82">
+      <c r="E31" s="84">
         <f>(C13*'Income Valuation'!C121)/D29</f>
         <v/>
       </c>
@@ -5600,7 +5654,7 @@
         <f>(C13*'Assemblage'!C28)</f>
         <v/>
       </c>
-      <c r="H31" s="82">
+      <c r="H31" s="84">
         <f>(C13*'Assemblage'!C28)/G29</f>
         <v/>
       </c>
@@ -5611,19 +5665,19 @@
           <t>Equity (plug)</t>
         </is>
       </c>
-      <c r="D32" s="76">
+      <c r="D32" s="78">
         <f>(('Income Valuation'!C121*(1+'Income Valuation'!C48))-MIN(C7*'Income Valuation'!C121,'Income Valuation'!C24/(C10*C22),'Income Valuation'!C24/C11)-(C13*'Income Valuation'!C121))</f>
         <v/>
       </c>
-      <c r="E32" s="82">
+      <c r="E32" s="84">
         <f>(('Income Valuation'!C121*(1+'Income Valuation'!C48))-MIN(C7*'Income Valuation'!C121,'Income Valuation'!C24/(C10*C22),'Income Valuation'!C24/C11)-(C13*'Income Valuation'!C121))/D29</f>
         <v/>
       </c>
-      <c r="G32" s="76">
+      <c r="G32" s="78">
         <f>(('Assemblage'!C28*(1+'Income Valuation'!C48))-MIN(C7*'Assemblage'!C28,'Income Valuation'!C24/(C10*C22),'Income Valuation'!C24/C11)-(C13*'Assemblage'!C28))</f>
         <v/>
       </c>
-      <c r="H32" s="82">
+      <c r="H32" s="84">
         <f>(('Assemblage'!C28*(1+'Income Valuation'!C48))-MIN(C7*'Assemblage'!C28,'Income Valuation'!C24/(C10*C22),'Income Valuation'!C24/C11)-(C13*'Assemblage'!C28))/G29</f>
         <v/>
       </c>
@@ -5650,11 +5704,11 @@
           <t>Year-1 DSCR (senior)</t>
         </is>
       </c>
-      <c r="D35" s="79">
+      <c r="D35" s="81">
         <f>'Income Valuation'!C24/(MIN(C7*'Income Valuation'!C121,'Income Valuation'!C24/(C10*C22),'Income Valuation'!C24/C11)*C22)</f>
         <v/>
       </c>
-      <c r="G35" s="79">
+      <c r="G35" s="81">
         <f>'Income Valuation'!C24/(MIN(C7*'Assemblage'!C28,'Income Valuation'!C24/(C10*C22),'Income Valuation'!C24/C11)*C22)</f>
         <v/>
       </c>
@@ -5759,7 +5813,7 @@
           <t>Total debt as % of cost (senior LTV + mezz)</t>
         </is>
       </c>
-      <c r="C43" s="82">
+      <c r="C43" s="84">
         <f>C7+C13</f>
         <v/>
       </c>
@@ -5770,7 +5824,7 @@
           <t>Equity share of cost</t>
         </is>
       </c>
-      <c r="C44" s="82">
+      <c r="C44" s="84">
         <f>1-C43</f>
         <v/>
       </c>
@@ -5781,7 +5835,7 @@
           <t>Max total cost you can fund</t>
         </is>
       </c>
-      <c r="C45" s="98">
+      <c r="C45" s="100">
         <f>C16/C44</f>
         <v/>
       </c>
@@ -5792,7 +5846,7 @@
           <t>→ MAX PURCHASE PRICE</t>
         </is>
       </c>
-      <c r="C46" s="99">
+      <c r="C46" s="101">
         <f>C45/(1+'Income Valuation'!C48)</f>
         <v/>
       </c>
@@ -5872,7 +5926,7 @@
         <f>'Income Valuation'!C121</f>
         <v/>
       </c>
-      <c r="D50" s="82">
+      <c r="D50" s="84">
         <f>C46/'Income Valuation'!C121</f>
         <v/>
       </c>
@@ -5897,7 +5951,7 @@
         <f>'Assemblage'!C16</f>
         <v/>
       </c>
-      <c r="D51" s="82">
+      <c r="D51" s="84">
         <f>C46/'Assemblage'!C16</f>
         <v/>
       </c>
@@ -5922,7 +5976,7 @@
         <f>'Assemblage'!C28</f>
         <v/>
       </c>
-      <c r="D52" s="82">
+      <c r="D52" s="84">
         <f>C46/'Assemblage'!C28</f>
         <v/>
       </c>
@@ -6423,7 +6477,7 @@
           <t>Total equity (at income price)</t>
         </is>
       </c>
-      <c r="C10" s="97">
+      <c r="C10" s="99">
         <f>'Income Valuation'!C85</f>
         <v/>
       </c>
@@ -6472,34 +6526,34 @@
           <t>0</t>
         </is>
       </c>
-      <c r="D13" s="75" t="n">
+      <c r="D13" s="77" t="n">
         <v>1</v>
       </c>
-      <c r="E13" s="75" t="n">
+      <c r="E13" s="77" t="n">
         <v>2</v>
       </c>
-      <c r="F13" s="75" t="n">
+      <c r="F13" s="77" t="n">
         <v>3</v>
       </c>
-      <c r="G13" s="75" t="n">
+      <c r="G13" s="77" t="n">
         <v>4</v>
       </c>
-      <c r="H13" s="75" t="n">
+      <c r="H13" s="77" t="n">
         <v>5</v>
       </c>
-      <c r="I13" s="75" t="n">
+      <c r="I13" s="77" t="n">
         <v>6</v>
       </c>
-      <c r="J13" s="75" t="n">
+      <c r="J13" s="77" t="n">
         <v>7</v>
       </c>
-      <c r="K13" s="75" t="n">
+      <c r="K13" s="77" t="n">
         <v>8</v>
       </c>
-      <c r="L13" s="75" t="n">
+      <c r="L13" s="77" t="n">
         <v>9</v>
       </c>
-      <c r="M13" s="75" t="n">
+      <c r="M13" s="77" t="n">
         <v>10</v>
       </c>
     </row>
@@ -6756,43 +6810,43 @@
         <f>-C5*C10</f>
         <v/>
       </c>
-      <c r="D19" s="76">
+      <c r="D19" s="78">
         <f>C5*D17+C8*D18</f>
         <v/>
       </c>
-      <c r="E19" s="76">
+      <c r="E19" s="78">
         <f>C5*E17+C8*E18</f>
         <v/>
       </c>
-      <c r="F19" s="76">
+      <c r="F19" s="78">
         <f>C5*F17+C8*F18</f>
         <v/>
       </c>
-      <c r="G19" s="76">
+      <c r="G19" s="78">
         <f>C5*G17+C8*G18</f>
         <v/>
       </c>
-      <c r="H19" s="76">
+      <c r="H19" s="78">
         <f>C5*H17+C8*H18</f>
         <v/>
       </c>
-      <c r="I19" s="76">
+      <c r="I19" s="78">
         <f>C5*I17+C8*I18</f>
         <v/>
       </c>
-      <c r="J19" s="76">
+      <c r="J19" s="78">
         <f>C5*J17+C8*J18</f>
         <v/>
       </c>
-      <c r="K19" s="76">
+      <c r="K19" s="78">
         <f>C5*K17+C8*K18</f>
         <v/>
       </c>
-      <c r="L19" s="76">
+      <c r="L19" s="78">
         <f>C5*L17+C8*L18</f>
         <v/>
       </c>
-      <c r="M19" s="76">
+      <c r="M19" s="78">
         <f>C5*M17+C8*M18</f>
         <v/>
       </c>
@@ -6807,43 +6861,43 @@
         <f>-C6*C10</f>
         <v/>
       </c>
-      <c r="D20" s="76">
+      <c r="D20" s="78">
         <f>C6*D17+C9*D18</f>
         <v/>
       </c>
-      <c r="E20" s="76">
+      <c r="E20" s="78">
         <f>C6*E17+C9*E18</f>
         <v/>
       </c>
-      <c r="F20" s="76">
+      <c r="F20" s="78">
         <f>C6*F17+C9*F18</f>
         <v/>
       </c>
-      <c r="G20" s="76">
+      <c r="G20" s="78">
         <f>C6*G17+C9*G18</f>
         <v/>
       </c>
-      <c r="H20" s="76">
+      <c r="H20" s="78">
         <f>C6*H17+C9*H18</f>
         <v/>
       </c>
-      <c r="I20" s="76">
+      <c r="I20" s="78">
         <f>C6*I17+C9*I18</f>
         <v/>
       </c>
-      <c r="J20" s="76">
+      <c r="J20" s="78">
         <f>C6*J17+C9*J18</f>
         <v/>
       </c>
-      <c r="K20" s="76">
+      <c r="K20" s="78">
         <f>C6*K17+C9*K18</f>
         <v/>
       </c>
-      <c r="L20" s="76">
+      <c r="L20" s="78">
         <f>C6*L17+C9*L18</f>
         <v/>
       </c>
-      <c r="M20" s="76">
+      <c r="M20" s="78">
         <f>C6*M17+C9*M18</f>
         <v/>
       </c>
@@ -6916,11 +6970,11 @@
           <t>Equity multiple</t>
         </is>
       </c>
-      <c r="E25" s="79">
+      <c r="E25" s="81">
         <f>SUM(D19:M19)/(C5*C10)</f>
         <v/>
       </c>
-      <c r="G25" s="79">
+      <c r="G25" s="81">
         <f>SUM(D20:M20)/(C6*C10)</f>
         <v/>
       </c>
@@ -7883,15 +7937,15 @@
         </is>
       </c>
       <c r="E29" s="9" t="n"/>
-      <c r="F29" s="100" t="n">
+      <c r="F29" s="102" t="n">
         <v>4422</v>
       </c>
-      <c r="G29" s="101" t="inlineStr">
+      <c r="G29" s="103" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H29" s="101" t="inlineStr">
+      <c r="H29" s="103" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -7919,11 +7973,11 @@
       </c>
       <c r="D30" s="30" t="inlineStr"/>
       <c r="E30" s="9" t="n"/>
-      <c r="F30" s="87">
+      <c r="F30" s="89">
         <f>SUM(F20:F29)</f>
         <v/>
       </c>
-      <c r="G30" s="102">
+      <c r="G30" s="104">
         <f>IFERROR(SUM(H20:H28)/SUM(F20:F28),0)</f>
         <v/>
       </c>
@@ -8033,7 +8087,7 @@
           <t>Land (SF)</t>
         </is>
       </c>
-      <c r="C36" s="85">
+      <c r="C36" s="87">
         <f>'Assumptions'!C60</f>
         <v/>
       </c>
@@ -8619,7 +8673,7 @@
           <t>Senior loan amortization (yrs)</t>
         </is>
       </c>
-      <c r="C61" s="103" t="n">
+      <c r="C61" s="105" t="n">
         <v>30</v>
       </c>
       <c r="D61" s="16" t="inlineStr">
@@ -8735,7 +8789,7 @@
           <t>Hold period (yrs)</t>
         </is>
       </c>
-      <c r="C66" s="103" t="n">
+      <c r="C66" s="105" t="n">
         <v>5</v>
       </c>
       <c r="D66" s="16" t="inlineStr">
@@ -9003,34 +9057,34 @@
           <t>0 / Acq</t>
         </is>
       </c>
-      <c r="D83" s="75" t="n">
+      <c r="D83" s="77" t="n">
         <v>1</v>
       </c>
-      <c r="E83" s="75" t="n">
+      <c r="E83" s="77" t="n">
         <v>2</v>
       </c>
-      <c r="F83" s="75" t="n">
+      <c r="F83" s="77" t="n">
         <v>3</v>
       </c>
-      <c r="G83" s="75" t="n">
+      <c r="G83" s="77" t="n">
         <v>4</v>
       </c>
-      <c r="H83" s="75" t="n">
+      <c r="H83" s="77" t="n">
         <v>5</v>
       </c>
-      <c r="I83" s="75" t="n">
+      <c r="I83" s="77" t="n">
         <v>6</v>
       </c>
-      <c r="J83" s="75" t="n">
+      <c r="J83" s="77" t="n">
         <v>7</v>
       </c>
-      <c r="K83" s="75" t="n">
+      <c r="K83" s="77" t="n">
         <v>8</v>
       </c>
-      <c r="L83" s="75" t="n">
+      <c r="L83" s="77" t="n">
         <v>9</v>
       </c>
-      <c r="M83" s="75" t="n">
+      <c r="M83" s="77" t="n">
         <v>10</v>
       </c>
     </row>
@@ -9753,39 +9807,39 @@
         <f>D92-D99</f>
         <v/>
       </c>
-      <c r="E100" s="76">
+      <c r="E100" s="78">
         <f>E92-E99</f>
         <v/>
       </c>
-      <c r="F100" s="76">
+      <c r="F100" s="78">
         <f>F92-F99</f>
         <v/>
       </c>
-      <c r="G100" s="76">
+      <c r="G100" s="78">
         <f>G92-G99</f>
         <v/>
       </c>
-      <c r="H100" s="76">
+      <c r="H100" s="78">
         <f>H92-H99</f>
         <v/>
       </c>
-      <c r="I100" s="76">
+      <c r="I100" s="78">
         <f>I92-I99</f>
         <v/>
       </c>
-      <c r="J100" s="76">
+      <c r="J100" s="78">
         <f>J92-J99</f>
         <v/>
       </c>
-      <c r="K100" s="76">
+      <c r="K100" s="78">
         <f>K92-K99</f>
         <v/>
       </c>
-      <c r="L100" s="76">
+      <c r="L100" s="78">
         <f>L92-L99</f>
         <v/>
       </c>
-      <c r="M100" s="76">
+      <c r="M100" s="78">
         <f>M92-M99</f>
         <v/>
       </c>
@@ -9963,39 +10017,39 @@
         <f>D100-D104</f>
         <v/>
       </c>
-      <c r="E105" s="76">
+      <c r="E105" s="78">
         <f>E100-E104</f>
         <v/>
       </c>
-      <c r="F105" s="76">
+      <c r="F105" s="78">
         <f>F100-F104</f>
         <v/>
       </c>
-      <c r="G105" s="76">
+      <c r="G105" s="78">
         <f>G100-G104</f>
         <v/>
       </c>
-      <c r="H105" s="76">
+      <c r="H105" s="78">
         <f>H100-H104</f>
         <v/>
       </c>
-      <c r="I105" s="76">
+      <c r="I105" s="78">
         <f>I100-I104</f>
         <v/>
       </c>
-      <c r="J105" s="76">
+      <c r="J105" s="78">
         <f>J100-J104</f>
         <v/>
       </c>
-      <c r="K105" s="76">
+      <c r="K105" s="78">
         <f>K100-K104</f>
         <v/>
       </c>
-      <c r="L105" s="76">
+      <c r="L105" s="78">
         <f>L100-L104</f>
         <v/>
       </c>
-      <c r="M105" s="76">
+      <c r="M105" s="78">
         <f>M100-M104</f>
         <v/>
       </c>
@@ -10080,39 +10134,39 @@
         <f>IF(1&lt;=C66,D105,0)+D108</f>
         <v/>
       </c>
-      <c r="E109" s="76">
+      <c r="E109" s="78">
         <f>IF(2&lt;=C66,E105,0)+E108</f>
         <v/>
       </c>
-      <c r="F109" s="76">
+      <c r="F109" s="78">
         <f>IF(3&lt;=C66,F105,0)+F108</f>
         <v/>
       </c>
-      <c r="G109" s="76">
+      <c r="G109" s="78">
         <f>IF(4&lt;=C66,G105,0)+G108</f>
         <v/>
       </c>
-      <c r="H109" s="76">
+      <c r="H109" s="78">
         <f>IF(5&lt;=C66,H105,0)+H108</f>
         <v/>
       </c>
-      <c r="I109" s="76">
+      <c r="I109" s="78">
         <f>IF(6&lt;=C66,I105,0)+I108</f>
         <v/>
       </c>
-      <c r="J109" s="76">
+      <c r="J109" s="78">
         <f>IF(7&lt;=C66,J105,0)+J108</f>
         <v/>
       </c>
-      <c r="K109" s="76">
+      <c r="K109" s="78">
         <f>IF(8&lt;=C66,K105,0)+K108</f>
         <v/>
       </c>
-      <c r="L109" s="76">
+      <c r="L109" s="78">
         <f>IF(9&lt;=C66,L105,0)+L108</f>
         <v/>
       </c>
-      <c r="M109" s="76">
+      <c r="M109" s="78">
         <f>IF(10&lt;=C66,M105,0)+M108</f>
         <v/>
       </c>
@@ -10217,43 +10271,43 @@
           <t>DSCR (NOI ÷ DS)</t>
         </is>
       </c>
-      <c r="D112" s="79">
+      <c r="D112" s="81">
         <f>D100/C73</f>
         <v/>
       </c>
-      <c r="E112" s="79">
+      <c r="E112" s="81">
         <f>E100/C73</f>
         <v/>
       </c>
-      <c r="F112" s="79">
+      <c r="F112" s="81">
         <f>F100/C73</f>
         <v/>
       </c>
-      <c r="G112" s="79">
+      <c r="G112" s="81">
         <f>G100/C73</f>
         <v/>
       </c>
-      <c r="H112" s="79">
+      <c r="H112" s="81">
         <f>H100/C73</f>
         <v/>
       </c>
-      <c r="I112" s="79">
+      <c r="I112" s="81">
         <f>I100/C73</f>
         <v/>
       </c>
-      <c r="J112" s="79">
+      <c r="J112" s="81">
         <f>J100/C73</f>
         <v/>
       </c>
-      <c r="K112" s="79">
+      <c r="K112" s="81">
         <f>K100/C73</f>
         <v/>
       </c>
-      <c r="L112" s="79">
+      <c r="L112" s="81">
         <f>L100/C73</f>
         <v/>
       </c>
-      <c r="M112" s="79">
+      <c r="M112" s="81">
         <f>M100/C73</f>
         <v/>
       </c>
@@ -10319,39 +10373,39 @@
         <f>IF(1&lt;=C66,D105-C73,0)+IF(1=C66,D108-D111,0)</f>
         <v/>
       </c>
-      <c r="E114" s="76">
+      <c r="E114" s="78">
         <f>IF(2&lt;=C66,E105-C73,0)+IF(2=C66,E108-E111,0)</f>
         <v/>
       </c>
-      <c r="F114" s="76">
+      <c r="F114" s="78">
         <f>IF(3&lt;=C66,F105-C73,0)+IF(3=C66,F108-F111,0)</f>
         <v/>
       </c>
-      <c r="G114" s="76">
+      <c r="G114" s="78">
         <f>IF(4&lt;=C66,G105-C73,0)+IF(4=C66,G108-G111,0)</f>
         <v/>
       </c>
-      <c r="H114" s="76">
+      <c r="H114" s="78">
         <f>IF(5&lt;=C66,H105-C73,0)+IF(5=C66,H108-H111,0)</f>
         <v/>
       </c>
-      <c r="I114" s="76">
+      <c r="I114" s="78">
         <f>IF(6&lt;=C66,I105-C73,0)+IF(6=C66,I108-I111,0)</f>
         <v/>
       </c>
-      <c r="J114" s="76">
+      <c r="J114" s="78">
         <f>IF(7&lt;=C66,J105-C73,0)+IF(7=C66,J108-J111,0)</f>
         <v/>
       </c>
-      <c r="K114" s="76">
+      <c r="K114" s="78">
         <f>IF(8&lt;=C66,K105-C73,0)+IF(8=C66,K108-K111,0)</f>
         <v/>
       </c>
-      <c r="L114" s="76">
+      <c r="L114" s="78">
         <f>IF(9&lt;=C66,L105-C73,0)+IF(9=C66,L108-L111,0)</f>
         <v/>
       </c>
-      <c r="M114" s="76">
+      <c r="M114" s="78">
         <f>IF(10&lt;=C66,M105-C73,0)+IF(10=C66,M108-M111,0)</f>
         <v/>
       </c>
@@ -10392,7 +10446,7 @@
           <t>Unlevered equity multiple</t>
         </is>
       </c>
-      <c r="C118" s="79">
+      <c r="C118" s="81">
         <f>SUM(D109:M109)/-C109</f>
         <v/>
       </c>
@@ -10425,7 +10479,7 @@
           <t>Levered equity multiple</t>
         </is>
       </c>
-      <c r="C121" s="79">
+      <c r="C121" s="81">
         <f>SUM(D114:M114)/C74</f>
         <v/>
       </c>
@@ -10502,7 +10556,7 @@
           <t>Year-1 DSCR</t>
         </is>
       </c>
-      <c r="C128" s="79">
+      <c r="C128" s="81">
         <f>D100/C73</f>
         <v/>
       </c>
@@ -10543,19 +10597,19 @@
           <t>$ / year</t>
         </is>
       </c>
-      <c r="F132" s="104" t="inlineStr">
+      <c r="F132" s="106" t="inlineStr">
         <is>
           <t>In-place (Yr 1)</t>
         </is>
       </c>
       <c r="G132" s="9" t="n"/>
-      <c r="H132" s="104" t="inlineStr">
+      <c r="H132" s="106" t="inlineStr">
         <is>
           <t>Stabilized (Yr 2)</t>
         </is>
       </c>
       <c r="I132" s="9" t="n"/>
-      <c r="J132" s="104" t="inlineStr">
+      <c r="J132" s="106" t="inlineStr">
         <is>
           <t>Per SF (stab.)</t>
         </is>
@@ -10570,7 +10624,7 @@
           <t>Base rental income</t>
         </is>
       </c>
-      <c r="F133" s="76">
+      <c r="F133" s="78">
         <f>D88</f>
         <v/>
       </c>
@@ -10642,7 +10696,7 @@
           <t>Effective Gross Income</t>
         </is>
       </c>
-      <c r="F136" s="76">
+      <c r="F136" s="78">
         <f>D92</f>
         <v/>
       </c>
@@ -10786,7 +10840,7 @@
           <t>Net Operating Income</t>
         </is>
       </c>
-      <c r="F142" s="76">
+      <c r="F142" s="78">
         <f>D100</f>
         <v/>
       </c>
@@ -10858,7 +10912,7 @@
           <t>Cash Flow Before Debt</t>
         </is>
       </c>
-      <c r="F145" s="76">
+      <c r="F145" s="78">
         <f>D105</f>
         <v/>
       </c>
@@ -11504,11 +11558,11 @@
       <c r="D20" s="9" t="n"/>
       <c r="E20" s="30" t="inlineStr"/>
       <c r="F20" s="9" t="n"/>
-      <c r="G20" s="87">
+      <c r="G20" s="89">
         <f>SUM(G18:G19)</f>
         <v/>
       </c>
-      <c r="H20" s="102">
+      <c r="H20" s="104">
         <f>IFERROR(SUM(I18:I19)/SUM(G18:G19),0)</f>
         <v/>
       </c>
@@ -11592,7 +11646,7 @@
           <t>Land (SF)</t>
         </is>
       </c>
-      <c r="C25" s="85">
+      <c r="C25" s="87">
         <f>'Assumptions'!C76</f>
         <v/>
       </c>
@@ -12137,7 +12191,7 @@
           <t>Senior loan amortization (yrs)</t>
         </is>
       </c>
-      <c r="C48" s="103" t="n">
+      <c r="C48" s="105" t="n">
         <v>30</v>
       </c>
       <c r="D48" s="16" t="inlineStr">
@@ -12253,7 +12307,7 @@
           <t>Hold period (yrs)</t>
         </is>
       </c>
-      <c r="C53" s="103" t="n">
+      <c r="C53" s="105" t="n">
         <v>5</v>
       </c>
       <c r="D53" s="16" t="inlineStr">
@@ -12521,34 +12575,34 @@
           <t>0 / Acq</t>
         </is>
       </c>
-      <c r="D70" s="75" t="n">
+      <c r="D70" s="77" t="n">
         <v>1</v>
       </c>
-      <c r="E70" s="75" t="n">
+      <c r="E70" s="77" t="n">
         <v>2</v>
       </c>
-      <c r="F70" s="75" t="n">
+      <c r="F70" s="77" t="n">
         <v>3</v>
       </c>
-      <c r="G70" s="75" t="n">
+      <c r="G70" s="77" t="n">
         <v>4</v>
       </c>
-      <c r="H70" s="75" t="n">
+      <c r="H70" s="77" t="n">
         <v>5</v>
       </c>
-      <c r="I70" s="75" t="n">
+      <c r="I70" s="77" t="n">
         <v>6</v>
       </c>
-      <c r="J70" s="75" t="n">
+      <c r="J70" s="77" t="n">
         <v>7</v>
       </c>
-      <c r="K70" s="75" t="n">
+      <c r="K70" s="77" t="n">
         <v>8</v>
       </c>
-      <c r="L70" s="75" t="n">
+      <c r="L70" s="77" t="n">
         <v>9</v>
       </c>
-      <c r="M70" s="75" t="n">
+      <c r="M70" s="77" t="n">
         <v>10</v>
       </c>
     </row>
@@ -13271,39 +13325,39 @@
         <f>D79-D86</f>
         <v/>
       </c>
-      <c r="E87" s="76">
+      <c r="E87" s="78">
         <f>E79-E86</f>
         <v/>
       </c>
-      <c r="F87" s="76">
+      <c r="F87" s="78">
         <f>F79-F86</f>
         <v/>
       </c>
-      <c r="G87" s="76">
+      <c r="G87" s="78">
         <f>G79-G86</f>
         <v/>
       </c>
-      <c r="H87" s="76">
+      <c r="H87" s="78">
         <f>H79-H86</f>
         <v/>
       </c>
-      <c r="I87" s="76">
+      <c r="I87" s="78">
         <f>I79-I86</f>
         <v/>
       </c>
-      <c r="J87" s="76">
+      <c r="J87" s="78">
         <f>J79-J86</f>
         <v/>
       </c>
-      <c r="K87" s="76">
+      <c r="K87" s="78">
         <f>K79-K86</f>
         <v/>
       </c>
-      <c r="L87" s="76">
+      <c r="L87" s="78">
         <f>L79-L86</f>
         <v/>
       </c>
-      <c r="M87" s="76">
+      <c r="M87" s="78">
         <f>M79-M86</f>
         <v/>
       </c>
@@ -13481,39 +13535,39 @@
         <f>D87-D91</f>
         <v/>
       </c>
-      <c r="E92" s="76">
+      <c r="E92" s="78">
         <f>E87-E91</f>
         <v/>
       </c>
-      <c r="F92" s="76">
+      <c r="F92" s="78">
         <f>F87-F91</f>
         <v/>
       </c>
-      <c r="G92" s="76">
+      <c r="G92" s="78">
         <f>G87-G91</f>
         <v/>
       </c>
-      <c r="H92" s="76">
+      <c r="H92" s="78">
         <f>H87-H91</f>
         <v/>
       </c>
-      <c r="I92" s="76">
+      <c r="I92" s="78">
         <f>I87-I91</f>
         <v/>
       </c>
-      <c r="J92" s="76">
+      <c r="J92" s="78">
         <f>J87-J91</f>
         <v/>
       </c>
-      <c r="K92" s="76">
+      <c r="K92" s="78">
         <f>K87-K91</f>
         <v/>
       </c>
-      <c r="L92" s="76">
+      <c r="L92" s="78">
         <f>L87-L91</f>
         <v/>
       </c>
-      <c r="M92" s="76">
+      <c r="M92" s="78">
         <f>M87-M91</f>
         <v/>
       </c>
@@ -13598,39 +13652,39 @@
         <f>IF(1&lt;=C53,D92,0)+D95</f>
         <v/>
       </c>
-      <c r="E96" s="76">
+      <c r="E96" s="78">
         <f>IF(2&lt;=C53,E92,0)+E95</f>
         <v/>
       </c>
-      <c r="F96" s="76">
+      <c r="F96" s="78">
         <f>IF(3&lt;=C53,F92,0)+F95</f>
         <v/>
       </c>
-      <c r="G96" s="76">
+      <c r="G96" s="78">
         <f>IF(4&lt;=C53,G92,0)+G95</f>
         <v/>
       </c>
-      <c r="H96" s="76">
+      <c r="H96" s="78">
         <f>IF(5&lt;=C53,H92,0)+H95</f>
         <v/>
       </c>
-      <c r="I96" s="76">
+      <c r="I96" s="78">
         <f>IF(6&lt;=C53,I92,0)+I95</f>
         <v/>
       </c>
-      <c r="J96" s="76">
+      <c r="J96" s="78">
         <f>IF(7&lt;=C53,J92,0)+J95</f>
         <v/>
       </c>
-      <c r="K96" s="76">
+      <c r="K96" s="78">
         <f>IF(8&lt;=C53,K92,0)+K95</f>
         <v/>
       </c>
-      <c r="L96" s="76">
+      <c r="L96" s="78">
         <f>IF(9&lt;=C53,L92,0)+L95</f>
         <v/>
       </c>
-      <c r="M96" s="76">
+      <c r="M96" s="78">
         <f>IF(10&lt;=C53,M92,0)+M95</f>
         <v/>
       </c>
@@ -13735,43 +13789,43 @@
           <t>DSCR (NOI ÷ DS)</t>
         </is>
       </c>
-      <c r="D99" s="79">
+      <c r="D99" s="81">
         <f>D87/C60</f>
         <v/>
       </c>
-      <c r="E99" s="79">
+      <c r="E99" s="81">
         <f>E87/C60</f>
         <v/>
       </c>
-      <c r="F99" s="79">
+      <c r="F99" s="81">
         <f>F87/C60</f>
         <v/>
       </c>
-      <c r="G99" s="79">
+      <c r="G99" s="81">
         <f>G87/C60</f>
         <v/>
       </c>
-      <c r="H99" s="79">
+      <c r="H99" s="81">
         <f>H87/C60</f>
         <v/>
       </c>
-      <c r="I99" s="79">
+      <c r="I99" s="81">
         <f>I87/C60</f>
         <v/>
       </c>
-      <c r="J99" s="79">
+      <c r="J99" s="81">
         <f>J87/C60</f>
         <v/>
       </c>
-      <c r="K99" s="79">
+      <c r="K99" s="81">
         <f>K87/C60</f>
         <v/>
       </c>
-      <c r="L99" s="79">
+      <c r="L99" s="81">
         <f>L87/C60</f>
         <v/>
       </c>
-      <c r="M99" s="79">
+      <c r="M99" s="81">
         <f>M87/C60</f>
         <v/>
       </c>
@@ -13837,39 +13891,39 @@
         <f>IF(1&lt;=C53,D92-C60,0)+IF(1=C53,D95-D98,0)</f>
         <v/>
       </c>
-      <c r="E101" s="76">
+      <c r="E101" s="78">
         <f>IF(2&lt;=C53,E92-C60,0)+IF(2=C53,E95-E98,0)</f>
         <v/>
       </c>
-      <c r="F101" s="76">
+      <c r="F101" s="78">
         <f>IF(3&lt;=C53,F92-C60,0)+IF(3=C53,F95-F98,0)</f>
         <v/>
       </c>
-      <c r="G101" s="76">
+      <c r="G101" s="78">
         <f>IF(4&lt;=C53,G92-C60,0)+IF(4=C53,G95-G98,0)</f>
         <v/>
       </c>
-      <c r="H101" s="76">
+      <c r="H101" s="78">
         <f>IF(5&lt;=C53,H92-C60,0)+IF(5=C53,H95-H98,0)</f>
         <v/>
       </c>
-      <c r="I101" s="76">
+      <c r="I101" s="78">
         <f>IF(6&lt;=C53,I92-C60,0)+IF(6=C53,I95-I98,0)</f>
         <v/>
       </c>
-      <c r="J101" s="76">
+      <c r="J101" s="78">
         <f>IF(7&lt;=C53,J92-C60,0)+IF(7=C53,J95-J98,0)</f>
         <v/>
       </c>
-      <c r="K101" s="76">
+      <c r="K101" s="78">
         <f>IF(8&lt;=C53,K92-C60,0)+IF(8=C53,K95-K98,0)</f>
         <v/>
       </c>
-      <c r="L101" s="76">
+      <c r="L101" s="78">
         <f>IF(9&lt;=C53,L92-C60,0)+IF(9=C53,L95-L98,0)</f>
         <v/>
       </c>
-      <c r="M101" s="76">
+      <c r="M101" s="78">
         <f>IF(10&lt;=C53,M92-C60,0)+IF(10=C53,M95-M98,0)</f>
         <v/>
       </c>
@@ -13910,7 +13964,7 @@
           <t>Unlevered equity multiple</t>
         </is>
       </c>
-      <c r="C105" s="79">
+      <c r="C105" s="81">
         <f>SUM(D96:M96)/-C96</f>
         <v/>
       </c>
@@ -13943,7 +13997,7 @@
           <t>Levered equity multiple</t>
         </is>
       </c>
-      <c r="C108" s="79">
+      <c r="C108" s="81">
         <f>SUM(D101:M101)/C61</f>
         <v/>
       </c>
@@ -14020,7 +14074,7 @@
           <t>Year-1 DSCR</t>
         </is>
       </c>
-      <c r="C115" s="79">
+      <c r="C115" s="81">
         <f>D87/C60</f>
         <v/>
       </c>
@@ -14061,7 +14115,7 @@
           <t>Target Year-1 DSCR</t>
         </is>
       </c>
-      <c r="C119" s="105" t="n">
+      <c r="C119" s="107" t="n">
         <v>1.2</v>
       </c>
       <c r="D119" s="16" t="inlineStr">
@@ -14352,19 +14406,19 @@
           <t>$ / year</t>
         </is>
       </c>
-      <c r="F135" s="104" t="inlineStr">
+      <c r="F135" s="106" t="inlineStr">
         <is>
           <t>Year 1</t>
         </is>
       </c>
       <c r="G135" s="9" t="n"/>
-      <c r="H135" s="104" t="inlineStr">
+      <c r="H135" s="106" t="inlineStr">
         <is>
           <t>Stabilized</t>
         </is>
       </c>
       <c r="I135" s="9" t="n"/>
-      <c r="J135" s="104" t="inlineStr">
+      <c r="J135" s="106" t="inlineStr">
         <is>
           <t>Per SF (stab.)</t>
         </is>
@@ -14379,7 +14433,7 @@
           <t>Base rental income</t>
         </is>
       </c>
-      <c r="F136" s="76">
+      <c r="F136" s="78">
         <f>D75</f>
         <v/>
       </c>
@@ -14451,7 +14505,7 @@
           <t>Effective Gross Income</t>
         </is>
       </c>
-      <c r="F139" s="76">
+      <c r="F139" s="78">
         <f>D79</f>
         <v/>
       </c>
@@ -14595,7 +14649,7 @@
           <t>Net Operating Income</t>
         </is>
       </c>
-      <c r="F145" s="76">
+      <c r="F145" s="78">
         <f>D87</f>
         <v/>
       </c>
@@ -14667,7 +14721,7 @@
           <t>Cash Flow Before Debt</t>
         </is>
       </c>
-      <c r="F148" s="76">
+      <c r="F148" s="78">
         <f>D92</f>
         <v/>
       </c>
@@ -15388,15 +15442,15 @@
         </is>
       </c>
       <c r="F22" s="9" t="n"/>
-      <c r="G22" s="100" t="n">
+      <c r="G22" s="102" t="n">
         <v>5000</v>
       </c>
-      <c r="H22" s="101" t="inlineStr">
+      <c r="H22" s="103" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I22" s="101" t="inlineStr">
+      <c r="I22" s="103" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -15420,11 +15474,11 @@
       <c r="D23" s="9" t="n"/>
       <c r="E23" s="30" t="inlineStr"/>
       <c r="F23" s="9" t="n"/>
-      <c r="G23" s="87">
+      <c r="G23" s="89">
         <f>SUM(G17:G22)</f>
         <v/>
       </c>
-      <c r="H23" s="102">
+      <c r="H23" s="104">
         <f>IFERROR(SUM(I17:I21)/SUM(G17:G21),0)</f>
         <v/>
       </c>
@@ -15508,7 +15562,7 @@
           <t>Land (SF)</t>
         </is>
       </c>
-      <c r="C28" s="85">
+      <c r="C28" s="87">
         <f>'Assumptions'!C96</f>
         <v/>
       </c>
@@ -16053,7 +16107,7 @@
           <t>Senior loan amortization (yrs)</t>
         </is>
       </c>
-      <c r="C51" s="103" t="n">
+      <c r="C51" s="105" t="n">
         <v>30</v>
       </c>
       <c r="D51" s="16" t="inlineStr">
@@ -16169,7 +16223,7 @@
           <t>Hold period (yrs)</t>
         </is>
       </c>
-      <c r="C56" s="103" t="n">
+      <c r="C56" s="105" t="n">
         <v>5</v>
       </c>
       <c r="D56" s="16" t="inlineStr">
@@ -16437,34 +16491,34 @@
           <t>0 / Acq</t>
         </is>
       </c>
-      <c r="D73" s="75" t="n">
+      <c r="D73" s="77" t="n">
         <v>1</v>
       </c>
-      <c r="E73" s="75" t="n">
+      <c r="E73" s="77" t="n">
         <v>2</v>
       </c>
-      <c r="F73" s="75" t="n">
+      <c r="F73" s="77" t="n">
         <v>3</v>
       </c>
-      <c r="G73" s="75" t="n">
+      <c r="G73" s="77" t="n">
         <v>4</v>
       </c>
-      <c r="H73" s="75" t="n">
+      <c r="H73" s="77" t="n">
         <v>5</v>
       </c>
-      <c r="I73" s="75" t="n">
+      <c r="I73" s="77" t="n">
         <v>6</v>
       </c>
-      <c r="J73" s="75" t="n">
+      <c r="J73" s="77" t="n">
         <v>7</v>
       </c>
-      <c r="K73" s="75" t="n">
+      <c r="K73" s="77" t="n">
         <v>8</v>
       </c>
-      <c r="L73" s="75" t="n">
+      <c r="L73" s="77" t="n">
         <v>9</v>
       </c>
-      <c r="M73" s="75" t="n">
+      <c r="M73" s="77" t="n">
         <v>10</v>
       </c>
     </row>
@@ -17187,39 +17241,39 @@
         <f>D82-D89</f>
         <v/>
       </c>
-      <c r="E90" s="76">
+      <c r="E90" s="78">
         <f>E82-E89</f>
         <v/>
       </c>
-      <c r="F90" s="76">
+      <c r="F90" s="78">
         <f>F82-F89</f>
         <v/>
       </c>
-      <c r="G90" s="76">
+      <c r="G90" s="78">
         <f>G82-G89</f>
         <v/>
       </c>
-      <c r="H90" s="76">
+      <c r="H90" s="78">
         <f>H82-H89</f>
         <v/>
       </c>
-      <c r="I90" s="76">
+      <c r="I90" s="78">
         <f>I82-I89</f>
         <v/>
       </c>
-      <c r="J90" s="76">
+      <c r="J90" s="78">
         <f>J82-J89</f>
         <v/>
       </c>
-      <c r="K90" s="76">
+      <c r="K90" s="78">
         <f>K82-K89</f>
         <v/>
       </c>
-      <c r="L90" s="76">
+      <c r="L90" s="78">
         <f>L82-L89</f>
         <v/>
       </c>
-      <c r="M90" s="76">
+      <c r="M90" s="78">
         <f>M82-M89</f>
         <v/>
       </c>
@@ -17397,39 +17451,39 @@
         <f>D90-D94</f>
         <v/>
       </c>
-      <c r="E95" s="76">
+      <c r="E95" s="78">
         <f>E90-E94</f>
         <v/>
       </c>
-      <c r="F95" s="76">
+      <c r="F95" s="78">
         <f>F90-F94</f>
         <v/>
       </c>
-      <c r="G95" s="76">
+      <c r="G95" s="78">
         <f>G90-G94</f>
         <v/>
       </c>
-      <c r="H95" s="76">
+      <c r="H95" s="78">
         <f>H90-H94</f>
         <v/>
       </c>
-      <c r="I95" s="76">
+      <c r="I95" s="78">
         <f>I90-I94</f>
         <v/>
       </c>
-      <c r="J95" s="76">
+      <c r="J95" s="78">
         <f>J90-J94</f>
         <v/>
       </c>
-      <c r="K95" s="76">
+      <c r="K95" s="78">
         <f>K90-K94</f>
         <v/>
       </c>
-      <c r="L95" s="76">
+      <c r="L95" s="78">
         <f>L90-L94</f>
         <v/>
       </c>
-      <c r="M95" s="76">
+      <c r="M95" s="78">
         <f>M90-M94</f>
         <v/>
       </c>
@@ -17514,39 +17568,39 @@
         <f>IF(1&lt;=C56,D95,0)+D98</f>
         <v/>
       </c>
-      <c r="E99" s="76">
+      <c r="E99" s="78">
         <f>IF(2&lt;=C56,E95,0)+E98</f>
         <v/>
       </c>
-      <c r="F99" s="76">
+      <c r="F99" s="78">
         <f>IF(3&lt;=C56,F95,0)+F98</f>
         <v/>
       </c>
-      <c r="G99" s="76">
+      <c r="G99" s="78">
         <f>IF(4&lt;=C56,G95,0)+G98</f>
         <v/>
       </c>
-      <c r="H99" s="76">
+      <c r="H99" s="78">
         <f>IF(5&lt;=C56,H95,0)+H98</f>
         <v/>
       </c>
-      <c r="I99" s="76">
+      <c r="I99" s="78">
         <f>IF(6&lt;=C56,I95,0)+I98</f>
         <v/>
       </c>
-      <c r="J99" s="76">
+      <c r="J99" s="78">
         <f>IF(7&lt;=C56,J95,0)+J98</f>
         <v/>
       </c>
-      <c r="K99" s="76">
+      <c r="K99" s="78">
         <f>IF(8&lt;=C56,K95,0)+K98</f>
         <v/>
       </c>
-      <c r="L99" s="76">
+      <c r="L99" s="78">
         <f>IF(9&lt;=C56,L95,0)+L98</f>
         <v/>
       </c>
-      <c r="M99" s="76">
+      <c r="M99" s="78">
         <f>IF(10&lt;=C56,M95,0)+M98</f>
         <v/>
       </c>
@@ -17651,43 +17705,43 @@
           <t>DSCR (NOI ÷ DS)</t>
         </is>
       </c>
-      <c r="D102" s="79">
+      <c r="D102" s="81">
         <f>D90/C63</f>
         <v/>
       </c>
-      <c r="E102" s="79">
+      <c r="E102" s="81">
         <f>E90/C63</f>
         <v/>
       </c>
-      <c r="F102" s="79">
+      <c r="F102" s="81">
         <f>F90/C63</f>
         <v/>
       </c>
-      <c r="G102" s="79">
+      <c r="G102" s="81">
         <f>G90/C63</f>
         <v/>
       </c>
-      <c r="H102" s="79">
+      <c r="H102" s="81">
         <f>H90/C63</f>
         <v/>
       </c>
-      <c r="I102" s="79">
+      <c r="I102" s="81">
         <f>I90/C63</f>
         <v/>
       </c>
-      <c r="J102" s="79">
+      <c r="J102" s="81">
         <f>J90/C63</f>
         <v/>
       </c>
-      <c r="K102" s="79">
+      <c r="K102" s="81">
         <f>K90/C63</f>
         <v/>
       </c>
-      <c r="L102" s="79">
+      <c r="L102" s="81">
         <f>L90/C63</f>
         <v/>
       </c>
-      <c r="M102" s="79">
+      <c r="M102" s="81">
         <f>M90/C63</f>
         <v/>
       </c>
@@ -17753,39 +17807,39 @@
         <f>IF(1&lt;=C56,D95-C63,0)+IF(1=C56,D98-D101,0)</f>
         <v/>
       </c>
-      <c r="E104" s="76">
+      <c r="E104" s="78">
         <f>IF(2&lt;=C56,E95-C63,0)+IF(2=C56,E98-E101,0)</f>
         <v/>
       </c>
-      <c r="F104" s="76">
+      <c r="F104" s="78">
         <f>IF(3&lt;=C56,F95-C63,0)+IF(3=C56,F98-F101,0)</f>
         <v/>
       </c>
-      <c r="G104" s="76">
+      <c r="G104" s="78">
         <f>IF(4&lt;=C56,G95-C63,0)+IF(4=C56,G98-G101,0)</f>
         <v/>
       </c>
-      <c r="H104" s="76">
+      <c r="H104" s="78">
         <f>IF(5&lt;=C56,H95-C63,0)+IF(5=C56,H98-H101,0)</f>
         <v/>
       </c>
-      <c r="I104" s="76">
+      <c r="I104" s="78">
         <f>IF(6&lt;=C56,I95-C63,0)+IF(6=C56,I98-I101,0)</f>
         <v/>
       </c>
-      <c r="J104" s="76">
+      <c r="J104" s="78">
         <f>IF(7&lt;=C56,J95-C63,0)+IF(7=C56,J98-J101,0)</f>
         <v/>
       </c>
-      <c r="K104" s="76">
+      <c r="K104" s="78">
         <f>IF(8&lt;=C56,K95-C63,0)+IF(8=C56,K98-K101,0)</f>
         <v/>
       </c>
-      <c r="L104" s="76">
+      <c r="L104" s="78">
         <f>IF(9&lt;=C56,L95-C63,0)+IF(9=C56,L98-L101,0)</f>
         <v/>
       </c>
-      <c r="M104" s="76">
+      <c r="M104" s="78">
         <f>IF(10&lt;=C56,M95-C63,0)+IF(10=C56,M98-M101,0)</f>
         <v/>
       </c>
@@ -17826,7 +17880,7 @@
           <t>Unlevered equity multiple</t>
         </is>
       </c>
-      <c r="C108" s="79">
+      <c r="C108" s="81">
         <f>SUM(D99:M99)/-C99</f>
         <v/>
       </c>
@@ -17859,7 +17913,7 @@
           <t>Levered equity multiple</t>
         </is>
       </c>
-      <c r="C111" s="79">
+      <c r="C111" s="81">
         <f>SUM(D104:M104)/C64</f>
         <v/>
       </c>
@@ -17936,7 +17990,7 @@
           <t>Year-1 DSCR</t>
         </is>
       </c>
-      <c r="C118" s="79">
+      <c r="C118" s="81">
         <f>D90/C63</f>
         <v/>
       </c>
@@ -17977,19 +18031,19 @@
           <t>$ / year</t>
         </is>
       </c>
-      <c r="F122" s="104" t="inlineStr">
+      <c r="F122" s="106" t="inlineStr">
         <is>
           <t>Year 1</t>
         </is>
       </c>
       <c r="G122" s="9" t="n"/>
-      <c r="H122" s="104" t="inlineStr">
+      <c r="H122" s="106" t="inlineStr">
         <is>
           <t>Stabilized</t>
         </is>
       </c>
       <c r="I122" s="9" t="n"/>
-      <c r="J122" s="104" t="inlineStr">
+      <c r="J122" s="106" t="inlineStr">
         <is>
           <t>Per SF (stab.)</t>
         </is>
@@ -18004,7 +18058,7 @@
           <t>Base rental income</t>
         </is>
       </c>
-      <c r="F123" s="76">
+      <c r="F123" s="78">
         <f>D78</f>
         <v/>
       </c>
@@ -18076,7 +18130,7 @@
           <t>Effective Gross Income</t>
         </is>
       </c>
-      <c r="F126" s="76">
+      <c r="F126" s="78">
         <f>D82</f>
         <v/>
       </c>
@@ -18220,7 +18274,7 @@
           <t>Net Operating Income</t>
         </is>
       </c>
-      <c r="F132" s="76">
+      <c r="F132" s="78">
         <f>D90</f>
         <v/>
       </c>
@@ -18292,7 +18346,7 @@
           <t>Cash Flow Before Debt</t>
         </is>
       </c>
-      <c r="F135" s="76">
+      <c r="F135" s="78">
         <f>D95</f>
         <v/>
       </c>
@@ -19209,7 +19263,7 @@
           <t>Amortization (yrs)</t>
         </is>
       </c>
-      <c r="C33" s="103" t="n">
+      <c r="C33" s="105" t="n">
         <v>30</v>
       </c>
       <c r="D33" s="16" t="inlineStr">
@@ -19307,7 +19361,7 @@
           <t>Hold period (yrs)</t>
         </is>
       </c>
-      <c r="C37" s="103" t="n">
+      <c r="C37" s="105" t="n">
         <v>5</v>
       </c>
       <c r="D37" s="16" t="inlineStr">
@@ -19502,34 +19556,34 @@
           <t>0 / Acq</t>
         </is>
       </c>
-      <c r="D50" s="75" t="n">
+      <c r="D50" s="77" t="n">
         <v>1</v>
       </c>
-      <c r="E50" s="75" t="n">
+      <c r="E50" s="77" t="n">
         <v>2</v>
       </c>
-      <c r="F50" s="75" t="n">
+      <c r="F50" s="77" t="n">
         <v>3</v>
       </c>
-      <c r="G50" s="75" t="n">
+      <c r="G50" s="77" t="n">
         <v>4</v>
       </c>
-      <c r="H50" s="75" t="n">
+      <c r="H50" s="77" t="n">
         <v>5</v>
       </c>
-      <c r="I50" s="75" t="n">
+      <c r="I50" s="77" t="n">
         <v>6</v>
       </c>
-      <c r="J50" s="75" t="n">
+      <c r="J50" s="77" t="n">
         <v>7</v>
       </c>
-      <c r="K50" s="75" t="n">
+      <c r="K50" s="77" t="n">
         <v>8</v>
       </c>
-      <c r="L50" s="75" t="n">
+      <c r="L50" s="77" t="n">
         <v>9</v>
       </c>
-      <c r="M50" s="75" t="n">
+      <c r="M50" s="77" t="n">
         <v>10</v>
       </c>
     </row>
@@ -20046,39 +20100,39 @@
         <f>D56-D61</f>
         <v/>
       </c>
-      <c r="E62" s="76">
+      <c r="E62" s="78">
         <f>E56-E61</f>
         <v/>
       </c>
-      <c r="F62" s="76">
+      <c r="F62" s="78">
         <f>F56-F61</f>
         <v/>
       </c>
-      <c r="G62" s="76">
+      <c r="G62" s="78">
         <f>G56-G61</f>
         <v/>
       </c>
-      <c r="H62" s="76">
+      <c r="H62" s="78">
         <f>H56-H61</f>
         <v/>
       </c>
-      <c r="I62" s="76">
+      <c r="I62" s="78">
         <f>I56-I61</f>
         <v/>
       </c>
-      <c r="J62" s="76">
+      <c r="J62" s="78">
         <f>J56-J61</f>
         <v/>
       </c>
-      <c r="K62" s="76">
+      <c r="K62" s="78">
         <f>K56-K61</f>
         <v/>
       </c>
-      <c r="L62" s="76">
+      <c r="L62" s="78">
         <f>L56-L61</f>
         <v/>
       </c>
-      <c r="M62" s="76">
+      <c r="M62" s="78">
         <f>M56-M61</f>
         <v/>
       </c>
@@ -20144,39 +20198,39 @@
         <f>D62-D63</f>
         <v/>
       </c>
-      <c r="E64" s="76">
+      <c r="E64" s="78">
         <f>E62-E63</f>
         <v/>
       </c>
-      <c r="F64" s="76">
+      <c r="F64" s="78">
         <f>F62-F63</f>
         <v/>
       </c>
-      <c r="G64" s="76">
+      <c r="G64" s="78">
         <f>G62-G63</f>
         <v/>
       </c>
-      <c r="H64" s="76">
+      <c r="H64" s="78">
         <f>H62-H63</f>
         <v/>
       </c>
-      <c r="I64" s="76">
+      <c r="I64" s="78">
         <f>I62-I63</f>
         <v/>
       </c>
-      <c r="J64" s="76">
+      <c r="J64" s="78">
         <f>J62-J63</f>
         <v/>
       </c>
-      <c r="K64" s="76">
+      <c r="K64" s="78">
         <f>K62-K63</f>
         <v/>
       </c>
-      <c r="L64" s="76">
+      <c r="L64" s="78">
         <f>L62-L63</f>
         <v/>
       </c>
-      <c r="M64" s="76">
+      <c r="M64" s="78">
         <f>M62-M63</f>
         <v/>
       </c>
@@ -20261,39 +20315,39 @@
         <f>IF(1&lt;=C37,D64,0)+D67</f>
         <v/>
       </c>
-      <c r="E68" s="76">
+      <c r="E68" s="78">
         <f>IF(2&lt;=C37,E64,0)+E67</f>
         <v/>
       </c>
-      <c r="F68" s="76">
+      <c r="F68" s="78">
         <f>IF(3&lt;=C37,F64,0)+F67</f>
         <v/>
       </c>
-      <c r="G68" s="76">
+      <c r="G68" s="78">
         <f>IF(4&lt;=C37,G64,0)+G67</f>
         <v/>
       </c>
-      <c r="H68" s="76">
+      <c r="H68" s="78">
         <f>IF(5&lt;=C37,H64,0)+H67</f>
         <v/>
       </c>
-      <c r="I68" s="76">
+      <c r="I68" s="78">
         <f>IF(6&lt;=C37,I64,0)+I67</f>
         <v/>
       </c>
-      <c r="J68" s="76">
+      <c r="J68" s="78">
         <f>IF(7&lt;=C37,J64,0)+J67</f>
         <v/>
       </c>
-      <c r="K68" s="76">
+      <c r="K68" s="78">
         <f>IF(8&lt;=C37,K64,0)+K67</f>
         <v/>
       </c>
-      <c r="L68" s="76">
+      <c r="L68" s="78">
         <f>IF(9&lt;=C37,L64,0)+L67</f>
         <v/>
       </c>
-      <c r="M68" s="76">
+      <c r="M68" s="78">
         <f>IF(10&lt;=C37,M64,0)+M67</f>
         <v/>
       </c>
@@ -20351,43 +20405,43 @@
           <t>DSCR (NOI ÷ DS)</t>
         </is>
       </c>
-      <c r="D70" s="79">
+      <c r="D70" s="81">
         <f>D62/C44</f>
         <v/>
       </c>
-      <c r="E70" s="79">
+      <c r="E70" s="81">
         <f>E62/C44</f>
         <v/>
       </c>
-      <c r="F70" s="79">
+      <c r="F70" s="81">
         <f>F62/C44</f>
         <v/>
       </c>
-      <c r="G70" s="79">
+      <c r="G70" s="81">
         <f>G62/C44</f>
         <v/>
       </c>
-      <c r="H70" s="79">
+      <c r="H70" s="81">
         <f>H62/C44</f>
         <v/>
       </c>
-      <c r="I70" s="79">
+      <c r="I70" s="81">
         <f>I62/C44</f>
         <v/>
       </c>
-      <c r="J70" s="79">
+      <c r="J70" s="81">
         <f>J62/C44</f>
         <v/>
       </c>
-      <c r="K70" s="79">
+      <c r="K70" s="81">
         <f>K62/C44</f>
         <v/>
       </c>
-      <c r="L70" s="79">
+      <c r="L70" s="81">
         <f>L62/C44</f>
         <v/>
       </c>
-      <c r="M70" s="79">
+      <c r="M70" s="81">
         <f>M62/C44</f>
         <v/>
       </c>
@@ -20406,39 +20460,39 @@
         <f>IF(1&lt;=C37,D64-C44,0)+IF(1=C37,D67-D69,0)</f>
         <v/>
       </c>
-      <c r="E71" s="76">
+      <c r="E71" s="78">
         <f>IF(2&lt;=C37,E64-C44,0)+IF(2=C37,E67-E69,0)</f>
         <v/>
       </c>
-      <c r="F71" s="76">
+      <c r="F71" s="78">
         <f>IF(3&lt;=C37,F64-C44,0)+IF(3=C37,F67-F69,0)</f>
         <v/>
       </c>
-      <c r="G71" s="76">
+      <c r="G71" s="78">
         <f>IF(4&lt;=C37,G64-C44,0)+IF(4=C37,G67-G69,0)</f>
         <v/>
       </c>
-      <c r="H71" s="76">
+      <c r="H71" s="78">
         <f>IF(5&lt;=C37,H64-C44,0)+IF(5=C37,H67-H69,0)</f>
         <v/>
       </c>
-      <c r="I71" s="76">
+      <c r="I71" s="78">
         <f>IF(6&lt;=C37,I64-C44,0)+IF(6=C37,I67-I69,0)</f>
         <v/>
       </c>
-      <c r="J71" s="76">
+      <c r="J71" s="78">
         <f>IF(7&lt;=C37,J64-C44,0)+IF(7=C37,J67-J69,0)</f>
         <v/>
       </c>
-      <c r="K71" s="76">
+      <c r="K71" s="78">
         <f>IF(8&lt;=C37,K64-C44,0)+IF(8=C37,K67-K69,0)</f>
         <v/>
       </c>
-      <c r="L71" s="76">
+      <c r="L71" s="78">
         <f>IF(9&lt;=C37,L64-C44,0)+IF(9=C37,L67-L69,0)</f>
         <v/>
       </c>
-      <c r="M71" s="76">
+      <c r="M71" s="78">
         <f>IF(10&lt;=C37,M64-C44,0)+IF(10=C37,M67-M69,0)</f>
         <v/>
       </c>
@@ -20479,7 +20533,7 @@
           <t>Unlevered equity multiple</t>
         </is>
       </c>
-      <c r="C75" s="79">
+      <c r="C75" s="81">
         <f>SUM(D68:M68)/-C68</f>
         <v/>
       </c>
@@ -20512,7 +20566,7 @@
           <t>Levered equity multiple</t>
         </is>
       </c>
-      <c r="C78" s="79">
+      <c r="C78" s="81">
         <f>SUM(D71:M71)/C45</f>
         <v/>
       </c>
@@ -20711,7 +20765,7 @@
       <c r="F91" s="55" t="n">
         <v>10000000</v>
       </c>
-      <c r="G91" s="106" t="inlineStr">
+      <c r="G91" s="108" t="inlineStr">
         <is>
           <t>09/2019</t>
         </is>
@@ -20750,7 +20804,7 @@
       <c r="F92" s="55" t="n">
         <v>410000</v>
       </c>
-      <c r="G92" s="106" t="inlineStr">
+      <c r="G92" s="108" t="inlineStr">
         <is>
           <t>11/2019</t>
         </is>
@@ -20789,7 +20843,7 @@
       <c r="F93" s="55" t="n">
         <v>515000</v>
       </c>
-      <c r="G93" s="106" t="inlineStr">
+      <c r="G93" s="108" t="inlineStr">
         <is>
           <t>02/2025</t>
         </is>
@@ -20828,7 +20882,7 @@
       <c r="F94" s="55" t="n">
         <v>260000</v>
       </c>
-      <c r="G94" s="106" t="inlineStr">
+      <c r="G94" s="108" t="inlineStr">
         <is>
           <t>06/2024</t>
         </is>
@@ -20864,12 +20918,12 @@
         <f>D95/C18</f>
         <v/>
       </c>
-      <c r="F95" s="107" t="inlineStr">
+      <c r="F95" s="109" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G95" s="106" t="inlineStr">
+      <c r="G95" s="108" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -20905,12 +20959,12 @@
         <f>D96/C18</f>
         <v/>
       </c>
-      <c r="F96" s="107" t="inlineStr">
+      <c r="F96" s="109" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G96" s="106" t="inlineStr">
+      <c r="G96" s="108" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -20946,12 +21000,12 @@
         <f>D97/C18</f>
         <v/>
       </c>
-      <c r="F97" s="107" t="inlineStr">
+      <c r="F97" s="109" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G97" s="106" t="inlineStr">
+      <c r="G97" s="108" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -20987,12 +21041,12 @@
         <f>D98/C18</f>
         <v/>
       </c>
-      <c r="F98" s="107" t="inlineStr">
+      <c r="F98" s="109" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G98" s="106" t="inlineStr">
+      <c r="G98" s="108" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -21021,20 +21075,20 @@
         </is>
       </c>
       <c r="C99" s="9" t="n"/>
-      <c r="D99" s="108">
+      <c r="D99" s="110">
         <f>SUM(D91:D98)</f>
         <v/>
       </c>
-      <c r="E99" s="109">
+      <c r="E99" s="111">
         <f>SUM(E91:E98)</f>
         <v/>
       </c>
-      <c r="F99" s="110" t="inlineStr">
+      <c r="F99" s="112" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G99" s="110" t="inlineStr">
+      <c r="G99" s="112" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -21117,19 +21171,19 @@
           <t>$ / year</t>
         </is>
       </c>
-      <c r="F104" s="104" t="inlineStr">
+      <c r="F104" s="106" t="inlineStr">
         <is>
           <t>Year 1</t>
         </is>
       </c>
       <c r="G104" s="9" t="n"/>
-      <c r="H104" s="104" t="inlineStr">
+      <c r="H104" s="106" t="inlineStr">
         <is>
           <t>Stabilized</t>
         </is>
       </c>
       <c r="I104" s="9" t="n"/>
-      <c r="J104" s="104" t="inlineStr">
+      <c r="J104" s="106" t="inlineStr">
         <is>
           <t>Per SF (stab.)</t>
         </is>
@@ -21144,7 +21198,7 @@
           <t>Gross rental income (MG)</t>
         </is>
       </c>
-      <c r="F105" s="76">
+      <c r="F105" s="78">
         <f>D54</f>
         <v/>
       </c>
@@ -21192,7 +21246,7 @@
           <t>Effective Gross Income</t>
         </is>
       </c>
-      <c r="F107" s="76">
+      <c r="F107" s="78">
         <f>D56</f>
         <v/>
       </c>
@@ -21288,7 +21342,7 @@
           <t>Net Operating Income</t>
         </is>
       </c>
-      <c r="F111" s="76">
+      <c r="F111" s="78">
         <f>D62</f>
         <v/>
       </c>
@@ -21336,7 +21390,7 @@
           <t>Cash Flow Before Debt</t>
         </is>
       </c>
-      <c r="F113" s="76">
+      <c r="F113" s="78">
         <f>D64</f>
         <v/>
       </c>
@@ -21517,7 +21571,7 @@
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="001F2D4E"/>
+    <tabColor rgb="002E7D4F"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -22164,7 +22218,7 @@
           <t>Hold period (yrs)</t>
         </is>
       </c>
-      <c r="C31" s="103" t="n">
+      <c r="C31" s="105" t="n">
         <v>5</v>
       </c>
       <c r="D31" s="16" t="inlineStr">
@@ -22329,17 +22383,17 @@
           <t>Approach</t>
         </is>
       </c>
-      <c r="D39" s="104" t="inlineStr">
+      <c r="D39" s="106" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E39" s="104" t="inlineStr">
+      <c r="E39" s="106" t="inlineStr">
         <is>
           <t>Base</t>
         </is>
       </c>
-      <c r="F39" s="104" t="inlineStr">
+      <c r="F39" s="106" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -22482,7 +22536,7 @@
           <t>Concluded acquisition basis</t>
         </is>
       </c>
-      <c r="E44" s="92">
+      <c r="E44" s="94">
         <f>C28</f>
         <v/>
       </c>
@@ -22686,34 +22740,34 @@
           <t>0 / Acq</t>
         </is>
       </c>
-      <c r="D60" s="75" t="n">
+      <c r="D60" s="77" t="n">
         <v>1</v>
       </c>
-      <c r="E60" s="75" t="n">
+      <c r="E60" s="77" t="n">
         <v>2</v>
       </c>
-      <c r="F60" s="75" t="n">
+      <c r="F60" s="77" t="n">
         <v>3</v>
       </c>
-      <c r="G60" s="75" t="n">
+      <c r="G60" s="77" t="n">
         <v>4</v>
       </c>
-      <c r="H60" s="75" t="n">
+      <c r="H60" s="77" t="n">
         <v>5</v>
       </c>
-      <c r="I60" s="75" t="n">
+      <c r="I60" s="77" t="n">
         <v>6</v>
       </c>
-      <c r="J60" s="75" t="n">
+      <c r="J60" s="77" t="n">
         <v>7</v>
       </c>
-      <c r="K60" s="75" t="n">
+      <c r="K60" s="77" t="n">
         <v>8</v>
       </c>
-      <c r="L60" s="75" t="n">
+      <c r="L60" s="77" t="n">
         <v>9</v>
       </c>
-      <c r="M60" s="75" t="n">
+      <c r="M60" s="77" t="n">
         <v>10</v>
       </c>
     </row>
@@ -22872,39 +22926,39 @@
         <f>IF(1&lt;=C31,D62,0)+D63</f>
         <v/>
       </c>
-      <c r="E64" s="76">
+      <c r="E64" s="78">
         <f>IF(2&lt;=C31,E62,0)+E63</f>
         <v/>
       </c>
-      <c r="F64" s="76">
+      <c r="F64" s="78">
         <f>IF(3&lt;=C31,F62,0)+F63</f>
         <v/>
       </c>
-      <c r="G64" s="76">
+      <c r="G64" s="78">
         <f>IF(4&lt;=C31,G62,0)+G63</f>
         <v/>
       </c>
-      <c r="H64" s="76">
+      <c r="H64" s="78">
         <f>IF(5&lt;=C31,H62,0)+H63</f>
         <v/>
       </c>
-      <c r="I64" s="76">
+      <c r="I64" s="78">
         <f>IF(6&lt;=C31,I62,0)+I63</f>
         <v/>
       </c>
-      <c r="J64" s="76">
+      <c r="J64" s="78">
         <f>IF(7&lt;=C31,J62,0)+J63</f>
         <v/>
       </c>
-      <c r="K64" s="76">
+      <c r="K64" s="78">
         <f>IF(8&lt;=C31,K62,0)+K63</f>
         <v/>
       </c>
-      <c r="L64" s="76">
+      <c r="L64" s="78">
         <f>IF(9&lt;=C31,L62,0)+L63</f>
         <v/>
       </c>
-      <c r="M64" s="76">
+      <c r="M64" s="78">
         <f>IF(10&lt;=C31,M62,0)+M63</f>
         <v/>
       </c>
@@ -22970,39 +23024,39 @@
         <f>IF(1&lt;=C31,D62-C55,0)+IF(1=C31,D63-C54,0)</f>
         <v/>
       </c>
-      <c r="E66" s="76">
+      <c r="E66" s="78">
         <f>IF(2&lt;=C31,E62-C55,0)+IF(2=C31,E63-C54,0)</f>
         <v/>
       </c>
-      <c r="F66" s="76">
+      <c r="F66" s="78">
         <f>IF(3&lt;=C31,F62-C55,0)+IF(3=C31,F63-C54,0)</f>
         <v/>
       </c>
-      <c r="G66" s="76">
+      <c r="G66" s="78">
         <f>IF(4&lt;=C31,G62-C55,0)+IF(4=C31,G63-C54,0)</f>
         <v/>
       </c>
-      <c r="H66" s="76">
+      <c r="H66" s="78">
         <f>IF(5&lt;=C31,H62-C55,0)+IF(5=C31,H63-C54,0)</f>
         <v/>
       </c>
-      <c r="I66" s="76">
+      <c r="I66" s="78">
         <f>IF(6&lt;=C31,I62-C55,0)+IF(6=C31,I63-C54,0)</f>
         <v/>
       </c>
-      <c r="J66" s="76">
+      <c r="J66" s="78">
         <f>IF(7&lt;=C31,J62-C55,0)+IF(7=C31,J63-C54,0)</f>
         <v/>
       </c>
-      <c r="K66" s="76">
+      <c r="K66" s="78">
         <f>IF(8&lt;=C31,K62-C55,0)+IF(8=C31,K63-C54,0)</f>
         <v/>
       </c>
-      <c r="L66" s="76">
+      <c r="L66" s="78">
         <f>IF(9&lt;=C31,L62-C55,0)+IF(9=C31,L63-C54,0)</f>
         <v/>
       </c>
-      <c r="M66" s="76">
+      <c r="M66" s="78">
         <f>IF(10&lt;=C31,M62-C55,0)+IF(10=C31,M63-C54,0)</f>
         <v/>
       </c>
@@ -23043,7 +23097,7 @@
           <t>Unlevered equity multiple</t>
         </is>
       </c>
-      <c r="C70" s="79">
+      <c r="C70" s="81">
         <f>SUM(D64:M64)/-C64</f>
         <v/>
       </c>
@@ -23076,7 +23130,7 @@
           <t>Levered equity multiple</t>
         </is>
       </c>
-      <c r="C73" s="79">
+      <c r="C73" s="81">
         <f>SUM(D66:M66)/C56</f>
         <v/>
       </c>
@@ -25810,12 +25864,12 @@
     <row r="29" ht="15" customHeight="1">
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>Redevelopment residual (Live Local)</t>
+          <t>Redevelopment (see Development Pro Forma)</t>
         </is>
       </c>
       <c r="C29" s="9" t="n"/>
       <c r="D29" s="24">
-        <f>'Land'!C82</f>
+        <f>'Bayview JV'!C82</f>
         <v/>
       </c>
       <c r="E29" s="8" t="n"/>
@@ -27734,11 +27788,11 @@
       </c>
       <c r="C70" s="42" t="n"/>
       <c r="D70" s="20">
-        <f>'Land'!E44</f>
+        <f>'Bayview JV'!E44</f>
         <v/>
       </c>
       <c r="F70" s="24">
-        <f>'Land'!C52</f>
+        <f>'Bayview JV'!C52</f>
         <v/>
       </c>
       <c r="G70" s="16" t="inlineStr">
@@ -28123,7 +28177,7 @@
       <c r="C86" s="8" t="n"/>
       <c r="D86" s="9" t="n"/>
       <c r="E86" s="24">
-        <f>'Land'!E44</f>
+        <f>'Bayview JV'!E44</f>
         <v/>
       </c>
       <c r="F86" s="9" t="n"/>
@@ -30768,7 +30822,7 @@
         <v/>
       </c>
       <c r="E21" s="24">
-        <f>'Land'!E44</f>
+        <f>'Bayview JV'!E44</f>
         <v/>
       </c>
       <c r="F21" s="64" t="inlineStr">
@@ -34077,7 +34131,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="B122" s="14" t="inlineStr">
         <is>
-          <t>1040 Bayview — covered land (interim office)  ⚠️ reported parcel</t>
+          <t>1040 Bayview — JV UPSIDE (sold to Willow Bridge ~Aug 2026; NOT in the 4-parcel core)</t>
         </is>
       </c>
       <c r="C122" s="8" t="n"/>
@@ -34420,9 +34474,10 @@
           <t>1040 Bayview — land SF</t>
         </is>
       </c>
-      <c r="C140" s="74">
-        <f>'Land'!C19</f>
-        <v/>
+      <c r="C140" s="75" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
       </c>
       <c r="D140" s="40" t="inlineStr">
         <is>
@@ -34449,9 +34504,10 @@
           <t>1040 Bayview — office SF</t>
         </is>
       </c>
-      <c r="C141" s="74">
-        <f>'Land'!C20</f>
-        <v/>
+      <c r="C141" s="75" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
       </c>
       <c r="D141" s="40" t="inlineStr">
         <is>
@@ -34478,9 +34534,10 @@
           <t>1040 Bayview — entitled units</t>
         </is>
       </c>
-      <c r="C142" s="74">
-        <f>'Land'!C21</f>
-        <v/>
+      <c r="C142" s="75" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
       </c>
       <c r="D142" s="40" t="inlineStr">
         <is>
@@ -34507,9 +34564,10 @@
           <t>1040 Bayview — BCPA value</t>
         </is>
       </c>
-      <c r="C143" s="73">
-        <f>'Land'!C22</f>
-        <v/>
+      <c r="C143" s="76" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
       </c>
       <c r="D143" s="40" t="inlineStr">
         <is>
@@ -34834,34 +34892,34 @@
           <t>Year</t>
         </is>
       </c>
-      <c r="D11" s="75" t="n">
+      <c r="D11" s="77" t="n">
         <v>1</v>
       </c>
-      <c r="E11" s="75" t="n">
+      <c r="E11" s="77" t="n">
         <v>2</v>
       </c>
-      <c r="F11" s="75" t="n">
+      <c r="F11" s="77" t="n">
         <v>3</v>
       </c>
-      <c r="G11" s="75" t="n">
+      <c r="G11" s="77" t="n">
         <v>4</v>
       </c>
-      <c r="H11" s="75" t="n">
+      <c r="H11" s="77" t="n">
         <v>5</v>
       </c>
-      <c r="I11" s="75" t="n">
+      <c r="I11" s="77" t="n">
         <v>6</v>
       </c>
-      <c r="J11" s="75" t="n">
+      <c r="J11" s="77" t="n">
         <v>7</v>
       </c>
-      <c r="K11" s="75" t="n">
+      <c r="K11" s="77" t="n">
         <v>8</v>
       </c>
-      <c r="L11" s="75" t="n">
+      <c r="L11" s="77" t="n">
         <v>9</v>
       </c>
-      <c r="M11" s="75" t="n">
+      <c r="M11" s="77" t="n">
         <v>10</v>
       </c>
     </row>
@@ -35138,39 +35196,39 @@
         <f>SUM(D14:D17)</f>
         <v/>
       </c>
-      <c r="E18" s="76">
+      <c r="E18" s="78">
         <f>SUM(E14:E17)</f>
         <v/>
       </c>
-      <c r="F18" s="76">
+      <c r="F18" s="78">
         <f>SUM(F14:F17)</f>
         <v/>
       </c>
-      <c r="G18" s="76">
+      <c r="G18" s="78">
         <f>SUM(G14:G17)</f>
         <v/>
       </c>
-      <c r="H18" s="76">
+      <c r="H18" s="78">
         <f>SUM(H14:H17)</f>
         <v/>
       </c>
-      <c r="I18" s="76">
+      <c r="I18" s="78">
         <f>SUM(I14:I17)</f>
         <v/>
       </c>
-      <c r="J18" s="76">
+      <c r="J18" s="78">
         <f>SUM(J14:J17)</f>
         <v/>
       </c>
-      <c r="K18" s="76">
+      <c r="K18" s="78">
         <f>SUM(K14:K17)</f>
         <v/>
       </c>
-      <c r="L18" s="76">
+      <c r="L18" s="78">
         <f>SUM(L14:L17)</f>
         <v/>
       </c>
-      <c r="M18" s="76">
+      <c r="M18" s="78">
         <f>SUM(M14:M17)</f>
         <v/>
       </c>
@@ -35232,39 +35290,39 @@
         <f>D18+D19</f>
         <v/>
       </c>
-      <c r="E20" s="76">
+      <c r="E20" s="78">
         <f>E18+E19</f>
         <v/>
       </c>
-      <c r="F20" s="76">
+      <c r="F20" s="78">
         <f>F18+F19</f>
         <v/>
       </c>
-      <c r="G20" s="76">
+      <c r="G20" s="78">
         <f>G18+G19</f>
         <v/>
       </c>
-      <c r="H20" s="76">
+      <c r="H20" s="78">
         <f>H18+H19</f>
         <v/>
       </c>
-      <c r="I20" s="76">
+      <c r="I20" s="78">
         <f>I18+I19</f>
         <v/>
       </c>
-      <c r="J20" s="76">
+      <c r="J20" s="78">
         <f>J18+J19</f>
         <v/>
       </c>
-      <c r="K20" s="76">
+      <c r="K20" s="78">
         <f>K18+K19</f>
         <v/>
       </c>
-      <c r="L20" s="76">
+      <c r="L20" s="78">
         <f>L18+L19</f>
         <v/>
       </c>
-      <c r="M20" s="76">
+      <c r="M20" s="78">
         <f>M18+M19</f>
         <v/>
       </c>
@@ -35341,7 +35399,7 @@
           <t>Consolidated AS-IS in-place NOI</t>
         </is>
       </c>
-      <c r="C24" s="77">
+      <c r="C24" s="79">
         <f>'Shahidi Retail'!C122+'Publix &amp; Starbucks'!C110+'Sunrise Plaza'!C113+'Office Condo'!C80</f>
         <v/>
       </c>
@@ -35366,7 +35424,7 @@
           <t>Consolidated STABILIZED NOI (lease-up complete)</t>
         </is>
       </c>
-      <c r="C25" s="77">
+      <c r="C25" s="79">
         <f>'Shahidi Retail'!C124+'Publix &amp; Starbucks'!C112+'Sunrise Plaza'!C115+'Office Condo'!C82</f>
         <v/>
       </c>
@@ -35521,7 +35579,7 @@
           <t>Hold period (yrs)</t>
         </is>
       </c>
-      <c r="C33" s="78">
+      <c r="C33" s="80">
         <f>'Assumptions'!C10</f>
         <v/>
       </c>
@@ -35771,7 +35829,7 @@
           <t>Amortization (yrs)</t>
         </is>
       </c>
-      <c r="C43" s="78">
+      <c r="C43" s="80">
         <f>'Assumptions'!C18</f>
         <v/>
       </c>
@@ -36715,11 +36773,11 @@
           <t>Unlevered equity multiple</t>
         </is>
       </c>
-      <c r="C92" s="79">
+      <c r="C92" s="81">
         <f>SUM(D87:M87)/-C87</f>
         <v/>
       </c>
-      <c r="E92" s="79">
+      <c r="E92" s="81">
         <f>SUM(D88:M88)/-C88</f>
         <v/>
       </c>
@@ -36747,11 +36805,11 @@
           <t>Levered equity multiple</t>
         </is>
       </c>
-      <c r="C94" s="79">
+      <c r="C94" s="81">
         <f>SUM(D89:M89)/C85</f>
         <v/>
       </c>
-      <c r="E94" s="79">
+      <c r="E94" s="81">
         <f>SUM(D90:M90)/E85</f>
         <v/>
       </c>
@@ -36763,11 +36821,11 @@
           <t>Year-1 DSCR</t>
         </is>
       </c>
-      <c r="C95" s="79">
+      <c r="C95" s="81">
         <f>C24/(C84*C47)</f>
         <v/>
       </c>
-      <c r="E95" s="79">
+      <c r="E95" s="81">
         <f>C24/(E84*C47)</f>
         <v/>
       </c>
@@ -37254,19 +37312,19 @@
           <t>Cap  ╲  NOI</t>
         </is>
       </c>
-      <c r="D127" s="80" t="n">
+      <c r="D127" s="82" t="n">
         <v>0.9</v>
       </c>
-      <c r="E127" s="80" t="n">
+      <c r="E127" s="82" t="n">
         <v>0.95</v>
       </c>
-      <c r="F127" s="80" t="n">
+      <c r="F127" s="82" t="n">
         <v>1</v>
       </c>
-      <c r="G127" s="80" t="n">
+      <c r="G127" s="82" t="n">
         <v>1.05</v>
       </c>
-      <c r="H127" s="80" t="n">
+      <c r="H127" s="82" t="n">
         <v>1.1</v>
       </c>
     </row>
@@ -37440,23 +37498,23 @@
       <c r="B136" s="70" t="n">
         <v>65000000</v>
       </c>
-      <c r="D136" s="81">
+      <c r="D136" s="83">
         <f>(C49-C33*(MIN(B136*C39,C64,C65)*C47)+(C51*C30/D135)-(MIN(B136*C39,C64,C65)*(1+C46)^(12*C33)-((MIN(B136*C39,C64,C65)*C47)/12)*((1+C46)^(12*C33)-1)/C46))/(B136*(1+C48)-MIN(B136*C39,C64,C65))</f>
         <v/>
       </c>
-      <c r="E136" s="81">
+      <c r="E136" s="83">
         <f>(C49-C33*(MIN(B136*C39,C64,C65)*C47)+(C51*C30/E135)-(MIN(B136*C39,C64,C65)*(1+C46)^(12*C33)-((MIN(B136*C39,C64,C65)*C47)/12)*((1+C46)^(12*C33)-1)/C46))/(B136*(1+C48)-MIN(B136*C39,C64,C65))</f>
         <v/>
       </c>
-      <c r="F136" s="81">
+      <c r="F136" s="83">
         <f>(C49-C33*(MIN(B136*C39,C64,C65)*C47)+(C51*C30/F135)-(MIN(B136*C39,C64,C65)*(1+C46)^(12*C33)-((MIN(B136*C39,C64,C65)*C47)/12)*((1+C46)^(12*C33)-1)/C46))/(B136*(1+C48)-MIN(B136*C39,C64,C65))</f>
         <v/>
       </c>
-      <c r="G136" s="81">
+      <c r="G136" s="83">
         <f>(C49-C33*(MIN(B136*C39,C64,C65)*C47)+(C51*C30/G135)-(MIN(B136*C39,C64,C65)*(1+C46)^(12*C33)-((MIN(B136*C39,C64,C65)*C47)/12)*((1+C46)^(12*C33)-1)/C46))/(B136*(1+C48)-MIN(B136*C39,C64,C65))</f>
         <v/>
       </c>
-      <c r="H136" s="81">
+      <c r="H136" s="83">
         <f>(C49-C33*(MIN(B136*C39,C64,C65)*C47)+(C51*C30/H135)-(MIN(B136*C39,C64,C65)*(1+C46)^(12*C33)-((MIN(B136*C39,C64,C65)*C47)/12)*((1+C46)^(12*C33)-1)/C46))/(B136*(1+C48)-MIN(B136*C39,C64,C65))</f>
         <v/>
       </c>
@@ -37465,23 +37523,23 @@
       <c r="B137" s="70" t="n">
         <v>75000000</v>
       </c>
-      <c r="D137" s="81">
+      <c r="D137" s="83">
         <f>(C49-C33*(MIN(B137*C39,C64,C65)*C47)+(C51*C30/D135)-(MIN(B137*C39,C64,C65)*(1+C46)^(12*C33)-((MIN(B137*C39,C64,C65)*C47)/12)*((1+C46)^(12*C33)-1)/C46))/(B137*(1+C48)-MIN(B137*C39,C64,C65))</f>
         <v/>
       </c>
-      <c r="E137" s="81">
+      <c r="E137" s="83">
         <f>(C49-C33*(MIN(B137*C39,C64,C65)*C47)+(C51*C30/E135)-(MIN(B137*C39,C64,C65)*(1+C46)^(12*C33)-((MIN(B137*C39,C64,C65)*C47)/12)*((1+C46)^(12*C33)-1)/C46))/(B137*(1+C48)-MIN(B137*C39,C64,C65))</f>
         <v/>
       </c>
-      <c r="F137" s="81">
+      <c r="F137" s="83">
         <f>(C49-C33*(MIN(B137*C39,C64,C65)*C47)+(C51*C30/F135)-(MIN(B137*C39,C64,C65)*(1+C46)^(12*C33)-((MIN(B137*C39,C64,C65)*C47)/12)*((1+C46)^(12*C33)-1)/C46))/(B137*(1+C48)-MIN(B137*C39,C64,C65))</f>
         <v/>
       </c>
-      <c r="G137" s="81">
+      <c r="G137" s="83">
         <f>(C49-C33*(MIN(B137*C39,C64,C65)*C47)+(C51*C30/G135)-(MIN(B137*C39,C64,C65)*(1+C46)^(12*C33)-((MIN(B137*C39,C64,C65)*C47)/12)*((1+C46)^(12*C33)-1)/C46))/(B137*(1+C48)-MIN(B137*C39,C64,C65))</f>
         <v/>
       </c>
-      <c r="H137" s="81">
+      <c r="H137" s="83">
         <f>(C49-C33*(MIN(B137*C39,C64,C65)*C47)+(C51*C30/H135)-(MIN(B137*C39,C64,C65)*(1+C46)^(12*C33)-((MIN(B137*C39,C64,C65)*C47)/12)*((1+C46)^(12*C33)-1)/C46))/(B137*(1+C48)-MIN(B137*C39,C64,C65))</f>
         <v/>
       </c>
@@ -37490,23 +37548,23 @@
       <c r="B138" s="70" t="n">
         <v>85000000</v>
       </c>
-      <c r="D138" s="81">
+      <c r="D138" s="83">
         <f>(C49-C33*(MIN(B138*C39,C64,C65)*C47)+(C51*C30/D135)-(MIN(B138*C39,C64,C65)*(1+C46)^(12*C33)-((MIN(B138*C39,C64,C65)*C47)/12)*((1+C46)^(12*C33)-1)/C46))/(B138*(1+C48)-MIN(B138*C39,C64,C65))</f>
         <v/>
       </c>
-      <c r="E138" s="81">
+      <c r="E138" s="83">
         <f>(C49-C33*(MIN(B138*C39,C64,C65)*C47)+(C51*C30/E135)-(MIN(B138*C39,C64,C65)*(1+C46)^(12*C33)-((MIN(B138*C39,C64,C65)*C47)/12)*((1+C46)^(12*C33)-1)/C46))/(B138*(1+C48)-MIN(B138*C39,C64,C65))</f>
         <v/>
       </c>
-      <c r="F138" s="81">
+      <c r="F138" s="83">
         <f>(C49-C33*(MIN(B138*C39,C64,C65)*C47)+(C51*C30/F135)-(MIN(B138*C39,C64,C65)*(1+C46)^(12*C33)-((MIN(B138*C39,C64,C65)*C47)/12)*((1+C46)^(12*C33)-1)/C46))/(B138*(1+C48)-MIN(B138*C39,C64,C65))</f>
         <v/>
       </c>
-      <c r="G138" s="81">
+      <c r="G138" s="83">
         <f>(C49-C33*(MIN(B138*C39,C64,C65)*C47)+(C51*C30/G135)-(MIN(B138*C39,C64,C65)*(1+C46)^(12*C33)-((MIN(B138*C39,C64,C65)*C47)/12)*((1+C46)^(12*C33)-1)/C46))/(B138*(1+C48)-MIN(B138*C39,C64,C65))</f>
         <v/>
       </c>
-      <c r="H138" s="81">
+      <c r="H138" s="83">
         <f>(C49-C33*(MIN(B138*C39,C64,C65)*C47)+(C51*C30/H135)-(MIN(B138*C39,C64,C65)*(1+C46)^(12*C33)-((MIN(B138*C39,C64,C65)*C47)/12)*((1+C46)^(12*C33)-1)/C46))/(B138*(1+C48)-MIN(B138*C39,C64,C65))</f>
         <v/>
       </c>
@@ -37515,23 +37573,23 @@
       <c r="B139" s="70" t="n">
         <v>95000000</v>
       </c>
-      <c r="D139" s="81">
+      <c r="D139" s="83">
         <f>(C49-C33*(MIN(B139*C39,C64,C65)*C47)+(C51*C30/D135)-(MIN(B139*C39,C64,C65)*(1+C46)^(12*C33)-((MIN(B139*C39,C64,C65)*C47)/12)*((1+C46)^(12*C33)-1)/C46))/(B139*(1+C48)-MIN(B139*C39,C64,C65))</f>
         <v/>
       </c>
-      <c r="E139" s="81">
+      <c r="E139" s="83">
         <f>(C49-C33*(MIN(B139*C39,C64,C65)*C47)+(C51*C30/E135)-(MIN(B139*C39,C64,C65)*(1+C46)^(12*C33)-((MIN(B139*C39,C64,C65)*C47)/12)*((1+C46)^(12*C33)-1)/C46))/(B139*(1+C48)-MIN(B139*C39,C64,C65))</f>
         <v/>
       </c>
-      <c r="F139" s="81">
+      <c r="F139" s="83">
         <f>(C49-C33*(MIN(B139*C39,C64,C65)*C47)+(C51*C30/F135)-(MIN(B139*C39,C64,C65)*(1+C46)^(12*C33)-((MIN(B139*C39,C64,C65)*C47)/12)*((1+C46)^(12*C33)-1)/C46))/(B139*(1+C48)-MIN(B139*C39,C64,C65))</f>
         <v/>
       </c>
-      <c r="G139" s="81">
+      <c r="G139" s="83">
         <f>(C49-C33*(MIN(B139*C39,C64,C65)*C47)+(C51*C30/G135)-(MIN(B139*C39,C64,C65)*(1+C46)^(12*C33)-((MIN(B139*C39,C64,C65)*C47)/12)*((1+C46)^(12*C33)-1)/C46))/(B139*(1+C48)-MIN(B139*C39,C64,C65))</f>
         <v/>
       </c>
-      <c r="H139" s="81">
+      <c r="H139" s="83">
         <f>(C49-C33*(MIN(B139*C39,C64,C65)*C47)+(C51*C30/H135)-(MIN(B139*C39,C64,C65)*(1+C46)^(12*C33)-((MIN(B139*C39,C64,C65)*C47)/12)*((1+C46)^(12*C33)-1)/C46))/(B139*(1+C48)-MIN(B139*C39,C64,C65))</f>
         <v/>
       </c>
@@ -37540,23 +37598,23 @@
       <c r="B140" s="70" t="n">
         <v>102000000</v>
       </c>
-      <c r="D140" s="81">
+      <c r="D140" s="83">
         <f>(C49-C33*(MIN(B140*C39,C64,C65)*C47)+(C51*C30/D135)-(MIN(B140*C39,C64,C65)*(1+C46)^(12*C33)-((MIN(B140*C39,C64,C65)*C47)/12)*((1+C46)^(12*C33)-1)/C46))/(B140*(1+C48)-MIN(B140*C39,C64,C65))</f>
         <v/>
       </c>
-      <c r="E140" s="81">
+      <c r="E140" s="83">
         <f>(C49-C33*(MIN(B140*C39,C64,C65)*C47)+(C51*C30/E135)-(MIN(B140*C39,C64,C65)*(1+C46)^(12*C33)-((MIN(B140*C39,C64,C65)*C47)/12)*((1+C46)^(12*C33)-1)/C46))/(B140*(1+C48)-MIN(B140*C39,C64,C65))</f>
         <v/>
       </c>
-      <c r="F140" s="81">
+      <c r="F140" s="83">
         <f>(C49-C33*(MIN(B140*C39,C64,C65)*C47)+(C51*C30/F135)-(MIN(B140*C39,C64,C65)*(1+C46)^(12*C33)-((MIN(B140*C39,C64,C65)*C47)/12)*((1+C46)^(12*C33)-1)/C46))/(B140*(1+C48)-MIN(B140*C39,C64,C65))</f>
         <v/>
       </c>
-      <c r="G140" s="81">
+      <c r="G140" s="83">
         <f>(C49-C33*(MIN(B140*C39,C64,C65)*C47)+(C51*C30/G135)-(MIN(B140*C39,C64,C65)*(1+C46)^(12*C33)-((MIN(B140*C39,C64,C65)*C47)/12)*((1+C46)^(12*C33)-1)/C46))/(B140*(1+C48)-MIN(B140*C39,C64,C65))</f>
         <v/>
       </c>
-      <c r="H140" s="81">
+      <c r="H140" s="83">
         <f>(C49-C33*(MIN(B140*C39,C64,C65)*C47)+(C51*C30/H135)-(MIN(B140*C39,C64,C65)*(1+C46)^(12*C33)-((MIN(B140*C39,C64,C65)*C47)/12)*((1+C46)^(12*C33)-1)/C46))/(B140*(1+C48)-MIN(B140*C39,C64,C65))</f>
         <v/>
       </c>
@@ -37795,7 +37853,7 @@
           <t>Downside</t>
         </is>
       </c>
-      <c r="C6" s="80" t="n">
+      <c r="C6" s="82" t="n">
         <v>0.92</v>
       </c>
       <c r="D6" s="66" t="n">
@@ -37811,7 +37869,7 @@
           <t>Base</t>
         </is>
       </c>
-      <c r="C7" s="80" t="n">
+      <c r="C7" s="82" t="n">
         <v>1</v>
       </c>
       <c r="D7" s="66" t="n">
@@ -37827,7 +37885,7 @@
           <t>Upside</t>
         </is>
       </c>
-      <c r="C8" s="80" t="n">
+      <c r="C8" s="82" t="n">
         <v>1.06</v>
       </c>
       <c r="D8" s="66" t="n">
@@ -37891,34 +37949,34 @@
           <t>0/Acq</t>
         </is>
       </c>
-      <c r="D12" s="75" t="n">
+      <c r="D12" s="77" t="n">
         <v>1</v>
       </c>
-      <c r="E12" s="75" t="n">
+      <c r="E12" s="77" t="n">
         <v>2</v>
       </c>
-      <c r="F12" s="75" t="n">
+      <c r="F12" s="77" t="n">
         <v>3</v>
       </c>
-      <c r="G12" s="75" t="n">
+      <c r="G12" s="77" t="n">
         <v>4</v>
       </c>
-      <c r="H12" s="75" t="n">
+      <c r="H12" s="77" t="n">
         <v>5</v>
       </c>
-      <c r="I12" s="75" t="n">
+      <c r="I12" s="77" t="n">
         <v>6</v>
       </c>
-      <c r="J12" s="75" t="n">
+      <c r="J12" s="77" t="n">
         <v>7</v>
       </c>
-      <c r="K12" s="75" t="n">
+      <c r="K12" s="77" t="n">
         <v>8</v>
       </c>
-      <c r="L12" s="75" t="n">
+      <c r="L12" s="77" t="n">
         <v>9</v>
       </c>
-      <c r="M12" s="75" t="n">
+      <c r="M12" s="77" t="n">
         <v>10</v>
       </c>
     </row>
@@ -38296,23 +38354,23 @@
         <v/>
       </c>
       <c r="E22" s="9" t="n"/>
-      <c r="F22" s="82">
+      <c r="F22" s="84">
         <f>IRR(C13:M13)</f>
         <v/>
       </c>
-      <c r="G22" s="82">
+      <c r="G22" s="84">
         <f>IRR(C14:M14)</f>
         <v/>
       </c>
-      <c r="H22" s="81">
+      <c r="H22" s="83">
         <f>SUM(D14:M14)/('Income Valuation'!C60*(1+'Income Valuation'!C48)+'Income Valuation'!C38*'Income Valuation'!C66-'Income Valuation'!C66)</f>
         <v/>
       </c>
-      <c r="I22" s="81">
+      <c r="I22" s="83">
         <f>'Income Valuation'!C24*C6/('Income Valuation'!C66*((E6/12)/(1-(1+(E6/12))^(-'Income Valuation'!C43*12))*12))</f>
         <v/>
       </c>
-      <c r="J22" s="82">
+      <c r="J22" s="84">
         <f>('Income Valuation'!C49*C6-'Income Valuation'!C33*('Income Valuation'!C66*((E6/12)/(1-(1+(E6/12))^(-'Income Valuation'!C43*12))*12)))/'Income Valuation'!C33/('Income Valuation'!C60*(1+'Income Valuation'!C48)+'Income Valuation'!C38*'Income Valuation'!C66-'Income Valuation'!C66)</f>
         <v/>
       </c>
@@ -38326,7 +38384,7 @@
           <t>Base</t>
         </is>
       </c>
-      <c r="D23" s="83">
+      <c r="D23" s="85">
         <f>'Income Valuation'!C24*C7/'Income Valuation'!C29</f>
         <v/>
       </c>
@@ -38339,11 +38397,11 @@
         <f>IRR(C16:M16)</f>
         <v/>
       </c>
-      <c r="H23" s="84">
+      <c r="H23" s="86">
         <f>SUM(D16:M16)/('Income Valuation'!C60*(1+'Income Valuation'!C48)+'Income Valuation'!C38*'Income Valuation'!C66-'Income Valuation'!C66)</f>
         <v/>
       </c>
-      <c r="I23" s="84">
+      <c r="I23" s="86">
         <f>'Income Valuation'!C24*C7/('Income Valuation'!C66*((E7/12)/(1-(1+(E7/12))^(-'Income Valuation'!C43*12))*12))</f>
         <v/>
       </c>
@@ -38366,23 +38424,23 @@
         <v/>
       </c>
       <c r="E24" s="9" t="n"/>
-      <c r="F24" s="82">
+      <c r="F24" s="84">
         <f>IRR(C17:M17)</f>
         <v/>
       </c>
-      <c r="G24" s="82">
+      <c r="G24" s="84">
         <f>IRR(C18:M18)</f>
         <v/>
       </c>
-      <c r="H24" s="81">
+      <c r="H24" s="83">
         <f>SUM(D18:M18)/('Income Valuation'!C60*(1+'Income Valuation'!C48)+'Income Valuation'!C38*'Income Valuation'!C66-'Income Valuation'!C66)</f>
         <v/>
       </c>
-      <c r="I24" s="81">
+      <c r="I24" s="83">
         <f>'Income Valuation'!C24*C8/('Income Valuation'!C66*((E8/12)/(1-(1+(E8/12))^(-'Income Valuation'!C43*12))*12))</f>
         <v/>
       </c>
-      <c r="J24" s="82">
+      <c r="J24" s="84">
         <f>('Income Valuation'!C49*C8-'Income Valuation'!C33*('Income Valuation'!C66*((E8/12)/(1-(1+(E8/12))^(-'Income Valuation'!C43*12))*12)))/'Income Valuation'!C33/('Income Valuation'!C60*(1+'Income Valuation'!C48)+'Income Valuation'!C38*'Income Valuation'!C66-'Income Valuation'!C66)</f>
         <v/>
       </c>
@@ -38686,7 +38744,7 @@
         <f>D12/C12</f>
         <v/>
       </c>
-      <c r="F12" s="85">
+      <c r="F12" s="87">
         <f>'Shahidi Retail'!C36</f>
         <v/>
       </c>
@@ -38729,7 +38787,7 @@
         <f>D13/C13</f>
         <v/>
       </c>
-      <c r="F13" s="85">
+      <c r="F13" s="87">
         <f>'Publix &amp; Starbucks'!C25</f>
         <v/>
       </c>
@@ -38772,7 +38830,7 @@
         <f>D14/C14</f>
         <v/>
       </c>
-      <c r="F14" s="85">
+      <c r="F14" s="87">
         <f>'Sunrise Plaza'!C28</f>
         <v/>
       </c>
@@ -38853,11 +38911,11 @@
         <f>SUM(D12:D15)</f>
         <v/>
       </c>
-      <c r="E16" s="86">
+      <c r="E16" s="88">
         <f>D16/C16</f>
         <v/>
       </c>
-      <c r="F16" s="87">
+      <c r="F16" s="89">
         <f>SUM(F12:F15)</f>
         <v/>
       </c>
@@ -39118,7 +39176,7 @@
         </is>
       </c>
       <c r="C31" s="20">
-        <f>'Land'!C82</f>
+        <f>'Bayview JV'!C82</f>
         <v/>
       </c>
     </row>
